--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3684" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3690" uniqueCount="642">
   <si>
     <t>trade_time</t>
   </si>
@@ -952,6 +952,9 @@
     <t>2021-07-16</t>
   </si>
   <si>
+    <t>2021-07-21</t>
+  </si>
+  <si>
     <t>2021-07-29</t>
   </si>
   <si>
@@ -962,9 +965,6 @@
   </si>
   <si>
     <t>2021-07-05</t>
-  </si>
-  <si>
-    <t>2021-07-21</t>
   </si>
   <si>
     <t>2021-07-30</t>
@@ -2297,7 +2297,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1224"/>
+  <dimension ref="A1:P1226"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -58355,7 +58355,7 @@
         <v>312</v>
       </c>
       <c r="C1122">
-        <v>6.859204597177963</v>
+        <v>6.814421939007731</v>
       </c>
       <c r="D1122" t="s">
         <v>308</v>
@@ -58367,22 +58367,22 @@
         <v>1</v>
       </c>
       <c r="G1122">
-        <v>0.007660795402822037</v>
+        <v>0.00766557806099227</v>
       </c>
       <c r="H1122">
         <v>0.007888486572599007</v>
       </c>
       <c r="I1122">
-        <v>0.2123088302230318</v>
+        <v>0.2570914883932636</v>
       </c>
       <c r="J1122">
         <v>0.08545744196631905</v>
       </c>
       <c r="K1122">
-        <v>4.69</v>
+        <v>4.98</v>
       </c>
       <c r="L1122">
-        <v>7.26</v>
+        <v>7.24</v>
       </c>
       <c r="M1122">
         <v>4.78</v>
@@ -58402,43 +58402,43 @@
         <v>4</v>
       </c>
       <c r="B1123" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="C1123">
-        <v>7.208095129722342</v>
+        <v>6.859204597177963</v>
       </c>
       <c r="D1123" t="s">
-        <v>497</v>
+        <v>308</v>
       </c>
       <c r="E1123">
-        <v>6.896385980883015</v>
+        <v>7.071513427400995</v>
       </c>
       <c r="F1123">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1123">
-        <v>0.008031904870277658</v>
+        <v>0.007660795402822037</v>
       </c>
       <c r="H1123">
-        <v>0.007723614019116984</v>
+        <v>0.007888486572599007</v>
       </c>
       <c r="I1123">
-        <v>0.3117091488393271</v>
+        <v>0.2123088302230318</v>
       </c>
       <c r="J1123">
         <v>0.08545744196631905</v>
       </c>
       <c r="K1123">
-        <v>4.82</v>
+        <v>4.69</v>
       </c>
       <c r="L1123">
-        <v>7.62</v>
+        <v>7.26</v>
       </c>
       <c r="M1123">
-        <v>4.84</v>
+        <v>4.78</v>
       </c>
       <c r="N1123">
-        <v>7.31</v>
+        <v>7.48</v>
       </c>
       <c r="O1123">
         <v>1</v>
@@ -58449,96 +58449,96 @@
     </row>
     <row r="1124" spans="1:16">
       <c r="A1124" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1124" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="C1124">
-        <v>7.041349143640623</v>
+        <v>7.208095129722342</v>
       </c>
       <c r="D1124" t="s">
-        <v>300</v>
+        <v>497</v>
       </c>
       <c r="E1124">
-        <v>6.882360158955165</v>
+        <v>6.896385980883015</v>
       </c>
       <c r="F1124">
         <v>-1</v>
       </c>
       <c r="G1124">
-        <v>0.008078650856359375</v>
+        <v>0.008031904870277658</v>
       </c>
       <c r="H1124">
-        <v>0.007917639841044837</v>
+        <v>0.007723614019116984</v>
       </c>
       <c r="I1124">
-        <v>0.1589889846854584</v>
+        <v>0.3117091488393271</v>
       </c>
       <c r="J1124">
-        <v>0.1011015314540694</v>
+        <v>0.08545744196631905</v>
       </c>
       <c r="K1124">
-        <v>5.13</v>
+        <v>4.82</v>
       </c>
       <c r="L1124">
-        <v>7.56</v>
+        <v>7.62</v>
       </c>
       <c r="M1124">
-        <v>5.12</v>
+        <v>4.84</v>
       </c>
       <c r="N1124">
-        <v>7.4</v>
+        <v>7.31</v>
       </c>
       <c r="O1124">
         <v>1</v>
       </c>
       <c r="P1124" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="1125" spans="1:16">
       <c r="A1125" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1125" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="C1125">
-        <v>6.78145929678603</v>
+        <v>7.041349143640623</v>
       </c>
       <c r="D1125" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="E1125">
-        <v>6.996734679649548</v>
+        <v>6.882360158955165</v>
       </c>
       <c r="F1125">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1125">
-        <v>0.00779854070321397</v>
+        <v>0.008078650856359375</v>
       </c>
       <c r="H1125">
-        <v>0.007963265320350453</v>
+        <v>0.007917639841044837</v>
       </c>
       <c r="I1125">
-        <v>0.2152753828635179</v>
+        <v>0.1589889846854584</v>
       </c>
       <c r="J1125">
         <v>0.1011015314540694</v>
       </c>
       <c r="K1125">
-        <v>5.03</v>
+        <v>5.13</v>
       </c>
       <c r="L1125">
-        <v>7.29</v>
+        <v>7.56</v>
       </c>
       <c r="M1125">
-        <v>4.78</v>
+        <v>5.12</v>
       </c>
       <c r="N1125">
-        <v>7.48</v>
+        <v>7.4</v>
       </c>
       <c r="O1125">
         <v>1</v>
@@ -58549,10 +58549,10 @@
     </row>
     <row r="1126" spans="1:16">
       <c r="A1126" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1126" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C1126">
         <v>6.78145929678603</v>
@@ -58599,10 +58599,10 @@
     </row>
     <row r="1127" spans="1:16">
       <c r="A1127" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1127" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C1127">
         <v>6.78145929678603</v>
@@ -58649,13 +58649,13 @@
     </row>
     <row r="1128" spans="1:16">
       <c r="A1128" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1128" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C1128">
-        <v>6.785833817480414</v>
+        <v>6.78145929678603</v>
       </c>
       <c r="D1128" t="s">
         <v>308</v>
@@ -58667,22 +58667,22 @@
         <v>1</v>
       </c>
       <c r="G1128">
-        <v>0.007734166182519585</v>
+        <v>0.00779854070321397</v>
       </c>
       <c r="H1128">
         <v>0.007963265320350453</v>
       </c>
       <c r="I1128">
-        <v>0.210900862169134</v>
+        <v>0.2152753828635179</v>
       </c>
       <c r="J1128">
         <v>0.1011015314540694</v>
       </c>
       <c r="K1128">
-        <v>4.69</v>
+        <v>5.03</v>
       </c>
       <c r="L1128">
-        <v>7.26</v>
+        <v>7.29</v>
       </c>
       <c r="M1128">
         <v>4.78</v>
@@ -58699,7 +58699,7 @@
     </row>
     <row r="1129" spans="1:16">
       <c r="A1129" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1129" t="s">
         <v>304</v>
@@ -58752,7 +58752,7 @@
         <v>0</v>
       </c>
       <c r="B1130" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C1130">
         <v>6.986421414106984</v>
@@ -59002,43 +59002,43 @@
         <v>0</v>
       </c>
       <c r="B1135" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C1135">
-        <v>7.014123139679393</v>
+        <v>6.754764014149581</v>
       </c>
       <c r="D1135" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="E1135">
-        <v>6.855187227126413</v>
+        <v>6.97136620032505</v>
       </c>
       <c r="F1135">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1135">
-        <v>0.008105876860320606</v>
+        <v>0.00782523598585042</v>
       </c>
       <c r="H1135">
-        <v>0.007944812772873589</v>
+        <v>0.007988633799674951</v>
       </c>
       <c r="I1135">
-        <v>0.1589359125529803</v>
+        <v>0.2166021861754688</v>
       </c>
       <c r="J1135">
         <v>0.1064087447018726</v>
       </c>
       <c r="K1135">
-        <v>5.13</v>
+        <v>5.03</v>
       </c>
       <c r="L1135">
-        <v>7.56</v>
+        <v>7.29</v>
       </c>
       <c r="M1135">
-        <v>5.12</v>
+        <v>4.78</v>
       </c>
       <c r="N1135">
-        <v>7.4</v>
+        <v>7.48</v>
       </c>
       <c r="O1135">
         <v>1</v>
@@ -59052,7 +59052,7 @@
         <v>1</v>
       </c>
       <c r="B1136" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C1136">
         <v>6.754764014149581</v>
@@ -59102,7 +59102,7 @@
         <v>2</v>
       </c>
       <c r="B1137" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C1137">
         <v>6.754764014149581</v>
@@ -59152,10 +59152,10 @@
         <v>3</v>
       </c>
       <c r="B1138" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C1138">
-        <v>6.754764014149581</v>
+        <v>6.710084451384675</v>
       </c>
       <c r="D1138" t="s">
         <v>308</v>
@@ -59167,22 +59167,22 @@
         <v>1</v>
       </c>
       <c r="G1138">
-        <v>0.00782523598585042</v>
+        <v>0.007769915548615326</v>
       </c>
       <c r="H1138">
         <v>0.007988633799674951</v>
       </c>
       <c r="I1138">
-        <v>0.2166021861754688</v>
+        <v>0.2612817489403749</v>
       </c>
       <c r="J1138">
         <v>0.1064087447018726</v>
       </c>
       <c r="K1138">
-        <v>5.03</v>
+        <v>4.98</v>
       </c>
       <c r="L1138">
-        <v>7.29</v>
+        <v>7.24</v>
       </c>
       <c r="M1138">
         <v>4.78</v>
@@ -59405,7 +59405,7 @@
         <v>312</v>
       </c>
       <c r="C1143">
-        <v>6.806344852974999</v>
+        <v>6.758293681836994</v>
       </c>
       <c r="D1143" t="s">
         <v>308</v>
@@ -59417,22 +59417,22 @@
         <v>1</v>
       </c>
       <c r="G1143">
-        <v>0.007713655147025</v>
+        <v>0.007721706318163006</v>
       </c>
       <c r="H1143">
         <v>0.007942360682895416</v>
       </c>
       <c r="I1143">
-        <v>0.2112944641295851</v>
+        <v>0.2593456352675902</v>
       </c>
       <c r="J1143">
         <v>0.09672817633795312</v>
       </c>
       <c r="K1143">
-        <v>4.69</v>
+        <v>4.98</v>
       </c>
       <c r="L1143">
-        <v>7.26</v>
+        <v>7.24</v>
       </c>
       <c r="M1143">
         <v>4.78</v>
@@ -59502,7 +59502,7 @@
         <v>0</v>
       </c>
       <c r="B1145" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C1145">
         <v>6.038657471720564</v>
@@ -59552,7 +59552,7 @@
         <v>1</v>
       </c>
       <c r="B1146" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C1146">
         <v>5.825747172057932</v>
@@ -59802,7 +59802,7 @@
         <v>0</v>
       </c>
       <c r="B1151" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C1151">
         <v>6.063408640507315</v>
@@ -59852,16 +59852,16 @@
         <v>1</v>
       </c>
       <c r="B1152" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C1152">
         <v>5.850546967895346</v>
       </c>
       <c r="D1152" t="s">
-        <v>318</v>
+        <v>500</v>
       </c>
       <c r="E1152">
-        <v>5.957907253269902</v>
+        <v>5.951993658343225</v>
       </c>
       <c r="F1152">
         <v>1</v>
@@ -59870,10 +59870,10 @@
         <v>0.008769453032104654</v>
       </c>
       <c r="H1152">
-        <v>0.008602092746730098</v>
+        <v>0.008848006341656776</v>
       </c>
       <c r="I1152">
-        <v>0.1073602853745559</v>
+        <v>0.1014466904478795</v>
       </c>
       <c r="J1152">
         <v>0.2861672611969911</v>
@@ -59885,10 +59885,10 @@
         <v>7.31</v>
       </c>
       <c r="M1152">
-        <v>4.62</v>
+        <v>5.06</v>
       </c>
       <c r="N1152">
-        <v>7.28</v>
+        <v>7.4</v>
       </c>
       <c r="O1152">
         <v>1</v>
@@ -59908,10 +59908,10 @@
         <v>5.850578676179135</v>
       </c>
       <c r="D1153" t="s">
-        <v>318</v>
+        <v>500</v>
       </c>
       <c r="E1153">
-        <v>5.957907253269902</v>
+        <v>5.951993658343225</v>
       </c>
       <c r="F1153">
         <v>1</v>
@@ -59920,10 +59920,10 @@
         <v>0.008729421323820865</v>
       </c>
       <c r="H1153">
-        <v>0.008602092746730098</v>
+        <v>0.008848006341656776</v>
       </c>
       <c r="I1153">
-        <v>0.107328577090767</v>
+        <v>0.1014149821640906</v>
       </c>
       <c r="J1153">
         <v>0.2861672611969911</v>
@@ -59935,10 +59935,10 @@
         <v>7.29</v>
       </c>
       <c r="M1153">
-        <v>4.62</v>
+        <v>5.06</v>
       </c>
       <c r="N1153">
-        <v>7.28</v>
+        <v>7.4</v>
       </c>
       <c r="O1153">
         <v>1</v>
@@ -59958,10 +59958,10 @@
         <v>5.850578676179135</v>
       </c>
       <c r="D1154" t="s">
-        <v>318</v>
+        <v>500</v>
       </c>
       <c r="E1154">
-        <v>5.957907253269902</v>
+        <v>5.951993658343225</v>
       </c>
       <c r="F1154">
         <v>1</v>
@@ -59970,10 +59970,10 @@
         <v>0.008729421323820865</v>
       </c>
       <c r="H1154">
-        <v>0.008602092746730098</v>
+        <v>0.008848006341656776</v>
       </c>
       <c r="I1154">
-        <v>0.107328577090767</v>
+        <v>0.1014149821640906</v>
       </c>
       <c r="J1154">
         <v>0.2861672611969911</v>
@@ -59985,10 +59985,10 @@
         <v>7.29</v>
       </c>
       <c r="M1154">
-        <v>4.62</v>
+        <v>5.06</v>
       </c>
       <c r="N1154">
-        <v>7.28</v>
+        <v>7.4</v>
       </c>
       <c r="O1154">
         <v>1</v>
@@ -60008,10 +60008,10 @@
         <v>5.850578676179135</v>
       </c>
       <c r="D1155" t="s">
-        <v>318</v>
+        <v>500</v>
       </c>
       <c r="E1155">
-        <v>5.957907253269902</v>
+        <v>5.951993658343225</v>
       </c>
       <c r="F1155">
         <v>1</v>
@@ -60020,10 +60020,10 @@
         <v>0.008729421323820865</v>
       </c>
       <c r="H1155">
-        <v>0.008602092746730098</v>
+        <v>0.008848006341656776</v>
       </c>
       <c r="I1155">
-        <v>0.107328577090767</v>
+        <v>0.1014149821640906</v>
       </c>
       <c r="J1155">
         <v>0.2861672611969911</v>
@@ -60035,10 +60035,10 @@
         <v>7.29</v>
       </c>
       <c r="M1155">
-        <v>4.62</v>
+        <v>5.06</v>
       </c>
       <c r="N1155">
-        <v>7.28</v>
+        <v>7.4</v>
       </c>
       <c r="O1155">
         <v>1</v>
@@ -60102,7 +60102,7 @@
         <v>0</v>
       </c>
       <c r="B1157" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C1157">
         <v>6.042400346620433</v>
@@ -60152,7 +60152,7 @@
         <v>1</v>
       </c>
       <c r="B1158" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C1158">
         <v>5.829497400346602</v>
@@ -60402,7 +60402,7 @@
         <v>0</v>
       </c>
       <c r="B1163" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C1163">
         <v>5.35524754596201</v>
@@ -60452,7 +60452,7 @@
         <v>1</v>
       </c>
       <c r="B1164" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C1164">
         <v>5.140994594185903</v>
@@ -60652,7 +60652,7 @@
         <v>5</v>
       </c>
       <c r="B1168" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C1168">
         <v>5.122030015499177</v>
@@ -60752,7 +60752,7 @@
         <v>0</v>
       </c>
       <c r="B1170" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C1170">
         <v>4.869243033976865</v>
@@ -60952,7 +60952,7 @@
         <v>4</v>
       </c>
       <c r="B1174" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C1174">
         <v>4.856672609647998</v>
@@ -61052,7 +61052,7 @@
         <v>0</v>
       </c>
       <c r="B1176" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C1176">
         <v>4.646081578409318</v>
@@ -61252,7 +61252,7 @@
         <v>4</v>
       </c>
       <c r="B1180" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C1180">
         <v>4.63876201185851</v>
@@ -61402,7 +61402,7 @@
         <v>0</v>
       </c>
       <c r="B1183" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C1183">
         <v>4.194367974425276</v>
@@ -61602,7 +61602,7 @@
         <v>4</v>
       </c>
       <c r="B1187" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C1187">
         <v>4.197676963262328</v>
@@ -61752,7 +61752,7 @@
         <v>0</v>
       </c>
       <c r="B1190" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C1190">
         <v>4.579720961796916</v>
@@ -61802,10 +61802,10 @@
         <v>1</v>
       </c>
       <c r="B1191" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="C1191">
-        <v>4.553255844898938</v>
+        <v>4.597195379968332</v>
       </c>
       <c r="D1191" t="s">
         <v>496</v>
@@ -61817,22 +61817,22 @@
         <v>1</v>
       </c>
       <c r="G1191">
-        <v>0.009906744155101063</v>
+        <v>0.009982804620031668</v>
       </c>
       <c r="H1191">
         <v>0.009786139505794999</v>
       </c>
       <c r="I1191">
-        <v>0.2006046493060625</v>
+        <v>0.1566651142366693</v>
       </c>
       <c r="J1191">
         <v>0.5353488310202125</v>
       </c>
       <c r="K1191">
-        <v>5</v>
+        <v>5.03</v>
       </c>
       <c r="L1191">
-        <v>7.23</v>
+        <v>7.29</v>
       </c>
       <c r="M1191">
         <v>4.7</v>
@@ -61852,10 +61852,10 @@
         <v>2</v>
       </c>
       <c r="B1192" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="C1192">
-        <v>4.573962821519341</v>
+        <v>4.597195379968332</v>
       </c>
       <c r="D1192" t="s">
         <v>496</v>
@@ -61867,22 +61867,22 @@
         <v>1</v>
       </c>
       <c r="G1192">
-        <v>0.009906037178480659</v>
+        <v>0.009982804620031668</v>
       </c>
       <c r="H1192">
         <v>0.009786139505794999</v>
       </c>
       <c r="I1192">
-        <v>0.1798976726856596</v>
+        <v>0.1566651142366693</v>
       </c>
       <c r="J1192">
         <v>0.5353488310202125</v>
       </c>
       <c r="K1192">
-        <v>4.98</v>
+        <v>5.03</v>
       </c>
       <c r="L1192">
-        <v>7.24</v>
+        <v>7.29</v>
       </c>
       <c r="M1192">
         <v>4.7</v>
@@ -61902,43 +61902,43 @@
         <v>3</v>
       </c>
       <c r="B1193" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="C1193">
-        <v>4.806688400686618</v>
+        <v>4.597195379968332</v>
       </c>
       <c r="D1193" t="s">
-        <v>304</v>
+        <v>496</v>
       </c>
       <c r="E1193">
-        <v>5.039618634482576</v>
+        <v>4.753860494205001</v>
       </c>
       <c r="F1193">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1193">
-        <v>0.009753311599313381</v>
+        <v>0.009982804620031668</v>
       </c>
       <c r="H1193">
-        <v>0.01020038136551743</v>
+        <v>0.009786139505794999</v>
       </c>
       <c r="I1193">
-        <v>-0.2329302337959573</v>
+        <v>0.1566651142366693</v>
       </c>
       <c r="J1193">
         <v>0.5353488310202125</v>
       </c>
       <c r="K1193">
-        <v>4.62</v>
+        <v>5.03</v>
       </c>
       <c r="L1193">
-        <v>7.28</v>
+        <v>7.29</v>
       </c>
       <c r="M1193">
-        <v>4.82</v>
+        <v>4.7</v>
       </c>
       <c r="N1193">
-        <v>7.62</v>
+        <v>7.27</v>
       </c>
       <c r="O1193">
         <v>1</v>
@@ -61952,43 +61952,43 @@
         <v>4</v>
       </c>
       <c r="B1194" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C1194">
-        <v>4.823153517584597</v>
+        <v>4.573962821519341</v>
       </c>
       <c r="D1194" t="s">
-        <v>304</v>
+        <v>496</v>
       </c>
       <c r="E1194">
-        <v>5.039618634482576</v>
+        <v>4.753860494205001</v>
       </c>
       <c r="F1194">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1194">
-        <v>0.009876846482415403</v>
+        <v>0.009906037178480659</v>
       </c>
       <c r="H1194">
-        <v>0.01020038136551743</v>
+        <v>0.009786139505794999</v>
       </c>
       <c r="I1194">
-        <v>-0.2164651168979788</v>
+        <v>0.1798976726856596</v>
       </c>
       <c r="J1194">
         <v>0.5353488310202125</v>
       </c>
       <c r="K1194">
-        <v>4.72</v>
+        <v>4.98</v>
       </c>
       <c r="L1194">
-        <v>7.35</v>
+        <v>7.24</v>
       </c>
       <c r="M1194">
-        <v>4.82</v>
+        <v>4.7</v>
       </c>
       <c r="N1194">
-        <v>7.62</v>
+        <v>7.27</v>
       </c>
       <c r="O1194">
         <v>1</v>
@@ -61999,113 +61999,113 @@
     </row>
     <row r="1195" spans="1:16">
       <c r="A1195" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1195" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C1195">
-        <v>4.844065934065937</v>
+        <v>4.806688400686618</v>
       </c>
       <c r="D1195" t="s">
-        <v>500</v>
+        <v>304</v>
       </c>
       <c r="E1195">
-        <v>4.953406593406597</v>
+        <v>5.039618634482576</v>
       </c>
       <c r="F1195">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1195">
-        <v>0.009775934065934064</v>
+        <v>0.009753311599313381</v>
       </c>
       <c r="H1195">
-        <v>0.009846593406593404</v>
+        <v>0.01020038136551743</v>
       </c>
       <c r="I1195">
-        <v>0.1093406593406598</v>
+        <v>-0.2329302337959573</v>
       </c>
       <c r="J1195">
-        <v>0.4835164835164829</v>
+        <v>0.5353488310202125</v>
       </c>
       <c r="K1195">
-        <v>5.1</v>
+        <v>4.62</v>
       </c>
       <c r="L1195">
-        <v>7.31</v>
+        <v>7.28</v>
       </c>
       <c r="M1195">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="N1195">
-        <v>7.4</v>
+        <v>7.62</v>
       </c>
       <c r="O1195">
         <v>1</v>
       </c>
       <c r="P1195" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="1196" spans="1:16">
       <c r="A1196" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B1196" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C1196">
-        <v>4.812417582417586</v>
+        <v>4.823153517584597</v>
       </c>
       <c r="D1196" t="s">
-        <v>500</v>
+        <v>304</v>
       </c>
       <c r="E1196">
-        <v>4.953406593406597</v>
+        <v>5.039618634482576</v>
       </c>
       <c r="F1196">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1196">
-        <v>0.009647582417582415</v>
+        <v>0.009876846482415403</v>
       </c>
       <c r="H1196">
-        <v>0.009846593406593404</v>
+        <v>0.01020038136551743</v>
       </c>
       <c r="I1196">
-        <v>0.1409890109890108</v>
+        <v>-0.2164651168979788</v>
       </c>
       <c r="J1196">
-        <v>0.4835164835164829</v>
+        <v>0.5353488310202125</v>
       </c>
       <c r="K1196">
-        <v>5</v>
+        <v>4.72</v>
       </c>
       <c r="L1196">
-        <v>7.23</v>
+        <v>7.35</v>
       </c>
       <c r="M1196">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="N1196">
-        <v>7.4</v>
+        <v>7.62</v>
       </c>
       <c r="O1196">
         <v>1</v>
       </c>
       <c r="P1196" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="1197" spans="1:16">
       <c r="A1197" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1197" t="s">
         <v>316</v>
       </c>
       <c r="C1197">
-        <v>4.832087912087915</v>
+        <v>4.844065934065937</v>
       </c>
       <c r="D1197" t="s">
         <v>500</v>
@@ -62117,22 +62117,22 @@
         <v>1</v>
       </c>
       <c r="G1197">
-        <v>0.009647912087912087</v>
+        <v>0.009775934065934064</v>
       </c>
       <c r="H1197">
         <v>0.009846593406593404</v>
       </c>
       <c r="I1197">
-        <v>0.121318681318682</v>
+        <v>0.1093406593406598</v>
       </c>
       <c r="J1197">
         <v>0.4835164835164829</v>
       </c>
       <c r="K1197">
-        <v>4.98</v>
+        <v>5.1</v>
       </c>
       <c r="L1197">
-        <v>7.24</v>
+        <v>7.31</v>
       </c>
       <c r="M1197">
         <v>5.06</v>
@@ -62149,46 +62149,46 @@
     </row>
     <row r="1198" spans="1:16">
       <c r="A1198" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1198" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C1198">
-        <v>5.0678021978022</v>
+        <v>4.812417582417586</v>
       </c>
       <c r="D1198" t="s">
-        <v>304</v>
+        <v>500</v>
       </c>
       <c r="E1198">
-        <v>5.289450549450552</v>
+        <v>4.953406593406597</v>
       </c>
       <c r="F1198">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1198">
-        <v>0.0096321978021978</v>
+        <v>0.009647582417582415</v>
       </c>
       <c r="H1198">
-        <v>0.00995054945054945</v>
+        <v>0.009846593406593404</v>
       </c>
       <c r="I1198">
-        <v>-0.2216483516483523</v>
+        <v>0.1409890109890108</v>
       </c>
       <c r="J1198">
         <v>0.4835164835164829</v>
       </c>
       <c r="K1198">
-        <v>4.72</v>
+        <v>5</v>
       </c>
       <c r="L1198">
-        <v>7.35</v>
+        <v>7.23</v>
       </c>
       <c r="M1198">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="N1198">
-        <v>7.62</v>
+        <v>7.4</v>
       </c>
       <c r="O1198">
         <v>1</v>
@@ -62199,40 +62199,40 @@
     </row>
     <row r="1199" spans="1:16">
       <c r="A1199" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1199" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C1199">
-        <v>4.976232772849881</v>
+        <v>4.832087912087915</v>
       </c>
       <c r="D1199" t="s">
         <v>500</v>
       </c>
       <c r="E1199">
-        <v>5.084536829533412</v>
+        <v>4.953406593406597</v>
       </c>
       <c r="F1199">
         <v>1</v>
       </c>
       <c r="G1199">
-        <v>0.009643767227150117</v>
+        <v>0.009647912087912087</v>
       </c>
       <c r="H1199">
-        <v>0.009715463170466588</v>
+        <v>0.009846593406593404</v>
       </c>
       <c r="I1199">
-        <v>0.1083040566835312</v>
+        <v>0.121318681318682</v>
       </c>
       <c r="J1199">
-        <v>0.4576014170882586</v>
+        <v>0.4835164835164829</v>
       </c>
       <c r="K1199">
-        <v>5.1</v>
+        <v>4.98</v>
       </c>
       <c r="L1199">
-        <v>7.31</v>
+        <v>7.24</v>
       </c>
       <c r="M1199">
         <v>5.06</v>
@@ -62244,68 +62244,68 @@
         <v>1</v>
       </c>
       <c r="P1199" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="1200" spans="1:16">
       <c r="A1200" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1200" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C1200">
-        <v>4.941992914558707</v>
+        <v>5.0678021978022</v>
       </c>
       <c r="D1200" t="s">
-        <v>500</v>
+        <v>304</v>
       </c>
       <c r="E1200">
-        <v>5.084536829533412</v>
+        <v>5.289450549450552</v>
       </c>
       <c r="F1200">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1200">
-        <v>0.009518007085441295</v>
+        <v>0.0096321978021978</v>
       </c>
       <c r="H1200">
-        <v>0.009715463170466588</v>
+        <v>0.00995054945054945</v>
       </c>
       <c r="I1200">
-        <v>0.1425439149747048</v>
+        <v>-0.2216483516483523</v>
       </c>
       <c r="J1200">
-        <v>0.4576014170882586</v>
+        <v>0.4835164835164829</v>
       </c>
       <c r="K1200">
-        <v>5</v>
+        <v>4.72</v>
       </c>
       <c r="L1200">
-        <v>7.23</v>
+        <v>7.35</v>
       </c>
       <c r="M1200">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="N1200">
-        <v>7.4</v>
+        <v>7.62</v>
       </c>
       <c r="O1200">
         <v>1</v>
       </c>
       <c r="P1200" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="1201" spans="1:16">
       <c r="A1201" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1201" t="s">
         <v>316</v>
       </c>
       <c r="C1201">
-        <v>4.961144942900471</v>
+        <v>4.976232772849881</v>
       </c>
       <c r="D1201" t="s">
         <v>500</v>
@@ -62317,22 +62317,22 @@
         <v>1</v>
       </c>
       <c r="G1201">
-        <v>0.00951885505709953</v>
+        <v>0.009643767227150117</v>
       </c>
       <c r="H1201">
         <v>0.009715463170466588</v>
       </c>
       <c r="I1201">
-        <v>0.1233918866329402</v>
+        <v>0.1083040566835312</v>
       </c>
       <c r="J1201">
         <v>0.4576014170882586</v>
       </c>
       <c r="K1201">
-        <v>4.98</v>
+        <v>5.1</v>
       </c>
       <c r="L1201">
-        <v>7.24</v>
+        <v>7.31</v>
       </c>
       <c r="M1201">
         <v>5.06</v>
@@ -62349,46 +62349,46 @@
     </row>
     <row r="1202" spans="1:16">
       <c r="A1202" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1202" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C1202">
-        <v>5.190121311343419</v>
+        <v>4.941992914558707</v>
       </c>
       <c r="D1202" t="s">
-        <v>304</v>
+        <v>500</v>
       </c>
       <c r="E1202">
-        <v>5.414361169634594</v>
+        <v>5.084536829533412</v>
       </c>
       <c r="F1202">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1202">
-        <v>0.009509878688656581</v>
+        <v>0.009518007085441295</v>
       </c>
       <c r="H1202">
-        <v>0.009825638830365406</v>
+        <v>0.009715463170466588</v>
       </c>
       <c r="I1202">
-        <v>-0.2242398582911749</v>
+        <v>0.1425439149747048</v>
       </c>
       <c r="J1202">
         <v>0.4576014170882586</v>
       </c>
       <c r="K1202">
-        <v>4.72</v>
+        <v>5</v>
       </c>
       <c r="L1202">
-        <v>7.35</v>
+        <v>7.23</v>
       </c>
       <c r="M1202">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="N1202">
-        <v>7.62</v>
+        <v>7.4</v>
       </c>
       <c r="O1202">
         <v>1</v>
@@ -62399,40 +62399,40 @@
     </row>
     <row r="1203" spans="1:16">
       <c r="A1203" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1203" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C1203">
-        <v>5.114447920426747</v>
+        <v>4.961144942900471</v>
       </c>
       <c r="D1203" t="s">
         <v>500</v>
       </c>
       <c r="E1203">
-        <v>5.221667936737125</v>
+        <v>5.084536829533412</v>
       </c>
       <c r="F1203">
         <v>1</v>
       </c>
       <c r="G1203">
-        <v>0.009505552079573253</v>
+        <v>0.00951885505709953</v>
       </c>
       <c r="H1203">
-        <v>0.009578332063262876</v>
+        <v>0.009715463170466588</v>
       </c>
       <c r="I1203">
-        <v>0.1072200163103787</v>
+        <v>0.1233918866329402</v>
       </c>
       <c r="J1203">
-        <v>0.4305004077594615</v>
+        <v>0.4576014170882586</v>
       </c>
       <c r="K1203">
-        <v>5.1</v>
+        <v>4.98</v>
       </c>
       <c r="L1203">
-        <v>7.31</v>
+        <v>7.24</v>
       </c>
       <c r="M1203">
         <v>5.06</v>
@@ -62444,68 +62444,68 @@
         <v>1</v>
       </c>
       <c r="P1203" t="s">
-        <v>303</v>
+        <v>639</v>
       </c>
     </row>
     <row r="1204" spans="1:16">
       <c r="A1204" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1204" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C1204">
-        <v>5.077497961202694</v>
+        <v>5.190121311343419</v>
       </c>
       <c r="D1204" t="s">
-        <v>500</v>
+        <v>304</v>
       </c>
       <c r="E1204">
-        <v>5.221667936737125</v>
+        <v>5.414361169634594</v>
       </c>
       <c r="F1204">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1204">
-        <v>0.009382502038797308</v>
+        <v>0.009509878688656581</v>
       </c>
       <c r="H1204">
-        <v>0.009578332063262876</v>
+        <v>0.009825638830365406</v>
       </c>
       <c r="I1204">
-        <v>0.1441699755344317</v>
+        <v>-0.2242398582911749</v>
       </c>
       <c r="J1204">
-        <v>0.4305004077594615</v>
+        <v>0.4576014170882586</v>
       </c>
       <c r="K1204">
-        <v>5</v>
+        <v>4.72</v>
       </c>
       <c r="L1204">
-        <v>7.23</v>
+        <v>7.35</v>
       </c>
       <c r="M1204">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="N1204">
-        <v>7.4</v>
+        <v>7.62</v>
       </c>
       <c r="O1204">
         <v>1</v>
       </c>
       <c r="P1204" t="s">
-        <v>303</v>
+        <v>639</v>
       </c>
     </row>
     <row r="1205" spans="1:16">
       <c r="A1205" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1205" t="s">
         <v>316</v>
       </c>
       <c r="C1205">
-        <v>5.096107969357882</v>
+        <v>5.114447920426747</v>
       </c>
       <c r="D1205" t="s">
         <v>500</v>
@@ -62517,22 +62517,22 @@
         <v>1</v>
       </c>
       <c r="G1205">
-        <v>0.00938389203064212</v>
+        <v>0.009505552079573253</v>
       </c>
       <c r="H1205">
         <v>0.009578332063262876</v>
       </c>
       <c r="I1205">
-        <v>0.1255599673792434</v>
+        <v>0.1072200163103787</v>
       </c>
       <c r="J1205">
         <v>0.4305004077594615</v>
       </c>
       <c r="K1205">
-        <v>4.98</v>
+        <v>5.1</v>
       </c>
       <c r="L1205">
-        <v>7.24</v>
+        <v>7.31</v>
       </c>
       <c r="M1205">
         <v>5.06</v>
@@ -62549,46 +62549,46 @@
     </row>
     <row r="1206" spans="1:16">
       <c r="A1206" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1206" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C1206">
-        <v>5.318038075375341</v>
+        <v>5.077497961202694</v>
       </c>
       <c r="D1206" t="s">
-        <v>304</v>
+        <v>500</v>
       </c>
       <c r="E1206">
-        <v>5.544988034599395</v>
+        <v>5.221667936737125</v>
       </c>
       <c r="F1206">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1206">
-        <v>0.009381961924624658</v>
+        <v>0.009382502038797308</v>
       </c>
       <c r="H1206">
-        <v>0.009695011965400605</v>
+        <v>0.009578332063262876</v>
       </c>
       <c r="I1206">
-        <v>-0.2269499592240543</v>
+        <v>0.1441699755344317</v>
       </c>
       <c r="J1206">
         <v>0.4305004077594615</v>
       </c>
       <c r="K1206">
-        <v>4.72</v>
+        <v>5</v>
       </c>
       <c r="L1206">
-        <v>7.35</v>
+        <v>7.23</v>
       </c>
       <c r="M1206">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="N1206">
-        <v>7.62</v>
+        <v>7.4</v>
       </c>
       <c r="O1206">
         <v>1</v>
@@ -62599,40 +62599,40 @@
     </row>
     <row r="1207" spans="1:16">
       <c r="A1207" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1207" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="C1207">
-        <v>5.395229280605809</v>
+        <v>5.096107969357882</v>
       </c>
       <c r="D1207" t="s">
         <v>500</v>
       </c>
       <c r="E1207">
-        <v>5.543212031973079</v>
+        <v>5.221667936737125</v>
       </c>
       <c r="F1207">
         <v>1</v>
       </c>
       <c r="G1207">
-        <v>0.009064770719394192</v>
+        <v>0.00938389203064212</v>
       </c>
       <c r="H1207">
-        <v>0.009256787968026921</v>
+        <v>0.009578332063262876</v>
       </c>
       <c r="I1207">
-        <v>0.1479827513672696</v>
+        <v>0.1255599673792434</v>
       </c>
       <c r="J1207">
-        <v>0.3669541438788382</v>
+        <v>0.4305004077594615</v>
       </c>
       <c r="K1207">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="L1207">
-        <v>7.23</v>
+        <v>7.24</v>
       </c>
       <c r="M1207">
         <v>5.06</v>
@@ -62644,101 +62644,101 @@
         <v>1</v>
       </c>
       <c r="P1207" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="1208" spans="1:16">
       <c r="A1208" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1208" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C1208">
-        <v>5.412568363483386</v>
+        <v>5.318038075375341</v>
       </c>
       <c r="D1208" t="s">
-        <v>500</v>
+        <v>304</v>
       </c>
       <c r="E1208">
-        <v>5.543212031973079</v>
+        <v>5.544988034599395</v>
       </c>
       <c r="F1208">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1208">
-        <v>0.009067431636516615</v>
+        <v>0.009381961924624658</v>
       </c>
       <c r="H1208">
-        <v>0.009256787968026921</v>
+        <v>0.009695011965400605</v>
       </c>
       <c r="I1208">
-        <v>0.130643668489693</v>
+        <v>-0.2269499592240543</v>
       </c>
       <c r="J1208">
-        <v>0.3669541438788382</v>
+        <v>0.4305004077594615</v>
       </c>
       <c r="K1208">
-        <v>4.98</v>
+        <v>4.72</v>
       </c>
       <c r="L1208">
-        <v>7.24</v>
+        <v>7.35</v>
       </c>
       <c r="M1208">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="N1208">
-        <v>7.4</v>
+        <v>7.62</v>
       </c>
       <c r="O1208">
         <v>1</v>
       </c>
       <c r="P1208" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="1209" spans="1:16">
       <c r="A1209" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1209" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C1209">
-        <v>5.617976440891884</v>
+        <v>5.395229280605809</v>
       </c>
       <c r="D1209" t="s">
-        <v>304</v>
+        <v>500</v>
       </c>
       <c r="E1209">
-        <v>5.851281026504</v>
+        <v>5.543212031973079</v>
       </c>
       <c r="F1209">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1209">
-        <v>0.009082023559108116</v>
+        <v>0.009064770719394192</v>
       </c>
       <c r="H1209">
-        <v>0.009388718973496002</v>
+        <v>0.009256787968026921</v>
       </c>
       <c r="I1209">
-        <v>-0.2333045856121165</v>
+        <v>0.1479827513672696</v>
       </c>
       <c r="J1209">
         <v>0.3669541438788382</v>
       </c>
       <c r="K1209">
-        <v>4.72</v>
+        <v>5</v>
       </c>
       <c r="L1209">
-        <v>7.35</v>
+        <v>7.23</v>
       </c>
       <c r="M1209">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="N1209">
-        <v>7.62</v>
+        <v>7.4</v>
       </c>
       <c r="O1209">
         <v>1</v>
@@ -62749,40 +62749,40 @@
     </row>
     <row r="1210" spans="1:16">
       <c r="A1210" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1210" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="C1210">
-        <v>5.589932664326452</v>
+        <v>5.412568363483386</v>
       </c>
       <c r="D1210" t="s">
         <v>500</v>
       </c>
       <c r="E1210">
-        <v>5.740251856298369</v>
+        <v>5.543212031973079</v>
       </c>
       <c r="F1210">
         <v>1</v>
       </c>
       <c r="G1210">
-        <v>0.00887006733567355</v>
+        <v>0.009067431636516615</v>
       </c>
       <c r="H1210">
-        <v>0.009059748143701632</v>
+        <v>0.009256787968026921</v>
       </c>
       <c r="I1210">
-        <v>0.1503191919719171</v>
+        <v>0.130643668489693</v>
       </c>
       <c r="J1210">
-        <v>0.3280134671347097</v>
+        <v>0.3669541438788382</v>
       </c>
       <c r="K1210">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="L1210">
-        <v>7.23</v>
+        <v>7.24</v>
       </c>
       <c r="M1210">
         <v>5.06</v>
@@ -62794,101 +62794,101 @@
         <v>1</v>
       </c>
       <c r="P1210" t="s">
-        <v>640</v>
+        <v>302</v>
       </c>
     </row>
     <row r="1211" spans="1:16">
       <c r="A1211" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1211" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C1211">
-        <v>5.606492933669146</v>
+        <v>5.617976440891884</v>
       </c>
       <c r="D1211" t="s">
-        <v>500</v>
+        <v>304</v>
       </c>
       <c r="E1211">
-        <v>5.740251856298369</v>
+        <v>5.851281026504</v>
       </c>
       <c r="F1211">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1211">
-        <v>0.008873507066330855</v>
+        <v>0.009082023559108116</v>
       </c>
       <c r="H1211">
-        <v>0.009059748143701632</v>
+        <v>0.009388718973496002</v>
       </c>
       <c r="I1211">
-        <v>0.1337589226292231</v>
+        <v>-0.2333045856121165</v>
       </c>
       <c r="J1211">
-        <v>0.3280134671347097</v>
+        <v>0.3669541438788382</v>
       </c>
       <c r="K1211">
-        <v>4.98</v>
+        <v>4.72</v>
       </c>
       <c r="L1211">
-        <v>7.24</v>
+        <v>7.35</v>
       </c>
       <c r="M1211">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="N1211">
-        <v>7.4</v>
+        <v>7.62</v>
       </c>
       <c r="O1211">
         <v>1</v>
       </c>
       <c r="P1211" t="s">
-        <v>640</v>
+        <v>302</v>
       </c>
     </row>
     <row r="1212" spans="1:16">
       <c r="A1212" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1212" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C1212">
-        <v>5.80177643512417</v>
+        <v>5.589932664326452</v>
       </c>
       <c r="D1212" t="s">
-        <v>304</v>
+        <v>500</v>
       </c>
       <c r="E1212">
-        <v>6.038975088410699</v>
+        <v>5.740251856298369</v>
       </c>
       <c r="F1212">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1212">
-        <v>0.00889822356487583</v>
+        <v>0.00887006733567355</v>
       </c>
       <c r="H1212">
-        <v>0.009201024911589301</v>
+        <v>0.009059748143701632</v>
       </c>
       <c r="I1212">
-        <v>-0.2371986532865291</v>
+        <v>0.1503191919719171</v>
       </c>
       <c r="J1212">
         <v>0.3280134671347097</v>
       </c>
       <c r="K1212">
-        <v>4.72</v>
+        <v>5</v>
       </c>
       <c r="L1212">
-        <v>7.35</v>
+        <v>7.23</v>
       </c>
       <c r="M1212">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="N1212">
-        <v>7.62</v>
+        <v>7.4</v>
       </c>
       <c r="O1212">
         <v>1</v>
@@ -62899,40 +62899,40 @@
     </row>
     <row r="1213" spans="1:16">
       <c r="A1213" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1213" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="C1213">
-        <v>5.496374966852297</v>
+        <v>5.606492933669146</v>
       </c>
       <c r="D1213" t="s">
         <v>500</v>
       </c>
       <c r="E1213">
-        <v>5.645571466454525</v>
+        <v>5.740251856298369</v>
       </c>
       <c r="F1213">
         <v>1</v>
       </c>
       <c r="G1213">
-        <v>0.008963625033147704</v>
+        <v>0.008873507066330855</v>
       </c>
       <c r="H1213">
-        <v>0.009154428533545476</v>
+        <v>0.009059748143701632</v>
       </c>
       <c r="I1213">
-        <v>0.1491964996022279</v>
+        <v>0.1337589226292231</v>
       </c>
       <c r="J1213">
-        <v>0.3467250066295405</v>
+        <v>0.3280134671347097</v>
       </c>
       <c r="K1213">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="L1213">
-        <v>7.23</v>
+        <v>7.24</v>
       </c>
       <c r="M1213">
         <v>5.06</v>
@@ -62944,101 +62944,101 @@
         <v>1</v>
       </c>
       <c r="P1213" t="s">
-        <v>499</v>
+        <v>640</v>
       </c>
     </row>
     <row r="1214" spans="1:16">
       <c r="A1214" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1214" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C1214">
-        <v>5.513309466984888</v>
+        <v>5.80177643512417</v>
       </c>
       <c r="D1214" t="s">
-        <v>500</v>
+        <v>304</v>
       </c>
       <c r="E1214">
-        <v>5.645571466454525</v>
+        <v>6.038975088410699</v>
       </c>
       <c r="F1214">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1214">
-        <v>0.008966690533015112</v>
+        <v>0.00889822356487583</v>
       </c>
       <c r="H1214">
-        <v>0.009154428533545476</v>
+        <v>0.009201024911589301</v>
       </c>
       <c r="I1214">
-        <v>0.1322619994696375</v>
+        <v>-0.2371986532865291</v>
       </c>
       <c r="J1214">
-        <v>0.3467250066295405</v>
+        <v>0.3280134671347097</v>
       </c>
       <c r="K1214">
-        <v>4.98</v>
+        <v>4.72</v>
       </c>
       <c r="L1214">
-        <v>7.24</v>
+        <v>7.35</v>
       </c>
       <c r="M1214">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="N1214">
-        <v>7.4</v>
+        <v>7.62</v>
       </c>
       <c r="O1214">
         <v>1</v>
       </c>
       <c r="P1214" t="s">
-        <v>499</v>
+        <v>640</v>
       </c>
     </row>
     <row r="1215" spans="1:16">
       <c r="A1215" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1215" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C1215">
-        <v>5.713457968708568</v>
+        <v>5.496374966852297</v>
       </c>
       <c r="D1215" t="s">
-        <v>304</v>
+        <v>500</v>
       </c>
       <c r="E1215">
-        <v>5.948785468045615</v>
+        <v>5.645571466454525</v>
       </c>
       <c r="F1215">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1215">
-        <v>0.008986542031291431</v>
+        <v>0.008963625033147704</v>
       </c>
       <c r="H1215">
-        <v>0.009291214531954384</v>
+        <v>0.009154428533545476</v>
       </c>
       <c r="I1215">
-        <v>-0.2353274993370462</v>
+        <v>0.1491964996022279</v>
       </c>
       <c r="J1215">
         <v>0.3467250066295405</v>
       </c>
       <c r="K1215">
-        <v>4.72</v>
+        <v>5</v>
       </c>
       <c r="L1215">
-        <v>7.35</v>
+        <v>7.23</v>
       </c>
       <c r="M1215">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="N1215">
-        <v>7.62</v>
+        <v>7.4</v>
       </c>
       <c r="O1215">
         <v>1</v>
@@ -63049,40 +63049,40 @@
     </row>
     <row r="1216" spans="1:16">
       <c r="A1216" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1216" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="C1216">
-        <v>5.171207853179688</v>
+        <v>5.513309466984888</v>
       </c>
       <c r="D1216" t="s">
         <v>500</v>
       </c>
       <c r="E1216">
-        <v>5.316502347417844</v>
+        <v>5.645571466454525</v>
       </c>
       <c r="F1216">
         <v>1</v>
       </c>
       <c r="G1216">
-        <v>0.009288792146820313</v>
+        <v>0.008966690533015112</v>
       </c>
       <c r="H1216">
-        <v>0.009483497652582157</v>
+        <v>0.009154428533545476</v>
       </c>
       <c r="I1216">
-        <v>0.145294494238156</v>
+        <v>0.1322619994696375</v>
       </c>
       <c r="J1216">
-        <v>0.4117584293640626</v>
+        <v>0.3467250066295405</v>
       </c>
       <c r="K1216">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="L1216">
-        <v>7.23</v>
+        <v>7.24</v>
       </c>
       <c r="M1216">
         <v>5.06</v>
@@ -63094,145 +63094,145 @@
         <v>1</v>
       </c>
       <c r="P1216" t="s">
-        <v>315</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1217" spans="1:16">
       <c r="A1217" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1217" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C1217">
-        <v>5.189443021766968</v>
+        <v>5.713457968708568</v>
       </c>
       <c r="D1217" t="s">
-        <v>500</v>
+        <v>304</v>
       </c>
       <c r="E1217">
-        <v>5.316502347417844</v>
+        <v>5.948785468045615</v>
       </c>
       <c r="F1217">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1217">
-        <v>0.009290556978233031</v>
+        <v>0.008986542031291431</v>
       </c>
       <c r="H1217">
-        <v>0.009483497652582157</v>
+        <v>0.009291214531954384</v>
       </c>
       <c r="I1217">
-        <v>0.1270593256508752</v>
+        <v>-0.2353274993370462</v>
       </c>
       <c r="J1217">
-        <v>0.4117584293640626</v>
+        <v>0.3467250066295405</v>
       </c>
       <c r="K1217">
-        <v>4.98</v>
+        <v>4.72</v>
       </c>
       <c r="L1217">
-        <v>7.24</v>
+        <v>7.35</v>
       </c>
       <c r="M1217">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="N1217">
-        <v>7.4</v>
+        <v>7.62</v>
       </c>
       <c r="O1217">
         <v>1</v>
       </c>
       <c r="P1217" t="s">
-        <v>315</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1218" spans="1:16">
       <c r="A1218" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1218" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C1218">
-        <v>5.406500213401625</v>
+        <v>5.171207853179688</v>
       </c>
       <c r="D1218" t="s">
-        <v>304</v>
+        <v>500</v>
       </c>
       <c r="E1218">
-        <v>5.635324370465218</v>
+        <v>5.316502347417844</v>
       </c>
       <c r="F1218">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1218">
-        <v>0.009293499786598375</v>
+        <v>0.009288792146820313</v>
       </c>
       <c r="H1218">
-        <v>0.009604675629534782</v>
+        <v>0.009483497652582157</v>
       </c>
       <c r="I1218">
-        <v>-0.2288241570635936</v>
+        <v>0.145294494238156</v>
       </c>
       <c r="J1218">
         <v>0.4117584293640626</v>
       </c>
       <c r="K1218">
-        <v>4.72</v>
+        <v>5</v>
       </c>
       <c r="L1218">
-        <v>7.35</v>
+        <v>7.23</v>
       </c>
       <c r="M1218">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="N1218">
-        <v>7.62</v>
+        <v>7.4</v>
       </c>
       <c r="O1218">
         <v>1</v>
       </c>
       <c r="P1218" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="1219" spans="1:16">
       <c r="A1219" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1219" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="C1219">
-        <v>4.974344857020913</v>
+        <v>5.189443021766968</v>
       </c>
       <c r="D1219" t="s">
         <v>500</v>
       </c>
       <c r="E1219">
-        <v>5.117276995305165</v>
+        <v>5.316502347417844</v>
       </c>
       <c r="F1219">
         <v>1</v>
       </c>
       <c r="G1219">
-        <v>0.009485655142979088</v>
+        <v>0.009290556978233031</v>
       </c>
       <c r="H1219">
-        <v>0.009682723004694836</v>
+        <v>0.009483497652582157</v>
       </c>
       <c r="I1219">
-        <v>0.1429321382842517</v>
+        <v>0.1270593256508752</v>
       </c>
       <c r="J1219">
-        <v>0.4511310285958173</v>
+        <v>0.4117584293640626</v>
       </c>
       <c r="K1219">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="L1219">
-        <v>7.23</v>
+        <v>7.24</v>
       </c>
       <c r="M1219">
         <v>5.06</v>
@@ -63244,101 +63244,101 @@
         <v>1</v>
       </c>
       <c r="P1219" t="s">
-        <v>641</v>
+        <v>316</v>
       </c>
     </row>
     <row r="1220" spans="1:16">
       <c r="A1220" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1220" t="s">
+        <v>317</v>
+      </c>
+      <c r="C1220">
+        <v>5.406500213401625</v>
+      </c>
+      <c r="D1220" t="s">
+        <v>304</v>
+      </c>
+      <c r="E1220">
+        <v>5.635324370465218</v>
+      </c>
+      <c r="F1220">
+        <v>-1</v>
+      </c>
+      <c r="G1220">
+        <v>0.009293499786598375</v>
+      </c>
+      <c r="H1220">
+        <v>0.009604675629534782</v>
+      </c>
+      <c r="I1220">
+        <v>-0.2288241570635936</v>
+      </c>
+      <c r="J1220">
+        <v>0.4117584293640626</v>
+      </c>
+      <c r="K1220">
+        <v>4.72</v>
+      </c>
+      <c r="L1220">
+        <v>7.35</v>
+      </c>
+      <c r="M1220">
+        <v>4.82</v>
+      </c>
+      <c r="N1220">
+        <v>7.62</v>
+      </c>
+      <c r="O1220">
+        <v>1</v>
+      </c>
+      <c r="P1220" t="s">
         <v>316</v>
-      </c>
-      <c r="C1220">
-        <v>4.99336747759283</v>
-      </c>
-      <c r="D1220" t="s">
-        <v>500</v>
-      </c>
-      <c r="E1220">
-        <v>5.117276995305165</v>
-      </c>
-      <c r="F1220">
-        <v>1</v>
-      </c>
-      <c r="G1220">
-        <v>0.00948663252240717</v>
-      </c>
-      <c r="H1220">
-        <v>0.009682723004694836</v>
-      </c>
-      <c r="I1220">
-        <v>0.1239095177123346</v>
-      </c>
-      <c r="J1220">
-        <v>0.4511310285958173</v>
-      </c>
-      <c r="K1220">
-        <v>4.98</v>
-      </c>
-      <c r="L1220">
-        <v>7.24</v>
-      </c>
-      <c r="M1220">
-        <v>5.06</v>
-      </c>
-      <c r="N1220">
-        <v>7.4</v>
-      </c>
-      <c r="O1220">
-        <v>1</v>
-      </c>
-      <c r="P1220" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="1221" spans="1:16">
       <c r="A1221" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1221" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C1221">
-        <v>5.220661545027742</v>
+        <v>4.974344857020913</v>
       </c>
       <c r="D1221" t="s">
-        <v>304</v>
+        <v>500</v>
       </c>
       <c r="E1221">
-        <v>5.44554844216816</v>
+        <v>5.117276995305165</v>
       </c>
       <c r="F1221">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1221">
-        <v>0.009479338454972258</v>
+        <v>0.009485655142979088</v>
       </c>
       <c r="H1221">
-        <v>0.009794451557831841</v>
+        <v>0.009682723004694836</v>
       </c>
       <c r="I1221">
-        <v>-0.2248868971404185</v>
+        <v>0.1429321382842517</v>
       </c>
       <c r="J1221">
         <v>0.4511310285958173</v>
       </c>
       <c r="K1221">
-        <v>4.72</v>
+        <v>5</v>
       </c>
       <c r="L1221">
-        <v>7.35</v>
+        <v>7.23</v>
       </c>
       <c r="M1221">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="N1221">
-        <v>7.62</v>
+        <v>7.4</v>
       </c>
       <c r="O1221">
         <v>1</v>
@@ -63349,40 +63349,40 @@
     </row>
     <row r="1222" spans="1:16">
       <c r="A1222" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1222" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="C1222">
-        <v>5.581350896955229</v>
+        <v>4.99336747759283</v>
       </c>
       <c r="D1222" t="s">
         <v>500</v>
       </c>
       <c r="E1222">
-        <v>5.731567107718692</v>
+        <v>5.117276995305165</v>
       </c>
       <c r="F1222">
         <v>1</v>
       </c>
       <c r="G1222">
-        <v>0.008878649103044773</v>
+        <v>0.00948663252240717</v>
       </c>
       <c r="H1222">
-        <v>0.009068432892281309</v>
+        <v>0.009682723004694836</v>
       </c>
       <c r="I1222">
-        <v>0.150216210763463</v>
+        <v>0.1239095177123346</v>
       </c>
       <c r="J1222">
-        <v>0.3297298206089543</v>
+        <v>0.4511310285958173</v>
       </c>
       <c r="K1222">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="L1222">
-        <v>7.23</v>
+        <v>7.24</v>
       </c>
       <c r="M1222">
         <v>5.06</v>
@@ -63394,106 +63394,206 @@
         <v>1</v>
       </c>
       <c r="P1222" t="s">
-        <v>309</v>
+        <v>641</v>
       </c>
     </row>
     <row r="1223" spans="1:16">
       <c r="A1223" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1223" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C1223">
-        <v>5.597945493367408</v>
+        <v>5.220661545027742</v>
       </c>
       <c r="D1223" t="s">
-        <v>500</v>
+        <v>304</v>
       </c>
       <c r="E1223">
-        <v>5.731567107718692</v>
+        <v>5.44554844216816</v>
       </c>
       <c r="F1223">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1223">
-        <v>0.008882054506632592</v>
+        <v>0.009479338454972258</v>
       </c>
       <c r="H1223">
-        <v>0.009068432892281309</v>
+        <v>0.009794451557831841</v>
       </c>
       <c r="I1223">
-        <v>0.1336216143512843</v>
+        <v>-0.2248868971404185</v>
       </c>
       <c r="J1223">
-        <v>0.3297298206089543</v>
+        <v>0.4511310285958173</v>
       </c>
       <c r="K1223">
-        <v>4.98</v>
+        <v>4.72</v>
       </c>
       <c r="L1223">
-        <v>7.24</v>
+        <v>7.35</v>
       </c>
       <c r="M1223">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="N1223">
-        <v>7.4</v>
+        <v>7.62</v>
       </c>
       <c r="O1223">
         <v>1</v>
       </c>
       <c r="P1223" t="s">
-        <v>309</v>
+        <v>641</v>
       </c>
     </row>
     <row r="1224" spans="1:16">
       <c r="A1224" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1224" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="C1224">
-        <v>5.903891457489198</v>
+        <v>5.581350896955229</v>
       </c>
       <c r="D1224" t="s">
-        <v>304</v>
+        <v>500</v>
       </c>
       <c r="E1224">
-        <v>6.03070226466484</v>
+        <v>5.731567107718692</v>
       </c>
       <c r="F1224">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1224">
-        <v>0.009056108542510802</v>
+        <v>0.008878649103044773</v>
       </c>
       <c r="H1224">
-        <v>0.009209297735335159</v>
+        <v>0.009068432892281309</v>
       </c>
       <c r="I1224">
-        <v>-0.1268108071756417</v>
+        <v>0.150216210763463</v>
       </c>
       <c r="J1224">
         <v>0.3297298206089543</v>
       </c>
       <c r="K1224">
+        <v>5</v>
+      </c>
+      <c r="L1224">
+        <v>7.23</v>
+      </c>
+      <c r="M1224">
+        <v>5.06</v>
+      </c>
+      <c r="N1224">
+        <v>7.4</v>
+      </c>
+      <c r="O1224">
+        <v>1</v>
+      </c>
+      <c r="P1224" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:16">
+      <c r="A1225" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1225" t="s">
+        <v>312</v>
+      </c>
+      <c r="C1225">
+        <v>5.597945493367408</v>
+      </c>
+      <c r="D1225" t="s">
+        <v>500</v>
+      </c>
+      <c r="E1225">
+        <v>5.731567107718692</v>
+      </c>
+      <c r="F1225">
+        <v>1</v>
+      </c>
+      <c r="G1225">
+        <v>0.008882054506632592</v>
+      </c>
+      <c r="H1225">
+        <v>0.009068432892281309</v>
+      </c>
+      <c r="I1225">
+        <v>0.1336216143512843</v>
+      </c>
+      <c r="J1225">
+        <v>0.3297298206089543</v>
+      </c>
+      <c r="K1225">
+        <v>4.98</v>
+      </c>
+      <c r="L1225">
+        <v>7.24</v>
+      </c>
+      <c r="M1225">
+        <v>5.06</v>
+      </c>
+      <c r="N1225">
+        <v>7.4</v>
+      </c>
+      <c r="O1225">
+        <v>1</v>
+      </c>
+      <c r="P1225" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:16">
+      <c r="A1226" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1226" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1226">
+        <v>5.903891457489198</v>
+      </c>
+      <c r="D1226" t="s">
+        <v>304</v>
+      </c>
+      <c r="E1226">
+        <v>6.03070226466484</v>
+      </c>
+      <c r="F1226">
+        <v>-1</v>
+      </c>
+      <c r="G1226">
+        <v>0.009056108542510802</v>
+      </c>
+      <c r="H1226">
+        <v>0.009209297735335159</v>
+      </c>
+      <c r="I1226">
+        <v>-0.1268108071756417</v>
+      </c>
+      <c r="J1226">
+        <v>0.3297298206089543</v>
+      </c>
+      <c r="K1226">
         <v>4.78</v>
       </c>
-      <c r="L1224">
+      <c r="L1226">
         <v>7.48</v>
       </c>
-      <c r="M1224">
+      <c r="M1226">
         <v>4.82</v>
       </c>
-      <c r="N1224">
+      <c r="N1226">
         <v>7.62</v>
       </c>
-      <c r="O1224">
-        <v>1</v>
-      </c>
-      <c r="P1224" t="s">
+      <c r="O1226">
+        <v>1</v>
+      </c>
+      <c r="P1226" t="s">
         <v>309</v>
       </c>
     </row>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -949,12 +949,15 @@
     <t>2021-06-11</t>
   </si>
   <si>
+    <t>2021-08-13</t>
+  </si>
+  <si>
+    <t>2021-06-22</t>
+  </si>
+  <si>
     <t>2021-06-25</t>
   </si>
   <si>
-    <t>2021-06-22</t>
-  </si>
-  <si>
     <t>2021-07-05</t>
   </si>
   <si>
@@ -967,9 +970,6 @@
     <t>2021-07-16</t>
   </si>
   <si>
-    <t>2021-08-13</t>
-  </si>
-  <si>
     <t>2021-07-30</t>
   </si>
   <si>
@@ -1510,7 +1510,7 @@
     <t>2021-06-09</t>
   </si>
   <si>
-    <t>2021-08-16</t>
+    <t>2021-08-17</t>
   </si>
   <si>
     <t>2021-07-23</t>
@@ -58052,7 +58052,7 @@
         <v>498</v>
       </c>
       <c r="E1116">
-        <v>6.835531406463352</v>
+        <v>6.822967683204364</v>
       </c>
       <c r="F1116">
         <v>1</v>
@@ -58061,10 +58061,10 @@
         <v>0.007670195721438331</v>
       </c>
       <c r="H1116">
-        <v>0.007664468593536648</v>
+        <v>0.007657032316795637</v>
       </c>
       <c r="I1116">
-        <v>-0.01427287209831629</v>
+        <v>-0.02683659535730509</v>
       </c>
       <c r="J1116">
         <v>0.08545744196631905</v>
@@ -58076,10 +58076,10 @@
         <v>7.26</v>
       </c>
       <c r="M1116">
-        <v>4.85</v>
+        <v>4.88</v>
       </c>
       <c r="N1116">
-        <v>7.25</v>
+        <v>7.24</v>
       </c>
       <c r="O1116">
         <v>1</v>
@@ -58293,43 +58293,43 @@
         <v>4</v>
       </c>
       <c r="B1121" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C1121">
-        <v>6.774712649020467</v>
+        <v>6.721679603076844</v>
       </c>
       <c r="D1121" t="s">
         <v>498</v>
       </c>
       <c r="E1121">
-        <v>6.759657572447764</v>
+        <v>6.746624526504141</v>
       </c>
       <c r="F1121">
         <v>1</v>
       </c>
       <c r="G1121">
-        <v>0.007745287350979533</v>
+        <v>0.007698320396923156</v>
       </c>
       <c r="H1121">
-        <v>0.007740342427552237</v>
+        <v>0.00773337547349586</v>
       </c>
       <c r="I1121">
-        <v>-0.01505507657270311</v>
+        <v>0.02494492342729693</v>
       </c>
       <c r="J1121">
         <v>0.1011015314540694</v>
       </c>
       <c r="K1121">
-        <v>4.8</v>
+        <v>4.83</v>
       </c>
       <c r="L1121">
-        <v>7.26</v>
+        <v>7.21</v>
       </c>
       <c r="M1121">
-        <v>4.85</v>
+        <v>4.88</v>
       </c>
       <c r="N1121">
-        <v>7.25</v>
+        <v>7.24</v>
       </c>
       <c r="O1121">
         <v>1</v>
@@ -58543,43 +58543,43 @@
         <v>4</v>
       </c>
       <c r="B1126" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C1126">
-        <v>6.723318282205366</v>
+        <v>6.669964021469148</v>
       </c>
       <c r="D1126" t="s">
         <v>498</v>
       </c>
       <c r="E1126">
-        <v>6.707727847645005</v>
+        <v>6.694373586908789</v>
       </c>
       <c r="F1126">
         <v>1</v>
       </c>
       <c r="G1126">
-        <v>0.007796681717794634</v>
+        <v>0.007750035978530852</v>
       </c>
       <c r="H1126">
-        <v>0.007792272152354995</v>
+        <v>0.007785626413091212</v>
       </c>
       <c r="I1126">
-        <v>-0.01559043456036058</v>
+        <v>0.02440956543964035</v>
       </c>
       <c r="J1126">
         <v>0.1118086912072155</v>
       </c>
       <c r="K1126">
-        <v>4.8</v>
+        <v>4.83</v>
       </c>
       <c r="L1126">
-        <v>7.26</v>
+        <v>7.21</v>
       </c>
       <c r="M1126">
-        <v>4.85</v>
+        <v>4.88</v>
       </c>
       <c r="N1126">
-        <v>7.25</v>
+        <v>7.24</v>
       </c>
       <c r="O1126">
         <v>1</v>
@@ -58743,43 +58743,43 @@
         <v>3</v>
       </c>
       <c r="B1130" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C1130">
-        <v>6.749238025431011</v>
+        <v>6.696045763089955</v>
       </c>
       <c r="D1130" t="s">
         <v>498</v>
       </c>
       <c r="E1130">
-        <v>6.733917588195918</v>
+        <v>6.720725325854862</v>
       </c>
       <c r="F1130">
         <v>1</v>
       </c>
       <c r="G1130">
-        <v>0.007770761974568988</v>
+        <v>0.007723954236910044</v>
       </c>
       <c r="H1130">
-        <v>0.007766082411804083</v>
+        <v>0.007759274674145138</v>
       </c>
       <c r="I1130">
-        <v>-0.01532043723509346</v>
+        <v>0.02467956276490657</v>
       </c>
       <c r="J1130">
         <v>0.1064087447018726</v>
       </c>
       <c r="K1130">
-        <v>4.8</v>
+        <v>4.83</v>
       </c>
       <c r="L1130">
-        <v>7.26</v>
+        <v>7.21</v>
       </c>
       <c r="M1130">
-        <v>4.85</v>
+        <v>4.88</v>
       </c>
       <c r="N1130">
-        <v>7.25</v>
+        <v>7.24</v>
       </c>
       <c r="O1130">
         <v>1</v>
@@ -58793,10 +58793,10 @@
         <v>0</v>
       </c>
       <c r="B1131" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C1131">
-        <v>7.032817173622921</v>
+        <v>7.027653582439818</v>
       </c>
       <c r="D1131" t="s">
         <v>305</v>
@@ -58808,22 +58808,22 @@
         <v>-1</v>
       </c>
       <c r="G1131">
-        <v>0.008027182826377079</v>
+        <v>0.008012346417560181</v>
       </c>
       <c r="H1131">
         <v>0.007853313699323562</v>
       </c>
       <c r="I1131">
-        <v>0.1661308729464812</v>
+        <v>0.1609672817633783</v>
       </c>
       <c r="J1131">
         <v>0.09672817633795312</v>
       </c>
       <c r="K1131">
-        <v>5.14</v>
+        <v>5.09</v>
       </c>
       <c r="L1131">
-        <v>7.53</v>
+        <v>7.52</v>
       </c>
       <c r="M1131">
         <v>5.1</v>
@@ -58843,43 +58843,43 @@
         <v>1</v>
       </c>
       <c r="B1132" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C1132">
-        <v>6.746359118310234</v>
+        <v>7.032817173622921</v>
       </c>
       <c r="D1132" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E1132">
-        <v>7.017639317104584</v>
+        <v>6.86668630067644</v>
       </c>
       <c r="F1132">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1132">
-        <v>0.007713640881689766</v>
+        <v>0.008027182826377079</v>
       </c>
       <c r="H1132">
-        <v>0.007942360682895416</v>
+        <v>0.007853313699323562</v>
       </c>
       <c r="I1132">
-        <v>0.2712801987943498</v>
+        <v>0.1661308729464812</v>
       </c>
       <c r="J1132">
         <v>0.09672817633795312</v>
       </c>
       <c r="K1132">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="L1132">
-        <v>7.23</v>
+        <v>7.53</v>
       </c>
       <c r="M1132">
-        <v>4.78</v>
+        <v>5.1</v>
       </c>
       <c r="N1132">
-        <v>7.48</v>
+        <v>7.36</v>
       </c>
       <c r="O1132">
         <v>1</v>
@@ -58893,43 +58893,43 @@
         <v>2</v>
       </c>
       <c r="B1133" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C1133">
-        <v>6.758293681836994</v>
+        <v>6.746359118310234</v>
       </c>
       <c r="D1133" t="s">
-        <v>306</v>
+        <v>499</v>
       </c>
       <c r="E1133">
-        <v>7.017639317104584</v>
+        <v>6.910555427729958</v>
       </c>
       <c r="F1133">
         <v>1</v>
       </c>
       <c r="G1133">
-        <v>0.007721706318163006</v>
+        <v>0.007713640881689766</v>
       </c>
       <c r="H1133">
-        <v>0.007942360682895416</v>
+        <v>0.007889444572270043</v>
       </c>
       <c r="I1133">
-        <v>0.2593456352675902</v>
+        <v>0.1641963094197232</v>
       </c>
       <c r="J1133">
         <v>0.09672817633795312</v>
       </c>
       <c r="K1133">
-        <v>4.98</v>
+        <v>5</v>
       </c>
       <c r="L1133">
-        <v>7.24</v>
+        <v>7.23</v>
       </c>
       <c r="M1133">
-        <v>4.78</v>
+        <v>5.06</v>
       </c>
       <c r="N1133">
-        <v>7.48</v>
+        <v>7.4</v>
       </c>
       <c r="O1133">
         <v>1</v>
@@ -58943,43 +58943,43 @@
         <v>3</v>
       </c>
       <c r="B1134" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="C1134">
-        <v>7.153770190051066</v>
+        <v>6.758293681836994</v>
       </c>
       <c r="D1134" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="E1134">
-        <v>6.841835626524307</v>
+        <v>6.910555427729958</v>
       </c>
       <c r="F1134">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1134">
-        <v>0.008086229809948935</v>
+        <v>0.007721706318163006</v>
       </c>
       <c r="H1134">
-        <v>0.007778164373475693</v>
+        <v>0.007889444572270043</v>
       </c>
       <c r="I1134">
-        <v>0.3119345635267594</v>
+        <v>0.1522617458929636</v>
       </c>
       <c r="J1134">
         <v>0.09672817633795312</v>
       </c>
       <c r="K1134">
-        <v>4.82</v>
+        <v>4.98</v>
       </c>
       <c r="L1134">
-        <v>7.62</v>
+        <v>7.24</v>
       </c>
       <c r="M1134">
-        <v>4.84</v>
+        <v>5.06</v>
       </c>
       <c r="N1134">
-        <v>7.31</v>
+        <v>7.4</v>
       </c>
       <c r="O1134">
         <v>1</v>
@@ -58993,43 +58993,43 @@
         <v>4</v>
       </c>
       <c r="B1135" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C1135">
-        <v>6.795704753577825</v>
+        <v>7.153770190051066</v>
       </c>
       <c r="D1135" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E1135">
-        <v>6.780868344760927</v>
+        <v>6.841835626524307</v>
       </c>
       <c r="F1135">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1135">
-        <v>0.007724295246422175</v>
+        <v>0.008086229809948935</v>
       </c>
       <c r="H1135">
-        <v>0.007719131655239073</v>
+        <v>0.007778164373475693</v>
       </c>
       <c r="I1135">
-        <v>-0.01483640881689752</v>
+        <v>0.3119345635267594</v>
       </c>
       <c r="J1135">
         <v>0.09672817633795312</v>
       </c>
       <c r="K1135">
-        <v>4.8</v>
+        <v>4.82</v>
       </c>
       <c r="L1135">
-        <v>7.26</v>
+        <v>7.62</v>
       </c>
       <c r="M1135">
-        <v>4.85</v>
+        <v>4.84</v>
       </c>
       <c r="N1135">
-        <v>7.25</v>
+        <v>7.31</v>
       </c>
       <c r="O1135">
         <v>1</v>
@@ -59040,96 +59040,96 @@
     </row>
     <row r="1136" spans="1:16">
       <c r="A1136" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B1136" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C1136">
-        <v>6.038657471720564</v>
+        <v>6.742802908287686</v>
       </c>
       <c r="D1136" t="s">
-        <v>305</v>
+        <v>498</v>
       </c>
       <c r="E1136">
-        <v>5.875747172057933</v>
+        <v>6.767966499470789</v>
       </c>
       <c r="F1136">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1136">
-        <v>0.009001342528279437</v>
+        <v>0.007677197091712314</v>
       </c>
       <c r="H1136">
-        <v>0.008844252827942068</v>
+        <v>0.007712033500529212</v>
       </c>
       <c r="I1136">
-        <v>0.1629102996626308</v>
+        <v>0.02516359118310252</v>
       </c>
       <c r="J1136">
-        <v>0.2910299662631506</v>
+        <v>0.09672817633795312</v>
       </c>
       <c r="K1136">
-        <v>5.09</v>
+        <v>4.83</v>
       </c>
       <c r="L1136">
-        <v>7.52</v>
+        <v>7.21</v>
       </c>
       <c r="M1136">
-        <v>5.1</v>
+        <v>4.88</v>
       </c>
       <c r="N1136">
-        <v>7.36</v>
+        <v>7.24</v>
       </c>
       <c r="O1136">
         <v>1</v>
       </c>
       <c r="P1136" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="1137" spans="1:16">
       <c r="A1137" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1137" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C1137">
-        <v>5.825747172057932</v>
+        <v>6.038657471720564</v>
       </c>
       <c r="D1137" t="s">
-        <v>499</v>
+        <v>305</v>
       </c>
       <c r="E1137">
-        <v>5.927388370708458</v>
+        <v>5.875747172057933</v>
       </c>
       <c r="F1137">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1137">
-        <v>0.008794252827942068</v>
+        <v>0.009001342528279437</v>
       </c>
       <c r="H1137">
-        <v>0.008872611629291543</v>
+        <v>0.008844252827942068</v>
       </c>
       <c r="I1137">
-        <v>0.1016411986505261</v>
+        <v>0.1629102996626308</v>
       </c>
       <c r="J1137">
         <v>0.2910299662631506</v>
       </c>
       <c r="K1137">
+        <v>5.09</v>
+      </c>
+      <c r="L1137">
+        <v>7.52</v>
+      </c>
+      <c r="M1137">
         <v>5.1</v>
       </c>
-      <c r="L1137">
-        <v>7.31</v>
-      </c>
-      <c r="M1137">
-        <v>5.06</v>
-      </c>
       <c r="N1137">
-        <v>7.4</v>
+        <v>7.36</v>
       </c>
       <c r="O1137">
         <v>1</v>
@@ -59140,13 +59140,13 @@
     </row>
     <row r="1138" spans="1:16">
       <c r="A1138" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1138" t="s">
         <v>314</v>
       </c>
       <c r="C1138">
-        <v>5.826119269696353</v>
+        <v>5.825747172057932</v>
       </c>
       <c r="D1138" t="s">
         <v>499</v>
@@ -59158,22 +59158,22 @@
         <v>1</v>
       </c>
       <c r="G1138">
-        <v>0.008753880730303648</v>
+        <v>0.008794252827942068</v>
       </c>
       <c r="H1138">
         <v>0.008872611629291543</v>
       </c>
       <c r="I1138">
-        <v>0.1012691010121056</v>
+        <v>0.1016411986505261</v>
       </c>
       <c r="J1138">
         <v>0.2910299662631506</v>
       </c>
       <c r="K1138">
-        <v>5.03</v>
+        <v>5.1</v>
       </c>
       <c r="L1138">
-        <v>7.29</v>
+        <v>7.31</v>
       </c>
       <c r="M1138">
         <v>5.06</v>
@@ -59190,7 +59190,7 @@
     </row>
     <row r="1139" spans="1:16">
       <c r="A1139" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1139" t="s">
         <v>315</v>
@@ -59240,7 +59240,7 @@
     </row>
     <row r="1140" spans="1:16">
       <c r="A1140" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1140" t="s">
         <v>316</v>
@@ -59290,13 +59290,13 @@
     </row>
     <row r="1141" spans="1:16">
       <c r="A1141" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1141" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="C1141">
-        <v>5.790670768009511</v>
+        <v>5.826119269696353</v>
       </c>
       <c r="D1141" t="s">
         <v>499</v>
@@ -59308,22 +59308,22 @@
         <v>1</v>
       </c>
       <c r="G1141">
-        <v>0.00868932923199049</v>
+        <v>0.008753880730303648</v>
       </c>
       <c r="H1141">
         <v>0.008872611629291543</v>
       </c>
       <c r="I1141">
-        <v>0.1367176026989476</v>
+        <v>0.1012691010121056</v>
       </c>
       <c r="J1141">
         <v>0.2910299662631506</v>
       </c>
       <c r="K1141">
-        <v>4.98</v>
+        <v>5.03</v>
       </c>
       <c r="L1141">
-        <v>7.24</v>
+        <v>7.29</v>
       </c>
       <c r="M1141">
         <v>5.06</v>
@@ -59340,46 +59340,46 @@
     </row>
     <row r="1142" spans="1:16">
       <c r="A1142" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1142" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C1142">
-        <v>6.08887676126214</v>
+        <v>5.790670768009511</v>
       </c>
       <c r="D1142" t="s">
-        <v>301</v>
+        <v>499</v>
       </c>
       <c r="E1142">
-        <v>6.217235562611615</v>
+        <v>5.927388370708458</v>
       </c>
       <c r="F1142">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1142">
-        <v>0.008871123238737861</v>
+        <v>0.00868932923199049</v>
       </c>
       <c r="H1142">
-        <v>0.009022764437388385</v>
+        <v>0.008872611629291543</v>
       </c>
       <c r="I1142">
-        <v>-0.1283588013494743</v>
+        <v>0.1367176026989476</v>
       </c>
       <c r="J1142">
         <v>0.2910299662631506</v>
       </c>
       <c r="K1142">
-        <v>4.78</v>
+        <v>4.98</v>
       </c>
       <c r="L1142">
-        <v>7.48</v>
+        <v>7.24</v>
       </c>
       <c r="M1142">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="N1142">
-        <v>7.62</v>
+        <v>7.4</v>
       </c>
       <c r="O1142">
         <v>1</v>
@@ -59390,46 +59390,46 @@
     </row>
     <row r="1143" spans="1:16">
       <c r="A1143" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1143" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="C1143">
-        <v>5.804325262948982</v>
+        <v>6.08887676126214</v>
       </c>
       <c r="D1143" t="s">
-        <v>498</v>
+        <v>301</v>
       </c>
       <c r="E1143">
-        <v>5.83850466362372</v>
+        <v>6.217235562611615</v>
       </c>
       <c r="F1143">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1143">
-        <v>0.008615674737051018</v>
+        <v>0.008871123238737861</v>
       </c>
       <c r="H1143">
-        <v>0.008661495336376281</v>
+        <v>0.009022764437388385</v>
       </c>
       <c r="I1143">
-        <v>0.03417940067473779</v>
+        <v>-0.1283588013494743</v>
       </c>
       <c r="J1143">
         <v>0.2910299662631506</v>
       </c>
       <c r="K1143">
-        <v>4.83</v>
+        <v>4.78</v>
       </c>
       <c r="L1143">
-        <v>7.21</v>
+        <v>7.48</v>
       </c>
       <c r="M1143">
-        <v>4.85</v>
+        <v>4.82</v>
       </c>
       <c r="N1143">
-        <v>7.25</v>
+        <v>7.62</v>
       </c>
       <c r="O1143">
         <v>1</v>
@@ -59440,96 +59440,96 @@
     </row>
     <row r="1144" spans="1:16">
       <c r="A1144" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B1144" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C1144">
-        <v>6.063408640507315</v>
+        <v>5.804325262948982</v>
       </c>
       <c r="D1144" t="s">
-        <v>305</v>
+        <v>498</v>
       </c>
       <c r="E1144">
-        <v>5.900546967895346</v>
+        <v>5.819773764635825</v>
       </c>
       <c r="F1144">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1144">
-        <v>0.008976591359492683</v>
+        <v>0.008615674737051018</v>
       </c>
       <c r="H1144">
-        <v>0.008819453032104654</v>
+        <v>0.008660226235364174</v>
       </c>
       <c r="I1144">
-        <v>0.1628616726119683</v>
+        <v>0.01544850168684331</v>
       </c>
       <c r="J1144">
-        <v>0.2861672611969911</v>
+        <v>0.2910299662631506</v>
       </c>
       <c r="K1144">
-        <v>5.09</v>
+        <v>4.83</v>
       </c>
       <c r="L1144">
-        <v>7.52</v>
+        <v>7.21</v>
       </c>
       <c r="M1144">
-        <v>5.1</v>
+        <v>4.88</v>
       </c>
       <c r="N1144">
-        <v>7.36</v>
+        <v>7.24</v>
       </c>
       <c r="O1144">
         <v>1</v>
       </c>
       <c r="P1144" t="s">
-        <v>497</v>
+        <v>631</v>
       </c>
     </row>
     <row r="1145" spans="1:16">
       <c r="A1145" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1145" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C1145">
-        <v>5.850546967895346</v>
+        <v>6.063408640507315</v>
       </c>
       <c r="D1145" t="s">
-        <v>499</v>
+        <v>305</v>
       </c>
       <c r="E1145">
-        <v>5.951993658343225</v>
+        <v>5.900546967895346</v>
       </c>
       <c r="F1145">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1145">
-        <v>0.008769453032104654</v>
+        <v>0.008976591359492683</v>
       </c>
       <c r="H1145">
-        <v>0.008848006341656776</v>
+        <v>0.008819453032104654</v>
       </c>
       <c r="I1145">
-        <v>0.1014466904478795</v>
+        <v>0.1628616726119683</v>
       </c>
       <c r="J1145">
         <v>0.2861672611969911</v>
       </c>
       <c r="K1145">
+        <v>5.09</v>
+      </c>
+      <c r="L1145">
+        <v>7.52</v>
+      </c>
+      <c r="M1145">
         <v>5.1</v>
       </c>
-      <c r="L1145">
-        <v>7.31</v>
-      </c>
-      <c r="M1145">
-        <v>5.06</v>
-      </c>
       <c r="N1145">
-        <v>7.4</v>
+        <v>7.36</v>
       </c>
       <c r="O1145">
         <v>1</v>
@@ -59540,13 +59540,13 @@
     </row>
     <row r="1146" spans="1:16">
       <c r="A1146" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1146" t="s">
         <v>314</v>
       </c>
       <c r="C1146">
-        <v>5.850578676179135</v>
+        <v>5.850546967895346</v>
       </c>
       <c r="D1146" t="s">
         <v>499</v>
@@ -59558,22 +59558,22 @@
         <v>1</v>
       </c>
       <c r="G1146">
-        <v>0.008729421323820865</v>
+        <v>0.008769453032104654</v>
       </c>
       <c r="H1146">
         <v>0.008848006341656776</v>
       </c>
       <c r="I1146">
-        <v>0.1014149821640906</v>
+        <v>0.1014466904478795</v>
       </c>
       <c r="J1146">
         <v>0.2861672611969911</v>
       </c>
       <c r="K1146">
-        <v>5.03</v>
+        <v>5.1</v>
       </c>
       <c r="L1146">
-        <v>7.29</v>
+        <v>7.31</v>
       </c>
       <c r="M1146">
         <v>5.06</v>
@@ -59590,7 +59590,7 @@
     </row>
     <row r="1147" spans="1:16">
       <c r="A1147" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1147" t="s">
         <v>315</v>
@@ -59640,7 +59640,7 @@
     </row>
     <row r="1148" spans="1:16">
       <c r="A1148" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1148" t="s">
         <v>316</v>
@@ -59690,13 +59690,13 @@
     </row>
     <row r="1149" spans="1:16">
       <c r="A1149" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1149" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="C1149">
-        <v>5.814887039238984</v>
+        <v>5.850578676179135</v>
       </c>
       <c r="D1149" t="s">
         <v>499</v>
@@ -59708,22 +59708,22 @@
         <v>1</v>
       </c>
       <c r="G1149">
-        <v>0.008665112960761017</v>
+        <v>0.008729421323820865</v>
       </c>
       <c r="H1149">
         <v>0.008848006341656776</v>
       </c>
       <c r="I1149">
-        <v>0.1371066191042409</v>
+        <v>0.1014149821640906</v>
       </c>
       <c r="J1149">
         <v>0.2861672611969911</v>
       </c>
       <c r="K1149">
-        <v>4.98</v>
+        <v>5.03</v>
       </c>
       <c r="L1149">
-        <v>7.24</v>
+        <v>7.29</v>
       </c>
       <c r="M1149">
         <v>5.06</v>
@@ -59740,46 +59740,46 @@
     </row>
     <row r="1150" spans="1:16">
       <c r="A1150" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1150" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C1150">
-        <v>6.112120491478382</v>
+        <v>5.814887039238984</v>
       </c>
       <c r="D1150" t="s">
-        <v>301</v>
+        <v>499</v>
       </c>
       <c r="E1150">
-        <v>6.240673801030503</v>
+        <v>5.951993658343225</v>
       </c>
       <c r="F1150">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1150">
-        <v>0.008847879508521618</v>
+        <v>0.008665112960761017</v>
       </c>
       <c r="H1150">
-        <v>0.008999326198969497</v>
+        <v>0.008848006341656776</v>
       </c>
       <c r="I1150">
-        <v>-0.128553309552121</v>
+        <v>0.1371066191042409</v>
       </c>
       <c r="J1150">
         <v>0.2861672611969911</v>
       </c>
       <c r="K1150">
-        <v>4.78</v>
+        <v>4.98</v>
       </c>
       <c r="L1150">
-        <v>7.48</v>
+        <v>7.24</v>
       </c>
       <c r="M1150">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="N1150">
-        <v>7.62</v>
+        <v>7.4</v>
       </c>
       <c r="O1150">
         <v>1</v>
@@ -59790,46 +59790,46 @@
     </row>
     <row r="1151" spans="1:16">
       <c r="A1151" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1151" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="C1151">
-        <v>5.827812128418532</v>
+        <v>6.112120491478382</v>
       </c>
       <c r="D1151" t="s">
-        <v>498</v>
+        <v>301</v>
       </c>
       <c r="E1151">
-        <v>5.862088783194594</v>
+        <v>6.240673801030503</v>
       </c>
       <c r="F1151">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1151">
-        <v>0.008592187871581468</v>
+        <v>0.008847879508521618</v>
       </c>
       <c r="H1151">
-        <v>0.008637911216805407</v>
+        <v>0.008999326198969497</v>
       </c>
       <c r="I1151">
-        <v>0.03427665477606112</v>
+        <v>-0.128553309552121</v>
       </c>
       <c r="J1151">
         <v>0.2861672611969911</v>
       </c>
       <c r="K1151">
-        <v>4.83</v>
+        <v>4.78</v>
       </c>
       <c r="L1151">
-        <v>7.21</v>
+        <v>7.48</v>
       </c>
       <c r="M1151">
-        <v>4.85</v>
+        <v>4.82</v>
       </c>
       <c r="N1151">
-        <v>7.25</v>
+        <v>7.62</v>
       </c>
       <c r="O1151">
         <v>1</v>
@@ -59840,96 +59840,96 @@
     </row>
     <row r="1152" spans="1:16">
       <c r="A1152" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B1152" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C1152">
-        <v>6.042400346620433</v>
+        <v>5.827812128418532</v>
       </c>
       <c r="D1152" t="s">
-        <v>305</v>
+        <v>498</v>
       </c>
       <c r="E1152">
-        <v>5.879497400346603</v>
+        <v>5.843503765358683</v>
       </c>
       <c r="F1152">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1152">
-        <v>0.008997599653379566</v>
+        <v>0.008592187871581468</v>
       </c>
       <c r="H1152">
-        <v>0.008840502599653398</v>
+        <v>0.008636496234641317</v>
       </c>
       <c r="I1152">
-        <v>0.1629029462738298</v>
+        <v>0.01569163694015074</v>
       </c>
       <c r="J1152">
-        <v>0.2902946273830191</v>
+        <v>0.2861672611969911</v>
       </c>
       <c r="K1152">
-        <v>5.09</v>
+        <v>4.83</v>
       </c>
       <c r="L1152">
-        <v>7.52</v>
+        <v>7.21</v>
       </c>
       <c r="M1152">
-        <v>5.1</v>
+        <v>4.88</v>
       </c>
       <c r="N1152">
-        <v>7.36</v>
+        <v>7.24</v>
       </c>
       <c r="O1152">
         <v>1</v>
       </c>
       <c r="P1152" t="s">
-        <v>632</v>
+        <v>497</v>
       </c>
     </row>
     <row r="1153" spans="1:16">
       <c r="A1153" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1153" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C1153">
-        <v>5.829497400346602</v>
+        <v>6.042400346620433</v>
       </c>
       <c r="D1153" t="s">
-        <v>499</v>
+        <v>305</v>
       </c>
       <c r="E1153">
-        <v>5.931109185441923</v>
+        <v>5.879497400346603</v>
       </c>
       <c r="F1153">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1153">
-        <v>0.008790502599653397</v>
+        <v>0.008997599653379566</v>
       </c>
       <c r="H1153">
-        <v>0.008868890814558076</v>
+        <v>0.008840502599653398</v>
       </c>
       <c r="I1153">
-        <v>0.1016117850953213</v>
+        <v>0.1629029462738298</v>
       </c>
       <c r="J1153">
         <v>0.2902946273830191</v>
       </c>
       <c r="K1153">
+        <v>5.09</v>
+      </c>
+      <c r="L1153">
+        <v>7.52</v>
+      </c>
+      <c r="M1153">
         <v>5.1</v>
       </c>
-      <c r="L1153">
-        <v>7.31</v>
-      </c>
-      <c r="M1153">
-        <v>5.06</v>
-      </c>
       <c r="N1153">
-        <v>7.4</v>
+        <v>7.36</v>
       </c>
       <c r="O1153">
         <v>1</v>
@@ -59940,13 +59940,13 @@
     </row>
     <row r="1154" spans="1:16">
       <c r="A1154" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1154" t="s">
         <v>314</v>
       </c>
       <c r="C1154">
-        <v>5.829818024263414</v>
+        <v>5.829497400346602</v>
       </c>
       <c r="D1154" t="s">
         <v>499</v>
@@ -59958,22 +59958,22 @@
         <v>1</v>
       </c>
       <c r="G1154">
-        <v>0.008750181975736586</v>
+        <v>0.008790502599653397</v>
       </c>
       <c r="H1154">
         <v>0.008868890814558076</v>
       </c>
       <c r="I1154">
-        <v>0.1012911611785094</v>
+        <v>0.1016117850953213</v>
       </c>
       <c r="J1154">
         <v>0.2902946273830191</v>
       </c>
       <c r="K1154">
-        <v>5.03</v>
+        <v>5.1</v>
       </c>
       <c r="L1154">
-        <v>7.29</v>
+        <v>7.31</v>
       </c>
       <c r="M1154">
         <v>5.06</v>
@@ -59990,7 +59990,7 @@
     </row>
     <row r="1155" spans="1:16">
       <c r="A1155" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1155" t="s">
         <v>315</v>
@@ -60040,7 +60040,7 @@
     </row>
     <row r="1156" spans="1:16">
       <c r="A1156" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1156" t="s">
         <v>316</v>
@@ -60090,13 +60090,13 @@
     </row>
     <row r="1157" spans="1:16">
       <c r="A1157" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1157" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="C1157">
-        <v>5.794332755632565</v>
+        <v>5.829818024263414</v>
       </c>
       <c r="D1157" t="s">
         <v>499</v>
@@ -60108,22 +60108,22 @@
         <v>1</v>
       </c>
       <c r="G1157">
-        <v>0.008685667244367435</v>
+        <v>0.008750181975736586</v>
       </c>
       <c r="H1157">
         <v>0.008868890814558076</v>
       </c>
       <c r="I1157">
-        <v>0.1367764298093581</v>
+        <v>0.1012911611785094</v>
       </c>
       <c r="J1157">
         <v>0.2902946273830191</v>
       </c>
       <c r="K1157">
-        <v>4.98</v>
+        <v>5.03</v>
       </c>
       <c r="L1157">
-        <v>7.24</v>
+        <v>7.29</v>
       </c>
       <c r="M1157">
         <v>5.06</v>
@@ -60140,46 +60140,46 @@
     </row>
     <row r="1158" spans="1:16">
       <c r="A1158" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1158" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C1158">
-        <v>6.092391681109169</v>
+        <v>5.794332755632565</v>
       </c>
       <c r="D1158" t="s">
-        <v>301</v>
+        <v>499</v>
       </c>
       <c r="E1158">
-        <v>6.220779896013848</v>
+        <v>5.931109185441923</v>
       </c>
       <c r="F1158">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1158">
-        <v>0.008867608318890833</v>
+        <v>0.008685667244367435</v>
       </c>
       <c r="H1158">
-        <v>0.009019220103986153</v>
+        <v>0.008868890814558076</v>
       </c>
       <c r="I1158">
-        <v>-0.1283882149046791</v>
+        <v>0.1367764298093581</v>
       </c>
       <c r="J1158">
         <v>0.2902946273830191</v>
       </c>
       <c r="K1158">
-        <v>4.78</v>
+        <v>4.98</v>
       </c>
       <c r="L1158">
-        <v>7.48</v>
+        <v>7.24</v>
       </c>
       <c r="M1158">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="N1158">
-        <v>7.62</v>
+        <v>7.4</v>
       </c>
       <c r="O1158">
         <v>1</v>
@@ -60190,46 +60190,46 @@
     </row>
     <row r="1159" spans="1:16">
       <c r="A1159" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1159" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="C1159">
-        <v>5.807876949740018</v>
+        <v>6.092391681109169</v>
       </c>
       <c r="D1159" t="s">
-        <v>498</v>
+        <v>301</v>
       </c>
       <c r="E1159">
-        <v>5.842071057192357</v>
+        <v>6.220779896013848</v>
       </c>
       <c r="F1159">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1159">
-        <v>0.008612123050259981</v>
+        <v>0.008867608318890833</v>
       </c>
       <c r="H1159">
-        <v>0.008657928942807643</v>
+        <v>0.009019220103986153</v>
       </c>
       <c r="I1159">
-        <v>0.03419410745233975</v>
+        <v>-0.1283882149046791</v>
       </c>
       <c r="J1159">
         <v>0.2902946273830191</v>
       </c>
       <c r="K1159">
-        <v>4.83</v>
+        <v>4.78</v>
       </c>
       <c r="L1159">
-        <v>7.21</v>
+        <v>7.48</v>
       </c>
       <c r="M1159">
-        <v>4.85</v>
+        <v>4.82</v>
       </c>
       <c r="N1159">
-        <v>7.25</v>
+        <v>7.62</v>
       </c>
       <c r="O1159">
         <v>1</v>
@@ -60240,96 +60240,96 @@
     </row>
     <row r="1160" spans="1:16">
       <c r="A1160" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B1160" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C1160">
-        <v>5.35524754596201</v>
+        <v>5.807876949740018</v>
       </c>
       <c r="D1160" t="s">
-        <v>299</v>
+        <v>498</v>
       </c>
       <c r="E1160">
-        <v>5.235476883529267</v>
+        <v>5.823362218370867</v>
       </c>
       <c r="F1160">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1160">
-        <v>0.009684752454037989</v>
+        <v>0.008612123050259981</v>
       </c>
       <c r="H1160">
-        <v>0.009624523116470734</v>
+        <v>0.008656637781629133</v>
       </c>
       <c r="I1160">
-        <v>0.1197706624327433</v>
+        <v>0.01548526863084909</v>
       </c>
       <c r="J1160">
-        <v>0.4252951776106071</v>
+        <v>0.2902946273830191</v>
       </c>
       <c r="K1160">
-        <v>5.09</v>
+        <v>4.83</v>
       </c>
       <c r="L1160">
-        <v>7.52</v>
+        <v>7.21</v>
       </c>
       <c r="M1160">
-        <v>5.16</v>
+        <v>4.88</v>
       </c>
       <c r="N1160">
-        <v>7.43</v>
+        <v>7.24</v>
       </c>
       <c r="O1160">
         <v>1</v>
       </c>
       <c r="P1160" t="s">
-        <v>297</v>
+        <v>632</v>
       </c>
     </row>
     <row r="1161" spans="1:16">
       <c r="A1161" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1161" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C1161">
-        <v>5.140994594185903</v>
+        <v>5.35524754596201</v>
       </c>
       <c r="D1161" t="s">
-        <v>499</v>
+        <v>299</v>
       </c>
       <c r="E1161">
-        <v>5.248006401290329</v>
+        <v>5.235476883529267</v>
       </c>
       <c r="F1161">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1161">
-        <v>0.009479005405814096</v>
+        <v>0.009684752454037989</v>
       </c>
       <c r="H1161">
-        <v>0.009551993598709672</v>
+        <v>0.009624523116470734</v>
       </c>
       <c r="I1161">
-        <v>0.1070118071044259</v>
+        <v>0.1197706624327433</v>
       </c>
       <c r="J1161">
         <v>0.4252951776106071</v>
       </c>
       <c r="K1161">
-        <v>5.1</v>
+        <v>5.09</v>
       </c>
       <c r="L1161">
-        <v>7.31</v>
+        <v>7.52</v>
       </c>
       <c r="M1161">
-        <v>5.06</v>
+        <v>5.16</v>
       </c>
       <c r="N1161">
-        <v>7.4</v>
+        <v>7.43</v>
       </c>
       <c r="O1161">
         <v>1</v>
@@ -60340,13 +60340,13 @@
     </row>
     <row r="1162" spans="1:16">
       <c r="A1162" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1162" t="s">
         <v>314</v>
       </c>
       <c r="C1162">
-        <v>5.150765256618646</v>
+        <v>5.140994594185903</v>
       </c>
       <c r="D1162" t="s">
         <v>499</v>
@@ -60358,22 +60358,22 @@
         <v>1</v>
       </c>
       <c r="G1162">
-        <v>0.009429234743381355</v>
+        <v>0.009479005405814096</v>
       </c>
       <c r="H1162">
         <v>0.009551993598709672</v>
       </c>
       <c r="I1162">
-        <v>0.09724114467168299</v>
+        <v>0.1070118071044259</v>
       </c>
       <c r="J1162">
         <v>0.4252951776106071</v>
       </c>
       <c r="K1162">
-        <v>5.03</v>
+        <v>5.1</v>
       </c>
       <c r="L1162">
-        <v>7.29</v>
+        <v>7.31</v>
       </c>
       <c r="M1162">
         <v>5.06</v>
@@ -60390,7 +60390,7 @@
     </row>
     <row r="1163" spans="1:16">
       <c r="A1163" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1163" t="s">
         <v>315</v>
@@ -60440,7 +60440,7 @@
     </row>
     <row r="1164" spans="1:16">
       <c r="A1164" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1164" t="s">
         <v>316</v>
@@ -60490,13 +60490,13 @@
     </row>
     <row r="1165" spans="1:16">
       <c r="A1165" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1165" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="C1165">
-        <v>5.122030015499177</v>
+        <v>5.150765256618646</v>
       </c>
       <c r="D1165" t="s">
         <v>499</v>
@@ -60508,22 +60508,22 @@
         <v>1</v>
       </c>
       <c r="G1165">
-        <v>0.009357969984500824</v>
+        <v>0.009429234743381355</v>
       </c>
       <c r="H1165">
         <v>0.009551993598709672</v>
       </c>
       <c r="I1165">
-        <v>0.1259763857911524</v>
+        <v>0.09724114467168299</v>
       </c>
       <c r="J1165">
         <v>0.4252951776106071</v>
       </c>
       <c r="K1165">
-        <v>4.98</v>
+        <v>5.03</v>
       </c>
       <c r="L1165">
-        <v>7.24</v>
+        <v>7.29</v>
       </c>
       <c r="M1165">
         <v>5.06</v>
@@ -60540,46 +60540,46 @@
     </row>
     <row r="1166" spans="1:16">
       <c r="A1166" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1166" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="C1166">
-        <v>5.342606761677935</v>
+        <v>5.122030015499177</v>
       </c>
       <c r="D1166" t="s">
-        <v>301</v>
+        <v>499</v>
       </c>
       <c r="E1166">
-        <v>5.570077243916874</v>
+        <v>5.248006401290329</v>
       </c>
       <c r="F1166">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1166">
-        <v>0.009357393238322064</v>
+        <v>0.009357969984500824</v>
       </c>
       <c r="H1166">
-        <v>0.009669922756083126</v>
+        <v>0.009551993598709672</v>
       </c>
       <c r="I1166">
-        <v>-0.2274704822389388</v>
+        <v>0.1259763857911524</v>
       </c>
       <c r="J1166">
         <v>0.4252951776106071</v>
       </c>
       <c r="K1166">
-        <v>4.72</v>
+        <v>4.98</v>
       </c>
       <c r="L1166">
-        <v>7.35</v>
+        <v>7.24</v>
       </c>
       <c r="M1166">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="N1166">
-        <v>7.62</v>
+        <v>7.4</v>
       </c>
       <c r="O1166">
         <v>1</v>
@@ -60590,46 +60590,46 @@
     </row>
     <row r="1167" spans="1:16">
       <c r="A1167" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1167" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C1167">
-        <v>5.155824292140768</v>
+        <v>5.342606761677935</v>
       </c>
       <c r="D1167" t="s">
-        <v>498</v>
+        <v>301</v>
       </c>
       <c r="E1167">
-        <v>5.187318388588556</v>
+        <v>5.570077243916874</v>
       </c>
       <c r="F1167">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1167">
-        <v>0.009264175707859233</v>
+        <v>0.009357393238322064</v>
       </c>
       <c r="H1167">
-        <v>0.009312681611411444</v>
+        <v>0.009669922756083126</v>
       </c>
       <c r="I1167">
-        <v>0.03149409644778878</v>
+        <v>-0.2274704822389388</v>
       </c>
       <c r="J1167">
         <v>0.4252951776106071</v>
       </c>
       <c r="K1167">
-        <v>4.83</v>
+        <v>4.72</v>
       </c>
       <c r="L1167">
-        <v>7.21</v>
+        <v>7.35</v>
       </c>
       <c r="M1167">
-        <v>4.85</v>
+        <v>4.82</v>
       </c>
       <c r="N1167">
-        <v>7.25</v>
+        <v>7.62</v>
       </c>
       <c r="O1167">
         <v>1</v>
@@ -60643,7 +60643,7 @@
         <v>0</v>
       </c>
       <c r="B1168" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C1168">
         <v>4.869243033976865</v>
@@ -60693,7 +60693,7 @@
         <v>1</v>
       </c>
       <c r="B1169" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C1169">
         <v>4.882743619785026</v>
@@ -60743,7 +60743,7 @@
         <v>2</v>
       </c>
       <c r="B1170" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C1170">
         <v>4.882743619785026</v>
@@ -60793,7 +60793,7 @@
         <v>3</v>
       </c>
       <c r="B1171" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C1171">
         <v>4.882743619785026</v>
@@ -60943,7 +60943,7 @@
         <v>0</v>
       </c>
       <c r="B1174" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C1174">
         <v>4.646081578409318</v>
@@ -60993,7 +60993,7 @@
         <v>1</v>
       </c>
       <c r="B1175" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C1175">
         <v>4.662645164588014</v>
@@ -61043,7 +61043,7 @@
         <v>2</v>
       </c>
       <c r="B1176" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C1176">
         <v>4.662645164588014</v>
@@ -61093,7 +61093,7 @@
         <v>3</v>
       </c>
       <c r="B1177" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C1177">
         <v>4.662645164588014</v>
@@ -61293,7 +61293,7 @@
         <v>0</v>
       </c>
       <c r="B1181" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C1181">
         <v>4.194367974425276</v>
@@ -61343,7 +61343,7 @@
         <v>1</v>
       </c>
       <c r="B1182" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C1182">
         <v>4.21713155124689</v>
@@ -61393,7 +61393,7 @@
         <v>2</v>
       </c>
       <c r="B1183" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C1183">
         <v>4.21713155124689</v>
@@ -61443,7 +61443,7 @@
         <v>3</v>
       </c>
       <c r="B1184" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C1184">
         <v>4.21713155124689</v>
@@ -61643,7 +61643,7 @@
         <v>0</v>
       </c>
       <c r="B1188" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C1188">
         <v>4.579720961796916</v>
@@ -61893,43 +61893,43 @@
         <v>0</v>
       </c>
       <c r="B1193" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C1193">
-        <v>5.044725274725279</v>
+        <v>4.844065934065937</v>
       </c>
       <c r="D1193" t="s">
-        <v>299</v>
+        <v>499</v>
       </c>
       <c r="E1193">
-        <v>4.935054945054947</v>
+        <v>4.953406593406597</v>
       </c>
       <c r="F1193">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1193">
-        <v>0.01001527472527472</v>
+        <v>0.009775934065934064</v>
       </c>
       <c r="H1193">
-        <v>0.009924945054945053</v>
+        <v>0.009846593406593404</v>
       </c>
       <c r="I1193">
-        <v>0.1096703296703314</v>
+        <v>0.1093406593406598</v>
       </c>
       <c r="J1193">
         <v>0.4835164835164829</v>
       </c>
       <c r="K1193">
-        <v>5.14</v>
+        <v>5.1</v>
       </c>
       <c r="L1193">
-        <v>7.53</v>
+        <v>7.31</v>
       </c>
       <c r="M1193">
-        <v>5.16</v>
+        <v>5.06</v>
       </c>
       <c r="N1193">
-        <v>7.43</v>
+        <v>7.4</v>
       </c>
       <c r="O1193">
         <v>1</v>
@@ -61943,10 +61943,10 @@
         <v>1</v>
       </c>
       <c r="B1194" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C1194">
-        <v>4.844065934065937</v>
+        <v>4.812417582417586</v>
       </c>
       <c r="D1194" t="s">
         <v>499</v>
@@ -61958,22 +61958,22 @@
         <v>1</v>
       </c>
       <c r="G1194">
-        <v>0.009775934065934064</v>
+        <v>0.009647582417582415</v>
       </c>
       <c r="H1194">
         <v>0.009846593406593404</v>
       </c>
       <c r="I1194">
-        <v>0.1093406593406598</v>
+        <v>0.1409890109890108</v>
       </c>
       <c r="J1194">
         <v>0.4835164835164829</v>
       </c>
       <c r="K1194">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L1194">
-        <v>7.31</v>
+        <v>7.23</v>
       </c>
       <c r="M1194">
         <v>5.06</v>
@@ -61993,10 +61993,10 @@
         <v>2</v>
       </c>
       <c r="B1195" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C1195">
-        <v>4.812417582417586</v>
+        <v>4.832087912087915</v>
       </c>
       <c r="D1195" t="s">
         <v>499</v>
@@ -62008,22 +62008,22 @@
         <v>1</v>
       </c>
       <c r="G1195">
-        <v>0.009647582417582415</v>
+        <v>0.009647912087912087</v>
       </c>
       <c r="H1195">
         <v>0.009846593406593404</v>
       </c>
       <c r="I1195">
-        <v>0.1409890109890108</v>
+        <v>0.121318681318682</v>
       </c>
       <c r="J1195">
         <v>0.4835164835164829</v>
       </c>
       <c r="K1195">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="L1195">
-        <v>7.23</v>
+        <v>7.24</v>
       </c>
       <c r="M1195">
         <v>5.06</v>
@@ -62043,43 +62043,43 @@
         <v>3</v>
       </c>
       <c r="B1196" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="C1196">
-        <v>4.832087912087915</v>
+        <v>5.04615384615385</v>
       </c>
       <c r="D1196" t="s">
-        <v>499</v>
+        <v>301</v>
       </c>
       <c r="E1196">
-        <v>4.953406593406597</v>
+        <v>5.289450549450552</v>
       </c>
       <c r="F1196">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1196">
-        <v>0.009647912087912087</v>
+        <v>0.009513846153846151</v>
       </c>
       <c r="H1196">
-        <v>0.009846593406593404</v>
+        <v>0.00995054945054945</v>
       </c>
       <c r="I1196">
-        <v>0.121318681318682</v>
+        <v>-0.2432967032967026</v>
       </c>
       <c r="J1196">
         <v>0.4835164835164829</v>
       </c>
       <c r="K1196">
-        <v>4.98</v>
+        <v>4.62</v>
       </c>
       <c r="L1196">
-        <v>7.24</v>
+        <v>7.28</v>
       </c>
       <c r="M1196">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="N1196">
-        <v>7.4</v>
+        <v>7.62</v>
       </c>
       <c r="O1196">
         <v>1</v>
@@ -62093,10 +62093,10 @@
         <v>4</v>
       </c>
       <c r="B1197" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C1197">
-        <v>5.04615384615385</v>
+        <v>5.0678021978022</v>
       </c>
       <c r="D1197" t="s">
         <v>301</v>
@@ -62108,22 +62108,22 @@
         <v>-1</v>
       </c>
       <c r="G1197">
-        <v>0.009513846153846151</v>
+        <v>0.0096321978021978</v>
       </c>
       <c r="H1197">
         <v>0.00995054945054945</v>
       </c>
       <c r="I1197">
-        <v>-0.2432967032967026</v>
+        <v>-0.2216483516483523</v>
       </c>
       <c r="J1197">
         <v>0.4835164835164829</v>
       </c>
       <c r="K1197">
-        <v>4.62</v>
+        <v>4.72</v>
       </c>
       <c r="L1197">
-        <v>7.28</v>
+        <v>7.35</v>
       </c>
       <c r="M1197">
         <v>4.82</v>
@@ -62140,63 +62140,63 @@
     </row>
     <row r="1198" spans="1:16">
       <c r="A1198" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1198" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C1198">
-        <v>5.0678021978022</v>
+        <v>4.976232772849881</v>
       </c>
       <c r="D1198" t="s">
-        <v>301</v>
+        <v>499</v>
       </c>
       <c r="E1198">
-        <v>5.289450549450552</v>
+        <v>5.084536829533412</v>
       </c>
       <c r="F1198">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1198">
-        <v>0.0096321978021978</v>
+        <v>0.009643767227150117</v>
       </c>
       <c r="H1198">
-        <v>0.00995054945054945</v>
+        <v>0.009715463170466588</v>
       </c>
       <c r="I1198">
-        <v>-0.2216483516483523</v>
+        <v>0.1083040566835312</v>
       </c>
       <c r="J1198">
-        <v>0.4835164835164829</v>
+        <v>0.4576014170882586</v>
       </c>
       <c r="K1198">
-        <v>4.72</v>
+        <v>5.1</v>
       </c>
       <c r="L1198">
-        <v>7.35</v>
+        <v>7.31</v>
       </c>
       <c r="M1198">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="N1198">
-        <v>7.62</v>
+        <v>7.4</v>
       </c>
       <c r="O1198">
         <v>1</v>
       </c>
       <c r="P1198" t="s">
-        <v>636</v>
+        <v>313</v>
       </c>
     </row>
     <row r="1199" spans="1:16">
       <c r="A1199" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1199" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C1199">
-        <v>4.976232772849881</v>
+        <v>4.941992914558707</v>
       </c>
       <c r="D1199" t="s">
         <v>499</v>
@@ -62208,22 +62208,22 @@
         <v>1</v>
       </c>
       <c r="G1199">
-        <v>0.009643767227150117</v>
+        <v>0.009518007085441295</v>
       </c>
       <c r="H1199">
         <v>0.009715463170466588</v>
       </c>
       <c r="I1199">
-        <v>0.1083040566835312</v>
+        <v>0.1425439149747048</v>
       </c>
       <c r="J1199">
         <v>0.4576014170882586</v>
       </c>
       <c r="K1199">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L1199">
-        <v>7.31</v>
+        <v>7.23</v>
       </c>
       <c r="M1199">
         <v>5.06</v>
@@ -62235,18 +62235,18 @@
         <v>1</v>
       </c>
       <c r="P1199" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="1200" spans="1:16">
       <c r="A1200" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1200" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C1200">
-        <v>4.941992914558707</v>
+        <v>4.961144942900471</v>
       </c>
       <c r="D1200" t="s">
         <v>499</v>
@@ -62258,22 +62258,22 @@
         <v>1</v>
       </c>
       <c r="G1200">
-        <v>0.009518007085441295</v>
+        <v>0.00951885505709953</v>
       </c>
       <c r="H1200">
         <v>0.009715463170466588</v>
       </c>
       <c r="I1200">
-        <v>0.1425439149747048</v>
+        <v>0.1233918866329402</v>
       </c>
       <c r="J1200">
         <v>0.4576014170882586</v>
       </c>
       <c r="K1200">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="L1200">
-        <v>7.23</v>
+        <v>7.24</v>
       </c>
       <c r="M1200">
         <v>5.06</v>
@@ -62285,62 +62285,62 @@
         <v>1</v>
       </c>
       <c r="P1200" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="1201" spans="1:16">
       <c r="A1201" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1201" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="C1201">
-        <v>4.961144942900471</v>
+        <v>5.165881453052245</v>
       </c>
       <c r="D1201" t="s">
-        <v>499</v>
+        <v>301</v>
       </c>
       <c r="E1201">
-        <v>5.084536829533412</v>
+        <v>5.414361169634594</v>
       </c>
       <c r="F1201">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1201">
-        <v>0.00951885505709953</v>
+        <v>0.009394118546947756</v>
       </c>
       <c r="H1201">
-        <v>0.009715463170466588</v>
+        <v>0.009825638830365406</v>
       </c>
       <c r="I1201">
-        <v>0.1233918866329402</v>
+        <v>-0.2484797165823487</v>
       </c>
       <c r="J1201">
         <v>0.4576014170882586</v>
       </c>
       <c r="K1201">
-        <v>4.98</v>
+        <v>4.62</v>
       </c>
       <c r="L1201">
-        <v>7.24</v>
+        <v>7.28</v>
       </c>
       <c r="M1201">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="N1201">
-        <v>7.4</v>
+        <v>7.62</v>
       </c>
       <c r="O1201">
         <v>1</v>
       </c>
       <c r="P1201" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="1202" spans="1:16">
       <c r="A1202" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1202" t="s">
         <v>318</v>
@@ -62385,7 +62385,7 @@
         <v>1</v>
       </c>
       <c r="P1202" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="1203" spans="1:16">
@@ -63035,7 +63035,7 @@
         <v>1</v>
       </c>
       <c r="P1215" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="1216" spans="1:16">
@@ -63085,7 +63085,7 @@
         <v>1</v>
       </c>
       <c r="P1216" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="1217" spans="1:16">
@@ -63135,7 +63135,7 @@
         <v>1</v>
       </c>
       <c r="P1217" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="1218" spans="1:16">
@@ -63335,7 +63335,7 @@
         <v>1</v>
       </c>
       <c r="P1221" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1222" spans="1:16">
@@ -63385,7 +63385,7 @@
         <v>1</v>
       </c>
       <c r="P1222" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1223" spans="1:16">
@@ -63393,10 +63393,10 @@
         <v>2</v>
       </c>
       <c r="B1223" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="C1223">
-        <v>5.903891457489198</v>
+        <v>5.793675246725735</v>
       </c>
       <c r="D1223" t="s">
         <v>301</v>
@@ -63408,22 +63408,22 @@
         <v>-1</v>
       </c>
       <c r="G1223">
-        <v>0.009056108542510802</v>
+        <v>0.008906324753274264</v>
       </c>
       <c r="H1223">
         <v>0.009209297735335159</v>
       </c>
       <c r="I1223">
-        <v>-0.1268108071756417</v>
+        <v>-0.2370270179391047</v>
       </c>
       <c r="J1223">
         <v>0.3297298206089543</v>
       </c>
       <c r="K1223">
-        <v>4.78</v>
+        <v>4.72</v>
       </c>
       <c r="L1223">
-        <v>7.48</v>
+        <v>7.35</v>
       </c>
       <c r="M1223">
         <v>4.82</v>
@@ -63435,7 +63435,7 @@
         <v>1</v>
       </c>
       <c r="P1223" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3720" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3729" uniqueCount="641">
   <si>
     <t>trade_time</t>
   </si>
@@ -952,13 +952,13 @@
     <t>2021-08-20</t>
   </si>
   <si>
+    <t>2021-06-22</t>
+  </si>
+  <si>
     <t>2021-06-25</t>
   </si>
   <si>
     <t>2021-06-16</t>
-  </si>
-  <si>
-    <t>2021-06-22</t>
   </si>
   <si>
     <t>2021-07-05</t>
@@ -1516,7 +1516,7 @@
     <t>2021-06-09</t>
   </si>
   <si>
-    <t>2021-08-23</t>
+    <t>2021-08-24</t>
   </si>
   <si>
     <t>2021-07-23</t>
@@ -2294,7 +2294,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1236"/>
+  <dimension ref="A1:P1239"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -58108,7 +58108,7 @@
         <v>500</v>
       </c>
       <c r="E1117">
-        <v>6.849804278561669</v>
+        <v>6.850658852981332</v>
       </c>
       <c r="F1117">
         <v>1</v>
@@ -58117,10 +58117,10 @@
         <v>0.007622759444697321</v>
       </c>
       <c r="H1117">
-        <v>0.007670195721438331</v>
+        <v>0.007669341147018668</v>
       </c>
       <c r="I1117">
-        <v>0.05256372325898973</v>
+        <v>0.05341829767865303</v>
       </c>
       <c r="J1117">
         <v>0.08545744196631905</v>
@@ -58132,7 +58132,7 @@
         <v>7.21</v>
       </c>
       <c r="M1117">
-        <v>4.8</v>
+        <v>4.79</v>
       </c>
       <c r="N1117">
         <v>7.26</v>
@@ -58158,7 +58158,7 @@
         <v>500</v>
       </c>
       <c r="E1118">
-        <v>6.849804278561669</v>
+        <v>6.850658852981332</v>
       </c>
       <c r="F1118">
         <v>1</v>
@@ -58167,10 +58167,10 @@
         <v>0.007657631998179342</v>
       </c>
       <c r="H1118">
-        <v>0.007670195721438331</v>
+        <v>0.007669341147018668</v>
       </c>
       <c r="I1118">
-        <v>0.007436276741010772</v>
+        <v>0.008290851160674073</v>
       </c>
       <c r="J1118">
         <v>0.08545744196631905</v>
@@ -58182,7 +58182,7 @@
         <v>7.25</v>
       </c>
       <c r="M1118">
-        <v>4.8</v>
+        <v>4.79</v>
       </c>
       <c r="N1118">
         <v>7.26</v>
@@ -58199,43 +58199,43 @@
         <v>0</v>
       </c>
       <c r="B1119" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C1119">
-        <v>7.041349143640623</v>
+        <v>6.724492342729653</v>
       </c>
       <c r="D1119" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="E1119">
-        <v>6.882360158955165</v>
+        <v>6.996734679649548</v>
       </c>
       <c r="F1119">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1119">
-        <v>0.008078650856359375</v>
+        <v>0.007735507657270347</v>
       </c>
       <c r="H1119">
-        <v>0.007917639841044837</v>
+        <v>0.007963265320350453</v>
       </c>
       <c r="I1119">
-        <v>0.1589889846854584</v>
+        <v>0.272242336919895</v>
       </c>
       <c r="J1119">
         <v>0.1011015314540694</v>
       </c>
       <c r="K1119">
-        <v>5.13</v>
+        <v>5</v>
       </c>
       <c r="L1119">
-        <v>7.56</v>
+        <v>7.23</v>
       </c>
       <c r="M1119">
-        <v>5.12</v>
+        <v>4.78</v>
       </c>
       <c r="N1119">
-        <v>7.4</v>
+        <v>7.48</v>
       </c>
       <c r="O1119">
         <v>1</v>
@@ -58249,10 +58249,10 @@
         <v>1</v>
       </c>
       <c r="B1120" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C1120">
-        <v>6.724492342729653</v>
+        <v>6.736514373358735</v>
       </c>
       <c r="D1120" t="s">
         <v>306</v>
@@ -58264,22 +58264,22 @@
         <v>1</v>
       </c>
       <c r="G1120">
-        <v>0.007735507657270347</v>
+        <v>0.007743485626641266</v>
       </c>
       <c r="H1120">
         <v>0.007963265320350453</v>
       </c>
       <c r="I1120">
-        <v>0.272242336919895</v>
+        <v>0.2602203062908135</v>
       </c>
       <c r="J1120">
         <v>0.1011015314540694</v>
       </c>
       <c r="K1120">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="L1120">
-        <v>7.23</v>
+        <v>7.24</v>
       </c>
       <c r="M1120">
         <v>4.78</v>
@@ -58299,43 +58299,43 @@
         <v>2</v>
       </c>
       <c r="B1121" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C1121">
-        <v>6.736514373358735</v>
+        <v>7.132690618391385</v>
       </c>
       <c r="D1121" t="s">
-        <v>306</v>
+        <v>498</v>
       </c>
       <c r="E1121">
-        <v>6.996734679649548</v>
+        <v>6.820668587762303</v>
       </c>
       <c r="F1121">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1121">
-        <v>0.007743485626641266</v>
+        <v>0.008107309381608616</v>
       </c>
       <c r="H1121">
-        <v>0.007963265320350453</v>
+        <v>0.007799331412237696</v>
       </c>
       <c r="I1121">
-        <v>0.2602203062908135</v>
+        <v>0.3120220306290822</v>
       </c>
       <c r="J1121">
         <v>0.1011015314540694</v>
       </c>
       <c r="K1121">
-        <v>4.98</v>
+        <v>4.82</v>
       </c>
       <c r="L1121">
-        <v>7.24</v>
+        <v>7.62</v>
       </c>
       <c r="M1121">
-        <v>4.78</v>
+        <v>4.84</v>
       </c>
       <c r="N1121">
-        <v>7.48</v>
+        <v>7.31</v>
       </c>
       <c r="O1121">
         <v>1</v>
@@ -58349,43 +58349,43 @@
         <v>3</v>
       </c>
       <c r="B1122" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="C1122">
-        <v>7.132690618391385</v>
+        <v>6.721679603076844</v>
       </c>
       <c r="D1122" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E1122">
-        <v>6.820668587762303</v>
+        <v>6.775723664335008</v>
       </c>
       <c r="F1122">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1122">
-        <v>0.008107309381608616</v>
+        <v>0.007698320396923156</v>
       </c>
       <c r="H1122">
-        <v>0.007799331412237696</v>
+        <v>0.007744276335664992</v>
       </c>
       <c r="I1122">
-        <v>0.3120220306290822</v>
+        <v>0.05404406125816319</v>
       </c>
       <c r="J1122">
         <v>0.1011015314540694</v>
       </c>
       <c r="K1122">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="L1122">
-        <v>7.62</v>
+        <v>7.21</v>
       </c>
       <c r="M1122">
-        <v>4.84</v>
+        <v>4.79</v>
       </c>
       <c r="N1122">
-        <v>7.31</v>
+        <v>7.26</v>
       </c>
       <c r="O1122">
         <v>1</v>
@@ -58396,146 +58396,146 @@
     </row>
     <row r="1123" spans="1:16">
       <c r="A1123" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1123" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C1123">
-        <v>6.721679603076844</v>
+        <v>6.670956543963923</v>
       </c>
       <c r="D1123" t="s">
-        <v>500</v>
+        <v>306</v>
       </c>
       <c r="E1123">
-        <v>6.774712649020467</v>
+        <v>6.945554456029511</v>
       </c>
       <c r="F1123">
         <v>1</v>
       </c>
       <c r="G1123">
-        <v>0.007698320396923156</v>
+        <v>0.007789043456036078</v>
       </c>
       <c r="H1123">
-        <v>0.007745287350979533</v>
+        <v>0.00801444554397049</v>
       </c>
       <c r="I1123">
-        <v>0.05303304594362235</v>
+        <v>0.2745979120655875</v>
       </c>
       <c r="J1123">
-        <v>0.1011015314540694</v>
+        <v>0.1118086912072155</v>
       </c>
       <c r="K1123">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="L1123">
-        <v>7.21</v>
+        <v>7.23</v>
       </c>
       <c r="M1123">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="N1123">
-        <v>7.26</v>
+        <v>7.48</v>
       </c>
       <c r="O1123">
         <v>1</v>
       </c>
       <c r="P1123" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="1124" spans="1:16">
       <c r="A1124" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B1124" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C1124">
-        <v>6.767745694964089</v>
+        <v>6.683192717788067</v>
       </c>
       <c r="D1124" t="s">
-        <v>500</v>
+        <v>306</v>
       </c>
       <c r="E1124">
-        <v>6.774712649020467</v>
+        <v>6.945554456029511</v>
       </c>
       <c r="F1124">
         <v>1</v>
       </c>
       <c r="G1124">
-        <v>0.007732254305035911</v>
+        <v>0.007796807282211934</v>
       </c>
       <c r="H1124">
-        <v>0.007745287350979533</v>
+        <v>0.00801444554397049</v>
       </c>
       <c r="I1124">
-        <v>0.00696695405637815</v>
+        <v>0.2623617382414434</v>
       </c>
       <c r="J1124">
-        <v>0.1011015314540694</v>
+        <v>0.1118086912072155</v>
       </c>
       <c r="K1124">
-        <v>4.77</v>
+        <v>4.98</v>
       </c>
       <c r="L1124">
-        <v>7.25</v>
+        <v>7.24</v>
       </c>
       <c r="M1124">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="N1124">
-        <v>7.26</v>
+        <v>7.48</v>
       </c>
       <c r="O1124">
         <v>1</v>
       </c>
       <c r="P1124" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="1125" spans="1:16">
       <c r="A1125" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1125" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="C1125">
-        <v>6.670956543963923</v>
+        <v>7.081082108381221</v>
       </c>
       <c r="D1125" t="s">
-        <v>306</v>
+        <v>498</v>
       </c>
       <c r="E1125">
-        <v>6.945554456029511</v>
+        <v>6.768845934557076</v>
       </c>
       <c r="F1125">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1125">
-        <v>0.007789043456036078</v>
+        <v>0.00815891789161878</v>
       </c>
       <c r="H1125">
-        <v>0.00801444554397049</v>
+        <v>0.007851154065442923</v>
       </c>
       <c r="I1125">
-        <v>0.2745979120655875</v>
+        <v>0.3122361738241448</v>
       </c>
       <c r="J1125">
         <v>0.1118086912072155</v>
       </c>
       <c r="K1125">
-        <v>5</v>
+        <v>4.82</v>
       </c>
       <c r="L1125">
-        <v>7.23</v>
+        <v>7.62</v>
       </c>
       <c r="M1125">
-        <v>4.78</v>
+        <v>4.84</v>
       </c>
       <c r="N1125">
-        <v>7.48</v>
+        <v>7.31</v>
       </c>
       <c r="O1125">
         <v>1</v>
@@ -58546,46 +58546,46 @@
     </row>
     <row r="1126" spans="1:16">
       <c r="A1126" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1126" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C1126">
-        <v>6.683192717788067</v>
+        <v>6.669964021469148</v>
       </c>
       <c r="D1126" t="s">
-        <v>306</v>
+        <v>500</v>
       </c>
       <c r="E1126">
-        <v>6.945554456029511</v>
+        <v>6.724436369117438</v>
       </c>
       <c r="F1126">
         <v>1</v>
       </c>
       <c r="G1126">
-        <v>0.007796807282211934</v>
+        <v>0.007750035978530852</v>
       </c>
       <c r="H1126">
-        <v>0.00801444554397049</v>
+        <v>0.007795563630882562</v>
       </c>
       <c r="I1126">
-        <v>0.2623617382414434</v>
+        <v>0.05447234764828934</v>
       </c>
       <c r="J1126">
         <v>0.1118086912072155</v>
       </c>
       <c r="K1126">
-        <v>4.98</v>
+        <v>4.83</v>
       </c>
       <c r="L1126">
-        <v>7.24</v>
+        <v>7.21</v>
       </c>
       <c r="M1126">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="N1126">
-        <v>7.48</v>
+        <v>7.26</v>
       </c>
       <c r="O1126">
         <v>1</v>
@@ -58596,146 +58596,146 @@
     </row>
     <row r="1127" spans="1:16">
       <c r="A1127" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1127" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="C1127">
-        <v>7.081082108381221</v>
+        <v>6.978379489467468</v>
       </c>
       <c r="D1127" t="s">
-        <v>498</v>
+        <v>305</v>
       </c>
       <c r="E1127">
-        <v>6.768845934557076</v>
+        <v>6.81731540202045</v>
       </c>
       <c r="F1127">
         <v>-1</v>
       </c>
       <c r="G1127">
-        <v>0.00815891789161878</v>
+        <v>0.008061620510532531</v>
       </c>
       <c r="H1127">
-        <v>0.007851154065442923</v>
+        <v>0.007902684597979551</v>
       </c>
       <c r="I1127">
-        <v>0.3122361738241448</v>
+        <v>0.1610640874470182</v>
       </c>
       <c r="J1127">
-        <v>0.1118086912072155</v>
+        <v>0.1064087447018726</v>
       </c>
       <c r="K1127">
-        <v>4.82</v>
+        <v>5.09</v>
       </c>
       <c r="L1127">
-        <v>7.62</v>
+        <v>7.52</v>
       </c>
       <c r="M1127">
-        <v>4.84</v>
+        <v>5.1</v>
       </c>
       <c r="N1127">
-        <v>7.31</v>
+        <v>7.36</v>
       </c>
       <c r="O1127">
         <v>1</v>
       </c>
       <c r="P1127" t="s">
-        <v>632</v>
+        <v>304</v>
       </c>
     </row>
     <row r="1128" spans="1:16">
       <c r="A1128" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1128" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C1128">
-        <v>6.669964021469148</v>
+        <v>6.983059052232375</v>
       </c>
       <c r="D1128" t="s">
-        <v>500</v>
+        <v>305</v>
       </c>
       <c r="E1128">
-        <v>6.723318282205366</v>
+        <v>6.81731540202045</v>
       </c>
       <c r="F1128">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1128">
-        <v>0.007750035978530852</v>
+        <v>0.008076940947767624</v>
       </c>
       <c r="H1128">
-        <v>0.007796681717794634</v>
+        <v>0.007902684597979551</v>
       </c>
       <c r="I1128">
-        <v>0.05335426073621719</v>
+        <v>0.1657436502119252</v>
       </c>
       <c r="J1128">
-        <v>0.1118086912072155</v>
+        <v>0.1064087447018726</v>
       </c>
       <c r="K1128">
-        <v>4.83</v>
+        <v>5.14</v>
       </c>
       <c r="L1128">
-        <v>7.21</v>
+        <v>7.53</v>
       </c>
       <c r="M1128">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="N1128">
-        <v>7.26</v>
+        <v>7.36</v>
       </c>
       <c r="O1128">
         <v>1</v>
       </c>
       <c r="P1128" t="s">
-        <v>632</v>
+        <v>304</v>
       </c>
     </row>
     <row r="1129" spans="1:16">
       <c r="A1129" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1129" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C1129">
-        <v>6.983059052232375</v>
+        <v>6.697956276490637</v>
       </c>
       <c r="D1129" t="s">
-        <v>305</v>
+        <v>501</v>
       </c>
       <c r="E1129">
-        <v>6.81731540202045</v>
+        <v>6.861571751808525</v>
       </c>
       <c r="F1129">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1129">
-        <v>0.008076940947767624</v>
+        <v>0.007762043723509364</v>
       </c>
       <c r="H1129">
-        <v>0.007902684597979551</v>
+        <v>0.007938428248191475</v>
       </c>
       <c r="I1129">
-        <v>0.1657436502119252</v>
+        <v>0.1636154753178882</v>
       </c>
       <c r="J1129">
         <v>0.1064087447018726</v>
       </c>
       <c r="K1129">
-        <v>5.14</v>
+        <v>5</v>
       </c>
       <c r="L1129">
-        <v>7.53</v>
+        <v>7.23</v>
       </c>
       <c r="M1129">
-        <v>5.1</v>
+        <v>5.06</v>
       </c>
       <c r="N1129">
-        <v>7.36</v>
+        <v>7.4</v>
       </c>
       <c r="O1129">
         <v>1</v>
@@ -58746,13 +58746,13 @@
     </row>
     <row r="1130" spans="1:16">
       <c r="A1130" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1130" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C1130">
-        <v>6.697956276490637</v>
+        <v>6.710084451384675</v>
       </c>
       <c r="D1130" t="s">
         <v>501</v>
@@ -58764,22 +58764,22 @@
         <v>1</v>
       </c>
       <c r="G1130">
-        <v>0.007762043723509364</v>
+        <v>0.007769915548615326</v>
       </c>
       <c r="H1130">
         <v>0.007938428248191475</v>
       </c>
       <c r="I1130">
-        <v>0.1636154753178882</v>
+        <v>0.1514873004238506</v>
       </c>
       <c r="J1130">
         <v>0.1064087447018726</v>
       </c>
       <c r="K1130">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="L1130">
-        <v>7.23</v>
+        <v>7.24</v>
       </c>
       <c r="M1130">
         <v>5.06</v>
@@ -58796,46 +58796,46 @@
     </row>
     <row r="1131" spans="1:16">
       <c r="A1131" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1131" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C1131">
-        <v>6.710084451384675</v>
+        <v>7.107109850536975</v>
       </c>
       <c r="D1131" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E1131">
-        <v>6.861571751808525</v>
+        <v>6.794981675642936</v>
       </c>
       <c r="F1131">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1131">
-        <v>0.007769915548615326</v>
+        <v>0.008132890149463027</v>
       </c>
       <c r="H1131">
-        <v>0.007938428248191475</v>
+        <v>0.007825018324357063</v>
       </c>
       <c r="I1131">
-        <v>0.1514873004238506</v>
+        <v>0.3121281748940383</v>
       </c>
       <c r="J1131">
         <v>0.1064087447018726</v>
       </c>
       <c r="K1131">
-        <v>4.98</v>
+        <v>4.82</v>
       </c>
       <c r="L1131">
-        <v>7.24</v>
+        <v>7.62</v>
       </c>
       <c r="M1131">
-        <v>5.06</v>
+        <v>4.84</v>
       </c>
       <c r="N1131">
-        <v>7.4</v>
+        <v>7.31</v>
       </c>
       <c r="O1131">
         <v>1</v>
@@ -58846,46 +58846,46 @@
     </row>
     <row r="1132" spans="1:16">
       <c r="A1132" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1132" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="C1132">
-        <v>7.107109850536975</v>
+        <v>6.696045763089955</v>
       </c>
       <c r="D1132" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E1132">
-        <v>6.794981675642936</v>
+        <v>6.75030211287803</v>
       </c>
       <c r="F1132">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1132">
-        <v>0.008132890149463027</v>
+        <v>0.007723954236910044</v>
       </c>
       <c r="H1132">
-        <v>0.007825018324357063</v>
+        <v>0.00776969788712197</v>
       </c>
       <c r="I1132">
-        <v>0.3121281748940383</v>
+        <v>0.05425634978807459</v>
       </c>
       <c r="J1132">
         <v>0.1064087447018726</v>
       </c>
       <c r="K1132">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="L1132">
-        <v>7.62</v>
+        <v>7.21</v>
       </c>
       <c r="M1132">
-        <v>4.84</v>
+        <v>4.79</v>
       </c>
       <c r="N1132">
-        <v>7.31</v>
+        <v>7.26</v>
       </c>
       <c r="O1132">
         <v>1</v>
@@ -58896,63 +58896,63 @@
     </row>
     <row r="1133" spans="1:16">
       <c r="A1133" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1133" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C1133">
-        <v>6.696045763089955</v>
+        <v>7.025719018913059</v>
       </c>
       <c r="D1133" t="s">
-        <v>500</v>
+        <v>305</v>
       </c>
       <c r="E1133">
-        <v>6.749238025431011</v>
+        <v>6.86668630067644</v>
       </c>
       <c r="F1133">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1133">
-        <v>0.007723954236910044</v>
+        <v>0.008014280981086941</v>
       </c>
       <c r="H1133">
-        <v>0.007770761974568988</v>
+        <v>0.007853313699323562</v>
       </c>
       <c r="I1133">
-        <v>0.05319226234105567</v>
+        <v>0.1590327182366194</v>
       </c>
       <c r="J1133">
-        <v>0.1064087447018726</v>
+        <v>0.09672817633795312</v>
       </c>
       <c r="K1133">
-        <v>4.83</v>
+        <v>5.11</v>
       </c>
       <c r="L1133">
-        <v>7.21</v>
+        <v>7.52</v>
       </c>
       <c r="M1133">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="N1133">
-        <v>7.26</v>
+        <v>7.36</v>
       </c>
       <c r="O1133">
         <v>1</v>
       </c>
       <c r="P1133" t="s">
-        <v>304</v>
+        <v>633</v>
       </c>
     </row>
     <row r="1134" spans="1:16">
       <c r="A1134" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1134" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C1134">
-        <v>7.025719018913059</v>
+        <v>7.027653582439818</v>
       </c>
       <c r="D1134" t="s">
         <v>305</v>
@@ -58964,19 +58964,19 @@
         <v>-1</v>
       </c>
       <c r="G1134">
-        <v>0.008014280981086941</v>
+        <v>0.008012346417560181</v>
       </c>
       <c r="H1134">
         <v>0.007853313699323562</v>
       </c>
       <c r="I1134">
-        <v>0.1590327182366194</v>
+        <v>0.1609672817633783</v>
       </c>
       <c r="J1134">
         <v>0.09672817633795312</v>
       </c>
       <c r="K1134">
-        <v>5.11</v>
+        <v>5.09</v>
       </c>
       <c r="L1134">
         <v>7.52</v>
@@ -58996,46 +58996,46 @@
     </row>
     <row r="1135" spans="1:16">
       <c r="A1135" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1135" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C1135">
-        <v>7.027653582439818</v>
+        <v>6.746359118310234</v>
       </c>
       <c r="D1135" t="s">
-        <v>305</v>
+        <v>501</v>
       </c>
       <c r="E1135">
-        <v>6.86668630067644</v>
+        <v>6.910555427729958</v>
       </c>
       <c r="F1135">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1135">
-        <v>0.008012346417560181</v>
+        <v>0.007713640881689766</v>
       </c>
       <c r="H1135">
-        <v>0.007853313699323562</v>
+        <v>0.007889444572270043</v>
       </c>
       <c r="I1135">
-        <v>0.1609672817633783</v>
+        <v>0.1641963094197232</v>
       </c>
       <c r="J1135">
         <v>0.09672817633795312</v>
       </c>
       <c r="K1135">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="L1135">
-        <v>7.52</v>
+        <v>7.23</v>
       </c>
       <c r="M1135">
-        <v>5.1</v>
+        <v>5.06</v>
       </c>
       <c r="N1135">
-        <v>7.36</v>
+        <v>7.4</v>
       </c>
       <c r="O1135">
         <v>1</v>
@@ -59046,13 +59046,13 @@
     </row>
     <row r="1136" spans="1:16">
       <c r="A1136" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1136" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C1136">
-        <v>6.746359118310234</v>
+        <v>6.758293681836994</v>
       </c>
       <c r="D1136" t="s">
         <v>501</v>
@@ -59064,22 +59064,22 @@
         <v>1</v>
       </c>
       <c r="G1136">
-        <v>0.007713640881689766</v>
+        <v>0.007721706318163006</v>
       </c>
       <c r="H1136">
         <v>0.007889444572270043</v>
       </c>
       <c r="I1136">
-        <v>0.1641963094197232</v>
+        <v>0.1522617458929636</v>
       </c>
       <c r="J1136">
         <v>0.09672817633795312</v>
       </c>
       <c r="K1136">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="L1136">
-        <v>7.23</v>
+        <v>7.24</v>
       </c>
       <c r="M1136">
         <v>5.06</v>
@@ -59096,46 +59096,46 @@
     </row>
     <row r="1137" spans="1:16">
       <c r="A1137" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1137" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C1137">
-        <v>6.758293681836994</v>
+        <v>7.153770190051066</v>
       </c>
       <c r="D1137" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E1137">
-        <v>6.910555427729958</v>
+        <v>6.841835626524307</v>
       </c>
       <c r="F1137">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1137">
-        <v>0.007721706318163006</v>
+        <v>0.008086229809948935</v>
       </c>
       <c r="H1137">
-        <v>0.007889444572270043</v>
+        <v>0.007778164373475693</v>
       </c>
       <c r="I1137">
-        <v>0.1522617458929636</v>
+        <v>0.3119345635267594</v>
       </c>
       <c r="J1137">
         <v>0.09672817633795312</v>
       </c>
       <c r="K1137">
-        <v>4.98</v>
+        <v>4.82</v>
       </c>
       <c r="L1137">
-        <v>7.24</v>
+        <v>7.62</v>
       </c>
       <c r="M1137">
-        <v>5.06</v>
+        <v>4.84</v>
       </c>
       <c r="N1137">
-        <v>7.4</v>
+        <v>7.31</v>
       </c>
       <c r="O1137">
         <v>1</v>
@@ -59146,46 +59146,46 @@
     </row>
     <row r="1138" spans="1:16">
       <c r="A1138" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1138" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="C1138">
-        <v>7.153770190051066</v>
+        <v>6.742802908287686</v>
       </c>
       <c r="D1138" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E1138">
-        <v>6.841835626524307</v>
+        <v>6.796672035341205</v>
       </c>
       <c r="F1138">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1138">
-        <v>0.008086229809948935</v>
+        <v>0.007677197091712314</v>
       </c>
       <c r="H1138">
-        <v>0.007778164373475693</v>
+        <v>0.007723327964658795</v>
       </c>
       <c r="I1138">
-        <v>0.3119345635267594</v>
+        <v>0.05386912705351854</v>
       </c>
       <c r="J1138">
         <v>0.09672817633795312</v>
       </c>
       <c r="K1138">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="L1138">
-        <v>7.62</v>
+        <v>7.21</v>
       </c>
       <c r="M1138">
-        <v>4.84</v>
+        <v>4.79</v>
       </c>
       <c r="N1138">
-        <v>7.31</v>
+        <v>7.26</v>
       </c>
       <c r="O1138">
         <v>1</v>
@@ -59196,146 +59196,146 @@
     </row>
     <row r="1139" spans="1:16">
       <c r="A1139" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1139" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C1139">
-        <v>6.742802908287686</v>
+        <v>6.038657471720564</v>
       </c>
       <c r="D1139" t="s">
-        <v>500</v>
+        <v>305</v>
       </c>
       <c r="E1139">
-        <v>6.795704753577825</v>
+        <v>5.875747172057933</v>
       </c>
       <c r="F1139">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1139">
-        <v>0.007677197091712314</v>
+        <v>0.009001342528279437</v>
       </c>
       <c r="H1139">
-        <v>0.007724295246422175</v>
+        <v>0.008844252827942068</v>
       </c>
       <c r="I1139">
-        <v>0.05290184529013864</v>
+        <v>0.1629102996626308</v>
       </c>
       <c r="J1139">
-        <v>0.09672817633795312</v>
+        <v>0.2910299662631506</v>
       </c>
       <c r="K1139">
-        <v>4.83</v>
+        <v>5.09</v>
       </c>
       <c r="L1139">
-        <v>7.21</v>
+        <v>7.52</v>
       </c>
       <c r="M1139">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="N1139">
-        <v>7.26</v>
+        <v>7.36</v>
       </c>
       <c r="O1139">
         <v>1</v>
       </c>
       <c r="P1139" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="1140" spans="1:16">
       <c r="A1140" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B1140" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C1140">
-        <v>6.788606598867964</v>
+        <v>5.825747172057932</v>
       </c>
       <c r="D1140" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E1140">
-        <v>6.795704753577825</v>
+        <v>5.927388370708458</v>
       </c>
       <c r="F1140">
         <v>1</v>
       </c>
       <c r="G1140">
-        <v>0.007711393401132036</v>
+        <v>0.008794252827942068</v>
       </c>
       <c r="H1140">
-        <v>0.007724295246422175</v>
+        <v>0.008872611629291543</v>
       </c>
       <c r="I1140">
-        <v>0.007098154709860971</v>
+        <v>0.1016411986505261</v>
       </c>
       <c r="J1140">
-        <v>0.09672817633795312</v>
+        <v>0.2910299662631506</v>
       </c>
       <c r="K1140">
-        <v>4.77</v>
+        <v>5.1</v>
       </c>
       <c r="L1140">
-        <v>7.25</v>
+        <v>7.31</v>
       </c>
       <c r="M1140">
-        <v>4.8</v>
+        <v>5.06</v>
       </c>
       <c r="N1140">
-        <v>7.26</v>
+        <v>7.4</v>
       </c>
       <c r="O1140">
         <v>1</v>
       </c>
       <c r="P1140" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="1141" spans="1:16">
       <c r="A1141" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1141" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C1141">
-        <v>6.038657471720564</v>
+        <v>5.826119269696353</v>
       </c>
       <c r="D1141" t="s">
-        <v>305</v>
+        <v>501</v>
       </c>
       <c r="E1141">
-        <v>5.875747172057933</v>
+        <v>5.927388370708458</v>
       </c>
       <c r="F1141">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1141">
-        <v>0.009001342528279437</v>
+        <v>0.008753880730303648</v>
       </c>
       <c r="H1141">
-        <v>0.008844252827942068</v>
+        <v>0.008872611629291543</v>
       </c>
       <c r="I1141">
-        <v>0.1629102996626308</v>
+        <v>0.1012691010121056</v>
       </c>
       <c r="J1141">
         <v>0.2910299662631506</v>
       </c>
       <c r="K1141">
-        <v>5.09</v>
+        <v>5.03</v>
       </c>
       <c r="L1141">
-        <v>7.52</v>
+        <v>7.29</v>
       </c>
       <c r="M1141">
-        <v>5.1</v>
+        <v>5.06</v>
       </c>
       <c r="N1141">
-        <v>7.36</v>
+        <v>7.4</v>
       </c>
       <c r="O1141">
         <v>1</v>
@@ -59346,13 +59346,13 @@
     </row>
     <row r="1142" spans="1:16">
       <c r="A1142" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1142" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C1142">
-        <v>5.825747172057932</v>
+        <v>5.826119269696353</v>
       </c>
       <c r="D1142" t="s">
         <v>501</v>
@@ -59364,22 +59364,22 @@
         <v>1</v>
       </c>
       <c r="G1142">
-        <v>0.008794252827942068</v>
+        <v>0.008753880730303648</v>
       </c>
       <c r="H1142">
         <v>0.008872611629291543</v>
       </c>
       <c r="I1142">
-        <v>0.1016411986505261</v>
+        <v>0.1012691010121056</v>
       </c>
       <c r="J1142">
         <v>0.2910299662631506</v>
       </c>
       <c r="K1142">
-        <v>5.1</v>
+        <v>5.03</v>
       </c>
       <c r="L1142">
-        <v>7.31</v>
+        <v>7.29</v>
       </c>
       <c r="M1142">
         <v>5.06</v>
@@ -59396,10 +59396,10 @@
     </row>
     <row r="1143" spans="1:16">
       <c r="A1143" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1143" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C1143">
         <v>5.826119269696353</v>
@@ -59446,13 +59446,13 @@
     </row>
     <row r="1144" spans="1:16">
       <c r="A1144" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1144" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="C1144">
-        <v>5.826119269696353</v>
+        <v>5.790670768009511</v>
       </c>
       <c r="D1144" t="s">
         <v>501</v>
@@ -59464,22 +59464,22 @@
         <v>1</v>
       </c>
       <c r="G1144">
-        <v>0.008753880730303648</v>
+        <v>0.00868932923199049</v>
       </c>
       <c r="H1144">
         <v>0.008872611629291543</v>
       </c>
       <c r="I1144">
-        <v>0.1012691010121056</v>
+        <v>0.1367176026989476</v>
       </c>
       <c r="J1144">
         <v>0.2910299662631506</v>
       </c>
       <c r="K1144">
-        <v>5.03</v>
+        <v>4.98</v>
       </c>
       <c r="L1144">
-        <v>7.29</v>
+        <v>7.24</v>
       </c>
       <c r="M1144">
         <v>5.06</v>
@@ -59496,46 +59496,46 @@
     </row>
     <row r="1145" spans="1:16">
       <c r="A1145" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1145" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="C1145">
-        <v>5.826119269696353</v>
+        <v>6.08887676126214</v>
       </c>
       <c r="D1145" t="s">
-        <v>501</v>
+        <v>301</v>
       </c>
       <c r="E1145">
-        <v>5.927388370708458</v>
+        <v>6.217235562611615</v>
       </c>
       <c r="F1145">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1145">
-        <v>0.008753880730303648</v>
+        <v>0.008871123238737861</v>
       </c>
       <c r="H1145">
-        <v>0.008872611629291543</v>
+        <v>0.009022764437388385</v>
       </c>
       <c r="I1145">
-        <v>0.1012691010121056</v>
+        <v>-0.1283588013494743</v>
       </c>
       <c r="J1145">
         <v>0.2910299662631506</v>
       </c>
       <c r="K1145">
-        <v>5.03</v>
+        <v>4.78</v>
       </c>
       <c r="L1145">
-        <v>7.29</v>
+        <v>7.48</v>
       </c>
       <c r="M1145">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="N1145">
-        <v>7.4</v>
+        <v>7.62</v>
       </c>
       <c r="O1145">
         <v>1</v>
@@ -59546,46 +59546,46 @@
     </row>
     <row r="1146" spans="1:16">
       <c r="A1146" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B1146" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C1146">
-        <v>5.790670768009511</v>
+        <v>5.804325262948982</v>
       </c>
       <c r="D1146" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E1146">
-        <v>5.927388370708458</v>
+        <v>5.941042865647931</v>
       </c>
       <c r="F1146">
         <v>1</v>
       </c>
       <c r="G1146">
-        <v>0.00868932923199049</v>
+        <v>0.008615674737051018</v>
       </c>
       <c r="H1146">
-        <v>0.008872611629291543</v>
+        <v>0.008798957134352069</v>
       </c>
       <c r="I1146">
-        <v>0.1367176026989476</v>
+        <v>0.1367176026989485</v>
       </c>
       <c r="J1146">
         <v>0.2910299662631506</v>
       </c>
       <c r="K1146">
-        <v>4.98</v>
+        <v>4.83</v>
       </c>
       <c r="L1146">
-        <v>7.24</v>
+        <v>7.21</v>
       </c>
       <c r="M1146">
-        <v>5.06</v>
+        <v>4.91</v>
       </c>
       <c r="N1146">
-        <v>7.4</v>
+        <v>7.37</v>
       </c>
       <c r="O1146">
         <v>1</v>
@@ -59596,46 +59596,46 @@
     </row>
     <row r="1147" spans="1:16">
       <c r="A1147" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B1147" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="C1147">
-        <v>6.08887676126214</v>
+        <v>5.819773764635825</v>
       </c>
       <c r="D1147" t="s">
-        <v>301</v>
+        <v>502</v>
       </c>
       <c r="E1147">
-        <v>6.217235562611615</v>
+        <v>5.941042865647931</v>
       </c>
       <c r="F1147">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1147">
-        <v>0.008871123238737861</v>
+        <v>0.008660226235364174</v>
       </c>
       <c r="H1147">
-        <v>0.009022764437388385</v>
+        <v>0.008798957134352069</v>
       </c>
       <c r="I1147">
-        <v>-0.1283588013494743</v>
+        <v>0.1212691010121052</v>
       </c>
       <c r="J1147">
         <v>0.2910299662631506</v>
       </c>
       <c r="K1147">
-        <v>4.78</v>
+        <v>4.88</v>
       </c>
       <c r="L1147">
-        <v>7.48</v>
+        <v>7.24</v>
       </c>
       <c r="M1147">
-        <v>4.82</v>
+        <v>4.91</v>
       </c>
       <c r="N1147">
-        <v>7.62</v>
+        <v>7.37</v>
       </c>
       <c r="O1147">
         <v>1</v>
@@ -59646,146 +59646,146 @@
     </row>
     <row r="1148" spans="1:16">
       <c r="A1148" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1148" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C1148">
-        <v>5.804325262948982</v>
+        <v>6.063408640507315</v>
       </c>
       <c r="D1148" t="s">
-        <v>502</v>
+        <v>305</v>
       </c>
       <c r="E1148">
-        <v>5.941042865647931</v>
+        <v>5.900546967895346</v>
       </c>
       <c r="F1148">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1148">
-        <v>0.008615674737051018</v>
+        <v>0.008976591359492683</v>
       </c>
       <c r="H1148">
-        <v>0.008798957134352069</v>
+        <v>0.008819453032104654</v>
       </c>
       <c r="I1148">
-        <v>0.1367176026989485</v>
+        <v>0.1628616726119683</v>
       </c>
       <c r="J1148">
-        <v>0.2910299662631506</v>
+        <v>0.2861672611969911</v>
       </c>
       <c r="K1148">
-        <v>4.83</v>
+        <v>5.09</v>
       </c>
       <c r="L1148">
-        <v>7.21</v>
+        <v>7.52</v>
       </c>
       <c r="M1148">
-        <v>4.91</v>
+        <v>5.1</v>
       </c>
       <c r="N1148">
-        <v>7.37</v>
+        <v>7.36</v>
       </c>
       <c r="O1148">
         <v>1</v>
       </c>
       <c r="P1148" t="s">
-        <v>634</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1149" spans="1:16">
       <c r="A1149" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B1149" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C1149">
-        <v>5.819773764635825</v>
+        <v>5.850546967895346</v>
       </c>
       <c r="D1149" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E1149">
-        <v>5.941042865647931</v>
+        <v>5.951993658343225</v>
       </c>
       <c r="F1149">
         <v>1</v>
       </c>
       <c r="G1149">
-        <v>0.008660226235364174</v>
+        <v>0.008769453032104654</v>
       </c>
       <c r="H1149">
-        <v>0.008798957134352069</v>
+        <v>0.008848006341656776</v>
       </c>
       <c r="I1149">
-        <v>0.1212691010121052</v>
+        <v>0.1014466904478795</v>
       </c>
       <c r="J1149">
-        <v>0.2910299662631506</v>
+        <v>0.2861672611969911</v>
       </c>
       <c r="K1149">
-        <v>4.88</v>
+        <v>5.1</v>
       </c>
       <c r="L1149">
-        <v>7.24</v>
+        <v>7.31</v>
       </c>
       <c r="M1149">
-        <v>4.91</v>
+        <v>5.06</v>
       </c>
       <c r="N1149">
-        <v>7.37</v>
+        <v>7.4</v>
       </c>
       <c r="O1149">
         <v>1</v>
       </c>
       <c r="P1149" t="s">
-        <v>634</v>
+        <v>499</v>
       </c>
     </row>
     <row r="1150" spans="1:16">
       <c r="A1150" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1150" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C1150">
-        <v>6.063408640507315</v>
+        <v>5.850578676179135</v>
       </c>
       <c r="D1150" t="s">
-        <v>305</v>
+        <v>501</v>
       </c>
       <c r="E1150">
-        <v>5.900546967895346</v>
+        <v>5.951993658343225</v>
       </c>
       <c r="F1150">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1150">
-        <v>0.008976591359492683</v>
+        <v>0.008729421323820865</v>
       </c>
       <c r="H1150">
-        <v>0.008819453032104654</v>
+        <v>0.008848006341656776</v>
       </c>
       <c r="I1150">
-        <v>0.1628616726119683</v>
+        <v>0.1014149821640906</v>
       </c>
       <c r="J1150">
         <v>0.2861672611969911</v>
       </c>
       <c r="K1150">
-        <v>5.09</v>
+        <v>5.03</v>
       </c>
       <c r="L1150">
-        <v>7.52</v>
+        <v>7.29</v>
       </c>
       <c r="M1150">
-        <v>5.1</v>
+        <v>5.06</v>
       </c>
       <c r="N1150">
-        <v>7.36</v>
+        <v>7.4</v>
       </c>
       <c r="O1150">
         <v>1</v>
@@ -59796,13 +59796,13 @@
     </row>
     <row r="1151" spans="1:16">
       <c r="A1151" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1151" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C1151">
-        <v>5.850546967895346</v>
+        <v>5.850578676179135</v>
       </c>
       <c r="D1151" t="s">
         <v>501</v>
@@ -59814,22 +59814,22 @@
         <v>1</v>
       </c>
       <c r="G1151">
-        <v>0.008769453032104654</v>
+        <v>0.008729421323820865</v>
       </c>
       <c r="H1151">
         <v>0.008848006341656776</v>
       </c>
       <c r="I1151">
-        <v>0.1014466904478795</v>
+        <v>0.1014149821640906</v>
       </c>
       <c r="J1151">
         <v>0.2861672611969911</v>
       </c>
       <c r="K1151">
-        <v>5.1</v>
+        <v>5.03</v>
       </c>
       <c r="L1151">
-        <v>7.31</v>
+        <v>7.29</v>
       </c>
       <c r="M1151">
         <v>5.06</v>
@@ -59846,10 +59846,10 @@
     </row>
     <row r="1152" spans="1:16">
       <c r="A1152" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1152" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C1152">
         <v>5.850578676179135</v>
@@ -59896,13 +59896,13 @@
     </row>
     <row r="1153" spans="1:16">
       <c r="A1153" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1153" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="C1153">
-        <v>5.850578676179135</v>
+        <v>5.814887039238984</v>
       </c>
       <c r="D1153" t="s">
         <v>501</v>
@@ -59914,22 +59914,22 @@
         <v>1</v>
       </c>
       <c r="G1153">
-        <v>0.008729421323820865</v>
+        <v>0.008665112960761017</v>
       </c>
       <c r="H1153">
         <v>0.008848006341656776</v>
       </c>
       <c r="I1153">
-        <v>0.1014149821640906</v>
+        <v>0.1371066191042409</v>
       </c>
       <c r="J1153">
         <v>0.2861672611969911</v>
       </c>
       <c r="K1153">
-        <v>5.03</v>
+        <v>4.98</v>
       </c>
       <c r="L1153">
-        <v>7.29</v>
+        <v>7.24</v>
       </c>
       <c r="M1153">
         <v>5.06</v>
@@ -59946,46 +59946,46 @@
     </row>
     <row r="1154" spans="1:16">
       <c r="A1154" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1154" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="C1154">
-        <v>5.850578676179135</v>
+        <v>6.112120491478382</v>
       </c>
       <c r="D1154" t="s">
-        <v>501</v>
+        <v>301</v>
       </c>
       <c r="E1154">
-        <v>5.951993658343225</v>
+        <v>6.240673801030503</v>
       </c>
       <c r="F1154">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1154">
-        <v>0.008729421323820865</v>
+        <v>0.008847879508521618</v>
       </c>
       <c r="H1154">
-        <v>0.008848006341656776</v>
+        <v>0.008999326198969497</v>
       </c>
       <c r="I1154">
-        <v>0.1014149821640906</v>
+        <v>-0.128553309552121</v>
       </c>
       <c r="J1154">
         <v>0.2861672611969911</v>
       </c>
       <c r="K1154">
-        <v>5.03</v>
+        <v>4.78</v>
       </c>
       <c r="L1154">
-        <v>7.29</v>
+        <v>7.48</v>
       </c>
       <c r="M1154">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="N1154">
-        <v>7.4</v>
+        <v>7.62</v>
       </c>
       <c r="O1154">
         <v>1</v>
@@ -59996,28 +59996,28 @@
     </row>
     <row r="1155" spans="1:16">
       <c r="A1155" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B1155" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C1155">
-        <v>5.814887039238984</v>
+        <v>5.827812128418532</v>
       </c>
       <c r="D1155" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E1155">
-        <v>5.951993658343225</v>
+        <v>5.964918747522773</v>
       </c>
       <c r="F1155">
         <v>1</v>
       </c>
       <c r="G1155">
-        <v>0.008665112960761017</v>
+        <v>0.008592187871581468</v>
       </c>
       <c r="H1155">
-        <v>0.008848006341656776</v>
+        <v>0.008775081252477227</v>
       </c>
       <c r="I1155">
         <v>0.1371066191042409</v>
@@ -60026,16 +60026,16 @@
         <v>0.2861672611969911</v>
       </c>
       <c r="K1155">
-        <v>4.98</v>
+        <v>4.83</v>
       </c>
       <c r="L1155">
-        <v>7.24</v>
+        <v>7.21</v>
       </c>
       <c r="M1155">
-        <v>5.06</v>
+        <v>4.91</v>
       </c>
       <c r="N1155">
-        <v>7.4</v>
+        <v>7.37</v>
       </c>
       <c r="O1155">
         <v>1</v>
@@ -60046,46 +60046,46 @@
     </row>
     <row r="1156" spans="1:16">
       <c r="A1156" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B1156" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="C1156">
-        <v>6.112120491478382</v>
+        <v>5.843503765358683</v>
       </c>
       <c r="D1156" t="s">
-        <v>301</v>
+        <v>502</v>
       </c>
       <c r="E1156">
-        <v>6.240673801030503</v>
+        <v>5.964918747522773</v>
       </c>
       <c r="F1156">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1156">
-        <v>0.008847879508521618</v>
+        <v>0.008636496234641317</v>
       </c>
       <c r="H1156">
-        <v>0.008999326198969497</v>
+        <v>0.008775081252477227</v>
       </c>
       <c r="I1156">
-        <v>-0.128553309552121</v>
+        <v>0.1214149821640902</v>
       </c>
       <c r="J1156">
         <v>0.2861672611969911</v>
       </c>
       <c r="K1156">
-        <v>4.78</v>
+        <v>4.88</v>
       </c>
       <c r="L1156">
-        <v>7.48</v>
+        <v>7.24</v>
       </c>
       <c r="M1156">
-        <v>4.82</v>
+        <v>4.91</v>
       </c>
       <c r="N1156">
-        <v>7.62</v>
+        <v>7.37</v>
       </c>
       <c r="O1156">
         <v>1</v>
@@ -60096,146 +60096,146 @@
     </row>
     <row r="1157" spans="1:16">
       <c r="A1157" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1157" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C1157">
-        <v>5.827812128418532</v>
+        <v>6.042400346620433</v>
       </c>
       <c r="D1157" t="s">
-        <v>502</v>
+        <v>305</v>
       </c>
       <c r="E1157">
-        <v>5.964918747522773</v>
+        <v>5.879497400346603</v>
       </c>
       <c r="F1157">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1157">
-        <v>0.008592187871581468</v>
+        <v>0.008997599653379566</v>
       </c>
       <c r="H1157">
-        <v>0.008775081252477227</v>
+        <v>0.008840502599653398</v>
       </c>
       <c r="I1157">
-        <v>0.1371066191042409</v>
+        <v>0.1629029462738298</v>
       </c>
       <c r="J1157">
-        <v>0.2861672611969911</v>
+        <v>0.2902946273830191</v>
       </c>
       <c r="K1157">
-        <v>4.83</v>
+        <v>5.09</v>
       </c>
       <c r="L1157">
-        <v>7.21</v>
+        <v>7.52</v>
       </c>
       <c r="M1157">
-        <v>4.91</v>
+        <v>5.1</v>
       </c>
       <c r="N1157">
-        <v>7.37</v>
+        <v>7.36</v>
       </c>
       <c r="O1157">
         <v>1</v>
       </c>
       <c r="P1157" t="s">
-        <v>499</v>
+        <v>635</v>
       </c>
     </row>
     <row r="1158" spans="1:16">
       <c r="A1158" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B1158" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C1158">
-        <v>5.843503765358683</v>
+        <v>5.829497400346602</v>
       </c>
       <c r="D1158" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E1158">
-        <v>5.964918747522773</v>
+        <v>5.931109185441923</v>
       </c>
       <c r="F1158">
         <v>1</v>
       </c>
       <c r="G1158">
-        <v>0.008636496234641317</v>
+        <v>0.008790502599653397</v>
       </c>
       <c r="H1158">
-        <v>0.008775081252477227</v>
+        <v>0.008868890814558076</v>
       </c>
       <c r="I1158">
-        <v>0.1214149821640902</v>
+        <v>0.1016117850953213</v>
       </c>
       <c r="J1158">
-        <v>0.2861672611969911</v>
+        <v>0.2902946273830191</v>
       </c>
       <c r="K1158">
-        <v>4.88</v>
+        <v>5.1</v>
       </c>
       <c r="L1158">
-        <v>7.24</v>
+        <v>7.31</v>
       </c>
       <c r="M1158">
-        <v>4.91</v>
+        <v>5.06</v>
       </c>
       <c r="N1158">
-        <v>7.37</v>
+        <v>7.4</v>
       </c>
       <c r="O1158">
         <v>1</v>
       </c>
       <c r="P1158" t="s">
-        <v>499</v>
+        <v>635</v>
       </c>
     </row>
     <row r="1159" spans="1:16">
       <c r="A1159" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1159" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C1159">
-        <v>6.042400346620433</v>
+        <v>5.829818024263414</v>
       </c>
       <c r="D1159" t="s">
-        <v>305</v>
+        <v>501</v>
       </c>
       <c r="E1159">
-        <v>5.879497400346603</v>
+        <v>5.931109185441923</v>
       </c>
       <c r="F1159">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1159">
-        <v>0.008997599653379566</v>
+        <v>0.008750181975736586</v>
       </c>
       <c r="H1159">
-        <v>0.008840502599653398</v>
+        <v>0.008868890814558076</v>
       </c>
       <c r="I1159">
-        <v>0.1629029462738298</v>
+        <v>0.1012911611785094</v>
       </c>
       <c r="J1159">
         <v>0.2902946273830191</v>
       </c>
       <c r="K1159">
-        <v>5.09</v>
+        <v>5.03</v>
       </c>
       <c r="L1159">
-        <v>7.52</v>
+        <v>7.29</v>
       </c>
       <c r="M1159">
-        <v>5.1</v>
+        <v>5.06</v>
       </c>
       <c r="N1159">
-        <v>7.36</v>
+        <v>7.4</v>
       </c>
       <c r="O1159">
         <v>1</v>
@@ -60246,13 +60246,13 @@
     </row>
     <row r="1160" spans="1:16">
       <c r="A1160" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1160" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C1160">
-        <v>5.829497400346602</v>
+        <v>5.829818024263414</v>
       </c>
       <c r="D1160" t="s">
         <v>501</v>
@@ -60264,22 +60264,22 @@
         <v>1</v>
       </c>
       <c r="G1160">
-        <v>0.008790502599653397</v>
+        <v>0.008750181975736586</v>
       </c>
       <c r="H1160">
         <v>0.008868890814558076</v>
       </c>
       <c r="I1160">
-        <v>0.1016117850953213</v>
+        <v>0.1012911611785094</v>
       </c>
       <c r="J1160">
         <v>0.2902946273830191</v>
       </c>
       <c r="K1160">
-        <v>5.1</v>
+        <v>5.03</v>
       </c>
       <c r="L1160">
-        <v>7.31</v>
+        <v>7.29</v>
       </c>
       <c r="M1160">
         <v>5.06</v>
@@ -60296,10 +60296,10 @@
     </row>
     <row r="1161" spans="1:16">
       <c r="A1161" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1161" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C1161">
         <v>5.829818024263414</v>
@@ -60346,13 +60346,13 @@
     </row>
     <row r="1162" spans="1:16">
       <c r="A1162" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1162" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="C1162">
-        <v>5.829818024263414</v>
+        <v>5.794332755632565</v>
       </c>
       <c r="D1162" t="s">
         <v>501</v>
@@ -60364,22 +60364,22 @@
         <v>1</v>
       </c>
       <c r="G1162">
-        <v>0.008750181975736586</v>
+        <v>0.008685667244367435</v>
       </c>
       <c r="H1162">
         <v>0.008868890814558076</v>
       </c>
       <c r="I1162">
-        <v>0.1012911611785094</v>
+        <v>0.1367764298093581</v>
       </c>
       <c r="J1162">
         <v>0.2902946273830191</v>
       </c>
       <c r="K1162">
-        <v>5.03</v>
+        <v>4.98</v>
       </c>
       <c r="L1162">
-        <v>7.29</v>
+        <v>7.24</v>
       </c>
       <c r="M1162">
         <v>5.06</v>
@@ -60396,46 +60396,46 @@
     </row>
     <row r="1163" spans="1:16">
       <c r="A1163" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1163" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="C1163">
-        <v>5.829818024263414</v>
+        <v>6.092391681109169</v>
       </c>
       <c r="D1163" t="s">
-        <v>501</v>
+        <v>301</v>
       </c>
       <c r="E1163">
-        <v>5.931109185441923</v>
+        <v>6.220779896013848</v>
       </c>
       <c r="F1163">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1163">
-        <v>0.008750181975736586</v>
+        <v>0.008867608318890833</v>
       </c>
       <c r="H1163">
-        <v>0.008868890814558076</v>
+        <v>0.009019220103986153</v>
       </c>
       <c r="I1163">
-        <v>0.1012911611785094</v>
+        <v>-0.1283882149046791</v>
       </c>
       <c r="J1163">
         <v>0.2902946273830191</v>
       </c>
       <c r="K1163">
-        <v>5.03</v>
+        <v>4.78</v>
       </c>
       <c r="L1163">
-        <v>7.29</v>
+        <v>7.48</v>
       </c>
       <c r="M1163">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="N1163">
-        <v>7.4</v>
+        <v>7.62</v>
       </c>
       <c r="O1163">
         <v>1</v>
@@ -60446,28 +60446,28 @@
     </row>
     <row r="1164" spans="1:16">
       <c r="A1164" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B1164" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C1164">
-        <v>5.794332755632565</v>
+        <v>5.807876949740018</v>
       </c>
       <c r="D1164" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E1164">
-        <v>5.931109185441923</v>
+        <v>5.944653379549376</v>
       </c>
       <c r="F1164">
         <v>1</v>
       </c>
       <c r="G1164">
-        <v>0.008685667244367435</v>
+        <v>0.008612123050259981</v>
       </c>
       <c r="H1164">
-        <v>0.008868890814558076</v>
+        <v>0.008795346620450624</v>
       </c>
       <c r="I1164">
         <v>0.1367764298093581</v>
@@ -60476,16 +60476,16 @@
         <v>0.2902946273830191</v>
       </c>
       <c r="K1164">
-        <v>4.98</v>
+        <v>4.83</v>
       </c>
       <c r="L1164">
-        <v>7.24</v>
+        <v>7.21</v>
       </c>
       <c r="M1164">
-        <v>5.06</v>
+        <v>4.91</v>
       </c>
       <c r="N1164">
-        <v>7.4</v>
+        <v>7.37</v>
       </c>
       <c r="O1164">
         <v>1</v>
@@ -60496,46 +60496,46 @@
     </row>
     <row r="1165" spans="1:16">
       <c r="A1165" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B1165" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="C1165">
-        <v>6.092391681109169</v>
+        <v>5.823362218370867</v>
       </c>
       <c r="D1165" t="s">
-        <v>301</v>
+        <v>502</v>
       </c>
       <c r="E1165">
-        <v>6.220779896013848</v>
+        <v>5.944653379549376</v>
       </c>
       <c r="F1165">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1165">
-        <v>0.008867608318890833</v>
+        <v>0.008656637781629133</v>
       </c>
       <c r="H1165">
-        <v>0.009019220103986153</v>
+        <v>0.008795346620450624</v>
       </c>
       <c r="I1165">
-        <v>-0.1283882149046791</v>
+        <v>0.121291161178509</v>
       </c>
       <c r="J1165">
         <v>0.2902946273830191</v>
       </c>
       <c r="K1165">
-        <v>4.78</v>
+        <v>4.88</v>
       </c>
       <c r="L1165">
-        <v>7.48</v>
+        <v>7.24</v>
       </c>
       <c r="M1165">
-        <v>4.82</v>
+        <v>4.91</v>
       </c>
       <c r="N1165">
-        <v>7.62</v>
+        <v>7.37</v>
       </c>
       <c r="O1165">
         <v>1</v>
@@ -60546,146 +60546,146 @@
     </row>
     <row r="1166" spans="1:16">
       <c r="A1166" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B1166" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C1166">
-        <v>5.807876949740018</v>
+        <v>5.35524754596201</v>
       </c>
       <c r="D1166" t="s">
-        <v>502</v>
+        <v>299</v>
       </c>
       <c r="E1166">
-        <v>5.944653379549376</v>
+        <v>5.235476883529267</v>
       </c>
       <c r="F1166">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1166">
-        <v>0.008612123050259981</v>
+        <v>0.009684752454037989</v>
       </c>
       <c r="H1166">
-        <v>0.008795346620450624</v>
+        <v>0.009624523116470734</v>
       </c>
       <c r="I1166">
-        <v>0.1367764298093581</v>
+        <v>0.1197706624327433</v>
       </c>
       <c r="J1166">
-        <v>0.2902946273830191</v>
+        <v>0.4252951776106071</v>
       </c>
       <c r="K1166">
-        <v>4.83</v>
+        <v>5.09</v>
       </c>
       <c r="L1166">
-        <v>7.21</v>
+        <v>7.52</v>
       </c>
       <c r="M1166">
-        <v>4.91</v>
+        <v>5.16</v>
       </c>
       <c r="N1166">
-        <v>7.37</v>
+        <v>7.43</v>
       </c>
       <c r="O1166">
         <v>1</v>
       </c>
       <c r="P1166" t="s">
-        <v>635</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1167" spans="1:16">
       <c r="A1167" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B1167" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C1167">
-        <v>5.823362218370867</v>
+        <v>5.140994594185903</v>
       </c>
       <c r="D1167" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E1167">
-        <v>5.944653379549376</v>
+        <v>5.248006401290329</v>
       </c>
       <c r="F1167">
         <v>1</v>
       </c>
       <c r="G1167">
-        <v>0.008656637781629133</v>
+        <v>0.009479005405814096</v>
       </c>
       <c r="H1167">
-        <v>0.008795346620450624</v>
+        <v>0.009551993598709672</v>
       </c>
       <c r="I1167">
-        <v>0.121291161178509</v>
+        <v>0.1070118071044259</v>
       </c>
       <c r="J1167">
-        <v>0.2902946273830191</v>
+        <v>0.4252951776106071</v>
       </c>
       <c r="K1167">
-        <v>4.88</v>
+        <v>5.1</v>
       </c>
       <c r="L1167">
-        <v>7.24</v>
+        <v>7.31</v>
       </c>
       <c r="M1167">
-        <v>4.91</v>
+        <v>5.06</v>
       </c>
       <c r="N1167">
-        <v>7.37</v>
+        <v>7.4</v>
       </c>
       <c r="O1167">
         <v>1</v>
       </c>
       <c r="P1167" t="s">
-        <v>635</v>
+        <v>297</v>
       </c>
     </row>
     <row r="1168" spans="1:16">
       <c r="A1168" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1168" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C1168">
-        <v>5.35524754596201</v>
+        <v>5.150765256618646</v>
       </c>
       <c r="D1168" t="s">
-        <v>299</v>
+        <v>501</v>
       </c>
       <c r="E1168">
-        <v>5.235476883529267</v>
+        <v>5.248006401290329</v>
       </c>
       <c r="F1168">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1168">
-        <v>0.009684752454037989</v>
+        <v>0.009429234743381355</v>
       </c>
       <c r="H1168">
-        <v>0.009624523116470734</v>
+        <v>0.009551993598709672</v>
       </c>
       <c r="I1168">
-        <v>0.1197706624327433</v>
+        <v>0.09724114467168299</v>
       </c>
       <c r="J1168">
         <v>0.4252951776106071</v>
       </c>
       <c r="K1168">
-        <v>5.09</v>
+        <v>5.03</v>
       </c>
       <c r="L1168">
-        <v>7.52</v>
+        <v>7.29</v>
       </c>
       <c r="M1168">
-        <v>5.16</v>
+        <v>5.06</v>
       </c>
       <c r="N1168">
-        <v>7.43</v>
+        <v>7.4</v>
       </c>
       <c r="O1168">
         <v>1</v>
@@ -60696,13 +60696,13 @@
     </row>
     <row r="1169" spans="1:16">
       <c r="A1169" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1169" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C1169">
-        <v>5.140994594185903</v>
+        <v>5.150765256618646</v>
       </c>
       <c r="D1169" t="s">
         <v>501</v>
@@ -60714,22 +60714,22 @@
         <v>1</v>
       </c>
       <c r="G1169">
-        <v>0.009479005405814096</v>
+        <v>0.009429234743381355</v>
       </c>
       <c r="H1169">
         <v>0.009551993598709672</v>
       </c>
       <c r="I1169">
-        <v>0.1070118071044259</v>
+        <v>0.09724114467168299</v>
       </c>
       <c r="J1169">
         <v>0.4252951776106071</v>
       </c>
       <c r="K1169">
-        <v>5.1</v>
+        <v>5.03</v>
       </c>
       <c r="L1169">
-        <v>7.31</v>
+        <v>7.29</v>
       </c>
       <c r="M1169">
         <v>5.06</v>
@@ -60746,10 +60746,10 @@
     </row>
     <row r="1170" spans="1:16">
       <c r="A1170" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1170" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C1170">
         <v>5.150765256618646</v>
@@ -60796,13 +60796,13 @@
     </row>
     <row r="1171" spans="1:16">
       <c r="A1171" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1171" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="C1171">
-        <v>5.150765256618646</v>
+        <v>5.122030015499177</v>
       </c>
       <c r="D1171" t="s">
         <v>501</v>
@@ -60814,22 +60814,22 @@
         <v>1</v>
       </c>
       <c r="G1171">
-        <v>0.009429234743381355</v>
+        <v>0.009357969984500824</v>
       </c>
       <c r="H1171">
         <v>0.009551993598709672</v>
       </c>
       <c r="I1171">
-        <v>0.09724114467168299</v>
+        <v>0.1259763857911524</v>
       </c>
       <c r="J1171">
         <v>0.4252951776106071</v>
       </c>
       <c r="K1171">
-        <v>5.03</v>
+        <v>4.98</v>
       </c>
       <c r="L1171">
-        <v>7.29</v>
+        <v>7.24</v>
       </c>
       <c r="M1171">
         <v>5.06</v>
@@ -60846,46 +60846,46 @@
     </row>
     <row r="1172" spans="1:16">
       <c r="A1172" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1172" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C1172">
-        <v>5.150765256618646</v>
+        <v>5.342606761677935</v>
       </c>
       <c r="D1172" t="s">
-        <v>501</v>
+        <v>301</v>
       </c>
       <c r="E1172">
-        <v>5.248006401290329</v>
+        <v>5.570077243916874</v>
       </c>
       <c r="F1172">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1172">
-        <v>0.009429234743381355</v>
+        <v>0.009357393238322064</v>
       </c>
       <c r="H1172">
-        <v>0.009551993598709672</v>
+        <v>0.009669922756083126</v>
       </c>
       <c r="I1172">
-        <v>0.09724114467168299</v>
+        <v>-0.2274704822389388</v>
       </c>
       <c r="J1172">
         <v>0.4252951776106071</v>
       </c>
       <c r="K1172">
-        <v>5.03</v>
+        <v>4.72</v>
       </c>
       <c r="L1172">
-        <v>7.29</v>
+        <v>7.35</v>
       </c>
       <c r="M1172">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="N1172">
-        <v>7.4</v>
+        <v>7.62</v>
       </c>
       <c r="O1172">
         <v>1</v>
@@ -60896,46 +60896,46 @@
     </row>
     <row r="1173" spans="1:16">
       <c r="A1173" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B1173" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C1173">
-        <v>5.122030015499177</v>
+        <v>5.155824292140768</v>
       </c>
       <c r="D1173" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E1173">
-        <v>5.248006401290329</v>
+        <v>5.281800677931919</v>
       </c>
       <c r="F1173">
         <v>1</v>
       </c>
       <c r="G1173">
-        <v>0.009357969984500824</v>
+        <v>0.009264175707859233</v>
       </c>
       <c r="H1173">
-        <v>0.009551993598709672</v>
+        <v>0.009458199322068081</v>
       </c>
       <c r="I1173">
-        <v>0.1259763857911524</v>
+        <v>0.1259763857911516</v>
       </c>
       <c r="J1173">
         <v>0.4252951776106071</v>
       </c>
       <c r="K1173">
-        <v>4.98</v>
+        <v>4.83</v>
       </c>
       <c r="L1173">
-        <v>7.24</v>
+        <v>7.21</v>
       </c>
       <c r="M1173">
-        <v>5.06</v>
+        <v>4.91</v>
       </c>
       <c r="N1173">
-        <v>7.4</v>
+        <v>7.37</v>
       </c>
       <c r="O1173">
         <v>1</v>
@@ -60946,113 +60946,113 @@
     </row>
     <row r="1174" spans="1:16">
       <c r="A1174" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B1174" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="C1174">
-        <v>5.342606761677935</v>
+        <v>5.084028831949459</v>
       </c>
       <c r="D1174" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E1174">
-        <v>5.570077243916874</v>
+        <v>4.960528246141299</v>
       </c>
       <c r="F1174">
         <v>-1</v>
       </c>
       <c r="G1174">
-        <v>0.009357393238322064</v>
+        <v>0.009955971168050541</v>
       </c>
       <c r="H1174">
-        <v>0.009669922756083126</v>
+        <v>0.009899471753858703</v>
       </c>
       <c r="I1174">
-        <v>-0.2274704822389388</v>
+        <v>0.1235005858081601</v>
       </c>
       <c r="J1174">
-        <v>0.4252951776106071</v>
+        <v>0.4785797972594382</v>
       </c>
       <c r="K1174">
-        <v>4.72</v>
+        <v>5.09</v>
       </c>
       <c r="L1174">
-        <v>7.35</v>
+        <v>7.52</v>
       </c>
       <c r="M1174">
-        <v>4.82</v>
+        <v>5.16</v>
       </c>
       <c r="N1174">
-        <v>7.62</v>
+        <v>7.43</v>
       </c>
       <c r="O1174">
         <v>1</v>
       </c>
       <c r="P1174" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
     </row>
     <row r="1175" spans="1:16">
       <c r="A1175" s="1">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B1175" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C1175">
-        <v>5.155824292140768</v>
+        <v>4.869243033976865</v>
       </c>
       <c r="D1175" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="E1175">
-        <v>5.281800677931919</v>
+        <v>5.02067495288064</v>
       </c>
       <c r="F1175">
         <v>1</v>
       </c>
       <c r="G1175">
-        <v>0.009264175707859233</v>
+        <v>0.009750756966023134</v>
       </c>
       <c r="H1175">
-        <v>0.009458199322068081</v>
+        <v>0.009519325047119359</v>
       </c>
       <c r="I1175">
-        <v>0.1259763857911516</v>
+        <v>0.1514319189037749</v>
       </c>
       <c r="J1175">
-        <v>0.4252951776106071</v>
+        <v>0.4785797972594382</v>
       </c>
       <c r="K1175">
-        <v>4.83</v>
+        <v>5.1</v>
       </c>
       <c r="L1175">
-        <v>7.21</v>
+        <v>7.31</v>
       </c>
       <c r="M1175">
-        <v>4.91</v>
+        <v>4.7</v>
       </c>
       <c r="N1175">
-        <v>7.37</v>
+        <v>7.27</v>
       </c>
       <c r="O1175">
         <v>1</v>
       </c>
       <c r="P1175" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
     </row>
     <row r="1176" spans="1:16">
       <c r="A1176" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1176" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C1176">
-        <v>4.869243033976865</v>
+        <v>4.882743619785026</v>
       </c>
       <c r="D1176" t="s">
         <v>497</v>
@@ -61064,22 +61064,22 @@
         <v>1</v>
       </c>
       <c r="G1176">
-        <v>0.009750756966023134</v>
+        <v>0.009697256380214974</v>
       </c>
       <c r="H1176">
         <v>0.009519325047119359</v>
       </c>
       <c r="I1176">
-        <v>0.1514319189037749</v>
+        <v>0.1379313330956142</v>
       </c>
       <c r="J1176">
         <v>0.4785797972594382</v>
       </c>
       <c r="K1176">
-        <v>5.1</v>
+        <v>5.03</v>
       </c>
       <c r="L1176">
-        <v>7.31</v>
+        <v>7.29</v>
       </c>
       <c r="M1176">
         <v>4.7</v>
@@ -61091,15 +61091,15 @@
         <v>1</v>
       </c>
       <c r="P1176" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="1177" spans="1:16">
       <c r="A1177" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1177" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C1177">
         <v>4.882743619785026</v>
@@ -61141,15 +61141,15 @@
         <v>1</v>
       </c>
       <c r="P1177" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="1178" spans="1:16">
       <c r="A1178" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1178" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C1178">
         <v>4.882743619785026</v>
@@ -61191,18 +61191,18 @@
         <v>1</v>
       </c>
       <c r="P1178" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="1179" spans="1:16">
       <c r="A1179" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1179" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="C1179">
-        <v>4.882743619785026</v>
+        <v>4.856672609647998</v>
       </c>
       <c r="D1179" t="s">
         <v>497</v>
@@ -61214,22 +61214,22 @@
         <v>1</v>
       </c>
       <c r="G1179">
-        <v>0.009697256380214974</v>
+        <v>0.009623327390352003</v>
       </c>
       <c r="H1179">
         <v>0.009519325047119359</v>
       </c>
       <c r="I1179">
-        <v>0.1379313330956142</v>
+        <v>0.1640023432326423</v>
       </c>
       <c r="J1179">
         <v>0.4785797972594382</v>
       </c>
       <c r="K1179">
-        <v>5.03</v>
+        <v>4.98</v>
       </c>
       <c r="L1179">
-        <v>7.29</v>
+        <v>7.24</v>
       </c>
       <c r="M1179">
         <v>4.7</v>
@@ -61241,68 +61241,68 @@
         <v>1</v>
       </c>
       <c r="P1179" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="1180" spans="1:16">
       <c r="A1180" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1180" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C1180">
-        <v>4.856672609647998</v>
+        <v>5.068961336661395</v>
       </c>
       <c r="D1180" t="s">
-        <v>497</v>
+        <v>301</v>
       </c>
       <c r="E1180">
-        <v>5.02067495288064</v>
+        <v>5.313245377209508</v>
       </c>
       <c r="F1180">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1180">
-        <v>0.009623327390352003</v>
+        <v>0.009491038663338605</v>
       </c>
       <c r="H1180">
-        <v>0.009519325047119359</v>
+        <v>0.009926754622790492</v>
       </c>
       <c r="I1180">
-        <v>0.1640023432326423</v>
+        <v>-0.2442840405481128</v>
       </c>
       <c r="J1180">
         <v>0.4785797972594382</v>
       </c>
       <c r="K1180">
-        <v>4.98</v>
+        <v>4.62</v>
       </c>
       <c r="L1180">
-        <v>7.24</v>
+        <v>7.28</v>
       </c>
       <c r="M1180">
-        <v>4.7</v>
+        <v>4.82</v>
       </c>
       <c r="N1180">
-        <v>7.27</v>
+        <v>7.62</v>
       </c>
       <c r="O1180">
         <v>1</v>
       </c>
       <c r="P1180" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="1181" spans="1:16">
       <c r="A1181" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B1181" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C1181">
-        <v>5.068961336661395</v>
+        <v>5.091103356935451</v>
       </c>
       <c r="D1181" t="s">
         <v>301</v>
@@ -61314,22 +61314,22 @@
         <v>-1</v>
       </c>
       <c r="G1181">
-        <v>0.009491038663338605</v>
+        <v>0.009608896643064547</v>
       </c>
       <c r="H1181">
         <v>0.009926754622790492</v>
       </c>
       <c r="I1181">
-        <v>-0.2442840405481128</v>
+        <v>-0.2221420202740569</v>
       </c>
       <c r="J1181">
         <v>0.4785797972594382</v>
       </c>
       <c r="K1181">
-        <v>4.62</v>
+        <v>4.72</v>
       </c>
       <c r="L1181">
-        <v>7.28</v>
+        <v>7.35</v>
       </c>
       <c r="M1181">
         <v>4.82</v>
@@ -61341,68 +61341,68 @@
         <v>1</v>
       </c>
       <c r="P1181" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="1182" spans="1:16">
       <c r="A1182" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B1182" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C1182">
-        <v>5.091103356935451</v>
+        <v>4.646081578409318</v>
       </c>
       <c r="D1182" t="s">
-        <v>301</v>
+        <v>497</v>
       </c>
       <c r="E1182">
-        <v>5.313245377209508</v>
+        <v>4.815016356573293</v>
       </c>
       <c r="F1182">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1182">
-        <v>0.009608896643064547</v>
+        <v>0.009973918421590683</v>
       </c>
       <c r="H1182">
-        <v>0.009926754622790492</v>
+        <v>0.009724983643426707</v>
       </c>
       <c r="I1182">
-        <v>-0.2221420202740569</v>
+        <v>0.1689347781639743</v>
       </c>
       <c r="J1182">
-        <v>0.4785797972594382</v>
+        <v>0.5223369454099376</v>
       </c>
       <c r="K1182">
-        <v>4.72</v>
+        <v>5.1</v>
       </c>
       <c r="L1182">
-        <v>7.35</v>
+        <v>7.31</v>
       </c>
       <c r="M1182">
-        <v>4.82</v>
+        <v>4.7</v>
       </c>
       <c r="N1182">
-        <v>7.62</v>
+        <v>7.27</v>
       </c>
       <c r="O1182">
         <v>1</v>
       </c>
       <c r="P1182" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1183" spans="1:16">
       <c r="A1183" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1183" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C1183">
-        <v>4.646081578409318</v>
+        <v>4.662645164588014</v>
       </c>
       <c r="D1183" t="s">
         <v>497</v>
@@ -61414,22 +61414,22 @@
         <v>1</v>
       </c>
       <c r="G1183">
-        <v>0.009973918421590683</v>
+        <v>0.009917354835411986</v>
       </c>
       <c r="H1183">
         <v>0.009724983643426707</v>
       </c>
       <c r="I1183">
-        <v>0.1689347781639743</v>
+        <v>0.1523711919852788</v>
       </c>
       <c r="J1183">
         <v>0.5223369454099376</v>
       </c>
       <c r="K1183">
-        <v>5.1</v>
+        <v>5.03</v>
       </c>
       <c r="L1183">
-        <v>7.31</v>
+        <v>7.29</v>
       </c>
       <c r="M1183">
         <v>4.7</v>
@@ -61446,10 +61446,10 @@
     </row>
     <row r="1184" spans="1:16">
       <c r="A1184" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1184" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C1184">
         <v>4.662645164588014</v>
@@ -61496,10 +61496,10 @@
     </row>
     <row r="1185" spans="1:16">
       <c r="A1185" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1185" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C1185">
         <v>4.662645164588014</v>
@@ -61546,13 +61546,13 @@
     </row>
     <row r="1186" spans="1:16">
       <c r="A1186" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1186" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="C1186">
-        <v>4.662645164588014</v>
+        <v>4.63876201185851</v>
       </c>
       <c r="D1186" t="s">
         <v>497</v>
@@ -61564,22 +61564,22 @@
         <v>1</v>
       </c>
       <c r="G1186">
-        <v>0.009917354835411986</v>
+        <v>0.00984123798814149</v>
       </c>
       <c r="H1186">
         <v>0.009724983643426707</v>
       </c>
       <c r="I1186">
-        <v>0.1523711919852788</v>
+        <v>0.1762543447147822</v>
       </c>
       <c r="J1186">
         <v>0.5223369454099376</v>
       </c>
       <c r="K1186">
-        <v>5.03</v>
+        <v>4.98</v>
       </c>
       <c r="L1186">
-        <v>7.29</v>
+        <v>7.24</v>
       </c>
       <c r="M1186">
         <v>4.7</v>
@@ -61596,46 +61596,46 @@
     </row>
     <row r="1187" spans="1:16">
       <c r="A1187" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1187" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C1187">
-        <v>4.63876201185851</v>
+        <v>4.866803312206089</v>
       </c>
       <c r="D1187" t="s">
-        <v>497</v>
+        <v>301</v>
       </c>
       <c r="E1187">
-        <v>4.815016356573293</v>
+        <v>5.102335923124101</v>
       </c>
       <c r="F1187">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1187">
-        <v>0.00984123798814149</v>
+        <v>0.009693196687793912</v>
       </c>
       <c r="H1187">
-        <v>0.009724983643426707</v>
+        <v>0.0101376640768759</v>
       </c>
       <c r="I1187">
-        <v>0.1762543447147822</v>
+        <v>-0.2355326109180123</v>
       </c>
       <c r="J1187">
         <v>0.5223369454099376</v>
       </c>
       <c r="K1187">
-        <v>4.98</v>
+        <v>4.62</v>
       </c>
       <c r="L1187">
-        <v>7.24</v>
+        <v>7.28</v>
       </c>
       <c r="M1187">
-        <v>4.7</v>
+        <v>4.82</v>
       </c>
       <c r="N1187">
-        <v>7.27</v>
+        <v>7.62</v>
       </c>
       <c r="O1187">
         <v>1</v>
@@ -61646,13 +61646,13 @@
     </row>
     <row r="1188" spans="1:16">
       <c r="A1188" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1188" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C1188">
-        <v>4.866803312206089</v>
+        <v>4.884569617665095</v>
       </c>
       <c r="D1188" t="s">
         <v>301</v>
@@ -61664,22 +61664,22 @@
         <v>-1</v>
       </c>
       <c r="G1188">
-        <v>0.009693196687793912</v>
+        <v>0.009815430382334905</v>
       </c>
       <c r="H1188">
         <v>0.0101376640768759</v>
       </c>
       <c r="I1188">
-        <v>-0.2355326109180123</v>
+        <v>-0.2177663054590058</v>
       </c>
       <c r="J1188">
         <v>0.5223369454099376</v>
       </c>
       <c r="K1188">
-        <v>4.62</v>
+        <v>4.72</v>
       </c>
       <c r="L1188">
-        <v>7.28</v>
+        <v>7.35</v>
       </c>
       <c r="M1188">
         <v>4.82</v>
@@ -61696,63 +61696,63 @@
     </row>
     <row r="1189" spans="1:16">
       <c r="A1189" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B1189" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C1189">
-        <v>4.884569617665095</v>
+        <v>4.194367974425276</v>
       </c>
       <c r="D1189" t="s">
-        <v>301</v>
+        <v>497</v>
       </c>
       <c r="E1189">
-        <v>5.102335923124101</v>
+        <v>4.398731270548783</v>
       </c>
       <c r="F1189">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1189">
-        <v>0.009815430382334905</v>
+        <v>0.01042563202557472</v>
       </c>
       <c r="H1189">
-        <v>0.0101376640768759</v>
+        <v>0.01014126872945122</v>
       </c>
       <c r="I1189">
-        <v>-0.2177663054590058</v>
+        <v>0.2043632961235069</v>
       </c>
       <c r="J1189">
-        <v>0.5223369454099376</v>
+        <v>0.6109082403087693</v>
       </c>
       <c r="K1189">
-        <v>4.72</v>
+        <v>5.1</v>
       </c>
       <c r="L1189">
-        <v>7.35</v>
+        <v>7.31</v>
       </c>
       <c r="M1189">
-        <v>4.82</v>
+        <v>4.7</v>
       </c>
       <c r="N1189">
-        <v>7.62</v>
+        <v>7.27</v>
       </c>
       <c r="O1189">
         <v>1</v>
       </c>
       <c r="P1189" t="s">
-        <v>298</v>
+        <v>636</v>
       </c>
     </row>
     <row r="1190" spans="1:16">
       <c r="A1190" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1190" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C1190">
-        <v>4.194367974425276</v>
+        <v>4.21713155124689</v>
       </c>
       <c r="D1190" t="s">
         <v>497</v>
@@ -61764,22 +61764,22 @@
         <v>1</v>
       </c>
       <c r="G1190">
-        <v>0.01042563202557472</v>
+        <v>0.01036286844875311</v>
       </c>
       <c r="H1190">
         <v>0.01014126872945122</v>
       </c>
       <c r="I1190">
-        <v>0.2043632961235069</v>
+        <v>0.181599719301893</v>
       </c>
       <c r="J1190">
         <v>0.6109082403087693</v>
       </c>
       <c r="K1190">
-        <v>5.1</v>
+        <v>5.03</v>
       </c>
       <c r="L1190">
-        <v>7.31</v>
+        <v>7.29</v>
       </c>
       <c r="M1190">
         <v>4.7</v>
@@ -61796,10 +61796,10 @@
     </row>
     <row r="1191" spans="1:16">
       <c r="A1191" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1191" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C1191">
         <v>4.21713155124689</v>
@@ -61846,10 +61846,10 @@
     </row>
     <row r="1192" spans="1:16">
       <c r="A1192" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1192" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C1192">
         <v>4.21713155124689</v>
@@ -61896,13 +61896,13 @@
     </row>
     <row r="1193" spans="1:16">
       <c r="A1193" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1193" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="C1193">
-        <v>4.21713155124689</v>
+        <v>4.197676963262328</v>
       </c>
       <c r="D1193" t="s">
         <v>497</v>
@@ -61914,22 +61914,22 @@
         <v>1</v>
       </c>
       <c r="G1193">
-        <v>0.01036286844875311</v>
+        <v>0.01028232303673767</v>
       </c>
       <c r="H1193">
         <v>0.01014126872945122</v>
       </c>
       <c r="I1193">
-        <v>0.181599719301893</v>
+        <v>0.201054307286455</v>
       </c>
       <c r="J1193">
         <v>0.6109082403087693</v>
       </c>
       <c r="K1193">
-        <v>5.03</v>
+        <v>4.98</v>
       </c>
       <c r="L1193">
-        <v>7.29</v>
+        <v>7.24</v>
       </c>
       <c r="M1193">
         <v>4.7</v>
@@ -61946,46 +61946,46 @@
     </row>
     <row r="1194" spans="1:16">
       <c r="A1194" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1194" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C1194">
-        <v>4.197676963262328</v>
+        <v>4.457603929773486</v>
       </c>
       <c r="D1194" t="s">
-        <v>497</v>
+        <v>301</v>
       </c>
       <c r="E1194">
-        <v>4.398731270548783</v>
+        <v>4.675422281711732</v>
       </c>
       <c r="F1194">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1194">
-        <v>0.01028232303673767</v>
+        <v>0.01010239607022652</v>
       </c>
       <c r="H1194">
-        <v>0.01014126872945122</v>
+        <v>0.01056457771828827</v>
       </c>
       <c r="I1194">
-        <v>0.201054307286455</v>
+        <v>-0.2178183519382468</v>
       </c>
       <c r="J1194">
         <v>0.6109082403087693</v>
       </c>
       <c r="K1194">
-        <v>4.98</v>
+        <v>4.62</v>
       </c>
       <c r="L1194">
-        <v>7.24</v>
+        <v>7.28</v>
       </c>
       <c r="M1194">
-        <v>4.7</v>
+        <v>4.82</v>
       </c>
       <c r="N1194">
-        <v>7.27</v>
+        <v>7.62</v>
       </c>
       <c r="O1194">
         <v>1</v>
@@ -61996,13 +61996,13 @@
     </row>
     <row r="1195" spans="1:16">
       <c r="A1195" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1195" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C1195">
-        <v>4.457603929773486</v>
+        <v>4.466513105742608</v>
       </c>
       <c r="D1195" t="s">
         <v>301</v>
@@ -62014,22 +62014,22 @@
         <v>-1</v>
       </c>
       <c r="G1195">
-        <v>0.01010239607022652</v>
+        <v>0.01023348689425739</v>
       </c>
       <c r="H1195">
         <v>0.01056457771828827</v>
       </c>
       <c r="I1195">
-        <v>-0.2178183519382468</v>
+        <v>-0.208909175969124</v>
       </c>
       <c r="J1195">
         <v>0.6109082403087693</v>
       </c>
       <c r="K1195">
-        <v>4.62</v>
+        <v>4.72</v>
       </c>
       <c r="L1195">
-        <v>7.28</v>
+        <v>7.35</v>
       </c>
       <c r="M1195">
         <v>4.82</v>
@@ -62046,63 +62046,63 @@
     </row>
     <row r="1196" spans="1:16">
       <c r="A1196" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B1196" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C1196">
-        <v>4.466513105742608</v>
+        <v>4.579720961796916</v>
       </c>
       <c r="D1196" t="s">
-        <v>301</v>
+        <v>497</v>
       </c>
       <c r="E1196">
-        <v>4.675422281711732</v>
+        <v>4.753860494205001</v>
       </c>
       <c r="F1196">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1196">
-        <v>0.01023348689425739</v>
+        <v>0.01004027903820308</v>
       </c>
       <c r="H1196">
-        <v>0.01056457771828827</v>
+        <v>0.009786139505794999</v>
       </c>
       <c r="I1196">
-        <v>-0.208909175969124</v>
+        <v>0.174139532408085</v>
       </c>
       <c r="J1196">
-        <v>0.6109082403087693</v>
+        <v>0.5353488310202125</v>
       </c>
       <c r="K1196">
-        <v>4.72</v>
+        <v>5.1</v>
       </c>
       <c r="L1196">
-        <v>7.35</v>
+        <v>7.31</v>
       </c>
       <c r="M1196">
-        <v>4.82</v>
+        <v>4.7</v>
       </c>
       <c r="N1196">
-        <v>7.62</v>
+        <v>7.27</v>
       </c>
       <c r="O1196">
         <v>1</v>
       </c>
       <c r="P1196" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="1197" spans="1:16">
       <c r="A1197" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1197" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C1197">
-        <v>4.579720961796916</v>
+        <v>4.597195379968332</v>
       </c>
       <c r="D1197" t="s">
         <v>497</v>
@@ -62114,22 +62114,22 @@
         <v>1</v>
       </c>
       <c r="G1197">
-        <v>0.01004027903820308</v>
+        <v>0.009982804620031668</v>
       </c>
       <c r="H1197">
         <v>0.009786139505794999</v>
       </c>
       <c r="I1197">
-        <v>0.174139532408085</v>
+        <v>0.1566651142366693</v>
       </c>
       <c r="J1197">
         <v>0.5353488310202125</v>
       </c>
       <c r="K1197">
-        <v>5.1</v>
+        <v>5.03</v>
       </c>
       <c r="L1197">
-        <v>7.31</v>
+        <v>7.29</v>
       </c>
       <c r="M1197">
         <v>4.7</v>
@@ -62146,10 +62146,10 @@
     </row>
     <row r="1198" spans="1:16">
       <c r="A1198" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1198" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C1198">
         <v>4.597195379968332</v>
@@ -62196,10 +62196,10 @@
     </row>
     <row r="1199" spans="1:16">
       <c r="A1199" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1199" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C1199">
         <v>4.597195379968332</v>
@@ -62246,13 +62246,13 @@
     </row>
     <row r="1200" spans="1:16">
       <c r="A1200" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1200" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="C1200">
-        <v>4.597195379968332</v>
+        <v>4.573962821519341</v>
       </c>
       <c r="D1200" t="s">
         <v>497</v>
@@ -62264,22 +62264,22 @@
         <v>1</v>
       </c>
       <c r="G1200">
-        <v>0.009982804620031668</v>
+        <v>0.009906037178480659</v>
       </c>
       <c r="H1200">
         <v>0.009786139505794999</v>
       </c>
       <c r="I1200">
-        <v>0.1566651142366693</v>
+        <v>0.1798976726856596</v>
       </c>
       <c r="J1200">
         <v>0.5353488310202125</v>
       </c>
       <c r="K1200">
-        <v>5.03</v>
+        <v>4.98</v>
       </c>
       <c r="L1200">
-        <v>7.29</v>
+        <v>7.24</v>
       </c>
       <c r="M1200">
         <v>4.7</v>
@@ -62296,46 +62296,46 @@
     </row>
     <row r="1201" spans="1:16">
       <c r="A1201" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1201" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C1201">
-        <v>4.573962821519341</v>
+        <v>4.806688400686618</v>
       </c>
       <c r="D1201" t="s">
-        <v>497</v>
+        <v>301</v>
       </c>
       <c r="E1201">
-        <v>4.753860494205001</v>
+        <v>5.039618634482576</v>
       </c>
       <c r="F1201">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1201">
-        <v>0.009906037178480659</v>
+        <v>0.009753311599313381</v>
       </c>
       <c r="H1201">
-        <v>0.009786139505794999</v>
+        <v>0.01020038136551743</v>
       </c>
       <c r="I1201">
-        <v>0.1798976726856596</v>
+        <v>-0.2329302337959573</v>
       </c>
       <c r="J1201">
         <v>0.5353488310202125</v>
       </c>
       <c r="K1201">
-        <v>4.98</v>
+        <v>4.62</v>
       </c>
       <c r="L1201">
-        <v>7.24</v>
+        <v>7.28</v>
       </c>
       <c r="M1201">
-        <v>4.7</v>
+        <v>4.82</v>
       </c>
       <c r="N1201">
-        <v>7.27</v>
+        <v>7.62</v>
       </c>
       <c r="O1201">
         <v>1</v>
@@ -62346,13 +62346,13 @@
     </row>
     <row r="1202" spans="1:16">
       <c r="A1202" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B1202" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C1202">
-        <v>4.806688400686618</v>
+        <v>4.823153517584597</v>
       </c>
       <c r="D1202" t="s">
         <v>301</v>
@@ -62364,22 +62364,22 @@
         <v>-1</v>
       </c>
       <c r="G1202">
-        <v>0.009753311599313381</v>
+        <v>0.009876846482415403</v>
       </c>
       <c r="H1202">
         <v>0.01020038136551743</v>
       </c>
       <c r="I1202">
-        <v>-0.2329302337959573</v>
+        <v>-0.2164651168979788</v>
       </c>
       <c r="J1202">
         <v>0.5353488310202125</v>
       </c>
       <c r="K1202">
-        <v>4.62</v>
+        <v>4.72</v>
       </c>
       <c r="L1202">
-        <v>7.28</v>
+        <v>7.35</v>
       </c>
       <c r="M1202">
         <v>4.82</v>
@@ -62396,63 +62396,63 @@
     </row>
     <row r="1203" spans="1:16">
       <c r="A1203" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B1203" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C1203">
-        <v>4.823153517584597</v>
+        <v>4.844065934065937</v>
       </c>
       <c r="D1203" t="s">
-        <v>301</v>
+        <v>501</v>
       </c>
       <c r="E1203">
-        <v>5.039618634482576</v>
+        <v>4.953406593406597</v>
       </c>
       <c r="F1203">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1203">
-        <v>0.009876846482415403</v>
+        <v>0.009775934065934064</v>
       </c>
       <c r="H1203">
-        <v>0.01020038136551743</v>
+        <v>0.009846593406593404</v>
       </c>
       <c r="I1203">
-        <v>-0.2164651168979788</v>
+        <v>0.1093406593406598</v>
       </c>
       <c r="J1203">
-        <v>0.5353488310202125</v>
+        <v>0.4835164835164829</v>
       </c>
       <c r="K1203">
-        <v>4.72</v>
+        <v>5.1</v>
       </c>
       <c r="L1203">
-        <v>7.35</v>
+        <v>7.31</v>
       </c>
       <c r="M1203">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="N1203">
-        <v>7.62</v>
+        <v>7.4</v>
       </c>
       <c r="O1203">
         <v>1</v>
       </c>
       <c r="P1203" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="1204" spans="1:16">
       <c r="A1204" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1204" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C1204">
-        <v>4.844065934065937</v>
+        <v>4.857912087912091</v>
       </c>
       <c r="D1204" t="s">
         <v>501</v>
@@ -62464,22 +62464,22 @@
         <v>1</v>
       </c>
       <c r="G1204">
-        <v>0.009775934065934064</v>
+        <v>0.009722087912087909</v>
       </c>
       <c r="H1204">
         <v>0.009846593406593404</v>
       </c>
       <c r="I1204">
-        <v>0.1093406593406598</v>
+        <v>0.09549450549450622</v>
       </c>
       <c r="J1204">
         <v>0.4835164835164829</v>
       </c>
       <c r="K1204">
-        <v>5.1</v>
+        <v>5.03</v>
       </c>
       <c r="L1204">
-        <v>7.31</v>
+        <v>7.29</v>
       </c>
       <c r="M1204">
         <v>5.06</v>
@@ -62496,13 +62496,13 @@
     </row>
     <row r="1205" spans="1:16">
       <c r="A1205" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1205" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="C1205">
-        <v>4.812417582417586</v>
+        <v>4.857912087912091</v>
       </c>
       <c r="D1205" t="s">
         <v>501</v>
@@ -62514,22 +62514,22 @@
         <v>1</v>
       </c>
       <c r="G1205">
-        <v>0.009647582417582415</v>
+        <v>0.009722087912087909</v>
       </c>
       <c r="H1205">
         <v>0.009846593406593404</v>
       </c>
       <c r="I1205">
-        <v>0.1409890109890108</v>
+        <v>0.09549450549450622</v>
       </c>
       <c r="J1205">
         <v>0.4835164835164829</v>
       </c>
       <c r="K1205">
-        <v>5</v>
+        <v>5.03</v>
       </c>
       <c r="L1205">
-        <v>7.23</v>
+        <v>7.29</v>
       </c>
       <c r="M1205">
         <v>5.06</v>
@@ -62546,13 +62546,13 @@
     </row>
     <row r="1206" spans="1:16">
       <c r="A1206" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1206" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C1206">
-        <v>4.832087912087915</v>
+        <v>4.857912087912091</v>
       </c>
       <c r="D1206" t="s">
         <v>501</v>
@@ -62564,22 +62564,22 @@
         <v>1</v>
       </c>
       <c r="G1206">
-        <v>0.009647912087912087</v>
+        <v>0.009722087912087909</v>
       </c>
       <c r="H1206">
         <v>0.009846593406593404</v>
       </c>
       <c r="I1206">
-        <v>0.121318681318682</v>
+        <v>0.09549450549450622</v>
       </c>
       <c r="J1206">
         <v>0.4835164835164829</v>
       </c>
       <c r="K1206">
-        <v>4.98</v>
+        <v>5.03</v>
       </c>
       <c r="L1206">
-        <v>7.24</v>
+        <v>7.29</v>
       </c>
       <c r="M1206">
         <v>5.06</v>
@@ -62596,46 +62596,46 @@
     </row>
     <row r="1207" spans="1:16">
       <c r="A1207" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1207" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="C1207">
-        <v>5.04615384615385</v>
+        <v>4.832087912087915</v>
       </c>
       <c r="D1207" t="s">
-        <v>301</v>
+        <v>501</v>
       </c>
       <c r="E1207">
-        <v>5.289450549450552</v>
+        <v>4.953406593406597</v>
       </c>
       <c r="F1207">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1207">
-        <v>0.009513846153846151</v>
+        <v>0.009647912087912087</v>
       </c>
       <c r="H1207">
-        <v>0.00995054945054945</v>
+        <v>0.009846593406593404</v>
       </c>
       <c r="I1207">
-        <v>-0.2432967032967026</v>
+        <v>0.121318681318682</v>
       </c>
       <c r="J1207">
         <v>0.4835164835164829</v>
       </c>
       <c r="K1207">
-        <v>4.62</v>
+        <v>4.98</v>
       </c>
       <c r="L1207">
-        <v>7.28</v>
+        <v>7.24</v>
       </c>
       <c r="M1207">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="N1207">
-        <v>7.62</v>
+        <v>7.4</v>
       </c>
       <c r="O1207">
         <v>1</v>
@@ -62646,13 +62646,13 @@
     </row>
     <row r="1208" spans="1:16">
       <c r="A1208" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1208" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C1208">
-        <v>5.0678021978022</v>
+        <v>5.04615384615385</v>
       </c>
       <c r="D1208" t="s">
         <v>301</v>
@@ -62664,22 +62664,22 @@
         <v>-1</v>
       </c>
       <c r="G1208">
-        <v>0.0096321978021978</v>
+        <v>0.009513846153846151</v>
       </c>
       <c r="H1208">
         <v>0.00995054945054945</v>
       </c>
       <c r="I1208">
-        <v>-0.2216483516483523</v>
+        <v>-0.2432967032967026</v>
       </c>
       <c r="J1208">
         <v>0.4835164835164829</v>
       </c>
       <c r="K1208">
-        <v>4.72</v>
+        <v>4.62</v>
       </c>
       <c r="L1208">
-        <v>7.35</v>
+        <v>7.28</v>
       </c>
       <c r="M1208">
         <v>4.82</v>
@@ -62696,63 +62696,63 @@
     </row>
     <row r="1209" spans="1:16">
       <c r="A1209" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1209" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C1209">
-        <v>4.976232772849881</v>
+        <v>5.0678021978022</v>
       </c>
       <c r="D1209" t="s">
-        <v>501</v>
+        <v>301</v>
       </c>
       <c r="E1209">
-        <v>5.084536829533412</v>
+        <v>5.289450549450552</v>
       </c>
       <c r="F1209">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1209">
-        <v>0.009643767227150117</v>
+        <v>0.0096321978021978</v>
       </c>
       <c r="H1209">
-        <v>0.009715463170466588</v>
+        <v>0.00995054945054945</v>
       </c>
       <c r="I1209">
-        <v>0.1083040566835312</v>
+        <v>-0.2216483516483523</v>
       </c>
       <c r="J1209">
-        <v>0.4576014170882586</v>
+        <v>0.4835164835164829</v>
       </c>
       <c r="K1209">
-        <v>5.1</v>
+        <v>4.72</v>
       </c>
       <c r="L1209">
-        <v>7.31</v>
+        <v>7.35</v>
       </c>
       <c r="M1209">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="N1209">
-        <v>7.4</v>
+        <v>7.62</v>
       </c>
       <c r="O1209">
         <v>1</v>
       </c>
       <c r="P1209" t="s">
-        <v>312</v>
+        <v>638</v>
       </c>
     </row>
     <row r="1210" spans="1:16">
       <c r="A1210" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1210" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="C1210">
-        <v>4.941992914558707</v>
+        <v>4.976232772849881</v>
       </c>
       <c r="D1210" t="s">
         <v>501</v>
@@ -62764,22 +62764,22 @@
         <v>1</v>
       </c>
       <c r="G1210">
-        <v>0.009518007085441295</v>
+        <v>0.009643767227150117</v>
       </c>
       <c r="H1210">
         <v>0.009715463170466588</v>
       </c>
       <c r="I1210">
-        <v>0.1425439149747048</v>
+        <v>0.1083040566835312</v>
       </c>
       <c r="J1210">
         <v>0.4576014170882586</v>
       </c>
       <c r="K1210">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L1210">
-        <v>7.23</v>
+        <v>7.31</v>
       </c>
       <c r="M1210">
         <v>5.06</v>
@@ -62791,18 +62791,18 @@
         <v>1</v>
       </c>
       <c r="P1210" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="1211" spans="1:16">
       <c r="A1211" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1211" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C1211">
-        <v>4.961144942900471</v>
+        <v>4.941992914558707</v>
       </c>
       <c r="D1211" t="s">
         <v>501</v>
@@ -62814,22 +62814,22 @@
         <v>1</v>
       </c>
       <c r="G1211">
-        <v>0.00951885505709953</v>
+        <v>0.009518007085441295</v>
       </c>
       <c r="H1211">
         <v>0.009715463170466588</v>
       </c>
       <c r="I1211">
-        <v>0.1233918866329402</v>
+        <v>0.1425439149747048</v>
       </c>
       <c r="J1211">
         <v>0.4576014170882586</v>
       </c>
       <c r="K1211">
-        <v>4.98</v>
+        <v>5</v>
       </c>
       <c r="L1211">
-        <v>7.24</v>
+        <v>7.23</v>
       </c>
       <c r="M1211">
         <v>5.06</v>
@@ -62841,68 +62841,68 @@
         <v>1</v>
       </c>
       <c r="P1211" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="1212" spans="1:16">
       <c r="A1212" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1212" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="C1212">
-        <v>5.165881453052245</v>
+        <v>4.961144942900471</v>
       </c>
       <c r="D1212" t="s">
-        <v>301</v>
+        <v>501</v>
       </c>
       <c r="E1212">
-        <v>5.414361169634594</v>
+        <v>5.084536829533412</v>
       </c>
       <c r="F1212">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1212">
-        <v>0.009394118546947756</v>
+        <v>0.00951885505709953</v>
       </c>
       <c r="H1212">
-        <v>0.009825638830365406</v>
+        <v>0.009715463170466588</v>
       </c>
       <c r="I1212">
-        <v>-0.2484797165823487</v>
+        <v>0.1233918866329402</v>
       </c>
       <c r="J1212">
         <v>0.4576014170882586</v>
       </c>
       <c r="K1212">
-        <v>4.62</v>
+        <v>4.98</v>
       </c>
       <c r="L1212">
-        <v>7.28</v>
+        <v>7.24</v>
       </c>
       <c r="M1212">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="N1212">
-        <v>7.62</v>
+        <v>7.4</v>
       </c>
       <c r="O1212">
         <v>1</v>
       </c>
       <c r="P1212" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="1213" spans="1:16">
       <c r="A1213" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1213" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C1213">
-        <v>5.190121311343419</v>
+        <v>5.165881453052245</v>
       </c>
       <c r="D1213" t="s">
         <v>301</v>
@@ -62914,22 +62914,22 @@
         <v>-1</v>
       </c>
       <c r="G1213">
-        <v>0.009509878688656581</v>
+        <v>0.009394118546947756</v>
       </c>
       <c r="H1213">
         <v>0.009825638830365406</v>
       </c>
       <c r="I1213">
-        <v>-0.2242398582911749</v>
+        <v>-0.2484797165823487</v>
       </c>
       <c r="J1213">
         <v>0.4576014170882586</v>
       </c>
       <c r="K1213">
-        <v>4.72</v>
+        <v>4.62</v>
       </c>
       <c r="L1213">
-        <v>7.35</v>
+        <v>7.28</v>
       </c>
       <c r="M1213">
         <v>4.82</v>
@@ -62941,68 +62941,68 @@
         <v>1</v>
       </c>
       <c r="P1213" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="1214" spans="1:16">
       <c r="A1214" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1214" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C1214">
-        <v>5.114447920426747</v>
+        <v>5.190121311343419</v>
       </c>
       <c r="D1214" t="s">
-        <v>501</v>
+        <v>301</v>
       </c>
       <c r="E1214">
-        <v>5.221667936737125</v>
+        <v>5.414361169634594</v>
       </c>
       <c r="F1214">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1214">
-        <v>0.009505552079573253</v>
+        <v>0.009509878688656581</v>
       </c>
       <c r="H1214">
-        <v>0.009578332063262876</v>
+        <v>0.009825638830365406</v>
       </c>
       <c r="I1214">
-        <v>0.1072200163103787</v>
+        <v>-0.2242398582911749</v>
       </c>
       <c r="J1214">
-        <v>0.4305004077594615</v>
+        <v>0.4576014170882586</v>
       </c>
       <c r="K1214">
-        <v>5.1</v>
+        <v>4.72</v>
       </c>
       <c r="L1214">
-        <v>7.31</v>
+        <v>7.35</v>
       </c>
       <c r="M1214">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="N1214">
-        <v>7.4</v>
+        <v>7.62</v>
       </c>
       <c r="O1214">
         <v>1</v>
       </c>
       <c r="P1214" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
     </row>
     <row r="1215" spans="1:16">
       <c r="A1215" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1215" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="C1215">
-        <v>5.077497961202694</v>
+        <v>5.114447920426747</v>
       </c>
       <c r="D1215" t="s">
         <v>501</v>
@@ -63014,22 +63014,22 @@
         <v>1</v>
       </c>
       <c r="G1215">
-        <v>0.009382502038797308</v>
+        <v>0.009505552079573253</v>
       </c>
       <c r="H1215">
         <v>0.009578332063262876</v>
       </c>
       <c r="I1215">
-        <v>0.1441699755344317</v>
+        <v>0.1072200163103787</v>
       </c>
       <c r="J1215">
         <v>0.4305004077594615</v>
       </c>
       <c r="K1215">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L1215">
-        <v>7.23</v>
+        <v>7.31</v>
       </c>
       <c r="M1215">
         <v>5.06</v>
@@ -63046,13 +63046,13 @@
     </row>
     <row r="1216" spans="1:16">
       <c r="A1216" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1216" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C1216">
-        <v>5.096107969357882</v>
+        <v>5.077497961202694</v>
       </c>
       <c r="D1216" t="s">
         <v>501</v>
@@ -63064,22 +63064,22 @@
         <v>1</v>
       </c>
       <c r="G1216">
-        <v>0.00938389203064212</v>
+        <v>0.009382502038797308</v>
       </c>
       <c r="H1216">
         <v>0.009578332063262876</v>
       </c>
       <c r="I1216">
-        <v>0.1255599673792434</v>
+        <v>0.1441699755344317</v>
       </c>
       <c r="J1216">
         <v>0.4305004077594615</v>
       </c>
       <c r="K1216">
-        <v>4.98</v>
+        <v>5</v>
       </c>
       <c r="L1216">
-        <v>7.24</v>
+        <v>7.23</v>
       </c>
       <c r="M1216">
         <v>5.06</v>
@@ -63096,46 +63096,46 @@
     </row>
     <row r="1217" spans="1:16">
       <c r="A1217" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1217" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="C1217">
-        <v>5.291088116151288</v>
+        <v>5.096107969357882</v>
       </c>
       <c r="D1217" t="s">
-        <v>301</v>
+        <v>501</v>
       </c>
       <c r="E1217">
-        <v>5.544988034599395</v>
+        <v>5.221667936737125</v>
       </c>
       <c r="F1217">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1217">
-        <v>0.009268911883848712</v>
+        <v>0.00938389203064212</v>
       </c>
       <c r="H1217">
-        <v>0.009695011965400605</v>
+        <v>0.009578332063262876</v>
       </c>
       <c r="I1217">
-        <v>-0.2538999184481074</v>
+        <v>0.1255599673792434</v>
       </c>
       <c r="J1217">
         <v>0.4305004077594615</v>
       </c>
       <c r="K1217">
-        <v>4.62</v>
+        <v>4.98</v>
       </c>
       <c r="L1217">
-        <v>7.28</v>
+        <v>7.24</v>
       </c>
       <c r="M1217">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="N1217">
-        <v>7.62</v>
+        <v>7.4</v>
       </c>
       <c r="O1217">
         <v>1</v>
@@ -63146,13 +63146,13 @@
     </row>
     <row r="1218" spans="1:16">
       <c r="A1218" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1218" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C1218">
-        <v>5.318038075375341</v>
+        <v>5.291088116151288</v>
       </c>
       <c r="D1218" t="s">
         <v>301</v>
@@ -63164,22 +63164,22 @@
         <v>-1</v>
       </c>
       <c r="G1218">
-        <v>0.009381961924624658</v>
+        <v>0.009268911883848712</v>
       </c>
       <c r="H1218">
         <v>0.009695011965400605</v>
       </c>
       <c r="I1218">
-        <v>-0.2269499592240543</v>
+        <v>-0.2538999184481074</v>
       </c>
       <c r="J1218">
         <v>0.4305004077594615</v>
       </c>
       <c r="K1218">
-        <v>4.72</v>
+        <v>4.62</v>
       </c>
       <c r="L1218">
-        <v>7.35</v>
+        <v>7.28</v>
       </c>
       <c r="M1218">
         <v>4.82</v>
@@ -63196,63 +63196,63 @@
     </row>
     <row r="1219" spans="1:16">
       <c r="A1219" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1219" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="C1219">
-        <v>5.395229280605809</v>
+        <v>5.318038075375341</v>
       </c>
       <c r="D1219" t="s">
-        <v>501</v>
+        <v>301</v>
       </c>
       <c r="E1219">
-        <v>5.543212031973079</v>
+        <v>5.544988034599395</v>
       </c>
       <c r="F1219">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1219">
-        <v>0.009064770719394192</v>
+        <v>0.009381961924624658</v>
       </c>
       <c r="H1219">
-        <v>0.009256787968026921</v>
+        <v>0.009695011965400605</v>
       </c>
       <c r="I1219">
-        <v>0.1479827513672696</v>
+        <v>-0.2269499592240543</v>
       </c>
       <c r="J1219">
-        <v>0.3669541438788382</v>
+        <v>0.4305004077594615</v>
       </c>
       <c r="K1219">
-        <v>5</v>
+        <v>4.72</v>
       </c>
       <c r="L1219">
-        <v>7.23</v>
+        <v>7.35</v>
       </c>
       <c r="M1219">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="N1219">
-        <v>7.4</v>
+        <v>7.62</v>
       </c>
       <c r="O1219">
         <v>1</v>
       </c>
       <c r="P1219" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="1220" spans="1:16">
       <c r="A1220" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1220" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C1220">
-        <v>5.412568363483386</v>
+        <v>5.395229280605809</v>
       </c>
       <c r="D1220" t="s">
         <v>501</v>
@@ -63264,22 +63264,22 @@
         <v>1</v>
       </c>
       <c r="G1220">
-        <v>0.009067431636516615</v>
+        <v>0.009064770719394192</v>
       </c>
       <c r="H1220">
         <v>0.009256787968026921</v>
       </c>
       <c r="I1220">
-        <v>0.130643668489693</v>
+        <v>0.1479827513672696</v>
       </c>
       <c r="J1220">
         <v>0.3669541438788382</v>
       </c>
       <c r="K1220">
-        <v>4.98</v>
+        <v>5</v>
       </c>
       <c r="L1220">
-        <v>7.24</v>
+        <v>7.23</v>
       </c>
       <c r="M1220">
         <v>5.06</v>
@@ -63296,46 +63296,46 @@
     </row>
     <row r="1221" spans="1:16">
       <c r="A1221" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1221" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="C1221">
-        <v>5.617976440891884</v>
+        <v>5.412568363483386</v>
       </c>
       <c r="D1221" t="s">
-        <v>301</v>
+        <v>501</v>
       </c>
       <c r="E1221">
-        <v>5.851281026504</v>
+        <v>5.543212031973079</v>
       </c>
       <c r="F1221">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1221">
-        <v>0.009082023559108116</v>
+        <v>0.009067431636516615</v>
       </c>
       <c r="H1221">
-        <v>0.009388718973496002</v>
+        <v>0.009256787968026921</v>
       </c>
       <c r="I1221">
-        <v>-0.2333045856121165</v>
+        <v>0.130643668489693</v>
       </c>
       <c r="J1221">
         <v>0.3669541438788382</v>
       </c>
       <c r="K1221">
-        <v>4.72</v>
+        <v>4.98</v>
       </c>
       <c r="L1221">
-        <v>7.35</v>
+        <v>7.24</v>
       </c>
       <c r="M1221">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="N1221">
-        <v>7.62</v>
+        <v>7.4</v>
       </c>
       <c r="O1221">
         <v>1</v>
@@ -63346,63 +63346,63 @@
     </row>
     <row r="1222" spans="1:16">
       <c r="A1222" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1222" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="C1222">
-        <v>5.589932664326452</v>
+        <v>5.617976440891884</v>
       </c>
       <c r="D1222" t="s">
-        <v>501</v>
+        <v>301</v>
       </c>
       <c r="E1222">
-        <v>5.740251856298369</v>
+        <v>5.851281026504</v>
       </c>
       <c r="F1222">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1222">
-        <v>0.00887006733567355</v>
+        <v>0.009082023559108116</v>
       </c>
       <c r="H1222">
-        <v>0.009059748143701632</v>
+        <v>0.009388718973496002</v>
       </c>
       <c r="I1222">
-        <v>0.1503191919719171</v>
+        <v>-0.2333045856121165</v>
       </c>
       <c r="J1222">
-        <v>0.3280134671347097</v>
+        <v>0.3669541438788382</v>
       </c>
       <c r="K1222">
-        <v>5</v>
+        <v>4.72</v>
       </c>
       <c r="L1222">
-        <v>7.23</v>
+        <v>7.35</v>
       </c>
       <c r="M1222">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="N1222">
-        <v>7.4</v>
+        <v>7.62</v>
       </c>
       <c r="O1222">
         <v>1</v>
       </c>
       <c r="P1222" t="s">
-        <v>639</v>
+        <v>299</v>
       </c>
     </row>
     <row r="1223" spans="1:16">
       <c r="A1223" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1223" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C1223">
-        <v>5.606492933669146</v>
+        <v>5.589932664326452</v>
       </c>
       <c r="D1223" t="s">
         <v>501</v>
@@ -63414,22 +63414,22 @@
         <v>1</v>
       </c>
       <c r="G1223">
-        <v>0.008873507066330855</v>
+        <v>0.00887006733567355</v>
       </c>
       <c r="H1223">
         <v>0.009059748143701632</v>
       </c>
       <c r="I1223">
-        <v>0.1337589226292231</v>
+        <v>0.1503191919719171</v>
       </c>
       <c r="J1223">
         <v>0.3280134671347097</v>
       </c>
       <c r="K1223">
-        <v>4.98</v>
+        <v>5</v>
       </c>
       <c r="L1223">
-        <v>7.24</v>
+        <v>7.23</v>
       </c>
       <c r="M1223">
         <v>5.06</v>
@@ -63446,46 +63446,46 @@
     </row>
     <row r="1224" spans="1:16">
       <c r="A1224" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1224" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="C1224">
-        <v>5.80177643512417</v>
+        <v>5.606492933669146</v>
       </c>
       <c r="D1224" t="s">
-        <v>301</v>
+        <v>501</v>
       </c>
       <c r="E1224">
-        <v>6.038975088410699</v>
+        <v>5.740251856298369</v>
       </c>
       <c r="F1224">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1224">
-        <v>0.00889822356487583</v>
+        <v>0.008873507066330855</v>
       </c>
       <c r="H1224">
-        <v>0.009201024911589301</v>
+        <v>0.009059748143701632</v>
       </c>
       <c r="I1224">
-        <v>-0.2371986532865291</v>
+        <v>0.1337589226292231</v>
       </c>
       <c r="J1224">
         <v>0.3280134671347097</v>
       </c>
       <c r="K1224">
-        <v>4.72</v>
+        <v>4.98</v>
       </c>
       <c r="L1224">
-        <v>7.35</v>
+        <v>7.24</v>
       </c>
       <c r="M1224">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="N1224">
-        <v>7.62</v>
+        <v>7.4</v>
       </c>
       <c r="O1224">
         <v>1</v>
@@ -63496,146 +63496,146 @@
     </row>
     <row r="1225" spans="1:16">
       <c r="A1225" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1225" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="C1225">
-        <v>5.496374966852297</v>
+        <v>5.80177643512417</v>
       </c>
       <c r="D1225" t="s">
-        <v>501</v>
+        <v>301</v>
       </c>
       <c r="E1225">
-        <v>5.645571466454525</v>
+        <v>6.038975088410699</v>
       </c>
       <c r="F1225">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1225">
-        <v>0.008963625033147704</v>
+        <v>0.00889822356487583</v>
       </c>
       <c r="H1225">
-        <v>0.009154428533545476</v>
+        <v>0.009201024911589301</v>
       </c>
       <c r="I1225">
-        <v>0.1491964996022279</v>
+        <v>-0.2371986532865291</v>
       </c>
       <c r="J1225">
-        <v>0.3467250066295405</v>
+        <v>0.3280134671347097</v>
       </c>
       <c r="K1225">
-        <v>5</v>
+        <v>4.72</v>
       </c>
       <c r="L1225">
-        <v>7.23</v>
+        <v>7.35</v>
       </c>
       <c r="M1225">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="N1225">
-        <v>7.4</v>
+        <v>7.62</v>
       </c>
       <c r="O1225">
         <v>1</v>
       </c>
       <c r="P1225" t="s">
-        <v>305</v>
+        <v>639</v>
       </c>
     </row>
     <row r="1226" spans="1:16">
       <c r="A1226" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1226" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C1226">
-        <v>5.513309466984888</v>
+        <v>5.625694953739352</v>
       </c>
       <c r="D1226" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E1226">
-        <v>5.645571466454525</v>
+        <v>5.759453876368575</v>
       </c>
       <c r="F1226">
         <v>1</v>
       </c>
       <c r="G1226">
-        <v>0.008966690533015112</v>
+        <v>0.008794305046260649</v>
       </c>
       <c r="H1226">
-        <v>0.009154428533545476</v>
+        <v>0.008980546123631425</v>
       </c>
       <c r="I1226">
-        <v>0.1322619994696375</v>
+        <v>0.1337589226292231</v>
       </c>
       <c r="J1226">
-        <v>0.3467250066295405</v>
+        <v>0.3280134671347097</v>
       </c>
       <c r="K1226">
-        <v>4.98</v>
+        <v>4.83</v>
       </c>
       <c r="L1226">
-        <v>7.24</v>
+        <v>7.21</v>
       </c>
       <c r="M1226">
-        <v>5.06</v>
+        <v>4.91</v>
       </c>
       <c r="N1226">
-        <v>7.4</v>
+        <v>7.37</v>
       </c>
       <c r="O1226">
         <v>1</v>
       </c>
       <c r="P1226" t="s">
-        <v>305</v>
+        <v>639</v>
       </c>
     </row>
     <row r="1227" spans="1:16">
       <c r="A1227" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1227" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="C1227">
-        <v>5.713457968708568</v>
+        <v>5.496374966852297</v>
       </c>
       <c r="D1227" t="s">
-        <v>301</v>
+        <v>501</v>
       </c>
       <c r="E1227">
-        <v>5.948785468045615</v>
+        <v>5.645571466454525</v>
       </c>
       <c r="F1227">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1227">
-        <v>0.008986542031291431</v>
+        <v>0.008963625033147704</v>
       </c>
       <c r="H1227">
-        <v>0.009291214531954384</v>
+        <v>0.009154428533545476</v>
       </c>
       <c r="I1227">
-        <v>-0.2353274993370462</v>
+        <v>0.1491964996022279</v>
       </c>
       <c r="J1227">
         <v>0.3467250066295405</v>
       </c>
       <c r="K1227">
-        <v>4.72</v>
+        <v>5</v>
       </c>
       <c r="L1227">
-        <v>7.35</v>
+        <v>7.23</v>
       </c>
       <c r="M1227">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="N1227">
-        <v>7.62</v>
+        <v>7.4</v>
       </c>
       <c r="O1227">
         <v>1</v>
@@ -63646,40 +63646,40 @@
     </row>
     <row r="1228" spans="1:16">
       <c r="A1228" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1228" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C1228">
-        <v>5.171207853179688</v>
+        <v>5.513309466984888</v>
       </c>
       <c r="D1228" t="s">
         <v>501</v>
       </c>
       <c r="E1228">
-        <v>5.316502347417844</v>
+        <v>5.645571466454525</v>
       </c>
       <c r="F1228">
         <v>1</v>
       </c>
       <c r="G1228">
-        <v>0.009288792146820313</v>
+        <v>0.008966690533015112</v>
       </c>
       <c r="H1228">
-        <v>0.009483497652582157</v>
+        <v>0.009154428533545476</v>
       </c>
       <c r="I1228">
-        <v>0.145294494238156</v>
+        <v>0.1322619994696375</v>
       </c>
       <c r="J1228">
-        <v>0.4117584293640626</v>
+        <v>0.3467250066295405</v>
       </c>
       <c r="K1228">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="L1228">
-        <v>7.23</v>
+        <v>7.24</v>
       </c>
       <c r="M1228">
         <v>5.06</v>
@@ -63691,101 +63691,101 @@
         <v>1</v>
       </c>
       <c r="P1228" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
     </row>
     <row r="1229" spans="1:16">
       <c r="A1229" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1229" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="C1229">
-        <v>5.189443021766968</v>
+        <v>5.713457968708568</v>
       </c>
       <c r="D1229" t="s">
-        <v>501</v>
+        <v>301</v>
       </c>
       <c r="E1229">
-        <v>5.316502347417844</v>
+        <v>5.948785468045615</v>
       </c>
       <c r="F1229">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1229">
-        <v>0.009290556978233031</v>
+        <v>0.008986542031291431</v>
       </c>
       <c r="H1229">
-        <v>0.009483497652582157</v>
+        <v>0.009291214531954384</v>
       </c>
       <c r="I1229">
-        <v>0.1270593256508752</v>
+        <v>-0.2353274993370462</v>
       </c>
       <c r="J1229">
-        <v>0.4117584293640626</v>
+        <v>0.3467250066295405</v>
       </c>
       <c r="K1229">
-        <v>4.98</v>
+        <v>4.72</v>
       </c>
       <c r="L1229">
-        <v>7.24</v>
+        <v>7.35</v>
       </c>
       <c r="M1229">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="N1229">
-        <v>7.4</v>
+        <v>7.62</v>
       </c>
       <c r="O1229">
         <v>1</v>
       </c>
       <c r="P1229" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
     </row>
     <row r="1230" spans="1:16">
       <c r="A1230" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1230" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="C1230">
-        <v>5.406500213401625</v>
+        <v>5.171207853179688</v>
       </c>
       <c r="D1230" t="s">
-        <v>301</v>
+        <v>501</v>
       </c>
       <c r="E1230">
-        <v>5.635324370465218</v>
+        <v>5.316502347417844</v>
       </c>
       <c r="F1230">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1230">
-        <v>0.009293499786598375</v>
+        <v>0.009288792146820313</v>
       </c>
       <c r="H1230">
-        <v>0.009604675629534782</v>
+        <v>0.009483497652582157</v>
       </c>
       <c r="I1230">
-        <v>-0.2288241570635936</v>
+        <v>0.145294494238156</v>
       </c>
       <c r="J1230">
         <v>0.4117584293640626</v>
       </c>
       <c r="K1230">
-        <v>4.72</v>
+        <v>5</v>
       </c>
       <c r="L1230">
-        <v>7.35</v>
+        <v>7.23</v>
       </c>
       <c r="M1230">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="N1230">
-        <v>7.62</v>
+        <v>7.4</v>
       </c>
       <c r="O1230">
         <v>1</v>
@@ -63796,40 +63796,40 @@
     </row>
     <row r="1231" spans="1:16">
       <c r="A1231" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1231" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C1231">
-        <v>4.974344857020913</v>
+        <v>5.189443021766968</v>
       </c>
       <c r="D1231" t="s">
         <v>501</v>
       </c>
       <c r="E1231">
-        <v>5.117276995305165</v>
+        <v>5.316502347417844</v>
       </c>
       <c r="F1231">
         <v>1</v>
       </c>
       <c r="G1231">
-        <v>0.009485655142979088</v>
+        <v>0.009290556978233031</v>
       </c>
       <c r="H1231">
-        <v>0.009682723004694836</v>
+        <v>0.009483497652582157</v>
       </c>
       <c r="I1231">
-        <v>0.1429321382842517</v>
+        <v>0.1270593256508752</v>
       </c>
       <c r="J1231">
-        <v>0.4511310285958173</v>
+        <v>0.4117584293640626</v>
       </c>
       <c r="K1231">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="L1231">
-        <v>7.23</v>
+        <v>7.24</v>
       </c>
       <c r="M1231">
         <v>5.06</v>
@@ -63841,101 +63841,101 @@
         <v>1</v>
       </c>
       <c r="P1231" t="s">
-        <v>640</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1232" spans="1:16">
       <c r="A1232" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1232" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="C1232">
-        <v>4.99336747759283</v>
+        <v>5.406500213401625</v>
       </c>
       <c r="D1232" t="s">
-        <v>501</v>
+        <v>301</v>
       </c>
       <c r="E1232">
-        <v>5.117276995305165</v>
+        <v>5.635324370465218</v>
       </c>
       <c r="F1232">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1232">
-        <v>0.00948663252240717</v>
+        <v>0.009293499786598375</v>
       </c>
       <c r="H1232">
-        <v>0.009682723004694836</v>
+        <v>0.009604675629534782</v>
       </c>
       <c r="I1232">
-        <v>0.1239095177123346</v>
+        <v>-0.2288241570635936</v>
       </c>
       <c r="J1232">
-        <v>0.4511310285958173</v>
+        <v>0.4117584293640626</v>
       </c>
       <c r="K1232">
-        <v>4.98</v>
+        <v>4.72</v>
       </c>
       <c r="L1232">
-        <v>7.24</v>
+        <v>7.35</v>
       </c>
       <c r="M1232">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="N1232">
-        <v>7.4</v>
+        <v>7.62</v>
       </c>
       <c r="O1232">
         <v>1</v>
       </c>
       <c r="P1232" t="s">
-        <v>640</v>
+        <v>315</v>
       </c>
     </row>
     <row r="1233" spans="1:16">
       <c r="A1233" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1233" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="C1233">
-        <v>5.220661545027742</v>
+        <v>4.974344857020913</v>
       </c>
       <c r="D1233" t="s">
-        <v>301</v>
+        <v>501</v>
       </c>
       <c r="E1233">
-        <v>5.44554844216816</v>
+        <v>5.117276995305165</v>
       </c>
       <c r="F1233">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1233">
-        <v>0.009479338454972258</v>
+        <v>0.009485655142979088</v>
       </c>
       <c r="H1233">
-        <v>0.009794451557831841</v>
+        <v>0.009682723004694836</v>
       </c>
       <c r="I1233">
-        <v>-0.2248868971404185</v>
+        <v>0.1429321382842517</v>
       </c>
       <c r="J1233">
         <v>0.4511310285958173</v>
       </c>
       <c r="K1233">
-        <v>4.72</v>
+        <v>5</v>
       </c>
       <c r="L1233">
-        <v>7.35</v>
+        <v>7.23</v>
       </c>
       <c r="M1233">
-        <v>4.82</v>
+        <v>5.06</v>
       </c>
       <c r="N1233">
-        <v>7.62</v>
+        <v>7.4</v>
       </c>
       <c r="O1233">
         <v>1</v>
@@ -63946,40 +63946,40 @@
     </row>
     <row r="1234" spans="1:16">
       <c r="A1234" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1234" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C1234">
-        <v>5.581350896955229</v>
+        <v>4.99336747759283</v>
       </c>
       <c r="D1234" t="s">
         <v>501</v>
       </c>
       <c r="E1234">
-        <v>5.731567107718692</v>
+        <v>5.117276995305165</v>
       </c>
       <c r="F1234">
         <v>1</v>
       </c>
       <c r="G1234">
-        <v>0.008878649103044773</v>
+        <v>0.00948663252240717</v>
       </c>
       <c r="H1234">
-        <v>0.009068432892281309</v>
+        <v>0.009682723004694836</v>
       </c>
       <c r="I1234">
-        <v>0.150216210763463</v>
+        <v>0.1239095177123346</v>
       </c>
       <c r="J1234">
-        <v>0.3297298206089543</v>
+        <v>0.4511310285958173</v>
       </c>
       <c r="K1234">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="L1234">
-        <v>7.23</v>
+        <v>7.24</v>
       </c>
       <c r="M1234">
         <v>5.06</v>
@@ -63991,89 +63991,89 @@
         <v>1</v>
       </c>
       <c r="P1234" t="s">
-        <v>316</v>
+        <v>640</v>
       </c>
     </row>
     <row r="1235" spans="1:16">
       <c r="A1235" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1235" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C1235">
-        <v>5.597945493367408</v>
+        <v>5.195774647887324</v>
       </c>
       <c r="D1235" t="s">
-        <v>501</v>
+        <v>301</v>
       </c>
       <c r="E1235">
-        <v>5.731567107718692</v>
+        <v>5.44554844216816</v>
       </c>
       <c r="F1235">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1235">
-        <v>0.008882054506632592</v>
+        <v>0.009364225352112676</v>
       </c>
       <c r="H1235">
-        <v>0.009068432892281309</v>
+        <v>0.009794451557831841</v>
       </c>
       <c r="I1235">
-        <v>0.1336216143512843</v>
+        <v>-0.249773794280836</v>
       </c>
       <c r="J1235">
-        <v>0.3297298206089543</v>
+        <v>0.4511310285958173</v>
       </c>
       <c r="K1235">
-        <v>4.98</v>
+        <v>4.62</v>
       </c>
       <c r="L1235">
-        <v>7.24</v>
+        <v>7.28</v>
       </c>
       <c r="M1235">
-        <v>5.06</v>
+        <v>4.82</v>
       </c>
       <c r="N1235">
-        <v>7.4</v>
+        <v>7.62</v>
       </c>
       <c r="O1235">
         <v>1</v>
       </c>
       <c r="P1235" t="s">
-        <v>316</v>
+        <v>640</v>
       </c>
     </row>
     <row r="1236" spans="1:16">
       <c r="A1236" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1236" t="s">
         <v>320</v>
       </c>
       <c r="C1236">
-        <v>5.793675246725735</v>
+        <v>5.220661545027742</v>
       </c>
       <c r="D1236" t="s">
         <v>301</v>
       </c>
       <c r="E1236">
-        <v>6.03070226466484</v>
+        <v>5.44554844216816</v>
       </c>
       <c r="F1236">
         <v>-1</v>
       </c>
       <c r="G1236">
-        <v>0.008906324753274264</v>
+        <v>0.009479338454972258</v>
       </c>
       <c r="H1236">
-        <v>0.009209297735335159</v>
+        <v>0.009794451557831841</v>
       </c>
       <c r="I1236">
-        <v>-0.2370270179391047</v>
+        <v>-0.2248868971404185</v>
       </c>
       <c r="J1236">
-        <v>0.3297298206089543</v>
+        <v>0.4511310285958173</v>
       </c>
       <c r="K1236">
         <v>4.72</v>
@@ -64091,6 +64091,156 @@
         <v>1</v>
       </c>
       <c r="P1236" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:16">
+      <c r="A1237" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1237" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1237">
+        <v>5.581350896955229</v>
+      </c>
+      <c r="D1237" t="s">
+        <v>501</v>
+      </c>
+      <c r="E1237">
+        <v>5.731567107718692</v>
+      </c>
+      <c r="F1237">
+        <v>1</v>
+      </c>
+      <c r="G1237">
+        <v>0.008878649103044773</v>
+      </c>
+      <c r="H1237">
+        <v>0.009068432892281309</v>
+      </c>
+      <c r="I1237">
+        <v>0.150216210763463</v>
+      </c>
+      <c r="J1237">
+        <v>0.3297298206089543</v>
+      </c>
+      <c r="K1237">
+        <v>5</v>
+      </c>
+      <c r="L1237">
+        <v>7.23</v>
+      </c>
+      <c r="M1237">
+        <v>5.06</v>
+      </c>
+      <c r="N1237">
+        <v>7.4</v>
+      </c>
+      <c r="O1237">
+        <v>1</v>
+      </c>
+      <c r="P1237" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:16">
+      <c r="A1238" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1238" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1238">
+        <v>5.597945493367408</v>
+      </c>
+      <c r="D1238" t="s">
+        <v>501</v>
+      </c>
+      <c r="E1238">
+        <v>5.731567107718692</v>
+      </c>
+      <c r="F1238">
+        <v>1</v>
+      </c>
+      <c r="G1238">
+        <v>0.008882054506632592</v>
+      </c>
+      <c r="H1238">
+        <v>0.009068432892281309</v>
+      </c>
+      <c r="I1238">
+        <v>0.1336216143512843</v>
+      </c>
+      <c r="J1238">
+        <v>0.3297298206089543</v>
+      </c>
+      <c r="K1238">
+        <v>4.98</v>
+      </c>
+      <c r="L1238">
+        <v>7.24</v>
+      </c>
+      <c r="M1238">
+        <v>5.06</v>
+      </c>
+      <c r="N1238">
+        <v>7.4</v>
+      </c>
+      <c r="O1238">
+        <v>1</v>
+      </c>
+      <c r="P1238" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:16">
+      <c r="A1239" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1239" t="s">
+        <v>320</v>
+      </c>
+      <c r="C1239">
+        <v>5.793675246725735</v>
+      </c>
+      <c r="D1239" t="s">
+        <v>301</v>
+      </c>
+      <c r="E1239">
+        <v>6.03070226466484</v>
+      </c>
+      <c r="F1239">
+        <v>-1</v>
+      </c>
+      <c r="G1239">
+        <v>0.008906324753274264</v>
+      </c>
+      <c r="H1239">
+        <v>0.009209297735335159</v>
+      </c>
+      <c r="I1239">
+        <v>-0.2370270179391047</v>
+      </c>
+      <c r="J1239">
+        <v>0.3297298206089543</v>
+      </c>
+      <c r="K1239">
+        <v>4.72</v>
+      </c>
+      <c r="L1239">
+        <v>7.35</v>
+      </c>
+      <c r="M1239">
+        <v>4.82</v>
+      </c>
+      <c r="N1239">
+        <v>7.62</v>
+      </c>
+      <c r="O1239">
+        <v>1</v>
+      </c>
+      <c r="P1239" t="s">
         <v>316</v>
       </c>
     </row>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3291" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3288" uniqueCount="610">
   <si>
     <t>trade_time</t>
   </si>
@@ -1427,6 +1427,9 @@
   </si>
   <si>
     <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
   </si>
   <si>
     <t>2016-01-29</t>
@@ -2198,7 +2201,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1093"/>
+  <dimension ref="A1:P1092"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2295,7 +2298,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2345,7 +2348,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2395,7 +2398,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2445,7 +2448,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2495,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2545,7 +2548,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2595,7 +2598,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2645,7 +2648,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2695,7 +2698,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2745,7 +2748,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2795,7 +2798,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2845,7 +2848,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2895,7 +2898,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2945,7 +2948,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2995,7 +2998,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -3045,7 +3048,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -3095,7 +3098,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -3145,7 +3148,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -3195,7 +3198,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -3245,7 +3248,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -3295,7 +3298,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3345,7 +3348,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3395,7 +3398,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3445,7 +3448,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3495,7 +3498,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3545,7 +3548,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3595,7 +3598,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3645,7 +3648,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3695,7 +3698,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3745,7 +3748,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3795,7 +3798,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3845,7 +3848,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3895,7 +3898,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3945,7 +3948,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3995,7 +3998,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -4045,7 +4048,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -4095,7 +4098,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -4145,7 +4148,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -4195,7 +4198,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -4245,7 +4248,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -4295,7 +4298,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4345,7 +4348,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4395,7 +4398,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4445,7 +4448,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4495,7 +4498,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4545,7 +4548,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4595,7 +4598,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4645,7 +4648,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4695,7 +4698,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4745,7 +4748,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4795,7 +4798,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4845,7 +4848,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4895,7 +4898,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -5795,7 +5798,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5845,7 +5848,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5895,7 +5898,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5945,7 +5948,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5995,7 +5998,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -6045,7 +6048,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -6095,7 +6098,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -6145,7 +6148,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -6195,7 +6198,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -6245,7 +6248,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -6295,7 +6298,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -6345,7 +6348,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -6395,7 +6398,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6445,7 +6448,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6495,7 +6498,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6545,7 +6548,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6595,7 +6598,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6645,7 +6648,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6695,7 +6698,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6745,7 +6748,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -7345,7 +7348,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7395,7 +7398,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7445,7 +7448,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7495,7 +7498,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7545,7 +7548,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7595,7 +7598,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7645,7 +7648,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7695,7 +7698,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7745,7 +7748,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7795,7 +7798,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7845,7 +7848,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7895,7 +7898,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7945,7 +7948,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7995,7 +7998,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -8045,7 +8048,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -8095,7 +8098,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -8145,7 +8148,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -8195,7 +8198,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -8245,7 +8248,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -8295,7 +8298,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -8345,7 +8348,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -8695,7 +8698,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8745,7 +8748,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8795,7 +8798,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8845,7 +8848,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8895,7 +8898,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8945,7 +8948,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8995,7 +8998,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -9045,7 +9048,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -9095,7 +9098,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -9145,7 +9148,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -9195,7 +9198,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -9245,7 +9248,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -9295,7 +9298,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -9345,7 +9348,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9395,7 +9398,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9445,7 +9448,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9495,7 +9498,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9545,7 +9548,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9595,7 +9598,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9945,7 +9948,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9995,7 +9998,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -10045,7 +10048,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -10095,7 +10098,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -10145,7 +10148,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -10195,7 +10198,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -10245,7 +10248,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10295,7 +10298,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -10345,7 +10348,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10395,7 +10398,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -10445,7 +10448,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10495,7 +10498,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10545,7 +10548,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10595,7 +10598,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10645,7 +10648,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10695,7 +10698,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10745,7 +10748,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10795,7 +10798,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -12145,7 +12148,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -12195,7 +12198,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -12245,7 +12248,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -12295,7 +12298,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -12345,7 +12348,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12395,7 +12398,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12445,7 +12448,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12495,7 +12498,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12545,7 +12548,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12695,7 +12698,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12745,7 +12748,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12945,7 +12948,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12995,7 +12998,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -13045,7 +13048,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -13095,7 +13098,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -13145,7 +13148,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -13195,7 +13198,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -13645,7 +13648,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13695,7 +13698,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13745,7 +13748,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13795,7 +13798,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13845,7 +13848,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -18545,7 +18548,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -18595,7 +18598,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18645,7 +18648,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18695,7 +18698,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18745,7 +18748,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18795,7 +18798,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18845,7 +18848,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -19095,7 +19098,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -19145,7 +19148,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -19195,7 +19198,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -19245,7 +19248,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -19295,7 +19298,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -19795,7 +19798,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19845,7 +19848,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19895,7 +19898,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19945,7 +19948,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -20095,7 +20098,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -20145,7 +20148,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -20195,7 +20198,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -20245,7 +20248,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -20295,7 +20298,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -20545,7 +20548,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20595,7 +20598,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20645,7 +20648,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20695,7 +20698,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20745,7 +20748,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20795,7 +20798,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20845,7 +20848,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20895,7 +20898,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20945,7 +20948,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20995,7 +20998,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -21045,7 +21048,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -21095,7 +21098,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -21145,7 +21148,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -21195,7 +21198,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -21245,7 +21248,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -21295,7 +21298,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -21345,7 +21348,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21395,7 +21398,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21445,7 +21448,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -21495,7 +21498,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21545,7 +21548,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21595,7 +21598,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21645,7 +21648,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21695,7 +21698,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21745,7 +21748,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21795,7 +21798,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21845,7 +21848,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21895,7 +21898,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21945,7 +21948,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21995,7 +21998,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -22045,7 +22048,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -22095,7 +22098,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -22145,7 +22148,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -22195,7 +22198,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -22245,7 +22248,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -22295,7 +22298,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -22345,7 +22348,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -22395,7 +22398,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22445,7 +22448,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22495,7 +22498,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22545,7 +22548,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22595,7 +22598,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22645,7 +22648,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22695,7 +22698,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22995,7 +22998,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -23045,7 +23048,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -23095,7 +23098,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -23145,7 +23148,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -23195,7 +23198,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -23895,7 +23898,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23945,7 +23948,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23995,7 +23998,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -24045,7 +24048,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -24095,7 +24098,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -24145,7 +24148,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -24195,7 +24198,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -24245,7 +24248,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -24295,7 +24298,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -24345,7 +24348,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24395,7 +24398,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24445,7 +24448,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24495,7 +24498,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24545,7 +24548,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24595,7 +24598,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24645,7 +24648,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24695,7 +24698,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24745,7 +24748,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24795,7 +24798,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24845,7 +24848,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24895,7 +24898,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -25245,7 +25248,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -25295,7 +25298,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -25345,7 +25348,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -25395,7 +25398,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25445,7 +25448,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -25495,7 +25498,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25545,7 +25548,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25595,7 +25598,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25645,7 +25648,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25695,7 +25698,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25745,7 +25748,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25795,7 +25798,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25845,7 +25848,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25895,7 +25898,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25945,7 +25948,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25995,7 +25998,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -26045,7 +26048,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -26095,7 +26098,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -26145,7 +26148,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -26195,7 +26198,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -26245,7 +26248,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -26295,7 +26298,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -26345,7 +26348,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26395,7 +26398,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26445,7 +26448,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26495,7 +26498,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26545,7 +26548,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26595,7 +26598,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26645,7 +26648,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26695,7 +26698,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26745,7 +26748,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26795,7 +26798,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26845,7 +26848,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26895,7 +26898,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26945,7 +26948,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26995,7 +26998,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -27045,7 +27048,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -27095,7 +27098,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -27145,7 +27148,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -27195,7 +27198,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -27245,7 +27248,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -27295,7 +27298,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -27345,7 +27348,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27395,7 +27398,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27445,7 +27448,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -27695,7 +27698,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27745,7 +27748,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27795,7 +27798,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27845,7 +27848,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27895,7 +27898,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -28195,7 +28198,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -28245,7 +28248,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -28295,7 +28298,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -28345,7 +28348,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -28395,7 +28398,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28945,7 +28948,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28995,7 +28998,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -29045,7 +29048,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -29095,7 +29098,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -29145,7 +29148,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -29195,7 +29198,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -29245,7 +29248,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -29545,7 +29548,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29595,7 +29598,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29645,7 +29648,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29695,7 +29698,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29745,7 +29748,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29795,7 +29798,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29845,7 +29848,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29895,7 +29898,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29945,7 +29948,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29995,7 +29998,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -30045,7 +30048,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -30095,7 +30098,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -30145,7 +30148,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -30195,7 +30198,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -30245,7 +30248,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -30295,7 +30298,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -30345,7 +30348,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -30645,7 +30648,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30695,7 +30698,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30745,7 +30748,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30795,7 +30798,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30845,7 +30848,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30895,7 +30898,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30945,7 +30948,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30995,7 +30998,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -31045,7 +31048,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -31645,7 +31648,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31695,7 +31698,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31745,7 +31748,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -31795,7 +31798,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -31845,7 +31848,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -31895,7 +31898,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -31945,7 +31948,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31995,7 +31998,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -32045,7 +32048,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -32095,7 +32098,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -32145,7 +32148,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -32195,7 +32198,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -32245,7 +32248,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -32295,7 +32298,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -32345,7 +32348,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -32395,7 +32398,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32445,7 +32448,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32495,7 +32498,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -32545,7 +32548,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32595,7 +32598,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32645,7 +32648,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32695,7 +32698,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32745,7 +32748,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32795,7 +32798,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32845,7 +32848,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32895,7 +32898,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32945,7 +32948,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32995,7 +32998,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -33045,7 +33048,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -33095,7 +33098,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -33145,7 +33148,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -33195,7 +33198,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -33245,7 +33248,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -33295,7 +33298,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -33545,7 +33548,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33595,7 +33598,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -33645,7 +33648,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -33695,7 +33698,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -33745,7 +33748,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33795,7 +33798,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33845,7 +33848,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33895,7 +33898,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33945,7 +33948,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33995,7 +33998,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -34045,7 +34048,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -34095,7 +34098,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -34645,7 +34648,7 @@
         <v>1</v>
       </c>
       <c r="P649" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="650" spans="1:16">
@@ -34695,7 +34698,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -34745,7 +34748,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -34795,7 +34798,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -34845,7 +34848,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -34895,7 +34898,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -34945,7 +34948,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -34995,7 +34998,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -35045,7 +35048,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -35095,7 +35098,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -35145,7 +35148,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -35195,7 +35198,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -35245,7 +35248,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -35295,7 +35298,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -35345,7 +35348,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -35395,7 +35398,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -35445,7 +35448,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -35495,7 +35498,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -35545,7 +35548,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35595,7 +35598,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35645,7 +35648,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -36145,7 +36148,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -36195,7 +36198,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -36245,7 +36248,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -36295,7 +36298,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36345,7 +36348,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36395,7 +36398,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36445,7 +36448,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -36495,7 +36498,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36545,7 +36548,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36595,7 +36598,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36645,7 +36648,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36695,7 +36698,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36745,7 +36748,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36795,7 +36798,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36845,7 +36848,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36895,7 +36898,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36945,7 +36948,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36995,7 +36998,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -37045,7 +37048,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -37095,7 +37098,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -37145,7 +37148,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -37195,7 +37198,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -37245,7 +37248,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -37295,7 +37298,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -37345,7 +37348,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -37395,7 +37398,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -37445,7 +37448,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -37495,7 +37498,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -37545,7 +37548,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -37595,7 +37598,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37645,7 +37648,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37695,7 +37698,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -38145,7 +38148,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -38195,7 +38198,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -38245,7 +38248,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -38295,7 +38298,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -38345,7 +38348,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38395,7 +38398,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38445,7 +38448,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38495,7 +38498,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -39095,7 +39098,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -39145,7 +39148,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -39195,7 +39198,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -39245,7 +39248,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -39295,7 +39298,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -39345,7 +39348,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -39395,7 +39398,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -39445,7 +39448,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -39495,7 +39498,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -39895,7 +39898,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39945,7 +39948,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39995,7 +39998,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -40045,7 +40048,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -40095,7 +40098,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -40145,7 +40148,7 @@
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -40195,7 +40198,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -40245,7 +40248,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -40295,7 +40298,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -40345,7 +40348,7 @@
         <v>1</v>
       </c>
       <c r="P763" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="764" spans="1:16">
@@ -40395,7 +40398,7 @@
         <v>1</v>
       </c>
       <c r="P764" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="765" spans="1:16">
@@ -40445,7 +40448,7 @@
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -40495,7 +40498,7 @@
         <v>1</v>
       </c>
       <c r="P766" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="767" spans="1:16">
@@ -40545,7 +40548,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -40595,7 +40598,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -40645,7 +40648,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -40695,7 +40698,7 @@
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="771" spans="1:16">
@@ -40745,7 +40748,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -40795,7 +40798,7 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -41095,7 +41098,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -41145,7 +41148,7 @@
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -41195,7 +41198,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -41245,7 +41248,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -41295,7 +41298,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -41345,7 +41348,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -41395,7 +41398,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -41445,7 +41448,7 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -41495,7 +41498,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -41545,7 +41548,7 @@
         <v>1</v>
       </c>
       <c r="P787" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="788" spans="1:16">
@@ -41595,7 +41598,7 @@
         <v>1</v>
       </c>
       <c r="P788" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="789" spans="1:16">
@@ -41645,7 +41648,7 @@
         <v>1</v>
       </c>
       <c r="P789" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="790" spans="1:16">
@@ -41995,7 +41998,7 @@
         <v>1</v>
       </c>
       <c r="P796" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="797" spans="1:16">
@@ -42045,7 +42048,7 @@
         <v>1</v>
       </c>
       <c r="P797" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="798" spans="1:16">
@@ -42095,7 +42098,7 @@
         <v>1</v>
       </c>
       <c r="P798" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="799" spans="1:16">
@@ -42145,7 +42148,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -42195,7 +42198,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -42245,7 +42248,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -42295,7 +42298,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -42345,7 +42348,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -42395,7 +42398,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -42445,7 +42448,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -42495,7 +42498,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -42545,7 +42548,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42595,7 +42598,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42645,7 +42648,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42695,7 +42698,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -43445,7 +43448,7 @@
         <v>1</v>
       </c>
       <c r="P825" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="826" spans="1:16">
@@ -43495,7 +43498,7 @@
         <v>1</v>
       </c>
       <c r="P826" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="827" spans="1:16">
@@ -43545,7 +43548,7 @@
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="828" spans="1:16">
@@ -43595,7 +43598,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -43645,7 +43648,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -43695,7 +43698,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -43745,7 +43748,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -43795,7 +43798,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43845,7 +43848,7 @@
         <v>1</v>
       </c>
       <c r="P833" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="834" spans="1:16">
@@ -43895,7 +43898,7 @@
         <v>1</v>
       </c>
       <c r="P834" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="835" spans="1:16">
@@ -43945,7 +43948,7 @@
         <v>1</v>
       </c>
       <c r="P835" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="836" spans="1:16">
@@ -43995,7 +43998,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -44045,7 +44048,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -44095,7 +44098,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -44645,7 +44648,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44695,7 +44698,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44745,7 +44748,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -44795,7 +44798,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -44845,7 +44848,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -44895,7 +44898,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44945,7 +44948,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -44995,7 +44998,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -45045,7 +45048,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -45095,7 +45098,7 @@
         <v>1</v>
       </c>
       <c r="P858" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="859" spans="1:16">
@@ -45145,7 +45148,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -45195,7 +45198,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -45245,7 +45248,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -45295,7 +45298,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -45345,7 +45348,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -45395,7 +45398,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -45445,7 +45448,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45495,7 +45498,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45545,7 +45548,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45595,7 +45598,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45645,7 +45648,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45695,7 +45698,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45745,7 +45748,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45795,7 +45798,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45845,7 +45848,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -45895,7 +45898,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45945,7 +45948,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45995,7 +45998,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -46045,7 +46048,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -46095,7 +46098,7 @@
         <v>1</v>
       </c>
       <c r="P878" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="879" spans="1:16">
@@ -46145,7 +46148,7 @@
         <v>1</v>
       </c>
       <c r="P879" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="880" spans="1:16">
@@ -46195,7 +46198,7 @@
         <v>1</v>
       </c>
       <c r="P880" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="881" spans="1:16">
@@ -46245,7 +46248,7 @@
         <v>1</v>
       </c>
       <c r="P881" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="882" spans="1:16">
@@ -46295,7 +46298,7 @@
         <v>1</v>
       </c>
       <c r="P882" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -46345,7 +46348,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46395,7 +46398,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46445,7 +46448,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46495,7 +46498,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46545,7 +46548,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46595,7 +46598,7 @@
         <v>1</v>
       </c>
       <c r="P888" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="889" spans="1:16">
@@ -46645,7 +46648,7 @@
         <v>1</v>
       </c>
       <c r="P889" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="890" spans="1:16">
@@ -46695,7 +46698,7 @@
         <v>1</v>
       </c>
       <c r="P890" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="891" spans="1:16">
@@ -46745,7 +46748,7 @@
         <v>1</v>
       </c>
       <c r="P891" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="892" spans="1:16">
@@ -46795,7 +46798,7 @@
         <v>1</v>
       </c>
       <c r="P892" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="893" spans="1:16">
@@ -46845,7 +46848,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46895,7 +46898,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46945,7 +46948,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -46995,7 +46998,7 @@
         <v>1</v>
       </c>
       <c r="P896" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="897" spans="1:16">
@@ -47045,7 +47048,7 @@
         <v>1</v>
       </c>
       <c r="P897" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="898" spans="1:16">
@@ -47095,7 +47098,7 @@
         <v>1</v>
       </c>
       <c r="P898" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="899" spans="1:16">
@@ -47145,7 +47148,7 @@
         <v>1</v>
       </c>
       <c r="P899" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="900" spans="1:16">
@@ -47195,7 +47198,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -47245,7 +47248,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -47295,7 +47298,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -47345,7 +47348,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -47395,7 +47398,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -47445,7 +47448,7 @@
         <v>1</v>
       </c>
       <c r="P905" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="906" spans="1:16">
@@ -47495,7 +47498,7 @@
         <v>1</v>
       </c>
       <c r="P906" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="907" spans="1:16">
@@ -47545,7 +47548,7 @@
         <v>1</v>
       </c>
       <c r="P907" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="908" spans="1:16">
@@ -47595,7 +47598,7 @@
         <v>1</v>
       </c>
       <c r="P908" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="909" spans="1:16">
@@ -47645,7 +47648,7 @@
         <v>1</v>
       </c>
       <c r="P909" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="910" spans="1:16">
@@ -47695,7 +47698,7 @@
         <v>1</v>
       </c>
       <c r="P910" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="911" spans="1:16">
@@ -47745,7 +47748,7 @@
         <v>1</v>
       </c>
       <c r="P911" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="912" spans="1:16">
@@ -47795,7 +47798,7 @@
         <v>1</v>
       </c>
       <c r="P912" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="913" spans="1:16">
@@ -47845,7 +47848,7 @@
         <v>1</v>
       </c>
       <c r="P913" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="914" spans="1:16">
@@ -47895,7 +47898,7 @@
         <v>1</v>
       </c>
       <c r="P914" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="915" spans="1:16">
@@ -47945,7 +47948,7 @@
         <v>1</v>
       </c>
       <c r="P915" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="916" spans="1:16">
@@ -47995,7 +47998,7 @@
         <v>1</v>
       </c>
       <c r="P916" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="917" spans="1:16">
@@ -48045,7 +48048,7 @@
         <v>1</v>
       </c>
       <c r="P917" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="918" spans="1:16">
@@ -48095,7 +48098,7 @@
         <v>1</v>
       </c>
       <c r="P918" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="919" spans="1:16">
@@ -48145,7 +48148,7 @@
         <v>1</v>
       </c>
       <c r="P919" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="920" spans="1:16">
@@ -48195,7 +48198,7 @@
         <v>1</v>
       </c>
       <c r="P920" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="921" spans="1:16">
@@ -48245,7 +48248,7 @@
         <v>1</v>
       </c>
       <c r="P921" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="922" spans="1:16">
@@ -48295,7 +48298,7 @@
         <v>1</v>
       </c>
       <c r="P922" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="923" spans="1:16">
@@ -48345,7 +48348,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -48395,7 +48398,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -48445,7 +48448,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48495,7 +48498,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48545,7 +48548,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -48595,7 +48598,7 @@
         <v>1</v>
       </c>
       <c r="P928" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="929" spans="1:16">
@@ -48645,7 +48648,7 @@
         <v>1</v>
       </c>
       <c r="P929" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="930" spans="1:16">
@@ -48695,7 +48698,7 @@
         <v>1</v>
       </c>
       <c r="P930" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="931" spans="1:16">
@@ -48745,7 +48748,7 @@
         <v>1</v>
       </c>
       <c r="P931" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="932" spans="1:16">
@@ -48795,7 +48798,7 @@
         <v>1</v>
       </c>
       <c r="P932" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="933" spans="1:16">
@@ -48845,7 +48848,7 @@
         <v>1</v>
       </c>
       <c r="P933" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="934" spans="1:16">
@@ -48895,7 +48898,7 @@
         <v>1</v>
       </c>
       <c r="P934" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="935" spans="1:16">
@@ -48945,7 +48948,7 @@
         <v>1</v>
       </c>
       <c r="P935" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="936" spans="1:16">
@@ -48995,7 +48998,7 @@
         <v>1</v>
       </c>
       <c r="P936" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="937" spans="1:16">
@@ -49045,7 +49048,7 @@
         <v>1</v>
       </c>
       <c r="P937" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="938" spans="1:16">
@@ -49095,7 +49098,7 @@
         <v>1</v>
       </c>
       <c r="P938" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="939" spans="1:16">
@@ -49145,7 +49148,7 @@
         <v>1</v>
       </c>
       <c r="P939" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="940" spans="1:16">
@@ -49195,7 +49198,7 @@
         <v>1</v>
       </c>
       <c r="P940" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="941" spans="1:16">
@@ -49245,7 +49248,7 @@
         <v>1</v>
       </c>
       <c r="P941" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="942" spans="1:16">
@@ -49295,7 +49298,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -49345,7 +49348,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49395,7 +49398,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49445,7 +49448,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -49495,7 +49498,7 @@
         <v>1</v>
       </c>
       <c r="P946" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="947" spans="1:16">
@@ -49545,7 +49548,7 @@
         <v>1</v>
       </c>
       <c r="P947" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="948" spans="1:16">
@@ -49595,7 +49598,7 @@
         <v>1</v>
       </c>
       <c r="P948" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="949" spans="1:16">
@@ -49645,7 +49648,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -49695,7 +49698,7 @@
         <v>1</v>
       </c>
       <c r="P950" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="951" spans="1:16">
@@ -49745,7 +49748,7 @@
         <v>1</v>
       </c>
       <c r="P951" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="952" spans="1:16">
@@ -49795,7 +49798,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -49845,7 +49848,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -49895,7 +49898,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -49945,7 +49948,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -49995,7 +49998,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -50045,7 +50048,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -50095,7 +50098,7 @@
         <v>1</v>
       </c>
       <c r="P958" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="959" spans="1:16">
@@ -50145,7 +50148,7 @@
         <v>1</v>
       </c>
       <c r="P959" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="960" spans="1:16">
@@ -50195,7 +50198,7 @@
         <v>1</v>
       </c>
       <c r="P960" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="961" spans="1:16">
@@ -50245,7 +50248,7 @@
         <v>1</v>
       </c>
       <c r="P961" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="962" spans="1:16">
@@ -50295,7 +50298,7 @@
         <v>1</v>
       </c>
       <c r="P962" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="963" spans="1:16">
@@ -50345,7 +50348,7 @@
         <v>1</v>
       </c>
       <c r="P963" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="964" spans="1:16">
@@ -50395,7 +50398,7 @@
         <v>1</v>
       </c>
       <c r="P964" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="965" spans="1:16">
@@ -50445,7 +50448,7 @@
         <v>1</v>
       </c>
       <c r="P965" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="966" spans="1:16">
@@ -50495,7 +50498,7 @@
         <v>1</v>
       </c>
       <c r="P966" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="967" spans="1:16">
@@ -50545,7 +50548,7 @@
         <v>1</v>
       </c>
       <c r="P967" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="968" spans="1:16">
@@ -50595,7 +50598,7 @@
         <v>1</v>
       </c>
       <c r="P968" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="969" spans="1:16">
@@ -51795,7 +51798,7 @@
         <v>1</v>
       </c>
       <c r="P992" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="993" spans="1:16">
@@ -51845,7 +51848,7 @@
         <v>1</v>
       </c>
       <c r="P993" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="994" spans="1:16">
@@ -51895,7 +51898,7 @@
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="995" spans="1:16">
@@ -51945,7 +51948,7 @@
         <v>1</v>
       </c>
       <c r="P995" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="996" spans="1:16">
@@ -52645,7 +52648,7 @@
         <v>1</v>
       </c>
       <c r="P1009" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1010" spans="1:16">
@@ -52695,7 +52698,7 @@
         <v>1</v>
       </c>
       <c r="P1010" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1011" spans="1:16">
@@ -52745,7 +52748,7 @@
         <v>1</v>
       </c>
       <c r="P1011" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1012" spans="1:16">
@@ -52795,7 +52798,7 @@
         <v>1</v>
       </c>
       <c r="P1012" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1013" spans="1:16">
@@ -52845,7 +52848,7 @@
         <v>1</v>
       </c>
       <c r="P1013" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1014" spans="1:16">
@@ -52895,7 +52898,7 @@
         <v>1</v>
       </c>
       <c r="P1014" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1015" spans="1:16">
@@ -52945,7 +52948,7 @@
         <v>1</v>
       </c>
       <c r="P1015" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1016" spans="1:16">
@@ -52995,7 +52998,7 @@
         <v>1</v>
       </c>
       <c r="P1016" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1017" spans="1:16">
@@ -53045,7 +53048,7 @@
         <v>1</v>
       </c>
       <c r="P1017" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1018" spans="1:16">
@@ -53495,7 +53498,7 @@
         <v>1</v>
       </c>
       <c r="P1026" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="1027" spans="1:16">
@@ -53545,7 +53548,7 @@
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
@@ -53595,7 +53598,7 @@
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
@@ -53645,7 +53648,7 @@
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
@@ -53695,7 +53698,7 @@
         <v>1</v>
       </c>
       <c r="P1030" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="1031" spans="1:16">
@@ -53745,7 +53748,7 @@
         <v>1</v>
       </c>
       <c r="P1031" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="1032" spans="1:16">
@@ -53795,7 +53798,7 @@
         <v>1</v>
       </c>
       <c r="P1032" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="1033" spans="1:16">
@@ -53845,7 +53848,7 @@
         <v>1</v>
       </c>
       <c r="P1033" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="1034" spans="1:16">
@@ -53895,7 +53898,7 @@
         <v>1</v>
       </c>
       <c r="P1034" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="1035" spans="1:16">
@@ -53945,7 +53948,7 @@
         <v>1</v>
       </c>
       <c r="P1035" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="1036" spans="1:16">
@@ -54795,7 +54798,7 @@
         <v>1</v>
       </c>
       <c r="P1052" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="1053" spans="1:16">
@@ -54845,7 +54848,7 @@
         <v>1</v>
       </c>
       <c r="P1053" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="1054" spans="1:16">
@@ -54895,7 +54898,7 @@
         <v>1</v>
       </c>
       <c r="P1054" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="1055" spans="1:16">
@@ -54945,7 +54948,7 @@
         <v>1</v>
       </c>
       <c r="P1055" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="1056" spans="1:16">
@@ -54995,7 +54998,7 @@
         <v>1</v>
       </c>
       <c r="P1056" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1057" spans="1:16">
@@ -55045,7 +55048,7 @@
         <v>1</v>
       </c>
       <c r="P1057" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1058" spans="1:16">
@@ -55095,7 +55098,7 @@
         <v>1</v>
       </c>
       <c r="P1058" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1059" spans="1:16">
@@ -55145,7 +55148,7 @@
         <v>1</v>
       </c>
       <c r="P1059" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1060" spans="1:16">
@@ -55195,7 +55198,7 @@
         <v>1</v>
       </c>
       <c r="P1060" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1061" spans="1:16">
@@ -55245,7 +55248,7 @@
         <v>1</v>
       </c>
       <c r="P1061" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1062" spans="1:16">
@@ -55295,7 +55298,7 @@
         <v>1</v>
       </c>
       <c r="P1062" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1063" spans="1:16">
@@ -55345,7 +55348,7 @@
         <v>1</v>
       </c>
       <c r="P1063" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1064" spans="1:16">
@@ -55395,7 +55398,7 @@
         <v>1</v>
       </c>
       <c r="P1064" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="1065" spans="1:16">
@@ -55445,7 +55448,7 @@
         <v>1</v>
       </c>
       <c r="P1065" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="1066" spans="1:16">
@@ -55495,7 +55498,7 @@
         <v>1</v>
       </c>
       <c r="P1066" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="1067" spans="1:16">
@@ -55545,7 +55548,7 @@
         <v>1</v>
       </c>
       <c r="P1067" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="1068" spans="1:16">
@@ -55595,7 +55598,7 @@
         <v>1</v>
       </c>
       <c r="P1068" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="1069" spans="1:16">
@@ -55645,7 +55648,7 @@
         <v>1</v>
       </c>
       <c r="P1069" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="1070" spans="1:16">
@@ -55695,7 +55698,7 @@
         <v>1</v>
       </c>
       <c r="P1070" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="1071" spans="1:16">
@@ -55745,7 +55748,7 @@
         <v>1</v>
       </c>
       <c r="P1071" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="1072" spans="1:16">
@@ -55795,7 +55798,7 @@
         <v>1</v>
       </c>
       <c r="P1072" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1073" spans="1:16">
@@ -55845,7 +55848,7 @@
         <v>1</v>
       </c>
       <c r="P1073" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="1074" spans="1:16">
@@ -55945,7 +55948,7 @@
         <v>1</v>
       </c>
       <c r="P1075" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="1076" spans="1:16">
@@ -55995,7 +55998,7 @@
         <v>1</v>
       </c>
       <c r="P1076" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="1077" spans="1:16">
@@ -56095,7 +56098,7 @@
         <v>1</v>
       </c>
       <c r="P1078" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="1079" spans="1:16">
@@ -56195,7 +56198,7 @@
         <v>1</v>
       </c>
       <c r="P1080" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="1081" spans="1:16">
@@ -56253,81 +56256,81 @@
         <v>0</v>
       </c>
       <c r="B1082" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C1082">
-        <v>4.675422281711732</v>
+        <v>5.044404491169697</v>
       </c>
       <c r="D1082" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E1082">
-        <v>4.353204116905556</v>
+        <v>5.287786513495593</v>
       </c>
       <c r="F1082">
         <v>-1</v>
       </c>
       <c r="G1082">
-        <v>0.01056457771828827</v>
+        <v>0.0114955955088303</v>
       </c>
       <c r="H1082">
-        <v>0.01026679588309444</v>
+        <v>0.01203221348650441</v>
       </c>
       <c r="I1082">
-        <v>0.3222181648061762</v>
+        <v>-0.2433820223258962</v>
       </c>
       <c r="J1082">
         <v>0.6109082403087693</v>
       </c>
       <c r="K1082">
-        <v>4.82</v>
+        <v>5.28</v>
       </c>
       <c r="L1082">
-        <v>7.62</v>
+        <v>8.27</v>
       </c>
       <c r="M1082">
-        <v>4.84</v>
+        <v>5.52</v>
       </c>
       <c r="N1082">
-        <v>7.31</v>
+        <v>8.66</v>
       </c>
       <c r="O1082">
         <v>1</v>
       </c>
       <c r="P1082" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="1083" spans="1:16">
       <c r="A1083" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1083" t="s">
         <v>297</v>
       </c>
       <c r="C1083">
-        <v>5.044404491169697</v>
+        <v>5.443358172213278</v>
       </c>
       <c r="D1083" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E1083">
-        <v>5.287786513495593</v>
+        <v>5.72891631515216</v>
       </c>
       <c r="F1083">
         <v>-1</v>
       </c>
       <c r="G1083">
-        <v>0.0114955955088303</v>
+        <v>0.01109664182778672</v>
       </c>
       <c r="H1083">
-        <v>0.01203221348650441</v>
+        <v>0.01197108368484784</v>
       </c>
       <c r="I1083">
-        <v>-0.2433820223258962</v>
+        <v>-0.285558142938882</v>
       </c>
       <c r="J1083">
-        <v>0.6109082403087693</v>
+        <v>0.5353488310202125</v>
       </c>
       <c r="K1083">
         <v>5.28</v>
@@ -56336,16 +56339,16 @@
         <v>8.27</v>
       </c>
       <c r="M1083">
-        <v>5.52</v>
+        <v>5.83</v>
       </c>
       <c r="N1083">
-        <v>8.66</v>
+        <v>8.85</v>
       </c>
       <c r="O1083">
         <v>1</v>
       </c>
       <c r="P1083" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="1084" spans="1:16">
@@ -56356,28 +56359,28 @@
         <v>297</v>
       </c>
       <c r="C1084">
-        <v>5.443358172213278</v>
+        <v>5.71703296703297</v>
       </c>
       <c r="D1084" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E1084">
-        <v>5.704874452768427</v>
+        <v>6.031098901098904</v>
       </c>
       <c r="F1084">
         <v>-1</v>
       </c>
       <c r="G1084">
-        <v>0.01109664182778672</v>
+        <v>0.01082296703296703</v>
       </c>
       <c r="H1084">
-        <v>0.01161512554723157</v>
+        <v>0.0116689010989011</v>
       </c>
       <c r="I1084">
-        <v>-0.2615162805551492</v>
+        <v>-0.3140659340659342</v>
       </c>
       <c r="J1084">
-        <v>0.5353488310202125</v>
+        <v>0.4835164835164829</v>
       </c>
       <c r="K1084">
         <v>5.28</v>
@@ -56386,16 +56389,16 @@
         <v>8.27</v>
       </c>
       <c r="M1084">
-        <v>5.52</v>
+        <v>5.83</v>
       </c>
       <c r="N1084">
-        <v>8.66</v>
+        <v>8.85</v>
       </c>
       <c r="O1084">
         <v>1</v>
       </c>
       <c r="P1084" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="1085" spans="1:16">
@@ -56406,28 +56409,28 @@
         <v>297</v>
       </c>
       <c r="C1085">
-        <v>5.71703296703297</v>
+        <v>5.853864517773994</v>
       </c>
       <c r="D1085" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E1085">
-        <v>5.990989010989015</v>
+        <v>6.182183738375452</v>
       </c>
       <c r="F1085">
         <v>-1</v>
       </c>
       <c r="G1085">
-        <v>0.01082296703296703</v>
+        <v>0.01068613548222601</v>
       </c>
       <c r="H1085">
-        <v>0.01132901098901099</v>
+        <v>0.01151781626162455</v>
       </c>
       <c r="I1085">
-        <v>-0.2739560439560451</v>
+        <v>-0.3283192206014576</v>
       </c>
       <c r="J1085">
-        <v>0.4835164835164829</v>
+        <v>0.4576014170882586</v>
       </c>
       <c r="K1085">
         <v>5.28</v>
@@ -56436,16 +56439,16 @@
         <v>8.27</v>
       </c>
       <c r="M1085">
-        <v>5.52</v>
+        <v>5.83</v>
       </c>
       <c r="N1085">
-        <v>8.66</v>
+        <v>8.85</v>
       </c>
       <c r="O1085">
         <v>1</v>
       </c>
       <c r="P1085" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="1086" spans="1:16">
@@ -56456,28 +56459,28 @@
         <v>297</v>
       </c>
       <c r="C1086">
-        <v>5.853864517773994</v>
+        <v>5.996957847030043</v>
       </c>
       <c r="D1086" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E1086">
-        <v>6.134040177672812</v>
+        <v>6.34018262276234</v>
       </c>
       <c r="F1086">
         <v>-1</v>
       </c>
       <c r="G1086">
-        <v>0.01068613548222601</v>
+        <v>0.01054304215296996</v>
       </c>
       <c r="H1086">
-        <v>0.01118595982232719</v>
+        <v>0.01135981737723766</v>
       </c>
       <c r="I1086">
-        <v>-0.2801756598988181</v>
+        <v>-0.3432247757322973</v>
       </c>
       <c r="J1086">
-        <v>0.4576014170882586</v>
+        <v>0.4305004077594615</v>
       </c>
       <c r="K1086">
         <v>5.28</v>
@@ -56486,16 +56489,16 @@
         <v>8.27</v>
       </c>
       <c r="M1086">
-        <v>5.52</v>
+        <v>5.83</v>
       </c>
       <c r="N1086">
-        <v>8.66</v>
+        <v>8.85</v>
       </c>
       <c r="O1086">
         <v>1</v>
       </c>
       <c r="P1086" t="s">
-        <v>604</v>
+        <v>290</v>
       </c>
     </row>
     <row r="1087" spans="1:16">
@@ -56506,28 +56509,28 @@
         <v>297</v>
       </c>
       <c r="C1087">
-        <v>5.996957847030043</v>
+        <v>6.332482120319733</v>
       </c>
       <c r="D1087" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E1087">
-        <v>6.283637749167773</v>
+        <v>6.710657341186373</v>
       </c>
       <c r="F1087">
         <v>-1</v>
       </c>
       <c r="G1087">
-        <v>0.01054304215296996</v>
+        <v>0.01020751787968027</v>
       </c>
       <c r="H1087">
-        <v>0.01103636225083223</v>
+        <v>0.01098934265881363</v>
       </c>
       <c r="I1087">
-        <v>-0.2866799021377302</v>
+        <v>-0.3781752208666393</v>
       </c>
       <c r="J1087">
-        <v>0.4305004077594615</v>
+        <v>0.3669541438788382</v>
       </c>
       <c r="K1087">
         <v>5.28</v>
@@ -56536,16 +56539,16 @@
         <v>8.27</v>
       </c>
       <c r="M1087">
-        <v>5.52</v>
+        <v>5.83</v>
       </c>
       <c r="N1087">
-        <v>8.66</v>
+        <v>8.85</v>
       </c>
       <c r="O1087">
         <v>1</v>
       </c>
       <c r="P1087" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="1088" spans="1:16">
@@ -56556,28 +56559,28 @@
         <v>297</v>
       </c>
       <c r="C1088">
-        <v>6.332482120319733</v>
+        <v>6.538088893528732</v>
       </c>
       <c r="D1088" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E1088">
-        <v>6.634413125788813</v>
+        <v>6.937681486604642</v>
       </c>
       <c r="F1088">
         <v>-1</v>
       </c>
       <c r="G1088">
-        <v>0.01020751787968027</v>
+        <v>0.01000191110647127</v>
       </c>
       <c r="H1088">
-        <v>0.01068558687421119</v>
+        <v>0.01076231851339536</v>
       </c>
       <c r="I1088">
-        <v>-0.30193100546908</v>
+        <v>-0.3995925930759103</v>
       </c>
       <c r="J1088">
-        <v>0.3669541438788382</v>
+        <v>0.3280134671347097</v>
       </c>
       <c r="K1088">
         <v>5.28</v>
@@ -56586,16 +56589,16 @@
         <v>8.27</v>
       </c>
       <c r="M1088">
-        <v>5.52</v>
+        <v>5.83</v>
       </c>
       <c r="N1088">
-        <v>8.66</v>
+        <v>8.85</v>
       </c>
       <c r="O1088">
         <v>1</v>
       </c>
       <c r="P1088" t="s">
-        <v>289</v>
+        <v>606</v>
       </c>
     </row>
     <row r="1089" spans="1:16">
@@ -56606,28 +56609,28 @@
         <v>297</v>
       </c>
       <c r="C1089">
-        <v>6.538088893528732</v>
+        <v>6.439291964996025</v>
       </c>
       <c r="D1089" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E1089">
-        <v>6.849365661416402</v>
+        <v>6.870200212145323</v>
       </c>
       <c r="F1089">
         <v>-1</v>
       </c>
       <c r="G1089">
-        <v>0.01000191110647127</v>
+        <v>0.01010070803500397</v>
       </c>
       <c r="H1089">
-        <v>0.0104706343385836</v>
+        <v>0.01082979978785467</v>
       </c>
       <c r="I1089">
-        <v>-0.3112767678876702</v>
+        <v>-0.430908247149298</v>
       </c>
       <c r="J1089">
-        <v>0.3280134671347097</v>
+        <v>0.3467250066295405</v>
       </c>
       <c r="K1089">
         <v>5.28</v>
@@ -56636,16 +56639,16 @@
         <v>8.27</v>
       </c>
       <c r="M1089">
-        <v>5.52</v>
+        <v>5.71</v>
       </c>
       <c r="N1089">
-        <v>8.66</v>
+        <v>8.85</v>
       </c>
       <c r="O1089">
         <v>1</v>
       </c>
       <c r="P1089" t="s">
-        <v>605</v>
+        <v>295</v>
       </c>
     </row>
     <row r="1090" spans="1:16">
@@ -56656,28 +56659,28 @@
         <v>297</v>
       </c>
       <c r="C1090">
-        <v>6.439291964996025</v>
+        <v>6.095915492957749</v>
       </c>
       <c r="D1090" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E1090">
-        <v>6.746077963404937</v>
+        <v>6.498859368331202</v>
       </c>
       <c r="F1090">
         <v>-1</v>
       </c>
       <c r="G1090">
-        <v>0.01010070803500397</v>
+        <v>0.01044408450704225</v>
       </c>
       <c r="H1090">
-        <v>0.01057392203659507</v>
+        <v>0.0112011406316688</v>
       </c>
       <c r="I1090">
-        <v>-0.3067859984089116</v>
+        <v>-0.4029438753734533</v>
       </c>
       <c r="J1090">
-        <v>0.3467250066295405</v>
+        <v>0.4117584293640626</v>
       </c>
       <c r="K1090">
         <v>5.28</v>
@@ -56686,16 +56689,16 @@
         <v>8.27</v>
       </c>
       <c r="M1090">
-        <v>5.52</v>
+        <v>5.71</v>
       </c>
       <c r="N1090">
-        <v>8.66</v>
+        <v>8.85</v>
       </c>
       <c r="O1090">
         <v>1</v>
       </c>
       <c r="P1090" t="s">
-        <v>295</v>
+        <v>607</v>
       </c>
     </row>
     <row r="1091" spans="1:16">
@@ -56706,28 +56709,28 @@
         <v>297</v>
       </c>
       <c r="C1091">
-        <v>6.095915492957749</v>
+        <v>5.888028169014084</v>
       </c>
       <c r="D1091" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E1091">
-        <v>6.387093469910375</v>
+        <v>6.274041826717882</v>
       </c>
       <c r="F1091">
         <v>-1</v>
       </c>
       <c r="G1091">
-        <v>0.01044408450704225</v>
+        <v>0.01065197183098592</v>
       </c>
       <c r="H1091">
-        <v>0.01093290653008962</v>
+        <v>0.01142595817328212</v>
       </c>
       <c r="I1091">
-        <v>-0.2911779769526257</v>
+        <v>-0.3860136577037983</v>
       </c>
       <c r="J1091">
-        <v>0.4117584293640626</v>
+        <v>0.4511310285958173</v>
       </c>
       <c r="K1091">
         <v>5.28</v>
@@ -56736,16 +56739,16 @@
         <v>8.27</v>
       </c>
       <c r="M1091">
-        <v>5.52</v>
+        <v>5.71</v>
       </c>
       <c r="N1091">
-        <v>8.66</v>
+        <v>8.85</v>
       </c>
       <c r="O1091">
         <v>1</v>
       </c>
       <c r="P1091" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="1092" spans="1:16">
@@ -56756,28 +56759,28 @@
         <v>297</v>
       </c>
       <c r="C1092">
-        <v>5.888028169014084</v>
+        <v>6.529026547184721</v>
       </c>
       <c r="D1092" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E1092">
-        <v>6.169756722151089</v>
+        <v>6.967242724322871</v>
       </c>
       <c r="F1092">
         <v>-1</v>
       </c>
       <c r="G1092">
-        <v>0.01065197183098592</v>
+        <v>0.01001097345281528</v>
       </c>
       <c r="H1092">
-        <v>0.01115024327784891</v>
+        <v>0.01073275727567713</v>
       </c>
       <c r="I1092">
-        <v>-0.2817285531370048</v>
+        <v>-0.4382161771381501</v>
       </c>
       <c r="J1092">
-        <v>0.4511310285958173</v>
+        <v>0.3297298206089543</v>
       </c>
       <c r="K1092">
         <v>5.28</v>
@@ -56786,66 +56789,16 @@
         <v>8.27</v>
       </c>
       <c r="M1092">
-        <v>5.52</v>
+        <v>5.71</v>
       </c>
       <c r="N1092">
-        <v>8.66</v>
+        <v>8.85</v>
       </c>
       <c r="O1092">
         <v>1</v>
       </c>
       <c r="P1092" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="1093" spans="1:16">
-      <c r="A1093" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1093" t="s">
-        <v>297</v>
-      </c>
-      <c r="C1093">
-        <v>6.529026547184721</v>
-      </c>
-      <c r="D1093" t="s">
-        <v>470</v>
-      </c>
-      <c r="E1093">
-        <v>6.927675145849796</v>
-      </c>
-      <c r="F1093">
-        <v>-1</v>
-      </c>
-      <c r="G1093">
-        <v>0.01001097345281528</v>
-      </c>
-      <c r="H1093">
-        <v>0.01077232485415021</v>
-      </c>
-      <c r="I1093">
-        <v>-0.3986485986650754</v>
-      </c>
-      <c r="J1093">
-        <v>0.3297298206089543</v>
-      </c>
-      <c r="K1093">
-        <v>5.28</v>
-      </c>
-      <c r="L1093">
-        <v>8.27</v>
-      </c>
-      <c r="M1093">
-        <v>5.83</v>
-      </c>
-      <c r="N1093">
-        <v>8.85</v>
-      </c>
-      <c r="O1093">
-        <v>1</v>
-      </c>
-      <c r="P1093" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -1423,13 +1423,13 @@
     <t>2021-06-09</t>
   </si>
   <si>
-    <t>2021-09-02</t>
-  </si>
-  <si>
     <t>2021-09-07</t>
   </si>
   <si>
     <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>2021-09-09</t>
   </si>
   <si>
     <t>2016-01-29</t>
@@ -55715,7 +55715,7 @@
         <v>469</v>
       </c>
       <c r="E1071">
-        <v>8.188274920345918</v>
+        <v>8.35178311333636</v>
       </c>
       <c r="F1071">
         <v>-1</v>
@@ -55724,10 +55724,10 @@
         <v>0.008721215293582165</v>
       </c>
       <c r="H1071">
-        <v>0.009131725079654082</v>
+        <v>0.00934821688666364</v>
       </c>
       <c r="I1071">
-        <v>-0.3694902139280831</v>
+        <v>-0.5329984069185247</v>
       </c>
       <c r="J1071">
         <v>0.08545744196631905</v>
@@ -55739,10 +55739,10 @@
         <v>8.27</v>
       </c>
       <c r="M1071">
-        <v>5.52</v>
+        <v>5.83</v>
       </c>
       <c r="N1071">
-        <v>8.66</v>
+        <v>8.85</v>
       </c>
       <c r="O1071">
         <v>1</v>
@@ -55765,7 +55765,7 @@
         <v>469</v>
       </c>
       <c r="E1072">
-        <v>8.101919546373537</v>
+        <v>8.260578071622774</v>
       </c>
       <c r="F1072">
         <v>-1</v>
@@ -55774,10 +55774,10 @@
         <v>0.008803816086077486</v>
       </c>
       <c r="H1072">
-        <v>0.009218080453626463</v>
+        <v>0.009439421928377226</v>
       </c>
       <c r="I1072">
-        <v>-0.3657356324510239</v>
+        <v>-0.5243941577002609</v>
       </c>
       <c r="J1072">
         <v>0.1011015314540694</v>
@@ -55789,10 +55789,10 @@
         <v>8.27</v>
       </c>
       <c r="M1072">
-        <v>5.52</v>
+        <v>5.83</v>
       </c>
       <c r="N1072">
-        <v>8.66</v>
+        <v>8.85</v>
       </c>
       <c r="O1072">
         <v>1</v>
@@ -55815,7 +55815,7 @@
         <v>469</v>
       </c>
       <c r="E1073">
-        <v>8.042816024536171</v>
+        <v>8.198155330261933</v>
       </c>
       <c r="F1073">
         <v>-1</v>
@@ -55824,10 +55824,10 @@
         <v>0.008860349889574097</v>
       </c>
       <c r="H1073">
-        <v>0.009277183975463829</v>
+        <v>0.009501844669738066</v>
       </c>
       <c r="I1073">
-        <v>-0.3631659141102688</v>
+        <v>-0.5185052198360314</v>
       </c>
       <c r="J1073">
         <v>0.1118086912072155</v>
@@ -55839,10 +55839,10 @@
         <v>8.27</v>
       </c>
       <c r="M1073">
-        <v>5.52</v>
+        <v>5.83</v>
       </c>
       <c r="N1073">
-        <v>8.66</v>
+        <v>8.85</v>
       </c>
       <c r="O1073">
         <v>1</v>
@@ -55865,7 +55865,7 @@
         <v>469</v>
       </c>
       <c r="E1074">
-        <v>8.072623729245663</v>
+        <v>8.229637018388082</v>
       </c>
       <c r="F1074">
         <v>-1</v>
@@ -55874,10 +55874,10 @@
         <v>0.008831838172025886</v>
       </c>
       <c r="H1074">
-        <v>0.009247376270754337</v>
+        <v>0.009470362981611916</v>
       </c>
       <c r="I1074">
-        <v>-0.3644619012715511</v>
+        <v>-0.5214751904139705</v>
       </c>
       <c r="J1074">
         <v>0.1064087447018726</v>
@@ -55889,10 +55889,10 @@
         <v>8.27</v>
       </c>
       <c r="M1074">
-        <v>5.52</v>
+        <v>5.83</v>
       </c>
       <c r="N1074">
-        <v>8.66</v>
+        <v>8.85</v>
       </c>
       <c r="O1074">
         <v>1</v>
@@ -55915,7 +55915,7 @@
         <v>469</v>
       </c>
       <c r="E1075">
-        <v>8.126060466614499</v>
+        <v>8.286074731949732</v>
       </c>
       <c r="F1075">
         <v>-1</v>
@@ -55924,10 +55924,10 @@
         <v>0.008780724771064393</v>
       </c>
       <c r="H1075">
-        <v>0.009193939533385502</v>
+        <v>0.009413925268050268</v>
       </c>
       <c r="I1075">
-        <v>-0.3667852376788918</v>
+        <v>-0.526799503014125</v>
       </c>
       <c r="J1075">
         <v>0.09672817633795312</v>
@@ -55939,10 +55939,10 @@
         <v>8.27</v>
       </c>
       <c r="M1075">
-        <v>5.52</v>
+        <v>5.83</v>
       </c>
       <c r="N1075">
-        <v>8.66</v>
+        <v>8.85</v>
       </c>
       <c r="O1075">
         <v>1</v>
@@ -55965,7 +55965,7 @@
         <v>469</v>
       </c>
       <c r="E1076">
-        <v>7.05351458622741</v>
+        <v>7.153295296685831</v>
       </c>
       <c r="F1076">
         <v>-1</v>
@@ -55974,10 +55974,10 @@
         <v>0.009806638221869434</v>
       </c>
       <c r="H1076">
-        <v>0.01026648541377259</v>
+        <v>0.01054670470331417</v>
       </c>
       <c r="I1076">
-        <v>-0.3201528080968448</v>
+        <v>-0.4199335185552666</v>
       </c>
       <c r="J1076">
         <v>0.2910299662631506</v>
@@ -55989,10 +55989,10 @@
         <v>8.27</v>
       </c>
       <c r="M1076">
-        <v>5.52</v>
+        <v>5.83</v>
       </c>
       <c r="N1076">
-        <v>8.66</v>
+        <v>8.85</v>
       </c>
       <c r="O1076">
         <v>1</v>
@@ -56012,10 +56012,10 @@
         <v>6.759036860879887</v>
       </c>
       <c r="D1077" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E1077">
-        <v>7.080356718192609</v>
+        <v>7.21598493856518</v>
       </c>
       <c r="F1077">
         <v>-1</v>
@@ -56024,10 +56024,10 @@
         <v>0.009780963139120113</v>
       </c>
       <c r="H1077">
-        <v>0.01023964328180739</v>
+        <v>0.01048401506143482</v>
       </c>
       <c r="I1077">
-        <v>-0.3213198573127229</v>
+        <v>-0.4569480776852934</v>
       </c>
       <c r="J1077">
         <v>0.2861672611969911</v>
@@ -56039,10 +56039,10 @@
         <v>8.27</v>
       </c>
       <c r="M1077">
-        <v>5.52</v>
+        <v>5.71</v>
       </c>
       <c r="N1077">
-        <v>8.66</v>
+        <v>8.85</v>
       </c>
       <c r="O1077">
         <v>1</v>
@@ -56062,10 +56062,10 @@
         <v>6.737244367417659</v>
       </c>
       <c r="D1078" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E1078">
-        <v>7.057573656845735</v>
+        <v>7.19241767764296</v>
       </c>
       <c r="F1078">
         <v>-1</v>
@@ -56074,10 +56074,10 @@
         <v>0.00980275563258234</v>
       </c>
       <c r="H1078">
-        <v>0.01026242634315427</v>
+        <v>0.01050758232235704</v>
       </c>
       <c r="I1078">
-        <v>-0.3203292894280763</v>
+        <v>-0.4551733102253017</v>
       </c>
       <c r="J1078">
         <v>0.2902946273830191</v>
@@ -56089,10 +56089,10 @@
         <v>8.27</v>
       </c>
       <c r="M1078">
-        <v>5.52</v>
+        <v>5.71</v>
       </c>
       <c r="N1078">
-        <v>8.66</v>
+        <v>8.85</v>
       </c>
       <c r="O1078">
         <v>1</v>
@@ -56112,10 +56112,10 @@
         <v>6.024441462215994</v>
       </c>
       <c r="D1079" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E1079">
-        <v>6.31237061958945</v>
+        <v>6.69328796985848</v>
       </c>
       <c r="F1079">
         <v>-1</v>
@@ -56124,10 +56124,10 @@
         <v>0.01051555853778401</v>
       </c>
       <c r="H1079">
-        <v>0.01100762938041055</v>
+        <v>0.01162671203014152</v>
       </c>
       <c r="I1079">
-        <v>-0.2879291573734557</v>
+        <v>-0.6688465076424857</v>
       </c>
       <c r="J1079">
         <v>0.4252951776106071</v>
@@ -56139,10 +56139,10 @@
         <v>8.27</v>
       </c>
       <c r="M1079">
-        <v>5.52</v>
+        <v>5.8</v>
       </c>
       <c r="N1079">
-        <v>8.66</v>
+        <v>9.16</v>
       </c>
       <c r="O1079">
         <v>1</v>
@@ -56162,10 +56162,10 @@
         <v>5.743098670470165</v>
       </c>
       <c r="D1080" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E1080">
-        <v>6.018239519127901</v>
+        <v>6.384237175895258</v>
       </c>
       <c r="F1080">
         <v>-1</v>
@@ -56174,10 +56174,10 @@
         <v>0.01079690132952984</v>
       </c>
       <c r="H1080">
-        <v>0.0113017604808721</v>
+        <v>0.01193576282410474</v>
       </c>
       <c r="I1080">
-        <v>-0.2751408486577356</v>
+        <v>-0.6411385054250927</v>
       </c>
       <c r="J1080">
         <v>0.4785797972594382</v>
@@ -56189,10 +56189,10 @@
         <v>8.27</v>
       </c>
       <c r="M1080">
-        <v>5.52</v>
+        <v>5.8</v>
       </c>
       <c r="N1080">
-        <v>8.66</v>
+        <v>9.16</v>
       </c>
       <c r="O1080">
         <v>1</v>
@@ -56212,10 +56212,10 @@
         <v>5.512060928235529</v>
       </c>
       <c r="D1081" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E1081">
-        <v>5.776700061337145</v>
+        <v>6.130445716622362</v>
       </c>
       <c r="F1081">
         <v>-1</v>
@@ -56224,10 +56224,10 @@
         <v>0.01102793907176447</v>
       </c>
       <c r="H1081">
-        <v>0.01154329993866286</v>
+        <v>0.01218955428337764</v>
       </c>
       <c r="I1081">
-        <v>-0.2646391331016158</v>
+        <v>-0.618384788386833</v>
       </c>
       <c r="J1081">
         <v>0.5223369454099376</v>
@@ -56239,10 +56239,10 @@
         <v>8.27</v>
       </c>
       <c r="M1081">
-        <v>5.52</v>
+        <v>5.8</v>
       </c>
       <c r="N1081">
-        <v>8.66</v>
+        <v>9.16</v>
       </c>
       <c r="O1081">
         <v>1</v>
@@ -56262,10 +56262,10 @@
         <v>5.044404491169697</v>
       </c>
       <c r="D1082" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E1082">
-        <v>5.287786513495593</v>
+        <v>5.616732206209138</v>
       </c>
       <c r="F1082">
         <v>-1</v>
@@ -56274,10 +56274,10 @@
         <v>0.0114955955088303</v>
       </c>
       <c r="H1082">
-        <v>0.01203221348650441</v>
+        <v>0.01270326779379086</v>
       </c>
       <c r="I1082">
-        <v>-0.2433820223258962</v>
+        <v>-0.5723277150394406</v>
       </c>
       <c r="J1082">
         <v>0.6109082403087693</v>
@@ -56289,10 +56289,10 @@
         <v>8.27</v>
       </c>
       <c r="M1082">
-        <v>5.52</v>
+        <v>5.8</v>
       </c>
       <c r="N1082">
-        <v>8.66</v>
+        <v>9.16</v>
       </c>
       <c r="O1082">
         <v>1</v>
@@ -56312,10 +56312,10 @@
         <v>5.443358172213278</v>
       </c>
       <c r="D1083" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E1083">
-        <v>5.72891631515216</v>
+        <v>6.054976780082768</v>
       </c>
       <c r="F1083">
         <v>-1</v>
@@ -56324,10 +56324,10 @@
         <v>0.01109664182778672</v>
       </c>
       <c r="H1083">
-        <v>0.01197108368484784</v>
+        <v>0.01226502321991723</v>
       </c>
       <c r="I1083">
-        <v>-0.285558142938882</v>
+        <v>-0.6116186078694898</v>
       </c>
       <c r="J1083">
         <v>0.5353488310202125</v>
@@ -56339,10 +56339,10 @@
         <v>8.27</v>
       </c>
       <c r="M1083">
-        <v>5.83</v>
+        <v>5.8</v>
       </c>
       <c r="N1083">
-        <v>8.85</v>
+        <v>9.16</v>
       </c>
       <c r="O1083">
         <v>1</v>
@@ -56362,10 +56362,10 @@
         <v>5.71703296703297</v>
       </c>
       <c r="D1084" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E1084">
-        <v>6.031098901098904</v>
+        <v>6.355604395604399</v>
       </c>
       <c r="F1084">
         <v>-1</v>
@@ -56374,10 +56374,10 @@
         <v>0.01082296703296703</v>
       </c>
       <c r="H1084">
-        <v>0.0116689010989011</v>
+        <v>0.0119643956043956</v>
       </c>
       <c r="I1084">
-        <v>-0.3140659340659342</v>
+        <v>-0.6385714285714297</v>
       </c>
       <c r="J1084">
         <v>0.4835164835164829</v>
@@ -56389,10 +56389,10 @@
         <v>8.27</v>
       </c>
       <c r="M1084">
-        <v>5.83</v>
+        <v>5.8</v>
       </c>
       <c r="N1084">
-        <v>8.85</v>
+        <v>9.16</v>
       </c>
       <c r="O1084">
         <v>1</v>
@@ -56412,10 +56412,10 @@
         <v>5.853864517773994</v>
       </c>
       <c r="D1085" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E1085">
-        <v>6.182183738375452</v>
+        <v>6.5059117808881</v>
       </c>
       <c r="F1085">
         <v>-1</v>
@@ -56424,10 +56424,10 @@
         <v>0.01068613548222601</v>
       </c>
       <c r="H1085">
-        <v>0.01151781626162455</v>
+        <v>0.0118140882191119</v>
       </c>
       <c r="I1085">
-        <v>-0.3283192206014576</v>
+        <v>-0.6520472631141061</v>
       </c>
       <c r="J1085">
         <v>0.4576014170882586</v>
@@ -56439,10 +56439,10 @@
         <v>8.27</v>
       </c>
       <c r="M1085">
-        <v>5.83</v>
+        <v>5.8</v>
       </c>
       <c r="N1085">
-        <v>8.85</v>
+        <v>9.16</v>
       </c>
       <c r="O1085">
         <v>1</v>
@@ -56462,10 +56462,10 @@
         <v>5.996957847030043</v>
       </c>
       <c r="D1086" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E1086">
-        <v>6.34018262276234</v>
+        <v>6.663097634995124</v>
       </c>
       <c r="F1086">
         <v>-1</v>
@@ -56474,10 +56474,10 @@
         <v>0.01054304215296996</v>
       </c>
       <c r="H1086">
-        <v>0.01135981737723766</v>
+        <v>0.01165690236500488</v>
       </c>
       <c r="I1086">
-        <v>-0.3432247757322973</v>
+        <v>-0.666139787965081</v>
       </c>
       <c r="J1086">
         <v>0.4305004077594615</v>
@@ -56489,10 +56489,10 @@
         <v>8.27</v>
       </c>
       <c r="M1086">
-        <v>5.83</v>
+        <v>5.8</v>
       </c>
       <c r="N1086">
-        <v>8.85</v>
+        <v>9.16</v>
       </c>
       <c r="O1086">
         <v>1</v>
@@ -56512,10 +56512,10 @@
         <v>6.332482120319733</v>
       </c>
       <c r="D1087" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E1087">
-        <v>6.710657341186373</v>
+        <v>7.031665965502739</v>
       </c>
       <c r="F1087">
         <v>-1</v>
@@ -56524,10 +56524,10 @@
         <v>0.01020751787968027</v>
       </c>
       <c r="H1087">
-        <v>0.01098934265881363</v>
+        <v>0.01128833403449726</v>
       </c>
       <c r="I1087">
-        <v>-0.3781752208666393</v>
+        <v>-0.6991838451830059</v>
       </c>
       <c r="J1087">
         <v>0.3669541438788382</v>
@@ -56539,10 +56539,10 @@
         <v>8.27</v>
       </c>
       <c r="M1087">
-        <v>5.83</v>
+        <v>5.8</v>
       </c>
       <c r="N1087">
-        <v>8.85</v>
+        <v>9.16</v>
       </c>
       <c r="O1087">
         <v>1</v>
@@ -56562,10 +56562,10 @@
         <v>6.538088893528732</v>
       </c>
       <c r="D1088" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E1088">
-        <v>6.937681486604642</v>
+        <v>7.257521890618683</v>
       </c>
       <c r="F1088">
         <v>-1</v>
@@ -56574,10 +56574,10 @@
         <v>0.01000191110647127</v>
       </c>
       <c r="H1088">
-        <v>0.01076231851339536</v>
+        <v>0.01106247810938132</v>
       </c>
       <c r="I1088">
-        <v>-0.3995925930759103</v>
+        <v>-0.7194329970899513</v>
       </c>
       <c r="J1088">
         <v>0.3280134671347097</v>
@@ -56589,10 +56589,10 @@
         <v>8.27</v>
       </c>
       <c r="M1088">
-        <v>5.83</v>
+        <v>5.8</v>
       </c>
       <c r="N1088">
-        <v>8.85</v>
+        <v>9.16</v>
       </c>
       <c r="O1088">
         <v>1</v>
@@ -56615,7 +56615,7 @@
         <v>471</v>
       </c>
       <c r="E1089">
-        <v>6.870200212145323</v>
+        <v>7.148994961548665</v>
       </c>
       <c r="F1089">
         <v>-1</v>
@@ -56624,10 +56624,10 @@
         <v>0.01010070803500397</v>
       </c>
       <c r="H1089">
-        <v>0.01082979978785467</v>
+        <v>0.01117100503845134</v>
       </c>
       <c r="I1089">
-        <v>-0.430908247149298</v>
+        <v>-0.7097029965526396</v>
       </c>
       <c r="J1089">
         <v>0.3467250066295405</v>
@@ -56639,10 +56639,10 @@
         <v>8.27</v>
       </c>
       <c r="M1089">
-        <v>5.71</v>
+        <v>5.8</v>
       </c>
       <c r="N1089">
-        <v>8.85</v>
+        <v>9.16</v>
       </c>
       <c r="O1089">
         <v>1</v>
@@ -56665,7 +56665,7 @@
         <v>471</v>
       </c>
       <c r="E1090">
-        <v>6.498859368331202</v>
+        <v>6.771801109688437</v>
       </c>
       <c r="F1090">
         <v>-1</v>
@@ -56674,10 +56674,10 @@
         <v>0.01044408450704225</v>
       </c>
       <c r="H1090">
-        <v>0.0112011406316688</v>
+        <v>0.01154819889031156</v>
       </c>
       <c r="I1090">
-        <v>-0.4029438753734533</v>
+        <v>-0.6758856167306879</v>
       </c>
       <c r="J1090">
         <v>0.4117584293640626</v>
@@ -56689,10 +56689,10 @@
         <v>8.27</v>
       </c>
       <c r="M1090">
-        <v>5.71</v>
+        <v>5.8</v>
       </c>
       <c r="N1090">
-        <v>8.85</v>
+        <v>9.16</v>
       </c>
       <c r="O1090">
         <v>1</v>
@@ -56715,7 +56715,7 @@
         <v>471</v>
       </c>
       <c r="E1091">
-        <v>6.274041826717882</v>
+        <v>6.543440034144259</v>
       </c>
       <c r="F1091">
         <v>-1</v>
@@ -56724,10 +56724,10 @@
         <v>0.01065197183098592</v>
       </c>
       <c r="H1091">
-        <v>0.01142595817328212</v>
+        <v>0.01177655996585574</v>
       </c>
       <c r="I1091">
-        <v>-0.3860136577037983</v>
+        <v>-0.6554118651301755</v>
       </c>
       <c r="J1091">
         <v>0.4511310285958173</v>
@@ -56739,10 +56739,10 @@
         <v>8.27</v>
       </c>
       <c r="M1091">
-        <v>5.71</v>
+        <v>5.8</v>
       </c>
       <c r="N1091">
-        <v>8.85</v>
+        <v>9.16</v>
       </c>
       <c r="O1091">
         <v>1</v>
@@ -56765,7 +56765,7 @@
         <v>471</v>
       </c>
       <c r="E1092">
-        <v>6.967242724322871</v>
+        <v>7.247567040468065</v>
       </c>
       <c r="F1092">
         <v>-1</v>
@@ -56774,10 +56774,10 @@
         <v>0.01001097345281528</v>
       </c>
       <c r="H1092">
-        <v>0.01073275727567713</v>
+        <v>0.01107243295953194</v>
       </c>
       <c r="I1092">
-        <v>-0.4382161771381501</v>
+        <v>-0.7185404932833439</v>
       </c>
       <c r="J1092">
         <v>0.3297298206089543</v>
@@ -56789,10 +56789,10 @@
         <v>8.27</v>
       </c>
       <c r="M1092">
-        <v>5.71</v>
+        <v>5.8</v>
       </c>
       <c r="N1092">
-        <v>8.85</v>
+        <v>9.16</v>
       </c>
       <c r="O1092">
         <v>1</v>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3288" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3288" uniqueCount="609">
   <si>
     <t>trade_time</t>
   </si>
@@ -1423,13 +1423,10 @@
     <t>2021-06-09</t>
   </si>
   <si>
-    <t>2021-09-07</t>
-  </si>
-  <si>
-    <t>2021-09-08</t>
-  </si>
-  <si>
     <t>2021-09-09</t>
+  </si>
+  <si>
+    <t>2021-09-13</t>
   </si>
   <si>
     <t>2016-01-29</t>
@@ -2298,7 +2295,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2348,7 +2345,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2398,7 +2395,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2448,7 +2445,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2498,7 +2495,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2548,7 +2545,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2598,7 +2595,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2648,7 +2645,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2698,7 +2695,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2748,7 +2745,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2798,7 +2795,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2848,7 +2845,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2898,7 +2895,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2948,7 +2945,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2998,7 +2995,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -3048,7 +3045,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -3098,7 +3095,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -3148,7 +3145,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -3198,7 +3195,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -3248,7 +3245,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -3298,7 +3295,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3348,7 +3345,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3398,7 +3395,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3448,7 +3445,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3498,7 +3495,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3548,7 +3545,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3598,7 +3595,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3648,7 +3645,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3698,7 +3695,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3748,7 +3745,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3798,7 +3795,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3848,7 +3845,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3898,7 +3895,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3948,7 +3945,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3998,7 +3995,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -4048,7 +4045,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -4098,7 +4095,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -4148,7 +4145,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -4198,7 +4195,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -4248,7 +4245,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -4298,7 +4295,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4348,7 +4345,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4398,7 +4395,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4448,7 +4445,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4498,7 +4495,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4548,7 +4545,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4598,7 +4595,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4648,7 +4645,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4698,7 +4695,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4748,7 +4745,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4798,7 +4795,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4848,7 +4845,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4898,7 +4895,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -5798,7 +5795,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5848,7 +5845,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5898,7 +5895,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5948,7 +5945,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5998,7 +5995,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -6048,7 +6045,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -6098,7 +6095,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -6148,7 +6145,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -6198,7 +6195,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -6248,7 +6245,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -6298,7 +6295,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -6348,7 +6345,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -6398,7 +6395,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6448,7 +6445,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6498,7 +6495,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6548,7 +6545,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6598,7 +6595,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6648,7 +6645,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6698,7 +6695,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6748,7 +6745,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -7348,7 +7345,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7398,7 +7395,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7448,7 +7445,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7498,7 +7495,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7548,7 +7545,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7598,7 +7595,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7648,7 +7645,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7698,7 +7695,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7748,7 +7745,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7798,7 +7795,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7848,7 +7845,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7898,7 +7895,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7948,7 +7945,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7998,7 +7995,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -8048,7 +8045,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -8098,7 +8095,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -8148,7 +8145,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -8198,7 +8195,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -8248,7 +8245,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -8298,7 +8295,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -8348,7 +8345,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -8698,7 +8695,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8748,7 +8745,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8798,7 +8795,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8848,7 +8845,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8898,7 +8895,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8948,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8998,7 +8995,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -9048,7 +9045,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -9098,7 +9095,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -9148,7 +9145,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -9198,7 +9195,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -9248,7 +9245,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -9298,7 +9295,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -9348,7 +9345,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9398,7 +9395,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9448,7 +9445,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9498,7 +9495,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9548,7 +9545,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9598,7 +9595,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9948,7 +9945,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9998,7 +9995,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -10048,7 +10045,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -10098,7 +10095,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -10148,7 +10145,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -10198,7 +10195,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -10248,7 +10245,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10298,7 +10295,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -10348,7 +10345,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10398,7 +10395,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -10448,7 +10445,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10498,7 +10495,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10548,7 +10545,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10598,7 +10595,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10648,7 +10645,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10698,7 +10695,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10748,7 +10745,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10798,7 +10795,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -12148,7 +12145,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -12198,7 +12195,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -12248,7 +12245,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -12298,7 +12295,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -12348,7 +12345,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12398,7 +12395,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12448,7 +12445,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12498,7 +12495,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12548,7 +12545,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12698,7 +12695,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12748,7 +12745,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12948,7 +12945,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12998,7 +12995,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -13048,7 +13045,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -13098,7 +13095,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -13148,7 +13145,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -13198,7 +13195,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -13648,7 +13645,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13698,7 +13695,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13748,7 +13745,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13798,7 +13795,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13848,7 +13845,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -18548,7 +18545,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -18598,7 +18595,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18648,7 +18645,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18698,7 +18695,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18748,7 +18745,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18798,7 +18795,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18848,7 +18845,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -19098,7 +19095,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -19148,7 +19145,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -19198,7 +19195,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -19248,7 +19245,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -19298,7 +19295,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -19798,7 +19795,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19848,7 +19845,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19898,7 +19895,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19948,7 +19945,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -20098,7 +20095,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -20148,7 +20145,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -20198,7 +20195,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -20248,7 +20245,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -20298,7 +20295,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -20548,7 +20545,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20598,7 +20595,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20648,7 +20645,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20698,7 +20695,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20748,7 +20745,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20798,7 +20795,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20848,7 +20845,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20898,7 +20895,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20948,7 +20945,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20998,7 +20995,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -21048,7 +21045,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -21098,7 +21095,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -21148,7 +21145,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -21198,7 +21195,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -21248,7 +21245,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -21298,7 +21295,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -21348,7 +21345,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21398,7 +21395,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21448,7 +21445,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -21498,7 +21495,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21548,7 +21545,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21598,7 +21595,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21648,7 +21645,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21698,7 +21695,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21748,7 +21745,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21798,7 +21795,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21848,7 +21845,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21898,7 +21895,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21948,7 +21945,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21998,7 +21995,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -22048,7 +22045,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -22098,7 +22095,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -22148,7 +22145,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -22198,7 +22195,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -22248,7 +22245,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -22298,7 +22295,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -22348,7 +22345,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -22398,7 +22395,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22448,7 +22445,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22498,7 +22495,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22548,7 +22545,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22598,7 +22595,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22648,7 +22645,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22698,7 +22695,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22998,7 +22995,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -23048,7 +23045,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -23098,7 +23095,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -23148,7 +23145,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -23198,7 +23195,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -23898,7 +23895,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23948,7 +23945,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23998,7 +23995,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -24048,7 +24045,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -24098,7 +24095,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -24148,7 +24145,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -24198,7 +24195,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -24248,7 +24245,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -24298,7 +24295,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -24348,7 +24345,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24398,7 +24395,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24448,7 +24445,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24498,7 +24495,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24548,7 +24545,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24598,7 +24595,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24648,7 +24645,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24698,7 +24695,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24748,7 +24745,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24798,7 +24795,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24848,7 +24845,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24898,7 +24895,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -25248,7 +25245,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -25298,7 +25295,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -25348,7 +25345,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -25398,7 +25395,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25448,7 +25445,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -25498,7 +25495,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25548,7 +25545,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25598,7 +25595,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25648,7 +25645,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25698,7 +25695,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25748,7 +25745,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25798,7 +25795,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25848,7 +25845,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25898,7 +25895,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25948,7 +25945,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25998,7 +25995,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -26048,7 +26045,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -26098,7 +26095,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -26148,7 +26145,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -26198,7 +26195,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -26248,7 +26245,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -26298,7 +26295,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -26348,7 +26345,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26398,7 +26395,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26448,7 +26445,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26498,7 +26495,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26548,7 +26545,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26598,7 +26595,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26648,7 +26645,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26698,7 +26695,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26748,7 +26745,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26798,7 +26795,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26848,7 +26845,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26898,7 +26895,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26948,7 +26945,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26998,7 +26995,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -27048,7 +27045,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -27098,7 +27095,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -27148,7 +27145,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -27198,7 +27195,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -27248,7 +27245,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -27298,7 +27295,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -27348,7 +27345,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27398,7 +27395,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27448,7 +27445,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -27698,7 +27695,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27748,7 +27745,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27798,7 +27795,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27848,7 +27845,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27898,7 +27895,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -28198,7 +28195,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -28248,7 +28245,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -28298,7 +28295,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -28348,7 +28345,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -28398,7 +28395,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28948,7 +28945,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28998,7 +28995,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -29048,7 +29045,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -29098,7 +29095,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -29148,7 +29145,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -29198,7 +29195,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -29248,7 +29245,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -29548,7 +29545,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29598,7 +29595,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29648,7 +29645,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29698,7 +29695,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29748,7 +29745,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29798,7 +29795,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29848,7 +29845,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29898,7 +29895,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29948,7 +29945,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29998,7 +29995,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -30048,7 +30045,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -30098,7 +30095,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -30148,7 +30145,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -30198,7 +30195,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -30248,7 +30245,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -30298,7 +30295,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -30348,7 +30345,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -30648,7 +30645,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30698,7 +30695,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30748,7 +30745,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30798,7 +30795,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30848,7 +30845,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30898,7 +30895,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30948,7 +30945,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30998,7 +30995,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -31048,7 +31045,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -31648,7 +31645,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31698,7 +31695,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31748,7 +31745,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -31798,7 +31795,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -31848,7 +31845,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -31898,7 +31895,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -31948,7 +31945,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31998,7 +31995,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -32048,7 +32045,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -32098,7 +32095,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -32148,7 +32145,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -32198,7 +32195,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -32248,7 +32245,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -32298,7 +32295,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -32348,7 +32345,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -32398,7 +32395,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32448,7 +32445,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32498,7 +32495,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -32548,7 +32545,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32598,7 +32595,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32648,7 +32645,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32698,7 +32695,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32748,7 +32745,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32798,7 +32795,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32848,7 +32845,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32898,7 +32895,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32948,7 +32945,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32998,7 +32995,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -33048,7 +33045,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -33098,7 +33095,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -33148,7 +33145,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -33198,7 +33195,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -33248,7 +33245,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -33298,7 +33295,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -33548,7 +33545,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33598,7 +33595,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -33648,7 +33645,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -33698,7 +33695,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -33748,7 +33745,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33798,7 +33795,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33848,7 +33845,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33898,7 +33895,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33948,7 +33945,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33998,7 +33995,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -34048,7 +34045,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -34098,7 +34095,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -34648,7 +34645,7 @@
         <v>1</v>
       </c>
       <c r="P649" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="650" spans="1:16">
@@ -34698,7 +34695,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -34748,7 +34745,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -34798,7 +34795,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -34848,7 +34845,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -34898,7 +34895,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -34948,7 +34945,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -34998,7 +34995,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -35048,7 +35045,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -35098,7 +35095,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -35148,7 +35145,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -35198,7 +35195,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -35248,7 +35245,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -35298,7 +35295,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -35348,7 +35345,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -35398,7 +35395,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -35448,7 +35445,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -35498,7 +35495,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -35548,7 +35545,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35598,7 +35595,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35648,7 +35645,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -36148,7 +36145,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -36198,7 +36195,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -36248,7 +36245,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -36298,7 +36295,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36348,7 +36345,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36398,7 +36395,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36448,7 +36445,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -36498,7 +36495,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36548,7 +36545,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36598,7 +36595,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36648,7 +36645,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36698,7 +36695,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36748,7 +36745,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36798,7 +36795,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36848,7 +36845,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36898,7 +36895,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36948,7 +36945,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36998,7 +36995,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -37048,7 +37045,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -37098,7 +37095,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -37148,7 +37145,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -37198,7 +37195,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -37248,7 +37245,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -37298,7 +37295,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -37348,7 +37345,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -37398,7 +37395,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -37448,7 +37445,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -37498,7 +37495,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -37548,7 +37545,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -37598,7 +37595,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37648,7 +37645,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37698,7 +37695,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -38148,7 +38145,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -38198,7 +38195,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -38248,7 +38245,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -38298,7 +38295,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -38348,7 +38345,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38398,7 +38395,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38448,7 +38445,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38498,7 +38495,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -39098,7 +39095,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -39148,7 +39145,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -39198,7 +39195,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -39248,7 +39245,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -39298,7 +39295,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -39348,7 +39345,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -39398,7 +39395,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -39448,7 +39445,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -39498,7 +39495,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -39898,7 +39895,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39948,7 +39945,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39998,7 +39995,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -40048,7 +40045,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -40098,7 +40095,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -40148,7 +40145,7 @@
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -40198,7 +40195,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -40248,7 +40245,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -40298,7 +40295,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -40348,7 +40345,7 @@
         <v>1</v>
       </c>
       <c r="P763" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="764" spans="1:16">
@@ -40398,7 +40395,7 @@
         <v>1</v>
       </c>
       <c r="P764" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="765" spans="1:16">
@@ -40448,7 +40445,7 @@
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -40498,7 +40495,7 @@
         <v>1</v>
       </c>
       <c r="P766" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="767" spans="1:16">
@@ -40548,7 +40545,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -40598,7 +40595,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -40648,7 +40645,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -40698,7 +40695,7 @@
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="771" spans="1:16">
@@ -40748,7 +40745,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -40798,7 +40795,7 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -41098,7 +41095,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -41148,7 +41145,7 @@
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -41198,7 +41195,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -41248,7 +41245,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -41298,7 +41295,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -41348,7 +41345,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -41398,7 +41395,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -41448,7 +41445,7 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -41498,7 +41495,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -41548,7 +41545,7 @@
         <v>1</v>
       </c>
       <c r="P787" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="788" spans="1:16">
@@ -41598,7 +41595,7 @@
         <v>1</v>
       </c>
       <c r="P788" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="789" spans="1:16">
@@ -41648,7 +41645,7 @@
         <v>1</v>
       </c>
       <c r="P789" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="790" spans="1:16">
@@ -41998,7 +41995,7 @@
         <v>1</v>
       </c>
       <c r="P796" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="797" spans="1:16">
@@ -42048,7 +42045,7 @@
         <v>1</v>
       </c>
       <c r="P797" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="798" spans="1:16">
@@ -42098,7 +42095,7 @@
         <v>1</v>
       </c>
       <c r="P798" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="799" spans="1:16">
@@ -42148,7 +42145,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -42198,7 +42195,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -42248,7 +42245,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -42298,7 +42295,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -42348,7 +42345,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -42398,7 +42395,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -42448,7 +42445,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -42498,7 +42495,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -42548,7 +42545,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42598,7 +42595,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42648,7 +42645,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42698,7 +42695,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -43448,7 +43445,7 @@
         <v>1</v>
       </c>
       <c r="P825" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="826" spans="1:16">
@@ -43498,7 +43495,7 @@
         <v>1</v>
       </c>
       <c r="P826" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="827" spans="1:16">
@@ -43548,7 +43545,7 @@
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="828" spans="1:16">
@@ -43598,7 +43595,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -43648,7 +43645,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -43698,7 +43695,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -43748,7 +43745,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -43798,7 +43795,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43848,7 +43845,7 @@
         <v>1</v>
       </c>
       <c r="P833" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="834" spans="1:16">
@@ -43898,7 +43895,7 @@
         <v>1</v>
       </c>
       <c r="P834" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="835" spans="1:16">
@@ -43948,7 +43945,7 @@
         <v>1</v>
       </c>
       <c r="P835" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="836" spans="1:16">
@@ -43998,7 +43995,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -44048,7 +44045,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -44098,7 +44095,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -44648,7 +44645,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44698,7 +44695,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44748,7 +44745,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -44798,7 +44795,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -44848,7 +44845,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -44898,7 +44895,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44948,7 +44945,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -44998,7 +44995,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -45048,7 +45045,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -45098,7 +45095,7 @@
         <v>1</v>
       </c>
       <c r="P858" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="859" spans="1:16">
@@ -45148,7 +45145,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -45198,7 +45195,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -45248,7 +45245,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -45298,7 +45295,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -45348,7 +45345,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -45398,7 +45395,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -45448,7 +45445,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45498,7 +45495,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45548,7 +45545,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45598,7 +45595,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45648,7 +45645,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45698,7 +45695,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45748,7 +45745,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45798,7 +45795,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45848,7 +45845,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -45898,7 +45895,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45948,7 +45945,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45998,7 +45995,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -46048,7 +46045,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -46098,7 +46095,7 @@
         <v>1</v>
       </c>
       <c r="P878" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="879" spans="1:16">
@@ -46148,7 +46145,7 @@
         <v>1</v>
       </c>
       <c r="P879" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="880" spans="1:16">
@@ -46198,7 +46195,7 @@
         <v>1</v>
       </c>
       <c r="P880" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="881" spans="1:16">
@@ -46248,7 +46245,7 @@
         <v>1</v>
       </c>
       <c r="P881" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="882" spans="1:16">
@@ -46298,7 +46295,7 @@
         <v>1</v>
       </c>
       <c r="P882" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -46348,7 +46345,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46398,7 +46395,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46448,7 +46445,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46498,7 +46495,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46548,7 +46545,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46598,7 +46595,7 @@
         <v>1</v>
       </c>
       <c r="P888" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="889" spans="1:16">
@@ -46648,7 +46645,7 @@
         <v>1</v>
       </c>
       <c r="P889" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="890" spans="1:16">
@@ -46698,7 +46695,7 @@
         <v>1</v>
       </c>
       <c r="P890" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="891" spans="1:16">
@@ -46748,7 +46745,7 @@
         <v>1</v>
       </c>
       <c r="P891" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="892" spans="1:16">
@@ -46798,7 +46795,7 @@
         <v>1</v>
       </c>
       <c r="P892" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="893" spans="1:16">
@@ -46848,7 +46845,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46898,7 +46895,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46948,7 +46945,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -46998,7 +46995,7 @@
         <v>1</v>
       </c>
       <c r="P896" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="897" spans="1:16">
@@ -47048,7 +47045,7 @@
         <v>1</v>
       </c>
       <c r="P897" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="898" spans="1:16">
@@ -47098,7 +47095,7 @@
         <v>1</v>
       </c>
       <c r="P898" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="899" spans="1:16">
@@ -47148,7 +47145,7 @@
         <v>1</v>
       </c>
       <c r="P899" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="900" spans="1:16">
@@ -47198,7 +47195,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -47248,7 +47245,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -47298,7 +47295,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -47348,7 +47345,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -47398,7 +47395,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -47448,7 +47445,7 @@
         <v>1</v>
       </c>
       <c r="P905" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="906" spans="1:16">
@@ -47498,7 +47495,7 @@
         <v>1</v>
       </c>
       <c r="P906" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="907" spans="1:16">
@@ -47548,7 +47545,7 @@
         <v>1</v>
       </c>
       <c r="P907" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="908" spans="1:16">
@@ -47598,7 +47595,7 @@
         <v>1</v>
       </c>
       <c r="P908" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="909" spans="1:16">
@@ -47648,7 +47645,7 @@
         <v>1</v>
       </c>
       <c r="P909" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="910" spans="1:16">
@@ -47698,7 +47695,7 @@
         <v>1</v>
       </c>
       <c r="P910" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="911" spans="1:16">
@@ -47748,7 +47745,7 @@
         <v>1</v>
       </c>
       <c r="P911" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="912" spans="1:16">
@@ -47798,7 +47795,7 @@
         <v>1</v>
       </c>
       <c r="P912" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="913" spans="1:16">
@@ -47848,7 +47845,7 @@
         <v>1</v>
       </c>
       <c r="P913" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="914" spans="1:16">
@@ -47898,7 +47895,7 @@
         <v>1</v>
       </c>
       <c r="P914" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="915" spans="1:16">
@@ -47948,7 +47945,7 @@
         <v>1</v>
       </c>
       <c r="P915" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="916" spans="1:16">
@@ -47998,7 +47995,7 @@
         <v>1</v>
       </c>
       <c r="P916" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="917" spans="1:16">
@@ -48048,7 +48045,7 @@
         <v>1</v>
       </c>
       <c r="P917" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="918" spans="1:16">
@@ -48098,7 +48095,7 @@
         <v>1</v>
       </c>
       <c r="P918" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="919" spans="1:16">
@@ -48148,7 +48145,7 @@
         <v>1</v>
       </c>
       <c r="P919" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="920" spans="1:16">
@@ -48198,7 +48195,7 @@
         <v>1</v>
       </c>
       <c r="P920" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="921" spans="1:16">
@@ -48248,7 +48245,7 @@
         <v>1</v>
       </c>
       <c r="P921" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="922" spans="1:16">
@@ -48298,7 +48295,7 @@
         <v>1</v>
       </c>
       <c r="P922" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="923" spans="1:16">
@@ -48348,7 +48345,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -48398,7 +48395,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -48448,7 +48445,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48498,7 +48495,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48548,7 +48545,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -48598,7 +48595,7 @@
         <v>1</v>
       </c>
       <c r="P928" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="929" spans="1:16">
@@ -48648,7 +48645,7 @@
         <v>1</v>
       </c>
       <c r="P929" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="930" spans="1:16">
@@ -48698,7 +48695,7 @@
         <v>1</v>
       </c>
       <c r="P930" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="931" spans="1:16">
@@ -48748,7 +48745,7 @@
         <v>1</v>
       </c>
       <c r="P931" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="932" spans="1:16">
@@ -48798,7 +48795,7 @@
         <v>1</v>
       </c>
       <c r="P932" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="933" spans="1:16">
@@ -48848,7 +48845,7 @@
         <v>1</v>
       </c>
       <c r="P933" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="934" spans="1:16">
@@ -48898,7 +48895,7 @@
         <v>1</v>
       </c>
       <c r="P934" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="935" spans="1:16">
@@ -48948,7 +48945,7 @@
         <v>1</v>
       </c>
       <c r="P935" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="936" spans="1:16">
@@ -48998,7 +48995,7 @@
         <v>1</v>
       </c>
       <c r="P936" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="937" spans="1:16">
@@ -49048,7 +49045,7 @@
         <v>1</v>
       </c>
       <c r="P937" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="938" spans="1:16">
@@ -49098,7 +49095,7 @@
         <v>1</v>
       </c>
       <c r="P938" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="939" spans="1:16">
@@ -49148,7 +49145,7 @@
         <v>1</v>
       </c>
       <c r="P939" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="940" spans="1:16">
@@ -49198,7 +49195,7 @@
         <v>1</v>
       </c>
       <c r="P940" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="941" spans="1:16">
@@ -49248,7 +49245,7 @@
         <v>1</v>
       </c>
       <c r="P941" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="942" spans="1:16">
@@ -49298,7 +49295,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -49348,7 +49345,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49398,7 +49395,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49448,7 +49445,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -49498,7 +49495,7 @@
         <v>1</v>
       </c>
       <c r="P946" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="947" spans="1:16">
@@ -49548,7 +49545,7 @@
         <v>1</v>
       </c>
       <c r="P947" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="948" spans="1:16">
@@ -49598,7 +49595,7 @@
         <v>1</v>
       </c>
       <c r="P948" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="949" spans="1:16">
@@ -49648,7 +49645,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -49698,7 +49695,7 @@
         <v>1</v>
       </c>
       <c r="P950" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="951" spans="1:16">
@@ -49748,7 +49745,7 @@
         <v>1</v>
       </c>
       <c r="P951" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="952" spans="1:16">
@@ -49798,7 +49795,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -49848,7 +49845,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -49898,7 +49895,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -49948,7 +49945,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -49998,7 +49995,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -50048,7 +50045,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -50098,7 +50095,7 @@
         <v>1</v>
       </c>
       <c r="P958" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="959" spans="1:16">
@@ -50148,7 +50145,7 @@
         <v>1</v>
       </c>
       <c r="P959" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="960" spans="1:16">
@@ -50198,7 +50195,7 @@
         <v>1</v>
       </c>
       <c r="P960" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="961" spans="1:16">
@@ -50248,7 +50245,7 @@
         <v>1</v>
       </c>
       <c r="P961" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="962" spans="1:16">
@@ -50298,7 +50295,7 @@
         <v>1</v>
       </c>
       <c r="P962" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="963" spans="1:16">
@@ -50348,7 +50345,7 @@
         <v>1</v>
       </c>
       <c r="P963" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="964" spans="1:16">
@@ -50398,7 +50395,7 @@
         <v>1</v>
       </c>
       <c r="P964" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="965" spans="1:16">
@@ -50448,7 +50445,7 @@
         <v>1</v>
       </c>
       <c r="P965" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="966" spans="1:16">
@@ -50498,7 +50495,7 @@
         <v>1</v>
       </c>
       <c r="P966" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="967" spans="1:16">
@@ -50548,7 +50545,7 @@
         <v>1</v>
       </c>
       <c r="P967" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="968" spans="1:16">
@@ -50598,7 +50595,7 @@
         <v>1</v>
       </c>
       <c r="P968" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="969" spans="1:16">
@@ -51798,7 +51795,7 @@
         <v>1</v>
       </c>
       <c r="P992" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="993" spans="1:16">
@@ -51848,7 +51845,7 @@
         <v>1</v>
       </c>
       <c r="P993" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="994" spans="1:16">
@@ -51898,7 +51895,7 @@
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="995" spans="1:16">
@@ -51948,7 +51945,7 @@
         <v>1</v>
       </c>
       <c r="P995" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="996" spans="1:16">
@@ -52648,7 +52645,7 @@
         <v>1</v>
       </c>
       <c r="P1009" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="1010" spans="1:16">
@@ -52698,7 +52695,7 @@
         <v>1</v>
       </c>
       <c r="P1010" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="1011" spans="1:16">
@@ -52748,7 +52745,7 @@
         <v>1</v>
       </c>
       <c r="P1011" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="1012" spans="1:16">
@@ -52798,7 +52795,7 @@
         <v>1</v>
       </c>
       <c r="P1012" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1013" spans="1:16">
@@ -52848,7 +52845,7 @@
         <v>1</v>
       </c>
       <c r="P1013" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1014" spans="1:16">
@@ -52898,7 +52895,7 @@
         <v>1</v>
       </c>
       <c r="P1014" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1015" spans="1:16">
@@ -52948,7 +52945,7 @@
         <v>1</v>
       </c>
       <c r="P1015" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1016" spans="1:16">
@@ -52998,7 +52995,7 @@
         <v>1</v>
       </c>
       <c r="P1016" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1017" spans="1:16">
@@ -53048,7 +53045,7 @@
         <v>1</v>
       </c>
       <c r="P1017" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1018" spans="1:16">
@@ -53498,7 +53495,7 @@
         <v>1</v>
       </c>
       <c r="P1026" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1027" spans="1:16">
@@ -53548,7 +53545,7 @@
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
@@ -53598,7 +53595,7 @@
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
@@ -53648,7 +53645,7 @@
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
@@ -53698,7 +53695,7 @@
         <v>1</v>
       </c>
       <c r="P1030" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1031" spans="1:16">
@@ -53748,7 +53745,7 @@
         <v>1</v>
       </c>
       <c r="P1031" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="1032" spans="1:16">
@@ -53798,7 +53795,7 @@
         <v>1</v>
       </c>
       <c r="P1032" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="1033" spans="1:16">
@@ -53848,7 +53845,7 @@
         <v>1</v>
       </c>
       <c r="P1033" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="1034" spans="1:16">
@@ -53898,7 +53895,7 @@
         <v>1</v>
       </c>
       <c r="P1034" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="1035" spans="1:16">
@@ -53948,7 +53945,7 @@
         <v>1</v>
       </c>
       <c r="P1035" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="1036" spans="1:16">
@@ -54798,7 +54795,7 @@
         <v>1</v>
       </c>
       <c r="P1052" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="1053" spans="1:16">
@@ -54848,7 +54845,7 @@
         <v>1</v>
       </c>
       <c r="P1053" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="1054" spans="1:16">
@@ -54898,7 +54895,7 @@
         <v>1</v>
       </c>
       <c r="P1054" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="1055" spans="1:16">
@@ -54948,7 +54945,7 @@
         <v>1</v>
       </c>
       <c r="P1055" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="1056" spans="1:16">
@@ -54998,7 +54995,7 @@
         <v>1</v>
       </c>
       <c r="P1056" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="1057" spans="1:16">
@@ -55048,7 +55045,7 @@
         <v>1</v>
       </c>
       <c r="P1057" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="1058" spans="1:16">
@@ -55098,7 +55095,7 @@
         <v>1</v>
       </c>
       <c r="P1058" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="1059" spans="1:16">
@@ -55148,7 +55145,7 @@
         <v>1</v>
       </c>
       <c r="P1059" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="1060" spans="1:16">
@@ -55198,7 +55195,7 @@
         <v>1</v>
       </c>
       <c r="P1060" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1061" spans="1:16">
@@ -55248,7 +55245,7 @@
         <v>1</v>
       </c>
       <c r="P1061" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1062" spans="1:16">
@@ -55298,7 +55295,7 @@
         <v>1</v>
       </c>
       <c r="P1062" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1063" spans="1:16">
@@ -55348,7 +55345,7 @@
         <v>1</v>
       </c>
       <c r="P1063" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1064" spans="1:16">
@@ -55398,7 +55395,7 @@
         <v>1</v>
       </c>
       <c r="P1064" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1065" spans="1:16">
@@ -55448,7 +55445,7 @@
         <v>1</v>
       </c>
       <c r="P1065" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1066" spans="1:16">
@@ -55498,7 +55495,7 @@
         <v>1</v>
       </c>
       <c r="P1066" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1067" spans="1:16">
@@ -55548,7 +55545,7 @@
         <v>1</v>
       </c>
       <c r="P1067" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1068" spans="1:16">
@@ -55598,7 +55595,7 @@
         <v>1</v>
       </c>
       <c r="P1068" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1069" spans="1:16">
@@ -55648,7 +55645,7 @@
         <v>1</v>
       </c>
       <c r="P1069" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1070" spans="1:16">
@@ -55698,7 +55695,7 @@
         <v>1</v>
       </c>
       <c r="P1070" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1071" spans="1:16">
@@ -55715,7 +55712,7 @@
         <v>469</v>
       </c>
       <c r="E1071">
-        <v>8.35178311333636</v>
+        <v>8.66434683659535</v>
       </c>
       <c r="F1071">
         <v>-1</v>
@@ -55724,10 +55721,10 @@
         <v>0.008721215293582165</v>
       </c>
       <c r="H1071">
-        <v>0.00934821688666364</v>
+        <v>0.009655653163404651</v>
       </c>
       <c r="I1071">
-        <v>-0.5329984069185247</v>
+        <v>-0.8455621301775142</v>
       </c>
       <c r="J1071">
         <v>0.08545744196631905</v>
@@ -55739,16 +55736,16 @@
         <v>8.27</v>
       </c>
       <c r="M1071">
-        <v>5.83</v>
+        <v>5.8</v>
       </c>
       <c r="N1071">
-        <v>8.85</v>
+        <v>9.16</v>
       </c>
       <c r="O1071">
         <v>1</v>
       </c>
       <c r="P1071" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="1072" spans="1:16">
@@ -55765,7 +55762,7 @@
         <v>469</v>
       </c>
       <c r="E1072">
-        <v>8.260578071622774</v>
+        <v>8.573611117566397</v>
       </c>
       <c r="F1072">
         <v>-1</v>
@@ -55774,10 +55771,10 @@
         <v>0.008803816086077486</v>
       </c>
       <c r="H1072">
-        <v>0.009439421928377226</v>
+        <v>0.009746388882433604</v>
       </c>
       <c r="I1072">
-        <v>-0.5243941577002609</v>
+        <v>-0.8374272036438839</v>
       </c>
       <c r="J1072">
         <v>0.1011015314540694</v>
@@ -55789,16 +55786,16 @@
         <v>8.27</v>
       </c>
       <c r="M1072">
-        <v>5.83</v>
+        <v>5.8</v>
       </c>
       <c r="N1072">
-        <v>8.85</v>
+        <v>9.16</v>
       </c>
       <c r="O1072">
         <v>1</v>
       </c>
       <c r="P1072" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="1073" spans="1:16">
@@ -55815,7 +55812,7 @@
         <v>469</v>
       </c>
       <c r="E1073">
-        <v>8.198155330261933</v>
+        <v>8.51150959099815</v>
       </c>
       <c r="F1073">
         <v>-1</v>
@@ -55824,10 +55821,10 @@
         <v>0.008860349889574097</v>
       </c>
       <c r="H1073">
-        <v>0.009501844669738066</v>
+        <v>0.009808490409001851</v>
       </c>
       <c r="I1073">
-        <v>-0.5185052198360314</v>
+        <v>-0.8318594805722483</v>
       </c>
       <c r="J1073">
         <v>0.1118086912072155</v>
@@ -55839,16 +55836,16 @@
         <v>8.27</v>
       </c>
       <c r="M1073">
-        <v>5.83</v>
+        <v>5.8</v>
       </c>
       <c r="N1073">
-        <v>8.85</v>
+        <v>9.16</v>
       </c>
       <c r="O1073">
         <v>1</v>
       </c>
       <c r="P1073" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1074" spans="1:16">
@@ -55865,7 +55862,7 @@
         <v>469</v>
       </c>
       <c r="E1074">
-        <v>8.229637018388082</v>
+        <v>8.542829280729139</v>
       </c>
       <c r="F1074">
         <v>-1</v>
@@ -55874,10 +55871,10 @@
         <v>0.008831838172025886</v>
       </c>
       <c r="H1074">
-        <v>0.009470362981611916</v>
+        <v>0.009777170719270862</v>
       </c>
       <c r="I1074">
-        <v>-0.5214751904139705</v>
+        <v>-0.8346674527550269</v>
       </c>
       <c r="J1074">
         <v>0.1064087447018726</v>
@@ -55889,10 +55886,10 @@
         <v>8.27</v>
       </c>
       <c r="M1074">
-        <v>5.83</v>
+        <v>5.8</v>
       </c>
       <c r="N1074">
-        <v>8.85</v>
+        <v>9.16</v>
       </c>
       <c r="O1074">
         <v>1</v>
@@ -55915,7 +55912,7 @@
         <v>469</v>
       </c>
       <c r="E1075">
-        <v>8.286074731949732</v>
+        <v>8.598976577239872</v>
       </c>
       <c r="F1075">
         <v>-1</v>
@@ -55924,10 +55921,10 @@
         <v>0.008780724771064393</v>
       </c>
       <c r="H1075">
-        <v>0.009413925268050268</v>
+        <v>0.009721023422760128</v>
       </c>
       <c r="I1075">
-        <v>-0.526799503014125</v>
+        <v>-0.8397013483042652</v>
       </c>
       <c r="J1075">
         <v>0.09672817633795312</v>
@@ -55939,16 +55936,16 @@
         <v>8.27</v>
       </c>
       <c r="M1075">
-        <v>5.83</v>
+        <v>5.8</v>
       </c>
       <c r="N1075">
-        <v>8.85</v>
+        <v>9.16</v>
       </c>
       <c r="O1075">
         <v>1</v>
       </c>
       <c r="P1075" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="1076" spans="1:16">
@@ -55965,7 +55962,7 @@
         <v>469</v>
       </c>
       <c r="E1076">
-        <v>7.153295296685831</v>
+        <v>7.472026195673727</v>
       </c>
       <c r="F1076">
         <v>-1</v>
@@ -55974,10 +55971,10 @@
         <v>0.009806638221869434</v>
       </c>
       <c r="H1076">
-        <v>0.01054670470331417</v>
+        <v>0.01084797380432627</v>
       </c>
       <c r="I1076">
-        <v>-0.4199335185552666</v>
+        <v>-0.7386644175431618</v>
       </c>
       <c r="J1076">
         <v>0.2910299662631506</v>
@@ -55989,16 +55986,16 @@
         <v>8.27</v>
       </c>
       <c r="M1076">
-        <v>5.83</v>
+        <v>5.8</v>
       </c>
       <c r="N1076">
-        <v>8.85</v>
+        <v>9.16</v>
       </c>
       <c r="O1076">
         <v>1</v>
       </c>
       <c r="P1076" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="1077" spans="1:16">
@@ -56012,10 +56009,10 @@
         <v>6.759036860879887</v>
       </c>
       <c r="D1077" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E1077">
-        <v>7.21598493856518</v>
+        <v>7.500229885057452</v>
       </c>
       <c r="F1077">
         <v>-1</v>
@@ -56024,10 +56021,10 @@
         <v>0.009780963139120113</v>
       </c>
       <c r="H1077">
-        <v>0.01048401506143482</v>
+        <v>0.01081977011494255</v>
       </c>
       <c r="I1077">
-        <v>-0.4569480776852934</v>
+        <v>-0.7411930241775657</v>
       </c>
       <c r="J1077">
         <v>0.2861672611969911</v>
@@ -56039,10 +56036,10 @@
         <v>8.27</v>
       </c>
       <c r="M1077">
-        <v>5.71</v>
+        <v>5.8</v>
       </c>
       <c r="N1077">
-        <v>8.85</v>
+        <v>9.16</v>
       </c>
       <c r="O1077">
         <v>1</v>
@@ -56062,10 +56059,10 @@
         <v>6.737244367417659</v>
       </c>
       <c r="D1078" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E1078">
-        <v>7.19241767764296</v>
+        <v>7.476291161178489</v>
       </c>
       <c r="F1078">
         <v>-1</v>
@@ -56074,10 +56071,10 @@
         <v>0.00980275563258234</v>
       </c>
       <c r="H1078">
-        <v>0.01050758232235704</v>
+        <v>0.01084370883882151</v>
       </c>
       <c r="I1078">
-        <v>-0.4551733102253017</v>
+        <v>-0.7390467937608305</v>
       </c>
       <c r="J1078">
         <v>0.2902946273830191</v>
@@ -56089,16 +56086,16 @@
         <v>8.27</v>
       </c>
       <c r="M1078">
-        <v>5.71</v>
+        <v>5.8</v>
       </c>
       <c r="N1078">
-        <v>8.85</v>
+        <v>9.16</v>
       </c>
       <c r="O1078">
         <v>1</v>
       </c>
       <c r="P1078" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="1079" spans="1:16">
@@ -56112,7 +56109,7 @@
         <v>6.024441462215994</v>
       </c>
       <c r="D1079" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E1079">
         <v>6.69328796985848</v>
@@ -56162,7 +56159,7 @@
         <v>5.743098670470165</v>
       </c>
       <c r="D1080" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E1080">
         <v>6.384237175895258</v>
@@ -56198,7 +56195,7 @@
         <v>1</v>
       </c>
       <c r="P1080" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="1081" spans="1:16">
@@ -56212,7 +56209,7 @@
         <v>5.512060928235529</v>
       </c>
       <c r="D1081" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E1081">
         <v>6.130445716622362</v>
@@ -56262,7 +56259,7 @@
         <v>5.044404491169697</v>
       </c>
       <c r="D1082" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E1082">
         <v>5.616732206209138</v>
@@ -56298,7 +56295,7 @@
         <v>1</v>
       </c>
       <c r="P1082" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="1083" spans="1:16">
@@ -56312,10 +56309,10 @@
         <v>5.443358172213278</v>
       </c>
       <c r="D1083" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E1083">
-        <v>6.054976780082768</v>
+        <v>5.981037245013375</v>
       </c>
       <c r="F1083">
         <v>-1</v>
@@ -56324,10 +56321,10 @@
         <v>0.01109664182778672</v>
       </c>
       <c r="H1083">
-        <v>0.01226502321991723</v>
+        <v>0.01215896275498663</v>
       </c>
       <c r="I1083">
-        <v>-0.6116186078694898</v>
+        <v>-0.5376790728000964</v>
       </c>
       <c r="J1083">
         <v>0.5353488310202125</v>
@@ -56339,16 +56336,16 @@
         <v>8.27</v>
       </c>
       <c r="M1083">
-        <v>5.8</v>
+        <v>5.77</v>
       </c>
       <c r="N1083">
-        <v>9.16</v>
+        <v>9.07</v>
       </c>
       <c r="O1083">
         <v>1</v>
       </c>
       <c r="P1083" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="1084" spans="1:16">
@@ -56362,10 +56359,10 @@
         <v>5.71703296703297</v>
       </c>
       <c r="D1084" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E1084">
-        <v>6.355604395604399</v>
+        <v>6.280109890109895</v>
       </c>
       <c r="F1084">
         <v>-1</v>
@@ -56374,10 +56371,10 @@
         <v>0.01082296703296703</v>
       </c>
       <c r="H1084">
-        <v>0.0119643956043956</v>
+        <v>0.01185989010989011</v>
       </c>
       <c r="I1084">
-        <v>-0.6385714285714297</v>
+        <v>-0.5630769230769248</v>
       </c>
       <c r="J1084">
         <v>0.4835164835164829</v>
@@ -56389,16 +56386,16 @@
         <v>8.27</v>
       </c>
       <c r="M1084">
-        <v>5.8</v>
+        <v>5.77</v>
       </c>
       <c r="N1084">
-        <v>9.16</v>
+        <v>9.07</v>
       </c>
       <c r="O1084">
         <v>1</v>
       </c>
       <c r="P1084" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="1085" spans="1:16">
@@ -56412,10 +56409,10 @@
         <v>5.853864517773994</v>
       </c>
       <c r="D1085" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E1085">
-        <v>6.5059117808881</v>
+        <v>6.429639823400748</v>
       </c>
       <c r="F1085">
         <v>-1</v>
@@ -56424,10 +56421,10 @@
         <v>0.01068613548222601</v>
       </c>
       <c r="H1085">
-        <v>0.0118140882191119</v>
+        <v>0.01171036017659925</v>
       </c>
       <c r="I1085">
-        <v>-0.6520472631141061</v>
+        <v>-0.5757753056267543</v>
       </c>
       <c r="J1085">
         <v>0.4576014170882586</v>
@@ -56439,16 +56436,16 @@
         <v>8.27</v>
       </c>
       <c r="M1085">
-        <v>5.8</v>
+        <v>5.77</v>
       </c>
       <c r="N1085">
-        <v>9.16</v>
+        <v>9.07</v>
       </c>
       <c r="O1085">
         <v>1</v>
       </c>
       <c r="P1085" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="1086" spans="1:16">
@@ -56462,10 +56459,10 @@
         <v>5.996957847030043</v>
       </c>
       <c r="D1086" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E1086">
-        <v>6.663097634995124</v>
+        <v>6.586012647227908</v>
       </c>
       <c r="F1086">
         <v>-1</v>
@@ -56474,10 +56471,10 @@
         <v>0.01054304215296996</v>
       </c>
       <c r="H1086">
-        <v>0.01165690236500488</v>
+        <v>0.01155398735277209</v>
       </c>
       <c r="I1086">
-        <v>-0.666139787965081</v>
+        <v>-0.5890548001978653</v>
       </c>
       <c r="J1086">
         <v>0.4305004077594615</v>
@@ -56489,10 +56486,10 @@
         <v>8.27</v>
       </c>
       <c r="M1086">
-        <v>5.8</v>
+        <v>5.77</v>
       </c>
       <c r="N1086">
-        <v>9.16</v>
+        <v>9.07</v>
       </c>
       <c r="O1086">
         <v>1</v>
@@ -56512,10 +56509,10 @@
         <v>6.332482120319733</v>
       </c>
       <c r="D1087" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E1087">
-        <v>7.031665965502739</v>
+        <v>6.952674589819104</v>
       </c>
       <c r="F1087">
         <v>-1</v>
@@ -56524,10 +56521,10 @@
         <v>0.01020751787968027</v>
       </c>
       <c r="H1087">
-        <v>0.01128833403449726</v>
+        <v>0.0111873254101809</v>
       </c>
       <c r="I1087">
-        <v>-0.6991838451830059</v>
+        <v>-0.6201924694993703</v>
       </c>
       <c r="J1087">
         <v>0.3669541438788382</v>
@@ -56539,10 +56536,10 @@
         <v>8.27</v>
       </c>
       <c r="M1087">
-        <v>5.8</v>
+        <v>5.77</v>
       </c>
       <c r="N1087">
-        <v>9.16</v>
+        <v>9.07</v>
       </c>
       <c r="O1087">
         <v>1</v>
@@ -56562,10 +56559,10 @@
         <v>6.538088893528732</v>
       </c>
       <c r="D1088" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E1088">
-        <v>7.257521890618683</v>
+        <v>7.177362294632725</v>
       </c>
       <c r="F1088">
         <v>-1</v>
@@ -56574,10 +56571,10 @@
         <v>0.01000191110647127</v>
       </c>
       <c r="H1088">
-        <v>0.01106247810938132</v>
+        <v>0.01096263770536728</v>
       </c>
       <c r="I1088">
-        <v>-0.7194329970899513</v>
+        <v>-0.6392734011039929</v>
       </c>
       <c r="J1088">
         <v>0.3280134671347097</v>
@@ -56589,16 +56586,16 @@
         <v>8.27</v>
       </c>
       <c r="M1088">
-        <v>5.8</v>
+        <v>5.77</v>
       </c>
       <c r="N1088">
-        <v>9.16</v>
+        <v>9.07</v>
       </c>
       <c r="O1088">
         <v>1</v>
       </c>
       <c r="P1088" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="1089" spans="1:16">
@@ -56612,10 +56609,10 @@
         <v>6.439291964996025</v>
       </c>
       <c r="D1089" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E1089">
-        <v>7.148994961548665</v>
+        <v>7.069396711747551</v>
       </c>
       <c r="F1089">
         <v>-1</v>
@@ -56624,10 +56621,10 @@
         <v>0.01010070803500397</v>
       </c>
       <c r="H1089">
-        <v>0.01117100503845134</v>
+        <v>0.01107060328825245</v>
       </c>
       <c r="I1089">
-        <v>-0.7097029965526396</v>
+        <v>-0.6301047467515257</v>
       </c>
       <c r="J1089">
         <v>0.3467250066295405</v>
@@ -56639,10 +56636,10 @@
         <v>8.27</v>
       </c>
       <c r="M1089">
-        <v>5.8</v>
+        <v>5.77</v>
       </c>
       <c r="N1089">
-        <v>9.16</v>
+        <v>9.07</v>
       </c>
       <c r="O1089">
         <v>1</v>
@@ -56662,10 +56659,10 @@
         <v>6.095915492957749</v>
       </c>
       <c r="D1090" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E1090">
-        <v>6.771801109688437</v>
+        <v>6.694153862569359</v>
       </c>
       <c r="F1090">
         <v>-1</v>
@@ -56674,10 +56671,10 @@
         <v>0.01044408450704225</v>
       </c>
       <c r="H1090">
-        <v>0.01154819889031156</v>
+        <v>0.01144584613743064</v>
       </c>
       <c r="I1090">
-        <v>-0.6758856167306879</v>
+        <v>-0.59823836961161</v>
       </c>
       <c r="J1090">
         <v>0.4117584293640626</v>
@@ -56689,16 +56686,16 @@
         <v>8.27</v>
       </c>
       <c r="M1090">
-        <v>5.8</v>
+        <v>5.77</v>
       </c>
       <c r="N1090">
-        <v>9.16</v>
+        <v>9.07</v>
       </c>
       <c r="O1090">
         <v>1</v>
       </c>
       <c r="P1090" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="1091" spans="1:16">
@@ -56712,10 +56709,10 @@
         <v>5.888028169014084</v>
       </c>
       <c r="D1091" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E1091">
-        <v>6.543440034144259</v>
+        <v>6.466973965002135</v>
       </c>
       <c r="F1091">
         <v>-1</v>
@@ -56724,10 +56721,10 @@
         <v>0.01065197183098592</v>
       </c>
       <c r="H1091">
-        <v>0.01177655996585574</v>
+        <v>0.01167302603499787</v>
       </c>
       <c r="I1091">
-        <v>-0.6554118651301755</v>
+        <v>-0.5789457959880506</v>
       </c>
       <c r="J1091">
         <v>0.4511310285958173</v>
@@ -56739,16 +56736,16 @@
         <v>8.27</v>
       </c>
       <c r="M1091">
-        <v>5.8</v>
+        <v>5.77</v>
       </c>
       <c r="N1091">
-        <v>9.16</v>
+        <v>9.07</v>
       </c>
       <c r="O1091">
         <v>1</v>
       </c>
       <c r="P1091" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="1092" spans="1:16">
@@ -56762,10 +56759,10 @@
         <v>6.529026547184721</v>
       </c>
       <c r="D1092" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E1092">
-        <v>7.247567040468065</v>
+        <v>7.167458935086334</v>
       </c>
       <c r="F1092">
         <v>-1</v>
@@ -56774,10 +56771,10 @@
         <v>0.01001097345281528</v>
       </c>
       <c r="H1092">
-        <v>0.01107243295953194</v>
+        <v>0.01097254106491367</v>
       </c>
       <c r="I1092">
-        <v>-0.7185404932833439</v>
+        <v>-0.6384323879016129</v>
       </c>
       <c r="J1092">
         <v>0.3297298206089543</v>
@@ -56789,16 +56786,16 @@
         <v>8.27</v>
       </c>
       <c r="M1092">
-        <v>5.8</v>
+        <v>5.77</v>
       </c>
       <c r="N1092">
-        <v>9.16</v>
+        <v>9.07</v>
       </c>
       <c r="O1092">
         <v>1</v>
       </c>
       <c r="P1092" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3288" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3285" uniqueCount="608">
   <si>
     <t>trade_time</t>
   </si>
@@ -1426,7 +1426,7 @@
     <t>2021-09-09</t>
   </si>
   <si>
-    <t>2021-09-13</t>
+    <t>2021-09-14</t>
   </si>
   <si>
     <t>2016-01-29</t>
@@ -1838,9 +1838,6 @@
   </si>
   <si>
     <t>2021-07-06</t>
-  </si>
-  <si>
-    <t>2021-07-08</t>
   </si>
 </sst>
 </file>
@@ -2198,7 +2195,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1092"/>
+  <dimension ref="A1:P1091"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -56209,10 +56206,10 @@
         <v>5.512060928235529</v>
       </c>
       <c r="D1081" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E1081">
-        <v>6.130445716622362</v>
+        <v>5.791923430791244</v>
       </c>
       <c r="F1081">
         <v>-1</v>
@@ -56221,10 +56218,10 @@
         <v>0.01102793907176447</v>
       </c>
       <c r="H1081">
-        <v>0.01218955428337764</v>
+        <v>0.01154807656920876</v>
       </c>
       <c r="I1081">
-        <v>-0.618384788386833</v>
+        <v>-0.2798625025557149</v>
       </c>
       <c r="J1081">
         <v>0.5223369454099376</v>
@@ -56236,10 +56233,10 @@
         <v>8.27</v>
       </c>
       <c r="M1081">
-        <v>5.8</v>
+        <v>5.51</v>
       </c>
       <c r="N1081">
-        <v>9.16</v>
+        <v>8.67</v>
       </c>
       <c r="O1081">
         <v>1</v>
@@ -56259,10 +56256,10 @@
         <v>5.044404491169697</v>
       </c>
       <c r="D1082" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E1082">
-        <v>5.616732206209138</v>
+        <v>5.30389559589868</v>
       </c>
       <c r="F1082">
         <v>-1</v>
@@ -56271,10 +56268,10 @@
         <v>0.0114955955088303</v>
       </c>
       <c r="H1082">
-        <v>0.01270326779379086</v>
+        <v>0.01203610440410132</v>
       </c>
       <c r="I1082">
-        <v>-0.5723277150394406</v>
+        <v>-0.2594911047289834</v>
       </c>
       <c r="J1082">
         <v>0.6109082403087693</v>
@@ -56286,10 +56283,10 @@
         <v>8.27</v>
       </c>
       <c r="M1082">
-        <v>5.8</v>
+        <v>5.51</v>
       </c>
       <c r="N1082">
-        <v>9.16</v>
+        <v>8.67</v>
       </c>
       <c r="O1082">
         <v>1</v>
@@ -56312,7 +56309,7 @@
         <v>470</v>
       </c>
       <c r="E1083">
-        <v>5.981037245013375</v>
+        <v>5.72022794107863</v>
       </c>
       <c r="F1083">
         <v>-1</v>
@@ -56321,10 +56318,10 @@
         <v>0.01109664182778672</v>
       </c>
       <c r="H1083">
-        <v>0.01215896275498663</v>
+        <v>0.01161977205892137</v>
       </c>
       <c r="I1083">
-        <v>-0.5376790728000964</v>
+        <v>-0.2768697688653514</v>
       </c>
       <c r="J1083">
         <v>0.5353488310202125</v>
@@ -56336,10 +56333,10 @@
         <v>8.27</v>
       </c>
       <c r="M1083">
-        <v>5.77</v>
+        <v>5.51</v>
       </c>
       <c r="N1083">
-        <v>9.07</v>
+        <v>8.67</v>
       </c>
       <c r="O1083">
         <v>1</v>
@@ -56362,7 +56359,7 @@
         <v>470</v>
       </c>
       <c r="E1084">
-        <v>6.280109890109895</v>
+        <v>6.005824175824179</v>
       </c>
       <c r="F1084">
         <v>-1</v>
@@ -56371,10 +56368,10 @@
         <v>0.01082296703296703</v>
       </c>
       <c r="H1084">
-        <v>0.01185989010989011</v>
+        <v>0.01133417582417582</v>
       </c>
       <c r="I1084">
-        <v>-0.5630769230769248</v>
+        <v>-0.288791208791209</v>
       </c>
       <c r="J1084">
         <v>0.4835164835164829</v>
@@ -56386,10 +56383,10 @@
         <v>8.27</v>
       </c>
       <c r="M1084">
-        <v>5.77</v>
+        <v>5.51</v>
       </c>
       <c r="N1084">
-        <v>9.07</v>
+        <v>8.67</v>
       </c>
       <c r="O1084">
         <v>1</v>
@@ -56412,7 +56409,7 @@
         <v>470</v>
       </c>
       <c r="E1085">
-        <v>6.429639823400748</v>
+        <v>6.148616191843695</v>
       </c>
       <c r="F1085">
         <v>-1</v>
@@ -56421,10 +56418,10 @@
         <v>0.01068613548222601</v>
       </c>
       <c r="H1085">
-        <v>0.01171036017659925</v>
+        <v>0.0111913838081563</v>
       </c>
       <c r="I1085">
-        <v>-0.5757753056267543</v>
+        <v>-0.2947516740697012</v>
       </c>
       <c r="J1085">
         <v>0.4576014170882586</v>
@@ -56436,10 +56433,10 @@
         <v>8.27</v>
       </c>
       <c r="M1085">
-        <v>5.77</v>
+        <v>5.51</v>
       </c>
       <c r="N1085">
-        <v>9.07</v>
+        <v>8.67</v>
       </c>
       <c r="O1085">
         <v>1</v>
@@ -56462,7 +56459,7 @@
         <v>470</v>
       </c>
       <c r="E1086">
-        <v>6.586012647227908</v>
+        <v>6.297942753245367</v>
       </c>
       <c r="F1086">
         <v>-1</v>
@@ -56471,10 +56468,10 @@
         <v>0.01054304215296996</v>
       </c>
       <c r="H1086">
-        <v>0.01155398735277209</v>
+        <v>0.01104205724675463</v>
       </c>
       <c r="I1086">
-        <v>-0.5890548001978653</v>
+        <v>-0.3009849062153247</v>
       </c>
       <c r="J1086">
         <v>0.4305004077594615</v>
@@ -56486,10 +56483,10 @@
         <v>8.27</v>
       </c>
       <c r="M1086">
-        <v>5.77</v>
+        <v>5.51</v>
       </c>
       <c r="N1086">
-        <v>9.07</v>
+        <v>8.67</v>
       </c>
       <c r="O1086">
         <v>1</v>
@@ -56512,7 +56509,7 @@
         <v>470</v>
       </c>
       <c r="E1087">
-        <v>6.952674589819104</v>
+        <v>6.648082667227602</v>
       </c>
       <c r="F1087">
         <v>-1</v>
@@ -56521,10 +56518,10 @@
         <v>0.01020751787968027</v>
       </c>
       <c r="H1087">
-        <v>0.0111873254101809</v>
+        <v>0.0106919173327724</v>
       </c>
       <c r="I1087">
-        <v>-0.6201924694993703</v>
+        <v>-0.3156005469078682</v>
       </c>
       <c r="J1087">
         <v>0.3669541438788382</v>
@@ -56536,10 +56533,10 @@
         <v>8.27</v>
       </c>
       <c r="M1087">
-        <v>5.77</v>
+        <v>5.51</v>
       </c>
       <c r="N1087">
-        <v>9.07</v>
+        <v>8.67</v>
       </c>
       <c r="O1087">
         <v>1</v>
@@ -56562,7 +56559,7 @@
         <v>470</v>
       </c>
       <c r="E1088">
-        <v>7.177362294632725</v>
+        <v>6.862645796087749</v>
       </c>
       <c r="F1088">
         <v>-1</v>
@@ -56571,10 +56568,10 @@
         <v>0.01000191110647127</v>
       </c>
       <c r="H1088">
-        <v>0.01096263770536728</v>
+        <v>0.01047735420391225</v>
       </c>
       <c r="I1088">
-        <v>-0.6392734011039929</v>
+        <v>-0.3245569025590171</v>
       </c>
       <c r="J1088">
         <v>0.3280134671347097</v>
@@ -56586,10 +56583,10 @@
         <v>8.27</v>
       </c>
       <c r="M1088">
-        <v>5.77</v>
+        <v>5.51</v>
       </c>
       <c r="N1088">
-        <v>9.07</v>
+        <v>8.67</v>
       </c>
       <c r="O1088">
         <v>1</v>
@@ -56612,7 +56609,7 @@
         <v>470</v>
       </c>
       <c r="E1089">
-        <v>7.069396711747551</v>
+        <v>6.759545213471232</v>
       </c>
       <c r="F1089">
         <v>-1</v>
@@ -56621,10 +56618,10 @@
         <v>0.01010070803500397</v>
       </c>
       <c r="H1089">
-        <v>0.01107060328825245</v>
+        <v>0.01058045478652877</v>
       </c>
       <c r="I1089">
-        <v>-0.6301047467515257</v>
+        <v>-0.3202532484752068</v>
       </c>
       <c r="J1089">
         <v>0.3467250066295405</v>
@@ -56636,10 +56633,10 @@
         <v>8.27</v>
       </c>
       <c r="M1089">
-        <v>5.77</v>
+        <v>5.51</v>
       </c>
       <c r="N1089">
-        <v>9.07</v>
+        <v>8.67</v>
       </c>
       <c r="O1089">
         <v>1</v>
@@ -56662,7 +56659,7 @@
         <v>470</v>
       </c>
       <c r="E1090">
-        <v>6.694153862569359</v>
+        <v>6.401211054204015</v>
       </c>
       <c r="F1090">
         <v>-1</v>
@@ -56671,10 +56668,10 @@
         <v>0.01044408450704225</v>
       </c>
       <c r="H1090">
-        <v>0.01144584613743064</v>
+        <v>0.01093878894579598</v>
       </c>
       <c r="I1090">
-        <v>-0.59823836961161</v>
+        <v>-0.3052955612462664</v>
       </c>
       <c r="J1090">
         <v>0.4117584293640626</v>
@@ -56686,10 +56683,10 @@
         <v>8.27</v>
       </c>
       <c r="M1090">
-        <v>5.77</v>
+        <v>5.51</v>
       </c>
       <c r="N1090">
-        <v>9.07</v>
+        <v>8.67</v>
       </c>
       <c r="O1090">
         <v>1</v>
@@ -56712,7 +56709,7 @@
         <v>470</v>
       </c>
       <c r="E1091">
-        <v>6.466973965002135</v>
+        <v>6.184268032437046</v>
       </c>
       <c r="F1091">
         <v>-1</v>
@@ -56721,10 +56718,10 @@
         <v>0.01065197183098592</v>
       </c>
       <c r="H1091">
-        <v>0.01167302603499787</v>
+        <v>0.01115573196756295</v>
       </c>
       <c r="I1091">
-        <v>-0.5789457959880506</v>
+        <v>-0.2962398634229624</v>
       </c>
       <c r="J1091">
         <v>0.4511310285958173</v>
@@ -56736,66 +56733,16 @@
         <v>8.27</v>
       </c>
       <c r="M1091">
-        <v>5.77</v>
+        <v>5.51</v>
       </c>
       <c r="N1091">
-        <v>9.07</v>
+        <v>8.67</v>
       </c>
       <c r="O1091">
         <v>1</v>
       </c>
       <c r="P1091" t="s">
         <v>607</v>
-      </c>
-    </row>
-    <row r="1092" spans="1:16">
-      <c r="A1092" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1092" t="s">
-        <v>297</v>
-      </c>
-      <c r="C1092">
-        <v>6.529026547184721</v>
-      </c>
-      <c r="D1092" t="s">
-        <v>470</v>
-      </c>
-      <c r="E1092">
-        <v>7.167458935086334</v>
-      </c>
-      <c r="F1092">
-        <v>-1</v>
-      </c>
-      <c r="G1092">
-        <v>0.01001097345281528</v>
-      </c>
-      <c r="H1092">
-        <v>0.01097254106491367</v>
-      </c>
-      <c r="I1092">
-        <v>-0.6384323879016129</v>
-      </c>
-      <c r="J1092">
-        <v>0.3297298206089543</v>
-      </c>
-      <c r="K1092">
-        <v>5.28</v>
-      </c>
-      <c r="L1092">
-        <v>8.27</v>
-      </c>
-      <c r="M1092">
-        <v>5.77</v>
-      </c>
-      <c r="N1092">
-        <v>9.07</v>
-      </c>
-      <c r="O1092">
-        <v>1</v>
-      </c>
-      <c r="P1092" t="s">
-        <v>608</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3285" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3279" uniqueCount="606">
   <si>
     <t>trade_time</t>
   </si>
@@ -1426,7 +1426,7 @@
     <t>2021-09-09</t>
   </si>
   <si>
-    <t>2021-09-14</t>
+    <t>2021-09-15</t>
   </si>
   <si>
     <t>2016-01-29</t>
@@ -1832,12 +1832,6 @@
   </si>
   <si>
     <t>2021-06-30</t>
-  </si>
-  <si>
-    <t>2021-07-05</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
   </si>
 </sst>
 </file>
@@ -2195,7 +2189,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1091"/>
+  <dimension ref="A1:P1089"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -56006,10 +56000,10 @@
         <v>6.759036860879887</v>
       </c>
       <c r="D1077" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E1077">
-        <v>7.500229885057452</v>
+        <v>7.037526753864428</v>
       </c>
       <c r="F1077">
         <v>-1</v>
@@ -56018,10 +56012,10 @@
         <v>0.009780963139120113</v>
       </c>
       <c r="H1077">
-        <v>0.01081977011494255</v>
+        <v>0.01016247324613557</v>
       </c>
       <c r="I1077">
-        <v>-0.7411930241775657</v>
+        <v>-0.2784898929845419</v>
       </c>
       <c r="J1077">
         <v>0.2861672611969911</v>
@@ -56033,10 +56027,10 @@
         <v>8.27</v>
       </c>
       <c r="M1077">
-        <v>5.8</v>
+        <v>5.46</v>
       </c>
       <c r="N1077">
-        <v>9.16</v>
+        <v>8.6</v>
       </c>
       <c r="O1077">
         <v>1</v>
@@ -56056,10 +56050,10 @@
         <v>6.737244367417659</v>
       </c>
       <c r="D1078" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E1078">
-        <v>7.476291161178489</v>
+        <v>7.014991334488715</v>
       </c>
       <c r="F1078">
         <v>-1</v>
@@ -56068,10 +56062,10 @@
         <v>0.00980275563258234</v>
       </c>
       <c r="H1078">
-        <v>0.01084370883882151</v>
+        <v>0.01018500866551128</v>
       </c>
       <c r="I1078">
-        <v>-0.7390467937608305</v>
+        <v>-0.2777469670710566</v>
       </c>
       <c r="J1078">
         <v>0.2902946273830191</v>
@@ -56083,10 +56077,10 @@
         <v>8.27</v>
       </c>
       <c r="M1078">
-        <v>5.8</v>
+        <v>5.46</v>
       </c>
       <c r="N1078">
-        <v>9.16</v>
+        <v>8.6</v>
       </c>
       <c r="O1078">
         <v>1</v>
@@ -56106,10 +56100,10 @@
         <v>6.024441462215994</v>
       </c>
       <c r="D1079" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E1079">
-        <v>6.69328796985848</v>
+        <v>6.277888330246086</v>
       </c>
       <c r="F1079">
         <v>-1</v>
@@ -56118,10 +56112,10 @@
         <v>0.01051555853778401</v>
       </c>
       <c r="H1079">
-        <v>0.01162671203014152</v>
+        <v>0.01092211166975391</v>
       </c>
       <c r="I1079">
-        <v>-0.6688465076424857</v>
+        <v>-0.2534468680300916</v>
       </c>
       <c r="J1079">
         <v>0.4252951776106071</v>
@@ -56133,10 +56127,10 @@
         <v>8.27</v>
       </c>
       <c r="M1079">
-        <v>5.8</v>
+        <v>5.46</v>
       </c>
       <c r="N1079">
-        <v>9.16</v>
+        <v>8.6</v>
       </c>
       <c r="O1079">
         <v>1</v>
@@ -56156,10 +56150,10 @@
         <v>5.743098670470165</v>
       </c>
       <c r="D1080" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E1080">
-        <v>6.384237175895258</v>
+        <v>5.986954306963467</v>
       </c>
       <c r="F1080">
         <v>-1</v>
@@ -56168,10 +56162,10 @@
         <v>0.01079690132952984</v>
       </c>
       <c r="H1080">
-        <v>0.01193576282410474</v>
+        <v>0.01121304569303653</v>
       </c>
       <c r="I1080">
-        <v>-0.6411385054250927</v>
+        <v>-0.2438556364933016</v>
       </c>
       <c r="J1080">
         <v>0.4785797972594382</v>
@@ -56183,10 +56177,10 @@
         <v>8.27</v>
       </c>
       <c r="M1080">
-        <v>5.8</v>
+        <v>5.46</v>
       </c>
       <c r="N1080">
-        <v>9.16</v>
+        <v>8.6</v>
       </c>
       <c r="O1080">
         <v>1</v>
@@ -56209,7 +56203,7 @@
         <v>470</v>
       </c>
       <c r="E1081">
-        <v>5.791923430791244</v>
+        <v>5.74804027806174</v>
       </c>
       <c r="F1081">
         <v>-1</v>
@@ -56218,10 +56212,10 @@
         <v>0.01102793907176447</v>
       </c>
       <c r="H1081">
-        <v>0.01154807656920876</v>
+        <v>0.01145195972193826</v>
       </c>
       <c r="I1081">
-        <v>-0.2798625025557149</v>
+        <v>-0.235979349826211</v>
       </c>
       <c r="J1081">
         <v>0.5223369454099376</v>
@@ -56233,10 +56227,10 @@
         <v>8.27</v>
       </c>
       <c r="M1081">
-        <v>5.51</v>
+        <v>5.46</v>
       </c>
       <c r="N1081">
-        <v>8.67</v>
+        <v>8.6</v>
       </c>
       <c r="O1081">
         <v>1</v>
@@ -56259,7 +56253,7 @@
         <v>470</v>
       </c>
       <c r="E1082">
-        <v>5.30389559589868</v>
+        <v>5.264441007914119</v>
       </c>
       <c r="F1082">
         <v>-1</v>
@@ -56268,10 +56262,10 @@
         <v>0.0114955955088303</v>
       </c>
       <c r="H1082">
-        <v>0.01203610440410132</v>
+        <v>0.01193555899208588</v>
       </c>
       <c r="I1082">
-        <v>-0.2594911047289834</v>
+        <v>-0.2200365167444218</v>
       </c>
       <c r="J1082">
         <v>0.6109082403087693</v>
@@ -56283,10 +56277,10 @@
         <v>8.27</v>
       </c>
       <c r="M1082">
-        <v>5.51</v>
+        <v>5.46</v>
       </c>
       <c r="N1082">
-        <v>8.67</v>
+        <v>8.6</v>
       </c>
       <c r="O1082">
         <v>1</v>
@@ -56309,7 +56303,7 @@
         <v>470</v>
       </c>
       <c r="E1083">
-        <v>5.72022794107863</v>
+        <v>5.67699538262964</v>
       </c>
       <c r="F1083">
         <v>-1</v>
@@ -56318,10 +56312,10 @@
         <v>0.01109664182778672</v>
       </c>
       <c r="H1083">
-        <v>0.01161977205892137</v>
+        <v>0.01152300461737036</v>
       </c>
       <c r="I1083">
-        <v>-0.2768697688653514</v>
+        <v>-0.2336372104163615</v>
       </c>
       <c r="J1083">
         <v>0.5353488310202125</v>
@@ -56333,10 +56327,10 @@
         <v>8.27</v>
       </c>
       <c r="M1083">
-        <v>5.51</v>
+        <v>5.46</v>
       </c>
       <c r="N1083">
-        <v>8.67</v>
+        <v>8.6</v>
       </c>
       <c r="O1083">
         <v>1</v>
@@ -56359,7 +56353,7 @@
         <v>470</v>
       </c>
       <c r="E1084">
-        <v>6.005824175824179</v>
+        <v>5.960000000000003</v>
       </c>
       <c r="F1084">
         <v>-1</v>
@@ -56368,10 +56362,10 @@
         <v>0.01082296703296703</v>
       </c>
       <c r="H1084">
-        <v>0.01133417582417582</v>
+        <v>0.01124</v>
       </c>
       <c r="I1084">
-        <v>-0.288791208791209</v>
+        <v>-0.2429670329670328</v>
       </c>
       <c r="J1084">
         <v>0.4835164835164829</v>
@@ -56383,10 +56377,10 @@
         <v>8.27</v>
       </c>
       <c r="M1084">
-        <v>5.51</v>
+        <v>5.46</v>
       </c>
       <c r="N1084">
-        <v>8.67</v>
+        <v>8.6</v>
       </c>
       <c r="O1084">
         <v>1</v>
@@ -56409,7 +56403,7 @@
         <v>470</v>
       </c>
       <c r="E1085">
-        <v>6.148616191843695</v>
+        <v>6.101496262698108</v>
       </c>
       <c r="F1085">
         <v>-1</v>
@@ -56418,10 +56412,10 @@
         <v>0.01068613548222601</v>
       </c>
       <c r="H1085">
-        <v>0.0111913838081563</v>
+        <v>0.01109850373730189</v>
       </c>
       <c r="I1085">
-        <v>-0.2947516740697012</v>
+        <v>-0.2476317449241137</v>
       </c>
       <c r="J1085">
         <v>0.4576014170882586</v>
@@ -56433,10 +56427,10 @@
         <v>8.27</v>
       </c>
       <c r="M1085">
-        <v>5.51</v>
+        <v>5.46</v>
       </c>
       <c r="N1085">
-        <v>8.67</v>
+        <v>8.6</v>
       </c>
       <c r="O1085">
         <v>1</v>
@@ -56459,7 +56453,7 @@
         <v>470</v>
       </c>
       <c r="E1086">
-        <v>6.297942753245367</v>
+        <v>6.24946777363334</v>
       </c>
       <c r="F1086">
         <v>-1</v>
@@ -56468,10 +56462,10 @@
         <v>0.01054304215296996</v>
       </c>
       <c r="H1086">
-        <v>0.01104205724675463</v>
+        <v>0.01095053222636666</v>
       </c>
       <c r="I1086">
-        <v>-0.3009849062153247</v>
+        <v>-0.2525099266032971</v>
       </c>
       <c r="J1086">
         <v>0.4305004077594615</v>
@@ -56483,10 +56477,10 @@
         <v>8.27</v>
       </c>
       <c r="M1086">
-        <v>5.51</v>
+        <v>5.46</v>
       </c>
       <c r="N1086">
-        <v>8.67</v>
+        <v>8.6</v>
       </c>
       <c r="O1086">
         <v>1</v>
@@ -56509,7 +56503,7 @@
         <v>470</v>
       </c>
       <c r="E1087">
-        <v>6.648082667227602</v>
+        <v>6.596430374421543</v>
       </c>
       <c r="F1087">
         <v>-1</v>
@@ -56518,10 +56512,10 @@
         <v>0.01020751787968027</v>
       </c>
       <c r="H1087">
-        <v>0.0106919173327724</v>
+        <v>0.01060356962557846</v>
       </c>
       <c r="I1087">
-        <v>-0.3156005469078682</v>
+        <v>-0.2639482541018099</v>
       </c>
       <c r="J1087">
         <v>0.3669541438788382</v>
@@ -56533,10 +56527,10 @@
         <v>8.27</v>
       </c>
       <c r="M1087">
-        <v>5.51</v>
+        <v>5.46</v>
       </c>
       <c r="N1087">
-        <v>8.67</v>
+        <v>8.6</v>
       </c>
       <c r="O1087">
         <v>1</v>
@@ -56559,7 +56553,7 @@
         <v>470</v>
       </c>
       <c r="E1088">
-        <v>6.862645796087749</v>
+        <v>6.809046469444485</v>
       </c>
       <c r="F1088">
         <v>-1</v>
@@ -56568,10 +56562,10 @@
         <v>0.01000191110647127</v>
       </c>
       <c r="H1088">
-        <v>0.01047735420391225</v>
+        <v>0.01039095353055551</v>
       </c>
       <c r="I1088">
-        <v>-0.3245569025590171</v>
+        <v>-0.2709575759157525</v>
       </c>
       <c r="J1088">
         <v>0.3280134671347097</v>
@@ -56583,10 +56577,10 @@
         <v>8.27</v>
       </c>
       <c r="M1088">
-        <v>5.51</v>
+        <v>5.46</v>
       </c>
       <c r="N1088">
-        <v>8.67</v>
+        <v>8.6</v>
       </c>
       <c r="O1088">
         <v>1</v>
@@ -56609,7 +56603,7 @@
         <v>470</v>
       </c>
       <c r="E1089">
-        <v>6.759545213471232</v>
+        <v>6.706881463802708</v>
       </c>
       <c r="F1089">
         <v>-1</v>
@@ -56618,10 +56612,10 @@
         <v>0.01010070803500397</v>
       </c>
       <c r="H1089">
-        <v>0.01058045478652877</v>
+        <v>0.01049311853619729</v>
       </c>
       <c r="I1089">
-        <v>-0.3202532484752068</v>
+        <v>-0.2675894988066831</v>
       </c>
       <c r="J1089">
         <v>0.3467250066295405</v>
@@ -56633,116 +56627,16 @@
         <v>8.27</v>
       </c>
       <c r="M1089">
-        <v>5.51</v>
+        <v>5.46</v>
       </c>
       <c r="N1089">
-        <v>8.67</v>
+        <v>8.6</v>
       </c>
       <c r="O1089">
         <v>1</v>
       </c>
       <c r="P1089" t="s">
         <v>295</v>
-      </c>
-    </row>
-    <row r="1090" spans="1:16">
-      <c r="A1090" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1090" t="s">
-        <v>297</v>
-      </c>
-      <c r="C1090">
-        <v>6.095915492957749</v>
-      </c>
-      <c r="D1090" t="s">
-        <v>470</v>
-      </c>
-      <c r="E1090">
-        <v>6.401211054204015</v>
-      </c>
-      <c r="F1090">
-        <v>-1</v>
-      </c>
-      <c r="G1090">
-        <v>0.01044408450704225</v>
-      </c>
-      <c r="H1090">
-        <v>0.01093878894579598</v>
-      </c>
-      <c r="I1090">
-        <v>-0.3052955612462664</v>
-      </c>
-      <c r="J1090">
-        <v>0.4117584293640626</v>
-      </c>
-      <c r="K1090">
-        <v>5.28</v>
-      </c>
-      <c r="L1090">
-        <v>8.27</v>
-      </c>
-      <c r="M1090">
-        <v>5.51</v>
-      </c>
-      <c r="N1090">
-        <v>8.67</v>
-      </c>
-      <c r="O1090">
-        <v>1</v>
-      </c>
-      <c r="P1090" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="1091" spans="1:16">
-      <c r="A1091" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1091" t="s">
-        <v>297</v>
-      </c>
-      <c r="C1091">
-        <v>5.888028169014084</v>
-      </c>
-      <c r="D1091" t="s">
-        <v>470</v>
-      </c>
-      <c r="E1091">
-        <v>6.184268032437046</v>
-      </c>
-      <c r="F1091">
-        <v>-1</v>
-      </c>
-      <c r="G1091">
-        <v>0.01065197183098592</v>
-      </c>
-      <c r="H1091">
-        <v>0.01115573196756295</v>
-      </c>
-      <c r="I1091">
-        <v>-0.2962398634229624</v>
-      </c>
-      <c r="J1091">
-        <v>0.4511310285958173</v>
-      </c>
-      <c r="K1091">
-        <v>5.28</v>
-      </c>
-      <c r="L1091">
-        <v>8.27</v>
-      </c>
-      <c r="M1091">
-        <v>5.51</v>
-      </c>
-      <c r="N1091">
-        <v>8.67</v>
-      </c>
-      <c r="O1091">
-        <v>1</v>
-      </c>
-      <c r="P1091" t="s">
-        <v>607</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3273" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3261" uniqueCount="605">
   <si>
     <t>trade_time</t>
   </si>
@@ -1429,6 +1429,9 @@
     <t>2021-09-09</t>
   </si>
   <si>
+    <t>2021-09-17</t>
+  </si>
+  <si>
     <t>2021-09-16</t>
   </si>
   <si>
@@ -1823,15 +1826,6 @@
   </si>
   <si>
     <t>2021-06-18</t>
-  </si>
-  <si>
-    <t>2021-06-23</t>
-  </si>
-  <si>
-    <t>2021-06-24</t>
-  </si>
-  <si>
-    <t>2021-06-25</t>
   </si>
   <si>
     <t>2021-09-14</t>
@@ -2192,7 +2186,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1087"/>
+  <dimension ref="A1:P1083"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2289,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2339,7 +2333,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2389,7 +2383,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2439,7 +2433,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2489,7 +2483,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2539,7 +2533,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2589,7 +2583,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2639,7 +2633,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2689,7 +2683,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2739,7 +2733,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2789,7 +2783,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2839,7 +2833,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2889,7 +2883,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2939,7 +2933,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2989,7 +2983,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -3039,7 +3033,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -3089,7 +3083,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -3139,7 +3133,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -3189,7 +3183,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -3239,7 +3233,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -3289,7 +3283,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3339,7 +3333,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3389,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3439,7 +3433,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3489,7 +3483,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3539,7 +3533,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3589,7 +3583,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3639,7 +3633,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3689,7 +3683,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3739,7 +3733,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3789,7 +3783,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3839,7 +3833,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3889,7 +3883,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3939,7 +3933,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3989,7 +3983,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -4039,7 +4033,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -4089,7 +4083,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -4139,7 +4133,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -4189,7 +4183,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -4239,7 +4233,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -4289,7 +4283,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4339,7 +4333,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4389,7 +4383,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4439,7 +4433,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4489,7 +4483,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4539,7 +4533,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4589,7 +4583,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4639,7 +4633,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4689,7 +4683,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4739,7 +4733,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4789,7 +4783,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4839,7 +4833,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4889,7 +4883,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -5789,7 +5783,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5839,7 +5833,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5889,7 +5883,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5939,7 +5933,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5989,7 +5983,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -6039,7 +6033,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -6089,7 +6083,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -6139,7 +6133,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -6189,7 +6183,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -6239,7 +6233,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -6289,7 +6283,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -6339,7 +6333,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -6389,7 +6383,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6439,7 +6433,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6489,7 +6483,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6539,7 +6533,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6589,7 +6583,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6639,7 +6633,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6689,7 +6683,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6739,7 +6733,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -7339,7 +7333,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7389,7 +7383,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7439,7 +7433,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7489,7 +7483,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7539,7 +7533,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7589,7 +7583,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7639,7 +7633,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7689,7 +7683,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7739,7 +7733,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7789,7 +7783,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7839,7 +7833,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7889,7 +7883,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7939,7 +7933,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7989,7 +7983,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -8039,7 +8033,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -8089,7 +8083,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -8139,7 +8133,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -8189,7 +8183,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -8239,7 +8233,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -8289,7 +8283,7 @@
         <v>1</v>
       </c>
       <c r="P122" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -8339,7 +8333,7 @@
         <v>1</v>
       </c>
       <c r="P123" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -8689,7 +8683,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8739,7 +8733,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8789,7 +8783,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8839,7 +8833,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8889,7 +8883,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8939,7 +8933,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8989,7 +8983,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -9039,7 +9033,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -9089,7 +9083,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -9139,7 +9133,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -9189,7 +9183,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -9239,7 +9233,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -9289,7 +9283,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -9339,7 +9333,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9389,7 +9383,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9439,7 +9433,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9489,7 +9483,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9539,7 +9533,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -9589,7 +9583,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -9939,7 +9933,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9989,7 +9983,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -10039,7 +10033,7 @@
         <v>1</v>
       </c>
       <c r="P157" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -10089,7 +10083,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -10139,7 +10133,7 @@
         <v>1</v>
       </c>
       <c r="P159" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -10189,7 +10183,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -10239,7 +10233,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10289,7 +10283,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -10339,7 +10333,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10389,7 +10383,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -10439,7 +10433,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10489,7 +10483,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10539,7 +10533,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -10589,7 +10583,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10639,7 +10633,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -10689,7 +10683,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -10739,7 +10733,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -10789,7 +10783,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -12139,7 +12133,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -12189,7 +12183,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -12239,7 +12233,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -12289,7 +12283,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -12339,7 +12333,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12389,7 +12383,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12439,7 +12433,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12489,7 +12483,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12539,7 +12533,7 @@
         <v>1</v>
       </c>
       <c r="P207" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -12689,7 +12683,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12739,7 +12733,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12939,7 +12933,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12989,7 +12983,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -13039,7 +13033,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -13089,7 +13083,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -13139,7 +13133,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -13189,7 +13183,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -13639,7 +13633,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13689,7 +13683,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13739,7 +13733,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13789,7 +13783,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13839,7 +13833,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -18539,7 +18533,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -18589,7 +18583,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18639,7 +18633,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18689,7 +18683,7 @@
         <v>1</v>
       </c>
       <c r="P330" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="331" spans="1:16">
@@ -18739,7 +18733,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18789,7 +18783,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18839,7 +18833,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -19089,7 +19083,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -19139,7 +19133,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -19189,7 +19183,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -19239,7 +19233,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -19289,7 +19283,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -19789,7 +19783,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19839,7 +19833,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19889,7 +19883,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19939,7 +19933,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -20089,7 +20083,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -20139,7 +20133,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -20189,7 +20183,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -20239,7 +20233,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -20289,7 +20283,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -20539,7 +20533,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20589,7 +20583,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20639,7 +20633,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20689,7 +20683,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20739,7 +20733,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20789,7 +20783,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20839,7 +20833,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20889,7 +20883,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20939,7 +20933,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20989,7 +20983,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -21039,7 +21033,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -21089,7 +21083,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -21139,7 +21133,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -21189,7 +21183,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -21239,7 +21233,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -21289,7 +21283,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -21339,7 +21333,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21389,7 +21383,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21439,7 +21433,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -21489,7 +21483,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21539,7 +21533,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21589,7 +21583,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21639,7 +21633,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21689,7 +21683,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21739,7 +21733,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21789,7 +21783,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21839,7 +21833,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21889,7 +21883,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21939,7 +21933,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21989,7 +21983,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -22039,7 +22033,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -22089,7 +22083,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -22139,7 +22133,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -22189,7 +22183,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -22239,7 +22233,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -22289,7 +22283,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -22339,7 +22333,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -22389,7 +22383,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22439,7 +22433,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22489,7 +22483,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22539,7 +22533,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22589,7 +22583,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22639,7 +22633,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22689,7 +22683,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22989,7 +22983,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -23039,7 +23033,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -23089,7 +23083,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -23139,7 +23133,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -23189,7 +23183,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -23889,7 +23883,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23939,7 +23933,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23989,7 +23983,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -24039,7 +24033,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -24089,7 +24083,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -24139,7 +24133,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -24189,7 +24183,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -24239,7 +24233,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -24289,7 +24283,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -24339,7 +24333,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24389,7 +24383,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24439,7 +24433,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24489,7 +24483,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24539,7 +24533,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24589,7 +24583,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24639,7 +24633,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24689,7 +24683,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24739,7 +24733,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24789,7 +24783,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24839,7 +24833,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24889,7 +24883,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -25239,7 +25233,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -25289,7 +25283,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -25339,7 +25333,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -25389,7 +25383,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25439,7 +25433,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -25489,7 +25483,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25539,7 +25533,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25589,7 +25583,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25639,7 +25633,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25689,7 +25683,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25739,7 +25733,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25789,7 +25783,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25839,7 +25833,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25889,7 +25883,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25939,7 +25933,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25989,7 +25983,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -26039,7 +26033,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -26089,7 +26083,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -26139,7 +26133,7 @@
         <v>1</v>
       </c>
       <c r="P479" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -26189,7 +26183,7 @@
         <v>1</v>
       </c>
       <c r="P480" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="481" spans="1:16">
@@ -26239,7 +26233,7 @@
         <v>1</v>
       </c>
       <c r="P481" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="482" spans="1:16">
@@ -26289,7 +26283,7 @@
         <v>1</v>
       </c>
       <c r="P482" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="483" spans="1:16">
@@ -26339,7 +26333,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26389,7 +26383,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26439,7 +26433,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26489,7 +26483,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26539,7 +26533,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26589,7 +26583,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26639,7 +26633,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26689,7 +26683,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26739,7 +26733,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26789,7 +26783,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26839,7 +26833,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26889,7 +26883,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26939,7 +26933,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26989,7 +26983,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -27039,7 +27033,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -27089,7 +27083,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -27139,7 +27133,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -27189,7 +27183,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -27239,7 +27233,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -27289,7 +27283,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -27339,7 +27333,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27389,7 +27383,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27439,7 +27433,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -27689,7 +27683,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27739,7 +27733,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27789,7 +27783,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27839,7 +27833,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27889,7 +27883,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -28189,7 +28183,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -28239,7 +28233,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -28289,7 +28283,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -28339,7 +28333,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -28389,7 +28383,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28939,7 +28933,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28989,7 +28983,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -29039,7 +29033,7 @@
         <v>1</v>
       </c>
       <c r="P537" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -29089,7 +29083,7 @@
         <v>1</v>
       </c>
       <c r="P538" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -29139,7 +29133,7 @@
         <v>1</v>
       </c>
       <c r="P539" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -29189,7 +29183,7 @@
         <v>1</v>
       </c>
       <c r="P540" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -29239,7 +29233,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -29539,7 +29533,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29589,7 +29583,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29639,7 +29633,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29689,7 +29683,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29739,7 +29733,7 @@
         <v>1</v>
       </c>
       <c r="P551" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29789,7 +29783,7 @@
         <v>1</v>
       </c>
       <c r="P552" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29839,7 +29833,7 @@
         <v>1</v>
       </c>
       <c r="P553" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29889,7 +29883,7 @@
         <v>1</v>
       </c>
       <c r="P554" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -29939,7 +29933,7 @@
         <v>1</v>
       </c>
       <c r="P555" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -29989,7 +29983,7 @@
         <v>1</v>
       </c>
       <c r="P556" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -30039,7 +30033,7 @@
         <v>1</v>
       </c>
       <c r="P557" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -30089,7 +30083,7 @@
         <v>1</v>
       </c>
       <c r="P558" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -30139,7 +30133,7 @@
         <v>1</v>
       </c>
       <c r="P559" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="560" spans="1:16">
@@ -30189,7 +30183,7 @@
         <v>1</v>
       </c>
       <c r="P560" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -30239,7 +30233,7 @@
         <v>1</v>
       </c>
       <c r="P561" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -30289,7 +30283,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -30339,7 +30333,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -30639,7 +30633,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30689,7 +30683,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30739,7 +30733,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30789,7 +30783,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30839,7 +30833,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30889,7 +30883,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30939,7 +30933,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30989,7 +30983,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -31039,7 +31033,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -31639,7 +31633,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31689,7 +31683,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31739,7 +31733,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -31789,7 +31783,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -31839,7 +31833,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -31889,7 +31883,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -31939,7 +31933,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -31989,7 +31983,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -32039,7 +32033,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -32089,7 +32083,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -32139,7 +32133,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -32189,7 +32183,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -32239,7 +32233,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -32289,7 +32283,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -32339,7 +32333,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -32389,7 +32383,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32439,7 +32433,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32489,7 +32483,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -32539,7 +32533,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32589,7 +32583,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32639,7 +32633,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32689,7 +32683,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32739,7 +32733,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32789,7 +32783,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32839,7 +32833,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -32889,7 +32883,7 @@
         <v>1</v>
       </c>
       <c r="P614" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="615" spans="1:16">
@@ -32939,7 +32933,7 @@
         <v>1</v>
       </c>
       <c r="P615" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="616" spans="1:16">
@@ -32989,7 +32983,7 @@
         <v>1</v>
       </c>
       <c r="P616" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="617" spans="1:16">
@@ -33039,7 +33033,7 @@
         <v>1</v>
       </c>
       <c r="P617" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="618" spans="1:16">
@@ -33089,7 +33083,7 @@
         <v>1</v>
       </c>
       <c r="P618" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="619" spans="1:16">
@@ -33139,7 +33133,7 @@
         <v>1</v>
       </c>
       <c r="P619" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="620" spans="1:16">
@@ -33189,7 +33183,7 @@
         <v>1</v>
       </c>
       <c r="P620" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="621" spans="1:16">
@@ -33239,7 +33233,7 @@
         <v>1</v>
       </c>
       <c r="P621" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="622" spans="1:16">
@@ -33289,7 +33283,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -33539,7 +33533,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33589,7 +33583,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -33639,7 +33633,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -33689,7 +33683,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -33739,7 +33733,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33789,7 +33783,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33839,7 +33833,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33889,7 +33883,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33939,7 +33933,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33989,7 +33983,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -34039,7 +34033,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -34089,7 +34083,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -34639,7 +34633,7 @@
         <v>1</v>
       </c>
       <c r="P649" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="650" spans="1:16">
@@ -34689,7 +34683,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -34739,7 +34733,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -34789,7 +34783,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -34839,7 +34833,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -34889,7 +34883,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -34939,7 +34933,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -34989,7 +34983,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -35039,7 +35033,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -35089,7 +35083,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -35139,7 +35133,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -35189,7 +35183,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -35239,7 +35233,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -35289,7 +35283,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -35339,7 +35333,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -35389,7 +35383,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -35439,7 +35433,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -35489,7 +35483,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -35539,7 +35533,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35589,7 +35583,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35639,7 +35633,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -36139,7 +36133,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -36189,7 +36183,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -36239,7 +36233,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -36289,7 +36283,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36339,7 +36333,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36389,7 +36383,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36439,7 +36433,7 @@
         <v>1</v>
       </c>
       <c r="P685" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -36489,7 +36483,7 @@
         <v>1</v>
       </c>
       <c r="P686" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36539,7 +36533,7 @@
         <v>1</v>
       </c>
       <c r="P687" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36589,7 +36583,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36639,7 +36633,7 @@
         <v>1</v>
       </c>
       <c r="P689" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36689,7 +36683,7 @@
         <v>1</v>
       </c>
       <c r="P690" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36739,7 +36733,7 @@
         <v>1</v>
       </c>
       <c r="P691" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36789,7 +36783,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36839,7 +36833,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36889,7 +36883,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36939,7 +36933,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36989,7 +36983,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -37039,7 +37033,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -37089,7 +37083,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -37139,7 +37133,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -37189,7 +37183,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -37239,7 +37233,7 @@
         <v>1</v>
       </c>
       <c r="P701" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -37289,7 +37283,7 @@
         <v>1</v>
       </c>
       <c r="P702" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -37339,7 +37333,7 @@
         <v>1</v>
       </c>
       <c r="P703" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -37389,7 +37383,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -37439,7 +37433,7 @@
         <v>1</v>
       </c>
       <c r="P705" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -37489,7 +37483,7 @@
         <v>1</v>
       </c>
       <c r="P706" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -37539,7 +37533,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -37589,7 +37583,7 @@
         <v>1</v>
       </c>
       <c r="P708" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37639,7 +37633,7 @@
         <v>1</v>
       </c>
       <c r="P709" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37689,7 +37683,7 @@
         <v>1</v>
       </c>
       <c r="P710" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -38139,7 +38133,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -38189,7 +38183,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -38239,7 +38233,7 @@
         <v>1</v>
       </c>
       <c r="P721" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -38289,7 +38283,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -38339,7 +38333,7 @@
         <v>1</v>
       </c>
       <c r="P723" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38389,7 +38383,7 @@
         <v>1</v>
       </c>
       <c r="P724" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38439,7 +38433,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38489,7 +38483,7 @@
         <v>1</v>
       </c>
       <c r="P726" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -39089,7 +39083,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -39139,7 +39133,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -39189,7 +39183,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -39239,7 +39233,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -39289,7 +39283,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -39339,7 +39333,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -39389,7 +39383,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -39439,7 +39433,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -39489,7 +39483,7 @@
         <v>1</v>
       </c>
       <c r="P746" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -39889,7 +39883,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39939,7 +39933,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39989,7 +39983,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -40039,7 +40033,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -40089,7 +40083,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -40139,7 +40133,7 @@
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -40189,7 +40183,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -40239,7 +40233,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -40289,7 +40283,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -40339,7 +40333,7 @@
         <v>1</v>
       </c>
       <c r="P763" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="764" spans="1:16">
@@ -40389,7 +40383,7 @@
         <v>1</v>
       </c>
       <c r="P764" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="765" spans="1:16">
@@ -40439,7 +40433,7 @@
         <v>1</v>
       </c>
       <c r="P765" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -40489,7 +40483,7 @@
         <v>1</v>
       </c>
       <c r="P766" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="767" spans="1:16">
@@ -40539,7 +40533,7 @@
         <v>1</v>
       </c>
       <c r="P767" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -40589,7 +40583,7 @@
         <v>1</v>
       </c>
       <c r="P768" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -40639,7 +40633,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -40689,7 +40683,7 @@
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="771" spans="1:16">
@@ -40739,7 +40733,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -40789,7 +40783,7 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -41089,7 +41083,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -41139,7 +41133,7 @@
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -41189,7 +41183,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -41239,7 +41233,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -41289,7 +41283,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -41339,7 +41333,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -41389,7 +41383,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -41439,7 +41433,7 @@
         <v>1</v>
       </c>
       <c r="P785" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -41489,7 +41483,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -41539,7 +41533,7 @@
         <v>1</v>
       </c>
       <c r="P787" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="788" spans="1:16">
@@ -41589,7 +41583,7 @@
         <v>1</v>
       </c>
       <c r="P788" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="789" spans="1:16">
@@ -41639,7 +41633,7 @@
         <v>1</v>
       </c>
       <c r="P789" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="790" spans="1:16">
@@ -41989,7 +41983,7 @@
         <v>1</v>
       </c>
       <c r="P796" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="797" spans="1:16">
@@ -42039,7 +42033,7 @@
         <v>1</v>
       </c>
       <c r="P797" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="798" spans="1:16">
@@ -42089,7 +42083,7 @@
         <v>1</v>
       </c>
       <c r="P798" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="799" spans="1:16">
@@ -42139,7 +42133,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -42189,7 +42183,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -42239,7 +42233,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -42289,7 +42283,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -42339,7 +42333,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -42389,7 +42383,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -42439,7 +42433,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -42489,7 +42483,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -42539,7 +42533,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42589,7 +42583,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42639,7 +42633,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42689,7 +42683,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -43439,7 +43433,7 @@
         <v>1</v>
       </c>
       <c r="P825" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="826" spans="1:16">
@@ -43489,7 +43483,7 @@
         <v>1</v>
       </c>
       <c r="P826" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="827" spans="1:16">
@@ -43539,7 +43533,7 @@
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="828" spans="1:16">
@@ -43589,7 +43583,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -43639,7 +43633,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -43689,7 +43683,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -43739,7 +43733,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -43789,7 +43783,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43839,7 +43833,7 @@
         <v>1</v>
       </c>
       <c r="P833" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="834" spans="1:16">
@@ -43889,7 +43883,7 @@
         <v>1</v>
       </c>
       <c r="P834" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="835" spans="1:16">
@@ -43939,7 +43933,7 @@
         <v>1</v>
       </c>
       <c r="P835" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="836" spans="1:16">
@@ -43989,7 +43983,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -44039,7 +44033,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -44089,7 +44083,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -44639,7 +44633,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44689,7 +44683,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44739,7 +44733,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -44789,7 +44783,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -44839,7 +44833,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -44889,7 +44883,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44939,7 +44933,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -44989,7 +44983,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -45039,7 +45033,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -45089,7 +45083,7 @@
         <v>1</v>
       </c>
       <c r="P858" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="859" spans="1:16">
@@ -45139,7 +45133,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -45189,7 +45183,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -45239,7 +45233,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -45289,7 +45283,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -45339,7 +45333,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -45389,7 +45383,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -45439,7 +45433,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45489,7 +45483,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45539,7 +45533,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45589,7 +45583,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45639,7 +45633,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45689,7 +45683,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45739,7 +45733,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45789,7 +45783,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45839,7 +45833,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -45889,7 +45883,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45939,7 +45933,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45989,7 +45983,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -46039,7 +46033,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -46089,7 +46083,7 @@
         <v>1</v>
       </c>
       <c r="P878" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="879" spans="1:16">
@@ -46139,7 +46133,7 @@
         <v>1</v>
       </c>
       <c r="P879" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="880" spans="1:16">
@@ -46189,7 +46183,7 @@
         <v>1</v>
       </c>
       <c r="P880" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="881" spans="1:16">
@@ -46239,7 +46233,7 @@
         <v>1</v>
       </c>
       <c r="P881" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="882" spans="1:16">
@@ -46289,7 +46283,7 @@
         <v>1</v>
       </c>
       <c r="P882" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -46339,7 +46333,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46389,7 +46383,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46439,7 +46433,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46489,7 +46483,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46539,7 +46533,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46589,7 +46583,7 @@
         <v>1</v>
       </c>
       <c r="P888" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="889" spans="1:16">
@@ -46639,7 +46633,7 @@
         <v>1</v>
       </c>
       <c r="P889" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="890" spans="1:16">
@@ -46689,7 +46683,7 @@
         <v>1</v>
       </c>
       <c r="P890" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="891" spans="1:16">
@@ -46739,7 +46733,7 @@
         <v>1</v>
       </c>
       <c r="P891" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="892" spans="1:16">
@@ -46789,7 +46783,7 @@
         <v>1</v>
       </c>
       <c r="P892" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="893" spans="1:16">
@@ -46839,7 +46833,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46889,7 +46883,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46939,7 +46933,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -46989,7 +46983,7 @@
         <v>1</v>
       </c>
       <c r="P896" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="897" spans="1:16">
@@ -47039,7 +47033,7 @@
         <v>1</v>
       </c>
       <c r="P897" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="898" spans="1:16">
@@ -47089,7 +47083,7 @@
         <v>1</v>
       </c>
       <c r="P898" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="899" spans="1:16">
@@ -47139,7 +47133,7 @@
         <v>1</v>
       </c>
       <c r="P899" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="900" spans="1:16">
@@ -47189,7 +47183,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -47239,7 +47233,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -47289,7 +47283,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -47339,7 +47333,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -47389,7 +47383,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -47439,7 +47433,7 @@
         <v>1</v>
       </c>
       <c r="P905" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="906" spans="1:16">
@@ -47489,7 +47483,7 @@
         <v>1</v>
       </c>
       <c r="P906" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="907" spans="1:16">
@@ -47539,7 +47533,7 @@
         <v>1</v>
       </c>
       <c r="P907" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="908" spans="1:16">
@@ -47589,7 +47583,7 @@
         <v>1</v>
       </c>
       <c r="P908" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="909" spans="1:16">
@@ -47639,7 +47633,7 @@
         <v>1</v>
       </c>
       <c r="P909" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="910" spans="1:16">
@@ -47689,7 +47683,7 @@
         <v>1</v>
       </c>
       <c r="P910" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="911" spans="1:16">
@@ -47739,7 +47733,7 @@
         <v>1</v>
       </c>
       <c r="P911" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="912" spans="1:16">
@@ -47789,7 +47783,7 @@
         <v>1</v>
       </c>
       <c r="P912" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="913" spans="1:16">
@@ -47839,7 +47833,7 @@
         <v>1</v>
       </c>
       <c r="P913" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="914" spans="1:16">
@@ -47889,7 +47883,7 @@
         <v>1</v>
       </c>
       <c r="P914" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="915" spans="1:16">
@@ -47939,7 +47933,7 @@
         <v>1</v>
       </c>
       <c r="P915" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="916" spans="1:16">
@@ -47989,7 +47983,7 @@
         <v>1</v>
       </c>
       <c r="P916" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="917" spans="1:16">
@@ -48039,7 +48033,7 @@
         <v>1</v>
       </c>
       <c r="P917" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="918" spans="1:16">
@@ -48089,7 +48083,7 @@
         <v>1</v>
       </c>
       <c r="P918" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="919" spans="1:16">
@@ -48139,7 +48133,7 @@
         <v>1</v>
       </c>
       <c r="P919" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="920" spans="1:16">
@@ -48189,7 +48183,7 @@
         <v>1</v>
       </c>
       <c r="P920" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="921" spans="1:16">
@@ -48239,7 +48233,7 @@
         <v>1</v>
       </c>
       <c r="P921" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="922" spans="1:16">
@@ -48289,7 +48283,7 @@
         <v>1</v>
       </c>
       <c r="P922" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="923" spans="1:16">
@@ -48339,7 +48333,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -48389,7 +48383,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -48439,7 +48433,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48489,7 +48483,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48539,7 +48533,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -48589,7 +48583,7 @@
         <v>1</v>
       </c>
       <c r="P928" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="929" spans="1:16">
@@ -48639,7 +48633,7 @@
         <v>1</v>
       </c>
       <c r="P929" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="930" spans="1:16">
@@ -48689,7 +48683,7 @@
         <v>1</v>
       </c>
       <c r="P930" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="931" spans="1:16">
@@ -48739,7 +48733,7 @@
         <v>1</v>
       </c>
       <c r="P931" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="932" spans="1:16">
@@ -48789,7 +48783,7 @@
         <v>1</v>
       </c>
       <c r="P932" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="933" spans="1:16">
@@ -48839,7 +48833,7 @@
         <v>1</v>
       </c>
       <c r="P933" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="934" spans="1:16">
@@ -48889,7 +48883,7 @@
         <v>1</v>
       </c>
       <c r="P934" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="935" spans="1:16">
@@ -48939,7 +48933,7 @@
         <v>1</v>
       </c>
       <c r="P935" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="936" spans="1:16">
@@ -48989,7 +48983,7 @@
         <v>1</v>
       </c>
       <c r="P936" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="937" spans="1:16">
@@ -49039,7 +49033,7 @@
         <v>1</v>
       </c>
       <c r="P937" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="938" spans="1:16">
@@ -49089,7 +49083,7 @@
         <v>1</v>
       </c>
       <c r="P938" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="939" spans="1:16">
@@ -49139,7 +49133,7 @@
         <v>1</v>
       </c>
       <c r="P939" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="940" spans="1:16">
@@ -49189,7 +49183,7 @@
         <v>1</v>
       </c>
       <c r="P940" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="941" spans="1:16">
@@ -49239,7 +49233,7 @@
         <v>1</v>
       </c>
       <c r="P941" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="942" spans="1:16">
@@ -49289,7 +49283,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -49339,7 +49333,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49389,7 +49383,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49439,7 +49433,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -49489,7 +49483,7 @@
         <v>1</v>
       </c>
       <c r="P946" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="947" spans="1:16">
@@ -49539,7 +49533,7 @@
         <v>1</v>
       </c>
       <c r="P947" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="948" spans="1:16">
@@ -49589,7 +49583,7 @@
         <v>1</v>
       </c>
       <c r="P948" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="949" spans="1:16">
@@ -49639,7 +49633,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -49689,7 +49683,7 @@
         <v>1</v>
       </c>
       <c r="P950" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="951" spans="1:16">
@@ -49739,7 +49733,7 @@
         <v>1</v>
       </c>
       <c r="P951" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="952" spans="1:16">
@@ -49789,7 +49783,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -49839,7 +49833,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -49889,7 +49883,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -49939,7 +49933,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -49989,7 +49983,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -50039,7 +50033,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -50089,7 +50083,7 @@
         <v>1</v>
       </c>
       <c r="P958" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="959" spans="1:16">
@@ -50139,7 +50133,7 @@
         <v>1</v>
       </c>
       <c r="P959" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="960" spans="1:16">
@@ -50189,7 +50183,7 @@
         <v>1</v>
       </c>
       <c r="P960" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="961" spans="1:16">
@@ -50239,7 +50233,7 @@
         <v>1</v>
       </c>
       <c r="P961" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="962" spans="1:16">
@@ -50289,7 +50283,7 @@
         <v>1</v>
       </c>
       <c r="P962" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="963" spans="1:16">
@@ -50339,7 +50333,7 @@
         <v>1</v>
       </c>
       <c r="P963" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="964" spans="1:16">
@@ -50389,7 +50383,7 @@
         <v>1</v>
       </c>
       <c r="P964" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="965" spans="1:16">
@@ -50439,7 +50433,7 @@
         <v>1</v>
       </c>
       <c r="P965" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="966" spans="1:16">
@@ -50489,7 +50483,7 @@
         <v>1</v>
       </c>
       <c r="P966" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="967" spans="1:16">
@@ -50539,7 +50533,7 @@
         <v>1</v>
       </c>
       <c r="P967" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="968" spans="1:16">
@@ -50589,7 +50583,7 @@
         <v>1</v>
       </c>
       <c r="P968" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="969" spans="1:16">
@@ -51789,7 +51783,7 @@
         <v>1</v>
       </c>
       <c r="P992" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="993" spans="1:16">
@@ -51839,7 +51833,7 @@
         <v>1</v>
       </c>
       <c r="P993" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="994" spans="1:16">
@@ -51889,7 +51883,7 @@
         <v>1</v>
       </c>
       <c r="P994" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="995" spans="1:16">
@@ -51939,7 +51933,7 @@
         <v>1</v>
       </c>
       <c r="P995" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="996" spans="1:16">
@@ -52639,7 +52633,7 @@
         <v>1</v>
       </c>
       <c r="P1009" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1010" spans="1:16">
@@ -52689,7 +52683,7 @@
         <v>1</v>
       </c>
       <c r="P1010" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1011" spans="1:16">
@@ -52739,7 +52733,7 @@
         <v>1</v>
       </c>
       <c r="P1011" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1012" spans="1:16">
@@ -52789,7 +52783,7 @@
         <v>1</v>
       </c>
       <c r="P1012" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="1013" spans="1:16">
@@ -52839,7 +52833,7 @@
         <v>1</v>
       </c>
       <c r="P1013" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="1014" spans="1:16">
@@ -52889,7 +52883,7 @@
         <v>1</v>
       </c>
       <c r="P1014" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="1015" spans="1:16">
@@ -52939,7 +52933,7 @@
         <v>1</v>
       </c>
       <c r="P1015" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="1016" spans="1:16">
@@ -52989,7 +52983,7 @@
         <v>1</v>
       </c>
       <c r="P1016" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="1017" spans="1:16">
@@ -53039,7 +53033,7 @@
         <v>1</v>
       </c>
       <c r="P1017" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="1018" spans="1:16">
@@ -53489,7 +53483,7 @@
         <v>1</v>
       </c>
       <c r="P1026" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="1027" spans="1:16">
@@ -53539,7 +53533,7 @@
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
@@ -53589,7 +53583,7 @@
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
@@ -53639,7 +53633,7 @@
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
@@ -53689,7 +53683,7 @@
         <v>1</v>
       </c>
       <c r="P1030" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="1031" spans="1:16">
@@ -53739,7 +53733,7 @@
         <v>1</v>
       </c>
       <c r="P1031" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="1032" spans="1:16">
@@ -53789,7 +53783,7 @@
         <v>1</v>
       </c>
       <c r="P1032" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="1033" spans="1:16">
@@ -53839,7 +53833,7 @@
         <v>1</v>
       </c>
       <c r="P1033" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="1034" spans="1:16">
@@ -53889,7 +53883,7 @@
         <v>1</v>
       </c>
       <c r="P1034" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="1035" spans="1:16">
@@ -53939,7 +53933,7 @@
         <v>1</v>
       </c>
       <c r="P1035" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="1036" spans="1:16">
@@ -54789,7 +54783,7 @@
         <v>1</v>
       </c>
       <c r="P1052" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1053" spans="1:16">
@@ -54839,7 +54833,7 @@
         <v>1</v>
       </c>
       <c r="P1053" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1054" spans="1:16">
@@ -54889,7 +54883,7 @@
         <v>1</v>
       </c>
       <c r="P1054" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1055" spans="1:16">
@@ -54939,7 +54933,7 @@
         <v>1</v>
       </c>
       <c r="P1055" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1056" spans="1:16">
@@ -54989,7 +54983,7 @@
         <v>1</v>
       </c>
       <c r="P1056" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1057" spans="1:16">
@@ -55039,7 +55033,7 @@
         <v>1</v>
       </c>
       <c r="P1057" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1058" spans="1:16">
@@ -55089,7 +55083,7 @@
         <v>1</v>
       </c>
       <c r="P1058" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1059" spans="1:16">
@@ -55139,7 +55133,7 @@
         <v>1</v>
       </c>
       <c r="P1059" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1060" spans="1:16">
@@ -55189,7 +55183,7 @@
         <v>1</v>
       </c>
       <c r="P1060" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="1061" spans="1:16">
@@ -55239,7 +55233,7 @@
         <v>1</v>
       </c>
       <c r="P1061" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="1062" spans="1:16">
@@ -55289,7 +55283,7 @@
         <v>1</v>
       </c>
       <c r="P1062" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="1063" spans="1:16">
@@ -55339,7 +55333,7 @@
         <v>1</v>
       </c>
       <c r="P1063" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="1064" spans="1:16">
@@ -55389,7 +55383,7 @@
         <v>1</v>
       </c>
       <c r="P1064" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="1065" spans="1:16">
@@ -55439,7 +55433,7 @@
         <v>1</v>
       </c>
       <c r="P1065" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="1066" spans="1:16">
@@ -55489,7 +55483,7 @@
         <v>1</v>
       </c>
       <c r="P1066" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="1067" spans="1:16">
@@ -55539,7 +55533,7 @@
         <v>1</v>
       </c>
       <c r="P1067" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="1068" spans="1:16">
@@ -55589,7 +55583,7 @@
         <v>1</v>
       </c>
       <c r="P1068" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="1069" spans="1:16">
@@ -55639,7 +55633,7 @@
         <v>1</v>
       </c>
       <c r="P1069" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="1070" spans="1:16">
@@ -55689,7 +55683,7 @@
         <v>1</v>
       </c>
       <c r="P1070" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="1071" spans="1:16">
@@ -55739,7 +55733,7 @@
         <v>1</v>
       </c>
       <c r="P1071" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1072" spans="1:16">
@@ -55789,7 +55783,7 @@
         <v>1</v>
       </c>
       <c r="P1072" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="1073" spans="1:16">
@@ -55803,10 +55797,10 @@
         <v>7.679650110425902</v>
       </c>
       <c r="D1073" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E1073">
-        <v>8.51150959099815</v>
+        <v>7.798469241305181</v>
       </c>
       <c r="F1073">
         <v>-1</v>
@@ -55815,10 +55809,10 @@
         <v>0.008860349889574097</v>
       </c>
       <c r="H1073">
-        <v>0.009808490409001851</v>
+        <v>0.009001530758694819</v>
       </c>
       <c r="I1073">
-        <v>-0.8318594805722483</v>
+        <v>-0.1188191308792792</v>
       </c>
       <c r="J1073">
         <v>0.1118086912072155</v>
@@ -55830,16 +55824,16 @@
         <v>8.27</v>
       </c>
       <c r="M1073">
-        <v>5.8</v>
+        <v>5.38</v>
       </c>
       <c r="N1073">
-        <v>9.16</v>
+        <v>8.4</v>
       </c>
       <c r="O1073">
         <v>1</v>
       </c>
       <c r="P1073" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="1074" spans="1:16">
@@ -55853,10 +55847,10 @@
         <v>7.708161827974112</v>
       </c>
       <c r="D1074" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E1074">
-        <v>8.542829280729139</v>
+        <v>7.827520953503925</v>
       </c>
       <c r="F1074">
         <v>-1</v>
@@ -55865,10 +55859,10 @@
         <v>0.008831838172025886</v>
       </c>
       <c r="H1074">
-        <v>0.009777170719270862</v>
+        <v>0.008972479046496075</v>
       </c>
       <c r="I1074">
-        <v>-0.8346674527550269</v>
+        <v>-0.1193591255298134</v>
       </c>
       <c r="J1074">
         <v>0.1064087447018726</v>
@@ -55880,10 +55874,10 @@
         <v>8.27</v>
       </c>
       <c r="M1074">
-        <v>5.8</v>
+        <v>5.38</v>
       </c>
       <c r="N1074">
-        <v>9.16</v>
+        <v>8.4</v>
       </c>
       <c r="O1074">
         <v>1</v>
@@ -55903,10 +55897,10 @@
         <v>7.759275228935607</v>
       </c>
       <c r="D1075" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E1075">
-        <v>8.598976577239872</v>
+        <v>7.879602411301812</v>
       </c>
       <c r="F1075">
         <v>-1</v>
@@ -55915,10 +55909,10 @@
         <v>0.008780724771064393</v>
       </c>
       <c r="H1075">
-        <v>0.009721023422760128</v>
+        <v>0.008920397588698189</v>
       </c>
       <c r="I1075">
-        <v>-0.8397013483042652</v>
+        <v>-0.1203271823662053</v>
       </c>
       <c r="J1075">
         <v>0.09672817633795312</v>
@@ -55930,16 +55924,16 @@
         <v>8.27</v>
       </c>
       <c r="M1075">
-        <v>5.8</v>
+        <v>5.38</v>
       </c>
       <c r="N1075">
-        <v>9.16</v>
+        <v>8.4</v>
       </c>
       <c r="O1075">
         <v>1</v>
       </c>
       <c r="P1075" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="1076" spans="1:16">
@@ -55956,7 +55950,7 @@
         <v>471</v>
       </c>
       <c r="E1076">
-        <v>6.956796983528459</v>
+        <v>6.83425878150425</v>
       </c>
       <c r="F1076">
         <v>-1</v>
@@ -55965,10 +55959,10 @@
         <v>0.009806638221869434</v>
       </c>
       <c r="H1076">
-        <v>0.01012320301647154</v>
+        <v>0.009965741218495751</v>
       </c>
       <c r="I1076">
-        <v>-0.2234352053978945</v>
+        <v>-0.1008970033736851</v>
       </c>
       <c r="J1076">
         <v>0.2910299662631506</v>
@@ -55980,16 +55974,16 @@
         <v>8.27</v>
       </c>
       <c r="M1076">
-        <v>5.44</v>
+        <v>5.38</v>
       </c>
       <c r="N1076">
-        <v>8.539999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O1076">
         <v>1</v>
       </c>
       <c r="P1076" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="1077" spans="1:16">
@@ -56006,7 +56000,7 @@
         <v>471</v>
       </c>
       <c r="E1077">
-        <v>6.983250099088368</v>
+        <v>6.860420134760188</v>
       </c>
       <c r="F1077">
         <v>-1</v>
@@ -56015,10 +56009,10 @@
         <v>0.009780963139120113</v>
       </c>
       <c r="H1077">
-        <v>0.01009674990091163</v>
+        <v>0.009939579865239813</v>
       </c>
       <c r="I1077">
-        <v>-0.2242132382084812</v>
+        <v>-0.1013832738803018</v>
       </c>
       <c r="J1077">
         <v>0.2861672611969911</v>
@@ -56030,10 +56024,10 @@
         <v>8.27</v>
       </c>
       <c r="M1077">
-        <v>5.44</v>
+        <v>5.38</v>
       </c>
       <c r="N1077">
-        <v>8.539999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O1077">
         <v>1</v>
@@ -56056,7 +56050,7 @@
         <v>471</v>
       </c>
       <c r="E1078">
-        <v>6.960797227036375</v>
+        <v>6.838214904679358</v>
       </c>
       <c r="F1078">
         <v>-1</v>
@@ -56065,10 +56059,10 @@
         <v>0.00980275563258234</v>
       </c>
       <c r="H1078">
-        <v>0.01011920277296362</v>
+        <v>0.009961785095320643</v>
       </c>
       <c r="I1078">
-        <v>-0.2235528596187164</v>
+        <v>-0.1009705372616994</v>
       </c>
       <c r="J1078">
         <v>0.2902946273830191</v>
@@ -56080,16 +56074,16 @@
         <v>8.27</v>
       </c>
       <c r="M1078">
-        <v>5.44</v>
+        <v>5.38</v>
       </c>
       <c r="N1078">
-        <v>8.539999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O1078">
         <v>1</v>
       </c>
       <c r="P1078" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="1079" spans="1:16">
@@ -56106,7 +56100,7 @@
         <v>471</v>
       </c>
       <c r="E1079">
-        <v>6.226394233798296</v>
+        <v>6.111911944454935</v>
       </c>
       <c r="F1079">
         <v>-1</v>
@@ -56115,10 +56109,10 @@
         <v>0.01051555853778401</v>
       </c>
       <c r="H1079">
-        <v>0.0108536057662017</v>
+        <v>0.01068808805554507</v>
       </c>
       <c r="I1079">
-        <v>-0.2019527715823024</v>
+        <v>-0.08747048223894094</v>
       </c>
       <c r="J1079">
         <v>0.4252951776106071</v>
@@ -56130,10 +56124,10 @@
         <v>8.27</v>
       </c>
       <c r="M1079">
-        <v>5.44</v>
+        <v>5.38</v>
       </c>
       <c r="N1079">
-        <v>8.539999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O1079">
         <v>1</v>
@@ -56156,7 +56150,7 @@
         <v>471</v>
       </c>
       <c r="E1080">
-        <v>5.936525902908655</v>
+        <v>5.825240690744223</v>
       </c>
       <c r="F1080">
         <v>-1</v>
@@ -56165,10 +56159,10 @@
         <v>0.01079690132952984</v>
       </c>
       <c r="H1080">
-        <v>0.01114347409709134</v>
+        <v>0.01097475930925578</v>
       </c>
       <c r="I1080">
-        <v>-0.1934272324384896</v>
+        <v>-0.08214202027405726</v>
       </c>
       <c r="J1080">
         <v>0.4785797972594382</v>
@@ -56180,16 +56174,16 @@
         <v>8.27</v>
       </c>
       <c r="M1080">
-        <v>5.44</v>
+        <v>5.38</v>
       </c>
       <c r="N1080">
-        <v>8.539999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O1080">
         <v>1</v>
       </c>
       <c r="P1080" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="1081" spans="1:16">
@@ -56206,7 +56200,7 @@
         <v>471</v>
       </c>
       <c r="E1081">
-        <v>5.698487016969938</v>
+        <v>5.589827233694536</v>
       </c>
       <c r="F1081">
         <v>-1</v>
@@ -56215,10 +56209,10 @@
         <v>0.01102793907176447</v>
       </c>
       <c r="H1081">
-        <v>0.01138151298303006</v>
+        <v>0.01121017276630547</v>
       </c>
       <c r="I1081">
-        <v>-0.1864260887344091</v>
+        <v>-0.07776630545900698</v>
       </c>
       <c r="J1081">
         <v>0.5223369454099376</v>
@@ -56230,10 +56224,10 @@
         <v>8.27</v>
       </c>
       <c r="M1081">
-        <v>5.44</v>
+        <v>5.38</v>
       </c>
       <c r="N1081">
-        <v>8.539999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O1081">
         <v>1</v>
@@ -56256,7 +56250,7 @@
         <v>471</v>
       </c>
       <c r="E1082">
-        <v>5.216659172720293</v>
+        <v>5.113313667138821</v>
       </c>
       <c r="F1082">
         <v>-1</v>
@@ -56265,10 +56259,10 @@
         <v>0.0114955955088303</v>
       </c>
       <c r="H1082">
-        <v>0.0118633408272797</v>
+        <v>0.01168668633286118</v>
       </c>
       <c r="I1082">
-        <v>-0.1722546815505961</v>
+        <v>-0.06890917596912427</v>
       </c>
       <c r="J1082">
         <v>0.6109082403087693</v>
@@ -56280,16 +56274,16 @@
         <v>8.27</v>
       </c>
       <c r="M1082">
-        <v>5.44</v>
+        <v>5.38</v>
       </c>
       <c r="N1082">
-        <v>8.539999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O1082">
         <v>1</v>
       </c>
       <c r="P1082" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="1083" spans="1:16">
@@ -56297,37 +56291,37 @@
         <v>0</v>
       </c>
       <c r="B1083" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C1083">
-        <v>5.443358172213278</v>
+        <v>-0.4214043156284362</v>
       </c>
       <c r="D1083" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E1083">
-        <v>5.627702359250043</v>
+        <v>-0.4483588785748527</v>
       </c>
       <c r="F1083">
         <v>-1</v>
       </c>
       <c r="G1083">
-        <v>0.01109664182778672</v>
+        <v>0.01762140431562844</v>
       </c>
       <c r="H1083">
-        <v>0.01145229764074996</v>
+        <v>0.01752835887857485</v>
       </c>
       <c r="I1083">
-        <v>-0.184344187036765</v>
+        <v>0.02695456294641652</v>
       </c>
       <c r="J1083">
-        <v>0.5353488310202125</v>
+        <v>1.652271852679201</v>
       </c>
       <c r="K1083">
-        <v>5.28</v>
+        <v>5.46</v>
       </c>
       <c r="L1083">
-        <v>8.27</v>
+        <v>8.6</v>
       </c>
       <c r="M1083">
         <v>5.44</v>
@@ -56339,207 +56333,7 @@
         <v>1</v>
       </c>
       <c r="P1083" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="1084" spans="1:16">
-      <c r="A1084" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1084" t="s">
-        <v>297</v>
-      </c>
-      <c r="C1084">
-        <v>5.71703296703297</v>
-      </c>
-      <c r="D1084" t="s">
-        <v>471</v>
-      </c>
-      <c r="E1084">
-        <v>5.909670329670332</v>
-      </c>
-      <c r="F1084">
-        <v>-1</v>
-      </c>
-      <c r="G1084">
-        <v>0.01082296703296703</v>
-      </c>
-      <c r="H1084">
-        <v>0.01117032967032967</v>
-      </c>
-      <c r="I1084">
-        <v>-0.1926373626373623</v>
-      </c>
-      <c r="J1084">
-        <v>0.4835164835164829</v>
-      </c>
-      <c r="K1084">
-        <v>5.28</v>
-      </c>
-      <c r="L1084">
-        <v>8.27</v>
-      </c>
-      <c r="M1084">
-        <v>5.44</v>
-      </c>
-      <c r="N1084">
-        <v>8.539999999999999</v>
-      </c>
-      <c r="O1084">
-        <v>1</v>
-      </c>
-      <c r="P1084" t="s">
         <v>604</v>
-      </c>
-    </row>
-    <row r="1085" spans="1:16">
-      <c r="A1085" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1085" t="s">
-        <v>297</v>
-      </c>
-      <c r="C1085">
-        <v>5.853864517773994</v>
-      </c>
-      <c r="D1085" t="s">
-        <v>471</v>
-      </c>
-      <c r="E1085">
-        <v>6.050648291039872</v>
-      </c>
-      <c r="F1085">
-        <v>-1</v>
-      </c>
-      <c r="G1085">
-        <v>0.01068613548222601</v>
-      </c>
-      <c r="H1085">
-        <v>0.01102935170896013</v>
-      </c>
-      <c r="I1085">
-        <v>-0.1967837732658779</v>
-      </c>
-      <c r="J1085">
-        <v>0.4576014170882586</v>
-      </c>
-      <c r="K1085">
-        <v>5.28</v>
-      </c>
-      <c r="L1085">
-        <v>8.27</v>
-      </c>
-      <c r="M1085">
-        <v>5.44</v>
-      </c>
-      <c r="N1085">
-        <v>8.539999999999999</v>
-      </c>
-      <c r="O1085">
-        <v>1</v>
-      </c>
-      <c r="P1085" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="1086" spans="1:16">
-      <c r="A1086" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1086" t="s">
-        <v>297</v>
-      </c>
-      <c r="C1086">
-        <v>5.996957847030043</v>
-      </c>
-      <c r="D1086" t="s">
-        <v>471</v>
-      </c>
-      <c r="E1086">
-        <v>6.198077781788529</v>
-      </c>
-      <c r="F1086">
-        <v>-1</v>
-      </c>
-      <c r="G1086">
-        <v>0.01054304215296996</v>
-      </c>
-      <c r="H1086">
-        <v>0.01088192221821147</v>
-      </c>
-      <c r="I1086">
-        <v>-0.201119934758486</v>
-      </c>
-      <c r="J1086">
-        <v>0.4305004077594615</v>
-      </c>
-      <c r="K1086">
-        <v>5.28</v>
-      </c>
-      <c r="L1086">
-        <v>8.27</v>
-      </c>
-      <c r="M1086">
-        <v>5.44</v>
-      </c>
-      <c r="N1086">
-        <v>8.539999999999999</v>
-      </c>
-      <c r="O1086">
-        <v>1</v>
-      </c>
-      <c r="P1086" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="1087" spans="1:16">
-      <c r="A1087" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1087" t="s">
-        <v>298</v>
-      </c>
-      <c r="C1087">
-        <v>-0.4214043156284362</v>
-      </c>
-      <c r="D1087" t="s">
-        <v>471</v>
-      </c>
-      <c r="E1087">
-        <v>-0.4483588785748527</v>
-      </c>
-      <c r="F1087">
-        <v>-1</v>
-      </c>
-      <c r="G1087">
-        <v>0.01762140431562844</v>
-      </c>
-      <c r="H1087">
-        <v>0.01752835887857485</v>
-      </c>
-      <c r="I1087">
-        <v>0.02695456294641652</v>
-      </c>
-      <c r="J1087">
-        <v>1.652271852679201</v>
-      </c>
-      <c r="K1087">
-        <v>5.46</v>
-      </c>
-      <c r="L1087">
-        <v>8.6</v>
-      </c>
-      <c r="M1087">
-        <v>5.44</v>
-      </c>
-      <c r="N1087">
-        <v>8.539999999999999</v>
-      </c>
-      <c r="O1087">
-        <v>1</v>
-      </c>
-      <c r="P1087" t="s">
-        <v>606</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3261" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3255" uniqueCount="604">
   <si>
     <t>trade_time</t>
   </si>
@@ -910,7 +910,10 @@
     <t>2021-09-01</t>
   </si>
   <si>
-    <t>2021-09-15</t>
+    <t>2021-09-02</t>
+  </si>
+  <si>
+    <t>2021-09-17</t>
   </si>
   <si>
     <t>2016-04-08</t>
@@ -1429,10 +1432,7 @@
     <t>2021-09-09</t>
   </si>
   <si>
-    <t>2021-09-17</t>
-  </si>
-  <si>
-    <t>2021-09-16</t>
+    <t>2021-09-23</t>
   </si>
   <si>
     <t>2016-01-29</t>
@@ -1822,10 +1822,7 @@
     <t>2021-06-10</t>
   </si>
   <si>
-    <t>2021-06-16</t>
-  </si>
-  <si>
-    <t>2021-06-18</t>
+    <t>2021-07-08</t>
   </si>
   <si>
     <t>2021-09-14</t>
@@ -2186,7 +2183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1083"/>
+  <dimension ref="A1:P1081"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2247,7 +2244,7 @@
         <v>2.377907240969459</v>
       </c>
       <c r="D2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E2">
         <v>1.065805682738189</v>
@@ -2297,7 +2294,7 @@
         <v>2.257772006550848</v>
       </c>
       <c r="D3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E3">
         <v>1.065805682738189</v>
@@ -2347,7 +2344,7 @@
         <v>2.219467861526283</v>
       </c>
       <c r="D4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E4">
         <v>1.065805682738189</v>
@@ -2397,7 +2394,7 @@
         <v>2.538162161690053</v>
       </c>
       <c r="D5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E5">
         <v>1.065805682738189</v>
@@ -2447,7 +2444,7 @@
         <v>0.1821036085161012</v>
       </c>
       <c r="D6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E6">
         <v>-0.1249347321062295</v>
@@ -2497,7 +2494,7 @@
         <v>-0.1533741115494074</v>
       </c>
       <c r="D7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E7">
         <v>-0.1249347321062295</v>
@@ -2547,7 +2544,7 @@
         <v>-0.1586767017623103</v>
       </c>
       <c r="D8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E8">
         <v>-0.1249347321062295</v>
@@ -2597,7 +2594,7 @@
         <v>0.1065460975826067</v>
       </c>
       <c r="D9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E9">
         <v>-0.1249347321062295</v>
@@ -2647,7 +2644,7 @@
         <v>0.0008932476644929466</v>
       </c>
       <c r="D10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E10">
         <v>-0.1249347321062295</v>
@@ -2697,7 +2694,7 @@
         <v>-0.2096720373273193</v>
       </c>
       <c r="D11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E11">
         <v>-0.1249347321062295</v>
@@ -2747,7 +2744,7 @@
         <v>2.028970447511793</v>
       </c>
       <c r="D12" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E12">
         <v>0.938724962148946</v>
@@ -2797,7 +2794,7 @@
         <v>2.150190444147256</v>
       </c>
       <c r="D13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E13">
         <v>0.938724962148946</v>
@@ -2847,7 +2844,7 @@
         <v>2.112289729981704</v>
       </c>
       <c r="D14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E14">
         <v>0.938724962148946</v>
@@ -2897,7 +2894,7 @@
         <v>2.428294491085385</v>
       </c>
       <c r="D15" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E15">
         <v>0.938724962148946</v>
@@ -2947,7 +2944,7 @@
         <v>-0.2921543270500404</v>
       </c>
       <c r="D16" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E16">
         <v>-0.2945705148025581</v>
@@ -2997,7 +2994,7 @@
         <v>-0.2939605164848267</v>
       </c>
       <c r="D17" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E17">
         <v>-0.2945705148025581</v>
@@ -3047,7 +3044,7 @@
         <v>-0.01797956089955122</v>
       </c>
       <c r="D18" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E18">
         <v>-0.2945705148025581</v>
@@ -3097,7 +3094,7 @@
         <v>-0.1249771803477095</v>
       </c>
       <c r="D19" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E19">
         <v>-0.2945705148025581</v>
@@ -3147,7 +3144,7 @@
         <v>-0.3356769422925261</v>
       </c>
       <c r="D20" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E20">
         <v>-0.2945705148025581</v>
@@ -3197,7 +3194,7 @@
         <v>1.921145445432724</v>
       </c>
       <c r="D21" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E21">
         <v>0.796414030633974</v>
@@ -3247,7 +3244,7 @@
         <v>2.029715581489079</v>
       </c>
       <c r="D22" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E22">
         <v>0.796414030633974</v>
@@ -3297,7 +3294,7 @@
         <v>1.992266648058495</v>
       </c>
       <c r="D23" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E23">
         <v>0.796414030633974</v>
@@ -3347,7 +3344,7 @@
         <v>2.30525953759572</v>
       </c>
       <c r="D24" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E24">
         <v>0.796414030633974</v>
@@ -3397,7 +3394,7 @@
         <v>-0.4475668998790905</v>
       </c>
       <c r="D25" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E25">
         <v>-0.6141987681990191</v>
@@ -3447,7 +3444,7 @@
         <v>-0.445457656277485</v>
       </c>
       <c r="D26" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E26">
         <v>-0.6141987681990191</v>
@@ -3497,7 +3494,7 @@
         <v>-0.2659327696577787</v>
       </c>
       <c r="D27" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E27">
         <v>-0.6141987681990191</v>
@@ -3547,7 +3544,7 @@
         <v>-0.4767831251809174</v>
       </c>
       <c r="D28" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E28">
         <v>-0.6141987681990191</v>
@@ -3647,7 +3644,7 @@
         <v>2.930197902571042</v>
       </c>
       <c r="D30" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E30">
         <v>3.697845060893099</v>
@@ -3697,7 +3694,7 @@
         <v>2.93171853856563</v>
       </c>
       <c r="D31" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E31">
         <v>3.697845060893099</v>
@@ -3847,7 +3844,7 @@
         <v>1.909437857449102</v>
       </c>
       <c r="D34" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E34">
         <v>2.73123945259945</v>
@@ -3897,7 +3894,7 @@
         <v>1.927571287293738</v>
       </c>
       <c r="D35" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E35">
         <v>2.73123945259945</v>
@@ -4147,7 +4144,7 @@
         <v>0.9430396109046839</v>
       </c>
       <c r="D40" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E40">
         <v>0.8476461186055282</v>
@@ -4797,7 +4794,7 @@
         <v>2.232760263343966</v>
       </c>
       <c r="D53" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E53">
         <v>1.515079422678022</v>
@@ -4933,7 +4930,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4983,7 +4980,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4997,7 +4994,7 @@
         <v>0.6496455995207633</v>
       </c>
       <c r="D57" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E57">
         <v>1.139659067730454</v>
@@ -5033,7 +5030,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -5047,7 +5044,7 @@
         <v>0.6621691688877203</v>
       </c>
       <c r="D58" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E58">
         <v>1.139659067730454</v>
@@ -5083,7 +5080,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -5097,7 +5094,7 @@
         <v>0.5096590677304533</v>
       </c>
       <c r="D59" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E59">
         <v>1.139659067730454</v>
@@ -5133,7 +5130,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -5183,7 +5180,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -5233,7 +5230,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -5247,7 +5244,7 @@
         <v>-0.4482238035193742</v>
       </c>
       <c r="D62" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E62">
         <v>0.05100577720271815</v>
@@ -5283,7 +5280,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5297,7 +5294,7 @@
         <v>-0.5789942227972826</v>
       </c>
       <c r="D63" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E63">
         <v>0.05100577720271815</v>
@@ -5333,7 +5330,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5347,7 +5344,7 @@
         <v>-0.6485127107485908</v>
       </c>
       <c r="D64" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E64">
         <v>0.05100577720271815</v>
@@ -5383,7 +5380,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5397,7 +5394,7 @@
         <v>0.5534941892431284</v>
       </c>
       <c r="D65" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E65">
         <v>0.1656128422573726</v>
@@ -5433,7 +5430,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -5483,7 +5480,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -5533,7 +5530,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -5547,7 +5544,7 @@
         <v>-1.066969696969696</v>
       </c>
       <c r="D68" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E68">
         <v>-0.543771149985659</v>
@@ -5583,7 +5580,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5597,7 +5594,7 @@
         <v>-1.17377114998566</v>
       </c>
       <c r="D69" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E69">
         <v>-0.543771149985659</v>
@@ -5633,7 +5630,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5647,7 +5644,7 @@
         <v>-1.246436605805691</v>
       </c>
       <c r="D70" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E70">
         <v>-0.543771149985659</v>
@@ -5683,7 +5680,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5697,7 +5694,7 @@
         <v>0.007809960806808292</v>
       </c>
       <c r="D71" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E71">
         <v>-0.2591202243252724</v>
@@ -5733,7 +5730,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5847,7 +5844,7 @@
         <v>-1.678657860308897</v>
       </c>
       <c r="D74" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E74">
         <v>-1.151600082010416</v>
@@ -5897,7 +5894,7 @@
         <v>-1.781600082010417</v>
       </c>
       <c r="D75" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E75">
         <v>-1.151600082010416</v>
@@ -5947,7 +5944,7 @@
         <v>-1.857481563925816</v>
       </c>
       <c r="D76" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E76">
         <v>-1.151600082010416</v>
@@ -6147,7 +6144,7 @@
         <v>-1.819193108813611</v>
       </c>
       <c r="D80" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E80">
         <v>-1.291248672795858</v>
@@ -6197,7 +6194,7 @@
         <v>-1.921248672795858</v>
       </c>
       <c r="D81" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E81">
         <v>-1.291248672795858</v>
@@ -6247,7 +6244,7 @@
         <v>-1.997869036143985</v>
       </c>
       <c r="D82" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E82">
         <v>-1.291248672795858</v>
@@ -6297,7 +6294,7 @@
         <v>-0.6779710045650891</v>
       </c>
       <c r="D83" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E83">
         <v>-0.8744524579575934</v>
@@ -6347,7 +6344,7 @@
         <v>-0.7891561672790921</v>
       </c>
       <c r="D84" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E84">
         <v>-0.8744524579575934</v>
@@ -6497,7 +6494,7 @@
         <v>0.3390481079807373</v>
       </c>
       <c r="D87" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E87">
         <v>0.8316689003586539</v>
@@ -6547,7 +6544,7 @@
         <v>0.3561344946420899</v>
       </c>
       <c r="D88" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E88">
         <v>0.8316689003586539</v>
@@ -6597,7 +6594,7 @@
         <v>0.2016689003586531</v>
       </c>
       <c r="D89" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E89">
         <v>0.8316689003586539</v>
@@ -6647,7 +6644,7 @@
         <v>0.3550656832089647</v>
       </c>
       <c r="D90" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E90">
         <v>0.8316689003586539</v>
@@ -6847,7 +6844,7 @@
         <v>1.702993205626412</v>
       </c>
       <c r="D94" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E94">
         <v>2.213613017446391</v>
@@ -6897,7 +6894,7 @@
         <v>1.700042623382163</v>
       </c>
       <c r="D95" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E95">
         <v>2.213613017446391</v>
@@ -6947,7 +6944,7 @@
         <v>1.55416430148684</v>
       </c>
       <c r="D96" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E96">
         <v>2.213613017446391</v>
@@ -6997,7 +6994,7 @@
         <v>1.697734695551071</v>
       </c>
       <c r="D97" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E97">
         <v>2.213613017446391</v>
@@ -7047,7 +7044,7 @@
         <v>2.778308822184697</v>
       </c>
       <c r="D98" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E98">
         <v>2.907149147620857</v>
@@ -7097,7 +7094,7 @@
         <v>6.23470991605689</v>
       </c>
       <c r="D99" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E99">
         <v>6.96882467582045</v>
@@ -7133,7 +7130,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -7147,7 +7144,7 @@
         <v>6.165186370595404</v>
       </c>
       <c r="D100" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E100">
         <v>6.96882467582045</v>
@@ -7183,7 +7180,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -7197,7 +7194,7 @@
         <v>7.462192305683145</v>
       </c>
       <c r="D101" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E101">
         <v>7.5652188186885</v>
@@ -7233,7 +7230,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -7247,7 +7244,7 @@
         <v>7.766409955034785</v>
       </c>
       <c r="D102" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E102">
         <v>7.5652188186885</v>
@@ -7283,7 +7280,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -7347,7 +7344,7 @@
         <v>6.790335000164763</v>
       </c>
       <c r="D104" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E104">
         <v>7.58905888555706</v>
@@ -7397,7 +7394,7 @@
         <v>6.74758629353808</v>
       </c>
       <c r="D105" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E105">
         <v>7.58905888555706</v>
@@ -7597,7 +7594,7 @@
         <v>6.426886909355456</v>
       </c>
       <c r="D109" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E109">
         <v>7.170479443185158</v>
@@ -7647,7 +7644,7 @@
         <v>6.354540197150865</v>
       </c>
       <c r="D110" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E110">
         <v>7.170479443185158</v>
@@ -7847,7 +7844,7 @@
         <v>6.205686423858355</v>
       </c>
       <c r="D114" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E114">
         <v>6.974286460418881</v>
@@ -7897,7 +7894,7 @@
         <v>6.17031498633333</v>
       </c>
       <c r="D115" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E115">
         <v>6.974286460418881</v>
@@ -7947,7 +7944,7 @@
         <v>7.467572163512598</v>
       </c>
       <c r="D116" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E116">
         <v>7.999200804331553</v>
@@ -7997,7 +7994,7 @@
         <v>7.771800736433435</v>
       </c>
       <c r="D117" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E117">
         <v>7.999200804331553</v>
@@ -8097,7 +8094,7 @@
         <v>5.758523378301289</v>
       </c>
       <c r="D119" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E119">
         <v>6.469153597378058</v>
@@ -8147,7 +8144,7 @@
         <v>5.695995227937997</v>
       </c>
       <c r="D120" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E120">
         <v>6.469153597378058</v>
@@ -8197,7 +8194,7 @@
         <v>5.575650149522264</v>
       </c>
       <c r="D121" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E121">
         <v>6.469153597378058</v>
@@ -8247,7 +8244,7 @@
         <v>6.970016293417387</v>
       </c>
       <c r="D122" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E122">
         <v>7.634780179426718</v>
@@ -8297,7 +8294,7 @@
         <v>7.273234600612143</v>
       </c>
       <c r="D123" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E123">
         <v>7.634780179426718</v>
@@ -8347,7 +8344,7 @@
         <v>5.679717798863969</v>
       </c>
       <c r="D124" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E124">
         <v>6.421217454115635</v>
@@ -8397,7 +8394,7 @@
         <v>5.650983189414583</v>
       </c>
       <c r="D125" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E125">
         <v>6.421217454115635</v>
@@ -8447,7 +8444,7 @@
         <v>5.530350494139276</v>
       </c>
       <c r="D126" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E126">
         <v>6.421217454115635</v>
@@ -8647,7 +8644,7 @@
         <v>5.621464282690935</v>
       </c>
       <c r="D130" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E130">
         <v>6.359962442366914</v>
@@ -8697,7 +8694,7 @@
         <v>5.593464733382533</v>
       </c>
       <c r="D131" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E131">
         <v>6.359962442366914</v>
@@ -8747,7 +8744,7 @@
         <v>5.472464508036733</v>
       </c>
       <c r="D132" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E132">
         <v>6.359962442366914</v>
@@ -8947,7 +8944,7 @@
         <v>4.812788531912378</v>
       </c>
       <c r="D136" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E136">
         <v>5.509619907373689</v>
@@ -8997,7 +8994,7 @@
         <v>4.794993093023895</v>
       </c>
       <c r="D137" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E137">
         <v>5.509619907373689</v>
@@ -9047,7 +9044,7 @@
         <v>4.668890812468137</v>
       </c>
       <c r="D138" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E138">
         <v>5.509619907373689</v>
@@ -9097,7 +9094,7 @@
         <v>6.099225988855712</v>
       </c>
       <c r="D139" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E139">
         <v>6.844581898111059</v>
@@ -9147,7 +9144,7 @@
         <v>6.071430549967227</v>
       </c>
       <c r="D140" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E140">
         <v>6.844581898111059</v>
@@ -9197,7 +9194,7 @@
         <v>6.326174848577831</v>
       </c>
       <c r="D141" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E141">
         <v>6.844581898111059</v>
@@ -9247,7 +9244,7 @@
         <v>4.312040252964167</v>
       </c>
       <c r="D142" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E142">
         <v>4.983070718153698</v>
@@ -9297,7 +9294,7 @@
         <v>4.300563404346324</v>
       </c>
       <c r="D143" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E143">
         <v>4.983070718153698</v>
@@ -9347,7 +9344,7 @@
         <v>4.171301828655245</v>
       </c>
       <c r="D144" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E144">
         <v>4.983070718153698</v>
@@ -9597,7 +9594,7 @@
         <v>3.944694008078107</v>
       </c>
       <c r="D149" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E149">
         <v>4.596797064225139</v>
@@ -9647,7 +9644,7 @@
         <v>3.937852443307407</v>
       </c>
       <c r="D150" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E150">
         <v>4.596797064225139</v>
@@ -9697,7 +9694,7 @@
         <v>3.806273225692757</v>
       </c>
       <c r="D151" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E151">
         <v>4.596797064225139</v>
@@ -9747,7 +9744,7 @@
         <v>5.201008311197539</v>
       </c>
       <c r="D152" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E152">
         <v>5.908899264592449</v>
@@ -9797,7 +9794,7 @@
         <v>5.425218702390213</v>
       </c>
       <c r="D153" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E153">
         <v>5.908899264592449</v>
@@ -9847,7 +9844,7 @@
         <v>5.478374570280344</v>
       </c>
       <c r="D154" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E154">
         <v>5.908899264592449</v>
@@ -9897,7 +9894,7 @@
         <v>4.103540950877517</v>
       </c>
       <c r="D155" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E155">
         <v>4.804785959699134</v>
@@ -9947,7 +9944,7 @@
         <v>4.065325239112265</v>
       </c>
       <c r="D156" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E156">
         <v>4.804785959699134</v>
@@ -9997,7 +9994,7 @@
         <v>3.934560544154515</v>
       </c>
       <c r="D157" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E157">
         <v>4.804785959699134</v>
@@ -10197,7 +10194,7 @@
         <v>3.580160099004089</v>
       </c>
       <c r="D161" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E161">
         <v>4.308315560860121</v>
@@ -10247,7 +10244,7 @@
         <v>3.549633088105812</v>
       </c>
       <c r="D162" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E162">
         <v>4.308315560860121</v>
@@ -10297,7 +10294,7 @@
         <v>3.415573235633644</v>
       </c>
       <c r="D163" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E163">
         <v>4.308315560860121</v>
@@ -10647,7 +10644,7 @@
         <v>3.927996868785175</v>
       </c>
       <c r="D170" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E170">
         <v>4.228792366606019</v>
@@ -10697,7 +10694,7 @@
         <v>4.067912029788856</v>
       </c>
       <c r="D171" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E171">
         <v>4.228792366606019</v>
@@ -10747,7 +10744,7 @@
         <v>4.059184614733637</v>
       </c>
       <c r="D172" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E172">
         <v>4.228792366606019</v>
@@ -10797,7 +10794,7 @@
         <v>2.005909712128765</v>
       </c>
       <c r="D173" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E173">
         <v>2.67318675835737</v>
@@ -10847,7 +10844,7 @@
         <v>1.861985812525753</v>
       </c>
       <c r="D174" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E174">
         <v>2.67318675835737</v>
@@ -10897,7 +10894,7 @@
         <v>3.25255656550317</v>
       </c>
       <c r="D175" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E175">
         <v>3.447665574766244</v>
@@ -10947,7 +10944,7 @@
         <v>3.347725014643028</v>
       </c>
       <c r="D176" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E176">
         <v>3.447665574766244</v>
@@ -10997,7 +10994,7 @@
         <v>3.394518515304676</v>
       </c>
       <c r="D177" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E177">
         <v>3.447665574766244</v>
@@ -11047,7 +11044,7 @@
         <v>3.355089268282093</v>
       </c>
       <c r="D178" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E178">
         <v>3.447665574766244</v>
@@ -11097,7 +11094,7 @@
         <v>3.579100375295562</v>
       </c>
       <c r="D179" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E179">
         <v>3.447665574766244</v>
@@ -11533,7 +11530,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -11583,7 +11580,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11633,7 +11630,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11683,7 +11680,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11733,7 +11730,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11783,7 +11780,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11833,7 +11830,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11897,7 +11894,7 @@
         <v>3.123371001188277</v>
       </c>
       <c r="D195" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E195">
         <v>4.195059763740991</v>
@@ -11947,7 +11944,7 @@
         <v>2.954328619026529</v>
       </c>
       <c r="D196" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E196">
         <v>4.195059763740991</v>
@@ -11997,7 +11994,7 @@
         <v>3.046412078566592</v>
       </c>
       <c r="D197" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E197">
         <v>4.195059763740991</v>
@@ -12047,7 +12044,7 @@
         <v>3.445059763740991</v>
       </c>
       <c r="D198" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E198">
         <v>4.195059763740991</v>
@@ -12147,7 +12144,7 @@
         <v>2.577752040845755</v>
       </c>
       <c r="D200" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E200">
         <v>3.401487870308934</v>
@@ -12197,7 +12194,7 @@
         <v>2.464829953558134</v>
       </c>
       <c r="D201" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E201">
         <v>3.401487870308934</v>
@@ -12247,7 +12244,7 @@
         <v>2.478250786050127</v>
       </c>
       <c r="D202" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E202">
         <v>3.401487870308934</v>
@@ -12297,7 +12294,7 @@
         <v>2.818408284535719</v>
       </c>
       <c r="D203" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E203">
         <v>3.401487870308934</v>
@@ -13197,7 +13194,7 @@
         <v>6.871264555787782</v>
       </c>
       <c r="D221" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E221">
         <v>5.968914093679149</v>
@@ -13247,7 +13244,7 @@
         <v>6.95746889119295</v>
       </c>
       <c r="D222" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E222">
         <v>5.968914093679149</v>
@@ -13297,7 +13294,7 @@
         <v>6.908484547625465</v>
       </c>
       <c r="D223" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E223">
         <v>6.962494985247139</v>
@@ -13447,7 +13444,7 @@
         <v>3.455949739008592</v>
       </c>
       <c r="D226" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E226">
         <v>2.626483427002986</v>
@@ -13697,7 +13694,7 @@
         <v>1.402030495249267</v>
       </c>
       <c r="D231" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E231">
         <v>0.6610634692540209</v>
@@ -13847,7 +13844,7 @@
         <v>-1.012190922870992</v>
       </c>
       <c r="D234" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E234">
         <v>0.08311492058150804</v>
@@ -13897,7 +13894,7 @@
         <v>-1.046879430812844</v>
       </c>
       <c r="D235" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E235">
         <v>0.08311492058150804</v>
@@ -13997,7 +13994,7 @@
         <v>0.5471409041675006</v>
       </c>
       <c r="D237" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E237">
         <v>-0.09752500935174702</v>
@@ -14047,7 +14044,7 @@
         <v>0.5771493770759779</v>
       </c>
       <c r="D238" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E238">
         <v>-0.1448636147170212</v>
@@ -14097,7 +14094,7 @@
         <v>0.7211216989082878</v>
       </c>
       <c r="D239" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E239">
         <v>0.3151194394660273</v>
@@ -14147,7 +14144,7 @@
         <v>0.6184603042735599</v>
       </c>
       <c r="D240" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E240">
         <v>0.3151194394660273</v>
@@ -14197,7 +14194,7 @@
         <v>0.8057932610331839</v>
       </c>
       <c r="D241" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E241">
         <v>0.3151194394660273</v>
@@ -14247,7 +14244,7 @@
         <v>0.1720291663575146</v>
       </c>
       <c r="D242" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E242">
         <v>-1.174782432733231</v>
@@ -14283,7 +14280,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -14297,7 +14294,7 @@
         <v>-0.5832848576420009</v>
       </c>
       <c r="D243" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E243">
         <v>-1.223526404187433</v>
@@ -14333,7 +14330,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -14347,7 +14344,7 @@
         <v>-0.5978983899145334</v>
       </c>
       <c r="D244" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E244">
         <v>-1.157197898187556</v>
@@ -14383,7 +14380,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -14397,7 +14394,7 @@
         <v>-0.522125420733472</v>
       </c>
       <c r="D245" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E245">
         <v>-1.167246194006191</v>
@@ -14433,7 +14430,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -14447,7 +14444,7 @@
         <v>-0.5938162465515013</v>
       </c>
       <c r="D246" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E246">
         <v>-1.167246194006191</v>
@@ -14483,7 +14480,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -14497,7 +14494,7 @@
         <v>-0.4086954732787849</v>
       </c>
       <c r="D247" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E247">
         <v>-1.167246194006191</v>
@@ -14533,7 +14530,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14547,7 +14544,7 @@
         <v>1.516859912216534</v>
       </c>
       <c r="D248" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E248">
         <v>0.1337015362106797</v>
@@ -14597,7 +14594,7 @@
         <v>0.6549286759327</v>
       </c>
       <c r="D249" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E249">
         <v>0.009840892465252438</v>
@@ -14647,7 +14644,7 @@
         <v>0.6801911119239215</v>
       </c>
       <c r="D250" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E250">
         <v>0.1028237015362095</v>
@@ -14697,7 +14694,7 @@
         <v>0.8396671543525969</v>
       </c>
       <c r="D251" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E251">
         <v>0.1921232626188711</v>
@@ -14747,7 +14744,7 @@
         <v>0.7340526700804659</v>
       </c>
       <c r="D252" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E252">
         <v>0.1921232626188711</v>
@@ -14847,7 +14844,7 @@
         <v>1.469564000694344</v>
       </c>
       <c r="D254" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E254">
         <v>0.08768389256746723</v>
@@ -14883,7 +14880,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14897,7 +14894,7 @@
         <v>0.6113823501888458</v>
       </c>
       <c r="D255" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E255">
         <v>-0.03353499756140543</v>
@@ -14933,7 +14930,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14947,7 +14944,7 @@
         <v>0.6047501988112209</v>
       </c>
       <c r="D256" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E256">
         <v>0.05851041506496912</v>
@@ -14983,7 +14980,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14997,7 +14994,7 @@
         <v>0.7917747178202177</v>
       </c>
       <c r="D257" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E257">
         <v>0.144316043945091</v>
@@ -15033,7 +15030,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -15047,7 +15044,7 @@
         <v>0.6873532835684664</v>
       </c>
       <c r="D258" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E258">
         <v>0.144316043945091</v>
@@ -15083,7 +15080,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -15133,7 +15130,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -15147,7 +15144,7 @@
         <v>1.44514430187747</v>
       </c>
       <c r="D260" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E260">
         <v>0.06392418561050839</v>
@@ -15197,7 +15194,7 @@
         <v>0.5888986274943893</v>
       </c>
       <c r="D261" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E261">
         <v>-0.05593072134120547</v>
@@ -15247,7 +15244,7 @@
         <v>0.5831904647206478</v>
       </c>
       <c r="D262" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E262">
         <v>0.03563069725456458</v>
@@ -15297,7 +15294,7 @@
         <v>0.7670470228020498</v>
       </c>
       <c r="D263" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E263">
         <v>0.1196323483842505</v>
@@ -15347,7 +15344,7 @@
         <v>0.6632415809528851</v>
       </c>
       <c r="D264" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E264">
         <v>0.1196323483842505</v>
@@ -15397,7 +15394,7 @@
         <v>-0.3588062330199779</v>
       </c>
       <c r="D265" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E265">
         <v>-0.2613915586021829</v>
@@ -15447,7 +15444,7 @@
         <v>-0.341391558602183</v>
       </c>
       <c r="D266" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E266">
         <v>-0.2613915586021829</v>
@@ -15497,7 +15494,7 @@
         <v>1.286085745836417</v>
       </c>
       <c r="D267" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E267">
         <v>-0.09083549053754325</v>
@@ -15533,7 +15530,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15547,7 +15544,7 @@
         <v>0.4424501191394743</v>
       </c>
       <c r="D268" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E268">
         <v>-0.2018060457103878</v>
@@ -15583,7 +15580,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15597,7 +15594,7 @@
         <v>0.4427603882159339</v>
       </c>
       <c r="D269" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E269">
         <v>-0.1133971390361523</v>
@@ -15633,7 +15630,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15647,7 +15644,7 @@
         <v>0.6059823228109291</v>
       </c>
       <c r="D270" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E270">
         <v>-0.04114575961400391</v>
@@ -15683,7 +15680,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15697,7 +15694,7 @@
         <v>0.5061891688618996</v>
       </c>
       <c r="D271" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E271">
         <v>-0.04114575961400391</v>
@@ -15733,7 +15730,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15747,7 +15744,7 @@
         <v>-0.5227368529397651</v>
       </c>
       <c r="D272" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E272">
         <v>-0.3415594517159466</v>
@@ -15783,7 +15780,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15797,7 +15794,7 @@
         <v>-0.5056087705148382</v>
       </c>
       <c r="D273" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E273">
         <v>-0.3415594517159466</v>
@@ -15833,7 +15830,7 @@
         <v>1</v>
       </c>
       <c r="P273" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -15847,7 +15844,7 @@
         <v>1.220304308582177</v>
       </c>
       <c r="D274" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E274">
         <v>-0.154839051109235</v>
@@ -15897,7 +15894,7 @@
         <v>0.3818837868207066</v>
       </c>
       <c r="D275" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E275">
         <v>-0.2621353278048151</v>
@@ -15947,7 +15944,7 @@
         <v>0.3846830832527317</v>
       </c>
       <c r="D276" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E276">
         <v>-0.1750301973644497</v>
@@ -15997,7 +15994,7 @@
         <v>0.5393712097715007</v>
       </c>
       <c r="D277" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E277">
         <v>-0.1076383475412612</v>
@@ -16047,7 +16044,7 @@
         <v>0.4412374073928493</v>
       </c>
       <c r="D278" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E278">
         <v>-0.1076383475412612</v>
@@ -16097,7 +16094,7 @@
         <v>-0.5905332171008926</v>
       </c>
       <c r="D279" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E279">
         <v>-0.318380300096722</v>
@@ -16147,7 +16144,7 @@
         <v>-0.5124949878498484</v>
       </c>
       <c r="D280" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E280">
         <v>-0.318380300096722</v>
@@ -16197,7 +16194,7 @@
         <v>0.5242887395747005</v>
       </c>
       <c r="D281" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E281">
         <v>-0.1202877329872347</v>
@@ -16247,7 +16244,7 @@
         <v>0.5212357776743701</v>
       </c>
       <c r="D282" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E282">
         <v>-0.03011713389658688</v>
@@ -16297,7 +16294,7 @@
         <v>0.6959887899040744</v>
       </c>
       <c r="D283" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E283">
         <v>0.04870055362310488</v>
@@ -16347,7 +16344,7 @@
         <v>0.5939534819705194</v>
       </c>
       <c r="D284" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E284">
         <v>0.04870055362310488</v>
@@ -16397,7 +16394,7 @@
         <v>-0.3211288472862446</v>
       </c>
       <c r="D285" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E285">
         <v>-0.1326523579478529</v>
@@ -16447,7 +16444,7 @@
         <v>-0.431128847286244</v>
       </c>
       <c r="D286" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E286">
         <v>-0.1326523579478529</v>
@@ -16497,7 +16494,7 @@
         <v>-0.351975902162371</v>
       </c>
       <c r="D287" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E287">
         <v>-0.1326523579478529</v>
@@ -16547,7 +16544,7 @@
         <v>0.5451410172423419</v>
       </c>
       <c r="D288" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E288">
         <v>-0.09951706893081891</v>
@@ -16583,7 +16580,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16597,7 +16594,7 @@
         <v>0.5412311124241622</v>
       </c>
       <c r="D289" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E289">
         <v>-0.008897594978440893</v>
@@ -16633,7 +16630,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16647,7 +16644,7 @@
         <v>0.7189222146579191</v>
       </c>
       <c r="D290" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E290">
         <v>0.07159317157133671</v>
@@ -16683,7 +16680,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16697,7 +16694,7 @@
         <v>0.6163156114457973</v>
       </c>
       <c r="D291" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E291">
         <v>0.07159317157133671</v>
@@ -16733,7 +16730,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16747,7 +16744,7 @@
         <v>-0.2977873544762826</v>
       </c>
       <c r="D292" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E292">
         <v>0.2641354210821554</v>
@@ -16783,7 +16780,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16797,7 +16794,7 @@
         <v>-0.407787354476282</v>
       </c>
       <c r="D293" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E293">
         <v>0.2641354210821554</v>
@@ -16833,7 +16830,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16847,7 +16844,7 @@
         <v>0.6831127115251583</v>
       </c>
       <c r="D294" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E294">
         <v>0.0379146187207553</v>
@@ -16883,7 +16880,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16897,7 +16894,7 @@
         <v>0.6735327370789186</v>
       </c>
       <c r="D295" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E295">
         <v>0.1315041291449752</v>
@@ -16933,7 +16930,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16947,7 +16944,7 @@
         <v>0.8706640780374553</v>
       </c>
       <c r="D296" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E296">
         <v>0.2230650316352509</v>
@@ -16983,7 +16980,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16997,7 +16994,7 @@
         <v>0.7642774284066274</v>
       </c>
       <c r="D297" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E297">
         <v>0.2230650316352509</v>
@@ -17033,7 +17030,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -17047,7 +17044,7 @@
         <v>-0.1433454579405264</v>
       </c>
       <c r="D298" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E298">
         <v>0.4234373772991074</v>
@@ -17083,7 +17080,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -17097,7 +17094,7 @@
         <v>-0.2533454579405259</v>
       </c>
       <c r="D299" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E299">
         <v>0.4234373772991074</v>
@@ -17133,7 +17130,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -17147,7 +17144,7 @@
         <v>-0.05222072710995107</v>
       </c>
       <c r="D300" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E300">
         <v>0.6345003208948405</v>
@@ -17197,7 +17194,7 @@
         <v>0.702314352898032</v>
       </c>
       <c r="D301" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E301">
         <v>0.05704110689843134</v>
@@ -17247,7 +17244,7 @@
         <v>0.6919452699022219</v>
       </c>
       <c r="D302" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E302">
         <v>0.151043959896235</v>
@@ -17297,7 +17294,7 @@
         <v>0.6723143528980309</v>
       </c>
       <c r="D303" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E303">
         <v>0.151043959896235</v>
@@ -17397,7 +17394,7 @@
         <v>0.8917821258878558</v>
       </c>
       <c r="D305" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E305">
         <v>0.2441455028880526</v>
@@ -17447,7 +17444,7 @@
         <v>0.7848694038906459</v>
       </c>
       <c r="D306" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E306">
         <v>0.2441455028880526</v>
@@ -17497,7 +17494,7 @@
         <v>-0.1218516441141411</v>
       </c>
       <c r="D307" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E307">
         <v>0.4456075698822666</v>
@@ -17547,7 +17544,7 @@
         <v>-0.03112774311154531</v>
       </c>
       <c r="D308" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E308">
         <v>0.4456075698822666</v>
@@ -17597,7 +17594,7 @@
         <v>-0.1599756512329034</v>
       </c>
       <c r="D309" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E309">
         <v>0.5314388961892202</v>
@@ -17647,7 +17644,7 @@
         <v>0.6023819278039682</v>
       </c>
       <c r="D310" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E310">
         <v>-0.04250019324418908</v>
@@ -17697,7 +17694,7 @@
         <v>0.5961196567983258</v>
       </c>
       <c r="D311" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E311">
         <v>0.04935147252067118</v>
@@ -17747,7 +17744,7 @@
         <v>0.572381927803967</v>
       </c>
       <c r="D312" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E312">
         <v>0.04935147252067118</v>
@@ -17847,7 +17844,7 @@
         <v>0.7818760145319583</v>
       </c>
       <c r="D314" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E314">
         <v>0.2188455592486616</v>
@@ -17897,7 +17894,7 @@
         <v>0.6777011671948596</v>
       </c>
       <c r="D315" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E315">
         <v>0.1344349540078777</v>
@@ -17947,7 +17944,7 @@
         <v>-0.2337133802272593</v>
       </c>
       <c r="D316" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E316">
         <v>0.3302257092061467</v>
@@ -17997,7 +17994,7 @@
         <v>-0.1404471670402767</v>
       </c>
       <c r="D317" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E317">
         <v>0.3302257092061467</v>
@@ -18047,7 +18044,7 @@
         <v>-0.5297221743420888</v>
       </c>
       <c r="D318" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E318">
         <v>0.177797484794409</v>
@@ -18083,7 +18080,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -18097,7 +18094,7 @@
         <v>0.2594772575520725</v>
       </c>
       <c r="D319" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E319">
         <v>-0.3840627708532196</v>
@@ -18133,7 +18130,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -18147,7 +18144,7 @@
         <v>0.2160020090057699</v>
       </c>
       <c r="D320" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E320">
         <v>-0.2995926146241139</v>
@@ -18183,7 +18180,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -18197,7 +18194,7 @@
         <v>0.2294772575520714</v>
       </c>
       <c r="D321" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E321">
         <v>-0.2995926146241139</v>
@@ -18233,7 +18230,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -18283,7 +18280,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -18297,7 +18294,7 @@
         <v>0.4047479818870166</v>
       </c>
       <c r="D323" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E323">
         <v>-0.1643218902891714</v>
@@ -18333,7 +18330,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -18347,7 +18344,7 @@
         <v>0.3099677830499701</v>
       </c>
       <c r="D324" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E324">
         <v>-0.2420220323156315</v>
@@ -18383,7 +18380,7 @@
         <v>1</v>
       </c>
       <c r="P324" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="325" spans="1:16">
@@ -18397,7 +18394,7 @@
         <v>-0.6175518760865248</v>
       </c>
       <c r="D325" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E325">
         <v>-0.06569162043889776</v>
@@ -18433,7 +18430,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -18447,7 +18444,7 @@
         <v>-0.5155620607209208</v>
       </c>
       <c r="D326" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E326">
         <v>-0.06569162043889776</v>
@@ -18483,7 +18480,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -18497,7 +18494,7 @@
         <v>3.711167000814271</v>
       </c>
       <c r="D327" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E327">
         <v>4.512707221119614</v>
@@ -18547,7 +18544,7 @@
         <v>5.260227025292643</v>
       </c>
       <c r="D328" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E328">
         <v>3.883216817226483</v>
@@ -18597,7 +18594,7 @@
         <v>3.612446707073811</v>
       </c>
       <c r="D329" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E329">
         <v>4.036376474529282</v>
@@ -18647,7 +18644,7 @@
         <v>2.778054848675449</v>
       </c>
       <c r="D330" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E330">
         <v>3.550231399857543</v>
@@ -18697,7 +18694,7 @@
         <v>2.800953545963342</v>
       </c>
       <c r="D331" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E331">
         <v>3.550231399857543</v>
@@ -18747,7 +18744,7 @@
         <v>4.323852243251237</v>
       </c>
       <c r="D332" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E332">
         <v>2.974574389357036</v>
@@ -18797,7 +18794,7 @@
         <v>2.718486113765989</v>
       </c>
       <c r="D333" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E333">
         <v>3.123410865296</v>
@@ -18847,7 +18844,7 @@
         <v>1.983160587873193</v>
       </c>
       <c r="D334" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E334">
         <v>2.730322983995075</v>
@@ -18897,7 +18894,7 @@
         <v>2.004669609879961</v>
       </c>
       <c r="D335" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E335">
         <v>2.730322983995075</v>
@@ -18947,7 +18944,7 @@
         <v>3.526178631886735</v>
       </c>
       <c r="D336" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E336">
         <v>2.200525257771622</v>
@@ -18997,7 +18994,7 @@
         <v>1.956944059710679</v>
       </c>
       <c r="D337" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E337">
         <v>2.409218509541397</v>
@@ -19047,7 +19044,7 @@
         <v>0.8799289586838714</v>
       </c>
       <c r="D338" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E338">
         <v>1.592374275565531</v>
@@ -19097,7 +19094,7 @@
         <v>0.9682501402131294</v>
       </c>
       <c r="D339" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E339">
         <v>1.592374275565531</v>
@@ -19147,7 +19144,7 @@
         <v>2.419089549448499</v>
       </c>
       <c r="D340" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E340">
         <v>1.126224527949153</v>
@@ -19197,7 +19194,7 @@
         <v>2.06419891568518</v>
       </c>
       <c r="D341" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E341">
         <v>1.126224527949153</v>
@@ -19247,7 +19244,7 @@
         <v>0.9000018695083227</v>
       </c>
       <c r="D342" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E342">
         <v>1.703012712656575</v>
@@ -19297,7 +19294,7 @@
         <v>0.3940106533845285</v>
       </c>
       <c r="D343" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E343">
         <v>0.9777032963232024</v>
@@ -19333,7 +19330,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19347,7 +19344,7 @@
         <v>0.284010653384529</v>
       </c>
       <c r="D344" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E344">
         <v>0.9777032963232024</v>
@@ -19383,7 +19380,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19397,7 +19394,7 @@
         <v>1.821087613711049</v>
       </c>
       <c r="D345" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E345">
         <v>0.5459334509356335</v>
@@ -19433,7 +19430,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19447,7 +19444,7 @@
         <v>1.5037023278337</v>
       </c>
       <c r="D346" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E346">
         <v>0.5459334509356335</v>
@@ -19483,7 +19480,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19497,7 +19494,7 @@
         <v>0.3290871294662949</v>
       </c>
       <c r="D347" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E347">
         <v>1.164394244405246</v>
@@ -19533,7 +19530,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19547,7 +19544,7 @@
         <v>-0.1303378620988589</v>
       </c>
       <c r="D348" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E348">
         <v>0.5687326111345428</v>
@@ -19597,7 +19594,7 @@
         <v>1.405290327194502</v>
       </c>
       <c r="D349" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E349">
         <v>0.1424507182009354</v>
@@ -19647,7 +19644,7 @@
         <v>1.113982919914012</v>
       </c>
       <c r="D350" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E350">
         <v>0.1424507182009354</v>
@@ -19697,7 +19694,7 @@
         <v>0.01807890749429752</v>
       </c>
       <c r="D351" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E351">
         <v>0.7898869323337241</v>
@@ -19747,7 +19744,7 @@
         <v>-0.1449533761282655</v>
       </c>
       <c r="D352" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E352">
         <v>0.5539893391153683</v>
@@ -19797,7 +19794,7 @@
         <v>1.390623709969187</v>
       </c>
       <c r="D353" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E353">
         <v>0.1282184781408322</v>
@@ -19847,7 +19844,7 @@
         <v>1.100236160215024</v>
       </c>
       <c r="D354" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E354">
         <v>0.1282184781408322</v>
@@ -19897,7 +19894,7 @@
         <v>0.003795564238286531</v>
       </c>
       <c r="D355" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E355">
         <v>0.77667675619176</v>
@@ -19947,7 +19944,7 @@
         <v>1.338895251493001</v>
       </c>
       <c r="D356" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E356">
         <v>0.5272283520481338</v>
@@ -19997,7 +19994,7 @@
         <v>-0.04658110525333115</v>
       </c>
       <c r="D357" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E357">
         <v>0.7300850958569374</v>
@@ -20047,7 +20044,7 @@
         <v>5.252623163353501</v>
       </c>
       <c r="D358" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E358">
         <v>5.811442523768368</v>
@@ -20197,7 +20194,7 @@
         <v>5.155821953327571</v>
       </c>
       <c r="D361" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E361">
         <v>5.436800777873812</v>
@@ -20247,7 +20244,7 @@
         <v>5.21461106309421</v>
       </c>
       <c r="D362" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E362">
         <v>5.436800777873812</v>
@@ -20397,7 +20394,7 @@
         <v>5.996975409186557</v>
       </c>
       <c r="D365" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E365">
         <v>6.322440349888621</v>
@@ -20447,7 +20444,7 @@
         <v>6.04103615104905</v>
       </c>
       <c r="D366" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E366">
         <v>6.322440349888621</v>
@@ -20597,7 +20594,7 @@
         <v>6.467595657864342</v>
       </c>
       <c r="D369" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E369">
         <v>6.75843983370544</v>
@@ -20647,7 +20644,7 @@
         <v>6.50341596735699</v>
       </c>
       <c r="D370" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E370">
         <v>6.75843983370544</v>
@@ -20747,7 +20744,7 @@
         <v>7.038673370415092</v>
       </c>
       <c r="D372" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E372">
         <v>7.57711369319794</v>
@@ -20797,7 +20794,7 @@
         <v>6.933612348269409</v>
       </c>
       <c r="D373" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E373">
         <v>7.57711369319794</v>
@@ -20847,7 +20844,7 @@
         <v>7.041012886240821</v>
       </c>
       <c r="D374" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E374">
         <v>7.57711369319794</v>
@@ -20947,7 +20944,7 @@
         <v>7.603480524142883</v>
       </c>
       <c r="D376" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E376">
         <v>8.074842039131216</v>
@@ -20997,7 +20994,7 @@
         <v>7.583949919224556</v>
       </c>
       <c r="D377" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E377">
         <v>8.115780829294561</v>
@@ -21047,7 +21044,7 @@
         <v>7.602119009154551</v>
       </c>
       <c r="D378" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E378">
         <v>8.115780829294561</v>
@@ -21097,7 +21094,7 @@
         <v>7.596203554119548</v>
       </c>
       <c r="D379" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E379">
         <v>8.115780829294561</v>
@@ -21197,7 +21194,7 @@
         <v>8.197082757216956</v>
       </c>
       <c r="D381" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E381">
         <v>8.669626746773165</v>
@@ -21247,7 +21244,7 @@
         <v>8.20282687732055</v>
       </c>
       <c r="D382" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E382">
         <v>8.694010892986238</v>
@@ -21297,7 +21294,7 @@
         <v>8.194538767660747</v>
       </c>
       <c r="D383" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E383">
         <v>8.694010892986238</v>
@@ -21347,7 +21344,7 @@
         <v>8.192170736329373</v>
       </c>
       <c r="D384" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E384">
         <v>8.694010892986238</v>
@@ -21397,7 +21394,7 @@
         <v>-0.9277197529705248</v>
       </c>
       <c r="D385" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E385">
         <v>-1.43484711683287</v>
@@ -21447,7 +21444,7 @@
         <v>-1.739101844557563</v>
       </c>
       <c r="D386" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E386">
         <v>-1.225064022760026</v>
@@ -21497,7 +21494,7 @@
         <v>-1.67793665889768</v>
       </c>
       <c r="D387" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E387">
         <v>-1.225064022760026</v>
@@ -21547,7 +21544,7 @@
         <v>-1.660809295035333</v>
       </c>
       <c r="D388" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E388">
         <v>-0.9252809286871813</v>
@@ -21597,7 +21594,7 @@
         <v>-1.665172475723605</v>
       </c>
       <c r="D389" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E389">
         <v>-0.9252809286871813</v>
@@ -21647,7 +21644,7 @@
         <v>-0.8321510586103233</v>
       </c>
       <c r="D390" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E390">
         <v>-0.4166226922621714</v>
@@ -21697,7 +21694,7 @@
         <v>-3.843022818180284</v>
       </c>
       <c r="D391" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E391">
         <v>-3.26412423419014</v>
@@ -21747,7 +21744,7 @@
         <v>-3.712943072690754</v>
       </c>
       <c r="D392" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E392">
         <v>-3.26412423419014</v>
@@ -21797,7 +21794,7 @@
         <v>-4.087117010683363</v>
       </c>
       <c r="D393" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E393">
         <v>-3.293178553948453</v>
@@ -21847,7 +21844,7 @@
         <v>-2.768453907950921</v>
       </c>
       <c r="D394" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E394">
         <v>-2.083569770974329</v>
@@ -21897,7 +21894,7 @@
         <v>-2.698924870466321</v>
       </c>
       <c r="D395" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E395">
         <v>-2.083569770974329</v>
@@ -21947,7 +21944,7 @@
         <v>-5.897343766119011</v>
       </c>
       <c r="D396" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E396">
         <v>-5.21377186018452</v>
@@ -21997,7 +21994,7 @@
         <v>-5.892794919062931</v>
       </c>
       <c r="D397" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E397">
         <v>-5.287381083735886</v>
@@ -22047,7 +22044,7 @@
         <v>-6.281892613175087</v>
       </c>
       <c r="D398" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E398">
         <v>-5.383339366049038</v>
@@ -22097,7 +22094,7 @@
         <v>-4.84153475427336</v>
       </c>
       <c r="D399" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E399">
         <v>-4.085725742427703</v>
@@ -22147,7 +22144,7 @@
         <v>-4.665255930675347</v>
       </c>
       <c r="D400" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E400">
         <v>-4.085725742427703</v>
@@ -22197,7 +22194,7 @@
         <v>-7.494239379929031</v>
       </c>
       <c r="D401" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E401">
         <v>-6.751752878533589</v>
@@ -22247,7 +22244,7 @@
         <v>-7.492791301055105</v>
       </c>
       <c r="D402" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E402">
         <v>-6.850168247542195</v>
@@ -22297,7 +22294,7 @@
         <v>-7.875687458802952</v>
       </c>
       <c r="D403" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E403">
         <v>-6.901165391214095</v>
@@ -22347,7 +22344,7 @@
         <v>-6.346957706709796</v>
       </c>
       <c r="D404" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E404">
         <v>-5.984607757431821</v>
@@ -22397,7 +22394,7 @@
         <v>-6.382299087003467</v>
       </c>
       <c r="D405" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E405">
         <v>-5.984607757431821</v>
@@ -22447,7 +22444,7 @@
         <v>-8.194922154350412</v>
       </c>
       <c r="D406" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E406">
         <v>-7.42658522050059</v>
@@ -22497,7 +22494,7 @@
         <v>-8.155009684147785</v>
       </c>
       <c r="D407" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E407">
         <v>-7.535884982121567</v>
@@ -22547,7 +22544,7 @@
         <v>-8.575009684147785</v>
       </c>
       <c r="D408" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E408">
         <v>-7.567154164183544</v>
@@ -22597,7 +22594,7 @@
         <v>-7.007504283373057</v>
       </c>
       <c r="D409" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E409">
         <v>-6.779342409117989</v>
@@ -22647,7 +22644,7 @@
         <v>-7.019036054827168</v>
       </c>
       <c r="D410" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E410">
         <v>-6.779342409117989</v>
@@ -22697,7 +22694,7 @@
         <v>-8.936969711340112</v>
       </c>
       <c r="D411" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E411">
         <v>-8.141256265679017</v>
@@ -22747,7 +22744,7 @@
         <v>-8.895616372094786</v>
       </c>
       <c r="D412" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E412">
         <v>-8.262082979641582</v>
@@ -22797,7 +22794,7 @@
         <v>-9.315616372094786</v>
       </c>
       <c r="D413" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E413">
         <v>-8.272459560584432</v>
@@ -22947,7 +22944,7 @@
         <v>-8.948241366187794</v>
       </c>
       <c r="D416" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E416">
         <v>-8.152112073066304</v>
@@ -22997,7 +22994,7 @@
         <v>-8.90686614023403</v>
       </c>
       <c r="D417" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E417">
         <v>-8.273113880696405</v>
@@ -23047,7 +23044,7 @@
         <v>-9.32686614023403</v>
       </c>
       <c r="D418" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E418">
         <v>-7.892485491389962</v>
@@ -23097,7 +23094,7 @@
         <v>-7.646984587574911</v>
       </c>
       <c r="D419" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E419">
         <v>-7.178478260869557</v>
@@ -23147,7 +23144,7 @@
         <v>-7.393291551707726</v>
       </c>
       <c r="D420" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E420">
         <v>-7.178478260869557</v>
@@ -23197,7 +23194,7 @@
         <v>-9.216500648310582</v>
       </c>
       <c r="D421" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E421">
         <v>-8.410474410800093</v>
@@ -23233,7 +23230,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -23247,7 +23244,7 @@
         <v>-9.174604530546869</v>
       </c>
       <c r="D422" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E422">
         <v>-8.477110822973078</v>
@@ -23283,7 +23280,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -23297,7 +23294,7 @@
         <v>-9.594604530546869</v>
       </c>
       <c r="D423" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E423">
         <v>-8.147201586454123</v>
@@ -23333,7 +23330,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -23383,7 +23380,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -23433,7 +23430,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -23447,7 +23444,7 @@
         <v>-9.488460946517886</v>
       </c>
       <c r="D426" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E426">
         <v>-8.782113312812619</v>
@@ -23497,7 +23494,7 @@
         <v>-9.908460946517886</v>
       </c>
       <c r="D427" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E427">
         <v>-8.445792612543283</v>
@@ -23547,7 +23544,7 @@
         <v>-7.945711812235471</v>
       </c>
       <c r="D428" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E428">
         <v>-7.898110811850708</v>
@@ -23597,7 +23594,7 @@
         <v>-7.914350711812233</v>
       </c>
       <c r="D429" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E429">
         <v>-7.898110811850708</v>
@@ -23647,7 +23644,7 @@
         <v>-9.731958922090953</v>
       </c>
       <c r="D430" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E430">
         <v>-8.922781252412936</v>
@@ -23697,7 +23694,7 @@
         <v>-10.15195892209095</v>
       </c>
       <c r="D431" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E431">
         <v>-8.677447301366684</v>
@@ -23847,7 +23844,7 @@
         <v>-9.713150682287534</v>
       </c>
       <c r="D434" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E434">
         <v>-8.904576779062349</v>
@@ -23897,7 +23894,7 @@
         <v>-10.13315068228753</v>
       </c>
       <c r="D435" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E435">
         <v>-8.659553859219074</v>
@@ -24047,7 +24044,7 @@
         <v>-9.786103124815638</v>
       </c>
       <c r="D438" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E438">
         <v>-9.096428585475211</v>
@@ -24097,7 +24094,7 @@
         <v>-9.885452203496488</v>
       </c>
       <c r="D439" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E439">
         <v>-9.071347220310315</v>
@@ -24147,7 +24144,7 @@
         <v>-10.30545220349649</v>
       </c>
       <c r="D440" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E440">
         <v>-8.823474956244713</v>
@@ -24297,7 +24294,7 @@
         <v>-9.843764571794191</v>
       </c>
       <c r="D443" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E443">
         <v>-9.128491781807984</v>
@@ -24347,7 +24344,7 @@
         <v>-9.944492011757397</v>
       </c>
       <c r="D444" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E444">
         <v>-9.128491781807984</v>
@@ -24397,7 +24394,7 @@
         <v>-10.3644920117574</v>
       </c>
       <c r="D445" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E445">
         <v>-8.879643178500714</v>
@@ -24447,7 +24444,7 @@
         <v>-8.368915738537504</v>
       </c>
       <c r="D446" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E446">
         <v>-7.670672951950555</v>
@@ -24497,7 +24494,7 @@
         <v>-8.412127831876973</v>
       </c>
       <c r="D447" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E447">
         <v>-7.670672951950555</v>
@@ -24547,7 +24544,7 @@
         <v>-8.3229155085881</v>
       </c>
       <c r="D448" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E448">
         <v>-7.670672951950555</v>
@@ -24597,7 +24594,7 @@
         <v>-9.413850870677146</v>
       </c>
       <c r="D449" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E449">
         <v>-8.460862700719371</v>
@@ -24647,7 +24644,7 @@
         <v>-9.504301489099706</v>
       </c>
       <c r="D450" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E450">
         <v>-8.460862700719371</v>
@@ -24697,7 +24694,7 @@
         <v>-9.381313319141935</v>
       </c>
       <c r="D451" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E451">
         <v>-8.460862700719371</v>
@@ -24747,7 +24744,7 @@
         <v>-7.960412082296807</v>
       </c>
       <c r="D452" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E452">
         <v>-7.188091863543228</v>
@@ -24797,7 +24794,7 @@
         <v>-7.928542481965792</v>
       </c>
       <c r="D453" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E453">
         <v>-7.188091863543228</v>
@@ -24847,7 +24844,7 @@
         <v>-7.787273706198183</v>
       </c>
       <c r="D454" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E454">
         <v>-7.188091863543228</v>
@@ -24897,7 +24894,7 @@
         <v>-9.172895884074581</v>
       </c>
       <c r="D455" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E455">
         <v>-8.145576045355</v>
@@ -24947,7 +24944,7 @@
         <v>-9.058289567940399</v>
       </c>
       <c r="D456" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E456">
         <v>-8.145576045355</v>
@@ -24997,7 +24994,7 @@
         <v>-7.622862522769601</v>
       </c>
       <c r="D457" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E457">
         <v>-6.959864303403672</v>
@@ -25047,7 +25044,7 @@
         <v>-7.631631429214679</v>
       </c>
       <c r="D458" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E458">
         <v>-6.959864303403672</v>
@@ -25097,7 +25094,7 @@
         <v>-7.222167461470761</v>
       </c>
       <c r="D459" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E459">
         <v>-6.959864303403672</v>
@@ -25147,7 +25144,7 @@
         <v>-7.490685032440284</v>
       </c>
       <c r="D460" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E460">
         <v>-6.959864303403672</v>
@@ -25197,7 +25194,7 @@
         <v>-8.561827797884455</v>
       </c>
       <c r="D461" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E461">
         <v>-7.564229169582681</v>
@@ -25247,7 +25244,7 @@
         <v>-8.46267651116753</v>
       </c>
       <c r="D462" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E462">
         <v>-7.564229169582681</v>
@@ -25297,7 +25294,7 @@
         <v>-7.05578182799783</v>
       </c>
       <c r="D463" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E463">
         <v>-6.720998980224341</v>
@@ -25347,7 +25344,7 @@
         <v>-6.680647007658305</v>
       </c>
       <c r="D464" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E464">
         <v>-6.720998980224341</v>
@@ -25397,7 +25394,7 @@
         <v>-6.943814760752625</v>
       </c>
       <c r="D465" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E465">
         <v>-6.720998980224341</v>
@@ -25447,7 +25444,7 @@
         <v>-7.900748535322215</v>
       </c>
       <c r="D466" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E466">
         <v>-7.068198896242816</v>
@@ -25497,7 +25494,7 @@
         <v>-7.954473715782516</v>
       </c>
       <c r="D467" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E467">
         <v>-7.068198896242816</v>
@@ -25547,7 +25544,7 @@
         <v>-7.896025874307643</v>
       </c>
       <c r="D468" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E468">
         <v>-7.068198896242816</v>
@@ -25597,7 +25594,7 @@
         <v>-6.218598358361149</v>
       </c>
       <c r="D469" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E469">
         <v>-6.369374437623716</v>
@@ -25647,7 +25644,7 @@
         <v>-6.477201415688539</v>
       </c>
       <c r="D470" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E470">
         <v>-6.369374437623716</v>
@@ -25697,7 +25694,7 @@
         <v>-6.477356631541051</v>
       </c>
       <c r="D471" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E471">
         <v>-6.369374437623716</v>
@@ -25747,7 +25744,7 @@
         <v>0.1544375412573284</v>
       </c>
       <c r="D472" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E472">
         <v>0.7763231468178482</v>
@@ -25797,7 +25794,7 @@
         <v>0.162551935696813</v>
       </c>
       <c r="D473" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E473">
         <v>0.7763231468178482</v>
@@ -25847,7 +25844,7 @@
         <v>1.050094357938882</v>
       </c>
       <c r="D474" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E474">
         <v>0.5910371607191394</v>
@@ -26047,7 +26044,7 @@
         <v>-0.05317325947102702</v>
       </c>
       <c r="D478" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E478">
         <v>0.5712288406437764</v>
@@ -26097,7 +26094,7 @@
         <v>-0.04757535958582615</v>
       </c>
       <c r="D479" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E479">
         <v>0.5712288406437764</v>
@@ -26147,7 +26144,7 @@
         <v>0.8500330408733774</v>
       </c>
       <c r="D480" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E480">
         <v>0.392234090930776</v>
@@ -26347,7 +26344,7 @@
         <v>-0.2692961577804383</v>
       </c>
       <c r="D484" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E484">
         <v>0.3577256138290235</v>
@@ -26397,7 +26394,7 @@
         <v>-0.2663179293898956</v>
       </c>
       <c r="D485" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E485">
         <v>0.3577256138290235</v>
@@ -26447,7 +26444,7 @@
         <v>0.6417691570479445</v>
       </c>
       <c r="D486" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E486">
         <v>0.1852800428526731</v>
@@ -26647,7 +26644,7 @@
         <v>0.05587008030584961</v>
       </c>
       <c r="D490" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E490">
         <v>0.6789504429688105</v>
@@ -26697,7 +26694,7 @@
         <v>0.06278971764289132</v>
       </c>
       <c r="D491" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E491">
         <v>0.6789504429688105</v>
@@ -26747,7 +26744,7 @@
         <v>0.9551111682947298</v>
       </c>
       <c r="D492" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E492">
         <v>0.4966513496262088</v>
@@ -26947,7 +26944,7 @@
         <v>-0.1893348809203133</v>
       </c>
       <c r="D496" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E496">
         <v>0.4367176630908425</v>
@@ -26997,7 +26994,7 @@
         <v>-0.1853874249314682</v>
       </c>
       <c r="D497" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E497">
         <v>0.4367176630908425</v>
@@ -27047,7 +27044,7 @@
         <v>0.7188227511131551</v>
       </c>
       <c r="D498" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E498">
         <v>0.2618490231187316</v>
@@ -27247,7 +27244,7 @@
         <v>4.371485982915774</v>
       </c>
       <c r="D502" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E502">
         <v>4.962528234821984</v>
@@ -27297,7 +27294,7 @@
         <v>5.060047010261989</v>
       </c>
       <c r="D503" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E503">
         <v>4.670741844866129</v>
@@ -27447,7 +27444,7 @@
         <v>3.620560894635664</v>
       </c>
       <c r="D506" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E506">
         <v>4.229589376201279</v>
@@ -27497,7 +27494,7 @@
         <v>4.317639349991246</v>
       </c>
       <c r="D507" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E507">
         <v>3.938374978158294</v>
@@ -27547,7 +27544,7 @@
         <v>4.370574873318176</v>
       </c>
       <c r="D508" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E508">
         <v>3.818139087890952</v>
@@ -27647,7 +27644,7 @@
         <v>6.853299645934258</v>
       </c>
       <c r="D510" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E510">
         <v>5.774682369171286</v>
@@ -27697,7 +27694,7 @@
         <v>6.891491094566248</v>
       </c>
       <c r="D511" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E511">
         <v>5.774682369171286</v>
@@ -27747,7 +27744,7 @@
         <v>5.361224864970907</v>
       </c>
       <c r="D512" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E512">
         <v>5.018618668978591</v>
@@ -27797,7 +27794,7 @@
         <v>5.403937692022923</v>
       </c>
       <c r="D513" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E513">
         <v>5.018618668978591</v>
@@ -27847,7 +27844,7 @@
         <v>5.435905841926575</v>
       </c>
       <c r="D514" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E514">
         <v>5.018618668978591</v>
@@ -27897,7 +27894,7 @@
         <v>6.006575212731824</v>
       </c>
       <c r="D515" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E515">
         <v>5.049928678956259</v>
@@ -27933,7 +27930,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27947,7 +27944,7 @@
         <v>6.064211272564705</v>
       </c>
       <c r="D516" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E516">
         <v>5.049928678956259</v>
@@ -27983,7 +27980,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27997,7 +27994,7 @@
         <v>4.663870399629863</v>
       </c>
       <c r="D517" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E517">
         <v>4.316971023154751</v>
@@ -28033,7 +28030,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -28047,7 +28044,7 @@
         <v>4.677416309880542</v>
       </c>
       <c r="D518" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E518">
         <v>4.316971023154751</v>
@@ -28083,7 +28080,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -28097,7 +28094,7 @@
         <v>4.678449851055503</v>
       </c>
       <c r="D519" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E519">
         <v>4.316971023154751</v>
@@ -28133,7 +28130,7 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -28147,7 +28144,7 @@
         <v>5.45724271386503</v>
       </c>
       <c r="D520" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E520">
         <v>4.579727583892824</v>
@@ -28197,7 +28194,7 @@
         <v>5.527493925028882</v>
       </c>
       <c r="D521" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E521">
         <v>4.579727583892824</v>
@@ -28247,7 +28244,7 @@
         <v>4.201445199623705</v>
       </c>
       <c r="D522" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E522">
         <v>3.460664324521434</v>
@@ -28297,7 +28294,7 @@
         <v>4.150453975773659</v>
       </c>
       <c r="D523" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E523">
         <v>3.460664324521434</v>
@@ -28347,7 +28344,7 @@
         <v>4.187032365117255</v>
       </c>
       <c r="D524" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E524">
         <v>3.460664324521434</v>
@@ -28397,7 +28394,7 @@
         <v>4.42199553766301</v>
       </c>
       <c r="D525" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E525">
         <v>3.693607871486083</v>
@@ -28447,7 +28444,7 @@
         <v>4.365726240572206</v>
       </c>
       <c r="D526" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E526">
         <v>3.693607871486083</v>
@@ -28497,7 +28494,7 @@
         <v>4.516020692330457</v>
       </c>
       <c r="D527" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E527">
         <v>3.693607871486083</v>
@@ -28547,7 +28544,7 @@
         <v>3.247044122637031</v>
       </c>
       <c r="D528" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E528">
         <v>2.605123035361114</v>
@@ -28597,7 +28594,7 @@
         <v>3.194659905181848</v>
       </c>
       <c r="D529" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E529">
         <v>2.605123035361114</v>
@@ -28647,7 +28644,7 @@
         <v>-3.705984123275019</v>
       </c>
       <c r="D530" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E530">
         <v>-2.970035313701199</v>
@@ -28697,7 +28694,7 @@
         <v>-3.693186241046869</v>
       </c>
       <c r="D531" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E531">
         <v>-2.970035313701199</v>
@@ -28747,7 +28744,7 @@
         <v>-2.752427193387811</v>
       </c>
       <c r="D532" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E532">
         <v>-3.420167707261241</v>
@@ -28797,7 +28794,7 @@
         <v>-2.600361880106711</v>
       </c>
       <c r="D533" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E533">
         <v>-3.420167707261241</v>
@@ -28847,7 +28844,7 @@
         <v>-3.678102393980136</v>
       </c>
       <c r="D534" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E534">
         <v>-3.136716692222066</v>
@@ -28897,7 +28894,7 @@
         <v>-4.366813091974395</v>
       </c>
       <c r="D535" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E535">
         <v>-3.818652183810219</v>
@@ -28947,7 +28944,7 @@
         <v>-4.484310216846968</v>
       </c>
       <c r="D536" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E536">
         <v>-3.818652183810219</v>
@@ -28997,7 +28994,7 @@
         <v>-4.322051603836151</v>
       </c>
       <c r="D537" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E537">
         <v>-3.818652183810219</v>
@@ -29047,7 +29044,7 @@
         <v>-3.347068854600705</v>
       </c>
       <c r="D538" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E538">
         <v>-4.118163659577004</v>
@@ -29097,7 +29094,7 @@
         <v>-3.324798741080183</v>
       </c>
       <c r="D539" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E539">
         <v>-4.118163659577004</v>
@@ -29147,7 +29144,7 @@
         <v>-3.351387820544549</v>
       </c>
       <c r="D540" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E540">
         <v>-4.118163659577004</v>
@@ -29197,7 +29194,7 @@
         <v>-4.379071704985211</v>
       </c>
       <c r="D541" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E541">
         <v>-3.832482625520846</v>
@@ -29247,7 +29244,7 @@
         <v>8.995980915690074</v>
       </c>
       <c r="D542" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E542">
         <v>10.66390789578366</v>
@@ -29297,7 +29294,7 @@
         <v>11.51142958743078</v>
       </c>
       <c r="D543" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E543">
         <v>11.61008037782884</v>
@@ -29347,7 +29344,7 @@
         <v>11.33896292349641</v>
       </c>
       <c r="D544" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E544">
         <v>11.61008037782884</v>
@@ -29397,7 +29394,7 @@
         <v>11.25741689188049</v>
       </c>
       <c r="D545" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E545">
         <v>11.61008037782884</v>
@@ -29447,7 +29444,7 @@
         <v>11.28637455971803</v>
       </c>
       <c r="D546" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E546">
         <v>11.61008037782884</v>
@@ -29497,7 +29494,7 @@
         <v>9.394053857479914</v>
       </c>
       <c r="D547" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E547">
         <v>11.10574062904685</v>
@@ -29547,7 +29544,7 @@
         <v>11.96926052402832</v>
       </c>
       <c r="D548" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E548">
         <v>11.78545564208547</v>
@@ -29597,7 +29594,7 @@
         <v>11.76715013038619</v>
       </c>
       <c r="D549" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E549">
         <v>11.78545564208547</v>
@@ -29647,7 +29644,7 @@
         <v>11.79715013038619</v>
       </c>
       <c r="D550" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E550">
         <v>11.78545564208547</v>
@@ -29697,7 +29694,7 @@
         <v>11.75785102268897</v>
       </c>
       <c r="D551" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E551">
         <v>11.78545564208547</v>
@@ -29747,7 +29744,7 @@
         <v>6.4997071892945</v>
       </c>
       <c r="D552" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E552">
         <v>7.893221100174392</v>
@@ -29947,7 +29944,7 @@
         <v>8.621088353970423</v>
       </c>
       <c r="D556" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E556">
         <v>8.269277714135617</v>
@@ -29997,7 +29994,7 @@
         <v>8.578286988055545</v>
       </c>
       <c r="D557" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E557">
         <v>8.269277714135617</v>
@@ -30047,7 +30044,7 @@
         <v>8.739580302223263</v>
       </c>
       <c r="D558" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E558">
         <v>8.269277714135617</v>
@@ -30097,7 +30094,7 @@
         <v>8.957510999554914</v>
       </c>
       <c r="D559" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E559">
         <v>8.269277714135617</v>
@@ -30347,7 +30344,7 @@
         <v>1.438738012295818</v>
       </c>
       <c r="D564" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E564">
         <v>2.100412073152636</v>
@@ -30397,7 +30394,7 @@
         <v>1.573030977807695</v>
       </c>
       <c r="D565" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E565">
         <v>2.100412073152636</v>
@@ -30447,7 +30444,7 @@
         <v>1.547818547789148</v>
       </c>
       <c r="D566" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E566">
         <v>2.100412073152636</v>
@@ -30597,7 +30594,7 @@
         <v>-0.8761721984660475</v>
       </c>
       <c r="D569" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E569">
         <v>-1.556082773365931</v>
@@ -30647,7 +30644,7 @@
         <v>-1.017858379148869</v>
       </c>
       <c r="D570" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E570">
         <v>-1.556082773365931</v>
@@ -30697,7 +30694,7 @@
         <v>-0.5723250526030199</v>
       </c>
       <c r="D571" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E571">
         <v>-1.556082773365931</v>
@@ -30747,7 +30744,7 @@
         <v>-1.931822609108822</v>
       </c>
       <c r="D572" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E572">
         <v>-1.673095771397564</v>
@@ -30797,7 +30794,7 @@
         <v>-2.066468132763205</v>
       </c>
       <c r="D573" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E573">
         <v>-1.673095771397564</v>
@@ -30847,7 +30844,7 @@
         <v>-1.956055114369123</v>
       </c>
       <c r="D574" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E574">
         <v>-1.673095771397564</v>
@@ -30897,7 +30894,7 @@
         <v>-1.910907147220547</v>
       </c>
       <c r="D575" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E575">
         <v>-1.673095771397564</v>
@@ -30947,7 +30944,7 @@
         <v>-1.911499015814858</v>
       </c>
       <c r="D576" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E576">
         <v>-1.673095771397564</v>
@@ -30997,7 +30994,7 @@
         <v>-2.047060001357517</v>
       </c>
       <c r="D577" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E577">
         <v>-1.673095771397564</v>
@@ -31197,7 +31194,7 @@
         <v>-1.458250204365703</v>
       </c>
       <c r="D581" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E581">
         <v>-2.203959675076526</v>
@@ -31297,7 +31294,7 @@
         <v>-1.426121365901643</v>
       </c>
       <c r="D583" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E583">
         <v>-1.878985527382707</v>
@@ -31347,7 +31344,7 @@
         <v>-1.43657143149991</v>
       </c>
       <c r="D584" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E584">
         <v>-1.878985527382707</v>
@@ -31397,7 +31394,7 @@
         <v>-1.282291566067462</v>
       </c>
       <c r="D585" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E585">
         <v>-1.878985527382707</v>
@@ -31447,7 +31444,7 @@
         <v>-2.390900427299799</v>
       </c>
       <c r="D586" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E586">
         <v>-1.749918412157532</v>
@@ -31497,7 +31494,7 @@
         <v>-1.371342304503491</v>
       </c>
       <c r="D587" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E587">
         <v>-2.176137742690791</v>
@@ -31547,7 +31544,7 @@
         <v>-2.66184968886377</v>
       </c>
       <c r="D588" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E588">
         <v>-3.062340696434903</v>
@@ -31597,7 +31594,7 @@
         <v>-1.173473832043332</v>
       </c>
       <c r="D589" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E589">
         <v>-1.733424630557323</v>
@@ -31647,7 +31644,7 @@
         <v>-1.200137867726374</v>
       </c>
       <c r="D590" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E590">
         <v>-1.733424630557323</v>
@@ -31697,7 +31694,7 @@
         <v>-1.042228008991366</v>
       </c>
       <c r="D591" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E591">
         <v>-1.733424630557323</v>
@@ -31747,7 +31744,7 @@
         <v>-2.127604913087305</v>
       </c>
       <c r="D592" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E592">
         <v>-1.505014864011352</v>
@@ -31797,7 +31794,7 @@
         <v>-1.173621436501358</v>
       </c>
       <c r="D593" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E593">
         <v>-1.913326227585305</v>
@@ -31847,7 +31844,7 @@
         <v>-1.12934275099936</v>
       </c>
       <c r="D594" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E594">
         <v>-1.913326227585305</v>
@@ -31947,7 +31944,7 @@
         <v>-1.009918389553857</v>
       </c>
       <c r="D596" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E596">
         <v>-1.567675915850558</v>
@@ -31997,7 +31994,7 @@
         <v>-1.047078799419653</v>
       </c>
       <c r="D597" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E597">
         <v>-1.567675915850558</v>
@@ -32047,7 +32044,7 @@
         <v>-0.8868190061661174</v>
       </c>
       <c r="D598" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E598">
         <v>-1.567675915850558</v>
@@ -32097,7 +32094,7 @@
         <v>-1.957156329343485</v>
       </c>
       <c r="D599" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E599">
         <v>-1.346472615161401</v>
@@ -32147,7 +32144,7 @@
         <v>-1.016645810663759</v>
       </c>
       <c r="D600" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E600">
         <v>-1.743190968443955</v>
@@ -32197,7 +32194,7 @@
         <v>-0.9726804497642316</v>
       </c>
       <c r="D601" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E601">
         <v>-1.743190968443955</v>
@@ -32247,7 +32244,7 @@
         <v>-2.23129488574537</v>
       </c>
       <c r="D602" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E602">
         <v>-2.752324990932166</v>
@@ -32297,7 +32294,7 @@
         <v>-2.130775299238296</v>
       </c>
       <c r="D603" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E603">
         <v>-2.752324990932166</v>
@@ -32347,7 +32344,7 @@
         <v>-0.896848743456049</v>
       </c>
       <c r="D604" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E604">
         <v>-1.453090010130747</v>
@@ -32397,7 +32394,7 @@
         <v>-0.9412655386557081</v>
       </c>
       <c r="D605" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E605">
         <v>-1.453090010130747</v>
@@ -32447,7 +32444,7 @@
         <v>-0.7793811815214564</v>
       </c>
       <c r="D606" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E606">
         <v>-1.453090010130747</v>
@@ -32497,7 +32494,7 @@
         <v>-1.860567553008542</v>
       </c>
       <c r="D607" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E607">
         <v>-1.236868705342454</v>
@@ -32547,7 +32544,7 @@
         <v>-0.9081249434319556</v>
       </c>
       <c r="D608" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E608">
         <v>-1.625572543480143</v>
@@ -32597,7 +32594,7 @@
         <v>-0.8643761910498551</v>
       </c>
       <c r="D609" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E609">
         <v>-1.625572543480143</v>
@@ -32847,7 +32844,7 @@
         <v>2.369548064861299</v>
       </c>
       <c r="D614" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E614">
         <v>1.926875447544282</v>
@@ -32897,7 +32894,7 @@
         <v>2.406754555749798</v>
       </c>
       <c r="D615" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E615">
         <v>1.926875447544282</v>
@@ -32947,7 +32944,7 @@
         <v>2.636430011324778</v>
       </c>
       <c r="D616" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E616">
         <v>1.926875447544282</v>
@@ -33097,7 +33094,7 @@
         <v>1.522496508679898</v>
       </c>
       <c r="D619" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E619">
         <v>0.6622717696267184</v>
@@ -33147,7 +33144,7 @@
         <v>0.1531498180160149</v>
       </c>
       <c r="D620" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E620">
         <v>0.9108693301133393</v>
@@ -33197,7 +33194,7 @@
         <v>0.1409442431310648</v>
       </c>
       <c r="D621" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E621">
         <v>0.9108693301133393</v>
@@ -33247,7 +33244,7 @@
         <v>0.1454303059186906</v>
       </c>
       <c r="D622" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E622">
         <v>0.9108693301133393</v>
@@ -33297,7 +33294,7 @@
         <v>1.410955900715591</v>
       </c>
       <c r="D623" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E623">
         <v>0.5447199911733147</v>
@@ -33347,7 +33344,7 @@
         <v>0.02936423312947767</v>
       </c>
       <c r="D624" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E624">
         <v>0.7855252936185178</v>
@@ -33397,7 +33394,7 @@
         <v>0.01760393013260675</v>
       </c>
       <c r="D625" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E625">
         <v>0.7855252936185178</v>
@@ -33447,7 +33444,7 @@
         <v>0.02320317264043581</v>
       </c>
       <c r="D626" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E626">
         <v>0.7855252936185178</v>
@@ -33497,7 +33494,7 @@
         <v>1.411909103777088</v>
       </c>
       <c r="D627" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E627">
         <v>0.545724564459686</v>
@@ -33547,7 +33544,7 @@
         <v>0.03042207924163876</v>
       </c>
       <c r="D628" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E628">
         <v>0.7865964579371276</v>
@@ -33597,7 +33594,7 @@
         <v>0.0186579710429271</v>
       </c>
       <c r="D629" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E629">
         <v>0.7865964579371276</v>
@@ -33647,7 +33644,7 @@
         <v>0.02424770054614989</v>
       </c>
       <c r="D630" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E630">
         <v>0.7865964579371276</v>
@@ -33697,7 +33694,7 @@
         <v>1.336834708204746</v>
       </c>
       <c r="D631" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E631">
         <v>0.4666042433774571</v>
@@ -33747,7 +33744,7 @@
         <v>-0.05289401644343528</v>
       </c>
       <c r="D632" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E632">
         <v>0.7022314186013414</v>
@@ -33797,7 +33794,7 @@
         <v>-0.06435842645623069</v>
       </c>
       <c r="D633" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E633">
         <v>0.7022314186013414</v>
@@ -33847,7 +33844,7 @@
         <v>-0.05801945148821375</v>
       </c>
       <c r="D634" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E634">
         <v>0.7022314186013414</v>
@@ -33897,7 +33894,7 @@
         <v>1.405196855980458</v>
       </c>
       <c r="D635" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E635">
         <v>0.5386505787578475</v>
@@ -33947,7 +33944,7 @@
         <v>0.02297295793440135</v>
       </c>
       <c r="D636" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E636">
         <v>0.7790535527285396</v>
@@ -33997,7 +33994,7 @@
         <v>0.01123564513607533</v>
       </c>
       <c r="D637" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E637">
         <v>0.7790535527285396</v>
@@ -34047,7 +34044,7 @@
         <v>0.01689236314026132</v>
       </c>
       <c r="D638" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E638">
         <v>0.7790535527285396</v>
@@ -34097,7 +34094,7 @@
         <v>1.640062494593103</v>
       </c>
       <c r="D639" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E639">
         <v>0.786173646996323</v>
@@ -34147,7 +34144,7 @@
         <v>0.2836222494885536</v>
       </c>
       <c r="D640" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E640">
         <v>0.8556593002896253</v>
@@ -34197,7 +34194,7 @@
         <v>0.2709473493105357</v>
       </c>
       <c r="D641" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E641">
         <v>0.8556593002896253</v>
@@ -34247,7 +34244,7 @@
         <v>0.2742600988654935</v>
       </c>
       <c r="D642" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E642">
         <v>0.8556593002896253</v>
@@ -34297,7 +34294,7 @@
         <v>4.955952265919407</v>
       </c>
       <c r="D643" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E643">
         <v>3.781714175282632</v>
@@ -34347,7 +34344,7 @@
         <v>4.836984732824422</v>
       </c>
       <c r="D644" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E644">
         <v>3.781714175282632</v>
@@ -34397,7 +34394,7 @@
         <v>3.399157889651168</v>
       </c>
       <c r="D645" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E645">
         <v>4.104212001159528</v>
@@ -34447,7 +34444,7 @@
         <v>3.413995555126094</v>
       </c>
       <c r="D646" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E646">
         <v>4.104212001159528</v>
@@ -34497,7 +34494,7 @@
         <v>3.388941443617735</v>
       </c>
       <c r="D647" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E647">
         <v>4.104212001159528</v>
@@ -34597,7 +34594,7 @@
         <v>5.39157323691697</v>
       </c>
       <c r="D649" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E649">
         <v>4.199910307440291</v>
@@ -34647,7 +34644,7 @@
         <v>5.274981818209244</v>
       </c>
       <c r="D650" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E650">
         <v>4.199910307440291</v>
@@ -34697,7 +34694,7 @@
         <v>3.849827585101373</v>
       </c>
       <c r="D651" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E651">
         <v>4.558841887255165</v>
@@ -34747,7 +34744,7 @@
         <v>3.716953213901664</v>
       </c>
       <c r="D652" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E652">
         <v>4.558841887255165</v>
@@ -34797,7 +34794,7 @@
         <v>3.823770376486211</v>
       </c>
       <c r="D653" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E653">
         <v>4.558841887255165</v>
@@ -34847,7 +34844,7 @@
         <v>3.783996120363035</v>
       </c>
       <c r="D654" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E654">
         <v>4.558841887255165</v>
@@ -34897,7 +34894,7 @@
         <v>5.240670261409678</v>
       </c>
       <c r="D655" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E655">
         <v>5.66120447150224</v>
@@ -34947,7 +34944,7 @@
         <v>13.35754674285762</v>
       </c>
       <c r="D656" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E656">
         <v>12.11200719763176</v>
@@ -34997,7 +34994,7 @@
         <v>13.63116000592201</v>
       </c>
       <c r="D657" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E657">
         <v>12.11200719763176</v>
@@ -35047,7 +35044,7 @@
         <v>13.48645284737274</v>
       </c>
       <c r="D658" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E658">
         <v>12.11200719763176</v>
@@ -35097,7 +35094,7 @@
         <v>13.35488379452298</v>
       </c>
       <c r="D659" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E659">
         <v>12.11200719763176</v>
@@ -35297,7 +35294,7 @@
         <v>12.00063570730863</v>
       </c>
       <c r="D663" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E663">
         <v>10.96336131546034</v>
@@ -35347,7 +35344,7 @@
         <v>12.16808033477629</v>
       </c>
       <c r="D664" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E664">
         <v>10.96336131546034</v>
@@ -35397,7 +35394,7 @@
         <v>12.18508198198523</v>
       </c>
       <c r="D665" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E665">
         <v>10.96336131546034</v>
@@ -35447,7 +35444,7 @@
         <v>11.93759839099766</v>
       </c>
       <c r="D666" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E666">
         <v>10.96336131546034</v>
@@ -35497,7 +35494,7 @@
         <v>12.10741586438821</v>
       </c>
       <c r="D667" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E667">
         <v>10.96336131546034</v>
@@ -35547,7 +35544,7 @@
         <v>9.996138178122038</v>
       </c>
       <c r="D668" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E668">
         <v>10.07070134335836</v>
@@ -35597,7 +35594,7 @@
         <v>9.950336290139454</v>
       </c>
       <c r="D669" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E669">
         <v>10.07070134335836</v>
@@ -35647,7 +35644,7 @@
         <v>3.726163694975139</v>
       </c>
       <c r="D670" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E670">
         <v>2.839609794743838</v>
@@ -35683,7 +35680,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35697,7 +35694,7 @@
         <v>2.070333381900306</v>
       </c>
       <c r="D671" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E671">
         <v>2.539922141074908</v>
@@ -35733,7 +35730,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35747,7 +35744,7 @@
         <v>2.116517657129328</v>
       </c>
       <c r="D672" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E672">
         <v>2.539922141074908</v>
@@ -35783,7 +35780,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35797,7 +35794,7 @@
         <v>2.11502886699328</v>
       </c>
       <c r="D673" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E673">
         <v>2.539922141074908</v>
@@ -35833,7 +35830,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35847,7 +35844,7 @@
         <v>-1.891199427015522</v>
       </c>
       <c r="D674" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E674">
         <v>-1.014426804305828</v>
@@ -35897,7 +35894,7 @@
         <v>-0.2104376111309492</v>
       </c>
       <c r="D675" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E675">
         <v>-1.044462827056231</v>
@@ -35947,7 +35944,7 @@
         <v>-0.08646642933127069</v>
       </c>
       <c r="D676" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E676">
         <v>-1.044462827056231</v>
@@ -35997,7 +35994,7 @@
         <v>-1.78244121340599</v>
       </c>
       <c r="D677" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E677">
         <v>-1.021661386146215</v>
@@ -36047,7 +36044,7 @@
         <v>-1.791643374771013</v>
       </c>
       <c r="D678" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E678">
         <v>-1.021661386146215</v>
@@ -36147,7 +36144,7 @@
         <v>-3.477913686861863</v>
       </c>
       <c r="D680" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E680">
         <v>-4.521174267980019</v>
@@ -36197,7 +36194,7 @@
         <v>-3.500008845709822</v>
       </c>
       <c r="D681" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E681">
         <v>-4.521174267980019</v>
@@ -36247,7 +36244,7 @@
         <v>-5.32431700625196</v>
       </c>
       <c r="D682" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E682">
         <v>-4.437952967810602</v>
@@ -36447,7 +36444,7 @@
         <v>-7.577993318403742</v>
       </c>
       <c r="D686" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E686">
         <v>-6.567354813971781</v>
@@ -36497,7 +36494,7 @@
         <v>-7.616049006530655</v>
       </c>
       <c r="D687" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E687">
         <v>-6.567354813971781</v>
@@ -36547,7 +36544,7 @@
         <v>-2.725135055328662</v>
       </c>
       <c r="D688" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E688">
         <v>-2.204192425359905</v>
@@ -36597,7 +36594,7 @@
         <v>-2.704148294566643</v>
       </c>
       <c r="D689" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E689">
         <v>-2.204192425359905</v>
@@ -36647,7 +36644,7 @@
         <v>-1.813662855840759</v>
       </c>
       <c r="D690" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E690">
         <v>-2.111011489107529</v>
@@ -36697,7 +36694,7 @@
         <v>-1.845002662948879</v>
       </c>
       <c r="D691" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E691">
         <v>-2.111011489107529</v>
@@ -36747,7 +36744,7 @@
         <v>-1.891998249869552</v>
       </c>
       <c r="D692" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E692">
         <v>-2.111011489107529</v>
@@ -36797,7 +36794,7 @@
         <v>1.830334637155163</v>
       </c>
       <c r="D693" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E693">
         <v>2.267871354156875</v>
@@ -36897,7 +36894,7 @@
         <v>1.518226736005792</v>
       </c>
       <c r="D695" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E695">
         <v>1.938055203296901</v>
@@ -36947,7 +36944,7 @@
         <v>1.532693205245188</v>
       </c>
       <c r="D696" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E696">
         <v>1.906531480554312</v>
@@ -36997,7 +36994,7 @@
         <v>2.271617246908757</v>
       </c>
       <c r="D697" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E697">
         <v>2.443417201348617</v>
@@ -37047,7 +37044,7 @@
         <v>1.121481137909713</v>
       </c>
       <c r="D698" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E698">
         <v>1.518799216656364</v>
@@ -37097,7 +37094,7 @@
         <v>1.1435965093108</v>
       </c>
       <c r="D699" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E699">
         <v>1.506034151034157</v>
@@ -37147,7 +37144,7 @@
         <v>1.093271662200239</v>
       </c>
       <c r="D700" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E700">
         <v>1.506034151034157</v>
@@ -37197,7 +37194,7 @@
         <v>1.88237511166083</v>
       </c>
       <c r="D701" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E701">
         <v>1.894895897753045</v>
@@ -37247,7 +37244,7 @@
         <v>0.849444604521004</v>
       </c>
       <c r="D702" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E702">
         <v>1.303653302247787</v>
@@ -37297,7 +37294,7 @@
         <v>0.8477648181552304</v>
       </c>
       <c r="D703" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E703">
         <v>1.303653302247787</v>
@@ -37347,7 +37344,7 @@
         <v>0.7919735158820114</v>
       </c>
       <c r="D704" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E704">
         <v>1.303653302247787</v>
@@ -37447,7 +37444,7 @@
         <v>0.4742545585727438</v>
       </c>
       <c r="D706" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E706">
         <v>0.9209239764164039</v>
@@ -37497,7 +37494,7 @@
         <v>0.4776016477910456</v>
       </c>
       <c r="D707" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E707">
         <v>0.9209239764164039</v>
@@ -37547,7 +37544,7 @@
         <v>0.4397567303627969</v>
       </c>
       <c r="D708" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E708">
         <v>0.9209239764164039</v>
@@ -37597,7 +37594,7 @@
         <v>0.3764261482064555</v>
       </c>
       <c r="D709" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E709">
         <v>0.9209239764164039</v>
@@ -37647,7 +37644,7 @@
         <v>1.247389224131652</v>
       </c>
       <c r="D710" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E710">
         <v>1.332491309195859</v>
@@ -37697,7 +37694,7 @@
         <v>0.06936123169383812</v>
       </c>
       <c r="D711" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E711">
         <v>0.5078944952148738</v>
@@ -37747,7 +37744,7 @@
         <v>0.03202754929901275</v>
       </c>
       <c r="D712" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E712">
         <v>0.5078944952148738</v>
@@ -37797,7 +37794,7 @@
         <v>0.06067852147795705</v>
       </c>
       <c r="D713" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E713">
         <v>0.5078944952148738</v>
@@ -37847,7 +37844,7 @@
         <v>-0.07201953416415208</v>
       </c>
       <c r="D714" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E714">
         <v>0.5078944952148738</v>
@@ -37897,7 +37894,7 @@
         <v>0.07833359180957977</v>
       </c>
       <c r="D715" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E715">
         <v>0.4747573429780569</v>
@@ -37947,7 +37944,7 @@
         <v>0.07349428577797745</v>
       </c>
       <c r="D716" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E716">
         <v>0.4747573429780569</v>
@@ -37997,7 +37994,7 @@
         <v>0.8501534542622782</v>
       </c>
       <c r="D717" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E717">
         <v>0.8793612316938386</v>
@@ -38047,7 +38044,7 @@
         <v>1.041941578678037</v>
       </c>
       <c r="D718" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E718">
         <v>0.8793612316938386</v>
@@ -38097,7 +38094,7 @@
         <v>0.09878287093698646</v>
       </c>
       <c r="D719" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E719">
         <v>0.5379073494309932</v>
@@ -38147,7 +38144,7 @@
         <v>0.06440526340701602</v>
       </c>
       <c r="D720" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E720">
         <v>0.5379073494309932</v>
@@ -38197,7 +38194,7 @@
         <v>0.09312579028866175</v>
       </c>
       <c r="D721" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E721">
         <v>0.5379073494309932</v>
@@ -38247,7 +38244,7 @@
         <v>-0.03943315594804098</v>
       </c>
       <c r="D722" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E722">
         <v>0.5379073494309932</v>
@@ -38297,7 +38294,7 @@
         <v>0.109354989214884</v>
       </c>
       <c r="D723" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E723">
         <v>0.503900763410396</v>
@@ -38347,7 +38344,7 @@
         <v>0.1052807849130097</v>
       </c>
       <c r="D724" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E724">
         <v>0.503900763410396</v>
@@ -38497,7 +38494,7 @@
         <v>0.2871962372863237</v>
       </c>
       <c r="D727" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E727">
         <v>0.9851462492612573</v>
@@ -38547,7 +38544,7 @@
         <v>0.4202978053995725</v>
       </c>
       <c r="D728" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E728">
         <v>0.9851462492612573</v>
@@ -38597,7 +38594,7 @@
         <v>0.423892594321984</v>
       </c>
       <c r="D729" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E729">
         <v>0.9851462492612573</v>
@@ -38647,7 +38644,7 @@
         <v>0.4949561407287284</v>
       </c>
       <c r="D730" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E730">
         <v>0.9851462492612573</v>
@@ -38697,7 +38694,7 @@
         <v>0.4370951998607797</v>
       </c>
       <c r="D731" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E731">
         <v>0.9851462492612573</v>
@@ -38747,7 +38744,7 @@
         <v>0.4441837402800548</v>
       </c>
       <c r="D732" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E732">
         <v>0.9851462492612573</v>
@@ -38797,7 +38794,7 @@
         <v>1.300386876506556</v>
       </c>
       <c r="D733" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E733">
         <v>1.066703016477163</v>
@@ -38847,7 +38844,7 @@
         <v>1.387766562883906</v>
       </c>
       <c r="D734" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E734">
         <v>1.066703016477163</v>
@@ -38897,7 +38894,7 @@
         <v>1.3704879139321</v>
       </c>
       <c r="D735" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E735">
         <v>1.066703016477163</v>
@@ -38947,7 +38944,7 @@
         <v>1.275437395219328</v>
       </c>
       <c r="D736" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E736">
         <v>1.066703016477163</v>
@@ -38997,7 +38994,7 @@
         <v>1.361652497764391</v>
       </c>
       <c r="D737" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E737">
         <v>1.066703016477163</v>
@@ -39047,7 +39044,7 @@
         <v>1.930987869234452</v>
       </c>
       <c r="D738" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E738">
         <v>2.371871770269339</v>
@@ -39097,7 +39094,7 @@
         <v>1.92605256665067</v>
       </c>
       <c r="D739" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E739">
         <v>2.371871770269339</v>
@@ -39147,7 +39144,7 @@
         <v>1.931979302309637</v>
       </c>
       <c r="D740" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E740">
         <v>2.371871770269339</v>
@@ -39397,7 +39394,7 @@
         <v>1.929178123500783</v>
       </c>
       <c r="D745" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E745">
         <v>1.904587279830026</v>
@@ -39447,7 +39444,7 @@
         <v>1.854846069494888</v>
       </c>
       <c r="D746" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E746">
         <v>1.904587279830026</v>
@@ -39497,7 +39494,7 @@
         <v>1.986094439213979</v>
       </c>
       <c r="D747" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E747">
         <v>2.427791166532621</v>
@@ -39747,7 +39744,7 @@
         <v>1.979578720846286</v>
       </c>
       <c r="D752" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E752">
         <v>1.826397195864058</v>
@@ -39797,7 +39794,7 @@
         <v>1.907972820522667</v>
       </c>
       <c r="D753" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E753">
         <v>1.826397195864058</v>
@@ -40047,7 +40044,7 @@
         <v>2.097186801510141</v>
       </c>
       <c r="D758" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E758">
         <v>2.32091239377587</v>
@@ -40097,7 +40094,7 @@
         <v>2.031942288135359</v>
       </c>
       <c r="D759" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E759">
         <v>2.32091239377587</v>
@@ -40647,7 +40644,7 @@
         <v>2.417703574220445</v>
       </c>
       <c r="D770" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E770">
         <v>2.366004733779205</v>
@@ -40697,7 +40694,7 @@
         <v>2.369795720055587</v>
       </c>
       <c r="D771" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E771">
         <v>2.366004733779205</v>
@@ -40747,7 +40744,7 @@
         <v>2.268006981238599</v>
       </c>
       <c r="D772" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E772">
         <v>2.366004733779205</v>
@@ -40997,7 +40994,7 @@
         <v>2.653994288166441</v>
       </c>
       <c r="D777" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E777">
         <v>3.270325396942835</v>
@@ -41047,7 +41044,7 @@
         <v>3.683411667997373</v>
       </c>
       <c r="D778" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E778">
         <v>3.25827796154194</v>
@@ -41097,7 +41094,7 @@
         <v>3.70572139342618</v>
       </c>
       <c r="D779" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E779">
         <v>3.25827796154194</v>
@@ -41147,7 +41144,7 @@
         <v>3.758092829526726</v>
       </c>
       <c r="D780" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E780">
         <v>3.25827796154194</v>
@@ -41197,7 +41194,7 @@
         <v>3.738113399750641</v>
       </c>
       <c r="D781" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E781">
         <v>3.25827796154194</v>
@@ -41247,7 +41244,7 @@
         <v>2.866153368128345</v>
       </c>
       <c r="D782" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E782">
         <v>3.327619714376737</v>
@@ -41297,7 +41294,7 @@
         <v>2.707907697511514</v>
       </c>
       <c r="D783" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E783">
         <v>3.327619714376737</v>
@@ -41347,7 +41344,7 @@
         <v>3.773013759826179</v>
       </c>
       <c r="D784" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E784">
         <v>3.350810436248167</v>
@@ -41397,7 +41394,7 @@
         <v>3.799493645503623</v>
       </c>
       <c r="D785" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E785">
         <v>3.350810436248167</v>
@@ -41447,7 +41444,7 @@
         <v>3.854682757447843</v>
       </c>
       <c r="D786" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E786">
         <v>3.350810436248167</v>
@@ -41497,7 +41494,7 @@
         <v>3.834252499536769</v>
       </c>
       <c r="D787" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E787">
         <v>3.350810436248167</v>
@@ -41547,7 +41544,7 @@
         <v>2.950458229371047</v>
       </c>
       <c r="D788" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E788">
         <v>3.434578689402571</v>
@@ -41597,7 +41594,7 @@
         <v>2.80855507864752</v>
       </c>
       <c r="D789" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E789">
         <v>3.434578689402571</v>
@@ -41647,7 +41644,7 @@
         <v>4.059126950443869</v>
       </c>
       <c r="D790" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E790">
         <v>3.646280787816876</v>
@@ -41697,7 +41694,7 @@
         <v>4.098922795936224</v>
       </c>
       <c r="D791" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E791">
         <v>3.646280787816876</v>
@@ -41747,7 +41744,7 @@
         <v>4.163109178025654</v>
       </c>
       <c r="D792" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E792">
         <v>3.646280787816876</v>
@@ -41797,7 +41794,7 @@
         <v>4.141239356891347</v>
       </c>
       <c r="D793" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E793">
         <v>3.646280787816876</v>
@@ -41847,7 +41844,7 @@
         <v>3.219656552115741</v>
       </c>
       <c r="D794" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E794">
         <v>3.776115064114756</v>
@@ -41897,7 +41894,7 @@
         <v>3.129937568234435</v>
       </c>
       <c r="D795" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E795">
         <v>3.776115064114756</v>
@@ -41947,7 +41944,7 @@
         <v>4.587925539948646</v>
       </c>
       <c r="D796" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E796">
         <v>4.161392287167092</v>
@@ -41997,7 +41994,7 @@
         <v>4.61478704123244</v>
       </c>
       <c r="D797" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E797">
         <v>4.161392287167092</v>
@@ -42047,7 +42044,7 @@
         <v>4.62093591099028</v>
       </c>
       <c r="D798" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E798">
         <v>4.161392287167092</v>
@@ -42097,7 +42094,7 @@
         <v>4.700807783315709</v>
       </c>
       <c r="D799" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E799">
         <v>4.161392287167092</v>
@@ -42147,7 +42144,7 @@
         <v>4.676428283743642</v>
       </c>
       <c r="D800" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E800">
         <v>4.161392287167092</v>
@@ -42197,7 +42194,7 @@
         <v>3.68896641997684</v>
       </c>
       <c r="D801" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E801">
         <v>4.371536273473288</v>
@@ -42247,7 +42244,7 @@
         <v>3.690223279464329</v>
       </c>
       <c r="D802" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E802">
         <v>4.371536273473288</v>
@@ -42297,7 +42294,7 @@
         <v>4.640951769621907</v>
       </c>
       <c r="D803" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E803">
         <v>4.4619926496501</v>
@@ -42347,7 +42344,7 @@
         <v>4.679892441845094</v>
       </c>
       <c r="D804" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E804">
         <v>4.229657336851623</v>
@@ -42397,7 +42394,7 @@
         <v>4.69011559593246</v>
       </c>
       <c r="D805" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E805">
         <v>4.229657336851623</v>
@@ -42447,7 +42444,7 @@
         <v>4.772066184752546</v>
       </c>
       <c r="D806" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E806">
         <v>4.229657336851623</v>
@@ -42497,7 +42494,7 @@
         <v>4.747354090541334</v>
       </c>
       <c r="D807" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E807">
         <v>4.229657336851623</v>
@@ -42547,7 +42544,7 @@
         <v>3.751161617496972</v>
       </c>
       <c r="D808" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E808">
         <v>4.450444351610463</v>
@@ -42597,7 +42594,7 @@
         <v>3.764475032653471</v>
       </c>
       <c r="D809" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E809">
         <v>4.450444351610463</v>
@@ -42647,7 +42644,7 @@
         <v>4.722853199511387</v>
       </c>
       <c r="D810" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E810">
         <v>4.494475032653471</v>
@@ -42697,7 +42694,7 @@
         <v>4.769412494689534</v>
       </c>
       <c r="D811" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E811">
         <v>4.258529056637524</v>
@@ -42747,7 +42744,7 @@
         <v>4.719374147530353</v>
       </c>
       <c r="D812" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E812">
         <v>4.258529056637524</v>
@@ -42797,7 +42794,7 @@
         <v>4.802203899559511</v>
       </c>
       <c r="D813" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E813">
         <v>4.258529056637524</v>
@@ -42847,7 +42844,7 @@
         <v>4.777351139234847</v>
       </c>
       <c r="D814" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E814">
         <v>4.258529056637524</v>
@@ -42897,7 +42894,7 @@
         <v>3.777466180712386</v>
       </c>
       <c r="D815" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E815">
         <v>4.483817387026809</v>
@@ -42947,7 +42944,7 @@
         <v>3.795878742481499</v>
       </c>
       <c r="D816" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E816">
         <v>4.483817387026809</v>
@@ -43047,7 +43044,7 @@
         <v>4.79820132156508</v>
       </c>
       <c r="D818" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E818">
         <v>4.288184799253363</v>
@@ -43097,7 +43094,7 @@
         <v>4.833160015785789</v>
       </c>
       <c r="D819" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E819">
         <v>4.288184799253363</v>
@@ -43147,7 +43144,7 @@
         <v>4.80816276950441</v>
       </c>
       <c r="D820" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E820">
         <v>4.288184799253363</v>
@@ -43197,7 +43194,7 @@
         <v>3.804485054618168</v>
       </c>
       <c r="D821" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E821">
         <v>4.518096680257542</v>
@@ -43247,7 +43244,7 @@
         <v>3.828135232318215</v>
       </c>
       <c r="D822" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E822">
         <v>4.518096680257542</v>
@@ -43297,7 +43294,7 @@
         <v>4.793071896789968</v>
       </c>
       <c r="D823" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E823">
         <v>4.976887297607179</v>
@@ -43347,7 +43344,7 @@
         <v>4.969372152154773</v>
       </c>
       <c r="D824" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E824">
         <v>4.976887297607179</v>
@@ -43397,7 +43394,7 @@
         <v>4.88512898189049</v>
       </c>
       <c r="D825" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E825">
         <v>4.377730105560969</v>
@@ -43447,7 +43444,7 @@
         <v>4.926631791066686</v>
       </c>
       <c r="D826" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E826">
         <v>4.377730105560969</v>
@@ -43497,7 +43494,7 @@
         <v>4.901198270454942</v>
       </c>
       <c r="D827" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E827">
         <v>4.377730105560969</v>
@@ -43547,7 +43544,7 @@
         <v>3.886068354396595</v>
       </c>
       <c r="D828" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E828">
         <v>4.621602765136856</v>
@@ -43597,7 +43594,7 @@
         <v>3.925533476572406</v>
       </c>
       <c r="D829" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E829">
         <v>4.621602765136856</v>
@@ -43647,7 +43644,7 @@
         <v>4.900504450642575</v>
       </c>
       <c r="D830" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E830">
         <v>5.323640452137244</v>
@@ -43697,7 +43694,7 @@
         <v>5.068842699478202</v>
       </c>
       <c r="D831" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E831">
         <v>5.323640452137244</v>
@@ -43747,7 +43744,7 @@
         <v>4.666640897343765</v>
       </c>
       <c r="D832" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E832">
         <v>4.152662706046714</v>
@@ -43797,7 +43794,7 @@
         <v>4.691695419101137</v>
       </c>
       <c r="D833" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E833">
         <v>4.152662706046714</v>
@@ -43847,7 +43844,7 @@
         <v>4.667358450983981</v>
       </c>
       <c r="D834" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E834">
         <v>4.152662706046714</v>
@@ -43897,7 +43894,7 @@
         <v>3.681013037908578</v>
       </c>
       <c r="D835" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E835">
         <v>4.361445685795776</v>
@@ -43947,7 +43944,7 @@
         <v>3.680728132155562</v>
       </c>
       <c r="D836" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E836">
         <v>4.361445685795776</v>
@@ -43997,7 +43994,7 @@
         <v>4.715209316235119</v>
       </c>
       <c r="D837" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E837">
         <v>5.110369355335455</v>
@@ -44047,7 +44044,7 @@
         <v>4.818828730712063</v>
       </c>
       <c r="D838" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E838">
         <v>5.110369355335455</v>
@@ -44097,7 +44094,7 @@
         <v>4.677780979452113</v>
       </c>
       <c r="D839" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E839">
         <v>4.139332770280262</v>
@@ -44133,7 +44130,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -44147,7 +44144,7 @@
         <v>4.685525171192977</v>
       </c>
       <c r="D840" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E840">
         <v>4.139332770280262</v>
@@ -44183,7 +44180,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -44197,7 +44194,7 @@
         <v>3.668868346126232</v>
       </c>
       <c r="D841" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E841">
         <v>4.346037514002399</v>
@@ -44233,7 +44230,7 @@
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -44247,7 +44244,7 @@
         <v>3.666229188623965</v>
       </c>
       <c r="D842" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E842">
         <v>4.346037514002399</v>
@@ -44283,7 +44280,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -44297,7 +44294,7 @@
         <v>4.699557601157337</v>
       </c>
       <c r="D843" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E843">
         <v>5.177220717987302</v>
@@ -44333,7 +44330,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -44347,7 +44344,7 @@
         <v>4.80402129902022</v>
       </c>
       <c r="D844" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E844">
         <v>5.177220717987302</v>
@@ -44383,7 +44380,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -44397,7 +44394,7 @@
         <v>3.803770388208568</v>
       </c>
       <c r="D845" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E845">
         <v>4.517189971136271</v>
@@ -44433,7 +44430,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44447,7 +44444,7 @@
         <v>3.827282027634027</v>
       </c>
       <c r="D846" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E846">
         <v>4.517189971136271</v>
@@ -44483,7 +44480,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44497,7 +44494,7 @@
         <v>4.873415313145802</v>
       </c>
       <c r="D847" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E847">
         <v>5.19492340011272</v>
@@ -44533,7 +44530,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44547,7 +44544,7 @@
         <v>4.968500794179431</v>
       </c>
       <c r="D848" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E848">
         <v>5.19492340011272</v>
@@ -44583,7 +44580,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44597,7 +44594,7 @@
         <v>4.15270680227816</v>
       </c>
       <c r="D849" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E849">
         <v>4.95989138417376</v>
@@ -44647,7 +44644,7 @@
         <v>4.243859858869514</v>
       </c>
       <c r="D850" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E850">
         <v>4.95989138417376</v>
@@ -44697,7 +44694,7 @@
         <v>5.32311411416597</v>
       </c>
       <c r="D851" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E851">
         <v>5.313449235585522</v>
@@ -44747,7 +44744,7 @@
         <v>5.393941983526312</v>
       </c>
       <c r="D852" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E852">
         <v>5.313449235585522</v>
@@ -44797,7 +44794,7 @@
         <v>4.427422884586818</v>
       </c>
       <c r="D853" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E853">
         <v>5.308428231915627</v>
@@ -44847,7 +44844,7 @@
         <v>4.571829727187204</v>
       </c>
       <c r="D854" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E854">
         <v>5.308428231915627</v>
@@ -44997,7 +44994,7 @@
         <v>4.492909746290213</v>
       </c>
       <c r="D857" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E857">
         <v>5.391512498969801</v>
@@ -45047,7 +45044,7 @@
         <v>4.650011234541658</v>
       </c>
       <c r="D858" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E858">
         <v>5.391512498969801</v>
@@ -45097,7 +45094,7 @@
         <v>5.699620454673608</v>
       </c>
       <c r="D859" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E859">
         <v>5.584366029175103</v>
@@ -45147,7 +45144,7 @@
         <v>5.808734877829779</v>
       </c>
       <c r="D860" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E860">
         <v>5.584366029175103</v>
@@ -45197,7 +45194,7 @@
         <v>4.400292583551392</v>
       </c>
       <c r="D861" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E861">
         <v>5.274007569238329</v>
@@ -45247,7 +45244,7 @@
         <v>4.539440210041969</v>
       </c>
       <c r="D862" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E862">
         <v>5.274007569238329</v>
@@ -45297,7 +45294,7 @@
         <v>5.577658014435989</v>
       </c>
       <c r="D863" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E863">
         <v>5.419384274951261</v>
@@ -45347,7 +45344,7 @@
         <v>5.695811278340734</v>
       </c>
       <c r="D864" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E864">
         <v>5.419384274951261</v>
@@ -45397,7 +45394,7 @@
         <v>4.244834847003374</v>
       </c>
       <c r="D865" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E865">
         <v>5.076775761772995</v>
@@ -45447,7 +45444,7 @@
         <v>4.353846949697878</v>
       </c>
       <c r="D866" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E866">
         <v>5.076775761772995</v>
@@ -45497,7 +45494,7 @@
         <v>5.441845979293118</v>
       </c>
       <c r="D867" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E867">
         <v>5.241229035520813</v>
@@ -45547,7 +45544,7 @@
         <v>5.506269225223365</v>
       </c>
       <c r="D868" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E868">
         <v>5.241229035520813</v>
@@ -45597,7 +45594,7 @@
         <v>4.273702172751312</v>
       </c>
       <c r="D869" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E869">
         <v>5.113400216498656</v>
@@ -45647,7 +45644,7 @@
         <v>4.38831021426059</v>
       </c>
       <c r="D870" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E870">
         <v>5.113400216498656</v>
@@ -45697,7 +45694,7 @@
         <v>5.479049324240996</v>
       </c>
       <c r="D871" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E871">
         <v>5.245636638515749</v>
@@ -45747,7 +45744,7 @@
         <v>5.54146575073422</v>
       </c>
       <c r="D872" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E872">
         <v>5.245636638515749</v>
@@ -45797,7 +45794,7 @@
         <v>5.560572351202844</v>
       </c>
       <c r="D873" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E873">
         <v>5.245636638515749</v>
@@ -45847,7 +45844,7 @@
         <v>4.347094984058314</v>
       </c>
       <c r="D874" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E874">
         <v>5.206514892876123</v>
@@ -45897,7 +45894,7 @@
         <v>4.475930241663201</v>
       </c>
       <c r="D875" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E875">
         <v>5.206514892876123</v>
@@ -45947,7 +45944,7 @@
         <v>5.573635781593871</v>
       </c>
       <c r="D876" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E876">
         <v>5.027134568809939</v>
@@ -45997,7 +45994,7 @@
         <v>5.630950034039015</v>
       </c>
       <c r="D877" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E877">
         <v>5.027134568809939</v>
@@ -46047,7 +46044,7 @@
         <v>5.633670806314765</v>
       </c>
       <c r="D878" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E878">
         <v>5.027134568809939</v>
@@ -46097,7 +46094,7 @@
         <v>5.402224156621893</v>
       </c>
       <c r="D879" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E879">
         <v>5.844101410902759</v>
@@ -46147,7 +46144,7 @@
         <v>5.365845252056308</v>
       </c>
       <c r="D880" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E880">
         <v>5.844101410902759</v>
@@ -46197,7 +46194,7 @@
         <v>5.351830183888868</v>
       </c>
       <c r="D881" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E881">
         <v>5.844101410902759</v>
@@ -46247,7 +46244,7 @@
         <v>6.177027170255381</v>
       </c>
       <c r="D882" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E882">
         <v>5.99166223366742</v>
@@ -46297,7 +46294,7 @@
         <v>6.176389906463717</v>
       </c>
       <c r="D883" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E883">
         <v>5.99166223366742</v>
@@ -46347,7 +46344,7 @@
         <v>6.145283329101833</v>
       </c>
       <c r="D884" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E884">
         <v>5.99166223366742</v>
@@ -46397,7 +46394,7 @@
         <v>6.120874288201371</v>
       </c>
       <c r="D885" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E885">
         <v>5.99166223366742</v>
@@ -46447,7 +46444,7 @@
         <v>5.357680894209214</v>
       </c>
       <c r="D886" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E886">
         <v>5.805234021262887</v>
@@ -46497,7 +46494,7 @@
         <v>5.321733849528515</v>
       </c>
       <c r="D887" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E887">
         <v>5.805234021262887</v>
@@ -46547,7 +46544,7 @@
         <v>5.307410310014729</v>
       </c>
       <c r="D888" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E888">
         <v>5.805234021262887</v>
@@ -46597,7 +46594,7 @@
         <v>6.132545602111971</v>
       </c>
       <c r="D889" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E889">
         <v>5.861451650138072</v>
@@ -46647,7 +46644,7 @@
         <v>6.135239828860867</v>
       </c>
       <c r="D890" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E890">
         <v>5.861451650138072</v>
@@ -46697,7 +46694,7 @@
         <v>6.106045773846343</v>
       </c>
       <c r="D891" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E891">
         <v>5.861451650138072</v>
@@ -46747,7 +46744,7 @@
         <v>6.081451650138071</v>
       </c>
       <c r="D892" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E892">
         <v>5.861451650138072</v>
@@ -46797,7 +46794,7 @@
         <v>5.32659332168792</v>
       </c>
       <c r="D893" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E893">
         <v>5.778107746071176</v>
@@ -46847,7 +46844,7 @@
         <v>5.290947680064908</v>
       </c>
       <c r="D894" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E894">
         <v>5.778107746071176</v>
@@ -46897,7 +46894,7 @@
         <v>5.276408852652773</v>
       </c>
       <c r="D895" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E895">
         <v>5.778107746071176</v>
@@ -46947,7 +46944,7 @@
         <v>6.101501087170347</v>
       </c>
       <c r="D896" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E896">
         <v>5.779952436422644</v>
@@ -46997,7 +46994,7 @@
         <v>6.10652042322139</v>
       </c>
       <c r="D897" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E897">
         <v>5.779952436422644</v>
@@ -47047,7 +47044,7 @@
         <v>6.078661153176616</v>
       </c>
       <c r="D898" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E898">
         <v>5.779952436422644</v>
@@ -47097,7 +47094,7 @@
         <v>6.053937856729336</v>
       </c>
       <c r="D899" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E899">
         <v>5.779952436422644</v>
@@ -47147,7 +47144,7 @@
         <v>5.388093706617724</v>
       </c>
       <c r="D900" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E900">
         <v>5.831771516854801</v>
@@ -47197,7 +47194,7 @@
         <v>5.351851800874894</v>
       </c>
       <c r="D901" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E901">
         <v>5.831771516854801</v>
@@ -47247,7 +47244,7 @@
         <v>5.337738876405488</v>
       </c>
       <c r="D902" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E902">
         <v>5.831771516854801</v>
@@ -47297,7 +47294,7 @@
         <v>6.162916291511607</v>
       </c>
       <c r="D903" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E903">
         <v>5.809432743446582</v>
@@ -47347,7 +47344,7 @@
         <v>6.163335875781195</v>
       </c>
       <c r="D904" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E904">
         <v>5.809432743446582</v>
@@ -47397,7 +47394,7 @@
         <v>6.132836007491512</v>
       </c>
       <c r="D905" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E905">
         <v>5.809432743446582</v>
@@ -47447,7 +47444,7 @@
         <v>6.10836825280987</v>
       </c>
       <c r="D906" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E906">
         <v>5.809432743446582</v>
@@ -47497,7 +47494,7 @@
         <v>5.504130795560521</v>
       </c>
       <c r="D907" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E907">
         <v>5.933022716347823</v>
@@ -47547,7 +47544,7 @@
         <v>5.46676387648999</v>
       </c>
       <c r="D908" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E908">
         <v>5.933022716347823</v>
@@ -47597,7 +47594,7 @@
         <v>5.453454532968942</v>
       </c>
       <c r="D909" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E909">
         <v>5.933022716347823</v>
@@ -47647,7 +47644,7 @@
         <v>6.278792664264731</v>
       </c>
       <c r="D910" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E910">
         <v>5.82295074691097</v>
@@ -47697,7 +47694,7 @@
         <v>6.270533574292061</v>
       </c>
       <c r="D911" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E911">
         <v>5.82295074691097</v>
@@ -47747,7 +47744,7 @@
         <v>6.235051504122564</v>
       </c>
       <c r="D912" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E912">
         <v>5.854447210967837</v>
@@ -47797,7 +47794,7 @@
         <v>6.211065898009934</v>
       </c>
       <c r="D913" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E913">
         <v>5.854447210967837</v>
@@ -47847,7 +47844,7 @@
         <v>5.527008554379917</v>
       </c>
       <c r="D914" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E914">
         <v>5.952985303683308</v>
@@ -47897,7 +47894,7 @@
         <v>5.489419828783438</v>
       </c>
       <c r="D915" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E915">
         <v>5.952985303683308</v>
@@ -47947,7 +47944,7 @@
         <v>5.47626891849521</v>
       </c>
       <c r="D916" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E916">
         <v>5.952985303683308</v>
@@ -47997,7 +47994,7 @@
         <v>6.301638736437564</v>
       </c>
       <c r="D917" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E917">
         <v>5.842438034547991</v>
@@ -48047,7 +48044,7 @@
         <v>6.291668567550424</v>
       </c>
       <c r="D918" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E918">
         <v>5.842438034547991</v>
@@ -48097,7 +48094,7 @@
         <v>6.255204211337434</v>
       </c>
       <c r="D919" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E919">
         <v>5.805943847222144</v>
@@ -48147,7 +48144,7 @@
         <v>6.231313665164498</v>
       </c>
       <c r="D920" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E920">
         <v>5.805943847222144</v>
@@ -48197,7 +48194,7 @@
         <v>5.362358580199855</v>
       </c>
       <c r="D921" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E921">
         <v>5.809315658623142</v>
@@ -48247,7 +48244,7 @@
         <v>5.326366183992933</v>
       </c>
       <c r="D922" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E922">
         <v>5.809315658623142</v>
@@ -48297,7 +48294,7 @@
         <v>5.31207503842645</v>
       </c>
       <c r="D923" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E923">
         <v>5.809315658623142</v>
@@ -48347,7 +48344,7 @@
         <v>6.137216809313153</v>
       </c>
       <c r="D924" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E924">
         <v>5.660449825716769</v>
@@ -48397,7 +48394,7 @@
         <v>6.139561181431169</v>
       </c>
       <c r="D925" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E925">
         <v>5.660449825716769</v>
@@ -48447,7 +48444,7 @@
         <v>6.110166283943363</v>
       </c>
       <c r="D926" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E926">
         <v>5.660449825716769</v>
@@ -48497,7 +48494,7 @@
         <v>6.085591596603473</v>
       </c>
       <c r="D927" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E927">
         <v>5.660449825716769</v>
@@ -48547,7 +48544,7 @@
         <v>5.21583595429709</v>
       </c>
       <c r="D928" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E928">
         <v>5.6814635058271</v>
@@ -48597,7 +48594,7 @@
         <v>5.181264137565678</v>
       </c>
       <c r="D929" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E929">
         <v>5.6814635058271</v>
@@ -48647,7 +48644,7 @@
         <v>5.16595829237383</v>
       </c>
       <c r="D930" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E930">
         <v>5.6814635058271</v>
@@ -48697,7 +48694,7 @@
         <v>5.990897123335461</v>
       </c>
       <c r="D931" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E931">
         <v>5.530974153520144</v>
@@ -48747,7 +48744,7 @@
         <v>6.00595829237383</v>
       </c>
       <c r="D932" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E932">
         <v>5.530974153520144</v>
@@ -48797,7 +48794,7 @@
         <v>6.004200251407424</v>
       </c>
       <c r="D933" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E933">
         <v>5.530974153520144</v>
@@ -48847,7 +48844,7 @@
         <v>5.981096491596882</v>
       </c>
       <c r="D934" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E934">
         <v>5.530974153520144</v>
@@ -48897,7 +48894,7 @@
         <v>5.955912984481774</v>
       </c>
       <c r="D935" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E935">
         <v>5.530974153520144</v>
@@ -48947,7 +48944,7 @@
         <v>5.246905622239758</v>
       </c>
       <c r="D936" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E936">
         <v>5.708574157910038</v>
@@ -48997,7 +48994,7 @@
         <v>5.212032576040759</v>
       </c>
       <c r="D937" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E937">
         <v>5.708574157910038</v>
@@ -49047,7 +49044,7 @@
         <v>5.19694189475433</v>
       </c>
       <c r="D938" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E938">
         <v>5.708574157910038</v>
@@ -49097,7 +49094,7 @@
         <v>6.021923758497046</v>
       </c>
       <c r="D939" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E939">
         <v>5.558429067851753</v>
@@ -49147,7 +49144,7 @@
         <v>6.03694189475433</v>
       </c>
       <c r="D940" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E940">
         <v>5.558429067851753</v>
@@ -49197,7 +49194,7 @@
         <v>6.032903116390471</v>
       </c>
       <c r="D941" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E941">
         <v>5.558429067851753</v>
@@ -49247,7 +49244,7 @@
         <v>6.008465340366325</v>
       </c>
       <c r="D942" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E942">
         <v>5.558429067851753</v>
@@ -49297,7 +49294,7 @@
         <v>5.983410931594468</v>
       </c>
       <c r="D943" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E943">
         <v>5.558429067851753</v>
@@ -49347,7 +49344,7 @@
         <v>5.260021169191447</v>
       </c>
       <c r="D944" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E944">
         <v>5.720018471732149</v>
@@ -49397,7 +49394,7 @@
         <v>5.22502096394998</v>
       </c>
       <c r="D945" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E945">
         <v>5.720018471732149</v>
@@ -49447,7 +49444,7 @@
         <v>5.210021110551029</v>
       </c>
       <c r="D946" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E946">
         <v>5.720018471732149</v>
@@ -49497,7 +49494,7 @@
         <v>6.035021139871239</v>
       </c>
       <c r="D947" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E947">
         <v>5.570018706293828</v>
@@ -49547,7 +49544,7 @@
         <v>6.050021110551029</v>
       </c>
       <c r="D948" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E948">
         <v>5.570018706293828</v>
@@ -49597,7 +49594,7 @@
         <v>6.045019556579911</v>
       </c>
       <c r="D949" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E949">
         <v>5.570018706293828</v>
@@ -49647,7 +49644,7 @@
         <v>6.020018647653407</v>
       </c>
       <c r="D950" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E950">
         <v>5.570018706293828</v>
@@ -49697,7 +49694,7 @@
         <v>5.995018735614037</v>
       </c>
       <c r="D951" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E951">
         <v>5.570018706293828</v>
@@ -49797,7 +49794,7 @@
         <v>5.615668781285493</v>
       </c>
       <c r="D953" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E953">
         <v>6.030348105553824</v>
@@ -49847,7 +49844,7 @@
         <v>5.577220469001563</v>
       </c>
       <c r="D954" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E954">
         <v>6.030348105553824</v>
@@ -49897,7 +49894,7 @@
         <v>5.56468354920437</v>
       </c>
       <c r="D955" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E955">
         <v>6.030348105553824</v>
@@ -49947,7 +49944,7 @@
         <v>6.390176165244933</v>
       </c>
       <c r="D956" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E956">
         <v>5.917958864945399</v>
@@ -49997,7 +49994,7 @@
         <v>6.373574899054605</v>
       </c>
       <c r="D957" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E957">
         <v>5.917958864945399</v>
@@ -50047,7 +50044,7 @@
         <v>6.333303801797193</v>
       </c>
       <c r="D958" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E958">
         <v>5.884289033878317</v>
@@ -50097,7 +50094,7 @@
         <v>6.309781649918879</v>
       </c>
       <c r="D959" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E959">
         <v>5.884289033878317</v>
@@ -50147,7 +50144,7 @@
         <v>6.262613928093605</v>
       </c>
       <c r="D960" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E960">
         <v>6.212195151647427</v>
@@ -50197,7 +50194,7 @@
         <v>7.24816372476549</v>
       </c>
       <c r="D961" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E961">
         <v>7.595603386150444</v>
@@ -50247,7 +50244,7 @@
         <v>7.261638134101141</v>
       </c>
       <c r="D962" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E962">
         <v>7.595603386150444</v>
@@ -50297,7 +50294,7 @@
         <v>7.253775244709231</v>
       </c>
       <c r="D963" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E963">
         <v>7.595603386150444</v>
@@ -50347,7 +50344,7 @@
         <v>8.181523875261066</v>
       </c>
       <c r="D964" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E964">
         <v>7.445946162670672</v>
@@ -50397,7 +50394,7 @@
         <v>8.030757870733884</v>
       </c>
       <c r="D965" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E965">
         <v>7.445946162670672</v>
@@ -50447,7 +50444,7 @@
         <v>7.913466275542353</v>
       </c>
       <c r="D966" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E966">
         <v>7.567169202558158</v>
@@ -50497,7 +50494,7 @@
         <v>7.897397720238308</v>
       </c>
       <c r="D967" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E967">
         <v>7.567169202558158</v>
@@ -50547,7 +50544,7 @@
         <v>7.886369390677626</v>
       </c>
       <c r="D968" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E968">
         <v>7.567169202558158</v>
@@ -50597,7 +50594,7 @@
         <v>6.461998806928756</v>
       </c>
       <c r="D969" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E969">
         <v>6.809943004706455</v>
@@ -50647,7 +50644,7 @@
         <v>6.455649148235951</v>
       </c>
       <c r="D970" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E970">
         <v>6.809943004706455</v>
@@ -50697,7 +50694,7 @@
         <v>7.28237921649739</v>
       </c>
       <c r="D971" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E971">
         <v>6.678991980784874</v>
@@ -50747,7 +50744,7 @@
         <v>7.198955530379694</v>
       </c>
       <c r="D972" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E972">
         <v>6.678991980784874</v>
@@ -50797,7 +50794,7 @@
         <v>7.120323414275088</v>
       </c>
       <c r="D973" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E973">
         <v>6.757814301673794</v>
@@ -50847,7 +50844,7 @@
         <v>7.100513619059405</v>
       </c>
       <c r="D974" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E974">
         <v>6.757814301673794</v>
@@ -50897,7 +50894,7 @@
         <v>5.391263694581674</v>
       </c>
       <c r="D975" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E975">
         <v>4.981328216936646</v>
@@ -50947,7 +50944,7 @@
         <v>5.376664084342806</v>
       </c>
       <c r="D976" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E976">
         <v>5.183908869880363</v>
@@ -50997,7 +50994,7 @@
         <v>4.255036972488333</v>
       </c>
       <c r="D977" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E977">
         <v>4.585738592012135</v>
@@ -51033,7 +51030,7 @@
         <v>1</v>
       </c>
       <c r="P977" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="978" spans="1:16">
@@ -51083,7 +51080,7 @@
         <v>1</v>
       </c>
       <c r="P978" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="979" spans="1:16">
@@ -51097,7 +51094,7 @@
         <v>3.887235867264729</v>
       </c>
       <c r="D979" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E979">
         <v>4.261316022454437</v>
@@ -51133,7 +51130,7 @@
         <v>1</v>
       </c>
       <c r="P979" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="980" spans="1:16">
@@ -51147,7 +51144,7 @@
         <v>4.52226704989957</v>
       </c>
       <c r="D980" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E980">
         <v>4.566623250498453</v>
@@ -51183,7 +51180,7 @@
         <v>1</v>
       </c>
       <c r="P980" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="981" spans="1:16">
@@ -51197,7 +51194,7 @@
         <v>3.595471601271687</v>
       </c>
       <c r="D981" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E981">
         <v>4.003962492151604</v>
@@ -51233,7 +51230,7 @@
         <v>1</v>
       </c>
       <c r="P981" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="982" spans="1:16">
@@ -51247,7 +51244,7 @@
         <v>4.274122026330736</v>
       </c>
       <c r="D982" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E982">
         <v>4.284760163047268</v>
@@ -51283,7 +51280,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -51297,7 +51294,7 @@
         <v>3.51283445556241</v>
       </c>
       <c r="D983" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E983">
         <v>3.931071587879801</v>
@@ -51333,7 +51330,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -51347,7 +51344,7 @@
         <v>4.203839271176003</v>
       </c>
       <c r="D984" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E984">
         <v>4.224910004360815</v>
@@ -51383,7 +51380,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -51397,7 +51394,7 @@
         <v>3.757771340160315</v>
       </c>
       <c r="D985" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E985">
         <v>4.020831110855603</v>
@@ -51433,7 +51430,7 @@
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="986" spans="1:16">
@@ -51447,7 +51444,7 @@
         <v>3.577092549221526</v>
       </c>
       <c r="D986" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E986">
         <v>3.987751069163838</v>
@@ -51483,7 +51480,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -51533,7 +51530,7 @@
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51547,7 +51544,7 @@
         <v>3.969181490046898</v>
       </c>
       <c r="D988" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E988">
         <v>4.227966423152568</v>
@@ -51583,7 +51580,7 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="989" spans="1:16">
@@ -51597,7 +51594,7 @@
         <v>3.987966423152567</v>
       </c>
       <c r="D989" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E989">
         <v>4.227966423152568</v>
@@ -51633,7 +51630,7 @@
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="990" spans="1:16">
@@ -51683,7 +51680,7 @@
         <v>1</v>
       </c>
       <c r="P990" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="991" spans="1:16">
@@ -51697,7 +51694,7 @@
         <v>4.457464931808846</v>
       </c>
       <c r="D991" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E991">
         <v>4.34281674843841</v>
@@ -51733,7 +51730,7 @@
         <v>1</v>
       </c>
       <c r="P991" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="992" spans="1:16">
@@ -51747,7 +51744,7 @@
         <v>4.129665945672787</v>
       </c>
       <c r="D992" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E992">
         <v>4.385205788683081</v>
@@ -51897,7 +51894,7 @@
         <v>4.608509125339094</v>
       </c>
       <c r="D995" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E995">
         <v>4.501722471963149</v>
@@ -51947,7 +51944,7 @@
         <v>4.165381741025112</v>
       </c>
       <c r="D996" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E996">
         <v>4.420199389644091</v>
@@ -52197,7 +52194,7 @@
         <v>4.358277886497062</v>
       </c>
       <c r="D1001" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E1001">
         <v>4.609195061586275</v>
@@ -52397,7 +52394,7 @@
         <v>4.823673304938412</v>
       </c>
       <c r="D1005" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E1005">
         <v>4.78043513295729</v>
@@ -52447,7 +52444,7 @@
         <v>4.773780937032344</v>
       </c>
       <c r="D1006" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E1006">
         <v>4.78043513295729</v>
@@ -52497,7 +52494,7 @@
         <v>4.76066910325774</v>
       </c>
       <c r="D1007" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E1007">
         <v>4.78043513295729</v>
@@ -52547,7 +52544,7 @@
         <v>4.781010705652122</v>
       </c>
       <c r="D1008" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E1008">
         <v>4.78043513295729</v>
@@ -52597,7 +52594,7 @@
         <v>6.134818623398694</v>
       </c>
       <c r="D1009" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E1009">
         <v>5.774464332861776</v>
@@ -52647,7 +52644,7 @@
         <v>6.102771384660437</v>
       </c>
       <c r="D1010" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E1010">
         <v>5.778795004029567</v>
@@ -52697,7 +52694,7 @@
         <v>5.514582429707415</v>
       </c>
       <c r="D1011" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E1011">
         <v>5.241133593669833</v>
@@ -52747,7 +52744,7 @@
         <v>6.089893354328455</v>
       </c>
       <c r="D1012" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1012">
         <v>5.69937873528254</v>
@@ -52797,7 +52794,7 @@
         <v>6.090496725476864</v>
       </c>
       <c r="D1013" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1013">
         <v>5.69937873528254</v>
@@ -52847,7 +52844,7 @@
         <v>6.083345023798447</v>
       </c>
       <c r="D1014" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1014">
         <v>5.69937873528254</v>
@@ -52897,7 +52894,7 @@
         <v>6.151446158250724</v>
       </c>
       <c r="D1015" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E1015">
         <v>5.740368070715386</v>
@@ -52947,7 +52944,7 @@
         <v>5.471792219876177</v>
       </c>
       <c r="D1016" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E1016">
         <v>5.499161328418567</v>
@@ -52997,7 +52994,7 @@
         <v>5.429161328418567</v>
       </c>
       <c r="D1017" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E1017">
         <v>5.499161328418567</v>
@@ -53047,7 +53044,7 @@
         <v>5.859820355215962</v>
       </c>
       <c r="D1018" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1018">
         <v>5.498824536056178</v>
@@ -53097,7 +53094,7 @@
         <v>5.962203814850136</v>
       </c>
       <c r="D1019" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1019">
         <v>5.498824536056178</v>
@@ -53147,7 +53144,7 @@
         <v>5.867235562966728</v>
       </c>
       <c r="D1020" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1020">
         <v>5.498824536056178</v>
@@ -53197,7 +53194,7 @@
         <v>5.864221779328541</v>
       </c>
       <c r="D1021" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1021">
         <v>5.498824536056178</v>
@@ -53247,7 +53244,7 @@
         <v>5.891472824538594</v>
       </c>
       <c r="D1022" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1022">
         <v>5.498824536056178</v>
@@ -53297,7 +53294,7 @@
         <v>5.933527959091345</v>
       </c>
       <c r="D1023" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E1023">
         <v>5.516806571577774</v>
@@ -53447,7 +53444,7 @@
         <v>5.536448803884926</v>
       </c>
       <c r="D1026" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1026">
         <v>5.114647162880539</v>
@@ -53497,7 +53494,7 @@
         <v>5.473079556721592</v>
       </c>
       <c r="D1027" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1027">
         <v>5.114647162880539</v>
@@ -53547,7 +53544,7 @@
         <v>5.516088475684048</v>
       </c>
       <c r="D1028" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E1028">
         <v>5.088556902345189</v>
@@ -53597,7 +53594,7 @@
         <v>4.87693542544124</v>
       </c>
       <c r="D1029" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E1029">
         <v>4.790484836705014</v>
@@ -53647,7 +53644,7 @@
         <v>4.782412771064838</v>
       </c>
       <c r="D1030" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E1030">
         <v>4.790484836705014</v>
@@ -53697,7 +53694,7 @@
         <v>5.183884767385427</v>
       </c>
       <c r="D1031" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1031">
         <v>4.796513208070444</v>
@@ -53747,7 +53744,7 @@
         <v>5.146682382306041</v>
       </c>
       <c r="D1032" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1032">
         <v>4.796513208070444</v>
@@ -53797,7 +53794,7 @@
         <v>5.170410455522431</v>
       </c>
       <c r="D1033" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E1033">
         <v>4.733927060944326</v>
@@ -53847,7 +53844,7 @@
         <v>4.433208070443044</v>
       </c>
       <c r="D1034" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E1034">
         <v>4.48045274908133</v>
@@ -53897,7 +53894,7 @@
         <v>4.430537336199128</v>
       </c>
       <c r="D1035" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E1035">
         <v>4.48045274908133</v>
@@ -53947,7 +53944,7 @@
         <v>6.107518054315049</v>
       </c>
       <c r="D1036" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1036">
         <v>5.738203236233369</v>
@@ -53997,7 +53994,7 @@
         <v>6.135203726571758</v>
       </c>
       <c r="D1037" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1037">
         <v>5.738203236233369</v>
@@ -54047,7 +54044,7 @@
         <v>6.102046072361725</v>
       </c>
       <c r="D1038" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1038">
         <v>5.738203236233369</v>
@@ -54097,7 +54094,7 @@
         <v>6.120488810422401</v>
       </c>
       <c r="D1039" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1039">
         <v>5.738203236233369</v>
@@ -54147,7 +54144,7 @@
         <v>6.193632087855306</v>
       </c>
       <c r="D1040" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E1040">
         <v>5.783646464632436</v>
@@ -54197,7 +54194,7 @@
         <v>5.378974678814465</v>
       </c>
       <c r="D1041" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E1041">
         <v>5.579789251726952</v>
@@ -54247,7 +54244,7 @@
         <v>5.416732234956823</v>
       </c>
       <c r="D1042" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E1042">
         <v>5.579789251726952</v>
@@ -54297,7 +54294,7 @@
         <v>5.472103579470241</v>
       </c>
       <c r="D1043" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E1043">
         <v>5.579789251726952</v>
@@ -54347,7 +54344,7 @@
         <v>5.430560694308047</v>
       </c>
       <c r="D1044" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E1044">
         <v>5.579789251726952</v>
@@ -54397,7 +54394,7 @@
         <v>5.402846268497081</v>
       </c>
       <c r="D1045" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E1045">
         <v>5.579789251726952</v>
@@ -54483,7 +54480,7 @@
         <v>1</v>
       </c>
       <c r="P1046" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="1047" spans="1:16">
@@ -54533,7 +54530,7 @@
         <v>1</v>
       </c>
       <c r="P1047" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="1048" spans="1:16">
@@ -54547,7 +54544,7 @@
         <v>5.020295300931229</v>
       </c>
       <c r="D1048" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E1048">
         <v>5.342572941191464</v>
@@ -54583,7 +54580,7 @@
         <v>1</v>
       </c>
       <c r="P1048" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="1049" spans="1:16">
@@ -54597,7 +54594,7 @@
         <v>5.54274578942891</v>
       </c>
       <c r="D1049" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E1049">
         <v>5.322745789428909</v>
@@ -54633,7 +54630,7 @@
         <v>1</v>
       </c>
       <c r="P1049" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="1050" spans="1:16">
@@ -54647,7 +54644,7 @@
         <v>5.6130914859038</v>
       </c>
       <c r="D1050" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E1050">
         <v>5.322745789428909</v>
@@ -54683,7 +54680,7 @@
         <v>1</v>
       </c>
       <c r="P1050" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="1051" spans="1:16">
@@ -54697,7 +54694,7 @@
         <v>5.147961849725716</v>
       </c>
       <c r="D1051" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E1051">
         <v>5.187875425606993</v>
@@ -54733,7 +54730,7 @@
         <v>1</v>
       </c>
       <c r="P1051" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="1052" spans="1:16">
@@ -54747,7 +54744,7 @@
         <v>4.481259603973901</v>
       </c>
       <c r="D1052" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E1052">
         <v>4.729065207154505</v>
@@ -54797,7 +54794,7 @@
         <v>4.933966438698594</v>
       </c>
       <c r="D1053" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E1053">
         <v>4.713966438698593</v>
@@ -54847,7 +54844,7 @@
         <v>4.545092978128704</v>
       </c>
       <c r="D1054" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E1054">
         <v>4.51376890178677</v>
@@ -54897,7 +54894,7 @@
         <v>4.556417054470637</v>
       </c>
       <c r="D1055" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E1055">
         <v>4.51376890178677</v>
@@ -54947,7 +54944,7 @@
         <v>4.521721707925945</v>
       </c>
       <c r="D1056" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E1056">
         <v>4.242337996671525</v>
@@ -54997,7 +54994,7 @@
         <v>3.995431662159355</v>
       </c>
       <c r="D1057" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E1057">
         <v>4.028576685042651</v>
@@ -55047,7 +55044,7 @@
         <v>4.0220812096942</v>
       </c>
       <c r="D1058" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E1058">
         <v>4.028576685042651</v>
@@ -55097,7 +55094,7 @@
         <v>3.998833472019975</v>
       </c>
       <c r="D1059" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E1059">
         <v>4.028576685042651</v>
@@ -55147,7 +55144,7 @@
         <v>2.312870417300224</v>
       </c>
       <c r="D1060" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E1060">
         <v>2.600174015881064</v>
@@ -55197,7 +55194,7 @@
         <v>2.342806217266434</v>
       </c>
       <c r="D1061" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E1061">
         <v>2.600174015881064</v>
@@ -55247,7 +55244,7 @@
         <v>2.333191417469171</v>
       </c>
       <c r="D1062" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E1062">
         <v>2.600174015881064</v>
@@ -55297,7 +55294,7 @@
         <v>2.830944416286538</v>
       </c>
       <c r="D1063" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E1063">
         <v>2.501072816354117</v>
@@ -55347,7 +55344,7 @@
         <v>3.735551545505884</v>
       </c>
       <c r="D1064" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E1064">
         <v>3.537025852544748</v>
@@ -55397,7 +55394,7 @@
         <v>3.727025852544749</v>
       </c>
       <c r="D1065" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E1065">
         <v>3.537025852544748</v>
@@ -55447,7 +55444,7 @@
         <v>3.707843043382194</v>
       </c>
       <c r="D1066" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E1066">
         <v>3.537025852544748</v>
@@ -55497,7 +55494,7 @@
         <v>3.371288699025316</v>
       </c>
       <c r="D1067" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E1067">
         <v>3.571768922933395</v>
@@ -55547,7 +55544,7 @@
         <v>3.36981439198645</v>
       </c>
       <c r="D1068" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E1068">
         <v>3.571768922933395</v>
@@ -55597,7 +55594,7 @@
         <v>3.347025852544749</v>
       </c>
       <c r="D1069" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E1069">
         <v>3.571768922933395</v>
@@ -55647,7 +55644,7 @@
         <v>3.718820308855666</v>
       </c>
       <c r="D1070" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E1070">
         <v>3.501608848297368</v>
@@ -55697,7 +55694,7 @@
         <v>7.818784706417835</v>
       </c>
       <c r="D1071" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E1071">
         <v>8.66434683659535</v>
@@ -55747,10 +55744,10 @@
         <v>7.736183913922513</v>
       </c>
       <c r="D1072" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E1072">
-        <v>8.573611117566397</v>
+        <v>8.114051730148025</v>
       </c>
       <c r="F1072">
         <v>-1</v>
@@ -55759,10 +55756,10 @@
         <v>0.008803816086077486</v>
       </c>
       <c r="H1072">
-        <v>0.009746388882433604</v>
+        <v>0.009205948269851974</v>
       </c>
       <c r="I1072">
-        <v>-0.8374272036438839</v>
+        <v>-0.3778678162255122</v>
       </c>
       <c r="J1072">
         <v>0.1011015314540694</v>
@@ -55774,10 +55771,10 @@
         <v>8.27</v>
       </c>
       <c r="M1072">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="N1072">
-        <v>9.16</v>
+        <v>8.66</v>
       </c>
       <c r="O1072">
         <v>1</v>
@@ -55797,10 +55794,10 @@
         <v>7.679650110425902</v>
       </c>
       <c r="D1073" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E1073">
-        <v>7.798469241305181</v>
+        <v>8.056233067481037</v>
       </c>
       <c r="F1073">
         <v>-1</v>
@@ -55809,10 +55806,10 @@
         <v>0.008860349889574097</v>
       </c>
       <c r="H1073">
-        <v>0.009001530758694819</v>
+        <v>0.009263766932518964</v>
       </c>
       <c r="I1073">
-        <v>-0.1188191308792792</v>
+        <v>-0.3765829570551347</v>
       </c>
       <c r="J1073">
         <v>0.1118086912072155</v>
@@ -55824,10 +55821,10 @@
         <v>8.27</v>
       </c>
       <c r="M1073">
-        <v>5.38</v>
+        <v>5.4</v>
       </c>
       <c r="N1073">
-        <v>8.4</v>
+        <v>8.66</v>
       </c>
       <c r="O1073">
         <v>1</v>
@@ -55847,10 +55844,10 @@
         <v>7.708161827974112</v>
       </c>
       <c r="D1074" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E1074">
-        <v>7.827520953503925</v>
+        <v>8.085392778609888</v>
       </c>
       <c r="F1074">
         <v>-1</v>
@@ -55859,10 +55856,10 @@
         <v>0.008831838172025886</v>
       </c>
       <c r="H1074">
-        <v>0.008972479046496075</v>
+        <v>0.009234607221390112</v>
       </c>
       <c r="I1074">
-        <v>-0.1193591255298134</v>
+        <v>-0.3772309506357763</v>
       </c>
       <c r="J1074">
         <v>0.1064087447018726</v>
@@ -55874,10 +55871,10 @@
         <v>8.27</v>
       </c>
       <c r="M1074">
-        <v>5.38</v>
+        <v>5.4</v>
       </c>
       <c r="N1074">
-        <v>8.4</v>
+        <v>8.66</v>
       </c>
       <c r="O1074">
         <v>1</v>
@@ -55897,10 +55894,10 @@
         <v>7.759275228935607</v>
       </c>
       <c r="D1075" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E1075">
-        <v>7.879602411301812</v>
+        <v>8.137667847775052</v>
       </c>
       <c r="F1075">
         <v>-1</v>
@@ -55909,10 +55906,10 @@
         <v>0.008780724771064393</v>
       </c>
       <c r="H1075">
-        <v>0.008920397588698189</v>
+        <v>0.009182332152224948</v>
       </c>
       <c r="I1075">
-        <v>-0.1203271823662053</v>
+        <v>-0.3783926188394453</v>
       </c>
       <c r="J1075">
         <v>0.09672817633795312</v>
@@ -55924,10 +55921,10 @@
         <v>8.27</v>
       </c>
       <c r="M1075">
-        <v>5.38</v>
+        <v>5.4</v>
       </c>
       <c r="N1075">
-        <v>8.4</v>
+        <v>8.66</v>
       </c>
       <c r="O1075">
         <v>1</v>
@@ -55947,10 +55944,10 @@
         <v>6.733361778130565</v>
       </c>
       <c r="D1076" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E1076">
-        <v>6.83425878150425</v>
+        <v>7.088438182178987</v>
       </c>
       <c r="F1076">
         <v>-1</v>
@@ -55959,10 +55956,10 @@
         <v>0.009806638221869434</v>
       </c>
       <c r="H1076">
-        <v>0.009965741218495751</v>
+        <v>0.01023156181782101</v>
       </c>
       <c r="I1076">
-        <v>-0.1008970033736851</v>
+        <v>-0.3550764040484218</v>
       </c>
       <c r="J1076">
         <v>0.2910299662631506</v>
@@ -55974,10 +55971,10 @@
         <v>8.27</v>
       </c>
       <c r="M1076">
-        <v>5.38</v>
+        <v>5.4</v>
       </c>
       <c r="N1076">
-        <v>8.4</v>
+        <v>8.66</v>
       </c>
       <c r="O1076">
         <v>1</v>
@@ -55997,10 +55994,10 @@
         <v>6.759036860879887</v>
       </c>
       <c r="D1077" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E1077">
-        <v>6.860420134760188</v>
+        <v>7.114696789536248</v>
       </c>
       <c r="F1077">
         <v>-1</v>
@@ -56009,10 +56006,10 @@
         <v>0.009780963139120113</v>
       </c>
       <c r="H1077">
-        <v>0.009939579865239813</v>
+        <v>0.01020530321046375</v>
       </c>
       <c r="I1077">
-        <v>-0.1013832738803018</v>
+        <v>-0.3556599286563618</v>
       </c>
       <c r="J1077">
         <v>0.2861672611969911</v>
@@ -56024,16 +56021,16 @@
         <v>8.27</v>
       </c>
       <c r="M1077">
-        <v>5.38</v>
+        <v>5.4</v>
       </c>
       <c r="N1077">
-        <v>8.4</v>
+        <v>8.66</v>
       </c>
       <c r="O1077">
         <v>1</v>
       </c>
       <c r="P1077" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="1078" spans="1:16">
@@ -56047,10 +56044,10 @@
         <v>6.737244367417659</v>
       </c>
       <c r="D1078" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E1078">
-        <v>6.838214904679358</v>
+        <v>7.092409012131696</v>
       </c>
       <c r="F1078">
         <v>-1</v>
@@ -56059,10 +56056,10 @@
         <v>0.00980275563258234</v>
       </c>
       <c r="H1078">
-        <v>0.009961785095320643</v>
+        <v>0.0102275909878683</v>
       </c>
       <c r="I1078">
-        <v>-0.1009705372616994</v>
+        <v>-0.355164644714038</v>
       </c>
       <c r="J1078">
         <v>0.2902946273830191</v>
@@ -56074,10 +56071,10 @@
         <v>8.27</v>
       </c>
       <c r="M1078">
-        <v>5.38</v>
+        <v>5.4</v>
       </c>
       <c r="N1078">
-        <v>8.4</v>
+        <v>8.66</v>
       </c>
       <c r="O1078">
         <v>1</v>
@@ -56097,10 +56094,10 @@
         <v>6.024441462215994</v>
       </c>
       <c r="D1079" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E1079">
-        <v>6.111911944454935</v>
+        <v>6.363406040902722</v>
       </c>
       <c r="F1079">
         <v>-1</v>
@@ -56109,10 +56106,10 @@
         <v>0.01051555853778401</v>
       </c>
       <c r="H1079">
-        <v>0.01068808805554507</v>
+        <v>0.01095659395909728</v>
       </c>
       <c r="I1079">
-        <v>-0.08747048223894094</v>
+        <v>-0.3389645786867277</v>
       </c>
       <c r="J1079">
         <v>0.4252951776106071</v>
@@ -56124,10 +56121,10 @@
         <v>8.27</v>
       </c>
       <c r="M1079">
-        <v>5.38</v>
+        <v>5.4</v>
       </c>
       <c r="N1079">
-        <v>8.4</v>
+        <v>8.66</v>
       </c>
       <c r="O1079">
         <v>1</v>
@@ -56141,43 +56138,43 @@
         <v>0</v>
       </c>
       <c r="B1080" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C1080">
-        <v>5.743098670470165</v>
+        <v>6.839891390238572</v>
       </c>
       <c r="D1080" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E1080">
-        <v>5.825240690744223</v>
+        <v>6.879458968711647</v>
       </c>
       <c r="F1080">
         <v>-1</v>
       </c>
       <c r="G1080">
-        <v>0.01079690132952984</v>
+        <v>0.01048010860976143</v>
       </c>
       <c r="H1080">
-        <v>0.01097475930925578</v>
+        <v>0.01044054103128835</v>
       </c>
       <c r="I1080">
-        <v>-0.08214202027405726</v>
+        <v>-0.03956757847307468</v>
       </c>
       <c r="J1080">
-        <v>0.4785797972594382</v>
+        <v>0.3297298206089543</v>
       </c>
       <c r="K1080">
-        <v>5.28</v>
+        <v>5.52</v>
       </c>
       <c r="L1080">
-        <v>8.27</v>
+        <v>8.66</v>
       </c>
       <c r="M1080">
-        <v>5.38</v>
+        <v>5.4</v>
       </c>
       <c r="N1080">
-        <v>8.4</v>
+        <v>8.66</v>
       </c>
       <c r="O1080">
         <v>1</v>
@@ -56191,149 +56188,49 @@
         <v>0</v>
       </c>
       <c r="B1081" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C1081">
-        <v>5.512060928235529</v>
+        <v>-0.4892225674140995</v>
       </c>
       <c r="D1081" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E1081">
-        <v>5.589827233694536</v>
+        <v>-0.2622680044676837</v>
       </c>
       <c r="F1081">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1081">
-        <v>0.01102793907176447</v>
+        <v>0.0172892225674141</v>
       </c>
       <c r="H1081">
-        <v>0.01121017276630547</v>
+        <v>0.01758226800446768</v>
       </c>
       <c r="I1081">
-        <v>-0.07776630545900698</v>
+        <v>0.2269545629464158</v>
       </c>
       <c r="J1081">
-        <v>0.5223369454099376</v>
+        <v>1.652271852679201</v>
       </c>
       <c r="K1081">
-        <v>5.28</v>
+        <v>5.38</v>
       </c>
       <c r="L1081">
-        <v>8.27</v>
+        <v>8.4</v>
       </c>
       <c r="M1081">
-        <v>5.38</v>
+        <v>5.4</v>
       </c>
       <c r="N1081">
-        <v>8.4</v>
+        <v>8.66</v>
       </c>
       <c r="O1081">
         <v>1</v>
       </c>
       <c r="P1081" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="1082" spans="1:16">
-      <c r="A1082" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1082" t="s">
-        <v>297</v>
-      </c>
-      <c r="C1082">
-        <v>5.044404491169697</v>
-      </c>
-      <c r="D1082" t="s">
-        <v>471</v>
-      </c>
-      <c r="E1082">
-        <v>5.113313667138821</v>
-      </c>
-      <c r="F1082">
-        <v>-1</v>
-      </c>
-      <c r="G1082">
-        <v>0.0114955955088303</v>
-      </c>
-      <c r="H1082">
-        <v>0.01168668633286118</v>
-      </c>
-      <c r="I1082">
-        <v>-0.06890917596912427</v>
-      </c>
-      <c r="J1082">
-        <v>0.6109082403087693</v>
-      </c>
-      <c r="K1082">
-        <v>5.28</v>
-      </c>
-      <c r="L1082">
-        <v>8.27</v>
-      </c>
-      <c r="M1082">
-        <v>5.38</v>
-      </c>
-      <c r="N1082">
-        <v>8.4</v>
-      </c>
-      <c r="O1082">
-        <v>1</v>
-      </c>
-      <c r="P1082" t="s">
         <v>603</v>
-      </c>
-    </row>
-    <row r="1083" spans="1:16">
-      <c r="A1083" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1083" t="s">
-        <v>298</v>
-      </c>
-      <c r="C1083">
-        <v>-0.4214043156284362</v>
-      </c>
-      <c r="D1083" t="s">
-        <v>472</v>
-      </c>
-      <c r="E1083">
-        <v>-0.4483588785748527</v>
-      </c>
-      <c r="F1083">
-        <v>-1</v>
-      </c>
-      <c r="G1083">
-        <v>0.01762140431562844</v>
-      </c>
-      <c r="H1083">
-        <v>0.01752835887857485</v>
-      </c>
-      <c r="I1083">
-        <v>0.02695456294641652</v>
-      </c>
-      <c r="J1083">
-        <v>1.652271852679201</v>
-      </c>
-      <c r="K1083">
-        <v>5.46</v>
-      </c>
-      <c r="L1083">
-        <v>8.6</v>
-      </c>
-      <c r="M1083">
-        <v>5.44</v>
-      </c>
-      <c r="N1083">
-        <v>8.539999999999999</v>
-      </c>
-      <c r="O1083">
-        <v>1</v>
-      </c>
-      <c r="P1083" t="s">
-        <v>604</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3189" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3174" uniqueCount="596">
   <si>
     <t>trade_time</t>
   </si>
@@ -883,529 +883,526 @@
     <t>2021-09-02</t>
   </si>
   <si>
+    <t>2021-09-23</t>
+  </si>
+  <si>
+    <t>2021-09-24</t>
+  </si>
+  <si>
+    <t>2016-04-28</t>
+  </si>
+  <si>
+    <t>2016-07-05</t>
+  </si>
+  <si>
+    <t>2016-04-21</t>
+  </si>
+  <si>
+    <t>2016-07-26</t>
+  </si>
+  <si>
+    <t>2016-05-17</t>
+  </si>
+  <si>
+    <t>2016-08-24</t>
+  </si>
+  <si>
+    <t>2016-09-29</t>
+  </si>
+  <si>
+    <t>2016-09-30</t>
+  </si>
+  <si>
+    <t>2016-10-12</t>
+  </si>
+  <si>
+    <t>2016-08-19</t>
+  </si>
+  <si>
+    <t>2016-10-25</t>
+  </si>
+  <si>
+    <t>2016-11-07</t>
+  </si>
+  <si>
+    <t>2016-11-10</t>
+  </si>
+  <si>
+    <t>2016-11-11</t>
+  </si>
+  <si>
+    <t>2016-11-16</t>
+  </si>
+  <si>
+    <t>2016-11-18</t>
+  </si>
+  <si>
+    <t>2016-10-13</t>
+  </si>
+  <si>
+    <t>2016-11-23</t>
+  </si>
+  <si>
+    <t>2016-09-14</t>
+  </si>
+  <si>
+    <t>2016-11-24</t>
+  </si>
+  <si>
+    <t>2016-11-29</t>
+  </si>
+  <si>
+    <t>2016-11-30</t>
+  </si>
+  <si>
+    <t>2016-12-14</t>
+  </si>
+  <si>
+    <t>2017-02-22</t>
+  </si>
+  <si>
+    <t>2017-01-12</t>
+  </si>
+  <si>
+    <t>2017-03-01</t>
+  </si>
+  <si>
+    <t>2016-12-06</t>
+  </si>
+  <si>
+    <t>2017-01-11</t>
+  </si>
+  <si>
+    <t>2017-03-06</t>
+  </si>
+  <si>
+    <t>2017-03-20</t>
+  </si>
+  <si>
+    <t>2017-03-21</t>
+  </si>
+  <si>
+    <t>2017-03-22</t>
+  </si>
+  <si>
+    <t>2017-03-23</t>
+  </si>
+  <si>
+    <t>2017-03-24</t>
+  </si>
+  <si>
+    <t>2016-12-09</t>
+  </si>
+  <si>
+    <t>2017-05-10</t>
+  </si>
+  <si>
+    <t>2017-06-01</t>
+  </si>
+  <si>
+    <t>2017-06-02</t>
+  </si>
+  <si>
+    <t>2017-06-05</t>
+  </si>
+  <si>
+    <t>2017-06-09</t>
+  </si>
+  <si>
+    <t>2017-03-27</t>
+  </si>
+  <si>
+    <t>2017-04-26</t>
+  </si>
+  <si>
+    <t>2017-07-14</t>
+  </si>
+  <si>
+    <t>2017-10-27</t>
+  </si>
+  <si>
+    <t>2017-10-30</t>
+  </si>
+  <si>
+    <t>2017-10-31</t>
+  </si>
+  <si>
+    <t>2017-11-01</t>
+  </si>
+  <si>
+    <t>2017-08-17</t>
+  </si>
+  <si>
+    <t>2017-08-02</t>
+  </si>
+  <si>
+    <t>2017-11-20</t>
+  </si>
+  <si>
+    <t>2017-11-21</t>
+  </si>
+  <si>
+    <t>2017-08-18</t>
+  </si>
+  <si>
+    <t>2017-09-06</t>
+  </si>
+  <si>
+    <t>2017-11-22</t>
+  </si>
+  <si>
+    <t>2017-11-23</t>
+  </si>
+  <si>
+    <t>2017-11-24</t>
+  </si>
+  <si>
+    <t>2017-11-28</t>
+  </si>
+  <si>
+    <t>2017-09-07</t>
+  </si>
+  <si>
+    <t>2017-11-30</t>
+  </si>
+  <si>
+    <t>2017-09-18</t>
+  </si>
+  <si>
+    <t>2017-12-06</t>
+  </si>
+  <si>
+    <t>2017-12-07</t>
+  </si>
+  <si>
+    <t>2017-12-08</t>
+  </si>
+  <si>
+    <t>2017-12-11</t>
+  </si>
+  <si>
+    <t>2017-12-12</t>
+  </si>
+  <si>
+    <t>2017-11-13</t>
+  </si>
+  <si>
+    <t>2017-12-15</t>
+  </si>
+  <si>
+    <t>2017-12-21</t>
+  </si>
+  <si>
+    <t>2018-02-09</t>
+  </si>
+  <si>
+    <t>2018-04-26</t>
+  </si>
+  <si>
+    <t>2018-04-27</t>
+  </si>
+  <si>
+    <t>2018-05-02</t>
+  </si>
+  <si>
+    <t>2018-05-03</t>
+  </si>
+  <si>
+    <t>2018-06-26</t>
+  </si>
+  <si>
+    <t>2018-07-24</t>
+  </si>
+  <si>
+    <t>2018-08-02</t>
+  </si>
+  <si>
+    <t>2018-06-25</t>
+  </si>
+  <si>
+    <t>2018-09-27</t>
+  </si>
+  <si>
+    <t>2018-10-08</t>
+  </si>
+  <si>
+    <t>2018-10-16</t>
+  </si>
+  <si>
+    <t>2018-07-23</t>
+  </si>
+  <si>
+    <t>2018-09-05</t>
+  </si>
+  <si>
+    <t>2018-10-22</t>
+  </si>
+  <si>
+    <t>2018-12-12</t>
+  </si>
+  <si>
+    <t>2018-11-02</t>
+  </si>
+  <si>
+    <t>2018-11-26</t>
+  </si>
+  <si>
+    <t>2018-12-20</t>
+  </si>
+  <si>
+    <t>2019-01-11</t>
+  </si>
+  <si>
+    <t>2018-11-06</t>
+  </si>
+  <si>
+    <t>2019-01-15</t>
+  </si>
+  <si>
+    <t>2018-12-27</t>
+  </si>
+  <si>
+    <t>2019-03-01</t>
+  </si>
+  <si>
+    <t>2019-02-28</t>
+  </si>
+  <si>
+    <t>2019-02-26</t>
+  </si>
+  <si>
+    <t>2019-04-15</t>
+  </si>
+  <si>
+    <t>2019-04-26</t>
+  </si>
+  <si>
+    <t>2019-06-19</t>
+  </si>
+  <si>
+    <t>2019-05-06</t>
+  </si>
+  <si>
+    <t>2019-07-03</t>
+  </si>
+  <si>
+    <t>2019-03-27</t>
+  </si>
+  <si>
+    <t>2019-05-08</t>
+  </si>
+  <si>
+    <t>2019-07-05</t>
+  </si>
+  <si>
+    <t>2019-05-15</t>
+  </si>
+  <si>
+    <t>2019-07-04</t>
+  </si>
+  <si>
+    <t>2019-09-23</t>
+  </si>
+  <si>
+    <t>2019-09-04</t>
+  </si>
+  <si>
+    <t>2019-09-27</t>
+  </si>
+  <si>
+    <t>2019-12-17</t>
+  </si>
+  <si>
+    <t>2019-12-18</t>
+  </si>
+  <si>
+    <t>2019-10-15</t>
+  </si>
+  <si>
+    <t>2019-12-20</t>
+  </si>
+  <si>
+    <t>2019-11-13</t>
+  </si>
+  <si>
+    <t>2019-12-23</t>
+  </si>
+  <si>
+    <t>2019-11-14</t>
+  </si>
+  <si>
+    <t>2020-01-15</t>
+  </si>
+  <si>
+    <t>2020-02-24</t>
+  </si>
+  <si>
+    <t>2020-02-25</t>
+  </si>
+  <si>
+    <t>2020-02-26</t>
+  </si>
+  <si>
+    <t>2020-02-28</t>
+  </si>
+  <si>
+    <t>2020-03-02</t>
+  </si>
+  <si>
+    <t>2020-01-23</t>
+  </si>
+  <si>
+    <t>2020-03-06</t>
+  </si>
+  <si>
+    <t>2020-03-09</t>
+  </si>
+  <si>
+    <t>2020-03-11</t>
+  </si>
+  <si>
+    <t>2020-03-12</t>
+  </si>
+  <si>
+    <t>2020-03-13</t>
+  </si>
+  <si>
+    <t>2020-03-16</t>
+  </si>
+  <si>
+    <t>2020-03-17</t>
+  </si>
+  <si>
+    <t>2020-03-18</t>
+  </si>
+  <si>
+    <t>2020-03-20</t>
+  </si>
+  <si>
+    <t>2020-03-23</t>
+  </si>
+  <si>
+    <t>2020-03-24</t>
+  </si>
+  <si>
+    <t>2020-03-25</t>
+  </si>
+  <si>
+    <t>2020-03-26</t>
+  </si>
+  <si>
+    <t>2020-07-02</t>
+  </si>
+  <si>
+    <t>2020-08-19</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>2020-08-21</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>2020-08-26</t>
+  </si>
+  <si>
+    <t>2020-09-02</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>2020-12-21</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>2020-12-23</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>2020-12-28</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>2021-01-11</t>
+  </si>
+  <si>
+    <t>2021-01-19</t>
+  </si>
+  <si>
+    <t>2021-03-01</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>2021-03-17</t>
+  </si>
+  <si>
+    <t>2021-02-19</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>2021-05-17</t>
+  </si>
+  <si>
+    <t>2021-05-24</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>2021-07-26</t>
+  </si>
+  <si>
+    <t>2021-07-27</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>2021-09-09</t>
+  </si>
+  <si>
+    <t>2021-10-12</t>
+  </si>
+  <si>
     <t>2021-10-08</t>
-  </si>
-  <si>
-    <t>2021-09-24</t>
-  </si>
-  <si>
-    <t>2016-04-28</t>
-  </si>
-  <si>
-    <t>2016-07-05</t>
-  </si>
-  <si>
-    <t>2016-04-21</t>
-  </si>
-  <si>
-    <t>2016-07-26</t>
-  </si>
-  <si>
-    <t>2016-05-17</t>
-  </si>
-  <si>
-    <t>2016-08-24</t>
-  </si>
-  <si>
-    <t>2016-09-29</t>
-  </si>
-  <si>
-    <t>2016-09-30</t>
-  </si>
-  <si>
-    <t>2016-10-12</t>
-  </si>
-  <si>
-    <t>2016-08-19</t>
-  </si>
-  <si>
-    <t>2016-10-25</t>
-  </si>
-  <si>
-    <t>2016-11-07</t>
-  </si>
-  <si>
-    <t>2016-11-10</t>
-  </si>
-  <si>
-    <t>2016-11-11</t>
-  </si>
-  <si>
-    <t>2016-11-16</t>
-  </si>
-  <si>
-    <t>2016-11-18</t>
-  </si>
-  <si>
-    <t>2016-10-13</t>
-  </si>
-  <si>
-    <t>2016-11-23</t>
-  </si>
-  <si>
-    <t>2016-09-14</t>
-  </si>
-  <si>
-    <t>2016-11-24</t>
-  </si>
-  <si>
-    <t>2016-11-29</t>
-  </si>
-  <si>
-    <t>2016-11-30</t>
-  </si>
-  <si>
-    <t>2016-12-14</t>
-  </si>
-  <si>
-    <t>2017-02-22</t>
-  </si>
-  <si>
-    <t>2017-01-12</t>
-  </si>
-  <si>
-    <t>2017-03-01</t>
-  </si>
-  <si>
-    <t>2016-12-06</t>
-  </si>
-  <si>
-    <t>2017-01-11</t>
-  </si>
-  <si>
-    <t>2017-03-06</t>
-  </si>
-  <si>
-    <t>2017-03-20</t>
-  </si>
-  <si>
-    <t>2017-03-21</t>
-  </si>
-  <si>
-    <t>2017-03-22</t>
-  </si>
-  <si>
-    <t>2017-03-23</t>
-  </si>
-  <si>
-    <t>2017-03-24</t>
-  </si>
-  <si>
-    <t>2016-12-09</t>
-  </si>
-  <si>
-    <t>2017-05-10</t>
-  </si>
-  <si>
-    <t>2017-06-01</t>
-  </si>
-  <si>
-    <t>2017-06-02</t>
-  </si>
-  <si>
-    <t>2017-06-05</t>
-  </si>
-  <si>
-    <t>2017-06-09</t>
-  </si>
-  <si>
-    <t>2017-03-27</t>
-  </si>
-  <si>
-    <t>2017-04-26</t>
-  </si>
-  <si>
-    <t>2017-07-14</t>
-  </si>
-  <si>
-    <t>2017-10-27</t>
-  </si>
-  <si>
-    <t>2017-10-30</t>
-  </si>
-  <si>
-    <t>2017-10-31</t>
-  </si>
-  <si>
-    <t>2017-11-01</t>
-  </si>
-  <si>
-    <t>2017-08-17</t>
-  </si>
-  <si>
-    <t>2017-08-02</t>
-  </si>
-  <si>
-    <t>2017-11-20</t>
-  </si>
-  <si>
-    <t>2017-11-21</t>
-  </si>
-  <si>
-    <t>2017-08-18</t>
-  </si>
-  <si>
-    <t>2017-09-06</t>
-  </si>
-  <si>
-    <t>2017-11-22</t>
-  </si>
-  <si>
-    <t>2017-11-23</t>
-  </si>
-  <si>
-    <t>2017-11-24</t>
-  </si>
-  <si>
-    <t>2017-11-28</t>
-  </si>
-  <si>
-    <t>2017-09-07</t>
-  </si>
-  <si>
-    <t>2017-11-30</t>
-  </si>
-  <si>
-    <t>2017-09-18</t>
-  </si>
-  <si>
-    <t>2017-12-06</t>
-  </si>
-  <si>
-    <t>2017-12-07</t>
-  </si>
-  <si>
-    <t>2017-12-08</t>
-  </si>
-  <si>
-    <t>2017-12-11</t>
-  </si>
-  <si>
-    <t>2017-12-12</t>
-  </si>
-  <si>
-    <t>2017-11-13</t>
-  </si>
-  <si>
-    <t>2017-12-15</t>
-  </si>
-  <si>
-    <t>2017-12-21</t>
-  </si>
-  <si>
-    <t>2018-02-09</t>
-  </si>
-  <si>
-    <t>2018-04-26</t>
-  </si>
-  <si>
-    <t>2018-04-27</t>
-  </si>
-  <si>
-    <t>2018-05-02</t>
-  </si>
-  <si>
-    <t>2018-05-03</t>
-  </si>
-  <si>
-    <t>2018-06-26</t>
-  </si>
-  <si>
-    <t>2018-07-24</t>
-  </si>
-  <si>
-    <t>2018-08-02</t>
-  </si>
-  <si>
-    <t>2018-06-25</t>
-  </si>
-  <si>
-    <t>2018-09-27</t>
-  </si>
-  <si>
-    <t>2018-10-08</t>
-  </si>
-  <si>
-    <t>2018-10-16</t>
-  </si>
-  <si>
-    <t>2018-07-23</t>
-  </si>
-  <si>
-    <t>2018-09-05</t>
-  </si>
-  <si>
-    <t>2018-10-22</t>
-  </si>
-  <si>
-    <t>2018-12-12</t>
-  </si>
-  <si>
-    <t>2018-11-02</t>
-  </si>
-  <si>
-    <t>2018-11-26</t>
-  </si>
-  <si>
-    <t>2018-12-20</t>
-  </si>
-  <si>
-    <t>2019-01-11</t>
-  </si>
-  <si>
-    <t>2018-11-06</t>
-  </si>
-  <si>
-    <t>2019-01-15</t>
-  </si>
-  <si>
-    <t>2018-12-27</t>
-  </si>
-  <si>
-    <t>2019-03-01</t>
-  </si>
-  <si>
-    <t>2019-02-28</t>
-  </si>
-  <si>
-    <t>2019-02-26</t>
-  </si>
-  <si>
-    <t>2019-04-15</t>
-  </si>
-  <si>
-    <t>2019-04-26</t>
-  </si>
-  <si>
-    <t>2019-06-19</t>
-  </si>
-  <si>
-    <t>2019-05-06</t>
-  </si>
-  <si>
-    <t>2019-07-03</t>
-  </si>
-  <si>
-    <t>2019-03-27</t>
-  </si>
-  <si>
-    <t>2019-05-08</t>
-  </si>
-  <si>
-    <t>2019-07-05</t>
-  </si>
-  <si>
-    <t>2019-05-15</t>
-  </si>
-  <si>
-    <t>2019-07-04</t>
-  </si>
-  <si>
-    <t>2019-09-23</t>
-  </si>
-  <si>
-    <t>2019-09-04</t>
-  </si>
-  <si>
-    <t>2019-09-27</t>
-  </si>
-  <si>
-    <t>2019-12-17</t>
-  </si>
-  <si>
-    <t>2019-12-18</t>
-  </si>
-  <si>
-    <t>2019-10-15</t>
-  </si>
-  <si>
-    <t>2019-12-20</t>
-  </si>
-  <si>
-    <t>2019-11-13</t>
-  </si>
-  <si>
-    <t>2019-12-23</t>
-  </si>
-  <si>
-    <t>2019-11-14</t>
-  </si>
-  <si>
-    <t>2020-01-15</t>
-  </si>
-  <si>
-    <t>2020-02-24</t>
-  </si>
-  <si>
-    <t>2020-02-25</t>
-  </si>
-  <si>
-    <t>2020-02-26</t>
-  </si>
-  <si>
-    <t>2020-02-28</t>
-  </si>
-  <si>
-    <t>2020-03-02</t>
-  </si>
-  <si>
-    <t>2020-01-23</t>
-  </si>
-  <si>
-    <t>2020-03-06</t>
-  </si>
-  <si>
-    <t>2020-03-09</t>
-  </si>
-  <si>
-    <t>2020-03-11</t>
-  </si>
-  <si>
-    <t>2020-03-12</t>
-  </si>
-  <si>
-    <t>2020-03-13</t>
-  </si>
-  <si>
-    <t>2020-03-16</t>
-  </si>
-  <si>
-    <t>2020-03-17</t>
-  </si>
-  <si>
-    <t>2020-03-18</t>
-  </si>
-  <si>
-    <t>2020-03-20</t>
-  </si>
-  <si>
-    <t>2020-03-23</t>
-  </si>
-  <si>
-    <t>2020-03-24</t>
-  </si>
-  <si>
-    <t>2020-03-25</t>
-  </si>
-  <si>
-    <t>2020-03-26</t>
-  </si>
-  <si>
-    <t>2020-07-02</t>
-  </si>
-  <si>
-    <t>2020-08-19</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>2020-08-21</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>2020-08-26</t>
-  </si>
-  <si>
-    <t>2020-09-02</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>2020-12-21</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>2020-12-23</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>2020-12-28</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>2021-01-11</t>
-  </si>
-  <si>
-    <t>2021-01-19</t>
-  </si>
-  <si>
-    <t>2021-03-01</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>2021-03-17</t>
-  </si>
-  <si>
-    <t>2021-02-19</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>2021-05-17</t>
-  </si>
-  <si>
-    <t>2021-05-24</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>2021-07-26</t>
-  </si>
-  <si>
-    <t>2021-07-27</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>2021-09-09</t>
-  </si>
-  <si>
-    <t>2021-09-23</t>
-  </si>
-  <si>
-    <t>2021-10-11</t>
-  </si>
-  <si>
-    <t>2021-09-29</t>
   </si>
   <si>
     <t>2016-03-24</t>
@@ -2162,7 +2159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1059"/>
+  <dimension ref="A1:P1054"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2259,7 +2256,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2309,7 +2306,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2359,7 +2356,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2409,7 +2406,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2459,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2509,7 +2506,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2559,7 +2556,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2609,7 +2606,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2659,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2709,7 +2706,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2759,7 +2756,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2809,7 +2806,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2859,7 +2856,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2909,7 +2906,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2959,7 +2956,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -3009,7 +3006,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -3059,7 +3056,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -3109,7 +3106,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -3159,7 +3156,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -3209,7 +3206,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -3259,7 +3256,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3309,7 +3306,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3359,7 +3356,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3409,7 +3406,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3459,7 +3456,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3509,7 +3506,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3559,7 +3556,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3609,7 +3606,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3659,7 +3656,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3709,7 +3706,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3759,7 +3756,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3809,7 +3806,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3859,7 +3856,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3909,7 +3906,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3959,7 +3956,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -4009,7 +4006,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -4059,7 +4056,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -4109,7 +4106,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -4159,7 +4156,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -4209,7 +4206,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -4259,7 +4256,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4309,7 +4306,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4359,7 +4356,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4409,7 +4406,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4459,7 +4456,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4509,7 +4506,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4559,7 +4556,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4609,7 +4606,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4659,7 +4656,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4709,7 +4706,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4759,7 +4756,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4809,7 +4806,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4859,7 +4856,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4909,7 +4906,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4959,7 +4956,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -5009,7 +5006,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -5059,7 +5056,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -5109,7 +5106,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -5159,7 +5156,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -5209,7 +5206,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -5259,7 +5256,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5309,7 +5306,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5359,7 +5356,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5959,7 +5956,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -6009,7 +6006,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -6059,7 +6056,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -6109,7 +6106,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -6159,7 +6156,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -6209,7 +6206,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -6259,7 +6256,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -6309,7 +6306,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -6359,7 +6356,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6409,7 +6406,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6459,7 +6456,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6509,7 +6506,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6559,7 +6556,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6609,7 +6606,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6659,7 +6656,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6709,7 +6706,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6759,7 +6756,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6809,7 +6806,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6859,7 +6856,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6909,7 +6906,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6959,7 +6956,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -7309,7 +7306,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7359,7 +7356,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7409,7 +7406,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7459,7 +7456,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7509,7 +7506,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7559,7 +7556,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7609,7 +7606,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7659,7 +7656,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7709,7 +7706,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7759,7 +7756,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7809,7 +7806,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7859,7 +7856,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7909,7 +7906,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7959,7 +7956,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -8009,7 +8006,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -8059,7 +8056,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -8109,7 +8106,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -8159,7 +8156,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -8209,7 +8206,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -8559,7 +8556,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8609,7 +8606,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8659,7 +8656,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8709,7 +8706,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8759,7 +8756,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8809,7 +8806,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8859,7 +8856,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8909,7 +8906,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8959,7 +8956,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -9009,7 +9006,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -9059,7 +9056,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -9109,7 +9106,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -9159,7 +9156,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -9209,7 +9206,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -9259,7 +9256,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -9309,7 +9306,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9359,7 +9356,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9409,7 +9406,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -10759,7 +10756,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10809,7 +10806,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10859,7 +10856,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10909,7 +10906,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10959,7 +10956,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -11009,7 +11006,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -11059,7 +11056,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -11109,7 +11106,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -11159,7 +11156,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -11309,7 +11306,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -11359,7 +11356,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11559,7 +11556,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11609,7 +11606,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11659,7 +11656,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11709,7 +11706,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11759,7 +11756,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11809,7 +11806,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -12259,7 +12256,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -12309,7 +12306,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12359,7 +12356,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12409,7 +12406,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12459,7 +12456,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -17159,7 +17156,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -17209,7 +17206,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -17259,7 +17256,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -17309,7 +17306,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17359,7 +17356,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17409,7 +17406,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17459,7 +17456,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17709,7 +17706,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17759,7 +17756,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17809,7 +17806,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17859,7 +17856,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17909,7 +17906,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -18409,7 +18406,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -18459,7 +18456,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -18509,7 +18506,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -18559,7 +18556,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18709,7 +18706,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18759,7 +18756,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18809,7 +18806,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18859,7 +18856,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18909,7 +18906,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -19159,7 +19156,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -19209,7 +19206,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -19259,7 +19256,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -19309,7 +19306,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19359,7 +19356,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19409,7 +19406,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19459,7 +19456,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19509,7 +19506,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19559,7 +19556,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19609,7 +19606,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19659,7 +19656,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19709,7 +19706,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19759,7 +19756,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19809,7 +19806,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19859,7 +19856,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19909,7 +19906,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19959,7 +19956,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -20009,7 +20006,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -20059,7 +20056,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -20109,7 +20106,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -20159,7 +20156,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -20209,7 +20206,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -20259,7 +20256,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -20309,7 +20306,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -20359,7 +20356,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20409,7 +20406,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20459,7 +20456,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20509,7 +20506,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20559,7 +20556,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20609,7 +20606,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20659,7 +20656,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20709,7 +20706,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20759,7 +20756,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20809,7 +20806,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20859,7 +20856,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20909,7 +20906,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20959,7 +20956,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -21009,7 +21006,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -21059,7 +21056,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -21109,7 +21106,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -21159,7 +21156,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -21209,7 +21206,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -21259,7 +21256,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -21309,7 +21306,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21609,7 +21606,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21659,7 +21656,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21709,7 +21706,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21759,7 +21756,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21809,7 +21806,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -22509,7 +22506,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22559,7 +22556,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22609,7 +22606,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22659,7 +22656,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22709,7 +22706,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22759,7 +22756,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22809,7 +22806,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22859,7 +22856,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22909,7 +22906,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22959,7 +22956,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -23009,7 +23006,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -23059,7 +23056,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -23109,7 +23106,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -23159,7 +23156,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -23209,7 +23206,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -23259,7 +23256,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -23309,7 +23306,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -23359,7 +23356,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -23409,7 +23406,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -23459,7 +23456,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -23509,7 +23506,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23859,7 +23856,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23909,7 +23906,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23959,7 +23956,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -24009,7 +24006,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -24059,7 +24056,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -24109,7 +24106,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -24159,7 +24156,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -24209,7 +24206,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -24259,7 +24256,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -24309,7 +24306,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24359,7 +24356,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24409,7 +24406,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24459,7 +24456,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24509,7 +24506,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24559,7 +24556,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24609,7 +24606,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24659,7 +24656,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24709,7 +24706,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24759,7 +24756,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24809,7 +24806,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24859,7 +24856,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24909,7 +24906,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24959,7 +24956,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -25009,7 +25006,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -25059,7 +25056,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -25109,7 +25106,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -25159,7 +25156,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -25209,7 +25206,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -25259,7 +25256,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -25309,7 +25306,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -25359,7 +25356,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25409,7 +25406,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -25459,7 +25456,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25509,7 +25506,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25559,7 +25556,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25609,7 +25606,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25659,7 +25656,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25709,7 +25706,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25759,7 +25756,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25809,7 +25806,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25859,7 +25856,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25909,7 +25906,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25959,7 +25956,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -26009,7 +26006,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -26059,7 +26056,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -26309,7 +26306,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26359,7 +26356,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26409,7 +26406,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26459,7 +26456,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26509,7 +26506,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26809,7 +26806,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26859,7 +26856,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26909,7 +26906,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26959,7 +26956,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -27009,7 +27006,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -27559,7 +27556,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27609,7 +27606,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27659,7 +27656,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27709,7 +27706,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27759,7 +27756,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27809,7 +27806,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27859,7 +27856,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -28159,7 +28156,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -28209,7 +28206,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -28259,7 +28256,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -28309,7 +28306,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -28359,7 +28356,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28409,7 +28406,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28459,7 +28456,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28509,7 +28506,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28559,7 +28556,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28609,7 +28606,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28659,7 +28656,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28709,7 +28706,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28759,7 +28756,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28809,7 +28806,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28859,7 +28856,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28909,7 +28906,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28959,7 +28956,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -29259,7 +29256,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -29309,7 +29306,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -29359,7 +29356,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -29409,7 +29406,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -29459,7 +29456,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -29509,7 +29506,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29559,7 +29556,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29609,7 +29606,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29659,7 +29656,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -30259,7 +30256,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -30309,7 +30306,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -30359,7 +30356,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -30409,7 +30406,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -30459,7 +30456,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -30509,7 +30506,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30559,7 +30556,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30609,7 +30606,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30659,7 +30656,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30709,7 +30706,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30759,7 +30756,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30809,7 +30806,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30859,7 +30856,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30909,7 +30906,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30959,7 +30956,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -31009,7 +31006,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -31059,7 +31056,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -31109,7 +31106,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -31159,7 +31156,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -31209,7 +31206,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -31259,7 +31256,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -31309,7 +31306,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31359,7 +31356,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31409,7 +31406,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -31459,7 +31456,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31509,7 +31506,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31559,7 +31556,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31609,7 +31606,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31659,7 +31656,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31709,7 +31706,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -31759,7 +31756,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -31809,7 +31806,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -31859,7 +31856,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -31909,7 +31906,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -32159,7 +32156,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -32209,7 +32206,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -32259,7 +32256,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -32309,7 +32306,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -32359,7 +32356,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32409,7 +32406,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32459,7 +32456,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -32509,7 +32506,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32559,7 +32556,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32609,7 +32606,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32659,7 +32656,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32709,7 +32706,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -33259,7 +33256,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -33309,7 +33306,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -33359,7 +33356,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -33409,7 +33406,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -33459,7 +33456,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -33509,7 +33506,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33559,7 +33556,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -33609,7 +33606,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -33659,7 +33656,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -33709,7 +33706,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33759,7 +33756,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33809,7 +33806,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33859,7 +33856,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33909,7 +33906,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33959,7 +33956,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -34009,7 +34006,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -34059,7 +34056,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -34109,7 +34106,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -34159,7 +34156,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -34209,7 +34206,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -34259,7 +34256,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -34759,7 +34756,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -34809,7 +34806,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -34859,7 +34856,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -34909,7 +34906,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -34959,7 +34956,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -35009,7 +35006,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -35059,7 +35056,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -35109,7 +35106,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -35159,7 +35156,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -35209,7 +35206,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -35259,7 +35256,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -35309,7 +35306,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -35359,7 +35356,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -35409,7 +35406,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -35459,7 +35456,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -35509,7 +35506,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35559,7 +35556,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35609,7 +35606,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35659,7 +35656,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35709,7 +35706,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35759,7 +35756,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35809,7 +35806,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35859,7 +35856,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35909,7 +35906,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35959,7 +35956,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -36009,7 +36006,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -36059,7 +36056,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -36109,7 +36106,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -36159,7 +36156,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -36209,7 +36206,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -36259,7 +36256,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36309,7 +36306,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36759,7 +36756,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36809,7 +36806,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36859,7 +36856,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36909,7 +36906,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36959,7 +36956,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -37009,7 +37006,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -37059,7 +37056,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -37109,7 +37106,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -37709,7 +37706,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37759,7 +37756,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37809,7 +37806,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37859,7 +37856,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37909,7 +37906,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37959,7 +37956,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -38009,7 +38006,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -38059,7 +38056,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -38109,7 +38106,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -38509,7 +38506,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38559,7 +38556,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -38609,7 +38606,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -38659,7 +38656,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -38709,7 +38706,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38759,7 +38756,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38809,7 +38806,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38859,7 +38856,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38909,7 +38906,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38959,7 +38956,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -39009,7 +39006,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -39059,7 +39056,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -39109,7 +39106,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -39159,7 +39156,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -39209,7 +39206,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -39259,7 +39256,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -39309,7 +39306,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -39359,7 +39356,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -39409,7 +39406,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -39709,7 +39706,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39759,7 +39756,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39809,7 +39806,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39859,7 +39856,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39909,7 +39906,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39959,7 +39956,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -40009,7 +40006,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -40059,7 +40056,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -40109,7 +40106,7 @@
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -40159,7 +40156,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -40209,7 +40206,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -40259,7 +40256,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -40609,7 +40606,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -40659,7 +40656,7 @@
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="771" spans="1:16">
@@ -40709,7 +40706,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -40759,7 +40756,7 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -40809,7 +40806,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40859,7 +40856,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40909,7 +40906,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40959,7 +40956,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -41009,7 +41006,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -41059,7 +41056,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -41109,7 +41106,7 @@
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -41159,7 +41156,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -41209,7 +41206,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -41259,7 +41256,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -41309,7 +41306,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -42059,7 +42056,7 @@
         <v>1</v>
       </c>
       <c r="P798" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="799" spans="1:16">
@@ -42109,7 +42106,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -42159,7 +42156,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -42209,7 +42206,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -42259,7 +42256,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -42309,7 +42306,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -42359,7 +42356,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -42409,7 +42406,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -42459,7 +42456,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -42509,7 +42506,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42559,7 +42556,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42609,7 +42606,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42659,7 +42656,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -42709,7 +42706,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -43259,7 +43256,7 @@
         <v>1</v>
       </c>
       <c r="P822" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="823" spans="1:16">
@@ -43309,7 +43306,7 @@
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="824" spans="1:16">
@@ -43359,7 +43356,7 @@
         <v>1</v>
       </c>
       <c r="P824" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="825" spans="1:16">
@@ -43409,7 +43406,7 @@
         <v>1</v>
       </c>
       <c r="P825" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="826" spans="1:16">
@@ -43459,7 +43456,7 @@
         <v>1</v>
       </c>
       <c r="P826" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="827" spans="1:16">
@@ -43509,7 +43506,7 @@
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="828" spans="1:16">
@@ -43559,7 +43556,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -43609,7 +43606,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -43659,7 +43656,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -43709,7 +43706,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -43759,7 +43756,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43809,7 +43806,7 @@
         <v>1</v>
       </c>
       <c r="P833" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="834" spans="1:16">
@@ -43859,7 +43856,7 @@
         <v>1</v>
       </c>
       <c r="P834" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="835" spans="1:16">
@@ -43909,7 +43906,7 @@
         <v>1</v>
       </c>
       <c r="P835" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="836" spans="1:16">
@@ -43959,7 +43956,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -44009,7 +44006,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -44059,7 +44056,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -44109,7 +44106,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -44159,7 +44156,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -44209,7 +44206,7 @@
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -44259,7 +44256,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -44309,7 +44306,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -44359,7 +44356,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -44409,7 +44406,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44459,7 +44456,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44509,7 +44506,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44559,7 +44556,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44609,7 +44606,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44659,7 +44656,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44709,7 +44706,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -44759,7 +44756,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -44809,7 +44806,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -44859,7 +44856,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44909,7 +44906,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -44959,7 +44956,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -45009,7 +45006,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -45059,7 +45056,7 @@
         <v>1</v>
       </c>
       <c r="P858" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="859" spans="1:16">
@@ -45109,7 +45106,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -45159,7 +45156,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -45209,7 +45206,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -45259,7 +45256,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -45309,7 +45306,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -45359,7 +45356,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -45409,7 +45406,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45459,7 +45456,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45509,7 +45506,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45559,7 +45556,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45609,7 +45606,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45659,7 +45656,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45709,7 +45706,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45759,7 +45756,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45809,7 +45806,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -45859,7 +45856,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45909,7 +45906,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45959,7 +45956,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -46009,7 +46006,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -46059,7 +46056,7 @@
         <v>1</v>
       </c>
       <c r="P878" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="879" spans="1:16">
@@ -46109,7 +46106,7 @@
         <v>1</v>
       </c>
       <c r="P879" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="880" spans="1:16">
@@ -46159,7 +46156,7 @@
         <v>1</v>
       </c>
       <c r="P880" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="881" spans="1:16">
@@ -46209,7 +46206,7 @@
         <v>1</v>
       </c>
       <c r="P881" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="882" spans="1:16">
@@ -46259,7 +46256,7 @@
         <v>1</v>
       </c>
       <c r="P882" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -46309,7 +46306,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46359,7 +46356,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46409,7 +46406,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46459,7 +46456,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46509,7 +46506,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46559,7 +46556,7 @@
         <v>1</v>
       </c>
       <c r="P888" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="889" spans="1:16">
@@ -46609,7 +46606,7 @@
         <v>1</v>
       </c>
       <c r="P889" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="890" spans="1:16">
@@ -46659,7 +46656,7 @@
         <v>1</v>
       </c>
       <c r="P890" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="891" spans="1:16">
@@ -46709,7 +46706,7 @@
         <v>1</v>
       </c>
       <c r="P891" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="892" spans="1:16">
@@ -46759,7 +46756,7 @@
         <v>1</v>
       </c>
       <c r="P892" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="893" spans="1:16">
@@ -46809,7 +46806,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46859,7 +46856,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46909,7 +46906,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -46959,7 +46956,7 @@
         <v>1</v>
       </c>
       <c r="P896" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="897" spans="1:16">
@@ -47009,7 +47006,7 @@
         <v>1</v>
       </c>
       <c r="P897" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="898" spans="1:16">
@@ -47059,7 +47056,7 @@
         <v>1</v>
       </c>
       <c r="P898" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="899" spans="1:16">
@@ -47109,7 +47106,7 @@
         <v>1</v>
       </c>
       <c r="P899" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="900" spans="1:16">
@@ -47159,7 +47156,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -47209,7 +47206,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -47259,7 +47256,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -47309,7 +47306,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -47359,7 +47356,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -47409,7 +47406,7 @@
         <v>1</v>
       </c>
       <c r="P905" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="906" spans="1:16">
@@ -47459,7 +47456,7 @@
         <v>1</v>
       </c>
       <c r="P906" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="907" spans="1:16">
@@ -47509,7 +47506,7 @@
         <v>1</v>
       </c>
       <c r="P907" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="908" spans="1:16">
@@ -47559,7 +47556,7 @@
         <v>1</v>
       </c>
       <c r="P908" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="909" spans="1:16">
@@ -47609,7 +47606,7 @@
         <v>1</v>
       </c>
       <c r="P909" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="910" spans="1:16">
@@ -47659,7 +47656,7 @@
         <v>1</v>
       </c>
       <c r="P910" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="911" spans="1:16">
@@ -47709,7 +47706,7 @@
         <v>1</v>
       </c>
       <c r="P911" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="912" spans="1:16">
@@ -47759,7 +47756,7 @@
         <v>1</v>
       </c>
       <c r="P912" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="913" spans="1:16">
@@ -47809,7 +47806,7 @@
         <v>1</v>
       </c>
       <c r="P913" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="914" spans="1:16">
@@ -47859,7 +47856,7 @@
         <v>1</v>
       </c>
       <c r="P914" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="915" spans="1:16">
@@ -47909,7 +47906,7 @@
         <v>1</v>
       </c>
       <c r="P915" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="916" spans="1:16">
@@ -47959,7 +47956,7 @@
         <v>1</v>
       </c>
       <c r="P916" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="917" spans="1:16">
@@ -48009,7 +48006,7 @@
         <v>1</v>
       </c>
       <c r="P917" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="918" spans="1:16">
@@ -48059,7 +48056,7 @@
         <v>1</v>
       </c>
       <c r="P918" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="919" spans="1:16">
@@ -48109,7 +48106,7 @@
         <v>1</v>
       </c>
       <c r="P919" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="920" spans="1:16">
@@ -48159,7 +48156,7 @@
         <v>1</v>
       </c>
       <c r="P920" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="921" spans="1:16">
@@ -48209,7 +48206,7 @@
         <v>1</v>
       </c>
       <c r="P921" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="922" spans="1:16">
@@ -48259,7 +48256,7 @@
         <v>1</v>
       </c>
       <c r="P922" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="923" spans="1:16">
@@ -48309,7 +48306,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -48359,7 +48356,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -48409,7 +48406,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48459,7 +48456,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48509,7 +48506,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -48559,7 +48556,7 @@
         <v>1</v>
       </c>
       <c r="P928" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="929" spans="1:16">
@@ -48609,7 +48606,7 @@
         <v>1</v>
       </c>
       <c r="P929" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="930" spans="1:16">
@@ -48659,7 +48656,7 @@
         <v>1</v>
       </c>
       <c r="P930" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="931" spans="1:16">
@@ -48709,7 +48706,7 @@
         <v>1</v>
       </c>
       <c r="P931" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="932" spans="1:16">
@@ -48759,7 +48756,7 @@
         <v>1</v>
       </c>
       <c r="P932" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="933" spans="1:16">
@@ -48809,7 +48806,7 @@
         <v>1</v>
       </c>
       <c r="P933" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="934" spans="1:16">
@@ -48859,7 +48856,7 @@
         <v>1</v>
       </c>
       <c r="P934" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="935" spans="1:16">
@@ -48909,7 +48906,7 @@
         <v>1</v>
       </c>
       <c r="P935" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="936" spans="1:16">
@@ -48959,7 +48956,7 @@
         <v>1</v>
       </c>
       <c r="P936" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="937" spans="1:16">
@@ -49009,7 +49006,7 @@
         <v>1</v>
       </c>
       <c r="P937" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="938" spans="1:16">
@@ -49059,7 +49056,7 @@
         <v>1</v>
       </c>
       <c r="P938" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="939" spans="1:16">
@@ -49109,7 +49106,7 @@
         <v>1</v>
       </c>
       <c r="P939" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="940" spans="1:16">
@@ -49159,7 +49156,7 @@
         <v>1</v>
       </c>
       <c r="P940" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="941" spans="1:16">
@@ -49209,7 +49206,7 @@
         <v>1</v>
       </c>
       <c r="P941" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="942" spans="1:16">
@@ -50409,7 +50406,7 @@
         <v>1</v>
       </c>
       <c r="P965" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="966" spans="1:16">
@@ -50459,7 +50456,7 @@
         <v>1</v>
       </c>
       <c r="P966" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="967" spans="1:16">
@@ -50509,7 +50506,7 @@
         <v>1</v>
       </c>
       <c r="P967" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="968" spans="1:16">
@@ -50559,7 +50556,7 @@
         <v>1</v>
       </c>
       <c r="P968" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="969" spans="1:16">
@@ -51259,7 +51256,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -51309,7 +51306,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -51359,7 +51356,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -51409,7 +51406,7 @@
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="986" spans="1:16">
@@ -51459,7 +51456,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -51509,7 +51506,7 @@
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51559,7 +51556,7 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="989" spans="1:16">
@@ -51609,7 +51606,7 @@
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="990" spans="1:16">
@@ -51659,7 +51656,7 @@
         <v>1</v>
       </c>
       <c r="P990" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="991" spans="1:16">
@@ -52109,7 +52106,7 @@
         <v>1</v>
       </c>
       <c r="P999" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="1000" spans="1:16">
@@ -52159,7 +52156,7 @@
         <v>1</v>
       </c>
       <c r="P1000" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="1001" spans="1:16">
@@ -52209,7 +52206,7 @@
         <v>1</v>
       </c>
       <c r="P1001" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="1002" spans="1:16">
@@ -52259,7 +52256,7 @@
         <v>1</v>
       </c>
       <c r="P1002" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="1003" spans="1:16">
@@ -52309,7 +52306,7 @@
         <v>1</v>
       </c>
       <c r="P1003" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="1004" spans="1:16">
@@ -52359,7 +52356,7 @@
         <v>1</v>
       </c>
       <c r="P1004" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="1005" spans="1:16">
@@ -52409,7 +52406,7 @@
         <v>1</v>
       </c>
       <c r="P1005" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="1006" spans="1:16">
@@ -52459,7 +52456,7 @@
         <v>1</v>
       </c>
       <c r="P1006" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="1007" spans="1:16">
@@ -52509,7 +52506,7 @@
         <v>1</v>
       </c>
       <c r="P1007" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="1008" spans="1:16">
@@ -52559,7 +52556,7 @@
         <v>1</v>
       </c>
       <c r="P1008" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="1009" spans="1:16">
@@ -53409,7 +53406,7 @@
         <v>1</v>
       </c>
       <c r="P1025" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="1026" spans="1:16">
@@ -53459,7 +53456,7 @@
         <v>1</v>
       </c>
       <c r="P1026" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="1027" spans="1:16">
@@ -53509,7 +53506,7 @@
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
@@ -53559,7 +53556,7 @@
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
@@ -53609,7 +53606,7 @@
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
@@ -53659,7 +53656,7 @@
         <v>1</v>
       </c>
       <c r="P1030" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="1031" spans="1:16">
@@ -53709,7 +53706,7 @@
         <v>1</v>
       </c>
       <c r="P1031" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="1032" spans="1:16">
@@ -53759,7 +53756,7 @@
         <v>1</v>
       </c>
       <c r="P1032" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="1033" spans="1:16">
@@ -53809,7 +53806,7 @@
         <v>1</v>
       </c>
       <c r="P1033" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="1034" spans="1:16">
@@ -53859,7 +53856,7 @@
         <v>1</v>
       </c>
       <c r="P1034" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="1035" spans="1:16">
@@ -53909,7 +53906,7 @@
         <v>1</v>
       </c>
       <c r="P1035" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="1036" spans="1:16">
@@ -53959,7 +53956,7 @@
         <v>1</v>
       </c>
       <c r="P1036" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="1037" spans="1:16">
@@ -54009,7 +54006,7 @@
         <v>1</v>
       </c>
       <c r="P1037" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="1038" spans="1:16">
@@ -54059,7 +54056,7 @@
         <v>1</v>
       </c>
       <c r="P1038" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="1039" spans="1:16">
@@ -54109,7 +54106,7 @@
         <v>1</v>
       </c>
       <c r="P1039" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="1040" spans="1:16">
@@ -54159,7 +54156,7 @@
         <v>1</v>
       </c>
       <c r="P1040" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="1041" spans="1:16">
@@ -54209,7 +54206,7 @@
         <v>1</v>
       </c>
       <c r="P1041" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="1042" spans="1:16">
@@ -54259,7 +54256,7 @@
         <v>1</v>
       </c>
       <c r="P1042" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="1043" spans="1:16">
@@ -54309,7 +54306,7 @@
         <v>1</v>
       </c>
       <c r="P1043" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="1044" spans="1:16">
@@ -54359,7 +54356,7 @@
         <v>1</v>
       </c>
       <c r="P1044" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="1045" spans="1:16">
@@ -54373,7 +54370,7 @@
         <v>7.736183913922513</v>
       </c>
       <c r="D1045" t="s">
-        <v>461</v>
+        <v>289</v>
       </c>
       <c r="E1045">
         <v>8.114051730148025</v>
@@ -54409,7 +54406,7 @@
         <v>1</v>
       </c>
       <c r="P1045" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1046" spans="1:16">
@@ -54423,10 +54420,10 @@
         <v>4.988258892022188</v>
       </c>
       <c r="D1046" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E1046">
-        <v>4.732186326363522</v>
+        <v>4.542731738378961</v>
       </c>
       <c r="F1046">
         <v>-1</v>
@@ -54435,10 +54432,10 @@
         <v>0.01123174110797781</v>
       </c>
       <c r="H1046">
-        <v>0.01120781367363648</v>
+        <v>0.01095726826162104</v>
       </c>
       <c r="I1046">
-        <v>0.2560725656586653</v>
+        <v>0.4455271536432264</v>
       </c>
       <c r="J1046">
         <v>0.6109082403087693</v>
@@ -54450,16 +54447,16 @@
         <v>8.109999999999999</v>
       </c>
       <c r="M1046">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="N1046">
-        <v>7.97</v>
+        <v>7.75</v>
       </c>
       <c r="O1046">
         <v>1</v>
       </c>
       <c r="P1046" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1047" spans="1:16">
@@ -54470,28 +54467,28 @@
         <v>288</v>
       </c>
       <c r="C1047">
-        <v>6.746077963404937</v>
+        <v>6.387093469910375</v>
       </c>
       <c r="D1047" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E1047">
-        <v>6.132357464863435</v>
+        <v>5.588268245838671</v>
       </c>
       <c r="F1047">
         <v>-1</v>
       </c>
       <c r="G1047">
-        <v>0.01057392203659507</v>
+        <v>0.01093290653008962</v>
       </c>
       <c r="H1047">
-        <v>0.009807642535136564</v>
+        <v>0.009911731754161329</v>
       </c>
       <c r="I1047">
-        <v>0.6137204985415021</v>
+        <v>0.7988252240717033</v>
       </c>
       <c r="J1047">
-        <v>0.3467250066295405</v>
+        <v>0.4117584293640626</v>
       </c>
       <c r="K1047">
         <v>5.52</v>
@@ -54500,16 +54497,16 @@
         <v>8.66</v>
       </c>
       <c r="M1047">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="N1047">
-        <v>7.97</v>
+        <v>7.75</v>
       </c>
       <c r="O1047">
         <v>1</v>
       </c>
       <c r="P1047" t="s">
-        <v>284</v>
+        <v>589</v>
       </c>
     </row>
     <row r="1048" spans="1:16">
@@ -54520,28 +54517,28 @@
         <v>288</v>
       </c>
       <c r="C1048">
-        <v>6.387093469910375</v>
+        <v>6.169756722151089</v>
       </c>
       <c r="D1048" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E1048">
-        <v>5.787680324370468</v>
+        <v>5.381562099871958</v>
       </c>
       <c r="F1048">
         <v>-1</v>
       </c>
       <c r="G1048">
-        <v>0.01093290653008962</v>
+        <v>0.01115024327784891</v>
       </c>
       <c r="H1048">
-        <v>0.01015231967562953</v>
+        <v>0.01011843790012804</v>
       </c>
       <c r="I1048">
-        <v>0.5994131455399065</v>
+        <v>0.7881946222791303</v>
       </c>
       <c r="J1048">
-        <v>0.4117584293640626</v>
+        <v>0.4511310285958173</v>
       </c>
       <c r="K1048">
         <v>5.52</v>
@@ -54550,10 +54547,10 @@
         <v>8.66</v>
       </c>
       <c r="M1048">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="N1048">
-        <v>7.97</v>
+        <v>7.75</v>
       </c>
       <c r="O1048">
         <v>1</v>
@@ -54570,28 +54567,28 @@
         <v>288</v>
       </c>
       <c r="C1049">
-        <v>6.169756722151089</v>
+        <v>6.839891390238572</v>
       </c>
       <c r="D1049" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E1049">
-        <v>5.579005548442169</v>
+        <v>6.01891844180299</v>
       </c>
       <c r="F1049">
         <v>-1</v>
       </c>
       <c r="G1049">
-        <v>0.01115024327784891</v>
+        <v>0.01048010860976143</v>
       </c>
       <c r="H1049">
-        <v>0.01036099445155783</v>
+        <v>0.00948108155819701</v>
       </c>
       <c r="I1049">
-        <v>0.5907511737089202</v>
+        <v>0.8209729484355819</v>
       </c>
       <c r="J1049">
-        <v>0.4511310285958173</v>
+        <v>0.3297298206089543</v>
       </c>
       <c r="K1049">
         <v>5.52</v>
@@ -54600,10 +54597,10 @@
         <v>8.66</v>
       </c>
       <c r="M1049">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="N1049">
-        <v>7.97</v>
+        <v>7.75</v>
       </c>
       <c r="O1049">
         <v>1</v>
@@ -54617,43 +54614,43 @@
         <v>0</v>
       </c>
       <c r="B1050" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C1050">
-        <v>6.839891390238572</v>
+        <v>-0.2622680044676837</v>
       </c>
       <c r="D1050" t="s">
         <v>462</v>
       </c>
       <c r="E1050">
-        <v>6.222431950772542</v>
+        <v>-0.9183588785748515</v>
       </c>
       <c r="F1050">
         <v>-1</v>
       </c>
       <c r="G1050">
-        <v>0.01048010860976143</v>
+        <v>0.01758226800446768</v>
       </c>
       <c r="H1050">
-        <v>0.009717568049227458</v>
+        <v>0.01705835887857485</v>
       </c>
       <c r="I1050">
-        <v>0.61745943946603</v>
+        <v>0.6560908741071678</v>
       </c>
       <c r="J1050">
-        <v>0.3297298206089543</v>
+        <v>1.652271852679201</v>
       </c>
       <c r="K1050">
-        <v>5.52</v>
+        <v>5.4</v>
       </c>
       <c r="L1050">
         <v>8.66</v>
       </c>
       <c r="M1050">
-        <v>5.3</v>
+        <v>5.44</v>
       </c>
       <c r="N1050">
-        <v>7.97</v>
+        <v>8.07</v>
       </c>
       <c r="O1050">
         <v>1</v>
@@ -54670,40 +54667,40 @@
         <v>289</v>
       </c>
       <c r="C1051">
-        <v>-0.9183588785748515</v>
+        <v>-0.3478350132647545</v>
       </c>
       <c r="D1051" t="s">
         <v>462</v>
       </c>
       <c r="E1051">
-        <v>-0.7870408191997624</v>
+        <v>-1.004559717066716</v>
       </c>
       <c r="F1051">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1051">
-        <v>0.01705835887857485</v>
+        <v>0.01766783501326476</v>
       </c>
       <c r="H1051">
-        <v>0.01672704081919976</v>
+        <v>0.01714455971706672</v>
       </c>
       <c r="I1051">
-        <v>0.1313180593750891</v>
+        <v>0.6567247038019612</v>
       </c>
       <c r="J1051">
-        <v>1.652271852679201</v>
+        <v>1.668117595049029</v>
       </c>
       <c r="K1051">
+        <v>5.4</v>
+      </c>
+      <c r="L1051">
+        <v>8.66</v>
+      </c>
+      <c r="M1051">
         <v>5.44</v>
       </c>
-      <c r="L1051">
+      <c r="N1051">
         <v>8.07</v>
-      </c>
-      <c r="M1051">
-        <v>5.3</v>
-      </c>
-      <c r="N1051">
-        <v>7.97</v>
       </c>
       <c r="O1051">
         <v>1</v>
@@ -54717,43 +54714,43 @@
         <v>0</v>
       </c>
       <c r="B1052" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C1052">
-        <v>-0.2408491423539676</v>
+        <v>-0.40350806689964</v>
       </c>
       <c r="D1052" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E1052">
-        <v>-0.5773562068985756</v>
+        <v>-1.06064516369149</v>
       </c>
       <c r="F1052">
         <v>-1</v>
       </c>
       <c r="G1052">
-        <v>0.01704084914235397</v>
+        <v>0.01772350806689964</v>
       </c>
       <c r="H1052">
-        <v>0.01633735620689858</v>
+        <v>0.01720064516369149</v>
       </c>
       <c r="I1052">
-        <v>0.336507064544608</v>
+        <v>0.6571370967918497</v>
       </c>
       <c r="J1052">
-        <v>1.668117595049029</v>
+        <v>1.67842741979623</v>
       </c>
       <c r="K1052">
-        <v>5.18</v>
+        <v>5.4</v>
       </c>
       <c r="L1052">
-        <v>8.4</v>
+        <v>8.66</v>
       </c>
       <c r="M1052">
-        <v>5.07</v>
+        <v>5.44</v>
       </c>
       <c r="N1052">
-        <v>7.88</v>
+        <v>8.07</v>
       </c>
       <c r="O1052">
         <v>1</v>
@@ -54764,52 +54761,52 @@
     </row>
     <row r="1053" spans="1:16">
       <c r="A1053" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1053" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C1053">
-        <v>-1.004559717066716</v>
+        <v>-0.328840688939037</v>
       </c>
       <c r="D1053" t="s">
         <v>462</v>
       </c>
       <c r="E1053">
-        <v>-0.8710232537598506</v>
+        <v>-1.096967827766093</v>
       </c>
       <c r="F1053">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1053">
-        <v>0.01714455971706672</v>
+        <v>0.01712884068893904</v>
       </c>
       <c r="H1053">
-        <v>0.01681102325375985</v>
+        <v>0.01723696782776609</v>
       </c>
       <c r="I1053">
-        <v>0.1335364633068652</v>
+        <v>0.7681271388270563</v>
       </c>
       <c r="J1053">
-        <v>1.668117595049029</v>
+        <v>1.685104380104061</v>
       </c>
       <c r="K1053">
+        <v>5.18</v>
+      </c>
+      <c r="L1053">
+        <v>8.4</v>
+      </c>
+      <c r="M1053">
         <v>5.44</v>
       </c>
-      <c r="L1053">
+      <c r="N1053">
         <v>8.07</v>
       </c>
-      <c r="M1053">
-        <v>5.3</v>
-      </c>
-      <c r="N1053">
-        <v>7.97</v>
-      </c>
       <c r="O1053">
         <v>1</v>
       </c>
       <c r="P1053" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="1054" spans="1:16">
@@ -54820,28 +54817,28 @@
         <v>290</v>
       </c>
       <c r="C1054">
-        <v>-0.2942540345444691</v>
+        <v>-0.3540902770912258</v>
       </c>
       <c r="D1054" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E1054">
-        <v>-0.6296270183668851</v>
+        <v>-1.12348476976376</v>
       </c>
       <c r="F1054">
         <v>-1</v>
       </c>
       <c r="G1054">
-        <v>0.01709425403454447</v>
+        <v>0.01715409027709123</v>
       </c>
       <c r="H1054">
-        <v>0.01638962701836688</v>
+        <v>0.01726348476976376</v>
       </c>
       <c r="I1054">
-        <v>0.335372983822416</v>
+        <v>0.769394492672534</v>
       </c>
       <c r="J1054">
-        <v>1.67842741979623</v>
+        <v>1.689978817971279</v>
       </c>
       <c r="K1054">
         <v>5.18</v>
@@ -54850,266 +54847,16 @@
         <v>8.4</v>
       </c>
       <c r="M1054">
-        <v>5.07</v>
+        <v>5.44</v>
       </c>
       <c r="N1054">
-        <v>7.88</v>
+        <v>8.07</v>
       </c>
       <c r="O1054">
         <v>1</v>
       </c>
       <c r="P1054" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="1055" spans="1:16">
-      <c r="A1055" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1055" t="s">
         <v>289</v>
-      </c>
-      <c r="C1055">
-        <v>-1.06064516369149</v>
-      </c>
-      <c r="D1055" t="s">
-        <v>462</v>
-      </c>
-      <c r="E1055">
-        <v>-0.9256653249200175</v>
-      </c>
-      <c r="F1055">
-        <v>1</v>
-      </c>
-      <c r="G1055">
-        <v>0.01720064516369149</v>
-      </c>
-      <c r="H1055">
-        <v>0.01686566532492002</v>
-      </c>
-      <c r="I1055">
-        <v>0.1349798387714722</v>
-      </c>
-      <c r="J1055">
-        <v>1.67842741979623</v>
-      </c>
-      <c r="K1055">
-        <v>5.44</v>
-      </c>
-      <c r="L1055">
-        <v>8.07</v>
-      </c>
-      <c r="M1055">
-        <v>5.3</v>
-      </c>
-      <c r="N1055">
-        <v>7.97</v>
-      </c>
-      <c r="O1055">
-        <v>1</v>
-      </c>
-      <c r="P1055" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="1056" spans="1:16">
-      <c r="A1056" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1056" t="s">
-        <v>290</v>
-      </c>
-      <c r="C1056">
-        <v>-0.328840688939037</v>
-      </c>
-      <c r="D1056" t="s">
-        <v>463</v>
-      </c>
-      <c r="E1056">
-        <v>-0.6634792071275912</v>
-      </c>
-      <c r="F1056">
-        <v>-1</v>
-      </c>
-      <c r="G1056">
-        <v>0.01712884068893904</v>
-      </c>
-      <c r="H1056">
-        <v>0.01642347920712759</v>
-      </c>
-      <c r="I1056">
-        <v>0.3346385181885543</v>
-      </c>
-      <c r="J1056">
-        <v>1.685104380104061</v>
-      </c>
-      <c r="K1056">
-        <v>5.18</v>
-      </c>
-      <c r="L1056">
-        <v>8.4</v>
-      </c>
-      <c r="M1056">
-        <v>5.07</v>
-      </c>
-      <c r="N1056">
-        <v>7.88</v>
-      </c>
-      <c r="O1056">
-        <v>1</v>
-      </c>
-      <c r="P1056" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="1057" spans="1:16">
-      <c r="A1057" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1057" t="s">
-        <v>289</v>
-      </c>
-      <c r="C1057">
-        <v>-1.096967827766093</v>
-      </c>
-      <c r="D1057" t="s">
-        <v>462</v>
-      </c>
-      <c r="E1057">
-        <v>-0.9610532145515238</v>
-      </c>
-      <c r="F1057">
-        <v>1</v>
-      </c>
-      <c r="G1057">
-        <v>0.01723696782776609</v>
-      </c>
-      <c r="H1057">
-        <v>0.01690105321455153</v>
-      </c>
-      <c r="I1057">
-        <v>0.1359146132145694</v>
-      </c>
-      <c r="J1057">
-        <v>1.685104380104061</v>
-      </c>
-      <c r="K1057">
-        <v>5.44</v>
-      </c>
-      <c r="L1057">
-        <v>8.07</v>
-      </c>
-      <c r="M1057">
-        <v>5.3</v>
-      </c>
-      <c r="N1057">
-        <v>7.97</v>
-      </c>
-      <c r="O1057">
-        <v>1</v>
-      </c>
-      <c r="P1057" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="1058" spans="1:16">
-      <c r="A1058" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1058" t="s">
-        <v>290</v>
-      </c>
-      <c r="C1058">
-        <v>-0.3540902770912258</v>
-      </c>
-      <c r="D1058" t="s">
-        <v>463</v>
-      </c>
-      <c r="E1058">
-        <v>-0.6881926071143871</v>
-      </c>
-      <c r="F1058">
-        <v>-1</v>
-      </c>
-      <c r="G1058">
-        <v>0.01715409027709123</v>
-      </c>
-      <c r="H1058">
-        <v>0.01644819260711439</v>
-      </c>
-      <c r="I1058">
-        <v>0.3341023300231614</v>
-      </c>
-      <c r="J1058">
-        <v>1.689978817971279</v>
-      </c>
-      <c r="K1058">
-        <v>5.18</v>
-      </c>
-      <c r="L1058">
-        <v>8.4</v>
-      </c>
-      <c r="M1058">
-        <v>5.07</v>
-      </c>
-      <c r="N1058">
-        <v>7.88</v>
-      </c>
-      <c r="O1058">
-        <v>1</v>
-      </c>
-      <c r="P1058" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="1059" spans="1:16">
-      <c r="A1059" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1059" t="s">
-        <v>289</v>
-      </c>
-      <c r="C1059">
-        <v>-1.12348476976376</v>
-      </c>
-      <c r="D1059" t="s">
-        <v>462</v>
-      </c>
-      <c r="E1059">
-        <v>-0.9868877352477812</v>
-      </c>
-      <c r="F1059">
-        <v>1</v>
-      </c>
-      <c r="G1059">
-        <v>0.01726348476976376</v>
-      </c>
-      <c r="H1059">
-        <v>0.01692688773524778</v>
-      </c>
-      <c r="I1059">
-        <v>0.1365970345159786</v>
-      </c>
-      <c r="J1059">
-        <v>1.689978817971279</v>
-      </c>
-      <c r="K1059">
-        <v>5.44</v>
-      </c>
-      <c r="L1059">
-        <v>8.07</v>
-      </c>
-      <c r="M1059">
-        <v>5.3</v>
-      </c>
-      <c r="N1059">
-        <v>7.97</v>
-      </c>
-      <c r="O1059">
-        <v>1</v>
-      </c>
-      <c r="P1059" t="s">
-        <v>461</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3174" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3186" uniqueCount="595">
   <si>
     <t>trade_time</t>
   </si>
@@ -886,7 +886,7 @@
     <t>2021-09-23</t>
   </si>
   <si>
-    <t>2021-09-24</t>
+    <t>2021-10-12</t>
   </si>
   <si>
     <t>2016-04-28</t>
@@ -1399,12 +1399,12 @@
     <t>2021-09-09</t>
   </si>
   <si>
-    <t>2021-10-12</t>
-  </si>
-  <si>
     <t>2021-10-08</t>
   </si>
   <si>
+    <t>2021-10-18</t>
+  </si>
+  <si>
     <t>2016-03-24</t>
   </si>
   <si>
@@ -1780,13 +1780,10 @@
     <t>2021-05-28</t>
   </si>
   <si>
+    <t>2021-06-16</t>
+  </si>
+  <si>
     <t>2021-06-18</t>
-  </si>
-  <si>
-    <t>2021-07-05</t>
-  </si>
-  <si>
-    <t>2021-07-06</t>
   </si>
   <si>
     <t>2021-07-08</t>
@@ -2159,7 +2156,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1054"/>
+  <dimension ref="A1:P1058"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -54417,28 +54414,28 @@
         <v>287</v>
       </c>
       <c r="C1046">
-        <v>4.988258892022188</v>
+        <v>5.66445723600427</v>
       </c>
       <c r="D1046" t="s">
-        <v>461</v>
+        <v>290</v>
       </c>
       <c r="E1046">
-        <v>4.542731738378961</v>
+        <v>5.237456064387949</v>
       </c>
       <c r="F1046">
         <v>-1</v>
       </c>
       <c r="G1046">
-        <v>0.01123174110797781</v>
+        <v>0.01055554276399573</v>
       </c>
       <c r="H1046">
-        <v>0.01095726826162104</v>
+        <v>0.01026254393561205</v>
       </c>
       <c r="I1046">
-        <v>0.4455271536432264</v>
+        <v>0.4270011716163209</v>
       </c>
       <c r="J1046">
-        <v>0.6109082403087693</v>
+        <v>0.4785797972594382</v>
       </c>
       <c r="K1046">
         <v>5.11</v>
@@ -54464,37 +54461,37 @@
         <v>0</v>
       </c>
       <c r="B1047" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C1047">
-        <v>6.387093469910375</v>
+        <v>5.440858208955218</v>
       </c>
       <c r="D1047" t="s">
-        <v>461</v>
+        <v>290</v>
       </c>
       <c r="E1047">
-        <v>5.588268245838671</v>
+        <v>5.007731036597828</v>
       </c>
       <c r="F1047">
         <v>-1</v>
       </c>
       <c r="G1047">
-        <v>0.01093290653008962</v>
+        <v>0.01077914179104478</v>
       </c>
       <c r="H1047">
-        <v>0.009911731754161329</v>
+        <v>0.01049226896340217</v>
       </c>
       <c r="I1047">
-        <v>0.7988252240717033</v>
+        <v>0.4331271723573904</v>
       </c>
       <c r="J1047">
-        <v>0.4117584293640626</v>
+        <v>0.5223369454099376</v>
       </c>
       <c r="K1047">
-        <v>5.52</v>
+        <v>5.11</v>
       </c>
       <c r="L1047">
-        <v>8.66</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="M1047">
         <v>5.25</v>
@@ -54506,7 +54503,7 @@
         <v>1</v>
       </c>
       <c r="P1047" t="s">
-        <v>589</v>
+        <v>277</v>
       </c>
     </row>
     <row r="1048" spans="1:16">
@@ -54514,37 +54511,37 @@
         <v>0</v>
       </c>
       <c r="B1048" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C1048">
-        <v>6.169756722151089</v>
+        <v>4.988258892022188</v>
       </c>
       <c r="D1048" t="s">
-        <v>461</v>
+        <v>290</v>
       </c>
       <c r="E1048">
-        <v>5.381562099871958</v>
+        <v>4.542731738378961</v>
       </c>
       <c r="F1048">
         <v>-1</v>
       </c>
       <c r="G1048">
-        <v>0.01115024327784891</v>
+        <v>0.01123174110797781</v>
       </c>
       <c r="H1048">
-        <v>0.01011843790012804</v>
+        <v>0.01095726826162104</v>
       </c>
       <c r="I1048">
-        <v>0.7881946222791303</v>
+        <v>0.4455271536432264</v>
       </c>
       <c r="J1048">
-        <v>0.4511310285958173</v>
+        <v>0.6109082403087693</v>
       </c>
       <c r="K1048">
-        <v>5.52</v>
+        <v>5.11</v>
       </c>
       <c r="L1048">
-        <v>8.66</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="M1048">
         <v>5.25</v>
@@ -54556,7 +54553,7 @@
         <v>1</v>
       </c>
       <c r="P1048" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="1049" spans="1:16">
@@ -54570,7 +54567,7 @@
         <v>6.839891390238572</v>
       </c>
       <c r="D1049" t="s">
-        <v>461</v>
+        <v>290</v>
       </c>
       <c r="E1049">
         <v>6.01891844180299</v>
@@ -54606,7 +54603,7 @@
         <v>1</v>
       </c>
       <c r="P1049" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="1050" spans="1:16">
@@ -54620,7 +54617,7 @@
         <v>-0.2622680044676837</v>
       </c>
       <c r="D1050" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E1050">
         <v>-0.9183588785748515</v>
@@ -54656,57 +54653,57 @@
         <v>1</v>
       </c>
       <c r="P1050" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="1051" spans="1:16">
       <c r="A1051" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1051" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C1051">
-        <v>-0.3478350132647545</v>
+        <v>-0.924427226565804</v>
       </c>
       <c r="D1051" t="s">
         <v>462</v>
       </c>
       <c r="E1051">
-        <v>-1.004559717066716</v>
+        <v>-0.8983363524586361</v>
       </c>
       <c r="F1051">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1051">
-        <v>0.01766783501326476</v>
+        <v>0.0164244272265658</v>
       </c>
       <c r="H1051">
-        <v>0.01714455971706672</v>
+        <v>0.01631833635245864</v>
       </c>
       <c r="I1051">
-        <v>0.6567247038019612</v>
+        <v>0.02609087410716793</v>
       </c>
       <c r="J1051">
-        <v>1.668117595049029</v>
+        <v>1.652271852679201</v>
       </c>
       <c r="K1051">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="L1051">
-        <v>8.66</v>
+        <v>7.75</v>
       </c>
       <c r="M1051">
-        <v>5.44</v>
+        <v>5.21</v>
       </c>
       <c r="N1051">
-        <v>8.07</v>
+        <v>7.71</v>
       </c>
       <c r="O1051">
         <v>1</v>
       </c>
       <c r="P1051" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="1052" spans="1:16">
@@ -54717,28 +54714,28 @@
         <v>289</v>
       </c>
       <c r="C1052">
-        <v>-0.40350806689964</v>
+        <v>-0.3478350132647545</v>
       </c>
       <c r="D1052" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E1052">
-        <v>-1.06064516369149</v>
+        <v>-1.004559717066716</v>
       </c>
       <c r="F1052">
         <v>-1</v>
       </c>
       <c r="G1052">
-        <v>0.01772350806689964</v>
+        <v>0.01766783501326476</v>
       </c>
       <c r="H1052">
-        <v>0.01720064516369149</v>
+        <v>0.01714455971706672</v>
       </c>
       <c r="I1052">
-        <v>0.6571370967918497</v>
+        <v>0.6567247038019612</v>
       </c>
       <c r="J1052">
-        <v>1.67842741979623</v>
+        <v>1.668117595049029</v>
       </c>
       <c r="K1052">
         <v>5.4</v>
@@ -54756,57 +54753,57 @@
         <v>1</v>
       </c>
       <c r="P1052" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1053" spans="1:16">
       <c r="A1053" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1053" t="s">
         <v>290</v>
       </c>
       <c r="C1053">
-        <v>-0.328840688939037</v>
+        <v>-1.007617374007401</v>
       </c>
       <c r="D1053" t="s">
         <v>462</v>
       </c>
       <c r="E1053">
-        <v>-1.096967827766093</v>
+        <v>-0.9808926702054395</v>
       </c>
       <c r="F1053">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1053">
-        <v>0.01712884068893904</v>
+        <v>0.0165076173740074</v>
       </c>
       <c r="H1053">
-        <v>0.01723696782776609</v>
+        <v>0.01640089267020544</v>
       </c>
       <c r="I1053">
-        <v>0.7681271388270563</v>
+        <v>0.02672470380196135</v>
       </c>
       <c r="J1053">
-        <v>1.685104380104061</v>
+        <v>1.668117595049029</v>
       </c>
       <c r="K1053">
-        <v>5.18</v>
+        <v>5.25</v>
       </c>
       <c r="L1053">
-        <v>8.4</v>
+        <v>7.75</v>
       </c>
       <c r="M1053">
-        <v>5.44</v>
+        <v>5.21</v>
       </c>
       <c r="N1053">
-        <v>8.07</v>
+        <v>7.71</v>
       </c>
       <c r="O1053">
         <v>1</v>
       </c>
       <c r="P1053" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1054" spans="1:16">
@@ -54814,37 +54811,37 @@
         <v>0</v>
       </c>
       <c r="B1054" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C1054">
-        <v>-0.3540902770912258</v>
+        <v>-0.40350806689964</v>
       </c>
       <c r="D1054" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E1054">
-        <v>-1.12348476976376</v>
+        <v>-1.06064516369149</v>
       </c>
       <c r="F1054">
         <v>-1</v>
       </c>
       <c r="G1054">
-        <v>0.01715409027709123</v>
+        <v>0.01772350806689964</v>
       </c>
       <c r="H1054">
-        <v>0.01726348476976376</v>
+        <v>0.01720064516369149</v>
       </c>
       <c r="I1054">
-        <v>0.769394492672534</v>
+        <v>0.6571370967918497</v>
       </c>
       <c r="J1054">
-        <v>1.689978817971279</v>
+        <v>1.67842741979623</v>
       </c>
       <c r="K1054">
-        <v>5.18</v>
+        <v>5.4</v>
       </c>
       <c r="L1054">
-        <v>8.4</v>
+        <v>8.66</v>
       </c>
       <c r="M1054">
         <v>5.44</v>
@@ -54856,6 +54853,206 @@
         <v>1</v>
       </c>
       <c r="P1054" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:16">
+      <c r="A1055" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1055" t="s">
+        <v>290</v>
+      </c>
+      <c r="C1055">
+        <v>-1.061743953930206</v>
+      </c>
+      <c r="D1055" t="s">
+        <v>462</v>
+      </c>
+      <c r="E1055">
+        <v>-1.034606857138356</v>
+      </c>
+      <c r="F1055">
+        <v>1</v>
+      </c>
+      <c r="G1055">
+        <v>0.01656174395393021</v>
+      </c>
+      <c r="H1055">
+        <v>0.01645460685713836</v>
+      </c>
+      <c r="I1055">
+        <v>0.02713709679184984</v>
+      </c>
+      <c r="J1055">
+        <v>1.67842741979623</v>
+      </c>
+      <c r="K1055">
+        <v>5.25</v>
+      </c>
+      <c r="L1055">
+        <v>7.75</v>
+      </c>
+      <c r="M1055">
+        <v>5.21</v>
+      </c>
+      <c r="N1055">
+        <v>7.71</v>
+      </c>
+      <c r="O1055">
+        <v>1</v>
+      </c>
+      <c r="P1055" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:16">
+      <c r="A1056" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1056" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1056">
+        <v>-0.4395636525619313</v>
+      </c>
+      <c r="D1056" t="s">
+        <v>461</v>
+      </c>
+      <c r="E1056">
+        <v>-1.096967827766093</v>
+      </c>
+      <c r="F1056">
+        <v>-1</v>
+      </c>
+      <c r="G1056">
+        <v>0.01775956365256193</v>
+      </c>
+      <c r="H1056">
+        <v>0.01723696782776609</v>
+      </c>
+      <c r="I1056">
+        <v>0.6574041752041619</v>
+      </c>
+      <c r="J1056">
+        <v>1.685104380104061</v>
+      </c>
+      <c r="K1056">
+        <v>5.4</v>
+      </c>
+      <c r="L1056">
+        <v>8.66</v>
+      </c>
+      <c r="M1056">
+        <v>5.44</v>
+      </c>
+      <c r="N1056">
+        <v>8.07</v>
+      </c>
+      <c r="O1056">
+        <v>1</v>
+      </c>
+      <c r="P1056" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:16">
+      <c r="A1057" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1057" t="s">
+        <v>290</v>
+      </c>
+      <c r="C1057">
+        <v>-1.096797995546321</v>
+      </c>
+      <c r="D1057" t="s">
+        <v>462</v>
+      </c>
+      <c r="E1057">
+        <v>-1.069393820342159</v>
+      </c>
+      <c r="F1057">
+        <v>1</v>
+      </c>
+      <c r="G1057">
+        <v>0.01659679799554632</v>
+      </c>
+      <c r="H1057">
+        <v>0.01648939382034216</v>
+      </c>
+      <c r="I1057">
+        <v>0.02740417520416205</v>
+      </c>
+      <c r="J1057">
+        <v>1.685104380104061</v>
+      </c>
+      <c r="K1057">
+        <v>5.25</v>
+      </c>
+      <c r="L1057">
+        <v>7.75</v>
+      </c>
+      <c r="M1057">
+        <v>5.21</v>
+      </c>
+      <c r="N1057">
+        <v>7.71</v>
+      </c>
+      <c r="O1057">
+        <v>1</v>
+      </c>
+      <c r="P1057" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:16">
+      <c r="A1058" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1058" t="s">
+        <v>290</v>
+      </c>
+      <c r="C1058">
+        <v>-1.122388794349217</v>
+      </c>
+      <c r="D1058" t="s">
+        <v>462</v>
+      </c>
+      <c r="E1058">
+        <v>-1.094789641630366</v>
+      </c>
+      <c r="F1058">
+        <v>1</v>
+      </c>
+      <c r="G1058">
+        <v>0.01662238879434922</v>
+      </c>
+      <c r="H1058">
+        <v>0.01651478964163037</v>
+      </c>
+      <c r="I1058">
+        <v>0.02759915271885038</v>
+      </c>
+      <c r="J1058">
+        <v>1.689978817971279</v>
+      </c>
+      <c r="K1058">
+        <v>5.25</v>
+      </c>
+      <c r="L1058">
+        <v>7.75</v>
+      </c>
+      <c r="M1058">
+        <v>5.21</v>
+      </c>
+      <c r="N1058">
+        <v>7.71</v>
+      </c>
+      <c r="O1058">
+        <v>1</v>
+      </c>
+      <c r="P1058" t="s">
         <v>289</v>
       </c>
     </row>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3186" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3192" uniqueCount="595">
   <si>
     <t>trade_time</t>
   </si>
@@ -1402,7 +1402,7 @@
     <t>2021-10-08</t>
   </si>
   <si>
-    <t>2021-10-18</t>
+    <t>2021-10-19</t>
   </si>
   <si>
     <t>2016-03-24</t>
@@ -2156,7 +2156,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1058"/>
+  <dimension ref="A1:P1060"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -54670,7 +54670,7 @@
         <v>462</v>
       </c>
       <c r="E1051">
-        <v>-0.8983363524586361</v>
+        <v>-0.8452909154050516</v>
       </c>
       <c r="F1051">
         <v>1</v>
@@ -54679,10 +54679,10 @@
         <v>0.0164244272265658</v>
       </c>
       <c r="H1051">
-        <v>0.01631833635245864</v>
+        <v>0.01630529091540505</v>
       </c>
       <c r="I1051">
-        <v>0.02609087410716793</v>
+        <v>0.07913631116075237</v>
       </c>
       <c r="J1051">
         <v>1.652271852679201</v>
@@ -54694,10 +54694,10 @@
         <v>7.75</v>
       </c>
       <c r="M1051">
-        <v>5.21</v>
+        <v>5.19</v>
       </c>
       <c r="N1051">
-        <v>7.71</v>
+        <v>7.73</v>
       </c>
       <c r="O1051">
         <v>1</v>
@@ -54770,7 +54770,7 @@
         <v>462</v>
       </c>
       <c r="E1053">
-        <v>-0.9808926702054395</v>
+        <v>-0.9275303183044592</v>
       </c>
       <c r="F1053">
         <v>1</v>
@@ -54779,10 +54779,10 @@
         <v>0.0165076173740074</v>
       </c>
       <c r="H1053">
-        <v>0.01640089267020544</v>
+        <v>0.01638753031830446</v>
       </c>
       <c r="I1053">
-        <v>0.02672470380196135</v>
+        <v>0.08008705570294161</v>
       </c>
       <c r="J1053">
         <v>1.668117595049029</v>
@@ -54794,10 +54794,10 @@
         <v>7.75</v>
       </c>
       <c r="M1053">
-        <v>5.21</v>
+        <v>5.19</v>
       </c>
       <c r="N1053">
-        <v>7.71</v>
+        <v>7.73</v>
       </c>
       <c r="O1053">
         <v>1</v>
@@ -54870,7 +54870,7 @@
         <v>462</v>
       </c>
       <c r="E1055">
-        <v>-1.034606857138356</v>
+        <v>-0.9810383087424324</v>
       </c>
       <c r="F1055">
         <v>1</v>
@@ -54879,10 +54879,10 @@
         <v>0.01656174395393021</v>
       </c>
       <c r="H1055">
-        <v>0.01645460685713836</v>
+        <v>0.01644103830874244</v>
       </c>
       <c r="I1055">
-        <v>0.02713709679184984</v>
+        <v>0.08070564518777346</v>
       </c>
       <c r="J1055">
         <v>1.67842741979623</v>
@@ -54894,10 +54894,10 @@
         <v>7.75</v>
       </c>
       <c r="M1055">
-        <v>5.21</v>
+        <v>5.19</v>
       </c>
       <c r="N1055">
-        <v>7.71</v>
+        <v>7.73</v>
       </c>
       <c r="O1055">
         <v>1</v>
@@ -54961,43 +54961,43 @@
         <v>1</v>
       </c>
       <c r="B1057" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C1057">
-        <v>-1.096797995546321</v>
+        <v>-0.5008833823317538</v>
       </c>
       <c r="D1057" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E1057">
-        <v>-1.069393820342159</v>
+        <v>-1.096967827766093</v>
       </c>
       <c r="F1057">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1057">
-        <v>0.01659679799554632</v>
+        <v>0.01672088338233175</v>
       </c>
       <c r="H1057">
-        <v>0.01648939382034216</v>
+        <v>0.01723696782776609</v>
       </c>
       <c r="I1057">
-        <v>0.02740417520416205</v>
+        <v>0.5960844454343395</v>
       </c>
       <c r="J1057">
         <v>1.685104380104061</v>
       </c>
       <c r="K1057">
-        <v>5.25</v>
+        <v>5.11</v>
       </c>
       <c r="L1057">
-        <v>7.75</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="M1057">
-        <v>5.21</v>
+        <v>5.44</v>
       </c>
       <c r="N1057">
-        <v>7.71</v>
+        <v>8.07</v>
       </c>
       <c r="O1057">
         <v>1</v>
@@ -55008,34 +55008,34 @@
     </row>
     <row r="1058" spans="1:16">
       <c r="A1058" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1058" t="s">
         <v>290</v>
       </c>
       <c r="C1058">
-        <v>-1.122388794349217</v>
+        <v>-1.096797995546321</v>
       </c>
       <c r="D1058" t="s">
         <v>462</v>
       </c>
       <c r="E1058">
-        <v>-1.094789641630366</v>
+        <v>-1.015691732740079</v>
       </c>
       <c r="F1058">
         <v>1</v>
       </c>
       <c r="G1058">
-        <v>0.01662238879434922</v>
+        <v>0.01659679799554632</v>
       </c>
       <c r="H1058">
-        <v>0.01651478964163037</v>
+        <v>0.01647569173274008</v>
       </c>
       <c r="I1058">
-        <v>0.02759915271885038</v>
+        <v>0.08110626280624267</v>
       </c>
       <c r="J1058">
-        <v>1.689978817971279</v>
+        <v>1.685104380104061</v>
       </c>
       <c r="K1058">
         <v>5.25</v>
@@ -55044,15 +55044,115 @@
         <v>7.75</v>
       </c>
       <c r="M1058">
-        <v>5.21</v>
+        <v>5.19</v>
       </c>
       <c r="N1058">
-        <v>7.71</v>
+        <v>7.73</v>
       </c>
       <c r="O1058">
         <v>1</v>
       </c>
       <c r="P1058" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:16">
+      <c r="A1059" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1059" t="s">
+        <v>287</v>
+      </c>
+      <c r="C1059">
+        <v>-0.525791759833238</v>
+      </c>
+      <c r="D1059" t="s">
+        <v>461</v>
+      </c>
+      <c r="E1059">
+        <v>-1.12348476976376</v>
+      </c>
+      <c r="F1059">
+        <v>-1</v>
+      </c>
+      <c r="G1059">
+        <v>0.01674579175983324</v>
+      </c>
+      <c r="H1059">
+        <v>0.01726348476976376</v>
+      </c>
+      <c r="I1059">
+        <v>0.5976930099305218</v>
+      </c>
+      <c r="J1059">
+        <v>1.689978817971279</v>
+      </c>
+      <c r="K1059">
+        <v>5.11</v>
+      </c>
+      <c r="L1059">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="M1059">
+        <v>5.44</v>
+      </c>
+      <c r="N1059">
+        <v>8.07</v>
+      </c>
+      <c r="O1059">
+        <v>1</v>
+      </c>
+      <c r="P1059" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:16">
+      <c r="A1060" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1060" t="s">
+        <v>290</v>
+      </c>
+      <c r="C1060">
+        <v>-1.122388794349217</v>
+      </c>
+      <c r="D1060" t="s">
+        <v>462</v>
+      </c>
+      <c r="E1060">
+        <v>-1.04099006527094</v>
+      </c>
+      <c r="F1060">
+        <v>1</v>
+      </c>
+      <c r="G1060">
+        <v>0.01662238879434922</v>
+      </c>
+      <c r="H1060">
+        <v>0.01650099006527094</v>
+      </c>
+      <c r="I1060">
+        <v>0.08139872907827694</v>
+      </c>
+      <c r="J1060">
+        <v>1.689978817971279</v>
+      </c>
+      <c r="K1060">
+        <v>5.25</v>
+      </c>
+      <c r="L1060">
+        <v>7.75</v>
+      </c>
+      <c r="M1060">
+        <v>5.19</v>
+      </c>
+      <c r="N1060">
+        <v>7.73</v>
+      </c>
+      <c r="O1060">
+        <v>1</v>
+      </c>
+      <c r="P1060" t="s">
         <v>289</v>
       </c>
     </row>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3189" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3195" uniqueCount="600">
   <si>
     <t>trade_time</t>
   </si>
@@ -1405,10 +1405,13 @@
     <t>2021-10-12</t>
   </si>
   <si>
+    <t>2021-10-15</t>
+  </si>
+  <si>
     <t>2021-10-08</t>
   </si>
   <si>
-    <t>2021-10-28</t>
+    <t>2021-11-01</t>
   </si>
   <si>
     <t>2016-03-24</t>
@@ -1796,6 +1799,9 @@
   </si>
   <si>
     <t>2021-06-24</t>
+  </si>
+  <si>
+    <t>2021-06-25</t>
   </si>
   <si>
     <t>2021-09-14</t>
@@ -2165,7 +2171,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1059"/>
+  <dimension ref="A1:P1061"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2262,7 +2268,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2312,7 +2318,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2362,7 +2368,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2412,7 +2418,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2462,7 +2468,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2512,7 +2518,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2562,7 +2568,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2612,7 +2618,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2662,7 +2668,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2712,7 +2718,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2762,7 +2768,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2812,7 +2818,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2862,7 +2868,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2912,7 +2918,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2962,7 +2968,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -3012,7 +3018,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -3062,7 +3068,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -3112,7 +3118,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -3162,7 +3168,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -3212,7 +3218,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -3262,7 +3268,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3312,7 +3318,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3362,7 +3368,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3412,7 +3418,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3462,7 +3468,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3512,7 +3518,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3562,7 +3568,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3612,7 +3618,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3662,7 +3668,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3712,7 +3718,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3762,7 +3768,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3812,7 +3818,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3862,7 +3868,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3912,7 +3918,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3962,7 +3968,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -4012,7 +4018,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -4062,7 +4068,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -4112,7 +4118,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -4162,7 +4168,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -4212,7 +4218,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -4262,7 +4268,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4312,7 +4318,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4362,7 +4368,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4412,7 +4418,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4462,7 +4468,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4512,7 +4518,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4562,7 +4568,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4612,7 +4618,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4662,7 +4668,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4712,7 +4718,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4762,7 +4768,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4812,7 +4818,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4862,7 +4868,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4912,7 +4918,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4962,7 +4968,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -5012,7 +5018,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -5062,7 +5068,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -5112,7 +5118,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -5162,7 +5168,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -5212,7 +5218,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -5262,7 +5268,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5312,7 +5318,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5362,7 +5368,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5962,7 +5968,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -6012,7 +6018,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -6062,7 +6068,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -6112,7 +6118,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -6162,7 +6168,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -6212,7 +6218,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -6262,7 +6268,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -6312,7 +6318,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -6362,7 +6368,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6412,7 +6418,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6462,7 +6468,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6512,7 +6518,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6562,7 +6568,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6612,7 +6618,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6662,7 +6668,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6712,7 +6718,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6762,7 +6768,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6812,7 +6818,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6862,7 +6868,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6912,7 +6918,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6962,7 +6968,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -7312,7 +7318,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7362,7 +7368,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7412,7 +7418,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7462,7 +7468,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7512,7 +7518,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7562,7 +7568,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7612,7 +7618,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7662,7 +7668,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7712,7 +7718,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7762,7 +7768,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7812,7 +7818,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7862,7 +7868,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7912,7 +7918,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7962,7 +7968,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -8012,7 +8018,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -8062,7 +8068,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -8112,7 +8118,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -8162,7 +8168,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -8212,7 +8218,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -8562,7 +8568,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8612,7 +8618,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8662,7 +8668,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8712,7 +8718,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8762,7 +8768,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8812,7 +8818,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8862,7 +8868,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8912,7 +8918,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8962,7 +8968,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -9012,7 +9018,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -9062,7 +9068,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -9112,7 +9118,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -9162,7 +9168,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -9212,7 +9218,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -9262,7 +9268,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -9312,7 +9318,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9362,7 +9368,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9412,7 +9418,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -10762,7 +10768,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10812,7 +10818,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10862,7 +10868,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10912,7 +10918,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10962,7 +10968,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -11012,7 +11018,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -11062,7 +11068,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -11112,7 +11118,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -11162,7 +11168,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -11312,7 +11318,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -11362,7 +11368,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11562,7 +11568,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11612,7 +11618,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11662,7 +11668,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11712,7 +11718,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11762,7 +11768,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11812,7 +11818,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -12262,7 +12268,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -12312,7 +12318,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12362,7 +12368,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12412,7 +12418,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12462,7 +12468,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -17162,7 +17168,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -17212,7 +17218,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -17262,7 +17268,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -17312,7 +17318,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17362,7 +17368,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17412,7 +17418,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17462,7 +17468,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17712,7 +17718,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17762,7 +17768,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17812,7 +17818,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17862,7 +17868,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17912,7 +17918,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -18412,7 +18418,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -18462,7 +18468,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -18512,7 +18518,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -18562,7 +18568,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18712,7 +18718,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18762,7 +18768,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18812,7 +18818,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18862,7 +18868,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18912,7 +18918,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -19162,7 +19168,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -19212,7 +19218,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -19262,7 +19268,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -19312,7 +19318,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19362,7 +19368,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19412,7 +19418,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19462,7 +19468,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19512,7 +19518,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19562,7 +19568,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19612,7 +19618,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19662,7 +19668,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19712,7 +19718,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19762,7 +19768,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19812,7 +19818,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19862,7 +19868,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19912,7 +19918,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19962,7 +19968,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -20012,7 +20018,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -20062,7 +20068,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -20112,7 +20118,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -20162,7 +20168,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -20212,7 +20218,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -20262,7 +20268,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -20312,7 +20318,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -20362,7 +20368,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20412,7 +20418,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20462,7 +20468,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20512,7 +20518,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20562,7 +20568,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20612,7 +20618,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20662,7 +20668,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20712,7 +20718,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20762,7 +20768,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20812,7 +20818,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20862,7 +20868,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20912,7 +20918,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20962,7 +20968,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -21012,7 +21018,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -21062,7 +21068,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -21112,7 +21118,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -21162,7 +21168,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -21212,7 +21218,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -21262,7 +21268,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -21312,7 +21318,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21612,7 +21618,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21662,7 +21668,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21712,7 +21718,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21762,7 +21768,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21812,7 +21818,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -22512,7 +22518,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22562,7 +22568,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22612,7 +22618,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22662,7 +22668,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22712,7 +22718,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22762,7 +22768,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22812,7 +22818,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22862,7 +22868,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22912,7 +22918,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22962,7 +22968,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -23012,7 +23018,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -23062,7 +23068,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -23112,7 +23118,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -23162,7 +23168,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -23212,7 +23218,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -23262,7 +23268,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -23312,7 +23318,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -23362,7 +23368,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -23412,7 +23418,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -23462,7 +23468,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -23512,7 +23518,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23862,7 +23868,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23912,7 +23918,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23962,7 +23968,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -24012,7 +24018,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -24062,7 +24068,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -24112,7 +24118,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -24162,7 +24168,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -24212,7 +24218,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -24262,7 +24268,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -24312,7 +24318,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24362,7 +24368,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24412,7 +24418,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24462,7 +24468,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24512,7 +24518,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24562,7 +24568,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24612,7 +24618,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24662,7 +24668,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24712,7 +24718,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24762,7 +24768,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24812,7 +24818,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24862,7 +24868,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24912,7 +24918,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24962,7 +24968,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -25012,7 +25018,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -25062,7 +25068,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -25112,7 +25118,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -25162,7 +25168,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -25212,7 +25218,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -25262,7 +25268,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -25312,7 +25318,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -25362,7 +25368,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25412,7 +25418,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -25462,7 +25468,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25512,7 +25518,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25562,7 +25568,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25612,7 +25618,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25662,7 +25668,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25712,7 +25718,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25762,7 +25768,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25812,7 +25818,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25862,7 +25868,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25912,7 +25918,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25962,7 +25968,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -26012,7 +26018,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -26062,7 +26068,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -26312,7 +26318,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26362,7 +26368,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26412,7 +26418,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26462,7 +26468,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26512,7 +26518,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26812,7 +26818,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26862,7 +26868,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26912,7 +26918,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26962,7 +26968,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -27012,7 +27018,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -27562,7 +27568,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27612,7 +27618,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27662,7 +27668,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27712,7 +27718,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27762,7 +27768,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27812,7 +27818,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27862,7 +27868,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -28162,7 +28168,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -28212,7 +28218,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -28262,7 +28268,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -28312,7 +28318,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -28362,7 +28368,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28412,7 +28418,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28462,7 +28468,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28512,7 +28518,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28562,7 +28568,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28612,7 +28618,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28662,7 +28668,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28712,7 +28718,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28762,7 +28768,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28812,7 +28818,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28862,7 +28868,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28912,7 +28918,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28962,7 +28968,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -29262,7 +29268,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -29312,7 +29318,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -29362,7 +29368,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -29412,7 +29418,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -29462,7 +29468,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -29512,7 +29518,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29562,7 +29568,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29612,7 +29618,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29662,7 +29668,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -30262,7 +30268,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -30312,7 +30318,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -30362,7 +30368,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -30412,7 +30418,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -30462,7 +30468,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -30512,7 +30518,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30562,7 +30568,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30612,7 +30618,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30662,7 +30668,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30712,7 +30718,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30762,7 +30768,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30812,7 +30818,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30862,7 +30868,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30912,7 +30918,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30962,7 +30968,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -31012,7 +31018,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -31062,7 +31068,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -31112,7 +31118,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -31162,7 +31168,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -31212,7 +31218,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -31262,7 +31268,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -31312,7 +31318,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31362,7 +31368,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31412,7 +31418,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -31462,7 +31468,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31512,7 +31518,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31562,7 +31568,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31612,7 +31618,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31662,7 +31668,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31712,7 +31718,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -31762,7 +31768,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -31812,7 +31818,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -31862,7 +31868,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -31912,7 +31918,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -32162,7 +32168,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -32212,7 +32218,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -32262,7 +32268,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -32312,7 +32318,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -32362,7 +32368,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32412,7 +32418,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32462,7 +32468,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -32512,7 +32518,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32562,7 +32568,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32612,7 +32618,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32662,7 +32668,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32712,7 +32718,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -33262,7 +33268,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -33312,7 +33318,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -33362,7 +33368,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -33412,7 +33418,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -33462,7 +33468,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -33512,7 +33518,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33562,7 +33568,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -33612,7 +33618,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -33662,7 +33668,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -33712,7 +33718,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33762,7 +33768,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33812,7 +33818,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33862,7 +33868,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33912,7 +33918,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33962,7 +33968,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -34012,7 +34018,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -34062,7 +34068,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -34112,7 +34118,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -34162,7 +34168,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -34212,7 +34218,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -34262,7 +34268,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -34762,7 +34768,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -34812,7 +34818,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -34862,7 +34868,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -34912,7 +34918,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -34962,7 +34968,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -35012,7 +35018,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -35062,7 +35068,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -35112,7 +35118,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -35162,7 +35168,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -35212,7 +35218,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -35262,7 +35268,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -35312,7 +35318,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -35362,7 +35368,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -35412,7 +35418,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -35462,7 +35468,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -35512,7 +35518,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35562,7 +35568,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35612,7 +35618,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35662,7 +35668,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35712,7 +35718,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35762,7 +35768,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35812,7 +35818,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35862,7 +35868,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35912,7 +35918,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35962,7 +35968,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -36012,7 +36018,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -36062,7 +36068,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -36112,7 +36118,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -36162,7 +36168,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -36212,7 +36218,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -36262,7 +36268,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36312,7 +36318,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36762,7 +36768,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36812,7 +36818,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36862,7 +36868,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36912,7 +36918,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36962,7 +36968,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -37012,7 +37018,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -37062,7 +37068,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -37112,7 +37118,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -37712,7 +37718,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37762,7 +37768,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37812,7 +37818,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37862,7 +37868,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37912,7 +37918,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37962,7 +37968,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -38012,7 +38018,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -38062,7 +38068,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -38112,7 +38118,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -38512,7 +38518,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38562,7 +38568,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -38612,7 +38618,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -38662,7 +38668,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -38712,7 +38718,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38762,7 +38768,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38812,7 +38818,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38862,7 +38868,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38912,7 +38918,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38962,7 +38968,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -39012,7 +39018,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -39062,7 +39068,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -39112,7 +39118,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -39162,7 +39168,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -39212,7 +39218,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -39262,7 +39268,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -39312,7 +39318,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -39362,7 +39368,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -39412,7 +39418,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -39712,7 +39718,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39762,7 +39768,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39812,7 +39818,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39862,7 +39868,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39912,7 +39918,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39962,7 +39968,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -40012,7 +40018,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -40062,7 +40068,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -40112,7 +40118,7 @@
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -40162,7 +40168,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -40212,7 +40218,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -40262,7 +40268,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -40612,7 +40618,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -40662,7 +40668,7 @@
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="771" spans="1:16">
@@ -40712,7 +40718,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -40762,7 +40768,7 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -40812,7 +40818,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40862,7 +40868,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40912,7 +40918,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40962,7 +40968,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -41012,7 +41018,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -41062,7 +41068,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -41112,7 +41118,7 @@
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -41162,7 +41168,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -41212,7 +41218,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -41262,7 +41268,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -41312,7 +41318,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -42062,7 +42068,7 @@
         <v>1</v>
       </c>
       <c r="P798" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="799" spans="1:16">
@@ -42112,7 +42118,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -42162,7 +42168,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -42212,7 +42218,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -42262,7 +42268,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -42312,7 +42318,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -42362,7 +42368,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -42412,7 +42418,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -42462,7 +42468,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -42512,7 +42518,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42562,7 +42568,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42612,7 +42618,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42662,7 +42668,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -42712,7 +42718,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -43262,7 +43268,7 @@
         <v>1</v>
       </c>
       <c r="P822" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="823" spans="1:16">
@@ -43312,7 +43318,7 @@
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="824" spans="1:16">
@@ -43362,7 +43368,7 @@
         <v>1</v>
       </c>
       <c r="P824" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="825" spans="1:16">
@@ -43412,7 +43418,7 @@
         <v>1</v>
       </c>
       <c r="P825" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="826" spans="1:16">
@@ -43462,7 +43468,7 @@
         <v>1</v>
       </c>
       <c r="P826" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="827" spans="1:16">
@@ -43512,7 +43518,7 @@
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="828" spans="1:16">
@@ -43562,7 +43568,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -43612,7 +43618,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -43662,7 +43668,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -43712,7 +43718,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -43762,7 +43768,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43812,7 +43818,7 @@
         <v>1</v>
       </c>
       <c r="P833" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="834" spans="1:16">
@@ -43862,7 +43868,7 @@
         <v>1</v>
       </c>
       <c r="P834" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="835" spans="1:16">
@@ -43912,7 +43918,7 @@
         <v>1</v>
       </c>
       <c r="P835" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="836" spans="1:16">
@@ -43962,7 +43968,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -44012,7 +44018,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -44062,7 +44068,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -44112,7 +44118,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -44162,7 +44168,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -44212,7 +44218,7 @@
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -44262,7 +44268,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -44312,7 +44318,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -44362,7 +44368,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -44412,7 +44418,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44462,7 +44468,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44512,7 +44518,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44562,7 +44568,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44612,7 +44618,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44662,7 +44668,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44712,7 +44718,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -44762,7 +44768,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -44812,7 +44818,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -44862,7 +44868,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44912,7 +44918,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -44962,7 +44968,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -45012,7 +45018,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -45062,7 +45068,7 @@
         <v>1</v>
       </c>
       <c r="P858" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="859" spans="1:16">
@@ -45112,7 +45118,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -45162,7 +45168,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -45212,7 +45218,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -45262,7 +45268,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -45312,7 +45318,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -45362,7 +45368,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -45412,7 +45418,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45462,7 +45468,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45512,7 +45518,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45562,7 +45568,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45612,7 +45618,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45662,7 +45668,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45712,7 +45718,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45762,7 +45768,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45812,7 +45818,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -45862,7 +45868,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45912,7 +45918,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45962,7 +45968,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -46012,7 +46018,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -46062,7 +46068,7 @@
         <v>1</v>
       </c>
       <c r="P878" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="879" spans="1:16">
@@ -46112,7 +46118,7 @@
         <v>1</v>
       </c>
       <c r="P879" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="880" spans="1:16">
@@ -46162,7 +46168,7 @@
         <v>1</v>
       </c>
       <c r="P880" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="881" spans="1:16">
@@ -46212,7 +46218,7 @@
         <v>1</v>
       </c>
       <c r="P881" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="882" spans="1:16">
@@ -46262,7 +46268,7 @@
         <v>1</v>
       </c>
       <c r="P882" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -46312,7 +46318,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46362,7 +46368,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46412,7 +46418,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46462,7 +46468,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46512,7 +46518,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46562,7 +46568,7 @@
         <v>1</v>
       </c>
       <c r="P888" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="889" spans="1:16">
@@ -46612,7 +46618,7 @@
         <v>1</v>
       </c>
       <c r="P889" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="890" spans="1:16">
@@ -46662,7 +46668,7 @@
         <v>1</v>
       </c>
       <c r="P890" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="891" spans="1:16">
@@ -46712,7 +46718,7 @@
         <v>1</v>
       </c>
       <c r="P891" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="892" spans="1:16">
@@ -46762,7 +46768,7 @@
         <v>1</v>
       </c>
       <c r="P892" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="893" spans="1:16">
@@ -46812,7 +46818,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46862,7 +46868,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46912,7 +46918,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -46962,7 +46968,7 @@
         <v>1</v>
       </c>
       <c r="P896" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="897" spans="1:16">
@@ -47012,7 +47018,7 @@
         <v>1</v>
       </c>
       <c r="P897" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="898" spans="1:16">
@@ -47062,7 +47068,7 @@
         <v>1</v>
       </c>
       <c r="P898" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="899" spans="1:16">
@@ -47112,7 +47118,7 @@
         <v>1</v>
       </c>
       <c r="P899" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="900" spans="1:16">
@@ -47162,7 +47168,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -47212,7 +47218,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -47262,7 +47268,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -47312,7 +47318,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -47362,7 +47368,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -47412,7 +47418,7 @@
         <v>1</v>
       </c>
       <c r="P905" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="906" spans="1:16">
@@ -47462,7 +47468,7 @@
         <v>1</v>
       </c>
       <c r="P906" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="907" spans="1:16">
@@ -47512,7 +47518,7 @@
         <v>1</v>
       </c>
       <c r="P907" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="908" spans="1:16">
@@ -47562,7 +47568,7 @@
         <v>1</v>
       </c>
       <c r="P908" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="909" spans="1:16">
@@ -47612,7 +47618,7 @@
         <v>1</v>
       </c>
       <c r="P909" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="910" spans="1:16">
@@ -47662,7 +47668,7 @@
         <v>1</v>
       </c>
       <c r="P910" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="911" spans="1:16">
@@ -47712,7 +47718,7 @@
         <v>1</v>
       </c>
       <c r="P911" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="912" spans="1:16">
@@ -47762,7 +47768,7 @@
         <v>1</v>
       </c>
       <c r="P912" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="913" spans="1:16">
@@ -47812,7 +47818,7 @@
         <v>1</v>
       </c>
       <c r="P913" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="914" spans="1:16">
@@ -47862,7 +47868,7 @@
         <v>1</v>
       </c>
       <c r="P914" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="915" spans="1:16">
@@ -47912,7 +47918,7 @@
         <v>1</v>
       </c>
       <c r="P915" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="916" spans="1:16">
@@ -47962,7 +47968,7 @@
         <v>1</v>
       </c>
       <c r="P916" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="917" spans="1:16">
@@ -48012,7 +48018,7 @@
         <v>1</v>
       </c>
       <c r="P917" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="918" spans="1:16">
@@ -48062,7 +48068,7 @@
         <v>1</v>
       </c>
       <c r="P918" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="919" spans="1:16">
@@ -48112,7 +48118,7 @@
         <v>1</v>
       </c>
       <c r="P919" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="920" spans="1:16">
@@ -48162,7 +48168,7 @@
         <v>1</v>
       </c>
       <c r="P920" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="921" spans="1:16">
@@ -48212,7 +48218,7 @@
         <v>1</v>
       </c>
       <c r="P921" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="922" spans="1:16">
@@ -48262,7 +48268,7 @@
         <v>1</v>
       </c>
       <c r="P922" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="923" spans="1:16">
@@ -48312,7 +48318,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -48362,7 +48368,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -48412,7 +48418,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48462,7 +48468,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48512,7 +48518,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -48562,7 +48568,7 @@
         <v>1</v>
       </c>
       <c r="P928" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="929" spans="1:16">
@@ -48612,7 +48618,7 @@
         <v>1</v>
       </c>
       <c r="P929" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="930" spans="1:16">
@@ -48662,7 +48668,7 @@
         <v>1</v>
       </c>
       <c r="P930" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="931" spans="1:16">
@@ -48712,7 +48718,7 @@
         <v>1</v>
       </c>
       <c r="P931" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="932" spans="1:16">
@@ -48762,7 +48768,7 @@
         <v>1</v>
       </c>
       <c r="P932" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="933" spans="1:16">
@@ -48812,7 +48818,7 @@
         <v>1</v>
       </c>
       <c r="P933" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="934" spans="1:16">
@@ -48862,7 +48868,7 @@
         <v>1</v>
       </c>
       <c r="P934" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="935" spans="1:16">
@@ -48912,7 +48918,7 @@
         <v>1</v>
       </c>
       <c r="P935" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="936" spans="1:16">
@@ -48962,7 +48968,7 @@
         <v>1</v>
       </c>
       <c r="P936" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="937" spans="1:16">
@@ -49012,7 +49018,7 @@
         <v>1</v>
       </c>
       <c r="P937" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="938" spans="1:16">
@@ -49062,7 +49068,7 @@
         <v>1</v>
       </c>
       <c r="P938" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="939" spans="1:16">
@@ -49112,7 +49118,7 @@
         <v>1</v>
       </c>
       <c r="P939" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="940" spans="1:16">
@@ -49162,7 +49168,7 @@
         <v>1</v>
       </c>
       <c r="P940" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="941" spans="1:16">
@@ -49212,7 +49218,7 @@
         <v>1</v>
       </c>
       <c r="P941" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="942" spans="1:16">
@@ -50412,7 +50418,7 @@
         <v>1</v>
       </c>
       <c r="P965" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="966" spans="1:16">
@@ -50462,7 +50468,7 @@
         <v>1</v>
       </c>
       <c r="P966" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="967" spans="1:16">
@@ -50512,7 +50518,7 @@
         <v>1</v>
       </c>
       <c r="P967" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="968" spans="1:16">
@@ -50562,7 +50568,7 @@
         <v>1</v>
       </c>
       <c r="P968" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="969" spans="1:16">
@@ -51262,7 +51268,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -51312,7 +51318,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -51362,7 +51368,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -51412,7 +51418,7 @@
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="986" spans="1:16">
@@ -51462,7 +51468,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -51512,7 +51518,7 @@
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51562,7 +51568,7 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="989" spans="1:16">
@@ -51612,7 +51618,7 @@
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="990" spans="1:16">
@@ -51662,7 +51668,7 @@
         <v>1</v>
       </c>
       <c r="P990" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="991" spans="1:16">
@@ -52112,7 +52118,7 @@
         <v>1</v>
       </c>
       <c r="P999" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="1000" spans="1:16">
@@ -52162,7 +52168,7 @@
         <v>1</v>
       </c>
       <c r="P1000" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="1001" spans="1:16">
@@ -52212,7 +52218,7 @@
         <v>1</v>
       </c>
       <c r="P1001" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="1002" spans="1:16">
@@ -52262,7 +52268,7 @@
         <v>1</v>
       </c>
       <c r="P1002" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="1003" spans="1:16">
@@ -52312,7 +52318,7 @@
         <v>1</v>
       </c>
       <c r="P1003" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="1004" spans="1:16">
@@ -52362,7 +52368,7 @@
         <v>1</v>
       </c>
       <c r="P1004" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="1005" spans="1:16">
@@ -52412,7 +52418,7 @@
         <v>1</v>
       </c>
       <c r="P1005" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="1006" spans="1:16">
@@ -52462,7 +52468,7 @@
         <v>1</v>
       </c>
       <c r="P1006" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="1007" spans="1:16">
@@ -52512,7 +52518,7 @@
         <v>1</v>
       </c>
       <c r="P1007" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="1008" spans="1:16">
@@ -52562,7 +52568,7 @@
         <v>1</v>
       </c>
       <c r="P1008" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="1009" spans="1:16">
@@ -53412,7 +53418,7 @@
         <v>1</v>
       </c>
       <c r="P1025" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="1026" spans="1:16">
@@ -53462,7 +53468,7 @@
         <v>1</v>
       </c>
       <c r="P1026" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="1027" spans="1:16">
@@ -53512,7 +53518,7 @@
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
@@ -53562,7 +53568,7 @@
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
@@ -53612,7 +53618,7 @@
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
@@ -53662,7 +53668,7 @@
         <v>1</v>
       </c>
       <c r="P1030" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="1031" spans="1:16">
@@ -53712,7 +53718,7 @@
         <v>1</v>
       </c>
       <c r="P1031" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="1032" spans="1:16">
@@ -53762,7 +53768,7 @@
         <v>1</v>
       </c>
       <c r="P1032" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="1033" spans="1:16">
@@ -53812,7 +53818,7 @@
         <v>1</v>
       </c>
       <c r="P1033" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1034" spans="1:16">
@@ -53862,7 +53868,7 @@
         <v>1</v>
       </c>
       <c r="P1034" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1035" spans="1:16">
@@ -53912,7 +53918,7 @@
         <v>1</v>
       </c>
       <c r="P1035" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1036" spans="1:16">
@@ -53962,7 +53968,7 @@
         <v>1</v>
       </c>
       <c r="P1036" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="1037" spans="1:16">
@@ -54012,7 +54018,7 @@
         <v>1</v>
       </c>
       <c r="P1037" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1038" spans="1:16">
@@ -54062,7 +54068,7 @@
         <v>1</v>
       </c>
       <c r="P1038" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1039" spans="1:16">
@@ -54112,7 +54118,7 @@
         <v>1</v>
       </c>
       <c r="P1039" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1040" spans="1:16">
@@ -54162,7 +54168,7 @@
         <v>1</v>
       </c>
       <c r="P1040" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1041" spans="1:16">
@@ -54212,7 +54218,7 @@
         <v>1</v>
       </c>
       <c r="P1041" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1042" spans="1:16">
@@ -54262,7 +54268,7 @@
         <v>1</v>
       </c>
       <c r="P1042" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1043" spans="1:16">
@@ -54312,7 +54318,7 @@
         <v>1</v>
       </c>
       <c r="P1043" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="1044" spans="1:16">
@@ -54362,7 +54368,7 @@
         <v>1</v>
       </c>
       <c r="P1044" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="1045" spans="1:16">
@@ -54412,7 +54418,7 @@
         <v>1</v>
       </c>
       <c r="P1045" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="1046" spans="1:16">
@@ -54462,7 +54468,7 @@
         <v>1</v>
       </c>
       <c r="P1046" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="1047" spans="1:16">
@@ -54562,7 +54568,7 @@
         <v>1</v>
       </c>
       <c r="P1048" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1049" spans="1:16">
@@ -54612,7 +54618,7 @@
         <v>1</v>
       </c>
       <c r="P1049" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1050" spans="1:16">
@@ -54662,7 +54668,7 @@
         <v>1</v>
       </c>
       <c r="P1050" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1051" spans="1:16">
@@ -54712,7 +54718,7 @@
         <v>1</v>
       </c>
       <c r="P1051" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="1052" spans="1:16">
@@ -54720,349 +54726,349 @@
         <v>0</v>
       </c>
       <c r="B1052" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C1052">
-        <v>-0.2622680044676837</v>
+        <v>5.771656758678997</v>
       </c>
       <c r="D1052" t="s">
         <v>463</v>
       </c>
       <c r="E1052">
-        <v>-0.9183588785748515</v>
+        <v>5.250472631141054</v>
       </c>
       <c r="F1052">
         <v>-1</v>
       </c>
       <c r="G1052">
-        <v>0.01758226800446768</v>
+        <v>0.010448343241321</v>
       </c>
       <c r="H1052">
-        <v>0.01705835887857485</v>
+        <v>0.01000952736885895</v>
       </c>
       <c r="I1052">
-        <v>0.6560908741071678</v>
+        <v>0.5211841275379427</v>
       </c>
       <c r="J1052">
-        <v>1.652271852679201</v>
+        <v>0.4576014170882586</v>
       </c>
       <c r="K1052">
-        <v>5.4</v>
+        <v>5.11</v>
       </c>
       <c r="L1052">
-        <v>8.66</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="M1052">
-        <v>5.44</v>
+        <v>5.2</v>
       </c>
       <c r="N1052">
-        <v>8.07</v>
+        <v>7.63</v>
       </c>
       <c r="O1052">
         <v>1</v>
       </c>
       <c r="P1052" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="1053" spans="1:16">
       <c r="A1053" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1053" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C1053">
-        <v>-1.021813633931844</v>
+        <v>-0.2622680044676837</v>
       </c>
       <c r="D1053" t="s">
         <v>464</v>
       </c>
       <c r="E1053">
-        <v>-0.9804955745567545</v>
+        <v>-0.9183588785748515</v>
       </c>
       <c r="F1053">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1053">
-        <v>0.01616181363393184</v>
+        <v>0.01758226800446768</v>
       </c>
       <c r="H1053">
-        <v>0.01574049557455675</v>
+        <v>0.01705835887857485</v>
       </c>
       <c r="I1053">
-        <v>0.04131805937508926</v>
+        <v>0.6560908741071678</v>
       </c>
       <c r="J1053">
         <v>1.652271852679201</v>
       </c>
       <c r="K1053">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="L1053">
-        <v>7.57</v>
+        <v>8.66</v>
       </c>
       <c r="M1053">
-        <v>5.06</v>
+        <v>5.44</v>
       </c>
       <c r="N1053">
-        <v>7.38</v>
+        <v>8.07</v>
       </c>
       <c r="O1053">
         <v>1</v>
       </c>
       <c r="P1053" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1054" spans="1:16">
       <c r="A1054" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1054" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C1054">
-        <v>-0.3478350132647545</v>
+        <v>-1.021813633931844</v>
       </c>
       <c r="D1054" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E1054">
-        <v>-1.004559717066716</v>
+        <v>-0.8739728560299627</v>
       </c>
       <c r="F1054">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1054">
-        <v>0.01766783501326476</v>
+        <v>0.01616181363393184</v>
       </c>
       <c r="H1054">
-        <v>0.01714455971706672</v>
+        <v>0.01581397285602996</v>
       </c>
       <c r="I1054">
-        <v>0.6567247038019612</v>
+        <v>0.1478407779018811</v>
       </c>
       <c r="J1054">
-        <v>1.668117595049029</v>
+        <v>1.652271852679201</v>
       </c>
       <c r="K1054">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L1054">
-        <v>8.66</v>
+        <v>7.57</v>
       </c>
       <c r="M1054">
-        <v>5.44</v>
+        <v>5.05</v>
       </c>
       <c r="N1054">
-        <v>8.07</v>
+        <v>7.47</v>
       </c>
       <c r="O1054">
         <v>1</v>
       </c>
       <c r="P1054" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1055" spans="1:16">
       <c r="A1055" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1055" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C1055">
-        <v>-1.104211494254949</v>
+        <v>-1.009631885717508</v>
       </c>
       <c r="D1055" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E1055">
-        <v>-1.060675030948084</v>
+        <v>-0.8739728560299627</v>
       </c>
       <c r="F1055">
         <v>1</v>
       </c>
       <c r="G1055">
-        <v>0.01624421149425495</v>
+        <v>0.01590963188571751</v>
       </c>
       <c r="H1055">
-        <v>0.01582067503094808</v>
+        <v>0.01581397285602996</v>
       </c>
       <c r="I1055">
-        <v>0.04353646330686534</v>
+        <v>0.1356590296875453</v>
       </c>
       <c r="J1055">
-        <v>1.668117595049029</v>
+        <v>1.652271852679201</v>
       </c>
       <c r="K1055">
-        <v>5.2</v>
+        <v>5.12</v>
       </c>
       <c r="L1055">
-        <v>7.57</v>
+        <v>7.45</v>
       </c>
       <c r="M1055">
-        <v>5.06</v>
+        <v>5.05</v>
       </c>
       <c r="N1055">
-        <v>7.38</v>
+        <v>7.47</v>
       </c>
       <c r="O1055">
         <v>1</v>
       </c>
       <c r="P1055" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1056" spans="1:16">
       <c r="A1056" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1056" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C1056">
-        <v>-1.090762086651027</v>
+        <v>-0.3478350132647545</v>
       </c>
       <c r="D1056" t="s">
         <v>464</v>
       </c>
       <c r="E1056">
-        <v>-1.060675030948084</v>
+        <v>-1.004559717066716</v>
       </c>
       <c r="F1056">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1056">
-        <v>0.01599076208665103</v>
+        <v>0.01766783501326476</v>
       </c>
       <c r="H1056">
-        <v>0.01582067503094808</v>
+        <v>0.01714455971706672</v>
       </c>
       <c r="I1056">
-        <v>0.03008705570294268</v>
+        <v>0.6567247038019612</v>
       </c>
       <c r="J1056">
         <v>1.668117595049029</v>
       </c>
       <c r="K1056">
-        <v>5.12</v>
+        <v>5.4</v>
       </c>
       <c r="L1056">
-        <v>7.45</v>
+        <v>8.66</v>
       </c>
       <c r="M1056">
-        <v>5.06</v>
+        <v>5.44</v>
       </c>
       <c r="N1056">
-        <v>7.38</v>
+        <v>8.07</v>
       </c>
       <c r="O1056">
         <v>1</v>
       </c>
       <c r="P1056" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="1057" spans="1:16">
       <c r="A1057" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1057" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C1057">
-        <v>-0.40350806689964</v>
+        <v>-1.104211494254949</v>
       </c>
       <c r="D1057" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E1057">
-        <v>-1.06064516369149</v>
+        <v>-0.9539938549975941</v>
       </c>
       <c r="F1057">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1057">
-        <v>0.01772350806689964</v>
+        <v>0.01624421149425495</v>
       </c>
       <c r="H1057">
-        <v>0.01720064516369149</v>
+        <v>0.01589399385499759</v>
       </c>
       <c r="I1057">
-        <v>0.6571370967918497</v>
+        <v>0.1502176392573551</v>
       </c>
       <c r="J1057">
-        <v>1.67842741979623</v>
+        <v>1.668117595049029</v>
       </c>
       <c r="K1057">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L1057">
-        <v>8.66</v>
+        <v>7.57</v>
       </c>
       <c r="M1057">
-        <v>5.44</v>
+        <v>5.05</v>
       </c>
       <c r="N1057">
-        <v>8.07</v>
+        <v>7.47</v>
       </c>
       <c r="O1057">
         <v>1</v>
       </c>
       <c r="P1057" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="1058" spans="1:16">
       <c r="A1058" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1058" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C1058">
-        <v>-1.157822582940394</v>
+        <v>-1.090762086651027</v>
       </c>
       <c r="D1058" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E1058">
-        <v>-1.112842744168922</v>
+        <v>-0.9539938549975941</v>
       </c>
       <c r="F1058">
         <v>1</v>
       </c>
       <c r="G1058">
-        <v>0.01629782258294039</v>
+        <v>0.01599076208665103</v>
       </c>
       <c r="H1058">
-        <v>0.01587284274416892</v>
+        <v>0.01589399385499759</v>
       </c>
       <c r="I1058">
-        <v>0.04497983877147238</v>
+        <v>0.1367682316534324</v>
       </c>
       <c r="J1058">
-        <v>1.67842741979623</v>
+        <v>1.668117595049029</v>
       </c>
       <c r="K1058">
-        <v>5.2</v>
+        <v>5.12</v>
       </c>
       <c r="L1058">
-        <v>7.57</v>
+        <v>7.45</v>
       </c>
       <c r="M1058">
-        <v>5.06</v>
+        <v>5.05</v>
       </c>
       <c r="N1058">
-        <v>7.38</v>
+        <v>7.47</v>
       </c>
       <c r="O1058">
         <v>1</v>
       </c>
       <c r="P1058" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="1059" spans="1:16">
@@ -55073,28 +55079,28 @@
         <v>289</v>
       </c>
       <c r="C1059">
-        <v>-0.4395636525619313</v>
+        <v>-0.40350806689964</v>
       </c>
       <c r="D1059" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E1059">
-        <v>-1.096967827766093</v>
+        <v>-1.06064516369149</v>
       </c>
       <c r="F1059">
         <v>-1</v>
       </c>
       <c r="G1059">
-        <v>0.01775956365256193</v>
+        <v>0.01772350806689964</v>
       </c>
       <c r="H1059">
-        <v>0.01723696782776609</v>
+        <v>0.01720064516369149</v>
       </c>
       <c r="I1059">
-        <v>0.6574041752041619</v>
+        <v>0.6571370967918497</v>
       </c>
       <c r="J1059">
-        <v>1.685104380104061</v>
+        <v>1.67842741979623</v>
       </c>
       <c r="K1059">
         <v>5.4</v>
@@ -55112,7 +55118,107 @@
         <v>1</v>
       </c>
       <c r="P1059" t="s">
-        <v>597</v>
+        <v>598</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:16">
+      <c r="A1060" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1060" t="s">
+        <v>290</v>
+      </c>
+      <c r="C1060">
+        <v>-1.157822582940394</v>
+      </c>
+      <c r="D1060" t="s">
+        <v>465</v>
+      </c>
+      <c r="E1060">
+        <v>-1.00605846997096</v>
+      </c>
+      <c r="F1060">
+        <v>1</v>
+      </c>
+      <c r="G1060">
+        <v>0.01629782258294039</v>
+      </c>
+      <c r="H1060">
+        <v>0.01594605846997096</v>
+      </c>
+      <c r="I1060">
+        <v>0.1517641129694338</v>
+      </c>
+      <c r="J1060">
+        <v>1.67842741979623</v>
+      </c>
+      <c r="K1060">
+        <v>5.2</v>
+      </c>
+      <c r="L1060">
+        <v>7.57</v>
+      </c>
+      <c r="M1060">
+        <v>5.05</v>
+      </c>
+      <c r="N1060">
+        <v>7.47</v>
+      </c>
+      <c r="O1060">
+        <v>1</v>
+      </c>
+      <c r="P1060" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:16">
+      <c r="A1061" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1061" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1061">
+        <v>-0.4395636525619313</v>
+      </c>
+      <c r="D1061" t="s">
+        <v>464</v>
+      </c>
+      <c r="E1061">
+        <v>-1.096967827766093</v>
+      </c>
+      <c r="F1061">
+        <v>-1</v>
+      </c>
+      <c r="G1061">
+        <v>0.01775956365256193</v>
+      </c>
+      <c r="H1061">
+        <v>0.01723696782776609</v>
+      </c>
+      <c r="I1061">
+        <v>0.6574041752041619</v>
+      </c>
+      <c r="J1061">
+        <v>1.685104380104061</v>
+      </c>
+      <c r="K1061">
+        <v>5.4</v>
+      </c>
+      <c r="L1061">
+        <v>8.66</v>
+      </c>
+      <c r="M1061">
+        <v>5.44</v>
+      </c>
+      <c r="N1061">
+        <v>8.07</v>
+      </c>
+      <c r="O1061">
+        <v>1</v>
+      </c>
+      <c r="P1061" t="s">
+        <v>599</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3195" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3189" uniqueCount="600">
   <si>
     <t>trade_time</t>
   </si>
@@ -1411,7 +1411,7 @@
     <t>2021-10-08</t>
   </si>
   <si>
-    <t>2021-11-01</t>
+    <t>2021-11-02</t>
   </si>
   <si>
     <t>2016-03-24</t>
@@ -2171,7 +2171,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1061"/>
+  <dimension ref="A1:P1059"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -54835,7 +54835,7 @@
         <v>465</v>
       </c>
       <c r="E1054">
-        <v>-0.8739728560299627</v>
+        <v>-0.9417911078156269</v>
       </c>
       <c r="F1054">
         <v>1</v>
@@ -54844,10 +54844,10 @@
         <v>0.01616181363393184</v>
       </c>
       <c r="H1054">
-        <v>0.01581397285602996</v>
+        <v>0.01548179110781563</v>
       </c>
       <c r="I1054">
-        <v>0.1478407779018811</v>
+        <v>0.08002252611621685</v>
       </c>
       <c r="J1054">
         <v>1.652271852679201</v>
@@ -54859,10 +54859,10 @@
         <v>7.57</v>
       </c>
       <c r="M1054">
-        <v>5.05</v>
+        <v>4.97</v>
       </c>
       <c r="N1054">
-        <v>7.47</v>
+        <v>7.27</v>
       </c>
       <c r="O1054">
         <v>1</v>
@@ -54885,7 +54885,7 @@
         <v>465</v>
       </c>
       <c r="E1055">
-        <v>-0.8739728560299627</v>
+        <v>-0.9417911078156269</v>
       </c>
       <c r="F1055">
         <v>1</v>
@@ -54894,10 +54894,10 @@
         <v>0.01590963188571751</v>
       </c>
       <c r="H1055">
-        <v>0.01581397285602996</v>
+        <v>0.01548179110781563</v>
       </c>
       <c r="I1055">
-        <v>0.1356590296875453</v>
+        <v>0.06784077790188103</v>
       </c>
       <c r="J1055">
         <v>1.652271852679201</v>
@@ -54909,10 +54909,10 @@
         <v>7.45</v>
       </c>
       <c r="M1055">
-        <v>5.05</v>
+        <v>4.97</v>
       </c>
       <c r="N1055">
-        <v>7.47</v>
+        <v>7.27</v>
       </c>
       <c r="O1055">
         <v>1</v>
@@ -54985,7 +54985,7 @@
         <v>465</v>
       </c>
       <c r="E1057">
-        <v>-0.9539938549975941</v>
+        <v>-1.020544447393672</v>
       </c>
       <c r="F1057">
         <v>1</v>
@@ -54994,10 +54994,10 @@
         <v>0.01624421149425495</v>
       </c>
       <c r="H1057">
-        <v>0.01589399385499759</v>
+        <v>0.01556054444739367</v>
       </c>
       <c r="I1057">
-        <v>0.1502176392573551</v>
+        <v>0.08366704686127768</v>
       </c>
       <c r="J1057">
         <v>1.668117595049029</v>
@@ -55009,10 +55009,10 @@
         <v>7.57</v>
       </c>
       <c r="M1057">
-        <v>5.05</v>
+        <v>4.97</v>
       </c>
       <c r="N1057">
-        <v>7.47</v>
+        <v>7.27</v>
       </c>
       <c r="O1057">
         <v>1</v>
@@ -55023,52 +55023,52 @@
     </row>
     <row r="1058" spans="1:16">
       <c r="A1058" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1058" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C1058">
-        <v>-1.090762086651027</v>
+        <v>-0.40350806689964</v>
       </c>
       <c r="D1058" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E1058">
-        <v>-0.9539938549975941</v>
+        <v>-1.06064516369149</v>
       </c>
       <c r="F1058">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1058">
-        <v>0.01599076208665103</v>
+        <v>0.01772350806689964</v>
       </c>
       <c r="H1058">
-        <v>0.01589399385499759</v>
+        <v>0.01720064516369149</v>
       </c>
       <c r="I1058">
-        <v>0.1367682316534324</v>
+        <v>0.6571370967918497</v>
       </c>
       <c r="J1058">
-        <v>1.668117595049029</v>
+        <v>1.67842741979623</v>
       </c>
       <c r="K1058">
-        <v>5.12</v>
+        <v>5.4</v>
       </c>
       <c r="L1058">
-        <v>7.45</v>
+        <v>8.66</v>
       </c>
       <c r="M1058">
-        <v>5.05</v>
+        <v>5.44</v>
       </c>
       <c r="N1058">
-        <v>7.47</v>
+        <v>8.07</v>
       </c>
       <c r="O1058">
         <v>1</v>
       </c>
       <c r="P1058" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="1059" spans="1:16">
@@ -55079,28 +55079,28 @@
         <v>289</v>
       </c>
       <c r="C1059">
-        <v>-0.40350806689964</v>
+        <v>-0.4395636525619313</v>
       </c>
       <c r="D1059" t="s">
         <v>464</v>
       </c>
       <c r="E1059">
-        <v>-1.06064516369149</v>
+        <v>-1.096967827766093</v>
       </c>
       <c r="F1059">
         <v>-1</v>
       </c>
       <c r="G1059">
-        <v>0.01772350806689964</v>
+        <v>0.01775956365256193</v>
       </c>
       <c r="H1059">
-        <v>0.01720064516369149</v>
+        <v>0.01723696782776609</v>
       </c>
       <c r="I1059">
-        <v>0.6571370967918497</v>
+        <v>0.6574041752041619</v>
       </c>
       <c r="J1059">
-        <v>1.67842741979623</v>
+        <v>1.685104380104061</v>
       </c>
       <c r="K1059">
         <v>5.4</v>
@@ -55118,106 +55118,6 @@
         <v>1</v>
       </c>
       <c r="P1059" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="1060" spans="1:16">
-      <c r="A1060" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1060" t="s">
-        <v>290</v>
-      </c>
-      <c r="C1060">
-        <v>-1.157822582940394</v>
-      </c>
-      <c r="D1060" t="s">
-        <v>465</v>
-      </c>
-      <c r="E1060">
-        <v>-1.00605846997096</v>
-      </c>
-      <c r="F1060">
-        <v>1</v>
-      </c>
-      <c r="G1060">
-        <v>0.01629782258294039</v>
-      </c>
-      <c r="H1060">
-        <v>0.01594605846997096</v>
-      </c>
-      <c r="I1060">
-        <v>0.1517641129694338</v>
-      </c>
-      <c r="J1060">
-        <v>1.67842741979623</v>
-      </c>
-      <c r="K1060">
-        <v>5.2</v>
-      </c>
-      <c r="L1060">
-        <v>7.57</v>
-      </c>
-      <c r="M1060">
-        <v>5.05</v>
-      </c>
-      <c r="N1060">
-        <v>7.47</v>
-      </c>
-      <c r="O1060">
-        <v>1</v>
-      </c>
-      <c r="P1060" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="1061" spans="1:16">
-      <c r="A1061" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1061" t="s">
-        <v>289</v>
-      </c>
-      <c r="C1061">
-        <v>-0.4395636525619313</v>
-      </c>
-      <c r="D1061" t="s">
-        <v>464</v>
-      </c>
-      <c r="E1061">
-        <v>-1.096967827766093</v>
-      </c>
-      <c r="F1061">
-        <v>-1</v>
-      </c>
-      <c r="G1061">
-        <v>0.01775956365256193</v>
-      </c>
-      <c r="H1061">
-        <v>0.01723696782776609</v>
-      </c>
-      <c r="I1061">
-        <v>0.6574041752041619</v>
-      </c>
-      <c r="J1061">
-        <v>1.685104380104061</v>
-      </c>
-      <c r="K1061">
-        <v>5.4</v>
-      </c>
-      <c r="L1061">
-        <v>8.66</v>
-      </c>
-      <c r="M1061">
-        <v>5.44</v>
-      </c>
-      <c r="N1061">
-        <v>8.07</v>
-      </c>
-      <c r="O1061">
-        <v>1</v>
-      </c>
-      <c r="P1061" t="s">
         <v>599</v>
       </c>
     </row>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3189" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3186" uniqueCount="599">
   <si>
     <t>trade_time</t>
   </si>
@@ -1411,7 +1411,7 @@
     <t>2021-10-08</t>
   </si>
   <si>
-    <t>2021-11-02</t>
+    <t>2021-11-03</t>
   </si>
   <si>
     <t>2016-03-24</t>
@@ -1811,9 +1811,6 @@
   </si>
   <si>
     <t>2021-09-16</t>
-  </si>
-  <si>
-    <t>2021-09-17</t>
   </si>
 </sst>
 </file>
@@ -2171,7 +2168,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1059"/>
+  <dimension ref="A1:P1058"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -54835,7 +54832,7 @@
         <v>465</v>
       </c>
       <c r="E1054">
-        <v>-0.9417911078156269</v>
+        <v>-0.9022229522352525</v>
       </c>
       <c r="F1054">
         <v>1</v>
@@ -54844,10 +54841,10 @@
         <v>0.01616181363393184</v>
       </c>
       <c r="H1054">
-        <v>0.01548179110781563</v>
+        <v>0.01542222295223525</v>
       </c>
       <c r="I1054">
-        <v>0.08002252611621685</v>
+        <v>0.1195906816965913</v>
       </c>
       <c r="J1054">
         <v>1.652271852679201</v>
@@ -54859,10 +54856,10 @@
         <v>7.57</v>
       </c>
       <c r="M1054">
-        <v>4.97</v>
+        <v>4.94</v>
       </c>
       <c r="N1054">
-        <v>7.27</v>
+        <v>7.26</v>
       </c>
       <c r="O1054">
         <v>1</v>
@@ -54885,7 +54882,7 @@
         <v>465</v>
       </c>
       <c r="E1055">
-        <v>-0.9417911078156269</v>
+        <v>-0.9022229522352525</v>
       </c>
       <c r="F1055">
         <v>1</v>
@@ -54894,10 +54891,10 @@
         <v>0.01590963188571751</v>
       </c>
       <c r="H1055">
-        <v>0.01548179110781563</v>
+        <v>0.01542222295223525</v>
       </c>
       <c r="I1055">
-        <v>0.06784077790188103</v>
+        <v>0.1074089334822554</v>
       </c>
       <c r="J1055">
         <v>1.652271852679201</v>
@@ -54909,10 +54906,10 @@
         <v>7.45</v>
       </c>
       <c r="M1055">
-        <v>4.97</v>
+        <v>4.94</v>
       </c>
       <c r="N1055">
-        <v>7.27</v>
+        <v>7.26</v>
       </c>
       <c r="O1055">
         <v>1</v>
@@ -54985,7 +54982,7 @@
         <v>465</v>
       </c>
       <c r="E1057">
-        <v>-1.020544447393672</v>
+        <v>-0.9805009195422016</v>
       </c>
       <c r="F1057">
         <v>1</v>
@@ -54994,10 +54991,10 @@
         <v>0.01624421149425495</v>
       </c>
       <c r="H1057">
-        <v>0.01556054444739367</v>
+        <v>0.0155005009195422</v>
       </c>
       <c r="I1057">
-        <v>0.08366704686127768</v>
+        <v>0.1237105747127476</v>
       </c>
       <c r="J1057">
         <v>1.668117595049029</v>
@@ -55009,10 +55006,10 @@
         <v>7.57</v>
       </c>
       <c r="M1057">
-        <v>4.97</v>
+        <v>4.94</v>
       </c>
       <c r="N1057">
-        <v>7.27</v>
+        <v>7.26</v>
       </c>
       <c r="O1057">
         <v>1</v>
@@ -55069,56 +55066,6 @@
       </c>
       <c r="P1058" t="s">
         <v>598</v>
-      </c>
-    </row>
-    <row r="1059" spans="1:16">
-      <c r="A1059" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1059" t="s">
-        <v>289</v>
-      </c>
-      <c r="C1059">
-        <v>-0.4395636525619313</v>
-      </c>
-      <c r="D1059" t="s">
-        <v>464</v>
-      </c>
-      <c r="E1059">
-        <v>-1.096967827766093</v>
-      </c>
-      <c r="F1059">
-        <v>-1</v>
-      </c>
-      <c r="G1059">
-        <v>0.01775956365256193</v>
-      </c>
-      <c r="H1059">
-        <v>0.01723696782776609</v>
-      </c>
-      <c r="I1059">
-        <v>0.6574041752041619</v>
-      </c>
-      <c r="J1059">
-        <v>1.685104380104061</v>
-      </c>
-      <c r="K1059">
-        <v>5.4</v>
-      </c>
-      <c r="L1059">
-        <v>8.66</v>
-      </c>
-      <c r="M1059">
-        <v>5.44</v>
-      </c>
-      <c r="N1059">
-        <v>8.07</v>
-      </c>
-      <c r="O1059">
-        <v>1</v>
-      </c>
-      <c r="P1059" t="s">
-        <v>599</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3189" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3186" uniqueCount="599">
   <si>
     <t>trade_time</t>
   </si>
@@ -1414,7 +1414,7 @@
     <t>2021-10-08</t>
   </si>
   <si>
-    <t>2021-11-04</t>
+    <t>2021-11-08</t>
   </si>
   <si>
     <t>2016-03-24</t>
@@ -1811,9 +1811,6 @@
   </si>
   <si>
     <t>2021-09-15</t>
-  </si>
-  <si>
-    <t>2021-09-16</t>
   </si>
 </sst>
 </file>
@@ -2171,7 +2168,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1059"/>
+  <dimension ref="A1:P1058"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -54835,7 +54832,7 @@
         <v>466</v>
       </c>
       <c r="E1054">
-        <v>-0.8361320781280845</v>
+        <v>-0.8596093596012908</v>
       </c>
       <c r="F1054">
         <v>1</v>
@@ -54844,10 +54841,10 @@
         <v>0.01616181363393184</v>
       </c>
       <c r="H1054">
-        <v>0.01535613207812808</v>
+        <v>0.01529960935960129</v>
       </c>
       <c r="I1054">
-        <v>0.1856815558037592</v>
+        <v>0.162204274330553</v>
       </c>
       <c r="J1054">
         <v>1.652271852679201</v>
@@ -54859,10 +54856,10 @@
         <v>7.57</v>
       </c>
       <c r="M1054">
-        <v>4.9</v>
+        <v>4.89</v>
       </c>
       <c r="N1054">
-        <v>7.26</v>
+        <v>7.22</v>
       </c>
       <c r="O1054">
         <v>1</v>
@@ -54885,7 +54882,7 @@
         <v>466</v>
       </c>
       <c r="E1055">
-        <v>-0.8361320781280845</v>
+        <v>-0.8596093596012908</v>
       </c>
       <c r="F1055">
         <v>1</v>
@@ -54894,10 +54891,10 @@
         <v>0.01590963188571751</v>
       </c>
       <c r="H1055">
-        <v>0.01535613207812808</v>
+        <v>0.01529960935960129</v>
       </c>
       <c r="I1055">
-        <v>0.1734998075894234</v>
+        <v>0.1500225261162171</v>
       </c>
       <c r="J1055">
         <v>1.652271852679201</v>
@@ -54909,10 +54906,10 @@
         <v>7.45</v>
       </c>
       <c r="M1055">
-        <v>4.9</v>
+        <v>4.89</v>
       </c>
       <c r="N1055">
-        <v>7.26</v>
+        <v>7.22</v>
       </c>
       <c r="O1055">
         <v>1</v>
@@ -54976,43 +54973,43 @@
         <v>1</v>
       </c>
       <c r="B1057" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C1057">
-        <v>-1.104211494254949</v>
+        <v>-0.574037382849065</v>
       </c>
       <c r="D1057" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E1057">
-        <v>-0.9137762157402403</v>
+        <v>-1.004559717066716</v>
       </c>
       <c r="F1057">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1057">
-        <v>0.01624421149425495</v>
+        <v>0.01637403738284907</v>
       </c>
       <c r="H1057">
-        <v>0.01543377621574024</v>
+        <v>0.01714455971706672</v>
       </c>
       <c r="I1057">
-        <v>0.190435278514709</v>
+        <v>0.4305223342176507</v>
       </c>
       <c r="J1057">
         <v>1.668117595049029</v>
       </c>
       <c r="K1057">
-        <v>5.2</v>
+        <v>5.08</v>
       </c>
       <c r="L1057">
-        <v>7.57</v>
+        <v>7.9</v>
       </c>
       <c r="M1057">
-        <v>4.9</v>
+        <v>5.44</v>
       </c>
       <c r="N1057">
-        <v>7.26</v>
+        <v>8.07</v>
       </c>
       <c r="O1057">
         <v>1</v>
@@ -55023,102 +55020,52 @@
     </row>
     <row r="1058" spans="1:16">
       <c r="A1058" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1058" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C1058">
-        <v>-0.40350806689964</v>
+        <v>-1.104211494254949</v>
       </c>
       <c r="D1058" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E1058">
-        <v>-1.06064516369149</v>
+        <v>-0.9370950397897486</v>
       </c>
       <c r="F1058">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1058">
-        <v>0.01772350806689964</v>
+        <v>0.01624421149425495</v>
       </c>
       <c r="H1058">
-        <v>0.01720064516369149</v>
+        <v>0.01537709503978975</v>
       </c>
       <c r="I1058">
-        <v>0.6571370967918497</v>
+        <v>0.1671164544652006</v>
       </c>
       <c r="J1058">
-        <v>1.67842741979623</v>
+        <v>1.668117595049029</v>
       </c>
       <c r="K1058">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L1058">
-        <v>8.66</v>
+        <v>7.57</v>
       </c>
       <c r="M1058">
-        <v>5.44</v>
+        <v>4.89</v>
       </c>
       <c r="N1058">
-        <v>8.07</v>
+        <v>7.22</v>
       </c>
       <c r="O1058">
         <v>1</v>
       </c>
       <c r="P1058" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="1059" spans="1:16">
-      <c r="A1059" s="1">
-        <v>1</v>
-      </c>
-      <c r="B1059" t="s">
-        <v>292</v>
-      </c>
-      <c r="C1059">
-        <v>-0.6264112925648462</v>
-      </c>
-      <c r="D1059" t="s">
-        <v>465</v>
-      </c>
-      <c r="E1059">
-        <v>-1.06064516369149</v>
-      </c>
-      <c r="F1059">
-        <v>-1</v>
-      </c>
-      <c r="G1059">
-        <v>0.01642641129256485</v>
-      </c>
-      <c r="H1059">
-        <v>0.01720064516369149</v>
-      </c>
-      <c r="I1059">
-        <v>0.4342338711266436</v>
-      </c>
-      <c r="J1059">
-        <v>1.67842741979623</v>
-      </c>
-      <c r="K1059">
-        <v>5.08</v>
-      </c>
-      <c r="L1059">
-        <v>7.9</v>
-      </c>
-      <c r="M1059">
-        <v>5.44</v>
-      </c>
-      <c r="N1059">
-        <v>8.07</v>
-      </c>
-      <c r="O1059">
-        <v>1</v>
-      </c>
-      <c r="P1059" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -54823,40 +54823,40 @@
     </row>
     <row r="1054" spans="1:16">
       <c r="A1054" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1054" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C1054">
-        <v>-1.009631885717508</v>
+        <v>-1.104211494254949</v>
       </c>
       <c r="D1054" t="s">
         <v>464</v>
       </c>
       <c r="E1054">
-        <v>-0.7426547966548744</v>
+        <v>-0.8204573916907298</v>
       </c>
       <c r="F1054">
         <v>1</v>
       </c>
       <c r="G1054">
-        <v>0.01590963188571751</v>
+        <v>0.01624421149425495</v>
       </c>
       <c r="H1054">
-        <v>0.01548265479665487</v>
+        <v>0.01556045739169073</v>
       </c>
       <c r="I1054">
-        <v>0.2669770890626335</v>
+        <v>0.2837541025642194</v>
       </c>
       <c r="J1054">
-        <v>1.652271852679201</v>
+        <v>1.668117595049029</v>
       </c>
       <c r="K1054">
-        <v>5.12</v>
+        <v>5.2</v>
       </c>
       <c r="L1054">
-        <v>7.45</v>
+        <v>7.57</v>
       </c>
       <c r="M1054">
         <v>4.91</v>
@@ -54868,18 +54868,18 @@
         <v>1</v>
       </c>
       <c r="P1054" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="1055" spans="1:16">
       <c r="A1055" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1055" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C1055">
-        <v>-1.104211494254949</v>
+        <v>-1.090762086651027</v>
       </c>
       <c r="D1055" t="s">
         <v>464</v>
@@ -54891,22 +54891,22 @@
         <v>1</v>
       </c>
       <c r="G1055">
-        <v>0.01624421149425495</v>
+        <v>0.01599076208665103</v>
       </c>
       <c r="H1055">
         <v>0.01556045739169073</v>
       </c>
       <c r="I1055">
-        <v>0.2837541025642194</v>
+        <v>0.2703046949602967</v>
       </c>
       <c r="J1055">
         <v>1.668117595049029</v>
       </c>
       <c r="K1055">
-        <v>5.2</v>
+        <v>5.12</v>
       </c>
       <c r="L1055">
-        <v>7.57</v>
+        <v>7.45</v>
       </c>
       <c r="M1055">
         <v>4.91</v>
@@ -54923,63 +54923,63 @@
     </row>
     <row r="1056" spans="1:16">
       <c r="A1056" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1056" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C1056">
-        <v>-1.090762086651027</v>
+        <v>-1.157822582940394</v>
       </c>
       <c r="D1056" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E1056">
-        <v>-0.8204573916907298</v>
+        <v>-0.8939415344076389</v>
       </c>
       <c r="F1056">
         <v>1</v>
       </c>
       <c r="G1056">
-        <v>0.01599076208665103</v>
+        <v>0.01629782258294039</v>
       </c>
       <c r="H1056">
-        <v>0.01556045739169073</v>
+        <v>0.01545394153440764</v>
       </c>
       <c r="I1056">
-        <v>0.2703046949602967</v>
+        <v>0.2638810485327552</v>
       </c>
       <c r="J1056">
-        <v>1.668117595049029</v>
+        <v>1.67842741979623</v>
       </c>
       <c r="K1056">
-        <v>5.12</v>
+        <v>5.2</v>
       </c>
       <c r="L1056">
-        <v>7.45</v>
+        <v>7.57</v>
       </c>
       <c r="M1056">
-        <v>4.91</v>
+        <v>4.87</v>
       </c>
       <c r="N1056">
-        <v>7.37</v>
+        <v>7.28</v>
       </c>
       <c r="O1056">
         <v>1</v>
       </c>
       <c r="P1056" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="1057" spans="1:16">
       <c r="A1057" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1057" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C1057">
-        <v>-1.157822582940394</v>
+        <v>-1.143548389356696</v>
       </c>
       <c r="D1057" t="s">
         <v>465</v>
@@ -54991,22 +54991,22 @@
         <v>1</v>
       </c>
       <c r="G1057">
-        <v>0.01629782258294039</v>
+        <v>0.0160435483893567</v>
       </c>
       <c r="H1057">
         <v>0.01545394153440764</v>
       </c>
       <c r="I1057">
-        <v>0.2638810485327552</v>
+        <v>0.2496068549490573</v>
       </c>
       <c r="J1057">
         <v>1.67842741979623</v>
       </c>
       <c r="K1057">
-        <v>5.2</v>
+        <v>5.12</v>
       </c>
       <c r="L1057">
-        <v>7.57</v>
+        <v>7.45</v>
       </c>
       <c r="M1057">
         <v>4.87</v>
@@ -55023,40 +55023,40 @@
     </row>
     <row r="1058" spans="1:16">
       <c r="A1058" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1058" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C1058">
-        <v>-1.143548389356696</v>
+        <v>-1.192542776541119</v>
       </c>
       <c r="D1058" t="s">
         <v>465</v>
       </c>
       <c r="E1058">
-        <v>-0.8939415344076389</v>
+        <v>-0.9264583311067787</v>
       </c>
       <c r="F1058">
         <v>1</v>
       </c>
       <c r="G1058">
-        <v>0.0160435483893567</v>
+        <v>0.01633254277654112</v>
       </c>
       <c r="H1058">
-        <v>0.01545394153440764</v>
+        <v>0.01548645833110678</v>
       </c>
       <c r="I1058">
-        <v>0.2496068549490573</v>
+        <v>0.2660844454343403</v>
       </c>
       <c r="J1058">
-        <v>1.67842741979623</v>
+        <v>1.685104380104061</v>
       </c>
       <c r="K1058">
-        <v>5.12</v>
+        <v>5.2</v>
       </c>
       <c r="L1058">
-        <v>7.45</v>
+        <v>7.57</v>
       </c>
       <c r="M1058">
         <v>4.87</v>
@@ -55068,18 +55068,18 @@
         <v>1</v>
       </c>
       <c r="P1058" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="1059" spans="1:16">
       <c r="A1059" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1059" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C1059">
-        <v>-1.192542776541119</v>
+        <v>-1.177734426132793</v>
       </c>
       <c r="D1059" t="s">
         <v>465</v>
@@ -55091,22 +55091,22 @@
         <v>1</v>
       </c>
       <c r="G1059">
-        <v>0.01633254277654112</v>
+        <v>0.01607773442613279</v>
       </c>
       <c r="H1059">
         <v>0.01548645833110678</v>
       </c>
       <c r="I1059">
-        <v>0.2660844454343403</v>
+        <v>0.2512760950260144</v>
       </c>
       <c r="J1059">
         <v>1.685104380104061</v>
       </c>
       <c r="K1059">
-        <v>5.2</v>
+        <v>5.12</v>
       </c>
       <c r="L1059">
-        <v>7.57</v>
+        <v>7.45</v>
       </c>
       <c r="M1059">
         <v>4.87</v>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -54841,10 +54841,10 @@
         <v>-1.104211494254949</v>
       </c>
       <c r="D1054" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E1054">
-        <v>-0.8204573916907298</v>
+        <v>-0.8437326878887683</v>
       </c>
       <c r="F1054">
         <v>1</v>
@@ -54853,10 +54853,10 @@
         <v>0.01624421149425495</v>
       </c>
       <c r="H1054">
-        <v>0.01556045739169073</v>
+        <v>0.01540373268788877</v>
       </c>
       <c r="I1054">
-        <v>0.2837541025642194</v>
+        <v>0.2604788063661809</v>
       </c>
       <c r="J1054">
         <v>1.668117595049029</v>
@@ -54868,10 +54868,10 @@
         <v>7.57</v>
       </c>
       <c r="M1054">
-        <v>4.91</v>
+        <v>4.87</v>
       </c>
       <c r="N1054">
-        <v>7.37</v>
+        <v>7.28</v>
       </c>
       <c r="O1054">
         <v>1</v>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -1417,7 +1417,7 @@
     <t>2021-11-10</t>
   </si>
   <si>
-    <t>2021-11-23</t>
+    <t>2021-11-24</t>
   </si>
   <si>
     <t>2016-03-24</t>
@@ -55094,7 +55094,7 @@
         <v>467</v>
       </c>
       <c r="E1059">
-        <v>-2.726224820560311</v>
+        <v>-2.807532631974992</v>
       </c>
       <c r="F1059">
         <v>-1</v>
@@ -55103,10 +55103,10 @@
         <v>0.01722186544917805</v>
       </c>
       <c r="H1059">
-        <v>0.01754622482056031</v>
+        <v>0.01758753263197499</v>
       </c>
       <c r="I1059">
-        <v>0.08435937138226191</v>
+        <v>0.1656671827969429</v>
       </c>
       <c r="J1059">
         <v>2.043593713822644</v>
@@ -55118,10 +55118,10 @@
         <v>7.29</v>
       </c>
       <c r="M1059">
-        <v>4.96</v>
+        <v>4.99</v>
       </c>
       <c r="N1059">
-        <v>7.41</v>
+        <v>7.39</v>
       </c>
       <c r="O1059">
         <v>1</v>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3186" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3192" uniqueCount="602">
   <si>
     <t>trade_time</t>
   </si>
@@ -883,6 +883,9 @@
     <t>2021-07-19</t>
   </si>
   <si>
+    <t>2021-10-15</t>
+  </si>
+  <si>
     <t>2021-10-22</t>
   </si>
   <si>
@@ -1403,9 +1406,6 @@
   </si>
   <si>
     <t>2021-10-12</t>
-  </si>
-  <si>
-    <t>2021-10-15</t>
   </si>
   <si>
     <t>2021-11-15</t>
@@ -2177,7 +2177,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1058"/>
+  <dimension ref="A1:P1060"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2238,7 +2238,7 @@
         <v>4.31128552097429</v>
       </c>
       <c r="D2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E2">
         <v>3.491640730717187</v>
@@ -2288,7 +2288,7 @@
         <v>2.930197902571042</v>
       </c>
       <c r="D3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E3">
         <v>3.697845060893099</v>
@@ -2338,7 +2338,7 @@
         <v>2.93171853856563</v>
       </c>
       <c r="D4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E4">
         <v>3.697845060893099</v>
@@ -2438,7 +2438,7 @@
         <v>3.256806675563038</v>
       </c>
       <c r="D6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E6">
         <v>2.536806675563037</v>
@@ -2488,7 +2488,7 @@
         <v>1.909437857449102</v>
       </c>
       <c r="D7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E7">
         <v>2.73123945259945</v>
@@ -2538,7 +2538,7 @@
         <v>1.927571287293738</v>
       </c>
       <c r="D8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E8">
         <v>2.73123945259945</v>
@@ -2638,7 +2638,7 @@
         <v>2.529267581722536</v>
       </c>
       <c r="D10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E10">
         <v>1.809267581722535</v>
@@ -2788,7 +2788,7 @@
         <v>0.9430396109046839</v>
       </c>
       <c r="D13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E13">
         <v>0.8476461186055282</v>
@@ -2838,7 +2838,7 @@
         <v>2.096084795296841</v>
       </c>
       <c r="D14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E14">
         <v>1.37608479529684</v>
@@ -2988,7 +2988,7 @@
         <v>1.855836876417781</v>
       </c>
       <c r="D17" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E17">
         <v>1.13583687641778</v>
@@ -3138,7 +3138,7 @@
         <v>1.689338262028841</v>
       </c>
       <c r="D20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E20">
         <v>0.96933826202884</v>
@@ -3188,7 +3188,7 @@
         <v>1.627006479834717</v>
       </c>
       <c r="D21" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E21">
         <v>0.9357502825591215</v>
@@ -3338,7 +3338,7 @@
         <v>1.911015876946134</v>
       </c>
       <c r="D24" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E24">
         <v>1.236185039124933</v>
@@ -3438,7 +3438,7 @@
         <v>2.232760263343966</v>
       </c>
       <c r="D26" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E26">
         <v>1.515079422678022</v>
@@ -3638,7 +3638,7 @@
         <v>0.6496455995207633</v>
       </c>
       <c r="D30" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E30">
         <v>1.139659067730454</v>
@@ -3688,7 +3688,7 @@
         <v>0.6621691688877203</v>
       </c>
       <c r="D31" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E31">
         <v>1.139659067730454</v>
@@ -3738,7 +3738,7 @@
         <v>0.5096590677304533</v>
       </c>
       <c r="D32" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E32">
         <v>1.139659067730454</v>
@@ -3888,7 +3888,7 @@
         <v>-0.4482238035193742</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E35">
         <v>0.05100577720271815</v>
@@ -3938,7 +3938,7 @@
         <v>-0.5789942227972826</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E36">
         <v>0.05100577720271815</v>
@@ -3988,7 +3988,7 @@
         <v>-0.6485127107485908</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E37">
         <v>0.05100577720271815</v>
@@ -4038,7 +4038,7 @@
         <v>0.5534941892431284</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E38">
         <v>0.1656128422573726</v>
@@ -4188,7 +4188,7 @@
         <v>-1.066969696969696</v>
       </c>
       <c r="D41" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E41">
         <v>-0.543771149985659</v>
@@ -4238,7 +4238,7 @@
         <v>-1.17377114998566</v>
       </c>
       <c r="D42" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E42">
         <v>-0.543771149985659</v>
@@ -4288,7 +4288,7 @@
         <v>-1.246436605805691</v>
       </c>
       <c r="D43" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E43">
         <v>-0.543771149985659</v>
@@ -4338,7 +4338,7 @@
         <v>0.007809960806808292</v>
       </c>
       <c r="D44" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E44">
         <v>-0.2591202243252724</v>
@@ -4488,7 +4488,7 @@
         <v>-1.678657860308897</v>
       </c>
       <c r="D47" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E47">
         <v>-1.151600082010416</v>
@@ -4538,7 +4538,7 @@
         <v>-1.781600082010417</v>
       </c>
       <c r="D48" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E48">
         <v>-1.151600082010416</v>
@@ -4588,7 +4588,7 @@
         <v>-1.857481563925816</v>
       </c>
       <c r="D49" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E49">
         <v>-1.151600082010416</v>
@@ -4788,7 +4788,7 @@
         <v>-1.819193108813611</v>
       </c>
       <c r="D53" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E53">
         <v>-1.291248672795858</v>
@@ -4838,7 +4838,7 @@
         <v>-1.921248672795858</v>
       </c>
       <c r="D54" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E54">
         <v>-1.291248672795858</v>
@@ -4888,7 +4888,7 @@
         <v>-1.997869036143985</v>
       </c>
       <c r="D55" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E55">
         <v>-1.291248672795858</v>
@@ -4938,7 +4938,7 @@
         <v>-0.6779710045650891</v>
       </c>
       <c r="D56" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E56">
         <v>-0.8744524579575934</v>
@@ -4988,7 +4988,7 @@
         <v>-0.7891561672790921</v>
       </c>
       <c r="D57" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E57">
         <v>-0.8744524579575934</v>
@@ -5138,7 +5138,7 @@
         <v>0.3390481079807373</v>
       </c>
       <c r="D60" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E60">
         <v>0.8316689003586539</v>
@@ -5188,7 +5188,7 @@
         <v>0.3561344946420899</v>
       </c>
       <c r="D61" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E61">
         <v>0.8316689003586539</v>
@@ -5238,7 +5238,7 @@
         <v>0.2016689003586531</v>
       </c>
       <c r="D62" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E62">
         <v>0.8316689003586539</v>
@@ -5288,7 +5288,7 @@
         <v>0.3550656832089647</v>
       </c>
       <c r="D63" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E63">
         <v>0.8316689003586539</v>
@@ -5488,7 +5488,7 @@
         <v>1.702993205626412</v>
       </c>
       <c r="D67" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E67">
         <v>2.213613017446391</v>
@@ -5538,7 +5538,7 @@
         <v>1.700042623382163</v>
       </c>
       <c r="D68" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E68">
         <v>2.213613017446391</v>
@@ -5588,7 +5588,7 @@
         <v>1.55416430148684</v>
       </c>
       <c r="D69" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E69">
         <v>2.213613017446391</v>
@@ -5638,7 +5638,7 @@
         <v>1.697734695551071</v>
       </c>
       <c r="D70" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E70">
         <v>2.213613017446391</v>
@@ -5688,7 +5688,7 @@
         <v>2.778308822184697</v>
       </c>
       <c r="D71" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E71">
         <v>2.907149147620857</v>
@@ -5738,7 +5738,7 @@
         <v>6.23470991605689</v>
       </c>
       <c r="D72" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E72">
         <v>6.96882467582045</v>
@@ -5774,7 +5774,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5788,7 +5788,7 @@
         <v>6.165186370595404</v>
       </c>
       <c r="D73" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E73">
         <v>6.96882467582045</v>
@@ -5824,7 +5824,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5838,7 +5838,7 @@
         <v>7.462192305683145</v>
       </c>
       <c r="D74" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E74">
         <v>7.5652188186885</v>
@@ -5874,7 +5874,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5888,7 +5888,7 @@
         <v>7.766409955034785</v>
       </c>
       <c r="D75" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E75">
         <v>7.5652188186885</v>
@@ -5924,7 +5924,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5988,7 +5988,7 @@
         <v>6.790335000164763</v>
       </c>
       <c r="D77" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E77">
         <v>7.58905888555706</v>
@@ -6038,7 +6038,7 @@
         <v>6.74758629353808</v>
       </c>
       <c r="D78" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E78">
         <v>7.58905888555706</v>
@@ -6238,7 +6238,7 @@
         <v>6.426886909355456</v>
       </c>
       <c r="D82" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E82">
         <v>7.170479443185158</v>
@@ -6288,7 +6288,7 @@
         <v>6.354540197150865</v>
       </c>
       <c r="D83" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E83">
         <v>7.170479443185158</v>
@@ -6488,7 +6488,7 @@
         <v>6.205686423858355</v>
       </c>
       <c r="D87" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E87">
         <v>6.974286460418881</v>
@@ -6538,7 +6538,7 @@
         <v>6.17031498633333</v>
       </c>
       <c r="D88" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E88">
         <v>6.974286460418881</v>
@@ -6588,7 +6588,7 @@
         <v>7.467572163512598</v>
       </c>
       <c r="D89" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E89">
         <v>7.999200804331553</v>
@@ -6638,7 +6638,7 @@
         <v>7.771800736433435</v>
       </c>
       <c r="D90" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E90">
         <v>7.999200804331553</v>
@@ -6738,7 +6738,7 @@
         <v>5.758523378301289</v>
       </c>
       <c r="D92" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E92">
         <v>6.469153597378058</v>
@@ -6788,7 +6788,7 @@
         <v>5.695995227937997</v>
       </c>
       <c r="D93" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E93">
         <v>6.469153597378058</v>
@@ -6838,7 +6838,7 @@
         <v>5.575650149522264</v>
       </c>
       <c r="D94" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E94">
         <v>6.469153597378058</v>
@@ -6888,7 +6888,7 @@
         <v>6.970016293417387</v>
       </c>
       <c r="D95" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E95">
         <v>7.634780179426718</v>
@@ -6938,7 +6938,7 @@
         <v>7.273234600612143</v>
       </c>
       <c r="D96" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E96">
         <v>7.634780179426718</v>
@@ -6988,7 +6988,7 @@
         <v>5.679717798863969</v>
       </c>
       <c r="D97" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E97">
         <v>6.421217454115635</v>
@@ -7038,7 +7038,7 @@
         <v>5.650983189414583</v>
       </c>
       <c r="D98" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E98">
         <v>6.421217454115635</v>
@@ -7088,7 +7088,7 @@
         <v>5.530350494139276</v>
       </c>
       <c r="D99" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E99">
         <v>6.421217454115635</v>
@@ -7288,7 +7288,7 @@
         <v>5.621464282690935</v>
       </c>
       <c r="D103" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E103">
         <v>6.359962442366914</v>
@@ -7338,7 +7338,7 @@
         <v>5.593464733382533</v>
       </c>
       <c r="D104" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E104">
         <v>6.359962442366914</v>
@@ -7388,7 +7388,7 @@
         <v>5.472464508036733</v>
       </c>
       <c r="D105" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E105">
         <v>6.359962442366914</v>
@@ -7588,7 +7588,7 @@
         <v>4.812788531912378</v>
       </c>
       <c r="D109" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E109">
         <v>5.509619907373689</v>
@@ -7638,7 +7638,7 @@
         <v>4.794993093023895</v>
       </c>
       <c r="D110" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E110">
         <v>5.509619907373689</v>
@@ -7688,7 +7688,7 @@
         <v>4.668890812468137</v>
       </c>
       <c r="D111" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E111">
         <v>5.509619907373689</v>
@@ -7738,7 +7738,7 @@
         <v>6.099225988855712</v>
       </c>
       <c r="D112" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E112">
         <v>6.844581898111059</v>
@@ -7788,7 +7788,7 @@
         <v>6.071430549967227</v>
       </c>
       <c r="D113" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E113">
         <v>6.844581898111059</v>
@@ -7838,7 +7838,7 @@
         <v>6.326174848577831</v>
       </c>
       <c r="D114" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E114">
         <v>6.844581898111059</v>
@@ -7888,7 +7888,7 @@
         <v>4.312040252964167</v>
       </c>
       <c r="D115" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E115">
         <v>4.983070718153698</v>
@@ -7938,7 +7938,7 @@
         <v>4.300563404346324</v>
       </c>
       <c r="D116" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E116">
         <v>4.983070718153698</v>
@@ -7988,7 +7988,7 @@
         <v>4.171301828655245</v>
       </c>
       <c r="D117" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E117">
         <v>4.983070718153698</v>
@@ -8238,7 +8238,7 @@
         <v>3.944694008078107</v>
       </c>
       <c r="D122" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E122">
         <v>4.596797064225139</v>
@@ -8288,7 +8288,7 @@
         <v>3.937852443307407</v>
       </c>
       <c r="D123" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E123">
         <v>4.596797064225139</v>
@@ -8338,7 +8338,7 @@
         <v>3.806273225692757</v>
       </c>
       <c r="D124" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E124">
         <v>4.596797064225139</v>
@@ -8388,7 +8388,7 @@
         <v>5.201008311197539</v>
       </c>
       <c r="D125" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E125">
         <v>5.908899264592449</v>
@@ -8438,7 +8438,7 @@
         <v>5.425218702390213</v>
       </c>
       <c r="D126" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E126">
         <v>5.908899264592449</v>
@@ -8488,7 +8488,7 @@
         <v>5.478374570280344</v>
       </c>
       <c r="D127" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E127">
         <v>5.908899264592449</v>
@@ -8538,7 +8538,7 @@
         <v>4.103540950877517</v>
       </c>
       <c r="D128" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E128">
         <v>4.804785959699134</v>
@@ -8588,7 +8588,7 @@
         <v>4.065325239112265</v>
       </c>
       <c r="D129" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E129">
         <v>4.804785959699134</v>
@@ -8638,7 +8638,7 @@
         <v>3.934560544154515</v>
       </c>
       <c r="D130" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E130">
         <v>4.804785959699134</v>
@@ -8838,7 +8838,7 @@
         <v>3.580160099004089</v>
       </c>
       <c r="D134" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E134">
         <v>4.308315560860121</v>
@@ -8888,7 +8888,7 @@
         <v>3.549633088105812</v>
       </c>
       <c r="D135" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E135">
         <v>4.308315560860121</v>
@@ -8938,7 +8938,7 @@
         <v>3.415573235633644</v>
       </c>
       <c r="D136" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E136">
         <v>4.308315560860121</v>
@@ -9288,7 +9288,7 @@
         <v>3.927996868785175</v>
       </c>
       <c r="D143" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E143">
         <v>4.228792366606019</v>
@@ -9338,7 +9338,7 @@
         <v>4.067912029788856</v>
       </c>
       <c r="D144" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E144">
         <v>4.228792366606019</v>
@@ -9388,7 +9388,7 @@
         <v>4.059184614733637</v>
       </c>
       <c r="D145" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E145">
         <v>4.228792366606019</v>
@@ -9438,7 +9438,7 @@
         <v>2.005909712128765</v>
       </c>
       <c r="D146" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E146">
         <v>2.67318675835737</v>
@@ -9488,7 +9488,7 @@
         <v>1.861985812525753</v>
       </c>
       <c r="D147" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E147">
         <v>2.67318675835737</v>
@@ -9538,7 +9538,7 @@
         <v>3.25255656550317</v>
       </c>
       <c r="D148" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E148">
         <v>3.447665574766244</v>
@@ -9588,7 +9588,7 @@
         <v>3.347725014643028</v>
       </c>
       <c r="D149" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E149">
         <v>3.447665574766244</v>
@@ -9638,7 +9638,7 @@
         <v>3.394518515304676</v>
       </c>
       <c r="D150" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E150">
         <v>3.447665574766244</v>
@@ -9688,7 +9688,7 @@
         <v>3.355089268282093</v>
       </c>
       <c r="D151" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E151">
         <v>3.447665574766244</v>
@@ -9738,7 +9738,7 @@
         <v>3.579100375295562</v>
       </c>
       <c r="D152" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E152">
         <v>3.447665574766244</v>
@@ -10174,7 +10174,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -10224,7 +10224,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10274,7 +10274,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -10324,7 +10324,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10374,7 +10374,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -10424,7 +10424,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10474,7 +10474,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10538,7 +10538,7 @@
         <v>3.123371001188277</v>
       </c>
       <c r="D168" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E168">
         <v>4.195059763740991</v>
@@ -10588,7 +10588,7 @@
         <v>2.954328619026529</v>
       </c>
       <c r="D169" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E169">
         <v>4.195059763740991</v>
@@ -10638,7 +10638,7 @@
         <v>3.046412078566592</v>
       </c>
       <c r="D170" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E170">
         <v>4.195059763740991</v>
@@ -10688,7 +10688,7 @@
         <v>3.445059763740991</v>
       </c>
       <c r="D171" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E171">
         <v>4.195059763740991</v>
@@ -10788,7 +10788,7 @@
         <v>2.577752040845755</v>
       </c>
       <c r="D173" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E173">
         <v>3.401487870308934</v>
@@ -10838,7 +10838,7 @@
         <v>2.464829953558134</v>
       </c>
       <c r="D174" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E174">
         <v>3.401487870308934</v>
@@ -10888,7 +10888,7 @@
         <v>2.478250786050127</v>
       </c>
       <c r="D175" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E175">
         <v>3.401487870308934</v>
@@ -10938,7 +10938,7 @@
         <v>2.818408284535719</v>
       </c>
       <c r="D176" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E176">
         <v>3.401487870308934</v>
@@ -11838,7 +11838,7 @@
         <v>6.871264555787782</v>
       </c>
       <c r="D194" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E194">
         <v>5.968914093679149</v>
@@ -11888,7 +11888,7 @@
         <v>6.95746889119295</v>
       </c>
       <c r="D195" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E195">
         <v>5.968914093679149</v>
@@ -11938,7 +11938,7 @@
         <v>6.908484547625465</v>
       </c>
       <c r="D196" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E196">
         <v>6.962494985247139</v>
@@ -12088,7 +12088,7 @@
         <v>3.455949739008592</v>
       </c>
       <c r="D199" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E199">
         <v>2.626483427002986</v>
@@ -12338,7 +12338,7 @@
         <v>1.402030495249267</v>
       </c>
       <c r="D204" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E204">
         <v>0.6610634692540209</v>
@@ -12488,7 +12488,7 @@
         <v>-1.012190922870992</v>
       </c>
       <c r="D207" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E207">
         <v>0.08311492058150804</v>
@@ -12538,7 +12538,7 @@
         <v>-1.046879430812844</v>
       </c>
       <c r="D208" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E208">
         <v>0.08311492058150804</v>
@@ -12638,7 +12638,7 @@
         <v>0.5471409041675006</v>
       </c>
       <c r="D210" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E210">
         <v>-0.09752500935174702</v>
@@ -12688,7 +12688,7 @@
         <v>0.5771493770759779</v>
       </c>
       <c r="D211" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E211">
         <v>-0.1448636147170212</v>
@@ -12738,7 +12738,7 @@
         <v>0.7211216989082878</v>
       </c>
       <c r="D212" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E212">
         <v>0.3151194394660273</v>
@@ -12788,7 +12788,7 @@
         <v>0.6184603042735599</v>
       </c>
       <c r="D213" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E213">
         <v>0.3151194394660273</v>
@@ -12838,7 +12838,7 @@
         <v>0.8057932610331839</v>
       </c>
       <c r="D214" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E214">
         <v>0.3151194394660273</v>
@@ -12888,7 +12888,7 @@
         <v>0.1720291663575146</v>
       </c>
       <c r="D215" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E215">
         <v>-1.174782432733231</v>
@@ -12924,7 +12924,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12938,7 +12938,7 @@
         <v>-0.5832848576420009</v>
       </c>
       <c r="D216" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E216">
         <v>-1.223526404187433</v>
@@ -12974,7 +12974,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -12988,7 +12988,7 @@
         <v>-0.5978983899145334</v>
       </c>
       <c r="D217" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E217">
         <v>-1.157197898187556</v>
@@ -13024,7 +13024,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -13038,7 +13038,7 @@
         <v>-0.522125420733472</v>
       </c>
       <c r="D218" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E218">
         <v>-1.167246194006191</v>
@@ -13074,7 +13074,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -13088,7 +13088,7 @@
         <v>-0.5938162465515013</v>
       </c>
       <c r="D219" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E219">
         <v>-1.167246194006191</v>
@@ -13124,7 +13124,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -13138,7 +13138,7 @@
         <v>-0.4086954732787849</v>
       </c>
       <c r="D220" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E220">
         <v>-1.167246194006191</v>
@@ -13174,7 +13174,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -13188,7 +13188,7 @@
         <v>1.516859912216534</v>
       </c>
       <c r="D221" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E221">
         <v>0.1337015362106797</v>
@@ -13238,7 +13238,7 @@
         <v>0.6549286759327</v>
       </c>
       <c r="D222" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E222">
         <v>0.009840892465252438</v>
@@ -13288,7 +13288,7 @@
         <v>0.6801911119239215</v>
       </c>
       <c r="D223" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E223">
         <v>0.1028237015362095</v>
@@ -13338,7 +13338,7 @@
         <v>0.8396671543525969</v>
       </c>
       <c r="D224" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E224">
         <v>0.1921232626188711</v>
@@ -13388,7 +13388,7 @@
         <v>0.7340526700804659</v>
       </c>
       <c r="D225" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E225">
         <v>0.1921232626188711</v>
@@ -13488,7 +13488,7 @@
         <v>1.469564000694344</v>
       </c>
       <c r="D227" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E227">
         <v>0.08768389256746723</v>
@@ -13524,7 +13524,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -13538,7 +13538,7 @@
         <v>0.6113823501888458</v>
       </c>
       <c r="D228" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E228">
         <v>-0.03353499756140543</v>
@@ -13574,7 +13574,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13588,7 +13588,7 @@
         <v>0.6047501988112209</v>
       </c>
       <c r="D229" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E229">
         <v>0.05851041506496912</v>
@@ -13624,7 +13624,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13638,7 +13638,7 @@
         <v>0.7917747178202177</v>
       </c>
       <c r="D230" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E230">
         <v>0.144316043945091</v>
@@ -13674,7 +13674,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13688,7 +13688,7 @@
         <v>0.6873532835684664</v>
       </c>
       <c r="D231" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E231">
         <v>0.144316043945091</v>
@@ -13724,7 +13724,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13774,7 +13774,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13788,7 +13788,7 @@
         <v>1.44514430187747</v>
       </c>
       <c r="D233" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E233">
         <v>0.06392418561050839</v>
@@ -13838,7 +13838,7 @@
         <v>0.5888986274943893</v>
       </c>
       <c r="D234" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E234">
         <v>-0.05593072134120547</v>
@@ -13888,7 +13888,7 @@
         <v>0.5831904647206478</v>
       </c>
       <c r="D235" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E235">
         <v>0.03563069725456458</v>
@@ -13938,7 +13938,7 @@
         <v>0.7670470228020498</v>
       </c>
       <c r="D236" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E236">
         <v>0.1196323483842505</v>
@@ -13988,7 +13988,7 @@
         <v>0.6632415809528851</v>
       </c>
       <c r="D237" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E237">
         <v>0.1196323483842505</v>
@@ -14038,7 +14038,7 @@
         <v>-0.3588062330199779</v>
       </c>
       <c r="D238" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E238">
         <v>-0.2613915586021829</v>
@@ -14088,7 +14088,7 @@
         <v>-0.341391558602183</v>
       </c>
       <c r="D239" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E239">
         <v>-0.2613915586021829</v>
@@ -14138,7 +14138,7 @@
         <v>1.286085745836417</v>
       </c>
       <c r="D240" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E240">
         <v>-0.09083549053754325</v>
@@ -14174,7 +14174,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -14188,7 +14188,7 @@
         <v>0.4424501191394743</v>
       </c>
       <c r="D241" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E241">
         <v>-0.2018060457103878</v>
@@ -14224,7 +14224,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -14238,7 +14238,7 @@
         <v>0.4427603882159339</v>
       </c>
       <c r="D242" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E242">
         <v>-0.1133971390361523</v>
@@ -14274,7 +14274,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -14288,7 +14288,7 @@
         <v>0.6059823228109291</v>
       </c>
       <c r="D243" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E243">
         <v>-0.04114575961400391</v>
@@ -14324,7 +14324,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -14338,7 +14338,7 @@
         <v>0.5061891688618996</v>
       </c>
       <c r="D244" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E244">
         <v>-0.04114575961400391</v>
@@ -14374,7 +14374,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -14388,7 +14388,7 @@
         <v>-0.5227368529397651</v>
       </c>
       <c r="D245" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E245">
         <v>-0.3415594517159466</v>
@@ -14424,7 +14424,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -14438,7 +14438,7 @@
         <v>-0.5056087705148382</v>
       </c>
       <c r="D246" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E246">
         <v>-0.3415594517159466</v>
@@ -14474,7 +14474,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -14488,7 +14488,7 @@
         <v>1.220304308582177</v>
       </c>
       <c r="D247" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E247">
         <v>-0.154839051109235</v>
@@ -14538,7 +14538,7 @@
         <v>0.3818837868207066</v>
       </c>
       <c r="D248" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E248">
         <v>-0.2621353278048151</v>
@@ -14588,7 +14588,7 @@
         <v>0.3846830832527317</v>
       </c>
       <c r="D249" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E249">
         <v>-0.1750301973644497</v>
@@ -14638,7 +14638,7 @@
         <v>0.5393712097715007</v>
       </c>
       <c r="D250" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E250">
         <v>-0.1076383475412612</v>
@@ -14688,7 +14688,7 @@
         <v>0.4412374073928493</v>
       </c>
       <c r="D251" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E251">
         <v>-0.1076383475412612</v>
@@ -14738,7 +14738,7 @@
         <v>-0.5905332171008926</v>
       </c>
       <c r="D252" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E252">
         <v>-0.318380300096722</v>
@@ -14788,7 +14788,7 @@
         <v>-0.5124949878498484</v>
       </c>
       <c r="D253" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E253">
         <v>-0.318380300096722</v>
@@ -14838,7 +14838,7 @@
         <v>0.5242887395747005</v>
       </c>
       <c r="D254" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E254">
         <v>-0.1202877329872347</v>
@@ -14888,7 +14888,7 @@
         <v>0.5212357776743701</v>
       </c>
       <c r="D255" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E255">
         <v>-0.03011713389658688</v>
@@ -14938,7 +14938,7 @@
         <v>0.6959887899040744</v>
       </c>
       <c r="D256" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E256">
         <v>0.04870055362310488</v>
@@ -14988,7 +14988,7 @@
         <v>0.5939534819705194</v>
       </c>
       <c r="D257" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E257">
         <v>0.04870055362310488</v>
@@ -15038,7 +15038,7 @@
         <v>-0.3211288472862446</v>
       </c>
       <c r="D258" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E258">
         <v>-0.1326523579478529</v>
@@ -15088,7 +15088,7 @@
         <v>-0.431128847286244</v>
       </c>
       <c r="D259" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E259">
         <v>-0.1326523579478529</v>
@@ -15138,7 +15138,7 @@
         <v>-0.351975902162371</v>
       </c>
       <c r="D260" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E260">
         <v>-0.1326523579478529</v>
@@ -15188,7 +15188,7 @@
         <v>0.5451410172423419</v>
       </c>
       <c r="D261" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E261">
         <v>-0.09951706893081891</v>
@@ -15224,7 +15224,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -15238,7 +15238,7 @@
         <v>0.5412311124241622</v>
       </c>
       <c r="D262" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E262">
         <v>-0.008897594978440893</v>
@@ -15274,7 +15274,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -15288,7 +15288,7 @@
         <v>0.7189222146579191</v>
       </c>
       <c r="D263" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E263">
         <v>0.07159317157133671</v>
@@ -15324,7 +15324,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -15338,7 +15338,7 @@
         <v>0.6163156114457973</v>
       </c>
       <c r="D264" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E264">
         <v>0.07159317157133671</v>
@@ -15374,7 +15374,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15388,7 +15388,7 @@
         <v>-0.2977873544762826</v>
       </c>
       <c r="D265" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E265">
         <v>0.2641354210821554</v>
@@ -15424,7 +15424,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15438,7 +15438,7 @@
         <v>-0.407787354476282</v>
       </c>
       <c r="D266" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E266">
         <v>0.2641354210821554</v>
@@ -15474,7 +15474,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15488,7 +15488,7 @@
         <v>0.6831127115251583</v>
       </c>
       <c r="D267" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E267">
         <v>0.0379146187207553</v>
@@ -15524,7 +15524,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15538,7 +15538,7 @@
         <v>0.6735327370789186</v>
       </c>
       <c r="D268" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E268">
         <v>0.1315041291449752</v>
@@ -15574,7 +15574,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15588,7 +15588,7 @@
         <v>0.8706640780374553</v>
       </c>
       <c r="D269" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E269">
         <v>0.2230650316352509</v>
@@ -15624,7 +15624,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15638,7 +15638,7 @@
         <v>0.7642774284066274</v>
       </c>
       <c r="D270" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E270">
         <v>0.2230650316352509</v>
@@ -15674,7 +15674,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15688,7 +15688,7 @@
         <v>-0.1433454579405264</v>
       </c>
       <c r="D271" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E271">
         <v>0.4234373772991074</v>
@@ -15724,7 +15724,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15738,7 +15738,7 @@
         <v>-0.2533454579405259</v>
       </c>
       <c r="D272" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E272">
         <v>0.4234373772991074</v>
@@ -15774,7 +15774,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15788,7 +15788,7 @@
         <v>-0.05222072710995107</v>
       </c>
       <c r="D273" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E273">
         <v>0.6345003208948405</v>
@@ -15838,7 +15838,7 @@
         <v>0.702314352898032</v>
       </c>
       <c r="D274" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E274">
         <v>0.05704110689843134</v>
@@ -15888,7 +15888,7 @@
         <v>0.6919452699022219</v>
       </c>
       <c r="D275" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E275">
         <v>0.151043959896235</v>
@@ -15938,7 +15938,7 @@
         <v>0.6723143528980309</v>
       </c>
       <c r="D276" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E276">
         <v>0.151043959896235</v>
@@ -16038,7 +16038,7 @@
         <v>0.8917821258878558</v>
       </c>
       <c r="D278" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E278">
         <v>0.2441455028880526</v>
@@ -16088,7 +16088,7 @@
         <v>0.7848694038906459</v>
       </c>
       <c r="D279" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E279">
         <v>0.2441455028880526</v>
@@ -16138,7 +16138,7 @@
         <v>-0.1218516441141411</v>
       </c>
       <c r="D280" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E280">
         <v>0.4456075698822666</v>
@@ -16188,7 +16188,7 @@
         <v>-0.03112774311154531</v>
       </c>
       <c r="D281" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E281">
         <v>0.4456075698822666</v>
@@ -16238,7 +16238,7 @@
         <v>-0.1599756512329034</v>
       </c>
       <c r="D282" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E282">
         <v>0.5314388961892202</v>
@@ -16288,7 +16288,7 @@
         <v>0.6023819278039682</v>
       </c>
       <c r="D283" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E283">
         <v>-0.04250019324418908</v>
@@ -16338,7 +16338,7 @@
         <v>0.5961196567983258</v>
       </c>
       <c r="D284" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E284">
         <v>0.04935147252067118</v>
@@ -16388,7 +16388,7 @@
         <v>0.572381927803967</v>
       </c>
       <c r="D285" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E285">
         <v>0.04935147252067118</v>
@@ -16488,7 +16488,7 @@
         <v>0.7818760145319583</v>
       </c>
       <c r="D287" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E287">
         <v>0.2188455592486616</v>
@@ -16538,7 +16538,7 @@
         <v>0.6777011671948596</v>
       </c>
       <c r="D288" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E288">
         <v>0.1344349540078777</v>
@@ -16588,7 +16588,7 @@
         <v>-0.2337133802272593</v>
       </c>
       <c r="D289" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E289">
         <v>0.3302257092061467</v>
@@ -16638,7 +16638,7 @@
         <v>-0.1404471670402767</v>
       </c>
       <c r="D290" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E290">
         <v>0.3302257092061467</v>
@@ -16688,7 +16688,7 @@
         <v>-0.5297221743420888</v>
       </c>
       <c r="D291" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E291">
         <v>0.177797484794409</v>
@@ -16724,7 +16724,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16738,7 +16738,7 @@
         <v>0.2594772575520725</v>
       </c>
       <c r="D292" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E292">
         <v>-0.3840627708532196</v>
@@ -16774,7 +16774,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16788,7 +16788,7 @@
         <v>0.2160020090057699</v>
       </c>
       <c r="D293" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E293">
         <v>-0.2995926146241139</v>
@@ -16824,7 +16824,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16838,7 +16838,7 @@
         <v>0.2294772575520714</v>
       </c>
       <c r="D294" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E294">
         <v>-0.2995926146241139</v>
@@ -16874,7 +16874,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16924,7 +16924,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16938,7 +16938,7 @@
         <v>0.4047479818870166</v>
       </c>
       <c r="D296" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E296">
         <v>-0.1643218902891714</v>
@@ -16974,7 +16974,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16988,7 +16988,7 @@
         <v>0.3099677830499701</v>
       </c>
       <c r="D297" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E297">
         <v>-0.2420220323156315</v>
@@ -17024,7 +17024,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -17038,7 +17038,7 @@
         <v>-0.6175518760865248</v>
       </c>
       <c r="D298" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E298">
         <v>-0.06569162043889776</v>
@@ -17074,7 +17074,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -17088,7 +17088,7 @@
         <v>-0.5155620607209208</v>
       </c>
       <c r="D299" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E299">
         <v>-0.06569162043889776</v>
@@ -17124,7 +17124,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -17138,7 +17138,7 @@
         <v>3.711167000814271</v>
       </c>
       <c r="D300" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E300">
         <v>4.512707221119614</v>
@@ -17188,7 +17188,7 @@
         <v>5.260227025292643</v>
       </c>
       <c r="D301" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E301">
         <v>3.883216817226483</v>
@@ -17238,7 +17238,7 @@
         <v>3.612446707073811</v>
       </c>
       <c r="D302" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E302">
         <v>4.036376474529282</v>
@@ -17288,7 +17288,7 @@
         <v>2.778054848675449</v>
       </c>
       <c r="D303" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E303">
         <v>3.550231399857543</v>
@@ -17338,7 +17338,7 @@
         <v>2.800953545963342</v>
       </c>
       <c r="D304" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E304">
         <v>3.550231399857543</v>
@@ -17388,7 +17388,7 @@
         <v>4.323852243251237</v>
       </c>
       <c r="D305" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E305">
         <v>2.974574389357036</v>
@@ -17438,7 +17438,7 @@
         <v>2.718486113765989</v>
       </c>
       <c r="D306" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E306">
         <v>3.123410865296</v>
@@ -17488,7 +17488,7 @@
         <v>1.983160587873193</v>
       </c>
       <c r="D307" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E307">
         <v>2.730322983995075</v>
@@ -17538,7 +17538,7 @@
         <v>2.004669609879961</v>
       </c>
       <c r="D308" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E308">
         <v>2.730322983995075</v>
@@ -17588,7 +17588,7 @@
         <v>3.526178631886735</v>
       </c>
       <c r="D309" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E309">
         <v>2.200525257771622</v>
@@ -17638,7 +17638,7 @@
         <v>1.956944059710679</v>
       </c>
       <c r="D310" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E310">
         <v>2.409218509541397</v>
@@ -17688,7 +17688,7 @@
         <v>0.8799289586838714</v>
       </c>
       <c r="D311" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E311">
         <v>1.592374275565531</v>
@@ -17738,7 +17738,7 @@
         <v>0.9682501402131294</v>
       </c>
       <c r="D312" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E312">
         <v>1.592374275565531</v>
@@ -17788,7 +17788,7 @@
         <v>2.419089549448499</v>
       </c>
       <c r="D313" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E313">
         <v>1.126224527949153</v>
@@ -17838,7 +17838,7 @@
         <v>2.06419891568518</v>
       </c>
       <c r="D314" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E314">
         <v>1.126224527949153</v>
@@ -17888,7 +17888,7 @@
         <v>0.9000018695083227</v>
       </c>
       <c r="D315" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E315">
         <v>1.703012712656575</v>
@@ -17938,7 +17938,7 @@
         <v>0.3940106533845285</v>
       </c>
       <c r="D316" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E316">
         <v>0.9777032963232024</v>
@@ -17974,7 +17974,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17988,7 +17988,7 @@
         <v>0.284010653384529</v>
       </c>
       <c r="D317" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E317">
         <v>0.9777032963232024</v>
@@ -18024,7 +18024,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -18038,7 +18038,7 @@
         <v>1.821087613711049</v>
       </c>
       <c r="D318" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E318">
         <v>0.5459334509356335</v>
@@ -18074,7 +18074,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -18088,7 +18088,7 @@
         <v>1.5037023278337</v>
       </c>
       <c r="D319" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E319">
         <v>0.5459334509356335</v>
@@ -18124,7 +18124,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -18138,7 +18138,7 @@
         <v>0.3290871294662949</v>
       </c>
       <c r="D320" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E320">
         <v>1.164394244405246</v>
@@ -18174,7 +18174,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -18188,7 +18188,7 @@
         <v>-0.1303378620988589</v>
       </c>
       <c r="D321" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E321">
         <v>0.5687326111345428</v>
@@ -18238,7 +18238,7 @@
         <v>1.405290327194502</v>
       </c>
       <c r="D322" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E322">
         <v>0.1424507182009354</v>
@@ -18288,7 +18288,7 @@
         <v>1.113982919914012</v>
       </c>
       <c r="D323" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E323">
         <v>0.1424507182009354</v>
@@ -18338,7 +18338,7 @@
         <v>0.01807890749429752</v>
       </c>
       <c r="D324" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E324">
         <v>0.7898869323337241</v>
@@ -18388,7 +18388,7 @@
         <v>-0.1449533761282655</v>
       </c>
       <c r="D325" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E325">
         <v>0.5539893391153683</v>
@@ -18438,7 +18438,7 @@
         <v>1.390623709969187</v>
       </c>
       <c r="D326" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E326">
         <v>0.1282184781408322</v>
@@ -18488,7 +18488,7 @@
         <v>1.100236160215024</v>
       </c>
       <c r="D327" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E327">
         <v>0.1282184781408322</v>
@@ -18538,7 +18538,7 @@
         <v>0.003795564238286531</v>
       </c>
       <c r="D328" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E328">
         <v>0.77667675619176</v>
@@ -18588,7 +18588,7 @@
         <v>1.338895251493001</v>
       </c>
       <c r="D329" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E329">
         <v>0.5272283520481338</v>
@@ -18638,7 +18638,7 @@
         <v>-0.04658110525333115</v>
       </c>
       <c r="D330" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E330">
         <v>0.7300850958569374</v>
@@ -18688,7 +18688,7 @@
         <v>5.252623163353501</v>
       </c>
       <c r="D331" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E331">
         <v>5.811442523768368</v>
@@ -18838,7 +18838,7 @@
         <v>5.155821953327571</v>
       </c>
       <c r="D334" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E334">
         <v>5.436800777873812</v>
@@ -18888,7 +18888,7 @@
         <v>5.21461106309421</v>
       </c>
       <c r="D335" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E335">
         <v>5.436800777873812</v>
@@ -19038,7 +19038,7 @@
         <v>5.996975409186557</v>
       </c>
       <c r="D338" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E338">
         <v>6.322440349888621</v>
@@ -19088,7 +19088,7 @@
         <v>6.04103615104905</v>
       </c>
       <c r="D339" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E339">
         <v>6.322440349888621</v>
@@ -19238,7 +19238,7 @@
         <v>6.467595657864342</v>
       </c>
       <c r="D342" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E342">
         <v>6.75843983370544</v>
@@ -19288,7 +19288,7 @@
         <v>6.50341596735699</v>
       </c>
       <c r="D343" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E343">
         <v>6.75843983370544</v>
@@ -19388,7 +19388,7 @@
         <v>7.038673370415092</v>
       </c>
       <c r="D345" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E345">
         <v>7.57711369319794</v>
@@ -19438,7 +19438,7 @@
         <v>6.933612348269409</v>
       </c>
       <c r="D346" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E346">
         <v>7.57711369319794</v>
@@ -19488,7 +19488,7 @@
         <v>7.041012886240821</v>
       </c>
       <c r="D347" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E347">
         <v>7.57711369319794</v>
@@ -19588,7 +19588,7 @@
         <v>7.603480524142883</v>
       </c>
       <c r="D349" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E349">
         <v>8.074842039131216</v>
@@ -19638,7 +19638,7 @@
         <v>7.583949919224556</v>
       </c>
       <c r="D350" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E350">
         <v>8.115780829294561</v>
@@ -19688,7 +19688,7 @@
         <v>7.602119009154551</v>
       </c>
       <c r="D351" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E351">
         <v>8.115780829294561</v>
@@ -19738,7 +19738,7 @@
         <v>7.596203554119548</v>
       </c>
       <c r="D352" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E352">
         <v>8.115780829294561</v>
@@ -19838,7 +19838,7 @@
         <v>8.197082757216956</v>
       </c>
       <c r="D354" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E354">
         <v>8.669626746773165</v>
@@ -19888,7 +19888,7 @@
         <v>8.20282687732055</v>
       </c>
       <c r="D355" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E355">
         <v>8.694010892986238</v>
@@ -19938,7 +19938,7 @@
         <v>8.194538767660747</v>
       </c>
       <c r="D356" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E356">
         <v>8.694010892986238</v>
@@ -19988,7 +19988,7 @@
         <v>8.192170736329373</v>
       </c>
       <c r="D357" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E357">
         <v>8.694010892986238</v>
@@ -20038,7 +20038,7 @@
         <v>-0.9277197529705248</v>
       </c>
       <c r="D358" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E358">
         <v>-1.43484711683287</v>
@@ -20088,7 +20088,7 @@
         <v>-1.739101844557563</v>
       </c>
       <c r="D359" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E359">
         <v>-1.225064022760026</v>
@@ -20138,7 +20138,7 @@
         <v>-1.67793665889768</v>
       </c>
       <c r="D360" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E360">
         <v>-1.225064022760026</v>
@@ -20188,7 +20188,7 @@
         <v>-1.660809295035333</v>
       </c>
       <c r="D361" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E361">
         <v>-0.9252809286871813</v>
@@ -20238,7 +20238,7 @@
         <v>-1.665172475723605</v>
       </c>
       <c r="D362" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E362">
         <v>-0.9252809286871813</v>
@@ -20288,7 +20288,7 @@
         <v>-0.8321510586103233</v>
       </c>
       <c r="D363" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E363">
         <v>-0.4166226922621714</v>
@@ -20338,7 +20338,7 @@
         <v>-3.843022818180284</v>
       </c>
       <c r="D364" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E364">
         <v>-3.26412423419014</v>
@@ -20388,7 +20388,7 @@
         <v>-3.712943072690754</v>
       </c>
       <c r="D365" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E365">
         <v>-3.26412423419014</v>
@@ -20438,7 +20438,7 @@
         <v>-4.087117010683363</v>
       </c>
       <c r="D366" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E366">
         <v>-3.293178553948453</v>
@@ -20488,7 +20488,7 @@
         <v>-2.768453907950921</v>
       </c>
       <c r="D367" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E367">
         <v>-2.083569770974329</v>
@@ -20538,7 +20538,7 @@
         <v>-2.698924870466321</v>
       </c>
       <c r="D368" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E368">
         <v>-2.083569770974329</v>
@@ -20588,7 +20588,7 @@
         <v>-5.897343766119011</v>
       </c>
       <c r="D369" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E369">
         <v>-5.21377186018452</v>
@@ -20638,7 +20638,7 @@
         <v>-5.892794919062931</v>
       </c>
       <c r="D370" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E370">
         <v>-5.287381083735886</v>
@@ -20688,7 +20688,7 @@
         <v>-6.281892613175087</v>
       </c>
       <c r="D371" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E371">
         <v>-5.383339366049038</v>
@@ -20738,7 +20738,7 @@
         <v>-4.84153475427336</v>
       </c>
       <c r="D372" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E372">
         <v>-4.085725742427703</v>
@@ -20788,7 +20788,7 @@
         <v>-4.665255930675347</v>
       </c>
       <c r="D373" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E373">
         <v>-4.085725742427703</v>
@@ -20838,7 +20838,7 @@
         <v>-7.494239379929031</v>
       </c>
       <c r="D374" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E374">
         <v>-6.751752878533589</v>
@@ -20888,7 +20888,7 @@
         <v>-7.492791301055105</v>
       </c>
       <c r="D375" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E375">
         <v>-6.850168247542195</v>
@@ -20938,7 +20938,7 @@
         <v>-7.875687458802952</v>
       </c>
       <c r="D376" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E376">
         <v>-6.901165391214095</v>
@@ -20988,7 +20988,7 @@
         <v>-6.346957706709796</v>
       </c>
       <c r="D377" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E377">
         <v>-5.984607757431821</v>
@@ -21038,7 +21038,7 @@
         <v>-6.382299087003467</v>
       </c>
       <c r="D378" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E378">
         <v>-5.984607757431821</v>
@@ -21088,7 +21088,7 @@
         <v>-8.194922154350412</v>
       </c>
       <c r="D379" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E379">
         <v>-7.42658522050059</v>
@@ -21138,7 +21138,7 @@
         <v>-8.155009684147785</v>
       </c>
       <c r="D380" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E380">
         <v>-7.535884982121567</v>
@@ -21188,7 +21188,7 @@
         <v>-8.575009684147785</v>
       </c>
       <c r="D381" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E381">
         <v>-7.567154164183544</v>
@@ -21238,7 +21238,7 @@
         <v>-7.007504283373057</v>
       </c>
       <c r="D382" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E382">
         <v>-6.779342409117989</v>
@@ -21288,7 +21288,7 @@
         <v>-7.019036054827168</v>
       </c>
       <c r="D383" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E383">
         <v>-6.779342409117989</v>
@@ -21338,7 +21338,7 @@
         <v>-8.936969711340112</v>
       </c>
       <c r="D384" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E384">
         <v>-8.141256265679017</v>
@@ -21388,7 +21388,7 @@
         <v>-8.895616372094786</v>
       </c>
       <c r="D385" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E385">
         <v>-8.262082979641582</v>
@@ -21438,7 +21438,7 @@
         <v>-9.315616372094786</v>
       </c>
       <c r="D386" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E386">
         <v>-8.272459560584432</v>
@@ -21588,7 +21588,7 @@
         <v>-8.948241366187794</v>
       </c>
       <c r="D389" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E389">
         <v>-8.152112073066304</v>
@@ -21638,7 +21638,7 @@
         <v>-8.90686614023403</v>
       </c>
       <c r="D390" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E390">
         <v>-8.273113880696405</v>
@@ -21688,7 +21688,7 @@
         <v>-9.32686614023403</v>
       </c>
       <c r="D391" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E391">
         <v>-7.892485491389962</v>
@@ -21738,7 +21738,7 @@
         <v>-7.646984587574911</v>
       </c>
       <c r="D392" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E392">
         <v>-7.178478260869557</v>
@@ -21788,7 +21788,7 @@
         <v>-7.393291551707726</v>
       </c>
       <c r="D393" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E393">
         <v>-7.178478260869557</v>
@@ -21838,7 +21838,7 @@
         <v>-9.216500648310582</v>
       </c>
       <c r="D394" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E394">
         <v>-8.410474410800093</v>
@@ -21874,7 +21874,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21888,7 +21888,7 @@
         <v>-9.174604530546869</v>
       </c>
       <c r="D395" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E395">
         <v>-8.477110822973078</v>
@@ -21924,7 +21924,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21938,7 +21938,7 @@
         <v>-9.594604530546869</v>
       </c>
       <c r="D396" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E396">
         <v>-8.147201586454123</v>
@@ -21974,7 +21974,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -22024,7 +22024,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -22074,7 +22074,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -22088,7 +22088,7 @@
         <v>-9.488460946517886</v>
       </c>
       <c r="D399" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E399">
         <v>-8.782113312812619</v>
@@ -22138,7 +22138,7 @@
         <v>-9.908460946517886</v>
       </c>
       <c r="D400" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E400">
         <v>-8.445792612543283</v>
@@ -22188,7 +22188,7 @@
         <v>-7.945711812235471</v>
       </c>
       <c r="D401" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E401">
         <v>-7.898110811850708</v>
@@ -22238,7 +22238,7 @@
         <v>-7.914350711812233</v>
       </c>
       <c r="D402" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E402">
         <v>-7.898110811850708</v>
@@ -22288,7 +22288,7 @@
         <v>-9.731958922090953</v>
       </c>
       <c r="D403" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E403">
         <v>-8.922781252412936</v>
@@ -22338,7 +22338,7 @@
         <v>-10.15195892209095</v>
       </c>
       <c r="D404" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E404">
         <v>-8.677447301366684</v>
@@ -22488,7 +22488,7 @@
         <v>-9.713150682287534</v>
       </c>
       <c r="D407" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E407">
         <v>-8.904576779062349</v>
@@ -22538,7 +22538,7 @@
         <v>-10.13315068228753</v>
       </c>
       <c r="D408" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E408">
         <v>-8.659553859219074</v>
@@ -22688,7 +22688,7 @@
         <v>-9.786103124815638</v>
       </c>
       <c r="D411" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E411">
         <v>-9.096428585475211</v>
@@ -22738,7 +22738,7 @@
         <v>-9.885452203496488</v>
       </c>
       <c r="D412" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E412">
         <v>-9.071347220310315</v>
@@ -22788,7 +22788,7 @@
         <v>-10.30545220349649</v>
       </c>
       <c r="D413" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E413">
         <v>-8.823474956244713</v>
@@ -22938,7 +22938,7 @@
         <v>-9.843764571794191</v>
       </c>
       <c r="D416" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E416">
         <v>-9.128491781807984</v>
@@ -22988,7 +22988,7 @@
         <v>-9.944492011757397</v>
       </c>
       <c r="D417" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E417">
         <v>-9.128491781807984</v>
@@ -23038,7 +23038,7 @@
         <v>-10.3644920117574</v>
       </c>
       <c r="D418" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E418">
         <v>-8.879643178500714</v>
@@ -23088,7 +23088,7 @@
         <v>-8.368915738537504</v>
       </c>
       <c r="D419" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E419">
         <v>-7.670672951950555</v>
@@ -23138,7 +23138,7 @@
         <v>-8.412127831876973</v>
       </c>
       <c r="D420" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E420">
         <v>-7.670672951950555</v>
@@ -23188,7 +23188,7 @@
         <v>-8.3229155085881</v>
       </c>
       <c r="D421" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E421">
         <v>-7.670672951950555</v>
@@ -23238,7 +23238,7 @@
         <v>-9.413850870677146</v>
       </c>
       <c r="D422" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E422">
         <v>-8.460862700719371</v>
@@ -23288,7 +23288,7 @@
         <v>-9.504301489099706</v>
       </c>
       <c r="D423" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E423">
         <v>-8.460862700719371</v>
@@ -23338,7 +23338,7 @@
         <v>-9.381313319141935</v>
       </c>
       <c r="D424" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E424">
         <v>-8.460862700719371</v>
@@ -23388,7 +23388,7 @@
         <v>-7.960412082296807</v>
       </c>
       <c r="D425" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E425">
         <v>-7.188091863543228</v>
@@ -23438,7 +23438,7 @@
         <v>-7.928542481965792</v>
       </c>
       <c r="D426" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E426">
         <v>-7.188091863543228</v>
@@ -23488,7 +23488,7 @@
         <v>-7.787273706198183</v>
       </c>
       <c r="D427" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E427">
         <v>-7.188091863543228</v>
@@ -23538,7 +23538,7 @@
         <v>-9.172895884074581</v>
       </c>
       <c r="D428" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E428">
         <v>-8.145576045355</v>
@@ -23588,7 +23588,7 @@
         <v>-9.058289567940399</v>
       </c>
       <c r="D429" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E429">
         <v>-8.145576045355</v>
@@ -23638,7 +23638,7 @@
         <v>-7.622862522769601</v>
       </c>
       <c r="D430" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E430">
         <v>-6.959864303403672</v>
@@ -23688,7 +23688,7 @@
         <v>-7.631631429214679</v>
       </c>
       <c r="D431" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E431">
         <v>-6.959864303403672</v>
@@ -23738,7 +23738,7 @@
         <v>-7.222167461470761</v>
       </c>
       <c r="D432" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E432">
         <v>-6.959864303403672</v>
@@ -23788,7 +23788,7 @@
         <v>-7.490685032440284</v>
       </c>
       <c r="D433" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E433">
         <v>-6.959864303403672</v>
@@ -23838,7 +23838,7 @@
         <v>-8.561827797884455</v>
       </c>
       <c r="D434" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E434">
         <v>-7.564229169582681</v>
@@ -23888,7 +23888,7 @@
         <v>-8.46267651116753</v>
       </c>
       <c r="D435" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E435">
         <v>-7.564229169582681</v>
@@ -23938,7 +23938,7 @@
         <v>-7.05578182799783</v>
       </c>
       <c r="D436" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E436">
         <v>-6.720998980224341</v>
@@ -23988,7 +23988,7 @@
         <v>-6.680647007658305</v>
       </c>
       <c r="D437" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E437">
         <v>-6.720998980224341</v>
@@ -24038,7 +24038,7 @@
         <v>-6.943814760752625</v>
       </c>
       <c r="D438" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E438">
         <v>-6.720998980224341</v>
@@ -24088,7 +24088,7 @@
         <v>-7.900748535322215</v>
       </c>
       <c r="D439" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E439">
         <v>-7.068198896242816</v>
@@ -24138,7 +24138,7 @@
         <v>-7.954473715782516</v>
       </c>
       <c r="D440" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E440">
         <v>-7.068198896242816</v>
@@ -24188,7 +24188,7 @@
         <v>-7.896025874307643</v>
       </c>
       <c r="D441" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E441">
         <v>-7.068198896242816</v>
@@ -24238,7 +24238,7 @@
         <v>-6.218598358361149</v>
       </c>
       <c r="D442" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E442">
         <v>-6.369374437623716</v>
@@ -24288,7 +24288,7 @@
         <v>-6.477201415688539</v>
       </c>
       <c r="D443" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E443">
         <v>-6.369374437623716</v>
@@ -24338,7 +24338,7 @@
         <v>-6.477356631541051</v>
       </c>
       <c r="D444" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E444">
         <v>-6.369374437623716</v>
@@ -24388,7 +24388,7 @@
         <v>0.1544375412573284</v>
       </c>
       <c r="D445" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E445">
         <v>0.7763231468178482</v>
@@ -24438,7 +24438,7 @@
         <v>0.162551935696813</v>
       </c>
       <c r="D446" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E446">
         <v>0.7763231468178482</v>
@@ -24488,7 +24488,7 @@
         <v>1.050094357938882</v>
       </c>
       <c r="D447" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E447">
         <v>0.5910371607191394</v>
@@ -24688,7 +24688,7 @@
         <v>-0.05317325947102702</v>
       </c>
       <c r="D451" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E451">
         <v>0.5712288406437764</v>
@@ -24738,7 +24738,7 @@
         <v>-0.04757535958582615</v>
       </c>
       <c r="D452" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E452">
         <v>0.5712288406437764</v>
@@ -24788,7 +24788,7 @@
         <v>0.8500330408733774</v>
       </c>
       <c r="D453" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E453">
         <v>0.392234090930776</v>
@@ -24988,7 +24988,7 @@
         <v>-0.2692961577804383</v>
       </c>
       <c r="D457" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E457">
         <v>0.3577256138290235</v>
@@ -25038,7 +25038,7 @@
         <v>-0.2663179293898956</v>
       </c>
       <c r="D458" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E458">
         <v>0.3577256138290235</v>
@@ -25088,7 +25088,7 @@
         <v>0.6417691570479445</v>
       </c>
       <c r="D459" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E459">
         <v>0.1852800428526731</v>
@@ -25288,7 +25288,7 @@
         <v>0.05587008030584961</v>
       </c>
       <c r="D463" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E463">
         <v>0.6789504429688105</v>
@@ -25338,7 +25338,7 @@
         <v>0.06278971764289132</v>
       </c>
       <c r="D464" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E464">
         <v>0.6789504429688105</v>
@@ -25388,7 +25388,7 @@
         <v>0.9551111682947298</v>
       </c>
       <c r="D465" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E465">
         <v>0.4966513496262088</v>
@@ -25588,7 +25588,7 @@
         <v>-0.1893348809203133</v>
       </c>
       <c r="D469" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E469">
         <v>0.4367176630908425</v>
@@ -25638,7 +25638,7 @@
         <v>-0.1853874249314682</v>
       </c>
       <c r="D470" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E470">
         <v>0.4367176630908425</v>
@@ -25688,7 +25688,7 @@
         <v>0.7188227511131551</v>
       </c>
       <c r="D471" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E471">
         <v>0.2618490231187316</v>
@@ -25888,7 +25888,7 @@
         <v>4.371485982915774</v>
       </c>
       <c r="D475" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E475">
         <v>4.962528234821984</v>
@@ -25938,7 +25938,7 @@
         <v>5.060047010261989</v>
       </c>
       <c r="D476" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E476">
         <v>4.670741844866129</v>
@@ -26088,7 +26088,7 @@
         <v>3.620560894635664</v>
       </c>
       <c r="D479" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E479">
         <v>4.229589376201279</v>
@@ -26138,7 +26138,7 @@
         <v>4.317639349991246</v>
       </c>
       <c r="D480" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E480">
         <v>3.938374978158294</v>
@@ -26188,7 +26188,7 @@
         <v>4.370574873318176</v>
       </c>
       <c r="D481" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E481">
         <v>3.818139087890952</v>
@@ -26288,7 +26288,7 @@
         <v>6.853299645934258</v>
       </c>
       <c r="D483" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E483">
         <v>5.774682369171286</v>
@@ -26338,7 +26338,7 @@
         <v>6.891491094566248</v>
       </c>
       <c r="D484" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E484">
         <v>5.774682369171286</v>
@@ -26388,7 +26388,7 @@
         <v>5.361224864970907</v>
       </c>
       <c r="D485" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E485">
         <v>5.018618668978591</v>
@@ -26438,7 +26438,7 @@
         <v>5.403937692022923</v>
       </c>
       <c r="D486" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E486">
         <v>5.018618668978591</v>
@@ -26488,7 +26488,7 @@
         <v>5.435905841926575</v>
       </c>
       <c r="D487" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E487">
         <v>5.018618668978591</v>
@@ -26538,7 +26538,7 @@
         <v>6.006575212731824</v>
       </c>
       <c r="D488" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E488">
         <v>5.049928678956259</v>
@@ -26574,7 +26574,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26588,7 +26588,7 @@
         <v>6.064211272564705</v>
       </c>
       <c r="D489" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E489">
         <v>5.049928678956259</v>
@@ -26624,7 +26624,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26638,7 +26638,7 @@
         <v>4.663870399629863</v>
       </c>
       <c r="D490" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E490">
         <v>4.316971023154751</v>
@@ -26674,7 +26674,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26688,7 +26688,7 @@
         <v>4.677416309880542</v>
       </c>
       <c r="D491" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E491">
         <v>4.316971023154751</v>
@@ -26724,7 +26724,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26738,7 +26738,7 @@
         <v>4.678449851055503</v>
       </c>
       <c r="D492" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E492">
         <v>4.316971023154751</v>
@@ -26774,7 +26774,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26788,7 +26788,7 @@
         <v>5.45724271386503</v>
       </c>
       <c r="D493" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E493">
         <v>4.579727583892824</v>
@@ -26838,7 +26838,7 @@
         <v>5.527493925028882</v>
       </c>
       <c r="D494" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E494">
         <v>4.579727583892824</v>
@@ -26888,7 +26888,7 @@
         <v>4.201445199623705</v>
       </c>
       <c r="D495" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E495">
         <v>3.460664324521434</v>
@@ -26938,7 +26938,7 @@
         <v>4.150453975773659</v>
       </c>
       <c r="D496" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E496">
         <v>3.460664324521434</v>
@@ -26988,7 +26988,7 @@
         <v>4.187032365117255</v>
       </c>
       <c r="D497" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E497">
         <v>3.460664324521434</v>
@@ -27038,7 +27038,7 @@
         <v>4.42199553766301</v>
       </c>
       <c r="D498" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E498">
         <v>3.693607871486083</v>
@@ -27088,7 +27088,7 @@
         <v>4.365726240572206</v>
       </c>
       <c r="D499" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E499">
         <v>3.693607871486083</v>
@@ -27138,7 +27138,7 @@
         <v>4.516020692330457</v>
       </c>
       <c r="D500" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E500">
         <v>3.693607871486083</v>
@@ -27188,7 +27188,7 @@
         <v>3.247044122637031</v>
       </c>
       <c r="D501" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E501">
         <v>2.605123035361114</v>
@@ -27238,7 +27238,7 @@
         <v>3.194659905181848</v>
       </c>
       <c r="D502" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E502">
         <v>2.605123035361114</v>
@@ -27288,7 +27288,7 @@
         <v>-3.705984123275019</v>
       </c>
       <c r="D503" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E503">
         <v>-2.970035313701199</v>
@@ -27338,7 +27338,7 @@
         <v>-3.693186241046869</v>
       </c>
       <c r="D504" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E504">
         <v>-2.970035313701199</v>
@@ -27388,7 +27388,7 @@
         <v>-2.752427193387811</v>
       </c>
       <c r="D505" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E505">
         <v>-3.420167707261241</v>
@@ -27438,7 +27438,7 @@
         <v>-2.600361880106711</v>
       </c>
       <c r="D506" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E506">
         <v>-3.420167707261241</v>
@@ -27488,7 +27488,7 @@
         <v>-3.678102393980136</v>
       </c>
       <c r="D507" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E507">
         <v>-3.136716692222066</v>
@@ -27538,7 +27538,7 @@
         <v>-4.366813091974395</v>
       </c>
       <c r="D508" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E508">
         <v>-3.818652183810219</v>
@@ -27588,7 +27588,7 @@
         <v>-4.484310216846968</v>
       </c>
       <c r="D509" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E509">
         <v>-3.818652183810219</v>
@@ -27638,7 +27638,7 @@
         <v>-4.322051603836151</v>
       </c>
       <c r="D510" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E510">
         <v>-3.818652183810219</v>
@@ -27688,7 +27688,7 @@
         <v>-3.347068854600705</v>
       </c>
       <c r="D511" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E511">
         <v>-4.118163659577004</v>
@@ -27738,7 +27738,7 @@
         <v>-3.324798741080183</v>
       </c>
       <c r="D512" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E512">
         <v>-4.118163659577004</v>
@@ -27788,7 +27788,7 @@
         <v>-3.351387820544549</v>
       </c>
       <c r="D513" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E513">
         <v>-4.118163659577004</v>
@@ -27838,7 +27838,7 @@
         <v>-4.379071704985211</v>
       </c>
       <c r="D514" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E514">
         <v>-3.832482625520846</v>
@@ -27888,7 +27888,7 @@
         <v>8.995980915690074</v>
       </c>
       <c r="D515" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E515">
         <v>10.66390789578366</v>
@@ -27938,7 +27938,7 @@
         <v>11.51142958743078</v>
       </c>
       <c r="D516" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E516">
         <v>11.61008037782884</v>
@@ -27988,7 +27988,7 @@
         <v>11.33896292349641</v>
       </c>
       <c r="D517" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E517">
         <v>11.61008037782884</v>
@@ -28038,7 +28038,7 @@
         <v>11.25741689188049</v>
       </c>
       <c r="D518" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E518">
         <v>11.61008037782884</v>
@@ -28088,7 +28088,7 @@
         <v>11.28637455971803</v>
       </c>
       <c r="D519" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E519">
         <v>11.61008037782884</v>
@@ -28138,7 +28138,7 @@
         <v>9.394053857479914</v>
       </c>
       <c r="D520" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E520">
         <v>11.10574062904685</v>
@@ -28188,7 +28188,7 @@
         <v>11.96926052402832</v>
       </c>
       <c r="D521" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E521">
         <v>11.78545564208547</v>
@@ -28238,7 +28238,7 @@
         <v>11.76715013038619</v>
       </c>
       <c r="D522" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E522">
         <v>11.78545564208547</v>
@@ -28288,7 +28288,7 @@
         <v>11.79715013038619</v>
       </c>
       <c r="D523" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E523">
         <v>11.78545564208547</v>
@@ -28338,7 +28338,7 @@
         <v>11.75785102268897</v>
       </c>
       <c r="D524" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E524">
         <v>11.78545564208547</v>
@@ -28388,7 +28388,7 @@
         <v>6.4997071892945</v>
       </c>
       <c r="D525" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E525">
         <v>7.893221100174392</v>
@@ -28588,7 +28588,7 @@
         <v>8.621088353970423</v>
       </c>
       <c r="D529" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E529">
         <v>8.269277714135617</v>
@@ -28638,7 +28638,7 @@
         <v>8.578286988055545</v>
       </c>
       <c r="D530" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E530">
         <v>8.269277714135617</v>
@@ -28688,7 +28688,7 @@
         <v>8.739580302223263</v>
       </c>
       <c r="D531" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E531">
         <v>8.269277714135617</v>
@@ -28738,7 +28738,7 @@
         <v>8.957510999554914</v>
       </c>
       <c r="D532" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E532">
         <v>8.269277714135617</v>
@@ -28988,7 +28988,7 @@
         <v>1.438738012295818</v>
       </c>
       <c r="D537" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E537">
         <v>2.100412073152636</v>
@@ -29038,7 +29038,7 @@
         <v>1.573030977807695</v>
       </c>
       <c r="D538" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E538">
         <v>2.100412073152636</v>
@@ -29088,7 +29088,7 @@
         <v>1.547818547789148</v>
       </c>
       <c r="D539" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E539">
         <v>2.100412073152636</v>
@@ -29238,7 +29238,7 @@
         <v>-0.8761721984660475</v>
       </c>
       <c r="D542" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E542">
         <v>-1.556082773365931</v>
@@ -29288,7 +29288,7 @@
         <v>-1.017858379148869</v>
       </c>
       <c r="D543" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E543">
         <v>-1.556082773365931</v>
@@ -29338,7 +29338,7 @@
         <v>-0.5723250526030199</v>
       </c>
       <c r="D544" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E544">
         <v>-1.556082773365931</v>
@@ -29388,7 +29388,7 @@
         <v>-1.931822609108822</v>
       </c>
       <c r="D545" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E545">
         <v>-1.673095771397564</v>
@@ -29438,7 +29438,7 @@
         <v>-2.066468132763205</v>
       </c>
       <c r="D546" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E546">
         <v>-1.673095771397564</v>
@@ -29488,7 +29488,7 @@
         <v>-1.956055114369123</v>
       </c>
       <c r="D547" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E547">
         <v>-1.673095771397564</v>
@@ -29538,7 +29538,7 @@
         <v>-1.910907147220547</v>
       </c>
       <c r="D548" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E548">
         <v>-1.673095771397564</v>
@@ -29588,7 +29588,7 @@
         <v>-1.911499015814858</v>
       </c>
       <c r="D549" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E549">
         <v>-1.673095771397564</v>
@@ -29638,7 +29638,7 @@
         <v>-2.047060001357517</v>
       </c>
       <c r="D550" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E550">
         <v>-1.673095771397564</v>
@@ -29838,7 +29838,7 @@
         <v>-1.458250204365703</v>
       </c>
       <c r="D554" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E554">
         <v>-2.203959675076526</v>
@@ -29938,7 +29938,7 @@
         <v>-1.426121365901643</v>
       </c>
       <c r="D556" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E556">
         <v>-1.878985527382707</v>
@@ -29988,7 +29988,7 @@
         <v>-1.43657143149991</v>
       </c>
       <c r="D557" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E557">
         <v>-1.878985527382707</v>
@@ -30038,7 +30038,7 @@
         <v>-1.282291566067462</v>
       </c>
       <c r="D558" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E558">
         <v>-1.878985527382707</v>
@@ -30088,7 +30088,7 @@
         <v>-2.390900427299799</v>
       </c>
       <c r="D559" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E559">
         <v>-1.749918412157532</v>
@@ -30138,7 +30138,7 @@
         <v>-1.371342304503491</v>
       </c>
       <c r="D560" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E560">
         <v>-2.176137742690791</v>
@@ -30188,7 +30188,7 @@
         <v>-2.66184968886377</v>
       </c>
       <c r="D561" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E561">
         <v>-3.062340696434903</v>
@@ -30238,7 +30238,7 @@
         <v>-1.173473832043332</v>
       </c>
       <c r="D562" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E562">
         <v>-1.733424630557323</v>
@@ -30288,7 +30288,7 @@
         <v>-1.200137867726374</v>
       </c>
       <c r="D563" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E563">
         <v>-1.733424630557323</v>
@@ -30338,7 +30338,7 @@
         <v>-1.042228008991366</v>
       </c>
       <c r="D564" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E564">
         <v>-1.733424630557323</v>
@@ -30388,7 +30388,7 @@
         <v>-2.127604913087305</v>
       </c>
       <c r="D565" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E565">
         <v>-1.505014864011352</v>
@@ -30438,7 +30438,7 @@
         <v>-1.173621436501358</v>
       </c>
       <c r="D566" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E566">
         <v>-1.913326227585305</v>
@@ -30488,7 +30488,7 @@
         <v>-1.12934275099936</v>
       </c>
       <c r="D567" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E567">
         <v>-1.913326227585305</v>
@@ -30588,7 +30588,7 @@
         <v>-1.009918389553857</v>
       </c>
       <c r="D569" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E569">
         <v>-1.567675915850558</v>
@@ -30638,7 +30638,7 @@
         <v>-1.047078799419653</v>
       </c>
       <c r="D570" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E570">
         <v>-1.567675915850558</v>
@@ -30688,7 +30688,7 @@
         <v>-0.8868190061661174</v>
       </c>
       <c r="D571" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E571">
         <v>-1.567675915850558</v>
@@ -30738,7 +30738,7 @@
         <v>-1.957156329343485</v>
       </c>
       <c r="D572" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E572">
         <v>-1.346472615161401</v>
@@ -30788,7 +30788,7 @@
         <v>-1.016645810663759</v>
       </c>
       <c r="D573" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E573">
         <v>-1.743190968443955</v>
@@ -30838,7 +30838,7 @@
         <v>-0.9726804497642316</v>
       </c>
       <c r="D574" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E574">
         <v>-1.743190968443955</v>
@@ -30888,7 +30888,7 @@
         <v>-2.23129488574537</v>
       </c>
       <c r="D575" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E575">
         <v>-2.752324990932166</v>
@@ -30938,7 +30938,7 @@
         <v>-2.130775299238296</v>
       </c>
       <c r="D576" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E576">
         <v>-2.752324990932166</v>
@@ -30988,7 +30988,7 @@
         <v>-0.896848743456049</v>
       </c>
       <c r="D577" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E577">
         <v>-1.453090010130747</v>
@@ -31038,7 +31038,7 @@
         <v>-0.9412655386557081</v>
       </c>
       <c r="D578" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E578">
         <v>-1.453090010130747</v>
@@ -31088,7 +31088,7 @@
         <v>-0.7793811815214564</v>
       </c>
       <c r="D579" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E579">
         <v>-1.453090010130747</v>
@@ -31138,7 +31138,7 @@
         <v>-1.860567553008542</v>
       </c>
       <c r="D580" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E580">
         <v>-1.236868705342454</v>
@@ -31188,7 +31188,7 @@
         <v>-0.9081249434319556</v>
       </c>
       <c r="D581" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E581">
         <v>-1.625572543480143</v>
@@ -31238,7 +31238,7 @@
         <v>-0.8643761910498551</v>
       </c>
       <c r="D582" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E582">
         <v>-1.625572543480143</v>
@@ -31488,7 +31488,7 @@
         <v>2.369548064861299</v>
       </c>
       <c r="D587" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E587">
         <v>1.926875447544282</v>
@@ -31538,7 +31538,7 @@
         <v>2.406754555749798</v>
       </c>
       <c r="D588" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E588">
         <v>1.926875447544282</v>
@@ -31588,7 +31588,7 @@
         <v>2.636430011324778</v>
       </c>
       <c r="D589" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E589">
         <v>1.926875447544282</v>
@@ -31738,7 +31738,7 @@
         <v>1.522496508679898</v>
       </c>
       <c r="D592" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E592">
         <v>0.6622717696267184</v>
@@ -31788,7 +31788,7 @@
         <v>0.1531498180160149</v>
       </c>
       <c r="D593" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E593">
         <v>0.9108693301133393</v>
@@ -31838,7 +31838,7 @@
         <v>0.1409442431310648</v>
       </c>
       <c r="D594" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E594">
         <v>0.9108693301133393</v>
@@ -31888,7 +31888,7 @@
         <v>0.1454303059186906</v>
       </c>
       <c r="D595" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E595">
         <v>0.9108693301133393</v>
@@ -31938,7 +31938,7 @@
         <v>1.410955900715591</v>
       </c>
       <c r="D596" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E596">
         <v>0.5447199911733147</v>
@@ -31988,7 +31988,7 @@
         <v>0.02936423312947767</v>
       </c>
       <c r="D597" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E597">
         <v>0.7855252936185178</v>
@@ -32038,7 +32038,7 @@
         <v>0.01760393013260675</v>
       </c>
       <c r="D598" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E598">
         <v>0.7855252936185178</v>
@@ -32088,7 +32088,7 @@
         <v>0.02320317264043581</v>
       </c>
       <c r="D599" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E599">
         <v>0.7855252936185178</v>
@@ -32138,7 +32138,7 @@
         <v>1.411909103777088</v>
       </c>
       <c r="D600" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E600">
         <v>0.545724564459686</v>
@@ -32188,7 +32188,7 @@
         <v>0.03042207924163876</v>
       </c>
       <c r="D601" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E601">
         <v>0.7865964579371276</v>
@@ -32238,7 +32238,7 @@
         <v>0.0186579710429271</v>
       </c>
       <c r="D602" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E602">
         <v>0.7865964579371276</v>
@@ -32288,7 +32288,7 @@
         <v>0.02424770054614989</v>
       </c>
       <c r="D603" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E603">
         <v>0.7865964579371276</v>
@@ -32338,7 +32338,7 @@
         <v>1.336834708204746</v>
       </c>
       <c r="D604" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E604">
         <v>0.4666042433774571</v>
@@ -32388,7 +32388,7 @@
         <v>-0.05289401644343528</v>
       </c>
       <c r="D605" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E605">
         <v>0.7022314186013414</v>
@@ -32438,7 +32438,7 @@
         <v>-0.06435842645623069</v>
       </c>
       <c r="D606" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E606">
         <v>0.7022314186013414</v>
@@ -32488,7 +32488,7 @@
         <v>-0.05801945148821375</v>
       </c>
       <c r="D607" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E607">
         <v>0.7022314186013414</v>
@@ -32538,7 +32538,7 @@
         <v>1.405196855980458</v>
       </c>
       <c r="D608" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E608">
         <v>0.5386505787578475</v>
@@ -32588,7 +32588,7 @@
         <v>0.02297295793440135</v>
       </c>
       <c r="D609" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E609">
         <v>0.7790535527285396</v>
@@ -32638,7 +32638,7 @@
         <v>0.01123564513607533</v>
       </c>
       <c r="D610" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E610">
         <v>0.7790535527285396</v>
@@ -32688,7 +32688,7 @@
         <v>0.01689236314026132</v>
       </c>
       <c r="D611" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E611">
         <v>0.7790535527285396</v>
@@ -32738,7 +32738,7 @@
         <v>1.640062494593103</v>
       </c>
       <c r="D612" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E612">
         <v>0.786173646996323</v>
@@ -32788,7 +32788,7 @@
         <v>0.2836222494885536</v>
       </c>
       <c r="D613" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E613">
         <v>0.8556593002896253</v>
@@ -32838,7 +32838,7 @@
         <v>0.2709473493105357</v>
       </c>
       <c r="D614" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E614">
         <v>0.8556593002896253</v>
@@ -32888,7 +32888,7 @@
         <v>0.2742600988654935</v>
       </c>
       <c r="D615" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E615">
         <v>0.8556593002896253</v>
@@ -32938,7 +32938,7 @@
         <v>4.955952265919407</v>
       </c>
       <c r="D616" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E616">
         <v>3.781714175282632</v>
@@ -32988,7 +32988,7 @@
         <v>4.836984732824422</v>
       </c>
       <c r="D617" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E617">
         <v>3.781714175282632</v>
@@ -33038,7 +33038,7 @@
         <v>3.399157889651168</v>
       </c>
       <c r="D618" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E618">
         <v>4.104212001159528</v>
@@ -33088,7 +33088,7 @@
         <v>3.413995555126094</v>
       </c>
       <c r="D619" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E619">
         <v>4.104212001159528</v>
@@ -33138,7 +33138,7 @@
         <v>3.388941443617735</v>
       </c>
       <c r="D620" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E620">
         <v>4.104212001159528</v>
@@ -33238,7 +33238,7 @@
         <v>5.39157323691697</v>
       </c>
       <c r="D622" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E622">
         <v>4.199910307440291</v>
@@ -33288,7 +33288,7 @@
         <v>5.274981818209244</v>
       </c>
       <c r="D623" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E623">
         <v>4.199910307440291</v>
@@ -33338,7 +33338,7 @@
         <v>3.849827585101373</v>
       </c>
       <c r="D624" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E624">
         <v>4.558841887255165</v>
@@ -33388,7 +33388,7 @@
         <v>3.716953213901664</v>
       </c>
       <c r="D625" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E625">
         <v>4.558841887255165</v>
@@ -33438,7 +33438,7 @@
         <v>3.823770376486211</v>
       </c>
       <c r="D626" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E626">
         <v>4.558841887255165</v>
@@ -33488,7 +33488,7 @@
         <v>3.783996120363035</v>
       </c>
       <c r="D627" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E627">
         <v>4.558841887255165</v>
@@ -33538,7 +33538,7 @@
         <v>5.240670261409678</v>
       </c>
       <c r="D628" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E628">
         <v>5.66120447150224</v>
@@ -33588,7 +33588,7 @@
         <v>13.35754674285762</v>
       </c>
       <c r="D629" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E629">
         <v>12.11200719763176</v>
@@ -33638,7 +33638,7 @@
         <v>13.63116000592201</v>
       </c>
       <c r="D630" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E630">
         <v>12.11200719763176</v>
@@ -33688,7 +33688,7 @@
         <v>13.48645284737274</v>
       </c>
       <c r="D631" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E631">
         <v>12.11200719763176</v>
@@ -33738,7 +33738,7 @@
         <v>13.35488379452298</v>
       </c>
       <c r="D632" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E632">
         <v>12.11200719763176</v>
@@ -33938,7 +33938,7 @@
         <v>12.00063570730863</v>
       </c>
       <c r="D636" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E636">
         <v>10.96336131546034</v>
@@ -33988,7 +33988,7 @@
         <v>12.16808033477629</v>
       </c>
       <c r="D637" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E637">
         <v>10.96336131546034</v>
@@ -34038,7 +34038,7 @@
         <v>12.18508198198523</v>
       </c>
       <c r="D638" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E638">
         <v>10.96336131546034</v>
@@ -34088,7 +34088,7 @@
         <v>11.93759839099766</v>
       </c>
       <c r="D639" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E639">
         <v>10.96336131546034</v>
@@ -34138,7 +34138,7 @@
         <v>12.10741586438821</v>
       </c>
       <c r="D640" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E640">
         <v>10.96336131546034</v>
@@ -34188,7 +34188,7 @@
         <v>9.996138178122038</v>
       </c>
       <c r="D641" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E641">
         <v>10.07070134335836</v>
@@ -34238,7 +34238,7 @@
         <v>9.950336290139454</v>
       </c>
       <c r="D642" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E642">
         <v>10.07070134335836</v>
@@ -34288,7 +34288,7 @@
         <v>3.726163694975139</v>
       </c>
       <c r="D643" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E643">
         <v>2.839609794743838</v>
@@ -34324,7 +34324,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -34338,7 +34338,7 @@
         <v>2.070333381900306</v>
       </c>
       <c r="D644" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E644">
         <v>2.539922141074908</v>
@@ -34374,7 +34374,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -34388,7 +34388,7 @@
         <v>2.116517657129328</v>
       </c>
       <c r="D645" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E645">
         <v>2.539922141074908</v>
@@ -34424,7 +34424,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -34438,7 +34438,7 @@
         <v>2.11502886699328</v>
       </c>
       <c r="D646" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E646">
         <v>2.539922141074908</v>
@@ -34474,7 +34474,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -34488,7 +34488,7 @@
         <v>-1.891199427015522</v>
       </c>
       <c r="D647" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E647">
         <v>-1.014426804305828</v>
@@ -34538,7 +34538,7 @@
         <v>-0.2104376111309492</v>
       </c>
       <c r="D648" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E648">
         <v>-1.044462827056231</v>
@@ -34588,7 +34588,7 @@
         <v>-0.08646642933127069</v>
       </c>
       <c r="D649" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E649">
         <v>-1.044462827056231</v>
@@ -34638,7 +34638,7 @@
         <v>-1.78244121340599</v>
       </c>
       <c r="D650" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E650">
         <v>-1.021661386146215</v>
@@ -34688,7 +34688,7 @@
         <v>-1.791643374771013</v>
       </c>
       <c r="D651" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E651">
         <v>-1.021661386146215</v>
@@ -34788,7 +34788,7 @@
         <v>-3.477913686861863</v>
       </c>
       <c r="D653" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E653">
         <v>-4.521174267980019</v>
@@ -34838,7 +34838,7 @@
         <v>-3.500008845709822</v>
       </c>
       <c r="D654" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E654">
         <v>-4.521174267980019</v>
@@ -34888,7 +34888,7 @@
         <v>-5.32431700625196</v>
       </c>
       <c r="D655" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E655">
         <v>-4.437952967810602</v>
@@ -35088,7 +35088,7 @@
         <v>-7.577993318403742</v>
       </c>
       <c r="D659" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E659">
         <v>-6.567354813971781</v>
@@ -35138,7 +35138,7 @@
         <v>-7.616049006530655</v>
       </c>
       <c r="D660" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E660">
         <v>-6.567354813971781</v>
@@ -35188,7 +35188,7 @@
         <v>-2.725135055328662</v>
       </c>
       <c r="D661" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E661">
         <v>-2.204192425359905</v>
@@ -35238,7 +35238,7 @@
         <v>-2.704148294566643</v>
       </c>
       <c r="D662" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E662">
         <v>-2.204192425359905</v>
@@ -35288,7 +35288,7 @@
         <v>-1.813662855840759</v>
       </c>
       <c r="D663" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E663">
         <v>-2.111011489107529</v>
@@ -35338,7 +35338,7 @@
         <v>-1.845002662948879</v>
       </c>
       <c r="D664" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E664">
         <v>-2.111011489107529</v>
@@ -35388,7 +35388,7 @@
         <v>-1.891998249869552</v>
       </c>
       <c r="D665" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E665">
         <v>-2.111011489107529</v>
@@ -35438,7 +35438,7 @@
         <v>1.830334637155163</v>
       </c>
       <c r="D666" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E666">
         <v>2.267871354156875</v>
@@ -35538,7 +35538,7 @@
         <v>1.518226736005792</v>
       </c>
       <c r="D668" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E668">
         <v>1.938055203296901</v>
@@ -35588,7 +35588,7 @@
         <v>1.532693205245188</v>
       </c>
       <c r="D669" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E669">
         <v>1.906531480554312</v>
@@ -35638,7 +35638,7 @@
         <v>2.271617246908757</v>
       </c>
       <c r="D670" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E670">
         <v>2.443417201348617</v>
@@ -35688,7 +35688,7 @@
         <v>1.121481137909713</v>
       </c>
       <c r="D671" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E671">
         <v>1.518799216656364</v>
@@ -35738,7 +35738,7 @@
         <v>1.1435965093108</v>
       </c>
       <c r="D672" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E672">
         <v>1.506034151034157</v>
@@ -35788,7 +35788,7 @@
         <v>1.093271662200239</v>
       </c>
       <c r="D673" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E673">
         <v>1.506034151034157</v>
@@ -35838,7 +35838,7 @@
         <v>1.88237511166083</v>
       </c>
       <c r="D674" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E674">
         <v>1.894895897753045</v>
@@ -35888,7 +35888,7 @@
         <v>0.849444604521004</v>
       </c>
       <c r="D675" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E675">
         <v>1.303653302247787</v>
@@ -35938,7 +35938,7 @@
         <v>0.8477648181552304</v>
       </c>
       <c r="D676" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E676">
         <v>1.303653302247787</v>
@@ -35988,7 +35988,7 @@
         <v>0.7919735158820114</v>
       </c>
       <c r="D677" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E677">
         <v>1.303653302247787</v>
@@ -36088,7 +36088,7 @@
         <v>0.4742545585727438</v>
       </c>
       <c r="D679" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E679">
         <v>0.9209239764164039</v>
@@ -36138,7 +36138,7 @@
         <v>0.4776016477910456</v>
       </c>
       <c r="D680" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E680">
         <v>0.9209239764164039</v>
@@ -36188,7 +36188,7 @@
         <v>0.4397567303627969</v>
       </c>
       <c r="D681" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E681">
         <v>0.9209239764164039</v>
@@ -36238,7 +36238,7 @@
         <v>0.3764261482064555</v>
       </c>
       <c r="D682" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E682">
         <v>0.9209239764164039</v>
@@ -36288,7 +36288,7 @@
         <v>1.247389224131652</v>
       </c>
       <c r="D683" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E683">
         <v>1.332491309195859</v>
@@ -36338,7 +36338,7 @@
         <v>0.06936123169383812</v>
       </c>
       <c r="D684" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E684">
         <v>0.5078944952148738</v>
@@ -36388,7 +36388,7 @@
         <v>0.03202754929901275</v>
       </c>
       <c r="D685" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E685">
         <v>0.5078944952148738</v>
@@ -36438,7 +36438,7 @@
         <v>0.06067852147795705</v>
       </c>
       <c r="D686" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E686">
         <v>0.5078944952148738</v>
@@ -36488,7 +36488,7 @@
         <v>-0.07201953416415208</v>
       </c>
       <c r="D687" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E687">
         <v>0.5078944952148738</v>
@@ -36538,7 +36538,7 @@
         <v>0.07833359180957977</v>
       </c>
       <c r="D688" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E688">
         <v>0.4747573429780569</v>
@@ -36588,7 +36588,7 @@
         <v>0.07349428577797745</v>
       </c>
       <c r="D689" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E689">
         <v>0.4747573429780569</v>
@@ -36638,7 +36638,7 @@
         <v>0.8501534542622782</v>
       </c>
       <c r="D690" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E690">
         <v>0.8793612316938386</v>
@@ -36688,7 +36688,7 @@
         <v>1.041941578678037</v>
       </c>
       <c r="D691" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E691">
         <v>0.8793612316938386</v>
@@ -36738,7 +36738,7 @@
         <v>0.09878287093698646</v>
       </c>
       <c r="D692" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E692">
         <v>0.5379073494309932</v>
@@ -36788,7 +36788,7 @@
         <v>0.06440526340701602</v>
       </c>
       <c r="D693" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E693">
         <v>0.5379073494309932</v>
@@ -36838,7 +36838,7 @@
         <v>0.09312579028866175</v>
       </c>
       <c r="D694" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E694">
         <v>0.5379073494309932</v>
@@ -36888,7 +36888,7 @@
         <v>-0.03943315594804098</v>
       </c>
       <c r="D695" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E695">
         <v>0.5379073494309932</v>
@@ -36938,7 +36938,7 @@
         <v>0.109354989214884</v>
       </c>
       <c r="D696" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E696">
         <v>0.503900763410396</v>
@@ -36988,7 +36988,7 @@
         <v>0.1052807849130097</v>
       </c>
       <c r="D697" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E697">
         <v>0.503900763410396</v>
@@ -37138,7 +37138,7 @@
         <v>0.2871962372863237</v>
       </c>
       <c r="D700" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E700">
         <v>0.9851462492612573</v>
@@ -37188,7 +37188,7 @@
         <v>0.4202978053995725</v>
       </c>
       <c r="D701" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E701">
         <v>0.9851462492612573</v>
@@ -37238,7 +37238,7 @@
         <v>0.423892594321984</v>
       </c>
       <c r="D702" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E702">
         <v>0.9851462492612573</v>
@@ -37288,7 +37288,7 @@
         <v>0.4949561407287284</v>
       </c>
       <c r="D703" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E703">
         <v>0.9851462492612573</v>
@@ -37338,7 +37338,7 @@
         <v>0.4370951998607797</v>
       </c>
       <c r="D704" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E704">
         <v>0.9851462492612573</v>
@@ -37388,7 +37388,7 @@
         <v>0.4441837402800548</v>
       </c>
       <c r="D705" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E705">
         <v>0.9851462492612573</v>
@@ -37438,7 +37438,7 @@
         <v>1.300386876506556</v>
       </c>
       <c r="D706" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E706">
         <v>1.066703016477163</v>
@@ -37488,7 +37488,7 @@
         <v>1.387766562883906</v>
       </c>
       <c r="D707" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E707">
         <v>1.066703016477163</v>
@@ -37538,7 +37538,7 @@
         <v>1.3704879139321</v>
       </c>
       <c r="D708" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E708">
         <v>1.066703016477163</v>
@@ -37588,7 +37588,7 @@
         <v>1.275437395219328</v>
       </c>
       <c r="D709" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E709">
         <v>1.066703016477163</v>
@@ -37638,7 +37638,7 @@
         <v>1.361652497764391</v>
       </c>
       <c r="D710" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E710">
         <v>1.066703016477163</v>
@@ -37688,7 +37688,7 @@
         <v>1.930987869234452</v>
       </c>
       <c r="D711" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E711">
         <v>2.371871770269339</v>
@@ -37738,7 +37738,7 @@
         <v>1.92605256665067</v>
       </c>
       <c r="D712" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E712">
         <v>2.371871770269339</v>
@@ -37788,7 +37788,7 @@
         <v>1.931979302309637</v>
       </c>
       <c r="D713" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E713">
         <v>2.371871770269339</v>
@@ -38038,7 +38038,7 @@
         <v>1.929178123500783</v>
       </c>
       <c r="D718" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E718">
         <v>1.904587279830026</v>
@@ -38088,7 +38088,7 @@
         <v>1.854846069494888</v>
       </c>
       <c r="D719" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E719">
         <v>1.904587279830026</v>
@@ -38138,7 +38138,7 @@
         <v>1.986094439213979</v>
       </c>
       <c r="D720" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E720">
         <v>2.427791166532621</v>
@@ -38388,7 +38388,7 @@
         <v>1.979578720846286</v>
       </c>
       <c r="D725" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E725">
         <v>1.826397195864058</v>
@@ -38438,7 +38438,7 @@
         <v>1.907972820522667</v>
       </c>
       <c r="D726" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E726">
         <v>1.826397195864058</v>
@@ -38688,7 +38688,7 @@
         <v>2.097186801510141</v>
       </c>
       <c r="D731" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E731">
         <v>2.32091239377587</v>
@@ -38738,7 +38738,7 @@
         <v>2.031942288135359</v>
       </c>
       <c r="D732" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E732">
         <v>2.32091239377587</v>
@@ -39288,7 +39288,7 @@
         <v>2.417703574220445</v>
       </c>
       <c r="D743" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E743">
         <v>2.366004733779205</v>
@@ -39338,7 +39338,7 @@
         <v>2.369795720055587</v>
       </c>
       <c r="D744" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E744">
         <v>2.366004733779205</v>
@@ -39388,7 +39388,7 @@
         <v>2.268006981238599</v>
       </c>
       <c r="D745" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E745">
         <v>2.366004733779205</v>
@@ -39638,7 +39638,7 @@
         <v>2.653994288166441</v>
       </c>
       <c r="D750" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E750">
         <v>3.270325396942835</v>
@@ -39688,7 +39688,7 @@
         <v>3.683411667997373</v>
       </c>
       <c r="D751" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E751">
         <v>3.25827796154194</v>
@@ -39738,7 +39738,7 @@
         <v>3.70572139342618</v>
       </c>
       <c r="D752" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E752">
         <v>3.25827796154194</v>
@@ -39788,7 +39788,7 @@
         <v>3.758092829526726</v>
       </c>
       <c r="D753" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E753">
         <v>3.25827796154194</v>
@@ -39838,7 +39838,7 @@
         <v>3.738113399750641</v>
       </c>
       <c r="D754" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E754">
         <v>3.25827796154194</v>
@@ -39888,7 +39888,7 @@
         <v>2.866153368128345</v>
       </c>
       <c r="D755" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E755">
         <v>3.327619714376737</v>
@@ -39938,7 +39938,7 @@
         <v>2.707907697511514</v>
       </c>
       <c r="D756" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E756">
         <v>3.327619714376737</v>
@@ -39988,7 +39988,7 @@
         <v>3.773013759826179</v>
       </c>
       <c r="D757" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E757">
         <v>3.350810436248167</v>
@@ -40038,7 +40038,7 @@
         <v>3.799493645503623</v>
       </c>
       <c r="D758" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E758">
         <v>3.350810436248167</v>
@@ -40088,7 +40088,7 @@
         <v>3.854682757447843</v>
       </c>
       <c r="D759" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E759">
         <v>3.350810436248167</v>
@@ -40138,7 +40138,7 @@
         <v>3.834252499536769</v>
       </c>
       <c r="D760" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E760">
         <v>3.350810436248167</v>
@@ -40188,7 +40188,7 @@
         <v>2.950458229371047</v>
       </c>
       <c r="D761" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E761">
         <v>3.434578689402571</v>
@@ -40238,7 +40238,7 @@
         <v>2.80855507864752</v>
       </c>
       <c r="D762" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E762">
         <v>3.434578689402571</v>
@@ -40288,7 +40288,7 @@
         <v>4.059126950443869</v>
       </c>
       <c r="D763" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E763">
         <v>3.646280787816876</v>
@@ -40338,7 +40338,7 @@
         <v>4.098922795936224</v>
       </c>
       <c r="D764" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E764">
         <v>3.646280787816876</v>
@@ -40388,7 +40388,7 @@
         <v>4.163109178025654</v>
       </c>
       <c r="D765" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E765">
         <v>3.646280787816876</v>
@@ -40438,7 +40438,7 @@
         <v>4.141239356891347</v>
       </c>
       <c r="D766" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E766">
         <v>3.646280787816876</v>
@@ -40488,7 +40488,7 @@
         <v>3.219656552115741</v>
       </c>
       <c r="D767" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E767">
         <v>3.776115064114756</v>
@@ -40538,7 +40538,7 @@
         <v>3.129937568234435</v>
       </c>
       <c r="D768" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E768">
         <v>3.776115064114756</v>
@@ -40588,7 +40588,7 @@
         <v>4.587925539948646</v>
       </c>
       <c r="D769" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E769">
         <v>4.161392287167092</v>
@@ -40638,7 +40638,7 @@
         <v>4.61478704123244</v>
       </c>
       <c r="D770" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E770">
         <v>4.161392287167092</v>
@@ -40688,7 +40688,7 @@
         <v>4.62093591099028</v>
       </c>
       <c r="D771" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E771">
         <v>4.161392287167092</v>
@@ -40738,7 +40738,7 @@
         <v>4.700807783315709</v>
       </c>
       <c r="D772" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E772">
         <v>4.161392287167092</v>
@@ -40788,7 +40788,7 @@
         <v>4.676428283743642</v>
       </c>
       <c r="D773" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E773">
         <v>4.161392287167092</v>
@@ -40838,7 +40838,7 @@
         <v>3.68896641997684</v>
       </c>
       <c r="D774" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E774">
         <v>4.371536273473288</v>
@@ -40888,7 +40888,7 @@
         <v>3.690223279464329</v>
       </c>
       <c r="D775" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E775">
         <v>4.371536273473288</v>
@@ -40938,7 +40938,7 @@
         <v>4.640951769621907</v>
       </c>
       <c r="D776" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E776">
         <v>4.4619926496501</v>
@@ -40988,7 +40988,7 @@
         <v>4.679892441845094</v>
       </c>
       <c r="D777" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E777">
         <v>4.229657336851623</v>
@@ -41038,7 +41038,7 @@
         <v>4.69011559593246</v>
       </c>
       <c r="D778" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E778">
         <v>4.229657336851623</v>
@@ -41088,7 +41088,7 @@
         <v>4.772066184752546</v>
       </c>
       <c r="D779" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E779">
         <v>4.229657336851623</v>
@@ -41138,7 +41138,7 @@
         <v>4.747354090541334</v>
       </c>
       <c r="D780" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E780">
         <v>4.229657336851623</v>
@@ -41188,7 +41188,7 @@
         <v>3.751161617496972</v>
       </c>
       <c r="D781" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E781">
         <v>4.450444351610463</v>
@@ -41238,7 +41238,7 @@
         <v>3.764475032653471</v>
       </c>
       <c r="D782" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E782">
         <v>4.450444351610463</v>
@@ -41288,7 +41288,7 @@
         <v>4.722853199511387</v>
       </c>
       <c r="D783" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E783">
         <v>4.494475032653471</v>
@@ -41338,7 +41338,7 @@
         <v>4.769412494689534</v>
       </c>
       <c r="D784" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E784">
         <v>4.258529056637524</v>
@@ -41388,7 +41388,7 @@
         <v>4.719374147530353</v>
       </c>
       <c r="D785" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E785">
         <v>4.258529056637524</v>
@@ -41438,7 +41438,7 @@
         <v>4.802203899559511</v>
       </c>
       <c r="D786" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E786">
         <v>4.258529056637524</v>
@@ -41488,7 +41488,7 @@
         <v>4.777351139234847</v>
       </c>
       <c r="D787" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E787">
         <v>4.258529056637524</v>
@@ -41538,7 +41538,7 @@
         <v>3.777466180712386</v>
       </c>
       <c r="D788" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E788">
         <v>4.483817387026809</v>
@@ -41588,7 +41588,7 @@
         <v>3.795878742481499</v>
       </c>
       <c r="D789" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E789">
         <v>4.483817387026809</v>
@@ -41688,7 +41688,7 @@
         <v>4.79820132156508</v>
       </c>
       <c r="D791" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E791">
         <v>4.288184799253363</v>
@@ -41738,7 +41738,7 @@
         <v>4.833160015785789</v>
       </c>
       <c r="D792" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E792">
         <v>4.288184799253363</v>
@@ -41788,7 +41788,7 @@
         <v>4.80816276950441</v>
       </c>
       <c r="D793" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E793">
         <v>4.288184799253363</v>
@@ -41838,7 +41838,7 @@
         <v>3.804485054618168</v>
       </c>
       <c r="D794" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E794">
         <v>4.518096680257542</v>
@@ -41888,7 +41888,7 @@
         <v>3.828135232318215</v>
       </c>
       <c r="D795" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E795">
         <v>4.518096680257542</v>
@@ -41938,7 +41938,7 @@
         <v>4.793071896789968</v>
       </c>
       <c r="D796" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E796">
         <v>4.976887297607179</v>
@@ -41988,7 +41988,7 @@
         <v>4.969372152154773</v>
       </c>
       <c r="D797" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E797">
         <v>4.976887297607179</v>
@@ -42038,7 +42038,7 @@
         <v>4.88512898189049</v>
       </c>
       <c r="D798" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E798">
         <v>4.377730105560969</v>
@@ -42088,7 +42088,7 @@
         <v>4.926631791066686</v>
       </c>
       <c r="D799" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E799">
         <v>4.377730105560969</v>
@@ -42138,7 +42138,7 @@
         <v>4.901198270454942</v>
       </c>
       <c r="D800" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E800">
         <v>4.377730105560969</v>
@@ -42188,7 +42188,7 @@
         <v>3.886068354396595</v>
       </c>
       <c r="D801" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E801">
         <v>4.621602765136856</v>
@@ -42238,7 +42238,7 @@
         <v>3.925533476572406</v>
       </c>
       <c r="D802" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E802">
         <v>4.621602765136856</v>
@@ -42288,7 +42288,7 @@
         <v>4.900504450642575</v>
       </c>
       <c r="D803" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E803">
         <v>5.323640452137244</v>
@@ -42338,7 +42338,7 @@
         <v>5.068842699478202</v>
       </c>
       <c r="D804" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E804">
         <v>5.323640452137244</v>
@@ -42388,7 +42388,7 @@
         <v>4.666640897343765</v>
       </c>
       <c r="D805" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E805">
         <v>4.152662706046714</v>
@@ -42438,7 +42438,7 @@
         <v>4.691695419101137</v>
       </c>
       <c r="D806" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E806">
         <v>4.152662706046714</v>
@@ -42488,7 +42488,7 @@
         <v>4.667358450983981</v>
       </c>
       <c r="D807" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E807">
         <v>4.152662706046714</v>
@@ -42538,7 +42538,7 @@
         <v>3.681013037908578</v>
       </c>
       <c r="D808" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E808">
         <v>4.361445685795776</v>
@@ -42588,7 +42588,7 @@
         <v>3.680728132155562</v>
       </c>
       <c r="D809" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E809">
         <v>4.361445685795776</v>
@@ -42638,7 +42638,7 @@
         <v>4.715209316235119</v>
       </c>
       <c r="D810" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E810">
         <v>5.110369355335455</v>
@@ -42688,7 +42688,7 @@
         <v>4.818828730712063</v>
       </c>
       <c r="D811" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E811">
         <v>5.110369355335455</v>
@@ -42738,7 +42738,7 @@
         <v>4.677780979452113</v>
       </c>
       <c r="D812" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E812">
         <v>4.139332770280262</v>
@@ -42774,7 +42774,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42788,7 +42788,7 @@
         <v>4.685525171192977</v>
       </c>
       <c r="D813" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E813">
         <v>4.139332770280262</v>
@@ -42824,7 +42824,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42838,7 +42838,7 @@
         <v>3.668868346126232</v>
       </c>
       <c r="D814" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E814">
         <v>4.346037514002399</v>
@@ -42874,7 +42874,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42888,7 +42888,7 @@
         <v>3.666229188623965</v>
       </c>
       <c r="D815" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E815">
         <v>4.346037514002399</v>
@@ -42924,7 +42924,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42938,7 +42938,7 @@
         <v>4.699557601157337</v>
       </c>
       <c r="D816" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E816">
         <v>5.177220717987302</v>
@@ -42974,7 +42974,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -42988,7 +42988,7 @@
         <v>4.80402129902022</v>
       </c>
       <c r="D817" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E817">
         <v>5.177220717987302</v>
@@ -43024,7 +43024,7 @@
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -43038,7 +43038,7 @@
         <v>3.803770388208568</v>
       </c>
       <c r="D818" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E818">
         <v>4.517189971136271</v>
@@ -43074,7 +43074,7 @@
         <v>1</v>
       </c>
       <c r="P818" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="819" spans="1:16">
@@ -43088,7 +43088,7 @@
         <v>3.827282027634027</v>
       </c>
       <c r="D819" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E819">
         <v>4.517189971136271</v>
@@ -43124,7 +43124,7 @@
         <v>1</v>
       </c>
       <c r="P819" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="820" spans="1:16">
@@ -43138,7 +43138,7 @@
         <v>4.873415313145802</v>
       </c>
       <c r="D820" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E820">
         <v>5.19492340011272</v>
@@ -43174,7 +43174,7 @@
         <v>1</v>
       </c>
       <c r="P820" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="821" spans="1:16">
@@ -43188,7 +43188,7 @@
         <v>4.968500794179431</v>
       </c>
       <c r="D821" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E821">
         <v>5.19492340011272</v>
@@ -43224,7 +43224,7 @@
         <v>1</v>
       </c>
       <c r="P821" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="822" spans="1:16">
@@ -43238,7 +43238,7 @@
         <v>4.15270680227816</v>
       </c>
       <c r="D822" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E822">
         <v>4.95989138417376</v>
@@ -43288,7 +43288,7 @@
         <v>4.243859858869514</v>
       </c>
       <c r="D823" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E823">
         <v>4.95989138417376</v>
@@ -43338,7 +43338,7 @@
         <v>5.32311411416597</v>
       </c>
       <c r="D824" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E824">
         <v>5.313449235585522</v>
@@ -43388,7 +43388,7 @@
         <v>5.393941983526312</v>
       </c>
       <c r="D825" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E825">
         <v>5.313449235585522</v>
@@ -43438,7 +43438,7 @@
         <v>4.427422884586818</v>
       </c>
       <c r="D826" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E826">
         <v>5.308428231915627</v>
@@ -43488,7 +43488,7 @@
         <v>4.571829727187204</v>
       </c>
       <c r="D827" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E827">
         <v>5.308428231915627</v>
@@ -43638,7 +43638,7 @@
         <v>4.492909746290213</v>
       </c>
       <c r="D830" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E830">
         <v>5.391512498969801</v>
@@ -43688,7 +43688,7 @@
         <v>4.650011234541658</v>
       </c>
       <c r="D831" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E831">
         <v>5.391512498969801</v>
@@ -43738,7 +43738,7 @@
         <v>5.699620454673608</v>
       </c>
       <c r="D832" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E832">
         <v>5.584366029175103</v>
@@ -43788,7 +43788,7 @@
         <v>5.808734877829779</v>
       </c>
       <c r="D833" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E833">
         <v>5.584366029175103</v>
@@ -43838,7 +43838,7 @@
         <v>4.400292583551392</v>
       </c>
       <c r="D834" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E834">
         <v>5.274007569238329</v>
@@ -43888,7 +43888,7 @@
         <v>4.539440210041969</v>
       </c>
       <c r="D835" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E835">
         <v>5.274007569238329</v>
@@ -43938,7 +43938,7 @@
         <v>5.577658014435989</v>
       </c>
       <c r="D836" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E836">
         <v>5.419384274951261</v>
@@ -43988,7 +43988,7 @@
         <v>5.695811278340734</v>
       </c>
       <c r="D837" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E837">
         <v>5.419384274951261</v>
@@ -44038,7 +44038,7 @@
         <v>4.244834847003374</v>
       </c>
       <c r="D838" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E838">
         <v>5.076775761772995</v>
@@ -44088,7 +44088,7 @@
         <v>4.353846949697878</v>
       </c>
       <c r="D839" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E839">
         <v>5.076775761772995</v>
@@ -44138,7 +44138,7 @@
         <v>5.441845979293118</v>
       </c>
       <c r="D840" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E840">
         <v>5.241229035520813</v>
@@ -44188,7 +44188,7 @@
         <v>5.506269225223365</v>
       </c>
       <c r="D841" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E841">
         <v>5.241229035520813</v>
@@ -44238,7 +44238,7 @@
         <v>4.273702172751312</v>
       </c>
       <c r="D842" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E842">
         <v>5.113400216498656</v>
@@ -44288,7 +44288,7 @@
         <v>4.38831021426059</v>
       </c>
       <c r="D843" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E843">
         <v>5.113400216498656</v>
@@ -44338,7 +44338,7 @@
         <v>5.479049324240996</v>
       </c>
       <c r="D844" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E844">
         <v>5.245636638515749</v>
@@ -44388,7 +44388,7 @@
         <v>5.54146575073422</v>
       </c>
       <c r="D845" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E845">
         <v>5.245636638515749</v>
@@ -44438,7 +44438,7 @@
         <v>5.560572351202844</v>
       </c>
       <c r="D846" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E846">
         <v>5.245636638515749</v>
@@ -44488,7 +44488,7 @@
         <v>4.347094984058314</v>
       </c>
       <c r="D847" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E847">
         <v>5.206514892876123</v>
@@ -44538,7 +44538,7 @@
         <v>4.475930241663201</v>
       </c>
       <c r="D848" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E848">
         <v>5.206514892876123</v>
@@ -44588,7 +44588,7 @@
         <v>5.573635781593871</v>
       </c>
       <c r="D849" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E849">
         <v>5.027134568809939</v>
@@ -44638,7 +44638,7 @@
         <v>5.630950034039015</v>
       </c>
       <c r="D850" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E850">
         <v>5.027134568809939</v>
@@ -44688,7 +44688,7 @@
         <v>5.633670806314765</v>
       </c>
       <c r="D851" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E851">
         <v>5.027134568809939</v>
@@ -44738,7 +44738,7 @@
         <v>5.402224156621893</v>
       </c>
       <c r="D852" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E852">
         <v>5.844101410902759</v>
@@ -44788,7 +44788,7 @@
         <v>5.365845252056308</v>
       </c>
       <c r="D853" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E853">
         <v>5.844101410902759</v>
@@ -44838,7 +44838,7 @@
         <v>5.351830183888868</v>
       </c>
       <c r="D854" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E854">
         <v>5.844101410902759</v>
@@ -44888,7 +44888,7 @@
         <v>6.177027170255381</v>
       </c>
       <c r="D855" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E855">
         <v>5.99166223366742</v>
@@ -44938,7 +44938,7 @@
         <v>6.176389906463717</v>
       </c>
       <c r="D856" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E856">
         <v>5.99166223366742</v>
@@ -44988,7 +44988,7 @@
         <v>6.145283329101833</v>
       </c>
       <c r="D857" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E857">
         <v>5.99166223366742</v>
@@ -45038,7 +45038,7 @@
         <v>6.120874288201371</v>
       </c>
       <c r="D858" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E858">
         <v>5.99166223366742</v>
@@ -45088,7 +45088,7 @@
         <v>5.357680894209214</v>
       </c>
       <c r="D859" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E859">
         <v>5.805234021262887</v>
@@ -45138,7 +45138,7 @@
         <v>5.321733849528515</v>
       </c>
       <c r="D860" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E860">
         <v>5.805234021262887</v>
@@ -45188,7 +45188,7 @@
         <v>5.307410310014729</v>
       </c>
       <c r="D861" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E861">
         <v>5.805234021262887</v>
@@ -45238,7 +45238,7 @@
         <v>6.132545602111971</v>
       </c>
       <c r="D862" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E862">
         <v>5.861451650138072</v>
@@ -45288,7 +45288,7 @@
         <v>6.135239828860867</v>
       </c>
       <c r="D863" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E863">
         <v>5.861451650138072</v>
@@ -45338,7 +45338,7 @@
         <v>6.106045773846343</v>
       </c>
       <c r="D864" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E864">
         <v>5.861451650138072</v>
@@ -45388,7 +45388,7 @@
         <v>6.081451650138071</v>
       </c>
       <c r="D865" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E865">
         <v>5.861451650138072</v>
@@ -45438,7 +45438,7 @@
         <v>5.32659332168792</v>
       </c>
       <c r="D866" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E866">
         <v>5.778107746071176</v>
@@ -45488,7 +45488,7 @@
         <v>5.290947680064908</v>
       </c>
       <c r="D867" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E867">
         <v>5.778107746071176</v>
@@ -45538,7 +45538,7 @@
         <v>5.276408852652773</v>
       </c>
       <c r="D868" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E868">
         <v>5.778107746071176</v>
@@ -45588,7 +45588,7 @@
         <v>6.101501087170347</v>
       </c>
       <c r="D869" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E869">
         <v>5.779952436422644</v>
@@ -45638,7 +45638,7 @@
         <v>6.10652042322139</v>
       </c>
       <c r="D870" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E870">
         <v>5.779952436422644</v>
@@ -45688,7 +45688,7 @@
         <v>6.078661153176616</v>
       </c>
       <c r="D871" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E871">
         <v>5.779952436422644</v>
@@ -45738,7 +45738,7 @@
         <v>6.053937856729336</v>
       </c>
       <c r="D872" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E872">
         <v>5.779952436422644</v>
@@ -45788,7 +45788,7 @@
         <v>5.388093706617724</v>
       </c>
       <c r="D873" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E873">
         <v>5.831771516854801</v>
@@ -45838,7 +45838,7 @@
         <v>5.351851800874894</v>
       </c>
       <c r="D874" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E874">
         <v>5.831771516854801</v>
@@ -45888,7 +45888,7 @@
         <v>5.337738876405488</v>
       </c>
       <c r="D875" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E875">
         <v>5.831771516854801</v>
@@ -45938,7 +45938,7 @@
         <v>6.162916291511607</v>
       </c>
       <c r="D876" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E876">
         <v>5.809432743446582</v>
@@ -45988,7 +45988,7 @@
         <v>6.163335875781195</v>
       </c>
       <c r="D877" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E877">
         <v>5.809432743446582</v>
@@ -46038,7 +46038,7 @@
         <v>6.132836007491512</v>
       </c>
       <c r="D878" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E878">
         <v>5.809432743446582</v>
@@ -46088,7 +46088,7 @@
         <v>6.10836825280987</v>
       </c>
       <c r="D879" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E879">
         <v>5.809432743446582</v>
@@ -46138,7 +46138,7 @@
         <v>5.504130795560521</v>
       </c>
       <c r="D880" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E880">
         <v>5.933022716347823</v>
@@ -46188,7 +46188,7 @@
         <v>5.46676387648999</v>
       </c>
       <c r="D881" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E881">
         <v>5.933022716347823</v>
@@ -46238,7 +46238,7 @@
         <v>5.453454532968942</v>
       </c>
       <c r="D882" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E882">
         <v>5.933022716347823</v>
@@ -46288,7 +46288,7 @@
         <v>6.278792664264731</v>
       </c>
       <c r="D883" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E883">
         <v>5.82295074691097</v>
@@ -46338,7 +46338,7 @@
         <v>6.270533574292061</v>
       </c>
       <c r="D884" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E884">
         <v>5.82295074691097</v>
@@ -46388,7 +46388,7 @@
         <v>6.235051504122564</v>
       </c>
       <c r="D885" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E885">
         <v>5.854447210967837</v>
@@ -46438,7 +46438,7 @@
         <v>6.211065898009934</v>
       </c>
       <c r="D886" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E886">
         <v>5.854447210967837</v>
@@ -46488,7 +46488,7 @@
         <v>5.527008554379917</v>
       </c>
       <c r="D887" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E887">
         <v>5.952985303683308</v>
@@ -46538,7 +46538,7 @@
         <v>5.489419828783438</v>
       </c>
       <c r="D888" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E888">
         <v>5.952985303683308</v>
@@ -46588,7 +46588,7 @@
         <v>5.47626891849521</v>
       </c>
       <c r="D889" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E889">
         <v>5.952985303683308</v>
@@ -46638,7 +46638,7 @@
         <v>6.301638736437564</v>
       </c>
       <c r="D890" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E890">
         <v>5.842438034547991</v>
@@ -46688,7 +46688,7 @@
         <v>6.291668567550424</v>
       </c>
       <c r="D891" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E891">
         <v>5.842438034547991</v>
@@ -46738,7 +46738,7 @@
         <v>6.255204211337434</v>
       </c>
       <c r="D892" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E892">
         <v>5.805943847222144</v>
@@ -46788,7 +46788,7 @@
         <v>6.231313665164498</v>
       </c>
       <c r="D893" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E893">
         <v>5.805943847222144</v>
@@ -46838,7 +46838,7 @@
         <v>5.362358580199855</v>
       </c>
       <c r="D894" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E894">
         <v>5.809315658623142</v>
@@ -46888,7 +46888,7 @@
         <v>5.326366183992933</v>
       </c>
       <c r="D895" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E895">
         <v>5.809315658623142</v>
@@ -46938,7 +46938,7 @@
         <v>5.31207503842645</v>
       </c>
       <c r="D896" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E896">
         <v>5.809315658623142</v>
@@ -46988,7 +46988,7 @@
         <v>6.137216809313153</v>
       </c>
       <c r="D897" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E897">
         <v>5.660449825716769</v>
@@ -47038,7 +47038,7 @@
         <v>6.139561181431169</v>
       </c>
       <c r="D898" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E898">
         <v>5.660449825716769</v>
@@ -47088,7 +47088,7 @@
         <v>6.110166283943363</v>
       </c>
       <c r="D899" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E899">
         <v>5.660449825716769</v>
@@ -47138,7 +47138,7 @@
         <v>6.085591596603473</v>
       </c>
       <c r="D900" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E900">
         <v>5.660449825716769</v>
@@ -47188,7 +47188,7 @@
         <v>5.21583595429709</v>
       </c>
       <c r="D901" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E901">
         <v>5.6814635058271</v>
@@ -47238,7 +47238,7 @@
         <v>5.181264137565678</v>
       </c>
       <c r="D902" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E902">
         <v>5.6814635058271</v>
@@ -47288,7 +47288,7 @@
         <v>5.16595829237383</v>
       </c>
       <c r="D903" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E903">
         <v>5.6814635058271</v>
@@ -47338,7 +47338,7 @@
         <v>5.990897123335461</v>
       </c>
       <c r="D904" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E904">
         <v>5.530974153520144</v>
@@ -47388,7 +47388,7 @@
         <v>6.00595829237383</v>
       </c>
       <c r="D905" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E905">
         <v>5.530974153520144</v>
@@ -47438,7 +47438,7 @@
         <v>6.004200251407424</v>
       </c>
       <c r="D906" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E906">
         <v>5.530974153520144</v>
@@ -47488,7 +47488,7 @@
         <v>5.981096491596882</v>
       </c>
       <c r="D907" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E907">
         <v>5.530974153520144</v>
@@ -47538,7 +47538,7 @@
         <v>5.955912984481774</v>
       </c>
       <c r="D908" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E908">
         <v>5.530974153520144</v>
@@ -47588,7 +47588,7 @@
         <v>5.246905622239758</v>
       </c>
       <c r="D909" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E909">
         <v>5.708574157910038</v>
@@ -47638,7 +47638,7 @@
         <v>5.212032576040759</v>
       </c>
       <c r="D910" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E910">
         <v>5.708574157910038</v>
@@ -47688,7 +47688,7 @@
         <v>5.19694189475433</v>
       </c>
       <c r="D911" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E911">
         <v>5.708574157910038</v>
@@ -47738,7 +47738,7 @@
         <v>6.021923758497046</v>
       </c>
       <c r="D912" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E912">
         <v>5.558429067851753</v>
@@ -47788,7 +47788,7 @@
         <v>6.03694189475433</v>
       </c>
       <c r="D913" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E913">
         <v>5.558429067851753</v>
@@ -47838,7 +47838,7 @@
         <v>6.032903116390471</v>
       </c>
       <c r="D914" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E914">
         <v>5.558429067851753</v>
@@ -47888,7 +47888,7 @@
         <v>6.008465340366325</v>
       </c>
       <c r="D915" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E915">
         <v>5.558429067851753</v>
@@ -47938,7 +47938,7 @@
         <v>5.983410931594468</v>
       </c>
       <c r="D916" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E916">
         <v>5.558429067851753</v>
@@ -47988,7 +47988,7 @@
         <v>5.260021169191447</v>
       </c>
       <c r="D917" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E917">
         <v>5.720018471732149</v>
@@ -48038,7 +48038,7 @@
         <v>5.22502096394998</v>
       </c>
       <c r="D918" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E918">
         <v>5.720018471732149</v>
@@ -48088,7 +48088,7 @@
         <v>5.210021110551029</v>
       </c>
       <c r="D919" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E919">
         <v>5.720018471732149</v>
@@ -48138,7 +48138,7 @@
         <v>6.035021139871239</v>
       </c>
       <c r="D920" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E920">
         <v>5.570018706293828</v>
@@ -48188,7 +48188,7 @@
         <v>6.050021110551029</v>
       </c>
       <c r="D921" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E921">
         <v>5.570018706293828</v>
@@ -48238,7 +48238,7 @@
         <v>6.045019556579911</v>
       </c>
       <c r="D922" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E922">
         <v>5.570018706293828</v>
@@ -48288,7 +48288,7 @@
         <v>6.020018647653407</v>
       </c>
       <c r="D923" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E923">
         <v>5.570018706293828</v>
@@ -48338,7 +48338,7 @@
         <v>5.995018735614037</v>
       </c>
       <c r="D924" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E924">
         <v>5.570018706293828</v>
@@ -48438,7 +48438,7 @@
         <v>5.615668781285493</v>
       </c>
       <c r="D926" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E926">
         <v>6.030348105553824</v>
@@ -48488,7 +48488,7 @@
         <v>5.577220469001563</v>
       </c>
       <c r="D927" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E927">
         <v>6.030348105553824</v>
@@ -48538,7 +48538,7 @@
         <v>5.56468354920437</v>
       </c>
       <c r="D928" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E928">
         <v>6.030348105553824</v>
@@ -48588,7 +48588,7 @@
         <v>6.390176165244933</v>
       </c>
       <c r="D929" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E929">
         <v>5.917958864945399</v>
@@ -48638,7 +48638,7 @@
         <v>6.373574899054605</v>
       </c>
       <c r="D930" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E930">
         <v>5.917958864945399</v>
@@ -48688,7 +48688,7 @@
         <v>6.333303801797193</v>
       </c>
       <c r="D931" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E931">
         <v>5.884289033878317</v>
@@ -48738,7 +48738,7 @@
         <v>6.309781649918879</v>
       </c>
       <c r="D932" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E932">
         <v>5.884289033878317</v>
@@ -48788,7 +48788,7 @@
         <v>6.262613928093605</v>
       </c>
       <c r="D933" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E933">
         <v>6.212195151647427</v>
@@ -48838,7 +48838,7 @@
         <v>7.24816372476549</v>
       </c>
       <c r="D934" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E934">
         <v>7.595603386150444</v>
@@ -48888,7 +48888,7 @@
         <v>7.261638134101141</v>
       </c>
       <c r="D935" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E935">
         <v>7.595603386150444</v>
@@ -48938,7 +48938,7 @@
         <v>7.253775244709231</v>
       </c>
       <c r="D936" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E936">
         <v>7.595603386150444</v>
@@ -48988,7 +48988,7 @@
         <v>8.181523875261066</v>
       </c>
       <c r="D937" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E937">
         <v>7.445946162670672</v>
@@ -49038,7 +49038,7 @@
         <v>8.030757870733884</v>
       </c>
       <c r="D938" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E938">
         <v>7.445946162670672</v>
@@ -49088,7 +49088,7 @@
         <v>7.913466275542353</v>
       </c>
       <c r="D939" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E939">
         <v>7.567169202558158</v>
@@ -49138,7 +49138,7 @@
         <v>7.897397720238308</v>
       </c>
       <c r="D940" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E940">
         <v>7.567169202558158</v>
@@ -49188,7 +49188,7 @@
         <v>7.886369390677626</v>
       </c>
       <c r="D941" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E941">
         <v>7.567169202558158</v>
@@ -49238,7 +49238,7 @@
         <v>6.461998806928756</v>
       </c>
       <c r="D942" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E942">
         <v>6.809943004706455</v>
@@ -49288,7 +49288,7 @@
         <v>6.455649148235951</v>
       </c>
       <c r="D943" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E943">
         <v>6.809943004706455</v>
@@ -49338,7 +49338,7 @@
         <v>7.28237921649739</v>
       </c>
       <c r="D944" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E944">
         <v>6.678991980784874</v>
@@ -49388,7 +49388,7 @@
         <v>7.198955530379694</v>
       </c>
       <c r="D945" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E945">
         <v>6.678991980784874</v>
@@ -49438,7 +49438,7 @@
         <v>7.120323414275088</v>
       </c>
       <c r="D946" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E946">
         <v>6.757814301673794</v>
@@ -49488,7 +49488,7 @@
         <v>7.100513619059405</v>
       </c>
       <c r="D947" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E947">
         <v>6.757814301673794</v>
@@ -49538,7 +49538,7 @@
         <v>5.391263694581674</v>
       </c>
       <c r="D948" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E948">
         <v>4.981328216936646</v>
@@ -49588,7 +49588,7 @@
         <v>5.376664084342806</v>
       </c>
       <c r="D949" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E949">
         <v>5.183908869880363</v>
@@ -49638,7 +49638,7 @@
         <v>4.255036972488333</v>
       </c>
       <c r="D950" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E950">
         <v>4.585738592012135</v>
@@ -49674,7 +49674,7 @@
         <v>1</v>
       </c>
       <c r="P950" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="951" spans="1:16">
@@ -49724,7 +49724,7 @@
         <v>1</v>
       </c>
       <c r="P951" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="952" spans="1:16">
@@ -49738,7 +49738,7 @@
         <v>3.887235867264729</v>
       </c>
       <c r="D952" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E952">
         <v>4.261316022454437</v>
@@ -49774,7 +49774,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -49788,7 +49788,7 @@
         <v>4.52226704989957</v>
       </c>
       <c r="D953" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E953">
         <v>4.566623250498453</v>
@@ -49824,7 +49824,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -49838,7 +49838,7 @@
         <v>3.595471601271687</v>
       </c>
       <c r="D954" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E954">
         <v>4.003962492151604</v>
@@ -49874,7 +49874,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -49888,7 +49888,7 @@
         <v>4.274122026330736</v>
       </c>
       <c r="D955" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E955">
         <v>4.284760163047268</v>
@@ -49924,7 +49924,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -49938,7 +49938,7 @@
         <v>3.51283445556241</v>
       </c>
       <c r="D956" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E956">
         <v>3.931071587879801</v>
@@ -49974,7 +49974,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -49988,7 +49988,7 @@
         <v>4.203839271176003</v>
       </c>
       <c r="D957" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E957">
         <v>4.224910004360815</v>
@@ -50024,7 +50024,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -50038,7 +50038,7 @@
         <v>3.757771340160315</v>
       </c>
       <c r="D958" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E958">
         <v>4.020831110855603</v>
@@ -50074,7 +50074,7 @@
         <v>1</v>
       </c>
       <c r="P958" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="959" spans="1:16">
@@ -50088,7 +50088,7 @@
         <v>3.577092549221526</v>
       </c>
       <c r="D959" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E959">
         <v>3.987751069163838</v>
@@ -50124,7 +50124,7 @@
         <v>1</v>
       </c>
       <c r="P959" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="960" spans="1:16">
@@ -50174,7 +50174,7 @@
         <v>1</v>
       </c>
       <c r="P960" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="961" spans="1:16">
@@ -50188,7 +50188,7 @@
         <v>3.969181490046898</v>
       </c>
       <c r="D961" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E961">
         <v>4.227966423152568</v>
@@ -50224,7 +50224,7 @@
         <v>1</v>
       </c>
       <c r="P961" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="962" spans="1:16">
@@ -50238,7 +50238,7 @@
         <v>3.987966423152567</v>
       </c>
       <c r="D962" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E962">
         <v>4.227966423152568</v>
@@ -50274,7 +50274,7 @@
         <v>1</v>
       </c>
       <c r="P962" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="963" spans="1:16">
@@ -50324,7 +50324,7 @@
         <v>1</v>
       </c>
       <c r="P963" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="964" spans="1:16">
@@ -50338,7 +50338,7 @@
         <v>4.457464931808846</v>
       </c>
       <c r="D964" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E964">
         <v>4.34281674843841</v>
@@ -50374,7 +50374,7 @@
         <v>1</v>
       </c>
       <c r="P964" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="965" spans="1:16">
@@ -50388,7 +50388,7 @@
         <v>4.129665945672787</v>
       </c>
       <c r="D965" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E965">
         <v>4.385205788683081</v>
@@ -50538,7 +50538,7 @@
         <v>4.608509125339094</v>
       </c>
       <c r="D968" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E968">
         <v>4.501722471963149</v>
@@ -50588,7 +50588,7 @@
         <v>4.165381741025112</v>
       </c>
       <c r="D969" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E969">
         <v>4.420199389644091</v>
@@ -50838,7 +50838,7 @@
         <v>4.358277886497062</v>
       </c>
       <c r="D974" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E974">
         <v>4.609195061586275</v>
@@ -51038,7 +51038,7 @@
         <v>4.823673304938412</v>
       </c>
       <c r="D978" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E978">
         <v>4.78043513295729</v>
@@ -51088,7 +51088,7 @@
         <v>4.773780937032344</v>
       </c>
       <c r="D979" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E979">
         <v>4.78043513295729</v>
@@ -51138,7 +51138,7 @@
         <v>4.76066910325774</v>
       </c>
       <c r="D980" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E980">
         <v>4.78043513295729</v>
@@ -51188,7 +51188,7 @@
         <v>4.781010705652122</v>
       </c>
       <c r="D981" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E981">
         <v>4.78043513295729</v>
@@ -51238,7 +51238,7 @@
         <v>6.134818623398694</v>
       </c>
       <c r="D982" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E982">
         <v>5.774464332861776</v>
@@ -51288,7 +51288,7 @@
         <v>6.102771384660437</v>
       </c>
       <c r="D983" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E983">
         <v>5.778795004029567</v>
@@ -51338,7 +51338,7 @@
         <v>5.514582429707415</v>
       </c>
       <c r="D984" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E984">
         <v>5.241133593669833</v>
@@ -51388,7 +51388,7 @@
         <v>6.089893354328455</v>
       </c>
       <c r="D985" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E985">
         <v>5.69937873528254</v>
@@ -51438,7 +51438,7 @@
         <v>6.090496725476864</v>
       </c>
       <c r="D986" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E986">
         <v>5.69937873528254</v>
@@ -51488,7 +51488,7 @@
         <v>6.083345023798447</v>
       </c>
       <c r="D987" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E987">
         <v>5.69937873528254</v>
@@ -51538,7 +51538,7 @@
         <v>6.151446158250724</v>
       </c>
       <c r="D988" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E988">
         <v>5.740368070715386</v>
@@ -51588,7 +51588,7 @@
         <v>5.471792219876177</v>
       </c>
       <c r="D989" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E989">
         <v>5.499161328418567</v>
@@ -51638,7 +51638,7 @@
         <v>5.429161328418567</v>
       </c>
       <c r="D990" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E990">
         <v>5.499161328418567</v>
@@ -51688,7 +51688,7 @@
         <v>5.859820355215962</v>
       </c>
       <c r="D991" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E991">
         <v>5.498824536056178</v>
@@ -51738,7 +51738,7 @@
         <v>5.962203814850136</v>
       </c>
       <c r="D992" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E992">
         <v>5.498824536056178</v>
@@ -51788,7 +51788,7 @@
         <v>5.867235562966728</v>
       </c>
       <c r="D993" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E993">
         <v>5.498824536056178</v>
@@ -51838,7 +51838,7 @@
         <v>5.864221779328541</v>
       </c>
       <c r="D994" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E994">
         <v>5.498824536056178</v>
@@ -51888,7 +51888,7 @@
         <v>5.891472824538594</v>
       </c>
       <c r="D995" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E995">
         <v>5.498824536056178</v>
@@ -51938,7 +51938,7 @@
         <v>5.933527959091345</v>
       </c>
       <c r="D996" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E996">
         <v>5.516806571577774</v>
@@ -52088,7 +52088,7 @@
         <v>5.536448803884926</v>
       </c>
       <c r="D999" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E999">
         <v>5.114647162880539</v>
@@ -52138,7 +52138,7 @@
         <v>5.473079556721592</v>
       </c>
       <c r="D1000" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E1000">
         <v>5.114647162880539</v>
@@ -52188,7 +52188,7 @@
         <v>5.516088475684048</v>
       </c>
       <c r="D1001" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1001">
         <v>5.088556902345189</v>
@@ -52238,7 +52238,7 @@
         <v>4.87693542544124</v>
       </c>
       <c r="D1002" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E1002">
         <v>4.790484836705014</v>
@@ -52288,7 +52288,7 @@
         <v>4.782412771064838</v>
       </c>
       <c r="D1003" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E1003">
         <v>4.790484836705014</v>
@@ -52338,7 +52338,7 @@
         <v>5.183884767385427</v>
       </c>
       <c r="D1004" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E1004">
         <v>4.796513208070444</v>
@@ -52388,7 +52388,7 @@
         <v>5.146682382306041</v>
       </c>
       <c r="D1005" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E1005">
         <v>4.796513208070444</v>
@@ -52438,7 +52438,7 @@
         <v>5.170410455522431</v>
       </c>
       <c r="D1006" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1006">
         <v>4.733927060944326</v>
@@ -52488,7 +52488,7 @@
         <v>4.433208070443044</v>
       </c>
       <c r="D1007" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E1007">
         <v>4.48045274908133</v>
@@ -52538,7 +52538,7 @@
         <v>4.430537336199128</v>
       </c>
       <c r="D1008" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E1008">
         <v>4.48045274908133</v>
@@ -52588,7 +52588,7 @@
         <v>6.107518054315049</v>
       </c>
       <c r="D1009" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E1009">
         <v>5.738203236233369</v>
@@ -52638,7 +52638,7 @@
         <v>6.135203726571758</v>
       </c>
       <c r="D1010" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E1010">
         <v>5.738203236233369</v>
@@ -52688,7 +52688,7 @@
         <v>6.102046072361725</v>
       </c>
       <c r="D1011" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E1011">
         <v>5.738203236233369</v>
@@ -52738,7 +52738,7 @@
         <v>6.120488810422401</v>
       </c>
       <c r="D1012" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E1012">
         <v>5.738203236233369</v>
@@ -52788,7 +52788,7 @@
         <v>6.193632087855306</v>
       </c>
       <c r="D1013" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E1013">
         <v>5.783646464632436</v>
@@ -52838,7 +52838,7 @@
         <v>5.378974678814465</v>
       </c>
       <c r="D1014" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E1014">
         <v>5.579789251726952</v>
@@ -52888,7 +52888,7 @@
         <v>5.416732234956823</v>
       </c>
       <c r="D1015" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E1015">
         <v>5.579789251726952</v>
@@ -52938,7 +52938,7 @@
         <v>5.472103579470241</v>
       </c>
       <c r="D1016" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E1016">
         <v>5.579789251726952</v>
@@ -52988,7 +52988,7 @@
         <v>5.430560694308047</v>
       </c>
       <c r="D1017" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E1017">
         <v>5.579789251726952</v>
@@ -53038,7 +53038,7 @@
         <v>5.402846268497081</v>
       </c>
       <c r="D1018" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E1018">
         <v>5.579789251726952</v>
@@ -53124,7 +53124,7 @@
         <v>1</v>
       </c>
       <c r="P1019" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1020" spans="1:16">
@@ -53174,7 +53174,7 @@
         <v>1</v>
       </c>
       <c r="P1020" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1021" spans="1:16">
@@ -53188,7 +53188,7 @@
         <v>5.020295300931229</v>
       </c>
       <c r="D1021" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E1021">
         <v>5.342572941191464</v>
@@ -53224,7 +53224,7 @@
         <v>1</v>
       </c>
       <c r="P1021" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1022" spans="1:16">
@@ -53238,7 +53238,7 @@
         <v>5.54274578942891</v>
       </c>
       <c r="D1022" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E1022">
         <v>5.322745789428909</v>
@@ -53274,7 +53274,7 @@
         <v>1</v>
       </c>
       <c r="P1022" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1023" spans="1:16">
@@ -53288,7 +53288,7 @@
         <v>5.6130914859038</v>
       </c>
       <c r="D1023" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E1023">
         <v>5.322745789428909</v>
@@ -53324,7 +53324,7 @@
         <v>1</v>
       </c>
       <c r="P1023" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1024" spans="1:16">
@@ -53338,7 +53338,7 @@
         <v>5.147961849725716</v>
       </c>
       <c r="D1024" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E1024">
         <v>5.187875425606993</v>
@@ -53374,7 +53374,7 @@
         <v>1</v>
       </c>
       <c r="P1024" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="1025" spans="1:16">
@@ -53388,7 +53388,7 @@
         <v>4.481259603973901</v>
       </c>
       <c r="D1025" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E1025">
         <v>4.729065207154505</v>
@@ -53438,7 +53438,7 @@
         <v>4.933966438698594</v>
       </c>
       <c r="D1026" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E1026">
         <v>4.713966438698593</v>
@@ -53488,7 +53488,7 @@
         <v>4.545092978128704</v>
       </c>
       <c r="D1027" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E1027">
         <v>4.51376890178677</v>
@@ -53538,7 +53538,7 @@
         <v>4.556417054470637</v>
       </c>
       <c r="D1028" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E1028">
         <v>4.51376890178677</v>
@@ -53588,7 +53588,7 @@
         <v>4.521721707925945</v>
       </c>
       <c r="D1029" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1029">
         <v>4.242337996671525</v>
@@ -53638,7 +53638,7 @@
         <v>3.995431662159355</v>
       </c>
       <c r="D1030" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E1030">
         <v>4.028576685042651</v>
@@ -53688,7 +53688,7 @@
         <v>4.0220812096942</v>
       </c>
       <c r="D1031" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E1031">
         <v>4.028576685042651</v>
@@ -53738,7 +53738,7 @@
         <v>3.998833472019975</v>
       </c>
       <c r="D1032" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E1032">
         <v>4.028576685042651</v>
@@ -53788,7 +53788,7 @@
         <v>2.312870417300224</v>
       </c>
       <c r="D1033" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E1033">
         <v>2.600174015881064</v>
@@ -53838,7 +53838,7 @@
         <v>2.342806217266434</v>
       </c>
       <c r="D1034" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E1034">
         <v>2.600174015881064</v>
@@ -53888,7 +53888,7 @@
         <v>2.333191417469171</v>
       </c>
       <c r="D1035" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E1035">
         <v>2.600174015881064</v>
@@ -53938,7 +53938,7 @@
         <v>2.830944416286538</v>
       </c>
       <c r="D1036" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E1036">
         <v>2.501072816354117</v>
@@ -53988,7 +53988,7 @@
         <v>3.735551545505884</v>
       </c>
       <c r="D1037" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E1037">
         <v>3.537025852544748</v>
@@ -54038,7 +54038,7 @@
         <v>3.727025852544749</v>
       </c>
       <c r="D1038" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E1038">
         <v>3.537025852544748</v>
@@ -54088,7 +54088,7 @@
         <v>3.707843043382194</v>
       </c>
       <c r="D1039" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E1039">
         <v>3.537025852544748</v>
@@ -54138,7 +54138,7 @@
         <v>3.371288699025316</v>
       </c>
       <c r="D1040" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E1040">
         <v>3.571768922933395</v>
@@ -54188,7 +54188,7 @@
         <v>3.36981439198645</v>
       </c>
       <c r="D1041" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E1041">
         <v>3.571768922933395</v>
@@ -54238,7 +54238,7 @@
         <v>3.347025852544749</v>
       </c>
       <c r="D1042" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E1042">
         <v>3.571768922933395</v>
@@ -54288,7 +54288,7 @@
         <v>3.718820308855666</v>
       </c>
       <c r="D1043" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E1043">
         <v>3.501608848297368</v>
@@ -54338,7 +54338,7 @@
         <v>7.818784706417835</v>
       </c>
       <c r="D1044" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E1044">
         <v>8.66434683659535</v>
@@ -54388,7 +54388,7 @@
         <v>7.736183913922513</v>
       </c>
       <c r="D1045" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E1045">
         <v>8.114051730148025</v>
@@ -54438,7 +54438,7 @@
         <v>5.66445723600427</v>
       </c>
       <c r="D1046" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E1046">
         <v>5.237456064387949</v>
@@ -54488,7 +54488,7 @@
         <v>5.440858208955218</v>
       </c>
       <c r="D1047" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E1047">
         <v>5.007731036597828</v>
@@ -54588,7 +54588,7 @@
         <v>4.988258892022188</v>
       </c>
       <c r="D1049" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E1049">
         <v>4.542731738378961</v>
@@ -54638,7 +54638,7 @@
         <v>5.374367473486714</v>
       </c>
       <c r="D1050" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E1050">
         <v>4.939418637143884</v>
@@ -54688,7 +54688,7 @@
         <v>5.639230769230771</v>
       </c>
       <c r="D1051" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E1051">
         <v>5.211538461538465</v>
@@ -54738,7 +54738,7 @@
         <v>5.771656758678997</v>
       </c>
       <c r="D1052" t="s">
-        <v>463</v>
+        <v>289</v>
       </c>
       <c r="E1052">
         <v>5.250472631141054</v>
@@ -54785,7 +54785,7 @@
         <v>289</v>
       </c>
       <c r="C1053">
-        <v>-1.021813633931844</v>
+        <v>-0.9618136339318442</v>
       </c>
       <c r="D1053" t="s">
         <v>464</v>
@@ -54797,13 +54797,13 @@
         <v>1</v>
       </c>
       <c r="G1053">
-        <v>0.01616181363393184</v>
+        <v>0.01622181363393185</v>
       </c>
       <c r="H1053">
         <v>0.01548265479665487</v>
       </c>
       <c r="I1053">
-        <v>0.2791588372769693</v>
+        <v>0.2191588372769697</v>
       </c>
       <c r="J1053">
         <v>1.652271852679201</v>
@@ -54812,7 +54812,7 @@
         <v>5.2</v>
       </c>
       <c r="L1053">
-        <v>7.57</v>
+        <v>7.63</v>
       </c>
       <c r="M1053">
         <v>4.91</v>
@@ -54829,34 +54829,34 @@
     </row>
     <row r="1054" spans="1:16">
       <c r="A1054" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1054" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C1054">
-        <v>-1.104211494254949</v>
+        <v>-1.021813633931844</v>
       </c>
       <c r="D1054" t="s">
         <v>464</v>
       </c>
       <c r="E1054">
-        <v>-0.8204573916907298</v>
+        <v>-0.7426547966548744</v>
       </c>
       <c r="F1054">
         <v>1</v>
       </c>
       <c r="G1054">
-        <v>0.01624421149425495</v>
+        <v>0.01616181363393184</v>
       </c>
       <c r="H1054">
-        <v>0.01556045739169073</v>
+        <v>0.01548265479665487</v>
       </c>
       <c r="I1054">
-        <v>0.2837541025642194</v>
+        <v>0.2791588372769693</v>
       </c>
       <c r="J1054">
-        <v>1.668117595049029</v>
+        <v>1.652271852679201</v>
       </c>
       <c r="K1054">
         <v>5.2</v>
@@ -54874,7 +54874,7 @@
         <v>1</v>
       </c>
       <c r="P1054" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="1055" spans="1:16">
@@ -54885,78 +54885,78 @@
         <v>289</v>
       </c>
       <c r="C1055">
-        <v>-1.157822582940394</v>
+        <v>-1.04421149425495</v>
       </c>
       <c r="D1055" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E1055">
-        <v>-0.8939415344076389</v>
+        <v>-0.8204573916907298</v>
       </c>
       <c r="F1055">
         <v>1</v>
       </c>
       <c r="G1055">
-        <v>0.01629782258294039</v>
+        <v>0.01630421149425495</v>
       </c>
       <c r="H1055">
-        <v>0.01545394153440764</v>
+        <v>0.01556045739169073</v>
       </c>
       <c r="I1055">
-        <v>0.2638810485327552</v>
+        <v>0.2237541025642198</v>
       </c>
       <c r="J1055">
-        <v>1.67842741979623</v>
+        <v>1.668117595049029</v>
       </c>
       <c r="K1055">
         <v>5.2</v>
       </c>
       <c r="L1055">
-        <v>7.57</v>
+        <v>7.63</v>
       </c>
       <c r="M1055">
-        <v>4.87</v>
+        <v>4.91</v>
       </c>
       <c r="N1055">
-        <v>7.28</v>
+        <v>7.37</v>
       </c>
       <c r="O1055">
         <v>1</v>
       </c>
       <c r="P1055" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="1056" spans="1:16">
       <c r="A1056" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1056" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C1056">
-        <v>-1.192542776541119</v>
+        <v>-1.104211494254949</v>
       </c>
       <c r="D1056" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E1056">
-        <v>-0.9264583311067787</v>
+        <v>-0.8204573916907298</v>
       </c>
       <c r="F1056">
         <v>1</v>
       </c>
       <c r="G1056">
-        <v>0.01633254277654112</v>
+        <v>0.01624421149425495</v>
       </c>
       <c r="H1056">
-        <v>0.01548645833110678</v>
+        <v>0.01556045739169073</v>
       </c>
       <c r="I1056">
-        <v>0.2660844454343403</v>
+        <v>0.2837541025642194</v>
       </c>
       <c r="J1056">
-        <v>1.685104380104061</v>
+        <v>1.668117595049029</v>
       </c>
       <c r="K1056">
         <v>5.2</v>
@@ -54965,16 +54965,16 @@
         <v>7.57</v>
       </c>
       <c r="M1056">
-        <v>4.87</v>
+        <v>4.91</v>
       </c>
       <c r="N1056">
-        <v>7.28</v>
+        <v>7.37</v>
       </c>
       <c r="O1056">
         <v>1</v>
       </c>
       <c r="P1056" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="1057" spans="1:16">
@@ -54982,31 +54982,31 @@
         <v>0</v>
       </c>
       <c r="B1057" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C1057">
-        <v>-1.217889853450652</v>
+        <v>-1.157822582940394</v>
       </c>
       <c r="D1057" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E1057">
-        <v>-0.9501968435201311</v>
+        <v>-0.8710786311994871</v>
       </c>
       <c r="F1057">
         <v>1</v>
       </c>
       <c r="G1057">
-        <v>0.01635788985345065</v>
+        <v>0.01629782258294039</v>
       </c>
       <c r="H1057">
-        <v>0.01551019684352013</v>
+        <v>0.01561107863119949</v>
       </c>
       <c r="I1057">
-        <v>0.2676930099305208</v>
+        <v>0.2867439517409069</v>
       </c>
       <c r="J1057">
-        <v>1.689978817971279</v>
+        <v>1.67842741979623</v>
       </c>
       <c r="K1057">
         <v>5.2</v>
@@ -55015,16 +55015,16 @@
         <v>7.57</v>
       </c>
       <c r="M1057">
-        <v>4.87</v>
+        <v>4.91</v>
       </c>
       <c r="N1057">
-        <v>7.28</v>
+        <v>7.37</v>
       </c>
       <c r="O1057">
         <v>1</v>
       </c>
       <c r="P1057" t="s">
-        <v>461</v>
+        <v>599</v>
       </c>
     </row>
     <row r="1058" spans="1:16">
@@ -55035,45 +55035,145 @@
         <v>290</v>
       </c>
       <c r="C1058">
+        <v>-1.192542776541119</v>
+      </c>
+      <c r="D1058" t="s">
+        <v>465</v>
+      </c>
+      <c r="E1058">
+        <v>-0.9264583311067787</v>
+      </c>
+      <c r="F1058">
+        <v>1</v>
+      </c>
+      <c r="G1058">
+        <v>0.01633254277654112</v>
+      </c>
+      <c r="H1058">
+        <v>0.01548645833110678</v>
+      </c>
+      <c r="I1058">
+        <v>0.2660844454343403</v>
+      </c>
+      <c r="J1058">
+        <v>1.685104380104061</v>
+      </c>
+      <c r="K1058">
+        <v>5.2</v>
+      </c>
+      <c r="L1058">
+        <v>7.57</v>
+      </c>
+      <c r="M1058">
+        <v>4.87</v>
+      </c>
+      <c r="N1058">
+        <v>7.28</v>
+      </c>
+      <c r="O1058">
+        <v>1</v>
+      </c>
+      <c r="P1058" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:16">
+      <c r="A1059" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1059" t="s">
+        <v>290</v>
+      </c>
+      <c r="C1059">
+        <v>-1.217889853450652</v>
+      </c>
+      <c r="D1059" t="s">
+        <v>465</v>
+      </c>
+      <c r="E1059">
+        <v>-0.9501968435201311</v>
+      </c>
+      <c r="F1059">
+        <v>1</v>
+      </c>
+      <c r="G1059">
+        <v>0.01635788985345065</v>
+      </c>
+      <c r="H1059">
+        <v>0.01551019684352013</v>
+      </c>
+      <c r="I1059">
+        <v>0.2676930099305208</v>
+      </c>
+      <c r="J1059">
+        <v>1.689978817971279</v>
+      </c>
+      <c r="K1059">
+        <v>5.2</v>
+      </c>
+      <c r="L1059">
+        <v>7.57</v>
+      </c>
+      <c r="M1059">
+        <v>4.87</v>
+      </c>
+      <c r="N1059">
+        <v>7.28</v>
+      </c>
+      <c r="O1059">
+        <v>1</v>
+      </c>
+      <c r="P1059" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:16">
+      <c r="A1060" s="1">
+        <v>0</v>
+      </c>
+      <c r="B1060" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1060">
         <v>-2.807532631974992</v>
       </c>
-      <c r="D1058" t="s">
+      <c r="D1060" t="s">
         <v>466</v>
       </c>
-      <c r="E1058">
+      <c r="E1060">
         <v>-2.509249826348689</v>
       </c>
-      <c r="F1058">
-        <v>1</v>
-      </c>
-      <c r="G1058">
+      <c r="F1060">
+        <v>1</v>
+      </c>
+      <c r="G1060">
         <v>0.01758753263197499</v>
       </c>
-      <c r="H1058">
+      <c r="H1060">
         <v>0.01710924982634869</v>
       </c>
-      <c r="I1058">
+      <c r="I1060">
         <v>0.2982828056263038</v>
       </c>
-      <c r="J1058">
+      <c r="J1060">
         <v>2.043593713822644</v>
       </c>
-      <c r="K1058">
+      <c r="K1060">
         <v>4.99</v>
       </c>
-      <c r="L1058">
+      <c r="L1060">
         <v>7.39</v>
       </c>
-      <c r="M1058">
+      <c r="M1060">
         <v>4.8</v>
       </c>
-      <c r="N1058">
+      <c r="N1060">
         <v>7.3</v>
       </c>
-      <c r="O1058">
-        <v>1</v>
-      </c>
-      <c r="P1058" t="s">
+      <c r="O1060">
+        <v>1</v>
+      </c>
+      <c r="P1060" t="s">
         <v>601</v>
       </c>
     </row>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -1420,7 +1420,7 @@
     <t>2021-11-29</t>
   </si>
   <si>
-    <t>2021-12-07</t>
+    <t>2021-12-08</t>
   </si>
   <si>
     <t>2021-11-22</t>
@@ -54903,7 +54903,7 @@
         <v>468</v>
       </c>
       <c r="E1055">
-        <v>-0.5831091671907158</v>
+        <v>-0.6731091671907166</v>
       </c>
       <c r="F1055">
         <v>-1</v>
@@ -54912,10 +54912,10 @@
         <v>0.01595831382634242</v>
       </c>
       <c r="H1055">
-        <v>0.01630310916719072</v>
+        <v>0.01621310916719072</v>
       </c>
       <c r="I1055">
-        <v>0.08479534084829599</v>
+        <v>0.1747953408482967</v>
       </c>
       <c r="J1055">
         <v>1.652271852679201</v>
@@ -54930,7 +54930,7 @@
         <v>5.11</v>
       </c>
       <c r="N1055">
-        <v>7.86</v>
+        <v>7.77</v>
       </c>
       <c r="O1055">
         <v>1</v>
@@ -55053,7 +55053,7 @@
         <v>468</v>
       </c>
       <c r="E1058">
-        <v>-0.6640809107005365</v>
+        <v>-0.7540809107005373</v>
       </c>
       <c r="F1058">
         <v>-1</v>
@@ -55062,10 +55062,10 @@
         <v>0.01603722562334416</v>
       </c>
       <c r="H1058">
-        <v>0.01638408091070054</v>
+        <v>0.01629408091070054</v>
       </c>
       <c r="I1058">
-        <v>0.08685528735637416</v>
+        <v>0.1768552873563749</v>
       </c>
       <c r="J1058">
         <v>1.668117595049029</v>
@@ -55080,7 +55080,7 @@
         <v>5.11</v>
       </c>
       <c r="N1058">
-        <v>7.86</v>
+        <v>7.77</v>
       </c>
       <c r="O1058">
         <v>1</v>
@@ -55203,7 +55203,7 @@
         <v>468</v>
       </c>
       <c r="E1061">
-        <v>-0.7167641151587345</v>
+        <v>-0.8067641151587353</v>
       </c>
       <c r="F1061">
         <v>-1</v>
@@ -55212,10 +55212,10 @@
         <v>0.01608856855058522</v>
       </c>
       <c r="H1061">
-        <v>0.01643676411515874</v>
+        <v>0.01634676411515874</v>
       </c>
       <c r="I1061">
-        <v>0.0881955645735113</v>
+        <v>0.178195564573512</v>
       </c>
       <c r="J1061">
         <v>1.67842741979623</v>
@@ -55230,7 +55230,7 @@
         <v>5.11</v>
       </c>
       <c r="N1061">
-        <v>7.86</v>
+        <v>7.77</v>
       </c>
       <c r="O1061">
         <v>1</v>
@@ -55353,7 +55353,7 @@
         <v>468</v>
       </c>
       <c r="E1064">
-        <v>-0.7508833823317529</v>
+        <v>-0.8408833823317536</v>
       </c>
       <c r="F1064">
         <v>-1</v>
@@ -55362,10 +55362,10 @@
         <v>0.01612181981291822</v>
       </c>
       <c r="H1064">
-        <v>0.01647088338233175</v>
+        <v>0.01638088338233175</v>
       </c>
       <c r="I1064">
-        <v>0.08906356941352822</v>
+        <v>0.179063569413529</v>
       </c>
       <c r="J1064">
         <v>1.685104380104061</v>
@@ -55380,7 +55380,7 @@
         <v>5.11</v>
       </c>
       <c r="N1064">
-        <v>7.86</v>
+        <v>7.77</v>
       </c>
       <c r="O1064">
         <v>1</v>
@@ -55503,7 +55503,7 @@
         <v>468</v>
       </c>
       <c r="E1067">
-        <v>-0.7757917598332371</v>
+        <v>-0.8657917598332379</v>
       </c>
       <c r="F1067">
         <v>-1</v>
@@ -55512,10 +55512,10 @@
         <v>0.01614609451349697</v>
       </c>
       <c r="H1067">
-        <v>0.01649579175983324</v>
+        <v>0.01640579175983323</v>
       </c>
       <c r="I1067">
-        <v>0.0896972463362653</v>
+        <v>0.179697246336266</v>
       </c>
       <c r="J1067">
         <v>1.689978817971279</v>
@@ -55530,7 +55530,7 @@
         <v>5.11</v>
       </c>
       <c r="N1067">
-        <v>7.86</v>
+        <v>7.77</v>
       </c>
       <c r="O1067">
         <v>1</v>
@@ -55553,7 +55553,7 @@
         <v>468</v>
       </c>
       <c r="E1068">
-        <v>-0.7757917598332371</v>
+        <v>-0.8657917598332379</v>
       </c>
       <c r="F1068">
         <v>-1</v>
@@ -55562,10 +55562,10 @@
         <v>0.01605919472531726</v>
       </c>
       <c r="H1068">
-        <v>0.01649579175983324</v>
+        <v>0.01640579175983323</v>
       </c>
       <c r="I1068">
-        <v>0.03659703451597895</v>
+        <v>0.1265970345159797</v>
       </c>
       <c r="J1068">
         <v>1.689978817971279</v>
@@ -55580,7 +55580,7 @@
         <v>5.11</v>
       </c>
       <c r="N1068">
-        <v>7.86</v>
+        <v>7.77</v>
       </c>
       <c r="O1068">
         <v>1</v>
@@ -55653,7 +55653,7 @@
         <v>468</v>
       </c>
       <c r="E1070">
-        <v>-2.582763877633709</v>
+        <v>-2.672763877633709</v>
       </c>
       <c r="F1070">
         <v>-1</v>
@@ -55662,10 +55662,10 @@
         <v>0.01704794201493401</v>
       </c>
       <c r="H1070">
-        <v>0.01830276387763371</v>
+        <v>0.01821276387763371</v>
       </c>
       <c r="I1070">
-        <v>0.1348218626996989</v>
+        <v>0.2248218626996996</v>
       </c>
       <c r="J1070">
         <v>2.043593713822644</v>
@@ -55680,7 +55680,7 @@
         <v>5.11</v>
       </c>
       <c r="N1070">
-        <v>7.86</v>
+        <v>7.77</v>
       </c>
       <c r="O1070">
         <v>1</v>
@@ -55694,43 +55694,43 @@
         <v>2</v>
       </c>
       <c r="B1071" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C1071">
-        <v>-2.447096694836766</v>
+        <v>-2.496660757698539</v>
       </c>
       <c r="D1071" t="s">
         <v>468</v>
       </c>
       <c r="E1071">
-        <v>-2.582763877633709</v>
+        <v>-2.672763877633709</v>
       </c>
       <c r="F1071">
         <v>-1</v>
       </c>
       <c r="G1071">
-        <v>0.01790709669483677</v>
+        <v>0.01781666075769854</v>
       </c>
       <c r="H1071">
-        <v>0.01830276387763371</v>
+        <v>0.01821276387763371</v>
       </c>
       <c r="I1071">
-        <v>0.1356671827969427</v>
+        <v>0.1761031199351706</v>
       </c>
       <c r="J1071">
         <v>2.043593713822644</v>
       </c>
       <c r="K1071">
-        <v>4.98</v>
+        <v>4.97</v>
       </c>
       <c r="L1071">
-        <v>7.73</v>
+        <v>7.66</v>
       </c>
       <c r="M1071">
         <v>5.11</v>
       </c>
       <c r="N1071">
-        <v>7.86</v>
+        <v>7.77</v>
       </c>
       <c r="O1071">
         <v>1</v>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3225" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3222" uniqueCount="606">
   <si>
     <t>trade_time</t>
   </si>
@@ -898,9 +898,6 @@
     <t>2021-11-24</t>
   </si>
   <si>
-    <t>2021-11-30</t>
-  </si>
-  <si>
     <t>2016-04-28</t>
   </si>
   <si>
@@ -1420,13 +1417,16 @@
     <t>2021-11-29</t>
   </si>
   <si>
+    <t>2021-12-09</t>
+  </si>
+  <si>
+    <t>2021-11-22</t>
+  </si>
+  <si>
+    <t>2021-11-15</t>
+  </si>
+  <si>
     <t>2021-12-08</t>
-  </si>
-  <si>
-    <t>2021-11-22</t>
-  </si>
-  <si>
-    <t>2021-11-15</t>
   </si>
   <si>
     <t>2016-03-24</t>
@@ -2189,7 +2189,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1071"/>
+  <dimension ref="A1:P1070"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2250,7 +2250,7 @@
         <v>4.31128552097429</v>
       </c>
       <c r="D2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E2">
         <v>3.491640730717187</v>
@@ -2300,7 +2300,7 @@
         <v>2.930197902571042</v>
       </c>
       <c r="D3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E3">
         <v>3.697845060893099</v>
@@ -2350,7 +2350,7 @@
         <v>2.93171853856563</v>
       </c>
       <c r="D4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E4">
         <v>3.697845060893099</v>
@@ -2450,7 +2450,7 @@
         <v>3.256806675563038</v>
       </c>
       <c r="D6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E6">
         <v>2.536806675563037</v>
@@ -2500,7 +2500,7 @@
         <v>1.909437857449102</v>
       </c>
       <c r="D7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E7">
         <v>2.73123945259945</v>
@@ -2550,7 +2550,7 @@
         <v>1.927571287293738</v>
       </c>
       <c r="D8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E8">
         <v>2.73123945259945</v>
@@ -2650,7 +2650,7 @@
         <v>2.529267581722536</v>
       </c>
       <c r="D10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E10">
         <v>1.809267581722535</v>
@@ -2800,7 +2800,7 @@
         <v>0.9430396109046839</v>
       </c>
       <c r="D13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E13">
         <v>0.8476461186055282</v>
@@ -2850,7 +2850,7 @@
         <v>2.096084795296841</v>
       </c>
       <c r="D14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E14">
         <v>1.37608479529684</v>
@@ -3000,7 +3000,7 @@
         <v>1.855836876417781</v>
       </c>
       <c r="D17" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E17">
         <v>1.13583687641778</v>
@@ -3150,7 +3150,7 @@
         <v>1.689338262028841</v>
       </c>
       <c r="D20" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E20">
         <v>0.96933826202884</v>
@@ -3200,7 +3200,7 @@
         <v>1.627006479834717</v>
       </c>
       <c r="D21" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E21">
         <v>0.9357502825591215</v>
@@ -3350,7 +3350,7 @@
         <v>1.911015876946134</v>
       </c>
       <c r="D24" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E24">
         <v>1.236185039124933</v>
@@ -3450,7 +3450,7 @@
         <v>2.232760263343966</v>
       </c>
       <c r="D26" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E26">
         <v>1.515079422678022</v>
@@ -3650,7 +3650,7 @@
         <v>0.6496455995207633</v>
       </c>
       <c r="D30" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E30">
         <v>1.139659067730454</v>
@@ -3700,7 +3700,7 @@
         <v>0.6621691688877203</v>
       </c>
       <c r="D31" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E31">
         <v>1.139659067730454</v>
@@ -3750,7 +3750,7 @@
         <v>0.5096590677304533</v>
       </c>
       <c r="D32" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E32">
         <v>1.139659067730454</v>
@@ -3900,7 +3900,7 @@
         <v>-0.4482238035193742</v>
       </c>
       <c r="D35" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E35">
         <v>0.05100577720271815</v>
@@ -3950,7 +3950,7 @@
         <v>-0.5789942227972826</v>
       </c>
       <c r="D36" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E36">
         <v>0.05100577720271815</v>
@@ -4000,7 +4000,7 @@
         <v>-0.6485127107485908</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E37">
         <v>0.05100577720271815</v>
@@ -4050,7 +4050,7 @@
         <v>0.5534941892431284</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E38">
         <v>0.1656128422573726</v>
@@ -4200,7 +4200,7 @@
         <v>-1.066969696969696</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E41">
         <v>-0.543771149985659</v>
@@ -4250,7 +4250,7 @@
         <v>-1.17377114998566</v>
       </c>
       <c r="D42" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E42">
         <v>-0.543771149985659</v>
@@ -4300,7 +4300,7 @@
         <v>-1.246436605805691</v>
       </c>
       <c r="D43" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E43">
         <v>-0.543771149985659</v>
@@ -4350,7 +4350,7 @@
         <v>0.007809960806808292</v>
       </c>
       <c r="D44" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E44">
         <v>-0.2591202243252724</v>
@@ -4500,7 +4500,7 @@
         <v>-1.678657860308897</v>
       </c>
       <c r="D47" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E47">
         <v>-1.151600082010416</v>
@@ -4550,7 +4550,7 @@
         <v>-1.781600082010417</v>
       </c>
       <c r="D48" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E48">
         <v>-1.151600082010416</v>
@@ -4600,7 +4600,7 @@
         <v>-1.857481563925816</v>
       </c>
       <c r="D49" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E49">
         <v>-1.151600082010416</v>
@@ -4800,7 +4800,7 @@
         <v>-1.819193108813611</v>
       </c>
       <c r="D53" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E53">
         <v>-1.291248672795858</v>
@@ -4850,7 +4850,7 @@
         <v>-1.921248672795858</v>
       </c>
       <c r="D54" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E54">
         <v>-1.291248672795858</v>
@@ -4900,7 +4900,7 @@
         <v>-1.997869036143985</v>
       </c>
       <c r="D55" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E55">
         <v>-1.291248672795858</v>
@@ -4950,7 +4950,7 @@
         <v>-0.6779710045650891</v>
       </c>
       <c r="D56" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E56">
         <v>-0.8744524579575934</v>
@@ -5000,7 +5000,7 @@
         <v>-0.7891561672790921</v>
       </c>
       <c r="D57" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E57">
         <v>-0.8744524579575934</v>
@@ -5150,7 +5150,7 @@
         <v>0.3390481079807373</v>
       </c>
       <c r="D60" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E60">
         <v>0.8316689003586539</v>
@@ -5200,7 +5200,7 @@
         <v>0.3561344946420899</v>
       </c>
       <c r="D61" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E61">
         <v>0.8316689003586539</v>
@@ -5250,7 +5250,7 @@
         <v>0.2016689003586531</v>
       </c>
       <c r="D62" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E62">
         <v>0.8316689003586539</v>
@@ -5300,7 +5300,7 @@
         <v>0.3550656832089647</v>
       </c>
       <c r="D63" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E63">
         <v>0.8316689003586539</v>
@@ -5500,7 +5500,7 @@
         <v>1.702993205626412</v>
       </c>
       <c r="D67" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E67">
         <v>2.213613017446391</v>
@@ -5550,7 +5550,7 @@
         <v>1.700042623382163</v>
       </c>
       <c r="D68" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E68">
         <v>2.213613017446391</v>
@@ -5600,7 +5600,7 @@
         <v>1.55416430148684</v>
       </c>
       <c r="D69" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E69">
         <v>2.213613017446391</v>
@@ -5650,7 +5650,7 @@
         <v>1.697734695551071</v>
       </c>
       <c r="D70" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E70">
         <v>2.213613017446391</v>
@@ -5700,7 +5700,7 @@
         <v>2.778308822184697</v>
       </c>
       <c r="D71" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E71">
         <v>2.907149147620857</v>
@@ -5750,7 +5750,7 @@
         <v>6.23470991605689</v>
       </c>
       <c r="D72" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E72">
         <v>6.96882467582045</v>
@@ -5786,7 +5786,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5800,7 +5800,7 @@
         <v>6.165186370595404</v>
       </c>
       <c r="D73" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E73">
         <v>6.96882467582045</v>
@@ -5836,7 +5836,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5850,7 +5850,7 @@
         <v>7.462192305683145</v>
       </c>
       <c r="D74" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E74">
         <v>7.5652188186885</v>
@@ -5886,7 +5886,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5900,7 +5900,7 @@
         <v>7.766409955034785</v>
       </c>
       <c r="D75" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E75">
         <v>7.5652188186885</v>
@@ -5936,7 +5936,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -6000,7 +6000,7 @@
         <v>6.790335000164763</v>
       </c>
       <c r="D77" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E77">
         <v>7.58905888555706</v>
@@ -6050,7 +6050,7 @@
         <v>6.74758629353808</v>
       </c>
       <c r="D78" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E78">
         <v>7.58905888555706</v>
@@ -6250,7 +6250,7 @@
         <v>6.426886909355456</v>
       </c>
       <c r="D82" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E82">
         <v>7.170479443185158</v>
@@ -6300,7 +6300,7 @@
         <v>6.354540197150865</v>
       </c>
       <c r="D83" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E83">
         <v>7.170479443185158</v>
@@ -6500,7 +6500,7 @@
         <v>6.205686423858355</v>
       </c>
       <c r="D87" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E87">
         <v>6.974286460418881</v>
@@ -6550,7 +6550,7 @@
         <v>6.17031498633333</v>
       </c>
       <c r="D88" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E88">
         <v>6.974286460418881</v>
@@ -6600,7 +6600,7 @@
         <v>7.467572163512598</v>
       </c>
       <c r="D89" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E89">
         <v>7.999200804331553</v>
@@ -6650,7 +6650,7 @@
         <v>7.771800736433435</v>
       </c>
       <c r="D90" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E90">
         <v>7.999200804331553</v>
@@ -6750,7 +6750,7 @@
         <v>5.758523378301289</v>
       </c>
       <c r="D92" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E92">
         <v>6.469153597378058</v>
@@ -6800,7 +6800,7 @@
         <v>5.695995227937997</v>
       </c>
       <c r="D93" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E93">
         <v>6.469153597378058</v>
@@ -6850,7 +6850,7 @@
         <v>5.575650149522264</v>
       </c>
       <c r="D94" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E94">
         <v>6.469153597378058</v>
@@ -6900,7 +6900,7 @@
         <v>6.970016293417387</v>
       </c>
       <c r="D95" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E95">
         <v>7.634780179426718</v>
@@ -6950,7 +6950,7 @@
         <v>7.273234600612143</v>
       </c>
       <c r="D96" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E96">
         <v>7.634780179426718</v>
@@ -7000,7 +7000,7 @@
         <v>5.679717798863969</v>
       </c>
       <c r="D97" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E97">
         <v>6.421217454115635</v>
@@ -7050,7 +7050,7 @@
         <v>5.650983189414583</v>
       </c>
       <c r="D98" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E98">
         <v>6.421217454115635</v>
@@ -7100,7 +7100,7 @@
         <v>5.530350494139276</v>
       </c>
       <c r="D99" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E99">
         <v>6.421217454115635</v>
@@ -7300,7 +7300,7 @@
         <v>5.621464282690935</v>
       </c>
       <c r="D103" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E103">
         <v>6.359962442366914</v>
@@ -7350,7 +7350,7 @@
         <v>5.593464733382533</v>
       </c>
       <c r="D104" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E104">
         <v>6.359962442366914</v>
@@ -7400,7 +7400,7 @@
         <v>5.472464508036733</v>
       </c>
       <c r="D105" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E105">
         <v>6.359962442366914</v>
@@ -7600,7 +7600,7 @@
         <v>4.812788531912378</v>
       </c>
       <c r="D109" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E109">
         <v>5.509619907373689</v>
@@ -7650,7 +7650,7 @@
         <v>4.794993093023895</v>
       </c>
       <c r="D110" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E110">
         <v>5.509619907373689</v>
@@ -7700,7 +7700,7 @@
         <v>4.668890812468137</v>
       </c>
       <c r="D111" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E111">
         <v>5.509619907373689</v>
@@ -7750,7 +7750,7 @@
         <v>6.099225988855712</v>
       </c>
       <c r="D112" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E112">
         <v>6.844581898111059</v>
@@ -7800,7 +7800,7 @@
         <v>6.071430549967227</v>
       </c>
       <c r="D113" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E113">
         <v>6.844581898111059</v>
@@ -7850,7 +7850,7 @@
         <v>6.326174848577831</v>
       </c>
       <c r="D114" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E114">
         <v>6.844581898111059</v>
@@ -7900,7 +7900,7 @@
         <v>4.312040252964167</v>
       </c>
       <c r="D115" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E115">
         <v>4.983070718153698</v>
@@ -7950,7 +7950,7 @@
         <v>4.300563404346324</v>
       </c>
       <c r="D116" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E116">
         <v>4.983070718153698</v>
@@ -8000,7 +8000,7 @@
         <v>4.171301828655245</v>
       </c>
       <c r="D117" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E117">
         <v>4.983070718153698</v>
@@ -8250,7 +8250,7 @@
         <v>3.944694008078107</v>
       </c>
       <c r="D122" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E122">
         <v>4.596797064225139</v>
@@ -8300,7 +8300,7 @@
         <v>3.937852443307407</v>
       </c>
       <c r="D123" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E123">
         <v>4.596797064225139</v>
@@ -8350,7 +8350,7 @@
         <v>3.806273225692757</v>
       </c>
       <c r="D124" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E124">
         <v>4.596797064225139</v>
@@ -8400,7 +8400,7 @@
         <v>5.201008311197539</v>
       </c>
       <c r="D125" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E125">
         <v>5.908899264592449</v>
@@ -8450,7 +8450,7 @@
         <v>5.425218702390213</v>
       </c>
       <c r="D126" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E126">
         <v>5.908899264592449</v>
@@ -8500,7 +8500,7 @@
         <v>5.478374570280344</v>
       </c>
       <c r="D127" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E127">
         <v>5.908899264592449</v>
@@ -8550,7 +8550,7 @@
         <v>4.103540950877517</v>
       </c>
       <c r="D128" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E128">
         <v>4.804785959699134</v>
@@ -8600,7 +8600,7 @@
         <v>4.065325239112265</v>
       </c>
       <c r="D129" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E129">
         <v>4.804785959699134</v>
@@ -8650,7 +8650,7 @@
         <v>3.934560544154515</v>
       </c>
       <c r="D130" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E130">
         <v>4.804785959699134</v>
@@ -8850,7 +8850,7 @@
         <v>3.580160099004089</v>
       </c>
       <c r="D134" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E134">
         <v>4.308315560860121</v>
@@ -8900,7 +8900,7 @@
         <v>3.549633088105812</v>
       </c>
       <c r="D135" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E135">
         <v>4.308315560860121</v>
@@ -8950,7 +8950,7 @@
         <v>3.415573235633644</v>
       </c>
       <c r="D136" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E136">
         <v>4.308315560860121</v>
@@ -9300,7 +9300,7 @@
         <v>3.927996868785175</v>
       </c>
       <c r="D143" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E143">
         <v>4.228792366606019</v>
@@ -9350,7 +9350,7 @@
         <v>4.067912029788856</v>
       </c>
       <c r="D144" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E144">
         <v>4.228792366606019</v>
@@ -9400,7 +9400,7 @@
         <v>4.059184614733637</v>
       </c>
       <c r="D145" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E145">
         <v>4.228792366606019</v>
@@ -9450,7 +9450,7 @@
         <v>2.005909712128765</v>
       </c>
       <c r="D146" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E146">
         <v>2.67318675835737</v>
@@ -9500,7 +9500,7 @@
         <v>1.861985812525753</v>
       </c>
       <c r="D147" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E147">
         <v>2.67318675835737</v>
@@ -9550,7 +9550,7 @@
         <v>3.25255656550317</v>
       </c>
       <c r="D148" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E148">
         <v>3.447665574766244</v>
@@ -9600,7 +9600,7 @@
         <v>3.347725014643028</v>
       </c>
       <c r="D149" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E149">
         <v>3.447665574766244</v>
@@ -9650,7 +9650,7 @@
         <v>3.394518515304676</v>
       </c>
       <c r="D150" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E150">
         <v>3.447665574766244</v>
@@ -9700,7 +9700,7 @@
         <v>3.355089268282093</v>
       </c>
       <c r="D151" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E151">
         <v>3.447665574766244</v>
@@ -9750,7 +9750,7 @@
         <v>3.579100375295562</v>
       </c>
       <c r="D152" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E152">
         <v>3.447665574766244</v>
@@ -10186,7 +10186,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -10236,7 +10236,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10286,7 +10286,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -10336,7 +10336,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10386,7 +10386,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -10436,7 +10436,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10486,7 +10486,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10550,7 +10550,7 @@
         <v>3.123371001188277</v>
       </c>
       <c r="D168" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E168">
         <v>4.195059763740991</v>
@@ -10600,7 +10600,7 @@
         <v>2.954328619026529</v>
       </c>
       <c r="D169" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E169">
         <v>4.195059763740991</v>
@@ -10650,7 +10650,7 @@
         <v>3.046412078566592</v>
       </c>
       <c r="D170" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E170">
         <v>4.195059763740991</v>
@@ -10700,7 +10700,7 @@
         <v>3.445059763740991</v>
       </c>
       <c r="D171" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E171">
         <v>4.195059763740991</v>
@@ -10800,7 +10800,7 @@
         <v>2.577752040845755</v>
       </c>
       <c r="D173" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E173">
         <v>3.401487870308934</v>
@@ -10850,7 +10850,7 @@
         <v>2.464829953558134</v>
       </c>
       <c r="D174" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E174">
         <v>3.401487870308934</v>
@@ -10900,7 +10900,7 @@
         <v>2.478250786050127</v>
       </c>
       <c r="D175" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E175">
         <v>3.401487870308934</v>
@@ -10950,7 +10950,7 @@
         <v>2.818408284535719</v>
       </c>
       <c r="D176" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E176">
         <v>3.401487870308934</v>
@@ -11850,7 +11850,7 @@
         <v>6.871264555787782</v>
       </c>
       <c r="D194" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E194">
         <v>5.968914093679149</v>
@@ -11900,7 +11900,7 @@
         <v>6.95746889119295</v>
       </c>
       <c r="D195" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E195">
         <v>5.968914093679149</v>
@@ -11950,7 +11950,7 @@
         <v>6.908484547625465</v>
       </c>
       <c r="D196" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E196">
         <v>6.962494985247139</v>
@@ -12100,7 +12100,7 @@
         <v>3.455949739008592</v>
       </c>
       <c r="D199" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E199">
         <v>2.626483427002986</v>
@@ -12350,7 +12350,7 @@
         <v>1.402030495249267</v>
       </c>
       <c r="D204" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E204">
         <v>0.6610634692540209</v>
@@ -12500,7 +12500,7 @@
         <v>-1.012190922870992</v>
       </c>
       <c r="D207" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E207">
         <v>0.08311492058150804</v>
@@ -12550,7 +12550,7 @@
         <v>-1.046879430812844</v>
       </c>
       <c r="D208" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E208">
         <v>0.08311492058150804</v>
@@ -12650,7 +12650,7 @@
         <v>0.5471409041675006</v>
       </c>
       <c r="D210" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E210">
         <v>-0.09752500935174702</v>
@@ -12700,7 +12700,7 @@
         <v>0.5771493770759779</v>
       </c>
       <c r="D211" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E211">
         <v>-0.1448636147170212</v>
@@ -12750,7 +12750,7 @@
         <v>0.7211216989082878</v>
       </c>
       <c r="D212" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E212">
         <v>0.3151194394660273</v>
@@ -12800,7 +12800,7 @@
         <v>0.6184603042735599</v>
       </c>
       <c r="D213" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E213">
         <v>0.3151194394660273</v>
@@ -12850,7 +12850,7 @@
         <v>0.8057932610331839</v>
       </c>
       <c r="D214" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E214">
         <v>0.3151194394660273</v>
@@ -12900,7 +12900,7 @@
         <v>0.1720291663575146</v>
       </c>
       <c r="D215" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E215">
         <v>-1.174782432733231</v>
@@ -12936,7 +12936,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12950,7 +12950,7 @@
         <v>-0.5832848576420009</v>
       </c>
       <c r="D216" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E216">
         <v>-1.223526404187433</v>
@@ -12986,7 +12986,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -13000,7 +13000,7 @@
         <v>-0.5978983899145334</v>
       </c>
       <c r="D217" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E217">
         <v>-1.157197898187556</v>
@@ -13036,7 +13036,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -13050,7 +13050,7 @@
         <v>-0.522125420733472</v>
       </c>
       <c r="D218" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E218">
         <v>-1.167246194006191</v>
@@ -13086,7 +13086,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -13100,7 +13100,7 @@
         <v>-0.5938162465515013</v>
       </c>
       <c r="D219" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E219">
         <v>-1.167246194006191</v>
@@ -13136,7 +13136,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -13150,7 +13150,7 @@
         <v>-0.4086954732787849</v>
       </c>
       <c r="D220" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E220">
         <v>-1.167246194006191</v>
@@ -13186,7 +13186,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -13200,7 +13200,7 @@
         <v>1.516859912216534</v>
       </c>
       <c r="D221" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E221">
         <v>0.1337015362106797</v>
@@ -13250,7 +13250,7 @@
         <v>0.6549286759327</v>
       </c>
       <c r="D222" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E222">
         <v>0.009840892465252438</v>
@@ -13300,7 +13300,7 @@
         <v>0.6801911119239215</v>
       </c>
       <c r="D223" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E223">
         <v>0.1028237015362095</v>
@@ -13350,7 +13350,7 @@
         <v>0.8396671543525969</v>
       </c>
       <c r="D224" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E224">
         <v>0.1921232626188711</v>
@@ -13400,7 +13400,7 @@
         <v>0.7340526700804659</v>
       </c>
       <c r="D225" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E225">
         <v>0.1921232626188711</v>
@@ -13500,7 +13500,7 @@
         <v>1.469564000694344</v>
       </c>
       <c r="D227" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E227">
         <v>0.08768389256746723</v>
@@ -13536,7 +13536,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -13550,7 +13550,7 @@
         <v>0.6113823501888458</v>
       </c>
       <c r="D228" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E228">
         <v>-0.03353499756140543</v>
@@ -13586,7 +13586,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13600,7 +13600,7 @@
         <v>0.6047501988112209</v>
       </c>
       <c r="D229" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E229">
         <v>0.05851041506496912</v>
@@ -13636,7 +13636,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13650,7 +13650,7 @@
         <v>0.7917747178202177</v>
       </c>
       <c r="D230" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E230">
         <v>0.144316043945091</v>
@@ -13686,7 +13686,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13700,7 +13700,7 @@
         <v>0.6873532835684664</v>
       </c>
       <c r="D231" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E231">
         <v>0.144316043945091</v>
@@ -13736,7 +13736,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13786,7 +13786,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13800,7 +13800,7 @@
         <v>1.44514430187747</v>
       </c>
       <c r="D233" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E233">
         <v>0.06392418561050839</v>
@@ -13850,7 +13850,7 @@
         <v>0.5888986274943893</v>
       </c>
       <c r="D234" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E234">
         <v>-0.05593072134120547</v>
@@ -13900,7 +13900,7 @@
         <v>0.5831904647206478</v>
       </c>
       <c r="D235" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E235">
         <v>0.03563069725456458</v>
@@ -13950,7 +13950,7 @@
         <v>0.7670470228020498</v>
       </c>
       <c r="D236" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E236">
         <v>0.1196323483842505</v>
@@ -14000,7 +14000,7 @@
         <v>0.6632415809528851</v>
       </c>
       <c r="D237" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E237">
         <v>0.1196323483842505</v>
@@ -14050,7 +14050,7 @@
         <v>-0.3588062330199779</v>
       </c>
       <c r="D238" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E238">
         <v>-0.2613915586021829</v>
@@ -14100,7 +14100,7 @@
         <v>-0.341391558602183</v>
       </c>
       <c r="D239" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E239">
         <v>-0.2613915586021829</v>
@@ -14150,7 +14150,7 @@
         <v>1.286085745836417</v>
       </c>
       <c r="D240" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E240">
         <v>-0.09083549053754325</v>
@@ -14186,7 +14186,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -14200,7 +14200,7 @@
         <v>0.4424501191394743</v>
       </c>
       <c r="D241" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E241">
         <v>-0.2018060457103878</v>
@@ -14236,7 +14236,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -14250,7 +14250,7 @@
         <v>0.4427603882159339</v>
       </c>
       <c r="D242" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E242">
         <v>-0.1133971390361523</v>
@@ -14286,7 +14286,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -14300,7 +14300,7 @@
         <v>0.6059823228109291</v>
       </c>
       <c r="D243" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E243">
         <v>-0.04114575961400391</v>
@@ -14336,7 +14336,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -14350,7 +14350,7 @@
         <v>0.5061891688618996</v>
       </c>
       <c r="D244" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E244">
         <v>-0.04114575961400391</v>
@@ -14386,7 +14386,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -14400,7 +14400,7 @@
         <v>-0.5227368529397651</v>
       </c>
       <c r="D245" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E245">
         <v>-0.3415594517159466</v>
@@ -14436,7 +14436,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -14450,7 +14450,7 @@
         <v>-0.5056087705148382</v>
       </c>
       <c r="D246" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E246">
         <v>-0.3415594517159466</v>
@@ -14486,7 +14486,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -14500,7 +14500,7 @@
         <v>1.220304308582177</v>
       </c>
       <c r="D247" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E247">
         <v>-0.154839051109235</v>
@@ -14550,7 +14550,7 @@
         <v>0.3818837868207066</v>
       </c>
       <c r="D248" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E248">
         <v>-0.2621353278048151</v>
@@ -14600,7 +14600,7 @@
         <v>0.3846830832527317</v>
       </c>
       <c r="D249" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E249">
         <v>-0.1750301973644497</v>
@@ -14650,7 +14650,7 @@
         <v>0.5393712097715007</v>
       </c>
       <c r="D250" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E250">
         <v>-0.1076383475412612</v>
@@ -14700,7 +14700,7 @@
         <v>0.4412374073928493</v>
       </c>
       <c r="D251" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E251">
         <v>-0.1076383475412612</v>
@@ -14750,7 +14750,7 @@
         <v>-0.5905332171008926</v>
       </c>
       <c r="D252" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E252">
         <v>-0.318380300096722</v>
@@ -14800,7 +14800,7 @@
         <v>-0.5124949878498484</v>
       </c>
       <c r="D253" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E253">
         <v>-0.318380300096722</v>
@@ -14850,7 +14850,7 @@
         <v>0.5242887395747005</v>
       </c>
       <c r="D254" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E254">
         <v>-0.1202877329872347</v>
@@ -14900,7 +14900,7 @@
         <v>0.5212357776743701</v>
       </c>
       <c r="D255" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E255">
         <v>-0.03011713389658688</v>
@@ -14950,7 +14950,7 @@
         <v>0.6959887899040744</v>
       </c>
       <c r="D256" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E256">
         <v>0.04870055362310488</v>
@@ -15000,7 +15000,7 @@
         <v>0.5939534819705194</v>
       </c>
       <c r="D257" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E257">
         <v>0.04870055362310488</v>
@@ -15050,7 +15050,7 @@
         <v>-0.3211288472862446</v>
       </c>
       <c r="D258" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E258">
         <v>-0.1326523579478529</v>
@@ -15100,7 +15100,7 @@
         <v>-0.431128847286244</v>
       </c>
       <c r="D259" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E259">
         <v>-0.1326523579478529</v>
@@ -15150,7 +15150,7 @@
         <v>-0.351975902162371</v>
       </c>
       <c r="D260" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E260">
         <v>-0.1326523579478529</v>
@@ -15200,7 +15200,7 @@
         <v>0.5451410172423419</v>
       </c>
       <c r="D261" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E261">
         <v>-0.09951706893081891</v>
@@ -15236,7 +15236,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -15250,7 +15250,7 @@
         <v>0.5412311124241622</v>
       </c>
       <c r="D262" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E262">
         <v>-0.008897594978440893</v>
@@ -15286,7 +15286,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -15300,7 +15300,7 @@
         <v>0.7189222146579191</v>
       </c>
       <c r="D263" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E263">
         <v>0.07159317157133671</v>
@@ -15336,7 +15336,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -15350,7 +15350,7 @@
         <v>0.6163156114457973</v>
       </c>
       <c r="D264" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E264">
         <v>0.07159317157133671</v>
@@ -15386,7 +15386,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15400,7 +15400,7 @@
         <v>-0.2977873544762826</v>
       </c>
       <c r="D265" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E265">
         <v>0.2641354210821554</v>
@@ -15436,7 +15436,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15450,7 +15450,7 @@
         <v>-0.407787354476282</v>
       </c>
       <c r="D266" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E266">
         <v>0.2641354210821554</v>
@@ -15486,7 +15486,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15500,7 +15500,7 @@
         <v>0.6831127115251583</v>
       </c>
       <c r="D267" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E267">
         <v>0.0379146187207553</v>
@@ -15536,7 +15536,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15550,7 +15550,7 @@
         <v>0.6735327370789186</v>
       </c>
       <c r="D268" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E268">
         <v>0.1315041291449752</v>
@@ -15586,7 +15586,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15600,7 +15600,7 @@
         <v>0.8706640780374553</v>
       </c>
       <c r="D269" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E269">
         <v>0.2230650316352509</v>
@@ -15636,7 +15636,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15650,7 +15650,7 @@
         <v>0.7642774284066274</v>
       </c>
       <c r="D270" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E270">
         <v>0.2230650316352509</v>
@@ -15686,7 +15686,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15700,7 +15700,7 @@
         <v>-0.1433454579405264</v>
       </c>
       <c r="D271" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E271">
         <v>0.4234373772991074</v>
@@ -15736,7 +15736,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15750,7 +15750,7 @@
         <v>-0.2533454579405259</v>
       </c>
       <c r="D272" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E272">
         <v>0.4234373772991074</v>
@@ -15786,7 +15786,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15800,7 +15800,7 @@
         <v>-0.05222072710995107</v>
       </c>
       <c r="D273" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E273">
         <v>0.6345003208948405</v>
@@ -15850,7 +15850,7 @@
         <v>0.702314352898032</v>
       </c>
       <c r="D274" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E274">
         <v>0.05704110689843134</v>
@@ -15900,7 +15900,7 @@
         <v>0.6919452699022219</v>
       </c>
       <c r="D275" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E275">
         <v>0.151043959896235</v>
@@ -15950,7 +15950,7 @@
         <v>0.6723143528980309</v>
       </c>
       <c r="D276" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E276">
         <v>0.151043959896235</v>
@@ -16050,7 +16050,7 @@
         <v>0.8917821258878558</v>
       </c>
       <c r="D278" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E278">
         <v>0.2441455028880526</v>
@@ -16100,7 +16100,7 @@
         <v>0.7848694038906459</v>
       </c>
       <c r="D279" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E279">
         <v>0.2441455028880526</v>
@@ -16150,7 +16150,7 @@
         <v>-0.1218516441141411</v>
       </c>
       <c r="D280" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E280">
         <v>0.4456075698822666</v>
@@ -16200,7 +16200,7 @@
         <v>-0.03112774311154531</v>
       </c>
       <c r="D281" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E281">
         <v>0.4456075698822666</v>
@@ -16250,7 +16250,7 @@
         <v>-0.1599756512329034</v>
       </c>
       <c r="D282" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E282">
         <v>0.5314388961892202</v>
@@ -16300,7 +16300,7 @@
         <v>0.6023819278039682</v>
       </c>
       <c r="D283" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E283">
         <v>-0.04250019324418908</v>
@@ -16350,7 +16350,7 @@
         <v>0.5961196567983258</v>
       </c>
       <c r="D284" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E284">
         <v>0.04935147252067118</v>
@@ -16400,7 +16400,7 @@
         <v>0.572381927803967</v>
       </c>
       <c r="D285" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E285">
         <v>0.04935147252067118</v>
@@ -16500,7 +16500,7 @@
         <v>0.7818760145319583</v>
       </c>
       <c r="D287" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E287">
         <v>0.2188455592486616</v>
@@ -16550,7 +16550,7 @@
         <v>0.6777011671948596</v>
       </c>
       <c r="D288" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E288">
         <v>0.1344349540078777</v>
@@ -16600,7 +16600,7 @@
         <v>-0.2337133802272593</v>
       </c>
       <c r="D289" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E289">
         <v>0.3302257092061467</v>
@@ -16650,7 +16650,7 @@
         <v>-0.1404471670402767</v>
       </c>
       <c r="D290" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E290">
         <v>0.3302257092061467</v>
@@ -16700,7 +16700,7 @@
         <v>-0.5297221743420888</v>
       </c>
       <c r="D291" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E291">
         <v>0.177797484794409</v>
@@ -16736,7 +16736,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16750,7 +16750,7 @@
         <v>0.2594772575520725</v>
       </c>
       <c r="D292" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E292">
         <v>-0.3840627708532196</v>
@@ -16786,7 +16786,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16800,7 +16800,7 @@
         <v>0.2160020090057699</v>
       </c>
       <c r="D293" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E293">
         <v>-0.2995926146241139</v>
@@ -16836,7 +16836,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16850,7 +16850,7 @@
         <v>0.2294772575520714</v>
       </c>
       <c r="D294" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E294">
         <v>-0.2995926146241139</v>
@@ -16886,7 +16886,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16936,7 +16936,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16950,7 +16950,7 @@
         <v>0.4047479818870166</v>
       </c>
       <c r="D296" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E296">
         <v>-0.1643218902891714</v>
@@ -16986,7 +16986,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -17000,7 +17000,7 @@
         <v>0.3099677830499701</v>
       </c>
       <c r="D297" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E297">
         <v>-0.2420220323156315</v>
@@ -17036,7 +17036,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -17050,7 +17050,7 @@
         <v>-0.6175518760865248</v>
       </c>
       <c r="D298" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E298">
         <v>-0.06569162043889776</v>
@@ -17086,7 +17086,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -17100,7 +17100,7 @@
         <v>-0.5155620607209208</v>
       </c>
       <c r="D299" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E299">
         <v>-0.06569162043889776</v>
@@ -17136,7 +17136,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -17150,7 +17150,7 @@
         <v>3.711167000814271</v>
       </c>
       <c r="D300" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E300">
         <v>4.512707221119614</v>
@@ -17200,7 +17200,7 @@
         <v>5.260227025292643</v>
       </c>
       <c r="D301" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E301">
         <v>3.883216817226483</v>
@@ -17250,7 +17250,7 @@
         <v>3.612446707073811</v>
       </c>
       <c r="D302" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E302">
         <v>4.036376474529282</v>
@@ -17300,7 +17300,7 @@
         <v>2.778054848675449</v>
       </c>
       <c r="D303" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E303">
         <v>3.550231399857543</v>
@@ -17350,7 +17350,7 @@
         <v>2.800953545963342</v>
       </c>
       <c r="D304" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E304">
         <v>3.550231399857543</v>
@@ -17400,7 +17400,7 @@
         <v>4.323852243251237</v>
       </c>
       <c r="D305" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E305">
         <v>2.974574389357036</v>
@@ -17450,7 +17450,7 @@
         <v>2.718486113765989</v>
       </c>
       <c r="D306" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E306">
         <v>3.123410865296</v>
@@ -17500,7 +17500,7 @@
         <v>1.983160587873193</v>
       </c>
       <c r="D307" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E307">
         <v>2.730322983995075</v>
@@ -17550,7 +17550,7 @@
         <v>2.004669609879961</v>
       </c>
       <c r="D308" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E308">
         <v>2.730322983995075</v>
@@ -17600,7 +17600,7 @@
         <v>3.526178631886735</v>
       </c>
       <c r="D309" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E309">
         <v>2.200525257771622</v>
@@ -17650,7 +17650,7 @@
         <v>1.956944059710679</v>
       </c>
       <c r="D310" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E310">
         <v>2.409218509541397</v>
@@ -17700,7 +17700,7 @@
         <v>0.8799289586838714</v>
       </c>
       <c r="D311" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E311">
         <v>1.592374275565531</v>
@@ -17750,7 +17750,7 @@
         <v>0.9682501402131294</v>
       </c>
       <c r="D312" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E312">
         <v>1.592374275565531</v>
@@ -17800,7 +17800,7 @@
         <v>2.419089549448499</v>
       </c>
       <c r="D313" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E313">
         <v>1.126224527949153</v>
@@ -17850,7 +17850,7 @@
         <v>2.06419891568518</v>
       </c>
       <c r="D314" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E314">
         <v>1.126224527949153</v>
@@ -17900,7 +17900,7 @@
         <v>0.9000018695083227</v>
       </c>
       <c r="D315" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E315">
         <v>1.703012712656575</v>
@@ -17950,7 +17950,7 @@
         <v>0.3940106533845285</v>
       </c>
       <c r="D316" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E316">
         <v>0.9777032963232024</v>
@@ -17986,7 +17986,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -18000,7 +18000,7 @@
         <v>0.284010653384529</v>
       </c>
       <c r="D317" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E317">
         <v>0.9777032963232024</v>
@@ -18036,7 +18036,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -18050,7 +18050,7 @@
         <v>1.821087613711049</v>
       </c>
       <c r="D318" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E318">
         <v>0.5459334509356335</v>
@@ -18086,7 +18086,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -18100,7 +18100,7 @@
         <v>1.5037023278337</v>
       </c>
       <c r="D319" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E319">
         <v>0.5459334509356335</v>
@@ -18136,7 +18136,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -18150,7 +18150,7 @@
         <v>0.3290871294662949</v>
       </c>
       <c r="D320" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E320">
         <v>1.164394244405246</v>
@@ -18186,7 +18186,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -18200,7 +18200,7 @@
         <v>-0.1303378620988589</v>
       </c>
       <c r="D321" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E321">
         <v>0.5687326111345428</v>
@@ -18250,7 +18250,7 @@
         <v>1.405290327194502</v>
       </c>
       <c r="D322" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E322">
         <v>0.1424507182009354</v>
@@ -18300,7 +18300,7 @@
         <v>1.113982919914012</v>
       </c>
       <c r="D323" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E323">
         <v>0.1424507182009354</v>
@@ -18350,7 +18350,7 @@
         <v>0.01807890749429752</v>
       </c>
       <c r="D324" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E324">
         <v>0.7898869323337241</v>
@@ -18400,7 +18400,7 @@
         <v>-0.1449533761282655</v>
       </c>
       <c r="D325" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E325">
         <v>0.5539893391153683</v>
@@ -18450,7 +18450,7 @@
         <v>1.390623709969187</v>
       </c>
       <c r="D326" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E326">
         <v>0.1282184781408322</v>
@@ -18500,7 +18500,7 @@
         <v>1.100236160215024</v>
       </c>
       <c r="D327" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E327">
         <v>0.1282184781408322</v>
@@ -18550,7 +18550,7 @@
         <v>0.003795564238286531</v>
       </c>
       <c r="D328" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E328">
         <v>0.77667675619176</v>
@@ -18600,7 +18600,7 @@
         <v>1.338895251493001</v>
       </c>
       <c r="D329" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E329">
         <v>0.5272283520481338</v>
@@ -18650,7 +18650,7 @@
         <v>-0.04658110525333115</v>
       </c>
       <c r="D330" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E330">
         <v>0.7300850958569374</v>
@@ -18700,7 +18700,7 @@
         <v>5.252623163353501</v>
       </c>
       <c r="D331" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E331">
         <v>5.811442523768368</v>
@@ -18850,7 +18850,7 @@
         <v>5.155821953327571</v>
       </c>
       <c r="D334" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E334">
         <v>5.436800777873812</v>
@@ -18900,7 +18900,7 @@
         <v>5.21461106309421</v>
       </c>
       <c r="D335" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E335">
         <v>5.436800777873812</v>
@@ -19050,7 +19050,7 @@
         <v>5.996975409186557</v>
       </c>
       <c r="D338" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E338">
         <v>6.322440349888621</v>
@@ -19100,7 +19100,7 @@
         <v>6.04103615104905</v>
       </c>
       <c r="D339" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E339">
         <v>6.322440349888621</v>
@@ -19250,7 +19250,7 @@
         <v>6.467595657864342</v>
       </c>
       <c r="D342" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E342">
         <v>6.75843983370544</v>
@@ -19300,7 +19300,7 @@
         <v>6.50341596735699</v>
       </c>
       <c r="D343" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E343">
         <v>6.75843983370544</v>
@@ -19400,7 +19400,7 @@
         <v>7.038673370415092</v>
       </c>
       <c r="D345" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E345">
         <v>7.57711369319794</v>
@@ -19450,7 +19450,7 @@
         <v>6.933612348269409</v>
       </c>
       <c r="D346" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E346">
         <v>7.57711369319794</v>
@@ -19500,7 +19500,7 @@
         <v>7.041012886240821</v>
       </c>
       <c r="D347" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E347">
         <v>7.57711369319794</v>
@@ -19600,7 +19600,7 @@
         <v>7.603480524142883</v>
       </c>
       <c r="D349" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E349">
         <v>8.074842039131216</v>
@@ -19650,7 +19650,7 @@
         <v>7.583949919224556</v>
       </c>
       <c r="D350" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E350">
         <v>8.115780829294561</v>
@@ -19700,7 +19700,7 @@
         <v>7.602119009154551</v>
       </c>
       <c r="D351" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E351">
         <v>8.115780829294561</v>
@@ -19750,7 +19750,7 @@
         <v>7.596203554119548</v>
       </c>
       <c r="D352" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E352">
         <v>8.115780829294561</v>
@@ -19850,7 +19850,7 @@
         <v>8.197082757216956</v>
       </c>
       <c r="D354" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E354">
         <v>8.669626746773165</v>
@@ -19900,7 +19900,7 @@
         <v>8.20282687732055</v>
       </c>
       <c r="D355" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E355">
         <v>8.694010892986238</v>
@@ -19950,7 +19950,7 @@
         <v>8.194538767660747</v>
       </c>
       <c r="D356" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E356">
         <v>8.694010892986238</v>
@@ -20000,7 +20000,7 @@
         <v>8.192170736329373</v>
       </c>
       <c r="D357" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E357">
         <v>8.694010892986238</v>
@@ -20050,7 +20050,7 @@
         <v>-0.9277197529705248</v>
       </c>
       <c r="D358" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E358">
         <v>-1.43484711683287</v>
@@ -20100,7 +20100,7 @@
         <v>-1.739101844557563</v>
       </c>
       <c r="D359" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E359">
         <v>-1.225064022760026</v>
@@ -20150,7 +20150,7 @@
         <v>-1.67793665889768</v>
       </c>
       <c r="D360" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E360">
         <v>-1.225064022760026</v>
@@ -20200,7 +20200,7 @@
         <v>-1.660809295035333</v>
       </c>
       <c r="D361" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E361">
         <v>-0.9252809286871813</v>
@@ -20250,7 +20250,7 @@
         <v>-1.665172475723605</v>
       </c>
       <c r="D362" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E362">
         <v>-0.9252809286871813</v>
@@ -20300,7 +20300,7 @@
         <v>-0.8321510586103233</v>
       </c>
       <c r="D363" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E363">
         <v>-0.4166226922621714</v>
@@ -20350,7 +20350,7 @@
         <v>-3.843022818180284</v>
       </c>
       <c r="D364" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E364">
         <v>-3.26412423419014</v>
@@ -20400,7 +20400,7 @@
         <v>-3.712943072690754</v>
       </c>
       <c r="D365" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E365">
         <v>-3.26412423419014</v>
@@ -20450,7 +20450,7 @@
         <v>-4.087117010683363</v>
       </c>
       <c r="D366" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E366">
         <v>-3.293178553948453</v>
@@ -20500,7 +20500,7 @@
         <v>-2.768453907950921</v>
       </c>
       <c r="D367" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E367">
         <v>-2.083569770974329</v>
@@ -20550,7 +20550,7 @@
         <v>-2.698924870466321</v>
       </c>
       <c r="D368" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E368">
         <v>-2.083569770974329</v>
@@ -20600,7 +20600,7 @@
         <v>-5.897343766119011</v>
       </c>
       <c r="D369" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E369">
         <v>-5.21377186018452</v>
@@ -20650,7 +20650,7 @@
         <v>-5.892794919062931</v>
       </c>
       <c r="D370" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E370">
         <v>-5.287381083735886</v>
@@ -20700,7 +20700,7 @@
         <v>-6.281892613175087</v>
       </c>
       <c r="D371" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E371">
         <v>-5.383339366049038</v>
@@ -20750,7 +20750,7 @@
         <v>-4.84153475427336</v>
       </c>
       <c r="D372" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E372">
         <v>-4.085725742427703</v>
@@ -20800,7 +20800,7 @@
         <v>-4.665255930675347</v>
       </c>
       <c r="D373" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E373">
         <v>-4.085725742427703</v>
@@ -20850,7 +20850,7 @@
         <v>-7.494239379929031</v>
       </c>
       <c r="D374" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E374">
         <v>-6.751752878533589</v>
@@ -20900,7 +20900,7 @@
         <v>-7.492791301055105</v>
       </c>
       <c r="D375" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E375">
         <v>-6.850168247542195</v>
@@ -20950,7 +20950,7 @@
         <v>-7.875687458802952</v>
       </c>
       <c r="D376" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E376">
         <v>-6.901165391214095</v>
@@ -21000,7 +21000,7 @@
         <v>-6.346957706709796</v>
       </c>
       <c r="D377" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E377">
         <v>-5.984607757431821</v>
@@ -21050,7 +21050,7 @@
         <v>-6.382299087003467</v>
       </c>
       <c r="D378" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E378">
         <v>-5.984607757431821</v>
@@ -21100,7 +21100,7 @@
         <v>-8.194922154350412</v>
       </c>
       <c r="D379" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E379">
         <v>-7.42658522050059</v>
@@ -21150,7 +21150,7 @@
         <v>-8.155009684147785</v>
       </c>
       <c r="D380" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E380">
         <v>-7.535884982121567</v>
@@ -21200,7 +21200,7 @@
         <v>-8.575009684147785</v>
       </c>
       <c r="D381" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E381">
         <v>-7.567154164183544</v>
@@ -21250,7 +21250,7 @@
         <v>-7.007504283373057</v>
       </c>
       <c r="D382" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E382">
         <v>-6.779342409117989</v>
@@ -21300,7 +21300,7 @@
         <v>-7.019036054827168</v>
       </c>
       <c r="D383" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E383">
         <v>-6.779342409117989</v>
@@ -21350,7 +21350,7 @@
         <v>-8.936969711340112</v>
       </c>
       <c r="D384" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E384">
         <v>-8.141256265679017</v>
@@ -21400,7 +21400,7 @@
         <v>-8.895616372094786</v>
       </c>
       <c r="D385" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E385">
         <v>-8.262082979641582</v>
@@ -21450,7 +21450,7 @@
         <v>-9.315616372094786</v>
       </c>
       <c r="D386" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E386">
         <v>-8.272459560584432</v>
@@ -21600,7 +21600,7 @@
         <v>-8.948241366187794</v>
       </c>
       <c r="D389" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E389">
         <v>-8.152112073066304</v>
@@ -21650,7 +21650,7 @@
         <v>-8.90686614023403</v>
       </c>
       <c r="D390" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E390">
         <v>-8.273113880696405</v>
@@ -21700,7 +21700,7 @@
         <v>-9.32686614023403</v>
       </c>
       <c r="D391" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E391">
         <v>-7.892485491389962</v>
@@ -21750,7 +21750,7 @@
         <v>-7.646984587574911</v>
       </c>
       <c r="D392" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E392">
         <v>-7.178478260869557</v>
@@ -21800,7 +21800,7 @@
         <v>-7.393291551707726</v>
       </c>
       <c r="D393" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E393">
         <v>-7.178478260869557</v>
@@ -21850,7 +21850,7 @@
         <v>-9.216500648310582</v>
       </c>
       <c r="D394" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E394">
         <v>-8.410474410800093</v>
@@ -21886,7 +21886,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21900,7 +21900,7 @@
         <v>-9.174604530546869</v>
       </c>
       <c r="D395" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E395">
         <v>-8.477110822973078</v>
@@ -21936,7 +21936,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21950,7 +21950,7 @@
         <v>-9.594604530546869</v>
       </c>
       <c r="D396" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E396">
         <v>-8.147201586454123</v>
@@ -21986,7 +21986,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -22036,7 +22036,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -22086,7 +22086,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -22100,7 +22100,7 @@
         <v>-9.488460946517886</v>
       </c>
       <c r="D399" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E399">
         <v>-8.782113312812619</v>
@@ -22150,7 +22150,7 @@
         <v>-9.908460946517886</v>
       </c>
       <c r="D400" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E400">
         <v>-8.445792612543283</v>
@@ -22200,7 +22200,7 @@
         <v>-7.945711812235471</v>
       </c>
       <c r="D401" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E401">
         <v>-7.898110811850708</v>
@@ -22250,7 +22250,7 @@
         <v>-7.914350711812233</v>
       </c>
       <c r="D402" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E402">
         <v>-7.898110811850708</v>
@@ -22300,7 +22300,7 @@
         <v>-9.731958922090953</v>
       </c>
       <c r="D403" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E403">
         <v>-8.922781252412936</v>
@@ -22350,7 +22350,7 @@
         <v>-10.15195892209095</v>
       </c>
       <c r="D404" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E404">
         <v>-8.677447301366684</v>
@@ -22500,7 +22500,7 @@
         <v>-9.713150682287534</v>
       </c>
       <c r="D407" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E407">
         <v>-8.904576779062349</v>
@@ -22550,7 +22550,7 @@
         <v>-10.13315068228753</v>
       </c>
       <c r="D408" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E408">
         <v>-8.659553859219074</v>
@@ -22700,7 +22700,7 @@
         <v>-9.786103124815638</v>
       </c>
       <c r="D411" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E411">
         <v>-9.096428585475211</v>
@@ -22750,7 +22750,7 @@
         <v>-9.885452203496488</v>
       </c>
       <c r="D412" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E412">
         <v>-9.071347220310315</v>
@@ -22800,7 +22800,7 @@
         <v>-10.30545220349649</v>
       </c>
       <c r="D413" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E413">
         <v>-8.823474956244713</v>
@@ -22950,7 +22950,7 @@
         <v>-9.843764571794191</v>
       </c>
       <c r="D416" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E416">
         <v>-9.128491781807984</v>
@@ -23000,7 +23000,7 @@
         <v>-9.944492011757397</v>
       </c>
       <c r="D417" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E417">
         <v>-9.128491781807984</v>
@@ -23050,7 +23050,7 @@
         <v>-10.3644920117574</v>
       </c>
       <c r="D418" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E418">
         <v>-8.879643178500714</v>
@@ -23100,7 +23100,7 @@
         <v>-8.368915738537504</v>
       </c>
       <c r="D419" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E419">
         <v>-7.670672951950555</v>
@@ -23150,7 +23150,7 @@
         <v>-8.412127831876973</v>
       </c>
       <c r="D420" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E420">
         <v>-7.670672951950555</v>
@@ -23200,7 +23200,7 @@
         <v>-8.3229155085881</v>
       </c>
       <c r="D421" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E421">
         <v>-7.670672951950555</v>
@@ -23250,7 +23250,7 @@
         <v>-9.413850870677146</v>
       </c>
       <c r="D422" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E422">
         <v>-8.460862700719371</v>
@@ -23300,7 +23300,7 @@
         <v>-9.504301489099706</v>
       </c>
       <c r="D423" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E423">
         <v>-8.460862700719371</v>
@@ -23350,7 +23350,7 @@
         <v>-9.381313319141935</v>
       </c>
       <c r="D424" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E424">
         <v>-8.460862700719371</v>
@@ -23400,7 +23400,7 @@
         <v>-7.960412082296807</v>
       </c>
       <c r="D425" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E425">
         <v>-7.188091863543228</v>
@@ -23450,7 +23450,7 @@
         <v>-7.928542481965792</v>
       </c>
       <c r="D426" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E426">
         <v>-7.188091863543228</v>
@@ -23500,7 +23500,7 @@
         <v>-7.787273706198183</v>
       </c>
       <c r="D427" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E427">
         <v>-7.188091863543228</v>
@@ -23550,7 +23550,7 @@
         <v>-9.172895884074581</v>
       </c>
       <c r="D428" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E428">
         <v>-8.145576045355</v>
@@ -23600,7 +23600,7 @@
         <v>-9.058289567940399</v>
       </c>
       <c r="D429" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E429">
         <v>-8.145576045355</v>
@@ -23650,7 +23650,7 @@
         <v>-7.622862522769601</v>
       </c>
       <c r="D430" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E430">
         <v>-6.959864303403672</v>
@@ -23700,7 +23700,7 @@
         <v>-7.631631429214679</v>
       </c>
       <c r="D431" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E431">
         <v>-6.959864303403672</v>
@@ -23750,7 +23750,7 @@
         <v>-7.222167461470761</v>
       </c>
       <c r="D432" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E432">
         <v>-6.959864303403672</v>
@@ -23800,7 +23800,7 @@
         <v>-7.490685032440284</v>
       </c>
       <c r="D433" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E433">
         <v>-6.959864303403672</v>
@@ -23850,7 +23850,7 @@
         <v>-8.561827797884455</v>
       </c>
       <c r="D434" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E434">
         <v>-7.564229169582681</v>
@@ -23900,7 +23900,7 @@
         <v>-8.46267651116753</v>
       </c>
       <c r="D435" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E435">
         <v>-7.564229169582681</v>
@@ -23950,7 +23950,7 @@
         <v>-7.05578182799783</v>
       </c>
       <c r="D436" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E436">
         <v>-6.720998980224341</v>
@@ -24000,7 +24000,7 @@
         <v>-6.680647007658305</v>
       </c>
       <c r="D437" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E437">
         <v>-6.720998980224341</v>
@@ -24050,7 +24050,7 @@
         <v>-6.943814760752625</v>
       </c>
       <c r="D438" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E438">
         <v>-6.720998980224341</v>
@@ -24100,7 +24100,7 @@
         <v>-7.900748535322215</v>
       </c>
       <c r="D439" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E439">
         <v>-7.068198896242816</v>
@@ -24150,7 +24150,7 @@
         <v>-7.954473715782516</v>
       </c>
       <c r="D440" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E440">
         <v>-7.068198896242816</v>
@@ -24200,7 +24200,7 @@
         <v>-7.896025874307643</v>
       </c>
       <c r="D441" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E441">
         <v>-7.068198896242816</v>
@@ -24250,7 +24250,7 @@
         <v>-6.218598358361149</v>
       </c>
       <c r="D442" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E442">
         <v>-6.369374437623716</v>
@@ -24300,7 +24300,7 @@
         <v>-6.477201415688539</v>
       </c>
       <c r="D443" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E443">
         <v>-6.369374437623716</v>
@@ -24350,7 +24350,7 @@
         <v>-6.477356631541051</v>
       </c>
       <c r="D444" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E444">
         <v>-6.369374437623716</v>
@@ -24400,7 +24400,7 @@
         <v>0.1544375412573284</v>
       </c>
       <c r="D445" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E445">
         <v>0.7763231468178482</v>
@@ -24450,7 +24450,7 @@
         <v>0.162551935696813</v>
       </c>
       <c r="D446" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E446">
         <v>0.7763231468178482</v>
@@ -24500,7 +24500,7 @@
         <v>1.050094357938882</v>
       </c>
       <c r="D447" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E447">
         <v>0.5910371607191394</v>
@@ -24700,7 +24700,7 @@
         <v>-0.05317325947102702</v>
       </c>
       <c r="D451" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E451">
         <v>0.5712288406437764</v>
@@ -24750,7 +24750,7 @@
         <v>-0.04757535958582615</v>
       </c>
       <c r="D452" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E452">
         <v>0.5712288406437764</v>
@@ -24800,7 +24800,7 @@
         <v>0.8500330408733774</v>
       </c>
       <c r="D453" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E453">
         <v>0.392234090930776</v>
@@ -25000,7 +25000,7 @@
         <v>-0.2692961577804383</v>
       </c>
       <c r="D457" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E457">
         <v>0.3577256138290235</v>
@@ -25050,7 +25050,7 @@
         <v>-0.2663179293898956</v>
       </c>
       <c r="D458" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E458">
         <v>0.3577256138290235</v>
@@ -25100,7 +25100,7 @@
         <v>0.6417691570479445</v>
       </c>
       <c r="D459" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E459">
         <v>0.1852800428526731</v>
@@ -25300,7 +25300,7 @@
         <v>0.05587008030584961</v>
       </c>
       <c r="D463" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E463">
         <v>0.6789504429688105</v>
@@ -25350,7 +25350,7 @@
         <v>0.06278971764289132</v>
       </c>
       <c r="D464" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E464">
         <v>0.6789504429688105</v>
@@ -25400,7 +25400,7 @@
         <v>0.9551111682947298</v>
       </c>
       <c r="D465" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E465">
         <v>0.4966513496262088</v>
@@ -25600,7 +25600,7 @@
         <v>-0.1893348809203133</v>
       </c>
       <c r="D469" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E469">
         <v>0.4367176630908425</v>
@@ -25650,7 +25650,7 @@
         <v>-0.1853874249314682</v>
       </c>
       <c r="D470" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E470">
         <v>0.4367176630908425</v>
@@ -25700,7 +25700,7 @@
         <v>0.7188227511131551</v>
       </c>
       <c r="D471" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E471">
         <v>0.2618490231187316</v>
@@ -25900,7 +25900,7 @@
         <v>4.371485982915774</v>
       </c>
       <c r="D475" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E475">
         <v>4.962528234821984</v>
@@ -25950,7 +25950,7 @@
         <v>5.060047010261989</v>
       </c>
       <c r="D476" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E476">
         <v>4.670741844866129</v>
@@ -26100,7 +26100,7 @@
         <v>3.620560894635664</v>
       </c>
       <c r="D479" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E479">
         <v>4.229589376201279</v>
@@ -26150,7 +26150,7 @@
         <v>4.317639349991246</v>
       </c>
       <c r="D480" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E480">
         <v>3.938374978158294</v>
@@ -26200,7 +26200,7 @@
         <v>4.370574873318176</v>
       </c>
       <c r="D481" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E481">
         <v>3.818139087890952</v>
@@ -26300,7 +26300,7 @@
         <v>6.853299645934258</v>
       </c>
       <c r="D483" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E483">
         <v>5.774682369171286</v>
@@ -26350,7 +26350,7 @@
         <v>6.891491094566248</v>
       </c>
       <c r="D484" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E484">
         <v>5.774682369171286</v>
@@ -26400,7 +26400,7 @@
         <v>5.361224864970907</v>
       </c>
       <c r="D485" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E485">
         <v>5.018618668978591</v>
@@ -26450,7 +26450,7 @@
         <v>5.403937692022923</v>
       </c>
       <c r="D486" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E486">
         <v>5.018618668978591</v>
@@ -26500,7 +26500,7 @@
         <v>5.435905841926575</v>
       </c>
       <c r="D487" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E487">
         <v>5.018618668978591</v>
@@ -26550,7 +26550,7 @@
         <v>6.006575212731824</v>
       </c>
       <c r="D488" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E488">
         <v>5.049928678956259</v>
@@ -26586,7 +26586,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26600,7 +26600,7 @@
         <v>6.064211272564705</v>
       </c>
       <c r="D489" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E489">
         <v>5.049928678956259</v>
@@ -26636,7 +26636,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26650,7 +26650,7 @@
         <v>4.663870399629863</v>
       </c>
       <c r="D490" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E490">
         <v>4.316971023154751</v>
@@ -26686,7 +26686,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26700,7 +26700,7 @@
         <v>4.677416309880542</v>
       </c>
       <c r="D491" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E491">
         <v>4.316971023154751</v>
@@ -26736,7 +26736,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26750,7 +26750,7 @@
         <v>4.678449851055503</v>
       </c>
       <c r="D492" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E492">
         <v>4.316971023154751</v>
@@ -26786,7 +26786,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26800,7 +26800,7 @@
         <v>5.45724271386503</v>
       </c>
       <c r="D493" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E493">
         <v>4.579727583892824</v>
@@ -26850,7 +26850,7 @@
         <v>5.527493925028882</v>
       </c>
       <c r="D494" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E494">
         <v>4.579727583892824</v>
@@ -26900,7 +26900,7 @@
         <v>4.201445199623705</v>
       </c>
       <c r="D495" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E495">
         <v>3.460664324521434</v>
@@ -26950,7 +26950,7 @@
         <v>4.150453975773659</v>
       </c>
       <c r="D496" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E496">
         <v>3.460664324521434</v>
@@ -27000,7 +27000,7 @@
         <v>4.187032365117255</v>
       </c>
       <c r="D497" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E497">
         <v>3.460664324521434</v>
@@ -27050,7 +27050,7 @@
         <v>4.42199553766301</v>
       </c>
       <c r="D498" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E498">
         <v>3.693607871486083</v>
@@ -27100,7 +27100,7 @@
         <v>4.365726240572206</v>
       </c>
       <c r="D499" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E499">
         <v>3.693607871486083</v>
@@ -27150,7 +27150,7 @@
         <v>4.516020692330457</v>
       </c>
       <c r="D500" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E500">
         <v>3.693607871486083</v>
@@ -27200,7 +27200,7 @@
         <v>3.247044122637031</v>
       </c>
       <c r="D501" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E501">
         <v>2.605123035361114</v>
@@ -27250,7 +27250,7 @@
         <v>3.194659905181848</v>
       </c>
       <c r="D502" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E502">
         <v>2.605123035361114</v>
@@ -27300,7 +27300,7 @@
         <v>-3.705984123275019</v>
       </c>
       <c r="D503" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E503">
         <v>-2.970035313701199</v>
@@ -27350,7 +27350,7 @@
         <v>-3.693186241046869</v>
       </c>
       <c r="D504" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E504">
         <v>-2.970035313701199</v>
@@ -27400,7 +27400,7 @@
         <v>-2.752427193387811</v>
       </c>
       <c r="D505" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E505">
         <v>-3.420167707261241</v>
@@ -27450,7 +27450,7 @@
         <v>-2.600361880106711</v>
       </c>
       <c r="D506" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E506">
         <v>-3.420167707261241</v>
@@ -27500,7 +27500,7 @@
         <v>-3.678102393980136</v>
       </c>
       <c r="D507" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E507">
         <v>-3.136716692222066</v>
@@ -27550,7 +27550,7 @@
         <v>-4.366813091974395</v>
       </c>
       <c r="D508" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E508">
         <v>-3.818652183810219</v>
@@ -27600,7 +27600,7 @@
         <v>-4.484310216846968</v>
       </c>
       <c r="D509" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E509">
         <v>-3.818652183810219</v>
@@ -27650,7 +27650,7 @@
         <v>-4.322051603836151</v>
       </c>
       <c r="D510" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E510">
         <v>-3.818652183810219</v>
@@ -27700,7 +27700,7 @@
         <v>-3.347068854600705</v>
       </c>
       <c r="D511" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E511">
         <v>-4.118163659577004</v>
@@ -27750,7 +27750,7 @@
         <v>-3.324798741080183</v>
       </c>
       <c r="D512" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E512">
         <v>-4.118163659577004</v>
@@ -27800,7 +27800,7 @@
         <v>-3.351387820544549</v>
       </c>
       <c r="D513" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E513">
         <v>-4.118163659577004</v>
@@ -27850,7 +27850,7 @@
         <v>-4.379071704985211</v>
       </c>
       <c r="D514" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E514">
         <v>-3.832482625520846</v>
@@ -27900,7 +27900,7 @@
         <v>8.995980915690074</v>
       </c>
       <c r="D515" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E515">
         <v>10.66390789578366</v>
@@ -27950,7 +27950,7 @@
         <v>11.51142958743078</v>
       </c>
       <c r="D516" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E516">
         <v>11.61008037782884</v>
@@ -28000,7 +28000,7 @@
         <v>11.33896292349641</v>
       </c>
       <c r="D517" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E517">
         <v>11.61008037782884</v>
@@ -28050,7 +28050,7 @@
         <v>11.25741689188049</v>
       </c>
       <c r="D518" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E518">
         <v>11.61008037782884</v>
@@ -28100,7 +28100,7 @@
         <v>11.28637455971803</v>
       </c>
       <c r="D519" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E519">
         <v>11.61008037782884</v>
@@ -28150,7 +28150,7 @@
         <v>9.394053857479914</v>
       </c>
       <c r="D520" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E520">
         <v>11.10574062904685</v>
@@ -28200,7 +28200,7 @@
         <v>11.96926052402832</v>
       </c>
       <c r="D521" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E521">
         <v>11.78545564208547</v>
@@ -28250,7 +28250,7 @@
         <v>11.76715013038619</v>
       </c>
       <c r="D522" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E522">
         <v>11.78545564208547</v>
@@ -28300,7 +28300,7 @@
         <v>11.79715013038619</v>
       </c>
       <c r="D523" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E523">
         <v>11.78545564208547</v>
@@ -28350,7 +28350,7 @@
         <v>11.75785102268897</v>
       </c>
       <c r="D524" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E524">
         <v>11.78545564208547</v>
@@ -28400,7 +28400,7 @@
         <v>6.4997071892945</v>
       </c>
       <c r="D525" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E525">
         <v>7.893221100174392</v>
@@ -28600,7 +28600,7 @@
         <v>8.621088353970423</v>
       </c>
       <c r="D529" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E529">
         <v>8.269277714135617</v>
@@ -28650,7 +28650,7 @@
         <v>8.578286988055545</v>
       </c>
       <c r="D530" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E530">
         <v>8.269277714135617</v>
@@ -28700,7 +28700,7 @@
         <v>8.739580302223263</v>
       </c>
       <c r="D531" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E531">
         <v>8.269277714135617</v>
@@ -28750,7 +28750,7 @@
         <v>8.957510999554914</v>
       </c>
       <c r="D532" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E532">
         <v>8.269277714135617</v>
@@ -29000,7 +29000,7 @@
         <v>1.438738012295818</v>
       </c>
       <c r="D537" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E537">
         <v>2.100412073152636</v>
@@ -29050,7 +29050,7 @@
         <v>1.573030977807695</v>
       </c>
       <c r="D538" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E538">
         <v>2.100412073152636</v>
@@ -29100,7 +29100,7 @@
         <v>1.547818547789148</v>
       </c>
       <c r="D539" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E539">
         <v>2.100412073152636</v>
@@ -29250,7 +29250,7 @@
         <v>-0.8761721984660475</v>
       </c>
       <c r="D542" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E542">
         <v>-1.556082773365931</v>
@@ -29300,7 +29300,7 @@
         <v>-1.017858379148869</v>
       </c>
       <c r="D543" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E543">
         <v>-1.556082773365931</v>
@@ -29350,7 +29350,7 @@
         <v>-0.5723250526030199</v>
       </c>
       <c r="D544" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E544">
         <v>-1.556082773365931</v>
@@ -29400,7 +29400,7 @@
         <v>-1.931822609108822</v>
       </c>
       <c r="D545" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E545">
         <v>-1.673095771397564</v>
@@ -29450,7 +29450,7 @@
         <v>-2.066468132763205</v>
       </c>
       <c r="D546" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E546">
         <v>-1.673095771397564</v>
@@ -29500,7 +29500,7 @@
         <v>-1.956055114369123</v>
       </c>
       <c r="D547" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E547">
         <v>-1.673095771397564</v>
@@ -29550,7 +29550,7 @@
         <v>-1.910907147220547</v>
       </c>
       <c r="D548" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E548">
         <v>-1.673095771397564</v>
@@ -29600,7 +29600,7 @@
         <v>-1.911499015814858</v>
       </c>
       <c r="D549" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E549">
         <v>-1.673095771397564</v>
@@ -29650,7 +29650,7 @@
         <v>-2.047060001357517</v>
       </c>
       <c r="D550" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E550">
         <v>-1.673095771397564</v>
@@ -29850,7 +29850,7 @@
         <v>-1.458250204365703</v>
       </c>
       <c r="D554" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E554">
         <v>-2.203959675076526</v>
@@ -29950,7 +29950,7 @@
         <v>-1.426121365901643</v>
       </c>
       <c r="D556" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E556">
         <v>-1.878985527382707</v>
@@ -30000,7 +30000,7 @@
         <v>-1.43657143149991</v>
       </c>
       <c r="D557" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E557">
         <v>-1.878985527382707</v>
@@ -30050,7 +30050,7 @@
         <v>-1.282291566067462</v>
       </c>
       <c r="D558" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E558">
         <v>-1.878985527382707</v>
@@ -30100,7 +30100,7 @@
         <v>-2.390900427299799</v>
       </c>
       <c r="D559" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E559">
         <v>-1.749918412157532</v>
@@ -30150,7 +30150,7 @@
         <v>-1.371342304503491</v>
       </c>
       <c r="D560" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E560">
         <v>-2.176137742690791</v>
@@ -30200,7 +30200,7 @@
         <v>-2.66184968886377</v>
       </c>
       <c r="D561" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E561">
         <v>-3.062340696434903</v>
@@ -30250,7 +30250,7 @@
         <v>-1.173473832043332</v>
       </c>
       <c r="D562" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E562">
         <v>-1.733424630557323</v>
@@ -30300,7 +30300,7 @@
         <v>-1.200137867726374</v>
       </c>
       <c r="D563" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E563">
         <v>-1.733424630557323</v>
@@ -30350,7 +30350,7 @@
         <v>-1.042228008991366</v>
       </c>
       <c r="D564" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E564">
         <v>-1.733424630557323</v>
@@ -30400,7 +30400,7 @@
         <v>-2.127604913087305</v>
       </c>
       <c r="D565" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E565">
         <v>-1.505014864011352</v>
@@ -30450,7 +30450,7 @@
         <v>-1.173621436501358</v>
       </c>
       <c r="D566" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E566">
         <v>-1.913326227585305</v>
@@ -30500,7 +30500,7 @@
         <v>-1.12934275099936</v>
       </c>
       <c r="D567" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E567">
         <v>-1.913326227585305</v>
@@ -30600,7 +30600,7 @@
         <v>-1.009918389553857</v>
       </c>
       <c r="D569" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E569">
         <v>-1.567675915850558</v>
@@ -30650,7 +30650,7 @@
         <v>-1.047078799419653</v>
       </c>
       <c r="D570" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E570">
         <v>-1.567675915850558</v>
@@ -30700,7 +30700,7 @@
         <v>-0.8868190061661174</v>
       </c>
       <c r="D571" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E571">
         <v>-1.567675915850558</v>
@@ -30750,7 +30750,7 @@
         <v>-1.957156329343485</v>
       </c>
       <c r="D572" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E572">
         <v>-1.346472615161401</v>
@@ -30800,7 +30800,7 @@
         <v>-1.016645810663759</v>
       </c>
       <c r="D573" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E573">
         <v>-1.743190968443955</v>
@@ -30850,7 +30850,7 @@
         <v>-0.9726804497642316</v>
       </c>
       <c r="D574" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E574">
         <v>-1.743190968443955</v>
@@ -30900,7 +30900,7 @@
         <v>-2.23129488574537</v>
       </c>
       <c r="D575" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E575">
         <v>-2.752324990932166</v>
@@ -30950,7 +30950,7 @@
         <v>-2.130775299238296</v>
       </c>
       <c r="D576" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E576">
         <v>-2.752324990932166</v>
@@ -31000,7 +31000,7 @@
         <v>-0.896848743456049</v>
       </c>
       <c r="D577" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E577">
         <v>-1.453090010130747</v>
@@ -31050,7 +31050,7 @@
         <v>-0.9412655386557081</v>
       </c>
       <c r="D578" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E578">
         <v>-1.453090010130747</v>
@@ -31100,7 +31100,7 @@
         <v>-0.7793811815214564</v>
       </c>
       <c r="D579" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E579">
         <v>-1.453090010130747</v>
@@ -31150,7 +31150,7 @@
         <v>-1.860567553008542</v>
       </c>
       <c r="D580" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E580">
         <v>-1.236868705342454</v>
@@ -31200,7 +31200,7 @@
         <v>-0.9081249434319556</v>
       </c>
       <c r="D581" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E581">
         <v>-1.625572543480143</v>
@@ -31250,7 +31250,7 @@
         <v>-0.8643761910498551</v>
       </c>
       <c r="D582" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E582">
         <v>-1.625572543480143</v>
@@ -31500,7 +31500,7 @@
         <v>2.369548064861299</v>
       </c>
       <c r="D587" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E587">
         <v>1.926875447544282</v>
@@ -31550,7 +31550,7 @@
         <v>2.406754555749798</v>
       </c>
       <c r="D588" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E588">
         <v>1.926875447544282</v>
@@ -31600,7 +31600,7 @@
         <v>2.636430011324778</v>
       </c>
       <c r="D589" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E589">
         <v>1.926875447544282</v>
@@ -31750,7 +31750,7 @@
         <v>1.522496508679898</v>
       </c>
       <c r="D592" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E592">
         <v>0.6622717696267184</v>
@@ -31800,7 +31800,7 @@
         <v>0.1531498180160149</v>
       </c>
       <c r="D593" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E593">
         <v>0.9108693301133393</v>
@@ -31850,7 +31850,7 @@
         <v>0.1409442431310648</v>
       </c>
       <c r="D594" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E594">
         <v>0.9108693301133393</v>
@@ -31900,7 +31900,7 @@
         <v>0.1454303059186906</v>
       </c>
       <c r="D595" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E595">
         <v>0.9108693301133393</v>
@@ -31950,7 +31950,7 @@
         <v>1.410955900715591</v>
       </c>
       <c r="D596" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E596">
         <v>0.5447199911733147</v>
@@ -32000,7 +32000,7 @@
         <v>0.02936423312947767</v>
       </c>
       <c r="D597" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E597">
         <v>0.7855252936185178</v>
@@ -32050,7 +32050,7 @@
         <v>0.01760393013260675</v>
       </c>
       <c r="D598" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E598">
         <v>0.7855252936185178</v>
@@ -32100,7 +32100,7 @@
         <v>0.02320317264043581</v>
       </c>
       <c r="D599" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E599">
         <v>0.7855252936185178</v>
@@ -32150,7 +32150,7 @@
         <v>1.411909103777088</v>
       </c>
       <c r="D600" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E600">
         <v>0.545724564459686</v>
@@ -32200,7 +32200,7 @@
         <v>0.03042207924163876</v>
       </c>
       <c r="D601" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E601">
         <v>0.7865964579371276</v>
@@ -32250,7 +32250,7 @@
         <v>0.0186579710429271</v>
       </c>
       <c r="D602" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E602">
         <v>0.7865964579371276</v>
@@ -32300,7 +32300,7 @@
         <v>0.02424770054614989</v>
       </c>
       <c r="D603" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E603">
         <v>0.7865964579371276</v>
@@ -32350,7 +32350,7 @@
         <v>1.336834708204746</v>
       </c>
       <c r="D604" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E604">
         <v>0.4666042433774571</v>
@@ -32400,7 +32400,7 @@
         <v>-0.05289401644343528</v>
       </c>
       <c r="D605" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E605">
         <v>0.7022314186013414</v>
@@ -32450,7 +32450,7 @@
         <v>-0.06435842645623069</v>
       </c>
       <c r="D606" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E606">
         <v>0.7022314186013414</v>
@@ -32500,7 +32500,7 @@
         <v>-0.05801945148821375</v>
       </c>
       <c r="D607" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E607">
         <v>0.7022314186013414</v>
@@ -32550,7 +32550,7 @@
         <v>1.405196855980458</v>
       </c>
       <c r="D608" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E608">
         <v>0.5386505787578475</v>
@@ -32600,7 +32600,7 @@
         <v>0.02297295793440135</v>
       </c>
       <c r="D609" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E609">
         <v>0.7790535527285396</v>
@@ -32650,7 +32650,7 @@
         <v>0.01123564513607533</v>
       </c>
       <c r="D610" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E610">
         <v>0.7790535527285396</v>
@@ -32700,7 +32700,7 @@
         <v>0.01689236314026132</v>
       </c>
       <c r="D611" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E611">
         <v>0.7790535527285396</v>
@@ -32750,7 +32750,7 @@
         <v>1.640062494593103</v>
       </c>
       <c r="D612" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E612">
         <v>0.786173646996323</v>
@@ -32800,7 +32800,7 @@
         <v>0.2836222494885536</v>
       </c>
       <c r="D613" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E613">
         <v>0.8556593002896253</v>
@@ -32850,7 +32850,7 @@
         <v>0.2709473493105357</v>
       </c>
       <c r="D614" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E614">
         <v>0.8556593002896253</v>
@@ -32900,7 +32900,7 @@
         <v>0.2742600988654935</v>
       </c>
       <c r="D615" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E615">
         <v>0.8556593002896253</v>
@@ -32950,7 +32950,7 @@
         <v>4.955952265919407</v>
       </c>
       <c r="D616" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E616">
         <v>3.781714175282632</v>
@@ -33000,7 +33000,7 @@
         <v>4.836984732824422</v>
       </c>
       <c r="D617" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E617">
         <v>3.781714175282632</v>
@@ -33050,7 +33050,7 @@
         <v>3.399157889651168</v>
       </c>
       <c r="D618" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E618">
         <v>4.104212001159528</v>
@@ -33100,7 +33100,7 @@
         <v>3.413995555126094</v>
       </c>
       <c r="D619" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E619">
         <v>4.104212001159528</v>
@@ -33150,7 +33150,7 @@
         <v>3.388941443617735</v>
       </c>
       <c r="D620" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E620">
         <v>4.104212001159528</v>
@@ -33250,7 +33250,7 @@
         <v>5.39157323691697</v>
       </c>
       <c r="D622" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E622">
         <v>4.199910307440291</v>
@@ -33300,7 +33300,7 @@
         <v>5.274981818209244</v>
       </c>
       <c r="D623" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E623">
         <v>4.199910307440291</v>
@@ -33350,7 +33350,7 @@
         <v>3.849827585101373</v>
       </c>
       <c r="D624" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E624">
         <v>4.558841887255165</v>
@@ -33400,7 +33400,7 @@
         <v>3.716953213901664</v>
       </c>
       <c r="D625" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E625">
         <v>4.558841887255165</v>
@@ -33450,7 +33450,7 @@
         <v>3.823770376486211</v>
       </c>
       <c r="D626" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E626">
         <v>4.558841887255165</v>
@@ -33500,7 +33500,7 @@
         <v>3.783996120363035</v>
       </c>
       <c r="D627" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E627">
         <v>4.558841887255165</v>
@@ -33550,7 +33550,7 @@
         <v>5.240670261409678</v>
       </c>
       <c r="D628" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E628">
         <v>5.66120447150224</v>
@@ -33600,7 +33600,7 @@
         <v>13.35754674285762</v>
       </c>
       <c r="D629" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E629">
         <v>12.11200719763176</v>
@@ -33650,7 +33650,7 @@
         <v>13.63116000592201</v>
       </c>
       <c r="D630" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E630">
         <v>12.11200719763176</v>
@@ -33700,7 +33700,7 @@
         <v>13.48645284737274</v>
       </c>
       <c r="D631" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E631">
         <v>12.11200719763176</v>
@@ -33750,7 +33750,7 @@
         <v>13.35488379452298</v>
       </c>
       <c r="D632" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E632">
         <v>12.11200719763176</v>
@@ -33950,7 +33950,7 @@
         <v>12.00063570730863</v>
       </c>
       <c r="D636" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E636">
         <v>10.96336131546034</v>
@@ -34000,7 +34000,7 @@
         <v>12.16808033477629</v>
       </c>
       <c r="D637" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E637">
         <v>10.96336131546034</v>
@@ -34050,7 +34050,7 @@
         <v>12.18508198198523</v>
       </c>
       <c r="D638" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E638">
         <v>10.96336131546034</v>
@@ -34100,7 +34100,7 @@
         <v>11.93759839099766</v>
       </c>
       <c r="D639" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E639">
         <v>10.96336131546034</v>
@@ -34150,7 +34150,7 @@
         <v>12.10741586438821</v>
       </c>
       <c r="D640" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E640">
         <v>10.96336131546034</v>
@@ -34200,7 +34200,7 @@
         <v>9.996138178122038</v>
       </c>
       <c r="D641" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E641">
         <v>10.07070134335836</v>
@@ -34250,7 +34250,7 @@
         <v>9.950336290139454</v>
       </c>
       <c r="D642" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E642">
         <v>10.07070134335836</v>
@@ -34300,7 +34300,7 @@
         <v>3.726163694975139</v>
       </c>
       <c r="D643" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E643">
         <v>2.839609794743838</v>
@@ -34336,7 +34336,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -34350,7 +34350,7 @@
         <v>2.070333381900306</v>
       </c>
       <c r="D644" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E644">
         <v>2.539922141074908</v>
@@ -34386,7 +34386,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -34400,7 +34400,7 @@
         <v>2.116517657129328</v>
       </c>
       <c r="D645" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E645">
         <v>2.539922141074908</v>
@@ -34436,7 +34436,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -34450,7 +34450,7 @@
         <v>2.11502886699328</v>
       </c>
       <c r="D646" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E646">
         <v>2.539922141074908</v>
@@ -34486,7 +34486,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -34500,7 +34500,7 @@
         <v>-1.891199427015522</v>
       </c>
       <c r="D647" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E647">
         <v>-1.014426804305828</v>
@@ -34550,7 +34550,7 @@
         <v>-0.2104376111309492</v>
       </c>
       <c r="D648" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E648">
         <v>-1.044462827056231</v>
@@ -34600,7 +34600,7 @@
         <v>-0.08646642933127069</v>
       </c>
       <c r="D649" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E649">
         <v>-1.044462827056231</v>
@@ -34650,7 +34650,7 @@
         <v>-1.78244121340599</v>
       </c>
       <c r="D650" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E650">
         <v>-1.021661386146215</v>
@@ -34700,7 +34700,7 @@
         <v>-1.791643374771013</v>
       </c>
       <c r="D651" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E651">
         <v>-1.021661386146215</v>
@@ -34800,7 +34800,7 @@
         <v>-3.477913686861863</v>
       </c>
       <c r="D653" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E653">
         <v>-4.521174267980019</v>
@@ -34850,7 +34850,7 @@
         <v>-3.500008845709822</v>
       </c>
       <c r="D654" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E654">
         <v>-4.521174267980019</v>
@@ -34900,7 +34900,7 @@
         <v>-5.32431700625196</v>
       </c>
       <c r="D655" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E655">
         <v>-4.437952967810602</v>
@@ -35100,7 +35100,7 @@
         <v>-7.577993318403742</v>
       </c>
       <c r="D659" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E659">
         <v>-6.567354813971781</v>
@@ -35150,7 +35150,7 @@
         <v>-7.616049006530655</v>
       </c>
       <c r="D660" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E660">
         <v>-6.567354813971781</v>
@@ -35200,7 +35200,7 @@
         <v>-2.725135055328662</v>
       </c>
       <c r="D661" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E661">
         <v>-2.204192425359905</v>
@@ -35250,7 +35250,7 @@
         <v>-2.704148294566643</v>
       </c>
       <c r="D662" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E662">
         <v>-2.204192425359905</v>
@@ -35300,7 +35300,7 @@
         <v>-1.813662855840759</v>
       </c>
       <c r="D663" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E663">
         <v>-2.111011489107529</v>
@@ -35350,7 +35350,7 @@
         <v>-1.845002662948879</v>
       </c>
       <c r="D664" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E664">
         <v>-2.111011489107529</v>
@@ -35400,7 +35400,7 @@
         <v>-1.891998249869552</v>
       </c>
       <c r="D665" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E665">
         <v>-2.111011489107529</v>
@@ -35450,7 +35450,7 @@
         <v>1.830334637155163</v>
       </c>
       <c r="D666" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E666">
         <v>2.267871354156875</v>
@@ -35550,7 +35550,7 @@
         <v>1.518226736005792</v>
       </c>
       <c r="D668" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E668">
         <v>1.938055203296901</v>
@@ -35600,7 +35600,7 @@
         <v>1.532693205245188</v>
       </c>
       <c r="D669" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E669">
         <v>1.906531480554312</v>
@@ -35650,7 +35650,7 @@
         <v>2.271617246908757</v>
       </c>
       <c r="D670" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E670">
         <v>2.443417201348617</v>
@@ -35700,7 +35700,7 @@
         <v>1.121481137909713</v>
       </c>
       <c r="D671" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E671">
         <v>1.518799216656364</v>
@@ -35750,7 +35750,7 @@
         <v>1.1435965093108</v>
       </c>
       <c r="D672" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E672">
         <v>1.506034151034157</v>
@@ -35800,7 +35800,7 @@
         <v>1.093271662200239</v>
       </c>
       <c r="D673" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E673">
         <v>1.506034151034157</v>
@@ -35850,7 +35850,7 @@
         <v>1.88237511166083</v>
       </c>
       <c r="D674" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E674">
         <v>1.894895897753045</v>
@@ -35900,7 +35900,7 @@
         <v>0.849444604521004</v>
       </c>
       <c r="D675" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E675">
         <v>1.303653302247787</v>
@@ -35950,7 +35950,7 @@
         <v>0.8477648181552304</v>
       </c>
       <c r="D676" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E676">
         <v>1.303653302247787</v>
@@ -36000,7 +36000,7 @@
         <v>0.7919735158820114</v>
       </c>
       <c r="D677" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E677">
         <v>1.303653302247787</v>
@@ -36100,7 +36100,7 @@
         <v>0.4742545585727438</v>
       </c>
       <c r="D679" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E679">
         <v>0.9209239764164039</v>
@@ -36150,7 +36150,7 @@
         <v>0.4776016477910456</v>
       </c>
       <c r="D680" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E680">
         <v>0.9209239764164039</v>
@@ -36200,7 +36200,7 @@
         <v>0.4397567303627969</v>
       </c>
       <c r="D681" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E681">
         <v>0.9209239764164039</v>
@@ -36250,7 +36250,7 @@
         <v>0.3764261482064555</v>
       </c>
       <c r="D682" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E682">
         <v>0.9209239764164039</v>
@@ -36300,7 +36300,7 @@
         <v>1.247389224131652</v>
       </c>
       <c r="D683" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E683">
         <v>1.332491309195859</v>
@@ -36350,7 +36350,7 @@
         <v>0.06936123169383812</v>
       </c>
       <c r="D684" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E684">
         <v>0.5078944952148738</v>
@@ -36400,7 +36400,7 @@
         <v>0.03202754929901275</v>
       </c>
       <c r="D685" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E685">
         <v>0.5078944952148738</v>
@@ -36450,7 +36450,7 @@
         <v>0.06067852147795705</v>
       </c>
       <c r="D686" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E686">
         <v>0.5078944952148738</v>
@@ -36500,7 +36500,7 @@
         <v>-0.07201953416415208</v>
       </c>
       <c r="D687" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E687">
         <v>0.5078944952148738</v>
@@ -36550,7 +36550,7 @@
         <v>0.07833359180957977</v>
       </c>
       <c r="D688" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E688">
         <v>0.4747573429780569</v>
@@ -36600,7 +36600,7 @@
         <v>0.07349428577797745</v>
       </c>
       <c r="D689" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E689">
         <v>0.4747573429780569</v>
@@ -36650,7 +36650,7 @@
         <v>0.8501534542622782</v>
       </c>
       <c r="D690" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E690">
         <v>0.8793612316938386</v>
@@ -36700,7 +36700,7 @@
         <v>1.041941578678037</v>
       </c>
       <c r="D691" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E691">
         <v>0.8793612316938386</v>
@@ -36750,7 +36750,7 @@
         <v>0.09878287093698646</v>
       </c>
       <c r="D692" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E692">
         <v>0.5379073494309932</v>
@@ -36800,7 +36800,7 @@
         <v>0.06440526340701602</v>
       </c>
       <c r="D693" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E693">
         <v>0.5379073494309932</v>
@@ -36850,7 +36850,7 @@
         <v>0.09312579028866175</v>
       </c>
       <c r="D694" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E694">
         <v>0.5379073494309932</v>
@@ -36900,7 +36900,7 @@
         <v>-0.03943315594804098</v>
       </c>
       <c r="D695" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E695">
         <v>0.5379073494309932</v>
@@ -36950,7 +36950,7 @@
         <v>0.109354989214884</v>
       </c>
       <c r="D696" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E696">
         <v>0.503900763410396</v>
@@ -37000,7 +37000,7 @@
         <v>0.1052807849130097</v>
       </c>
       <c r="D697" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E697">
         <v>0.503900763410396</v>
@@ -37150,7 +37150,7 @@
         <v>0.2871962372863237</v>
       </c>
       <c r="D700" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E700">
         <v>0.9851462492612573</v>
@@ -37200,7 +37200,7 @@
         <v>0.4202978053995725</v>
       </c>
       <c r="D701" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E701">
         <v>0.9851462492612573</v>
@@ -37250,7 +37250,7 @@
         <v>0.423892594321984</v>
       </c>
       <c r="D702" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E702">
         <v>0.9851462492612573</v>
@@ -37300,7 +37300,7 @@
         <v>0.4949561407287284</v>
       </c>
       <c r="D703" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E703">
         <v>0.9851462492612573</v>
@@ -37350,7 +37350,7 @@
         <v>0.4370951998607797</v>
       </c>
       <c r="D704" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E704">
         <v>0.9851462492612573</v>
@@ -37400,7 +37400,7 @@
         <v>0.4441837402800548</v>
       </c>
       <c r="D705" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E705">
         <v>0.9851462492612573</v>
@@ -37450,7 +37450,7 @@
         <v>1.300386876506556</v>
       </c>
       <c r="D706" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E706">
         <v>1.066703016477163</v>
@@ -37500,7 +37500,7 @@
         <v>1.387766562883906</v>
       </c>
       <c r="D707" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E707">
         <v>1.066703016477163</v>
@@ -37550,7 +37550,7 @@
         <v>1.3704879139321</v>
       </c>
       <c r="D708" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E708">
         <v>1.066703016477163</v>
@@ -37600,7 +37600,7 @@
         <v>1.275437395219328</v>
       </c>
       <c r="D709" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E709">
         <v>1.066703016477163</v>
@@ -37650,7 +37650,7 @@
         <v>1.361652497764391</v>
       </c>
       <c r="D710" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E710">
         <v>1.066703016477163</v>
@@ -37700,7 +37700,7 @@
         <v>1.930987869234452</v>
       </c>
       <c r="D711" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E711">
         <v>2.371871770269339</v>
@@ -37750,7 +37750,7 @@
         <v>1.92605256665067</v>
       </c>
       <c r="D712" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E712">
         <v>2.371871770269339</v>
@@ -37800,7 +37800,7 @@
         <v>1.931979302309637</v>
       </c>
       <c r="D713" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E713">
         <v>2.371871770269339</v>
@@ -38050,7 +38050,7 @@
         <v>1.929178123500783</v>
       </c>
       <c r="D718" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E718">
         <v>1.904587279830026</v>
@@ -38100,7 +38100,7 @@
         <v>1.854846069494888</v>
       </c>
       <c r="D719" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E719">
         <v>1.904587279830026</v>
@@ -38150,7 +38150,7 @@
         <v>1.986094439213979</v>
       </c>
       <c r="D720" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E720">
         <v>2.427791166532621</v>
@@ -38400,7 +38400,7 @@
         <v>1.979578720846286</v>
       </c>
       <c r="D725" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E725">
         <v>1.826397195864058</v>
@@ -38450,7 +38450,7 @@
         <v>1.907972820522667</v>
       </c>
       <c r="D726" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E726">
         <v>1.826397195864058</v>
@@ -38700,7 +38700,7 @@
         <v>2.097186801510141</v>
       </c>
       <c r="D731" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E731">
         <v>2.32091239377587</v>
@@ -38750,7 +38750,7 @@
         <v>2.031942288135359</v>
       </c>
       <c r="D732" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E732">
         <v>2.32091239377587</v>
@@ -39300,7 +39300,7 @@
         <v>2.417703574220445</v>
       </c>
       <c r="D743" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E743">
         <v>2.366004733779205</v>
@@ -39350,7 +39350,7 @@
         <v>2.369795720055587</v>
       </c>
       <c r="D744" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E744">
         <v>2.366004733779205</v>
@@ -39400,7 +39400,7 @@
         <v>2.268006981238599</v>
       </c>
       <c r="D745" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E745">
         <v>2.366004733779205</v>
@@ -39650,7 +39650,7 @@
         <v>2.653994288166441</v>
       </c>
       <c r="D750" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E750">
         <v>3.270325396942835</v>
@@ -39700,7 +39700,7 @@
         <v>3.683411667997373</v>
       </c>
       <c r="D751" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E751">
         <v>3.25827796154194</v>
@@ -39750,7 +39750,7 @@
         <v>3.70572139342618</v>
       </c>
       <c r="D752" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E752">
         <v>3.25827796154194</v>
@@ -39800,7 +39800,7 @@
         <v>3.758092829526726</v>
       </c>
       <c r="D753" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E753">
         <v>3.25827796154194</v>
@@ -39850,7 +39850,7 @@
         <v>3.738113399750641</v>
       </c>
       <c r="D754" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E754">
         <v>3.25827796154194</v>
@@ -39900,7 +39900,7 @@
         <v>2.866153368128345</v>
       </c>
       <c r="D755" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E755">
         <v>3.327619714376737</v>
@@ -39950,7 +39950,7 @@
         <v>2.707907697511514</v>
       </c>
       <c r="D756" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E756">
         <v>3.327619714376737</v>
@@ -40000,7 +40000,7 @@
         <v>3.773013759826179</v>
       </c>
       <c r="D757" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E757">
         <v>3.350810436248167</v>
@@ -40050,7 +40050,7 @@
         <v>3.799493645503623</v>
       </c>
       <c r="D758" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E758">
         <v>3.350810436248167</v>
@@ -40100,7 +40100,7 @@
         <v>3.854682757447843</v>
       </c>
       <c r="D759" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E759">
         <v>3.350810436248167</v>
@@ -40150,7 +40150,7 @@
         <v>3.834252499536769</v>
       </c>
       <c r="D760" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E760">
         <v>3.350810436248167</v>
@@ -40200,7 +40200,7 @@
         <v>2.950458229371047</v>
       </c>
       <c r="D761" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E761">
         <v>3.434578689402571</v>
@@ -40250,7 +40250,7 @@
         <v>2.80855507864752</v>
       </c>
       <c r="D762" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E762">
         <v>3.434578689402571</v>
@@ -40300,7 +40300,7 @@
         <v>4.059126950443869</v>
       </c>
       <c r="D763" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E763">
         <v>3.646280787816876</v>
@@ -40350,7 +40350,7 @@
         <v>4.098922795936224</v>
       </c>
       <c r="D764" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E764">
         <v>3.646280787816876</v>
@@ -40400,7 +40400,7 @@
         <v>4.163109178025654</v>
       </c>
       <c r="D765" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E765">
         <v>3.646280787816876</v>
@@ -40450,7 +40450,7 @@
         <v>4.141239356891347</v>
       </c>
       <c r="D766" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E766">
         <v>3.646280787816876</v>
@@ -40500,7 +40500,7 @@
         <v>3.219656552115741</v>
       </c>
       <c r="D767" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E767">
         <v>3.776115064114756</v>
@@ -40550,7 +40550,7 @@
         <v>3.129937568234435</v>
       </c>
       <c r="D768" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E768">
         <v>3.776115064114756</v>
@@ -40600,7 +40600,7 @@
         <v>4.587925539948646</v>
       </c>
       <c r="D769" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E769">
         <v>4.161392287167092</v>
@@ -40650,7 +40650,7 @@
         <v>4.61478704123244</v>
       </c>
       <c r="D770" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E770">
         <v>4.161392287167092</v>
@@ -40700,7 +40700,7 @@
         <v>4.62093591099028</v>
       </c>
       <c r="D771" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E771">
         <v>4.161392287167092</v>
@@ -40750,7 +40750,7 @@
         <v>4.700807783315709</v>
       </c>
       <c r="D772" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E772">
         <v>4.161392287167092</v>
@@ -40800,7 +40800,7 @@
         <v>4.676428283743642</v>
       </c>
       <c r="D773" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E773">
         <v>4.161392287167092</v>
@@ -40850,7 +40850,7 @@
         <v>3.68896641997684</v>
       </c>
       <c r="D774" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E774">
         <v>4.371536273473288</v>
@@ -40900,7 +40900,7 @@
         <v>3.690223279464329</v>
       </c>
       <c r="D775" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E775">
         <v>4.371536273473288</v>
@@ -40950,7 +40950,7 @@
         <v>4.640951769621907</v>
       </c>
       <c r="D776" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E776">
         <v>4.4619926496501</v>
@@ -41000,7 +41000,7 @@
         <v>4.679892441845094</v>
       </c>
       <c r="D777" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E777">
         <v>4.229657336851623</v>
@@ -41050,7 +41050,7 @@
         <v>4.69011559593246</v>
       </c>
       <c r="D778" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E778">
         <v>4.229657336851623</v>
@@ -41100,7 +41100,7 @@
         <v>4.772066184752546</v>
       </c>
       <c r="D779" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E779">
         <v>4.229657336851623</v>
@@ -41150,7 +41150,7 @@
         <v>4.747354090541334</v>
       </c>
       <c r="D780" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E780">
         <v>4.229657336851623</v>
@@ -41200,7 +41200,7 @@
         <v>3.751161617496972</v>
       </c>
       <c r="D781" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E781">
         <v>4.450444351610463</v>
@@ -41250,7 +41250,7 @@
         <v>3.764475032653471</v>
       </c>
       <c r="D782" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E782">
         <v>4.450444351610463</v>
@@ -41300,7 +41300,7 @@
         <v>4.722853199511387</v>
       </c>
       <c r="D783" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E783">
         <v>4.494475032653471</v>
@@ -41350,7 +41350,7 @@
         <v>4.769412494689534</v>
       </c>
       <c r="D784" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E784">
         <v>4.258529056637524</v>
@@ -41400,7 +41400,7 @@
         <v>4.719374147530353</v>
       </c>
       <c r="D785" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E785">
         <v>4.258529056637524</v>
@@ -41450,7 +41450,7 @@
         <v>4.802203899559511</v>
       </c>
       <c r="D786" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E786">
         <v>4.258529056637524</v>
@@ -41500,7 +41500,7 @@
         <v>4.777351139234847</v>
       </c>
       <c r="D787" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E787">
         <v>4.258529056637524</v>
@@ -41550,7 +41550,7 @@
         <v>3.777466180712386</v>
       </c>
       <c r="D788" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E788">
         <v>4.483817387026809</v>
@@ -41600,7 +41600,7 @@
         <v>3.795878742481499</v>
       </c>
       <c r="D789" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E789">
         <v>4.483817387026809</v>
@@ -41700,7 +41700,7 @@
         <v>4.79820132156508</v>
       </c>
       <c r="D791" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E791">
         <v>4.288184799253363</v>
@@ -41750,7 +41750,7 @@
         <v>4.833160015785789</v>
       </c>
       <c r="D792" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E792">
         <v>4.288184799253363</v>
@@ -41800,7 +41800,7 @@
         <v>4.80816276950441</v>
       </c>
       <c r="D793" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E793">
         <v>4.288184799253363</v>
@@ -41850,7 +41850,7 @@
         <v>3.804485054618168</v>
       </c>
       <c r="D794" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E794">
         <v>4.518096680257542</v>
@@ -41900,7 +41900,7 @@
         <v>3.828135232318215</v>
       </c>
       <c r="D795" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E795">
         <v>4.518096680257542</v>
@@ -41950,7 +41950,7 @@
         <v>4.793071896789968</v>
       </c>
       <c r="D796" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E796">
         <v>4.976887297607179</v>
@@ -42000,7 +42000,7 @@
         <v>4.969372152154773</v>
       </c>
       <c r="D797" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E797">
         <v>4.976887297607179</v>
@@ -42050,7 +42050,7 @@
         <v>4.88512898189049</v>
       </c>
       <c r="D798" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E798">
         <v>4.377730105560969</v>
@@ -42100,7 +42100,7 @@
         <v>4.926631791066686</v>
       </c>
       <c r="D799" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E799">
         <v>4.377730105560969</v>
@@ -42150,7 +42150,7 @@
         <v>4.901198270454942</v>
       </c>
       <c r="D800" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E800">
         <v>4.377730105560969</v>
@@ -42200,7 +42200,7 @@
         <v>3.886068354396595</v>
       </c>
       <c r="D801" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E801">
         <v>4.621602765136856</v>
@@ -42250,7 +42250,7 @@
         <v>3.925533476572406</v>
       </c>
       <c r="D802" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E802">
         <v>4.621602765136856</v>
@@ -42300,7 +42300,7 @@
         <v>4.900504450642575</v>
       </c>
       <c r="D803" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E803">
         <v>5.323640452137244</v>
@@ -42350,7 +42350,7 @@
         <v>5.068842699478202</v>
       </c>
       <c r="D804" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E804">
         <v>5.323640452137244</v>
@@ -42400,7 +42400,7 @@
         <v>4.666640897343765</v>
       </c>
       <c r="D805" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E805">
         <v>4.152662706046714</v>
@@ -42450,7 +42450,7 @@
         <v>4.691695419101137</v>
       </c>
       <c r="D806" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E806">
         <v>4.152662706046714</v>
@@ -42500,7 +42500,7 @@
         <v>4.667358450983981</v>
       </c>
       <c r="D807" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E807">
         <v>4.152662706046714</v>
@@ -42550,7 +42550,7 @@
         <v>3.681013037908578</v>
       </c>
       <c r="D808" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E808">
         <v>4.361445685795776</v>
@@ -42600,7 +42600,7 @@
         <v>3.680728132155562</v>
       </c>
       <c r="D809" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E809">
         <v>4.361445685795776</v>
@@ -42650,7 +42650,7 @@
         <v>4.715209316235119</v>
       </c>
       <c r="D810" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E810">
         <v>5.110369355335455</v>
@@ -42700,7 +42700,7 @@
         <v>4.818828730712063</v>
       </c>
       <c r="D811" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E811">
         <v>5.110369355335455</v>
@@ -42750,7 +42750,7 @@
         <v>4.677780979452113</v>
       </c>
       <c r="D812" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E812">
         <v>4.139332770280262</v>
@@ -42786,7 +42786,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42800,7 +42800,7 @@
         <v>4.685525171192977</v>
       </c>
       <c r="D813" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E813">
         <v>4.139332770280262</v>
@@ -42836,7 +42836,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42850,7 +42850,7 @@
         <v>3.668868346126232</v>
       </c>
       <c r="D814" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E814">
         <v>4.346037514002399</v>
@@ -42886,7 +42886,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42900,7 +42900,7 @@
         <v>3.666229188623965</v>
       </c>
       <c r="D815" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E815">
         <v>4.346037514002399</v>
@@ -42936,7 +42936,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42950,7 +42950,7 @@
         <v>4.699557601157337</v>
       </c>
       <c r="D816" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E816">
         <v>5.177220717987302</v>
@@ -42986,7 +42986,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -43000,7 +43000,7 @@
         <v>4.80402129902022</v>
       </c>
       <c r="D817" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E817">
         <v>5.177220717987302</v>
@@ -43036,7 +43036,7 @@
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -43050,7 +43050,7 @@
         <v>3.803770388208568</v>
       </c>
       <c r="D818" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E818">
         <v>4.517189971136271</v>
@@ -43086,7 +43086,7 @@
         <v>1</v>
       </c>
       <c r="P818" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="819" spans="1:16">
@@ -43100,7 +43100,7 @@
         <v>3.827282027634027</v>
       </c>
       <c r="D819" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E819">
         <v>4.517189971136271</v>
@@ -43136,7 +43136,7 @@
         <v>1</v>
       </c>
       <c r="P819" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="820" spans="1:16">
@@ -43150,7 +43150,7 @@
         <v>4.873415313145802</v>
       </c>
       <c r="D820" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E820">
         <v>5.19492340011272</v>
@@ -43186,7 +43186,7 @@
         <v>1</v>
       </c>
       <c r="P820" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="821" spans="1:16">
@@ -43200,7 +43200,7 @@
         <v>4.968500794179431</v>
       </c>
       <c r="D821" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E821">
         <v>5.19492340011272</v>
@@ -43236,7 +43236,7 @@
         <v>1</v>
       </c>
       <c r="P821" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="822" spans="1:16">
@@ -43250,7 +43250,7 @@
         <v>4.15270680227816</v>
       </c>
       <c r="D822" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E822">
         <v>4.95989138417376</v>
@@ -43300,7 +43300,7 @@
         <v>4.243859858869514</v>
       </c>
       <c r="D823" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E823">
         <v>4.95989138417376</v>
@@ -43350,7 +43350,7 @@
         <v>5.32311411416597</v>
       </c>
       <c r="D824" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E824">
         <v>5.313449235585522</v>
@@ -43400,7 +43400,7 @@
         <v>5.393941983526312</v>
       </c>
       <c r="D825" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E825">
         <v>5.313449235585522</v>
@@ -43450,7 +43450,7 @@
         <v>4.427422884586818</v>
       </c>
       <c r="D826" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E826">
         <v>5.308428231915627</v>
@@ -43500,7 +43500,7 @@
         <v>4.571829727187204</v>
       </c>
       <c r="D827" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E827">
         <v>5.308428231915627</v>
@@ -43650,7 +43650,7 @@
         <v>4.492909746290213</v>
       </c>
       <c r="D830" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E830">
         <v>5.391512498969801</v>
@@ -43700,7 +43700,7 @@
         <v>4.650011234541658</v>
       </c>
       <c r="D831" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E831">
         <v>5.391512498969801</v>
@@ -43750,7 +43750,7 @@
         <v>5.699620454673608</v>
       </c>
       <c r="D832" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E832">
         <v>5.584366029175103</v>
@@ -43800,7 +43800,7 @@
         <v>5.808734877829779</v>
       </c>
       <c r="D833" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E833">
         <v>5.584366029175103</v>
@@ -43850,7 +43850,7 @@
         <v>4.400292583551392</v>
       </c>
       <c r="D834" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E834">
         <v>5.274007569238329</v>
@@ -43900,7 +43900,7 @@
         <v>4.539440210041969</v>
       </c>
       <c r="D835" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E835">
         <v>5.274007569238329</v>
@@ -43950,7 +43950,7 @@
         <v>5.577658014435989</v>
       </c>
       <c r="D836" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E836">
         <v>5.419384274951261</v>
@@ -44000,7 +44000,7 @@
         <v>5.695811278340734</v>
       </c>
       <c r="D837" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E837">
         <v>5.419384274951261</v>
@@ -44050,7 +44050,7 @@
         <v>4.244834847003374</v>
       </c>
       <c r="D838" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E838">
         <v>5.076775761772995</v>
@@ -44100,7 +44100,7 @@
         <v>4.353846949697878</v>
       </c>
       <c r="D839" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E839">
         <v>5.076775761772995</v>
@@ -44150,7 +44150,7 @@
         <v>5.441845979293118</v>
       </c>
       <c r="D840" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E840">
         <v>5.241229035520813</v>
@@ -44200,7 +44200,7 @@
         <v>5.506269225223365</v>
       </c>
       <c r="D841" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E841">
         <v>5.241229035520813</v>
@@ -44250,7 +44250,7 @@
         <v>4.273702172751312</v>
       </c>
       <c r="D842" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E842">
         <v>5.113400216498656</v>
@@ -44300,7 +44300,7 @@
         <v>4.38831021426059</v>
       </c>
       <c r="D843" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E843">
         <v>5.113400216498656</v>
@@ -44350,7 +44350,7 @@
         <v>5.479049324240996</v>
       </c>
       <c r="D844" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E844">
         <v>5.245636638515749</v>
@@ -44400,7 +44400,7 @@
         <v>5.54146575073422</v>
       </c>
       <c r="D845" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E845">
         <v>5.245636638515749</v>
@@ -44450,7 +44450,7 @@
         <v>5.560572351202844</v>
       </c>
       <c r="D846" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E846">
         <v>5.245636638515749</v>
@@ -44500,7 +44500,7 @@
         <v>4.347094984058314</v>
       </c>
       <c r="D847" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E847">
         <v>5.206514892876123</v>
@@ -44550,7 +44550,7 @@
         <v>4.475930241663201</v>
       </c>
       <c r="D848" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E848">
         <v>5.206514892876123</v>
@@ -44600,7 +44600,7 @@
         <v>5.573635781593871</v>
       </c>
       <c r="D849" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E849">
         <v>5.027134568809939</v>
@@ -44650,7 +44650,7 @@
         <v>5.630950034039015</v>
       </c>
       <c r="D850" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E850">
         <v>5.027134568809939</v>
@@ -44700,7 +44700,7 @@
         <v>5.633670806314765</v>
       </c>
       <c r="D851" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E851">
         <v>5.027134568809939</v>
@@ -44750,7 +44750,7 @@
         <v>5.402224156621893</v>
       </c>
       <c r="D852" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E852">
         <v>5.844101410902759</v>
@@ -44800,7 +44800,7 @@
         <v>5.365845252056308</v>
       </c>
       <c r="D853" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E853">
         <v>5.844101410902759</v>
@@ -44850,7 +44850,7 @@
         <v>5.351830183888868</v>
       </c>
       <c r="D854" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E854">
         <v>5.844101410902759</v>
@@ -44900,7 +44900,7 @@
         <v>6.177027170255381</v>
       </c>
       <c r="D855" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E855">
         <v>5.99166223366742</v>
@@ -44950,7 +44950,7 @@
         <v>6.176389906463717</v>
       </c>
       <c r="D856" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E856">
         <v>5.99166223366742</v>
@@ -45000,7 +45000,7 @@
         <v>6.145283329101833</v>
       </c>
       <c r="D857" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E857">
         <v>5.99166223366742</v>
@@ -45050,7 +45050,7 @@
         <v>6.120874288201371</v>
       </c>
       <c r="D858" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E858">
         <v>5.99166223366742</v>
@@ -45100,7 +45100,7 @@
         <v>5.357680894209214</v>
       </c>
       <c r="D859" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E859">
         <v>5.805234021262887</v>
@@ -45150,7 +45150,7 @@
         <v>5.321733849528515</v>
       </c>
       <c r="D860" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E860">
         <v>5.805234021262887</v>
@@ -45200,7 +45200,7 @@
         <v>5.307410310014729</v>
       </c>
       <c r="D861" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E861">
         <v>5.805234021262887</v>
@@ -45250,7 +45250,7 @@
         <v>6.132545602111971</v>
       </c>
       <c r="D862" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E862">
         <v>5.861451650138072</v>
@@ -45300,7 +45300,7 @@
         <v>6.135239828860867</v>
       </c>
       <c r="D863" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E863">
         <v>5.861451650138072</v>
@@ -45350,7 +45350,7 @@
         <v>6.106045773846343</v>
       </c>
       <c r="D864" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E864">
         <v>5.861451650138072</v>
@@ -45400,7 +45400,7 @@
         <v>6.081451650138071</v>
       </c>
       <c r="D865" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E865">
         <v>5.861451650138072</v>
@@ -45450,7 +45450,7 @@
         <v>5.32659332168792</v>
       </c>
       <c r="D866" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E866">
         <v>5.778107746071176</v>
@@ -45500,7 +45500,7 @@
         <v>5.290947680064908</v>
       </c>
       <c r="D867" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E867">
         <v>5.778107746071176</v>
@@ -45550,7 +45550,7 @@
         <v>5.276408852652773</v>
       </c>
       <c r="D868" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E868">
         <v>5.778107746071176</v>
@@ -45600,7 +45600,7 @@
         <v>6.101501087170347</v>
       </c>
       <c r="D869" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E869">
         <v>5.779952436422644</v>
@@ -45650,7 +45650,7 @@
         <v>6.10652042322139</v>
       </c>
       <c r="D870" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E870">
         <v>5.779952436422644</v>
@@ -45700,7 +45700,7 @@
         <v>6.078661153176616</v>
       </c>
       <c r="D871" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E871">
         <v>5.779952436422644</v>
@@ -45750,7 +45750,7 @@
         <v>6.053937856729336</v>
       </c>
       <c r="D872" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E872">
         <v>5.779952436422644</v>
@@ -45800,7 +45800,7 @@
         <v>5.388093706617724</v>
       </c>
       <c r="D873" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E873">
         <v>5.831771516854801</v>
@@ -45850,7 +45850,7 @@
         <v>5.351851800874894</v>
       </c>
       <c r="D874" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E874">
         <v>5.831771516854801</v>
@@ -45900,7 +45900,7 @@
         <v>5.337738876405488</v>
       </c>
       <c r="D875" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E875">
         <v>5.831771516854801</v>
@@ -45950,7 +45950,7 @@
         <v>6.162916291511607</v>
       </c>
       <c r="D876" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E876">
         <v>5.809432743446582</v>
@@ -46000,7 +46000,7 @@
         <v>6.163335875781195</v>
       </c>
       <c r="D877" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E877">
         <v>5.809432743446582</v>
@@ -46050,7 +46050,7 @@
         <v>6.132836007491512</v>
       </c>
       <c r="D878" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E878">
         <v>5.809432743446582</v>
@@ -46100,7 +46100,7 @@
         <v>6.10836825280987</v>
       </c>
       <c r="D879" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E879">
         <v>5.809432743446582</v>
@@ -46150,7 +46150,7 @@
         <v>5.504130795560521</v>
       </c>
       <c r="D880" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E880">
         <v>5.933022716347823</v>
@@ -46200,7 +46200,7 @@
         <v>5.46676387648999</v>
       </c>
       <c r="D881" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E881">
         <v>5.933022716347823</v>
@@ -46250,7 +46250,7 @@
         <v>5.453454532968942</v>
       </c>
       <c r="D882" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E882">
         <v>5.933022716347823</v>
@@ -46300,7 +46300,7 @@
         <v>6.278792664264731</v>
       </c>
       <c r="D883" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E883">
         <v>5.82295074691097</v>
@@ -46350,7 +46350,7 @@
         <v>6.270533574292061</v>
       </c>
       <c r="D884" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E884">
         <v>5.82295074691097</v>
@@ -46400,7 +46400,7 @@
         <v>6.235051504122564</v>
       </c>
       <c r="D885" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E885">
         <v>5.854447210967837</v>
@@ -46450,7 +46450,7 @@
         <v>6.211065898009934</v>
       </c>
       <c r="D886" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E886">
         <v>5.854447210967837</v>
@@ -46500,7 +46500,7 @@
         <v>5.527008554379917</v>
       </c>
       <c r="D887" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E887">
         <v>5.952985303683308</v>
@@ -46550,7 +46550,7 @@
         <v>5.489419828783438</v>
       </c>
       <c r="D888" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E888">
         <v>5.952985303683308</v>
@@ -46600,7 +46600,7 @@
         <v>5.47626891849521</v>
       </c>
       <c r="D889" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E889">
         <v>5.952985303683308</v>
@@ -46650,7 +46650,7 @@
         <v>6.301638736437564</v>
       </c>
       <c r="D890" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E890">
         <v>5.842438034547991</v>
@@ -46700,7 +46700,7 @@
         <v>6.291668567550424</v>
       </c>
       <c r="D891" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E891">
         <v>5.842438034547991</v>
@@ -46750,7 +46750,7 @@
         <v>6.255204211337434</v>
       </c>
       <c r="D892" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E892">
         <v>5.805943847222144</v>
@@ -46800,7 +46800,7 @@
         <v>6.231313665164498</v>
       </c>
       <c r="D893" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E893">
         <v>5.805943847222144</v>
@@ -46850,7 +46850,7 @@
         <v>5.362358580199855</v>
       </c>
       <c r="D894" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E894">
         <v>5.809315658623142</v>
@@ -46900,7 +46900,7 @@
         <v>5.326366183992933</v>
       </c>
       <c r="D895" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E895">
         <v>5.809315658623142</v>
@@ -46950,7 +46950,7 @@
         <v>5.31207503842645</v>
       </c>
       <c r="D896" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E896">
         <v>5.809315658623142</v>
@@ -47000,7 +47000,7 @@
         <v>6.137216809313153</v>
       </c>
       <c r="D897" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E897">
         <v>5.660449825716769</v>
@@ -47050,7 +47050,7 @@
         <v>6.139561181431169</v>
       </c>
       <c r="D898" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E898">
         <v>5.660449825716769</v>
@@ -47100,7 +47100,7 @@
         <v>6.110166283943363</v>
       </c>
       <c r="D899" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E899">
         <v>5.660449825716769</v>
@@ -47150,7 +47150,7 @@
         <v>6.085591596603473</v>
       </c>
       <c r="D900" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E900">
         <v>5.660449825716769</v>
@@ -47200,7 +47200,7 @@
         <v>5.21583595429709</v>
       </c>
       <c r="D901" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E901">
         <v>5.6814635058271</v>
@@ -47250,7 +47250,7 @@
         <v>5.181264137565678</v>
       </c>
       <c r="D902" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E902">
         <v>5.6814635058271</v>
@@ -47300,7 +47300,7 @@
         <v>5.16595829237383</v>
       </c>
       <c r="D903" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E903">
         <v>5.6814635058271</v>
@@ -47350,7 +47350,7 @@
         <v>5.990897123335461</v>
       </c>
       <c r="D904" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E904">
         <v>5.530974153520144</v>
@@ -47400,7 +47400,7 @@
         <v>6.00595829237383</v>
       </c>
       <c r="D905" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E905">
         <v>5.530974153520144</v>
@@ -47450,7 +47450,7 @@
         <v>6.004200251407424</v>
       </c>
       <c r="D906" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E906">
         <v>5.530974153520144</v>
@@ -47500,7 +47500,7 @@
         <v>5.981096491596882</v>
       </c>
       <c r="D907" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E907">
         <v>5.530974153520144</v>
@@ -47550,7 +47550,7 @@
         <v>5.955912984481774</v>
       </c>
       <c r="D908" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E908">
         <v>5.530974153520144</v>
@@ -47600,7 +47600,7 @@
         <v>5.246905622239758</v>
       </c>
       <c r="D909" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E909">
         <v>5.708574157910038</v>
@@ -47650,7 +47650,7 @@
         <v>5.212032576040759</v>
       </c>
       <c r="D910" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E910">
         <v>5.708574157910038</v>
@@ -47700,7 +47700,7 @@
         <v>5.19694189475433</v>
       </c>
       <c r="D911" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E911">
         <v>5.708574157910038</v>
@@ -47750,7 +47750,7 @@
         <v>6.021923758497046</v>
       </c>
       <c r="D912" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E912">
         <v>5.558429067851753</v>
@@ -47800,7 +47800,7 @@
         <v>6.03694189475433</v>
       </c>
       <c r="D913" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E913">
         <v>5.558429067851753</v>
@@ -47850,7 +47850,7 @@
         <v>6.032903116390471</v>
       </c>
       <c r="D914" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E914">
         <v>5.558429067851753</v>
@@ -47900,7 +47900,7 @@
         <v>6.008465340366325</v>
       </c>
       <c r="D915" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E915">
         <v>5.558429067851753</v>
@@ -47950,7 +47950,7 @@
         <v>5.983410931594468</v>
       </c>
       <c r="D916" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E916">
         <v>5.558429067851753</v>
@@ -48000,7 +48000,7 @@
         <v>5.260021169191447</v>
       </c>
       <c r="D917" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E917">
         <v>5.720018471732149</v>
@@ -48050,7 +48050,7 @@
         <v>5.22502096394998</v>
       </c>
       <c r="D918" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E918">
         <v>5.720018471732149</v>
@@ -48100,7 +48100,7 @@
         <v>5.210021110551029</v>
       </c>
       <c r="D919" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E919">
         <v>5.720018471732149</v>
@@ -48150,7 +48150,7 @@
         <v>6.035021139871239</v>
       </c>
       <c r="D920" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E920">
         <v>5.570018706293828</v>
@@ -48200,7 +48200,7 @@
         <v>6.050021110551029</v>
       </c>
       <c r="D921" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E921">
         <v>5.570018706293828</v>
@@ -48250,7 +48250,7 @@
         <v>6.045019556579911</v>
       </c>
       <c r="D922" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E922">
         <v>5.570018706293828</v>
@@ -48300,7 +48300,7 @@
         <v>6.020018647653407</v>
       </c>
       <c r="D923" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E923">
         <v>5.570018706293828</v>
@@ -48350,7 +48350,7 @@
         <v>5.995018735614037</v>
       </c>
       <c r="D924" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E924">
         <v>5.570018706293828</v>
@@ -48450,7 +48450,7 @@
         <v>5.615668781285493</v>
       </c>
       <c r="D926" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E926">
         <v>6.030348105553824</v>
@@ -48500,7 +48500,7 @@
         <v>5.577220469001563</v>
       </c>
       <c r="D927" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E927">
         <v>6.030348105553824</v>
@@ -48550,7 +48550,7 @@
         <v>5.56468354920437</v>
       </c>
       <c r="D928" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E928">
         <v>6.030348105553824</v>
@@ -48600,7 +48600,7 @@
         <v>6.390176165244933</v>
       </c>
       <c r="D929" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E929">
         <v>5.917958864945399</v>
@@ -48650,7 +48650,7 @@
         <v>6.373574899054605</v>
       </c>
       <c r="D930" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E930">
         <v>5.917958864945399</v>
@@ -48700,7 +48700,7 @@
         <v>6.333303801797193</v>
       </c>
       <c r="D931" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E931">
         <v>5.884289033878317</v>
@@ -48750,7 +48750,7 @@
         <v>6.309781649918879</v>
       </c>
       <c r="D932" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E932">
         <v>5.884289033878317</v>
@@ -48800,7 +48800,7 @@
         <v>6.262613928093605</v>
       </c>
       <c r="D933" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E933">
         <v>6.212195151647427</v>
@@ -48850,7 +48850,7 @@
         <v>7.24816372476549</v>
       </c>
       <c r="D934" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E934">
         <v>7.595603386150444</v>
@@ -48900,7 +48900,7 @@
         <v>7.261638134101141</v>
       </c>
       <c r="D935" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E935">
         <v>7.595603386150444</v>
@@ -48950,7 +48950,7 @@
         <v>7.253775244709231</v>
       </c>
       <c r="D936" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E936">
         <v>7.595603386150444</v>
@@ -49000,7 +49000,7 @@
         <v>8.181523875261066</v>
       </c>
       <c r="D937" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E937">
         <v>7.445946162670672</v>
@@ -49050,7 +49050,7 @@
         <v>8.030757870733884</v>
       </c>
       <c r="D938" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E938">
         <v>7.445946162670672</v>
@@ -49100,7 +49100,7 @@
         <v>7.913466275542353</v>
       </c>
       <c r="D939" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E939">
         <v>7.567169202558158</v>
@@ -49150,7 +49150,7 @@
         <v>7.897397720238308</v>
       </c>
       <c r="D940" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E940">
         <v>7.567169202558158</v>
@@ -49200,7 +49200,7 @@
         <v>7.886369390677626</v>
       </c>
       <c r="D941" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E941">
         <v>7.567169202558158</v>
@@ -49250,7 +49250,7 @@
         <v>6.461998806928756</v>
       </c>
       <c r="D942" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E942">
         <v>6.809943004706455</v>
@@ -49300,7 +49300,7 @@
         <v>6.455649148235951</v>
       </c>
       <c r="D943" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E943">
         <v>6.809943004706455</v>
@@ -49350,7 +49350,7 @@
         <v>7.28237921649739</v>
       </c>
       <c r="D944" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E944">
         <v>6.678991980784874</v>
@@ -49400,7 +49400,7 @@
         <v>7.198955530379694</v>
       </c>
       <c r="D945" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E945">
         <v>6.678991980784874</v>
@@ -49450,7 +49450,7 @@
         <v>7.120323414275088</v>
       </c>
       <c r="D946" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E946">
         <v>6.757814301673794</v>
@@ -49500,7 +49500,7 @@
         <v>7.100513619059405</v>
       </c>
       <c r="D947" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E947">
         <v>6.757814301673794</v>
@@ -49550,7 +49550,7 @@
         <v>5.391263694581674</v>
       </c>
       <c r="D948" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E948">
         <v>4.981328216936646</v>
@@ -49600,7 +49600,7 @@
         <v>5.376664084342806</v>
       </c>
       <c r="D949" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E949">
         <v>5.183908869880363</v>
@@ -49650,7 +49650,7 @@
         <v>4.255036972488333</v>
       </c>
       <c r="D950" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E950">
         <v>4.585738592012135</v>
@@ -49686,7 +49686,7 @@
         <v>1</v>
       </c>
       <c r="P950" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="951" spans="1:16">
@@ -49736,7 +49736,7 @@
         <v>1</v>
       </c>
       <c r="P951" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="952" spans="1:16">
@@ -49750,7 +49750,7 @@
         <v>3.887235867264729</v>
       </c>
       <c r="D952" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E952">
         <v>4.261316022454437</v>
@@ -49786,7 +49786,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -49800,7 +49800,7 @@
         <v>4.52226704989957</v>
       </c>
       <c r="D953" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E953">
         <v>4.566623250498453</v>
@@ -49836,7 +49836,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -49850,7 +49850,7 @@
         <v>3.595471601271687</v>
       </c>
       <c r="D954" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E954">
         <v>4.003962492151604</v>
@@ -49886,7 +49886,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -49900,7 +49900,7 @@
         <v>4.274122026330736</v>
       </c>
       <c r="D955" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E955">
         <v>4.284760163047268</v>
@@ -49936,7 +49936,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -49950,7 +49950,7 @@
         <v>3.51283445556241</v>
       </c>
       <c r="D956" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E956">
         <v>3.931071587879801</v>
@@ -49986,7 +49986,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -50000,7 +50000,7 @@
         <v>4.203839271176003</v>
       </c>
       <c r="D957" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E957">
         <v>4.224910004360815</v>
@@ -50036,7 +50036,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -50050,7 +50050,7 @@
         <v>3.757771340160315</v>
       </c>
       <c r="D958" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E958">
         <v>4.020831110855603</v>
@@ -50086,7 +50086,7 @@
         <v>1</v>
       </c>
       <c r="P958" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="959" spans="1:16">
@@ -50100,7 +50100,7 @@
         <v>3.577092549221526</v>
       </c>
       <c r="D959" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E959">
         <v>3.987751069163838</v>
@@ -50136,7 +50136,7 @@
         <v>1</v>
       </c>
       <c r="P959" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="960" spans="1:16">
@@ -50186,7 +50186,7 @@
         <v>1</v>
       </c>
       <c r="P960" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="961" spans="1:16">
@@ -50200,7 +50200,7 @@
         <v>3.969181490046898</v>
       </c>
       <c r="D961" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E961">
         <v>4.227966423152568</v>
@@ -50236,7 +50236,7 @@
         <v>1</v>
       </c>
       <c r="P961" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="962" spans="1:16">
@@ -50250,7 +50250,7 @@
         <v>3.987966423152567</v>
       </c>
       <c r="D962" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E962">
         <v>4.227966423152568</v>
@@ -50286,7 +50286,7 @@
         <v>1</v>
       </c>
       <c r="P962" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="963" spans="1:16">
@@ -50336,7 +50336,7 @@
         <v>1</v>
       </c>
       <c r="P963" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="964" spans="1:16">
@@ -50350,7 +50350,7 @@
         <v>4.457464931808846</v>
       </c>
       <c r="D964" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E964">
         <v>4.34281674843841</v>
@@ -50386,7 +50386,7 @@
         <v>1</v>
       </c>
       <c r="P964" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="965" spans="1:16">
@@ -50400,7 +50400,7 @@
         <v>4.129665945672787</v>
       </c>
       <c r="D965" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E965">
         <v>4.385205788683081</v>
@@ -50550,7 +50550,7 @@
         <v>4.608509125339094</v>
       </c>
       <c r="D968" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E968">
         <v>4.501722471963149</v>
@@ -50600,7 +50600,7 @@
         <v>4.165381741025112</v>
       </c>
       <c r="D969" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E969">
         <v>4.420199389644091</v>
@@ -50850,7 +50850,7 @@
         <v>4.358277886497062</v>
       </c>
       <c r="D974" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E974">
         <v>4.609195061586275</v>
@@ -51050,7 +51050,7 @@
         <v>4.823673304938412</v>
       </c>
       <c r="D978" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E978">
         <v>4.78043513295729</v>
@@ -51100,7 +51100,7 @@
         <v>4.773780937032344</v>
       </c>
       <c r="D979" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E979">
         <v>4.78043513295729</v>
@@ -51150,7 +51150,7 @@
         <v>4.76066910325774</v>
       </c>
       <c r="D980" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E980">
         <v>4.78043513295729</v>
@@ -51200,7 +51200,7 @@
         <v>4.781010705652122</v>
       </c>
       <c r="D981" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E981">
         <v>4.78043513295729</v>
@@ -51250,7 +51250,7 @@
         <v>6.134818623398694</v>
       </c>
       <c r="D982" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E982">
         <v>5.774464332861776</v>
@@ -51300,7 +51300,7 @@
         <v>6.102771384660437</v>
       </c>
       <c r="D983" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E983">
         <v>5.778795004029567</v>
@@ -51350,7 +51350,7 @@
         <v>5.514582429707415</v>
       </c>
       <c r="D984" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E984">
         <v>5.241133593669833</v>
@@ -51400,7 +51400,7 @@
         <v>6.089893354328455</v>
       </c>
       <c r="D985" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E985">
         <v>5.69937873528254</v>
@@ -51450,7 +51450,7 @@
         <v>6.090496725476864</v>
       </c>
       <c r="D986" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E986">
         <v>5.69937873528254</v>
@@ -51500,7 +51500,7 @@
         <v>6.083345023798447</v>
       </c>
       <c r="D987" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E987">
         <v>5.69937873528254</v>
@@ -51550,7 +51550,7 @@
         <v>6.151446158250724</v>
       </c>
       <c r="D988" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E988">
         <v>5.740368070715386</v>
@@ -51600,7 +51600,7 @@
         <v>5.471792219876177</v>
       </c>
       <c r="D989" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E989">
         <v>5.499161328418567</v>
@@ -51650,7 +51650,7 @@
         <v>5.429161328418567</v>
       </c>
       <c r="D990" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E990">
         <v>5.499161328418567</v>
@@ -51700,7 +51700,7 @@
         <v>5.859820355215962</v>
       </c>
       <c r="D991" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E991">
         <v>5.498824536056178</v>
@@ -51750,7 +51750,7 @@
         <v>5.962203814850136</v>
       </c>
       <c r="D992" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E992">
         <v>5.498824536056178</v>
@@ -51800,7 +51800,7 @@
         <v>5.867235562966728</v>
       </c>
       <c r="D993" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E993">
         <v>5.498824536056178</v>
@@ -51850,7 +51850,7 @@
         <v>5.864221779328541</v>
       </c>
       <c r="D994" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E994">
         <v>5.498824536056178</v>
@@ -51900,7 +51900,7 @@
         <v>5.891472824538594</v>
       </c>
       <c r="D995" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E995">
         <v>5.498824536056178</v>
@@ -51950,7 +51950,7 @@
         <v>5.933527959091345</v>
       </c>
       <c r="D996" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E996">
         <v>5.516806571577774</v>
@@ -52100,7 +52100,7 @@
         <v>5.536448803884926</v>
       </c>
       <c r="D999" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E999">
         <v>5.114647162880539</v>
@@ -52150,7 +52150,7 @@
         <v>5.473079556721592</v>
       </c>
       <c r="D1000" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E1000">
         <v>5.114647162880539</v>
@@ -52200,7 +52200,7 @@
         <v>5.516088475684048</v>
       </c>
       <c r="D1001" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E1001">
         <v>5.088556902345189</v>
@@ -52250,7 +52250,7 @@
         <v>4.87693542544124</v>
       </c>
       <c r="D1002" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E1002">
         <v>4.790484836705014</v>
@@ -52300,7 +52300,7 @@
         <v>4.782412771064838</v>
       </c>
       <c r="D1003" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E1003">
         <v>4.790484836705014</v>
@@ -52350,7 +52350,7 @@
         <v>5.183884767385427</v>
       </c>
       <c r="D1004" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E1004">
         <v>4.796513208070444</v>
@@ -52400,7 +52400,7 @@
         <v>5.146682382306041</v>
       </c>
       <c r="D1005" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E1005">
         <v>4.796513208070444</v>
@@ -52450,7 +52450,7 @@
         <v>5.170410455522431</v>
       </c>
       <c r="D1006" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E1006">
         <v>4.733927060944326</v>
@@ -52500,7 +52500,7 @@
         <v>4.433208070443044</v>
       </c>
       <c r="D1007" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E1007">
         <v>4.48045274908133</v>
@@ -52550,7 +52550,7 @@
         <v>4.430537336199128</v>
       </c>
       <c r="D1008" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E1008">
         <v>4.48045274908133</v>
@@ -52600,7 +52600,7 @@
         <v>6.107518054315049</v>
       </c>
       <c r="D1009" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E1009">
         <v>5.738203236233369</v>
@@ -52650,7 +52650,7 @@
         <v>6.135203726571758</v>
       </c>
       <c r="D1010" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E1010">
         <v>5.738203236233369</v>
@@ -52700,7 +52700,7 @@
         <v>6.102046072361725</v>
       </c>
       <c r="D1011" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E1011">
         <v>5.738203236233369</v>
@@ -52750,7 +52750,7 @@
         <v>6.120488810422401</v>
       </c>
       <c r="D1012" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E1012">
         <v>5.738203236233369</v>
@@ -52800,7 +52800,7 @@
         <v>6.193632087855306</v>
       </c>
       <c r="D1013" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E1013">
         <v>5.783646464632436</v>
@@ -52850,7 +52850,7 @@
         <v>5.378974678814465</v>
       </c>
       <c r="D1014" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E1014">
         <v>5.579789251726952</v>
@@ -52900,7 +52900,7 @@
         <v>5.416732234956823</v>
       </c>
       <c r="D1015" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E1015">
         <v>5.579789251726952</v>
@@ -52950,7 +52950,7 @@
         <v>5.472103579470241</v>
       </c>
       <c r="D1016" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E1016">
         <v>5.579789251726952</v>
@@ -53000,7 +53000,7 @@
         <v>5.430560694308047</v>
       </c>
       <c r="D1017" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E1017">
         <v>5.579789251726952</v>
@@ -53050,7 +53050,7 @@
         <v>5.402846268497081</v>
       </c>
       <c r="D1018" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E1018">
         <v>5.579789251726952</v>
@@ -53136,7 +53136,7 @@
         <v>1</v>
       </c>
       <c r="P1019" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1020" spans="1:16">
@@ -53186,7 +53186,7 @@
         <v>1</v>
       </c>
       <c r="P1020" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1021" spans="1:16">
@@ -53200,7 +53200,7 @@
         <v>5.020295300931229</v>
       </c>
       <c r="D1021" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E1021">
         <v>5.342572941191464</v>
@@ -53236,7 +53236,7 @@
         <v>1</v>
       </c>
       <c r="P1021" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1022" spans="1:16">
@@ -53250,7 +53250,7 @@
         <v>5.54274578942891</v>
       </c>
       <c r="D1022" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E1022">
         <v>5.322745789428909</v>
@@ -53286,7 +53286,7 @@
         <v>1</v>
       </c>
       <c r="P1022" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1023" spans="1:16">
@@ -53300,7 +53300,7 @@
         <v>5.6130914859038</v>
       </c>
       <c r="D1023" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E1023">
         <v>5.322745789428909</v>
@@ -53336,7 +53336,7 @@
         <v>1</v>
       </c>
       <c r="P1023" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1024" spans="1:16">
@@ -53350,7 +53350,7 @@
         <v>5.147961849725716</v>
       </c>
       <c r="D1024" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E1024">
         <v>5.187875425606993</v>
@@ -53386,7 +53386,7 @@
         <v>1</v>
       </c>
       <c r="P1024" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="1025" spans="1:16">
@@ -53400,7 +53400,7 @@
         <v>4.481259603973901</v>
       </c>
       <c r="D1025" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E1025">
         <v>4.729065207154505</v>
@@ -53450,7 +53450,7 @@
         <v>4.933966438698594</v>
       </c>
       <c r="D1026" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E1026">
         <v>4.713966438698593</v>
@@ -53500,7 +53500,7 @@
         <v>4.545092978128704</v>
       </c>
       <c r="D1027" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E1027">
         <v>4.51376890178677</v>
@@ -53550,7 +53550,7 @@
         <v>4.556417054470637</v>
       </c>
       <c r="D1028" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E1028">
         <v>4.51376890178677</v>
@@ -53600,7 +53600,7 @@
         <v>4.521721707925945</v>
       </c>
       <c r="D1029" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E1029">
         <v>4.242337996671525</v>
@@ -53650,7 +53650,7 @@
         <v>3.995431662159355</v>
       </c>
       <c r="D1030" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E1030">
         <v>4.028576685042651</v>
@@ -53700,7 +53700,7 @@
         <v>4.0220812096942</v>
       </c>
       <c r="D1031" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E1031">
         <v>4.028576685042651</v>
@@ -53750,7 +53750,7 @@
         <v>3.998833472019975</v>
       </c>
       <c r="D1032" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E1032">
         <v>4.028576685042651</v>
@@ -53800,7 +53800,7 @@
         <v>2.312870417300224</v>
       </c>
       <c r="D1033" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E1033">
         <v>2.600174015881064</v>
@@ -53850,7 +53850,7 @@
         <v>2.342806217266434</v>
       </c>
       <c r="D1034" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E1034">
         <v>2.600174015881064</v>
@@ -53900,7 +53900,7 @@
         <v>2.333191417469171</v>
       </c>
       <c r="D1035" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E1035">
         <v>2.600174015881064</v>
@@ -53950,7 +53950,7 @@
         <v>2.830944416286538</v>
       </c>
       <c r="D1036" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E1036">
         <v>2.501072816354117</v>
@@ -54000,7 +54000,7 @@
         <v>3.735551545505884</v>
       </c>
       <c r="D1037" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E1037">
         <v>3.537025852544748</v>
@@ -54050,7 +54050,7 @@
         <v>3.727025852544749</v>
       </c>
       <c r="D1038" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E1038">
         <v>3.537025852544748</v>
@@ -54100,7 +54100,7 @@
         <v>3.707843043382194</v>
       </c>
       <c r="D1039" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E1039">
         <v>3.537025852544748</v>
@@ -54150,7 +54150,7 @@
         <v>3.371288699025316</v>
       </c>
       <c r="D1040" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E1040">
         <v>3.571768922933395</v>
@@ -54200,7 +54200,7 @@
         <v>3.36981439198645</v>
       </c>
       <c r="D1041" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E1041">
         <v>3.571768922933395</v>
@@ -54250,7 +54250,7 @@
         <v>3.347025852544749</v>
       </c>
       <c r="D1042" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E1042">
         <v>3.571768922933395</v>
@@ -54300,7 +54300,7 @@
         <v>3.718820308855666</v>
       </c>
       <c r="D1043" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E1043">
         <v>3.501608848297368</v>
@@ -54350,7 +54350,7 @@
         <v>7.818784706417835</v>
       </c>
       <c r="D1044" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E1044">
         <v>8.66434683659535</v>
@@ -54400,7 +54400,7 @@
         <v>7.736183913922513</v>
       </c>
       <c r="D1045" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E1045">
         <v>8.114051730148025</v>
@@ -54450,7 +54450,7 @@
         <v>5.66445723600427</v>
       </c>
       <c r="D1046" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E1046">
         <v>5.237456064387949</v>
@@ -54500,7 +54500,7 @@
         <v>5.440858208955218</v>
       </c>
       <c r="D1047" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E1047">
         <v>5.007731036597828</v>
@@ -54600,7 +54600,7 @@
         <v>4.988258892022188</v>
       </c>
       <c r="D1049" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E1049">
         <v>4.542731738378961</v>
@@ -54650,7 +54650,7 @@
         <v>5.374367473486714</v>
       </c>
       <c r="D1050" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E1050">
         <v>4.939418637143884</v>
@@ -54700,7 +54700,7 @@
         <v>5.639230769230771</v>
       </c>
       <c r="D1051" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E1051">
         <v>5.211538461538465</v>
@@ -54800,7 +54800,7 @@
         <v>-0.9618136339318442</v>
       </c>
       <c r="D1053" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E1053">
         <v>-0.6309048928601628</v>
@@ -54850,7 +54850,7 @@
         <v>-1.021813633931844</v>
       </c>
       <c r="D1054" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E1054">
         <v>-0.6309048928601628</v>
@@ -54900,10 +54900,10 @@
         <v>-0.4983138263424198</v>
       </c>
       <c r="D1055" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E1055">
-        <v>-0.6731091671907166</v>
+        <v>-0.7326773227710905</v>
       </c>
       <c r="F1055">
         <v>-1</v>
@@ -54912,10 +54912,10 @@
         <v>0.01595831382634242</v>
       </c>
       <c r="H1055">
-        <v>0.01621310916719072</v>
+        <v>0.01625267732277109</v>
       </c>
       <c r="I1055">
-        <v>0.1747953408482967</v>
+        <v>0.2343634964286707</v>
       </c>
       <c r="J1055">
         <v>1.652271852679201</v>
@@ -54927,10 +54927,10 @@
         <v>7.73</v>
       </c>
       <c r="M1055">
-        <v>5.11</v>
+        <v>5.14</v>
       </c>
       <c r="N1055">
-        <v>7.77</v>
+        <v>7.76</v>
       </c>
       <c r="O1055">
         <v>1</v>
@@ -54950,7 +54950,7 @@
         <v>-1.04421149425495</v>
       </c>
       <c r="D1056" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E1056">
         <v>-0.8170515119382786</v>
@@ -55000,7 +55000,7 @@
         <v>-1.104211494254949</v>
       </c>
       <c r="D1057" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E1057">
         <v>-0.8170515119382786</v>
@@ -55050,10 +55050,10 @@
         <v>-0.5772256233441624</v>
       </c>
       <c r="D1058" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E1058">
-        <v>-0.7540809107005373</v>
+        <v>-0.8141244385520068</v>
       </c>
       <c r="F1058">
         <v>-1</v>
@@ -55062,10 +55062,10 @@
         <v>0.01603722562334416</v>
       </c>
       <c r="H1058">
-        <v>0.01629408091070054</v>
+        <v>0.01633412443855201</v>
       </c>
       <c r="I1058">
-        <v>0.1768552873563749</v>
+        <v>0.2368988152078444</v>
       </c>
       <c r="J1058">
         <v>1.668117595049029</v>
@@ -55077,10 +55077,10 @@
         <v>7.73</v>
       </c>
       <c r="M1058">
-        <v>5.11</v>
+        <v>5.14</v>
       </c>
       <c r="N1058">
-        <v>7.77</v>
+        <v>7.76</v>
       </c>
       <c r="O1058">
         <v>1</v>
@@ -55100,7 +55100,7 @@
         <v>-1.097822582940394</v>
       </c>
       <c r="D1059" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E1059">
         <v>-0.8710786311994871</v>
@@ -55150,7 +55150,7 @@
         <v>-1.157822582940394</v>
       </c>
       <c r="D1060" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E1060">
         <v>-0.8710786311994871</v>
@@ -55200,10 +55200,10 @@
         <v>-0.6285685505852232</v>
       </c>
       <c r="D1061" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E1061">
-        <v>-0.8067641151587353</v>
+        <v>-0.8671169377526198</v>
       </c>
       <c r="F1061">
         <v>-1</v>
@@ -55212,10 +55212,10 @@
         <v>0.01608856855058522</v>
       </c>
       <c r="H1061">
-        <v>0.01634676411515874</v>
+        <v>0.01638711693775262</v>
       </c>
       <c r="I1061">
-        <v>0.178195564573512</v>
+        <v>0.2385483871673966</v>
       </c>
       <c r="J1061">
         <v>1.67842741979623</v>
@@ -55227,10 +55227,10 @@
         <v>7.73</v>
       </c>
       <c r="M1061">
-        <v>5.11</v>
+        <v>5.14</v>
       </c>
       <c r="N1061">
-        <v>7.77</v>
+        <v>7.76</v>
       </c>
       <c r="O1061">
         <v>1</v>
@@ -55250,7 +55250,7 @@
         <v>-1.132542776541119</v>
       </c>
       <c r="D1062" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E1062">
         <v>-0.9038625063109409</v>
@@ -55300,7 +55300,7 @@
         <v>-1.192542776541119</v>
       </c>
       <c r="D1063" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E1063">
         <v>-0.9038625063109409</v>
@@ -55350,10 +55350,10 @@
         <v>-0.6618198129182247</v>
       </c>
       <c r="D1064" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E1064">
-        <v>-0.8408833823317536</v>
+        <v>-0.9014365137348754</v>
       </c>
       <c r="F1064">
         <v>-1</v>
@@ -55362,10 +55362,10 @@
         <v>0.01612181981291822</v>
       </c>
       <c r="H1064">
-        <v>0.01638088338233175</v>
+        <v>0.01642143651373488</v>
       </c>
       <c r="I1064">
-        <v>0.179063569413529</v>
+        <v>0.2396167008166508</v>
       </c>
       <c r="J1064">
         <v>1.685104380104061</v>
@@ -55377,10 +55377,10 @@
         <v>7.73</v>
       </c>
       <c r="M1064">
-        <v>5.11</v>
+        <v>5.14</v>
       </c>
       <c r="N1064">
-        <v>7.77</v>
+        <v>7.76</v>
       </c>
       <c r="O1064">
         <v>1</v>
@@ -55400,7 +55400,7 @@
         <v>-1.157889853450652</v>
       </c>
       <c r="D1065" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E1065">
         <v>-0.9277959962389817</v>
@@ -55436,7 +55436,7 @@
         <v>1</v>
       </c>
       <c r="P1065" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="1066" spans="1:16">
@@ -55450,7 +55450,7 @@
         <v>-1.217889853450652</v>
       </c>
       <c r="D1066" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E1066">
         <v>-0.9277959962389817</v>
@@ -55486,7 +55486,7 @@
         <v>1</v>
       </c>
       <c r="P1066" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="1067" spans="1:16">
@@ -55500,10 +55500,10 @@
         <v>-0.6860945134969718</v>
       </c>
       <c r="D1067" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E1067">
-        <v>-0.8657917598332379</v>
+        <v>-0.9264911243723759</v>
       </c>
       <c r="F1067">
         <v>-1</v>
@@ -55512,10 +55512,10 @@
         <v>0.01614609451349697</v>
       </c>
       <c r="H1067">
-        <v>0.01640579175983323</v>
+        <v>0.01644649112437237</v>
       </c>
       <c r="I1067">
-        <v>0.179697246336266</v>
+        <v>0.2403966108754041</v>
       </c>
       <c r="J1067">
         <v>1.689978817971279</v>
@@ -55527,16 +55527,16 @@
         <v>7.73</v>
       </c>
       <c r="M1067">
-        <v>5.11</v>
+        <v>5.14</v>
       </c>
       <c r="N1067">
-        <v>7.77</v>
+        <v>7.76</v>
       </c>
       <c r="O1067">
         <v>1</v>
       </c>
       <c r="P1067" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="1068" spans="1:16">
@@ -55550,10 +55550,10 @@
         <v>-0.7391947253172582</v>
       </c>
       <c r="D1068" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E1068">
-        <v>-0.8657917598332379</v>
+        <v>-0.9264911243723759</v>
       </c>
       <c r="F1068">
         <v>-1</v>
@@ -55562,10 +55562,10 @@
         <v>0.01605919472531726</v>
       </c>
       <c r="H1068">
-        <v>0.01640579175983323</v>
+        <v>0.01644649112437237</v>
       </c>
       <c r="I1068">
-        <v>0.1265970345159797</v>
+        <v>0.1872963990551177</v>
       </c>
       <c r="J1068">
         <v>1.689978817971279</v>
@@ -55577,16 +55577,16 @@
         <v>7.66</v>
       </c>
       <c r="M1068">
-        <v>5.11</v>
+        <v>5.14</v>
       </c>
       <c r="N1068">
-        <v>7.77</v>
+        <v>7.76</v>
       </c>
       <c r="O1068">
         <v>1</v>
       </c>
       <c r="P1068" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="1069" spans="1:16">
@@ -55600,7 +55600,7 @@
         <v>-2.807532631974992</v>
       </c>
       <c r="D1069" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E1069">
         <v>-2.509249826348689</v>
@@ -55644,13 +55644,13 @@
         <v>1</v>
       </c>
       <c r="B1070" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C1070">
-        <v>-2.44794201493401</v>
+        <v>-2.496660757698539</v>
       </c>
       <c r="D1070" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E1070">
         <v>-2.672763877633709</v>
@@ -55659,22 +55659,22 @@
         <v>-1</v>
       </c>
       <c r="G1070">
-        <v>0.01704794201493401</v>
+        <v>0.01781666075769854</v>
       </c>
       <c r="H1070">
         <v>0.01821276387763371</v>
       </c>
       <c r="I1070">
-        <v>0.2248218626996996</v>
+        <v>0.1761031199351706</v>
       </c>
       <c r="J1070">
         <v>2.043593713822644</v>
       </c>
       <c r="K1070">
-        <v>4.77</v>
+        <v>4.97</v>
       </c>
       <c r="L1070">
-        <v>7.3</v>
+        <v>7.66</v>
       </c>
       <c r="M1070">
         <v>5.11</v>
@@ -55686,56 +55686,6 @@
         <v>1</v>
       </c>
       <c r="P1070" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="1071" spans="1:16">
-      <c r="A1071" s="1">
-        <v>2</v>
-      </c>
-      <c r="B1071" t="s">
-        <v>292</v>
-      </c>
-      <c r="C1071">
-        <v>-2.496660757698539</v>
-      </c>
-      <c r="D1071" t="s">
-        <v>468</v>
-      </c>
-      <c r="E1071">
-        <v>-2.672763877633709</v>
-      </c>
-      <c r="F1071">
-        <v>-1</v>
-      </c>
-      <c r="G1071">
-        <v>0.01781666075769854</v>
-      </c>
-      <c r="H1071">
-        <v>0.01821276387763371</v>
-      </c>
-      <c r="I1071">
-        <v>0.1761031199351706</v>
-      </c>
-      <c r="J1071">
-        <v>2.043593713822644</v>
-      </c>
-      <c r="K1071">
-        <v>4.97</v>
-      </c>
-      <c r="L1071">
-        <v>7.66</v>
-      </c>
-      <c r="M1071">
-        <v>5.11</v>
-      </c>
-      <c r="N1071">
-        <v>7.77</v>
-      </c>
-      <c r="O1071">
-        <v>1</v>
-      </c>
-      <c r="P1071" t="s">
         <v>605</v>
       </c>
     </row>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3228" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3234" uniqueCount="608">
   <si>
     <t>trade_time</t>
   </si>
@@ -901,6 +901,9 @@
     <t>2021-11-24</t>
   </si>
   <si>
+    <t>2021-12-13</t>
+  </si>
+  <si>
     <t>2016-04-28</t>
   </si>
   <si>
@@ -1423,16 +1426,13 @@
     <t>2021-12-09</t>
   </si>
   <si>
-    <t>2021-11-22</t>
-  </si>
-  <si>
-    <t>2021-12-13</t>
-  </si>
-  <si>
     <t>2021-11-15</t>
   </si>
   <si>
     <t>2021-12-08</t>
+  </si>
+  <si>
+    <t>2021-12-14</t>
   </si>
   <si>
     <t>2016-03-24</t>
@@ -2195,7 +2195,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1072"/>
+  <dimension ref="A1:P1074"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2256,7 +2256,7 @@
         <v>4.31128552097429</v>
       </c>
       <c r="D2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E2">
         <v>3.491640730717187</v>
@@ -2306,7 +2306,7 @@
         <v>2.930197902571042</v>
       </c>
       <c r="D3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E3">
         <v>3.697845060893099</v>
@@ -2356,7 +2356,7 @@
         <v>2.93171853856563</v>
       </c>
       <c r="D4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E4">
         <v>3.697845060893099</v>
@@ -2456,7 +2456,7 @@
         <v>3.256806675563038</v>
       </c>
       <c r="D6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E6">
         <v>2.536806675563037</v>
@@ -2506,7 +2506,7 @@
         <v>1.909437857449102</v>
       </c>
       <c r="D7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E7">
         <v>2.73123945259945</v>
@@ -2556,7 +2556,7 @@
         <v>1.927571287293738</v>
       </c>
       <c r="D8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E8">
         <v>2.73123945259945</v>
@@ -2656,7 +2656,7 @@
         <v>2.529267581722536</v>
       </c>
       <c r="D10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E10">
         <v>1.809267581722535</v>
@@ -2806,7 +2806,7 @@
         <v>0.9430396109046839</v>
       </c>
       <c r="D13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E13">
         <v>0.8476461186055282</v>
@@ -2856,7 +2856,7 @@
         <v>2.096084795296841</v>
       </c>
       <c r="D14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E14">
         <v>1.37608479529684</v>
@@ -3006,7 +3006,7 @@
         <v>1.855836876417781</v>
       </c>
       <c r="D17" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E17">
         <v>1.13583687641778</v>
@@ -3156,7 +3156,7 @@
         <v>1.689338262028841</v>
       </c>
       <c r="D20" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E20">
         <v>0.96933826202884</v>
@@ -3206,7 +3206,7 @@
         <v>1.627006479834717</v>
       </c>
       <c r="D21" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E21">
         <v>0.9357502825591215</v>
@@ -3356,7 +3356,7 @@
         <v>1.911015876946134</v>
       </c>
       <c r="D24" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E24">
         <v>1.236185039124933</v>
@@ -3456,7 +3456,7 @@
         <v>2.232760263343966</v>
       </c>
       <c r="D26" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E26">
         <v>1.515079422678022</v>
@@ -3656,7 +3656,7 @@
         <v>0.6496455995207633</v>
       </c>
       <c r="D30" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E30">
         <v>1.139659067730454</v>
@@ -3706,7 +3706,7 @@
         <v>0.6621691688877203</v>
       </c>
       <c r="D31" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E31">
         <v>1.139659067730454</v>
@@ -3756,7 +3756,7 @@
         <v>0.5096590677304533</v>
       </c>
       <c r="D32" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E32">
         <v>1.139659067730454</v>
@@ -3906,7 +3906,7 @@
         <v>-0.4482238035193742</v>
       </c>
       <c r="D35" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E35">
         <v>0.05100577720271815</v>
@@ -3956,7 +3956,7 @@
         <v>-0.5789942227972826</v>
       </c>
       <c r="D36" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E36">
         <v>0.05100577720271815</v>
@@ -4006,7 +4006,7 @@
         <v>-0.6485127107485908</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E37">
         <v>0.05100577720271815</v>
@@ -4056,7 +4056,7 @@
         <v>0.5534941892431284</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E38">
         <v>0.1656128422573726</v>
@@ -4206,7 +4206,7 @@
         <v>-1.066969696969696</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E41">
         <v>-0.543771149985659</v>
@@ -4256,7 +4256,7 @@
         <v>-1.17377114998566</v>
       </c>
       <c r="D42" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E42">
         <v>-0.543771149985659</v>
@@ -4306,7 +4306,7 @@
         <v>-1.246436605805691</v>
       </c>
       <c r="D43" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E43">
         <v>-0.543771149985659</v>
@@ -4356,7 +4356,7 @@
         <v>0.007809960806808292</v>
       </c>
       <c r="D44" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E44">
         <v>-0.2591202243252724</v>
@@ -4506,7 +4506,7 @@
         <v>-1.678657860308897</v>
       </c>
       <c r="D47" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E47">
         <v>-1.151600082010416</v>
@@ -4556,7 +4556,7 @@
         <v>-1.781600082010417</v>
       </c>
       <c r="D48" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E48">
         <v>-1.151600082010416</v>
@@ -4606,7 +4606,7 @@
         <v>-1.857481563925816</v>
       </c>
       <c r="D49" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E49">
         <v>-1.151600082010416</v>
@@ -4806,7 +4806,7 @@
         <v>-1.819193108813611</v>
       </c>
       <c r="D53" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E53">
         <v>-1.291248672795858</v>
@@ -4856,7 +4856,7 @@
         <v>-1.921248672795858</v>
       </c>
       <c r="D54" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E54">
         <v>-1.291248672795858</v>
@@ -4906,7 +4906,7 @@
         <v>-1.997869036143985</v>
       </c>
       <c r="D55" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E55">
         <v>-1.291248672795858</v>
@@ -4956,7 +4956,7 @@
         <v>-0.6779710045650891</v>
       </c>
       <c r="D56" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E56">
         <v>-0.8744524579575934</v>
@@ -5006,7 +5006,7 @@
         <v>-0.7891561672790921</v>
       </c>
       <c r="D57" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E57">
         <v>-0.8744524579575934</v>
@@ -5156,7 +5156,7 @@
         <v>0.3390481079807373</v>
       </c>
       <c r="D60" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E60">
         <v>0.8316689003586539</v>
@@ -5206,7 +5206,7 @@
         <v>0.3561344946420899</v>
       </c>
       <c r="D61" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E61">
         <v>0.8316689003586539</v>
@@ -5256,7 +5256,7 @@
         <v>0.2016689003586531</v>
       </c>
       <c r="D62" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E62">
         <v>0.8316689003586539</v>
@@ -5306,7 +5306,7 @@
         <v>0.3550656832089647</v>
       </c>
       <c r="D63" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E63">
         <v>0.8316689003586539</v>
@@ -5506,7 +5506,7 @@
         <v>1.702993205626412</v>
       </c>
       <c r="D67" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E67">
         <v>2.213613017446391</v>
@@ -5556,7 +5556,7 @@
         <v>1.700042623382163</v>
       </c>
       <c r="D68" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E68">
         <v>2.213613017446391</v>
@@ -5606,7 +5606,7 @@
         <v>1.55416430148684</v>
       </c>
       <c r="D69" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E69">
         <v>2.213613017446391</v>
@@ -5656,7 +5656,7 @@
         <v>1.697734695551071</v>
       </c>
       <c r="D70" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E70">
         <v>2.213613017446391</v>
@@ -5706,7 +5706,7 @@
         <v>2.778308822184697</v>
       </c>
       <c r="D71" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E71">
         <v>2.907149147620857</v>
@@ -5756,7 +5756,7 @@
         <v>6.23470991605689</v>
       </c>
       <c r="D72" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E72">
         <v>6.96882467582045</v>
@@ -5792,7 +5792,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5806,7 +5806,7 @@
         <v>6.165186370595404</v>
       </c>
       <c r="D73" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E73">
         <v>6.96882467582045</v>
@@ -5842,7 +5842,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5856,7 +5856,7 @@
         <v>7.462192305683145</v>
       </c>
       <c r="D74" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E74">
         <v>7.5652188186885</v>
@@ -5892,7 +5892,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5906,7 +5906,7 @@
         <v>7.766409955034785</v>
       </c>
       <c r="D75" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E75">
         <v>7.5652188186885</v>
@@ -5942,7 +5942,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -6006,7 +6006,7 @@
         <v>6.790335000164763</v>
       </c>
       <c r="D77" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E77">
         <v>7.58905888555706</v>
@@ -6056,7 +6056,7 @@
         <v>6.74758629353808</v>
       </c>
       <c r="D78" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E78">
         <v>7.58905888555706</v>
@@ -6256,7 +6256,7 @@
         <v>6.426886909355456</v>
       </c>
       <c r="D82" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E82">
         <v>7.170479443185158</v>
@@ -6306,7 +6306,7 @@
         <v>6.354540197150865</v>
       </c>
       <c r="D83" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E83">
         <v>7.170479443185158</v>
@@ -6506,7 +6506,7 @@
         <v>6.205686423858355</v>
       </c>
       <c r="D87" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E87">
         <v>6.974286460418881</v>
@@ -6556,7 +6556,7 @@
         <v>6.17031498633333</v>
       </c>
       <c r="D88" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E88">
         <v>6.974286460418881</v>
@@ -6606,7 +6606,7 @@
         <v>7.467572163512598</v>
       </c>
       <c r="D89" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E89">
         <v>7.999200804331553</v>
@@ -6656,7 +6656,7 @@
         <v>7.771800736433435</v>
       </c>
       <c r="D90" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E90">
         <v>7.999200804331553</v>
@@ -6756,7 +6756,7 @@
         <v>5.758523378301289</v>
       </c>
       <c r="D92" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E92">
         <v>6.469153597378058</v>
@@ -6806,7 +6806,7 @@
         <v>5.695995227937997</v>
       </c>
       <c r="D93" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E93">
         <v>6.469153597378058</v>
@@ -6856,7 +6856,7 @@
         <v>5.575650149522264</v>
       </c>
       <c r="D94" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E94">
         <v>6.469153597378058</v>
@@ -6906,7 +6906,7 @@
         <v>6.970016293417387</v>
       </c>
       <c r="D95" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E95">
         <v>7.634780179426718</v>
@@ -6956,7 +6956,7 @@
         <v>7.273234600612143</v>
       </c>
       <c r="D96" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E96">
         <v>7.634780179426718</v>
@@ -7006,7 +7006,7 @@
         <v>5.679717798863969</v>
       </c>
       <c r="D97" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E97">
         <v>6.421217454115635</v>
@@ -7056,7 +7056,7 @@
         <v>5.650983189414583</v>
       </c>
       <c r="D98" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E98">
         <v>6.421217454115635</v>
@@ -7106,7 +7106,7 @@
         <v>5.530350494139276</v>
       </c>
       <c r="D99" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E99">
         <v>6.421217454115635</v>
@@ -7306,7 +7306,7 @@
         <v>5.621464282690935</v>
       </c>
       <c r="D103" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E103">
         <v>6.359962442366914</v>
@@ -7356,7 +7356,7 @@
         <v>5.593464733382533</v>
       </c>
       <c r="D104" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E104">
         <v>6.359962442366914</v>
@@ -7406,7 +7406,7 @@
         <v>5.472464508036733</v>
       </c>
       <c r="D105" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E105">
         <v>6.359962442366914</v>
@@ -7606,7 +7606,7 @@
         <v>4.812788531912378</v>
       </c>
       <c r="D109" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E109">
         <v>5.509619907373689</v>
@@ -7656,7 +7656,7 @@
         <v>4.794993093023895</v>
       </c>
       <c r="D110" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E110">
         <v>5.509619907373689</v>
@@ -7706,7 +7706,7 @@
         <v>4.668890812468137</v>
       </c>
       <c r="D111" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E111">
         <v>5.509619907373689</v>
@@ -7756,7 +7756,7 @@
         <v>6.099225988855712</v>
       </c>
       <c r="D112" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E112">
         <v>6.844581898111059</v>
@@ -7806,7 +7806,7 @@
         <v>6.071430549967227</v>
       </c>
       <c r="D113" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E113">
         <v>6.844581898111059</v>
@@ -7856,7 +7856,7 @@
         <v>6.326174848577831</v>
       </c>
       <c r="D114" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E114">
         <v>6.844581898111059</v>
@@ -7906,7 +7906,7 @@
         <v>4.312040252964167</v>
       </c>
       <c r="D115" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E115">
         <v>4.983070718153698</v>
@@ -7956,7 +7956,7 @@
         <v>4.300563404346324</v>
       </c>
       <c r="D116" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E116">
         <v>4.983070718153698</v>
@@ -8006,7 +8006,7 @@
         <v>4.171301828655245</v>
       </c>
       <c r="D117" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E117">
         <v>4.983070718153698</v>
@@ -8256,7 +8256,7 @@
         <v>3.944694008078107</v>
       </c>
       <c r="D122" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E122">
         <v>4.596797064225139</v>
@@ -8306,7 +8306,7 @@
         <v>3.937852443307407</v>
       </c>
       <c r="D123" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E123">
         <v>4.596797064225139</v>
@@ -8356,7 +8356,7 @@
         <v>3.806273225692757</v>
       </c>
       <c r="D124" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E124">
         <v>4.596797064225139</v>
@@ -8406,7 +8406,7 @@
         <v>5.201008311197539</v>
       </c>
       <c r="D125" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E125">
         <v>5.908899264592449</v>
@@ -8456,7 +8456,7 @@
         <v>5.425218702390213</v>
       </c>
       <c r="D126" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E126">
         <v>5.908899264592449</v>
@@ -8506,7 +8506,7 @@
         <v>5.478374570280344</v>
       </c>
       <c r="D127" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E127">
         <v>5.908899264592449</v>
@@ -8556,7 +8556,7 @@
         <v>4.103540950877517</v>
       </c>
       <c r="D128" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E128">
         <v>4.804785959699134</v>
@@ -8606,7 +8606,7 @@
         <v>4.065325239112265</v>
       </c>
       <c r="D129" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E129">
         <v>4.804785959699134</v>
@@ -8656,7 +8656,7 @@
         <v>3.934560544154515</v>
       </c>
       <c r="D130" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E130">
         <v>4.804785959699134</v>
@@ -8856,7 +8856,7 @@
         <v>3.580160099004089</v>
       </c>
       <c r="D134" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E134">
         <v>4.308315560860121</v>
@@ -8906,7 +8906,7 @@
         <v>3.549633088105812</v>
       </c>
       <c r="D135" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E135">
         <v>4.308315560860121</v>
@@ -8956,7 +8956,7 @@
         <v>3.415573235633644</v>
       </c>
       <c r="D136" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E136">
         <v>4.308315560860121</v>
@@ -9306,7 +9306,7 @@
         <v>3.927996868785175</v>
       </c>
       <c r="D143" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E143">
         <v>4.228792366606019</v>
@@ -9356,7 +9356,7 @@
         <v>4.067912029788856</v>
       </c>
       <c r="D144" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E144">
         <v>4.228792366606019</v>
@@ -9406,7 +9406,7 @@
         <v>4.059184614733637</v>
       </c>
       <c r="D145" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E145">
         <v>4.228792366606019</v>
@@ -9456,7 +9456,7 @@
         <v>2.005909712128765</v>
       </c>
       <c r="D146" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E146">
         <v>2.67318675835737</v>
@@ -9506,7 +9506,7 @@
         <v>1.861985812525753</v>
       </c>
       <c r="D147" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E147">
         <v>2.67318675835737</v>
@@ -9556,7 +9556,7 @@
         <v>3.25255656550317</v>
       </c>
       <c r="D148" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E148">
         <v>3.447665574766244</v>
@@ -9606,7 +9606,7 @@
         <v>3.347725014643028</v>
       </c>
       <c r="D149" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E149">
         <v>3.447665574766244</v>
@@ -9656,7 +9656,7 @@
         <v>3.394518515304676</v>
       </c>
       <c r="D150" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E150">
         <v>3.447665574766244</v>
@@ -9706,7 +9706,7 @@
         <v>3.355089268282093</v>
       </c>
       <c r="D151" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E151">
         <v>3.447665574766244</v>
@@ -9756,7 +9756,7 @@
         <v>3.579100375295562</v>
       </c>
       <c r="D152" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E152">
         <v>3.447665574766244</v>
@@ -10192,7 +10192,7 @@
         <v>1</v>
       </c>
       <c r="P160" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -10242,7 +10242,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10292,7 +10292,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -10342,7 +10342,7 @@
         <v>1</v>
       </c>
       <c r="P163" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10392,7 +10392,7 @@
         <v>1</v>
       </c>
       <c r="P164" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -10442,7 +10442,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10492,7 +10492,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10556,7 +10556,7 @@
         <v>3.123371001188277</v>
       </c>
       <c r="D168" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E168">
         <v>4.195059763740991</v>
@@ -10606,7 +10606,7 @@
         <v>2.954328619026529</v>
       </c>
       <c r="D169" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E169">
         <v>4.195059763740991</v>
@@ -10656,7 +10656,7 @@
         <v>3.046412078566592</v>
       </c>
       <c r="D170" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E170">
         <v>4.195059763740991</v>
@@ -10706,7 +10706,7 @@
         <v>3.445059763740991</v>
       </c>
       <c r="D171" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E171">
         <v>4.195059763740991</v>
@@ -10806,7 +10806,7 @@
         <v>2.577752040845755</v>
       </c>
       <c r="D173" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E173">
         <v>3.401487870308934</v>
@@ -10856,7 +10856,7 @@
         <v>2.464829953558134</v>
       </c>
       <c r="D174" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E174">
         <v>3.401487870308934</v>
@@ -10906,7 +10906,7 @@
         <v>2.478250786050127</v>
       </c>
       <c r="D175" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E175">
         <v>3.401487870308934</v>
@@ -10956,7 +10956,7 @@
         <v>2.818408284535719</v>
       </c>
       <c r="D176" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E176">
         <v>3.401487870308934</v>
@@ -11856,7 +11856,7 @@
         <v>6.871264555787782</v>
       </c>
       <c r="D194" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E194">
         <v>5.968914093679149</v>
@@ -11906,7 +11906,7 @@
         <v>6.95746889119295</v>
       </c>
       <c r="D195" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E195">
         <v>5.968914093679149</v>
@@ -11956,7 +11956,7 @@
         <v>6.908484547625465</v>
       </c>
       <c r="D196" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E196">
         <v>6.962494985247139</v>
@@ -12106,7 +12106,7 @@
         <v>3.455949739008592</v>
       </c>
       <c r="D199" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E199">
         <v>2.626483427002986</v>
@@ -12356,7 +12356,7 @@
         <v>1.402030495249267</v>
       </c>
       <c r="D204" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E204">
         <v>0.6610634692540209</v>
@@ -12506,7 +12506,7 @@
         <v>-1.012190922870992</v>
       </c>
       <c r="D207" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E207">
         <v>0.08311492058150804</v>
@@ -12556,7 +12556,7 @@
         <v>-1.046879430812844</v>
       </c>
       <c r="D208" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E208">
         <v>0.08311492058150804</v>
@@ -12656,7 +12656,7 @@
         <v>0.5471409041675006</v>
       </c>
       <c r="D210" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E210">
         <v>-0.09752500935174702</v>
@@ -12706,7 +12706,7 @@
         <v>0.5771493770759779</v>
       </c>
       <c r="D211" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E211">
         <v>-0.1448636147170212</v>
@@ -12756,7 +12756,7 @@
         <v>0.7211216989082878</v>
       </c>
       <c r="D212" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E212">
         <v>0.3151194394660273</v>
@@ -12806,7 +12806,7 @@
         <v>0.6184603042735599</v>
       </c>
       <c r="D213" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E213">
         <v>0.3151194394660273</v>
@@ -12856,7 +12856,7 @@
         <v>0.8057932610331839</v>
       </c>
       <c r="D214" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E214">
         <v>0.3151194394660273</v>
@@ -12906,7 +12906,7 @@
         <v>0.1720291663575146</v>
       </c>
       <c r="D215" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E215">
         <v>-1.174782432733231</v>
@@ -12942,7 +12942,7 @@
         <v>1</v>
       </c>
       <c r="P215" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -12956,7 +12956,7 @@
         <v>-0.5832848576420009</v>
       </c>
       <c r="D216" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E216">
         <v>-1.223526404187433</v>
@@ -12992,7 +12992,7 @@
         <v>1</v>
       </c>
       <c r="P216" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -13006,7 +13006,7 @@
         <v>-0.5978983899145334</v>
       </c>
       <c r="D217" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E217">
         <v>-1.157197898187556</v>
@@ -13042,7 +13042,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -13056,7 +13056,7 @@
         <v>-0.522125420733472</v>
       </c>
       <c r="D218" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E218">
         <v>-1.167246194006191</v>
@@ -13092,7 +13092,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -13106,7 +13106,7 @@
         <v>-0.5938162465515013</v>
       </c>
       <c r="D219" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E219">
         <v>-1.167246194006191</v>
@@ -13142,7 +13142,7 @@
         <v>1</v>
       </c>
       <c r="P219" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -13156,7 +13156,7 @@
         <v>-0.4086954732787849</v>
       </c>
       <c r="D220" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E220">
         <v>-1.167246194006191</v>
@@ -13192,7 +13192,7 @@
         <v>1</v>
       </c>
       <c r="P220" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -13206,7 +13206,7 @@
         <v>1.516859912216534</v>
       </c>
       <c r="D221" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E221">
         <v>0.1337015362106797</v>
@@ -13256,7 +13256,7 @@
         <v>0.6549286759327</v>
       </c>
       <c r="D222" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E222">
         <v>0.009840892465252438</v>
@@ -13306,7 +13306,7 @@
         <v>0.6801911119239215</v>
       </c>
       <c r="D223" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E223">
         <v>0.1028237015362095</v>
@@ -13356,7 +13356,7 @@
         <v>0.8396671543525969</v>
       </c>
       <c r="D224" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E224">
         <v>0.1921232626188711</v>
@@ -13406,7 +13406,7 @@
         <v>0.7340526700804659</v>
       </c>
       <c r="D225" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E225">
         <v>0.1921232626188711</v>
@@ -13506,7 +13506,7 @@
         <v>1.469564000694344</v>
       </c>
       <c r="D227" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E227">
         <v>0.08768389256746723</v>
@@ -13542,7 +13542,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -13556,7 +13556,7 @@
         <v>0.6113823501888458</v>
       </c>
       <c r="D228" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E228">
         <v>-0.03353499756140543</v>
@@ -13592,7 +13592,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -13606,7 +13606,7 @@
         <v>0.6047501988112209</v>
       </c>
       <c r="D229" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E229">
         <v>0.05851041506496912</v>
@@ -13642,7 +13642,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13656,7 +13656,7 @@
         <v>0.7917747178202177</v>
       </c>
       <c r="D230" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E230">
         <v>0.144316043945091</v>
@@ -13692,7 +13692,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13706,7 +13706,7 @@
         <v>0.6873532835684664</v>
       </c>
       <c r="D231" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E231">
         <v>0.144316043945091</v>
@@ -13742,7 +13742,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13792,7 +13792,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13806,7 +13806,7 @@
         <v>1.44514430187747</v>
       </c>
       <c r="D233" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E233">
         <v>0.06392418561050839</v>
@@ -13856,7 +13856,7 @@
         <v>0.5888986274943893</v>
       </c>
       <c r="D234" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E234">
         <v>-0.05593072134120547</v>
@@ -13906,7 +13906,7 @@
         <v>0.5831904647206478</v>
       </c>
       <c r="D235" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E235">
         <v>0.03563069725456458</v>
@@ -13956,7 +13956,7 @@
         <v>0.7670470228020498</v>
       </c>
       <c r="D236" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E236">
         <v>0.1196323483842505</v>
@@ -14006,7 +14006,7 @@
         <v>0.6632415809528851</v>
       </c>
       <c r="D237" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E237">
         <v>0.1196323483842505</v>
@@ -14056,7 +14056,7 @@
         <v>-0.3588062330199779</v>
       </c>
       <c r="D238" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E238">
         <v>-0.2613915586021829</v>
@@ -14106,7 +14106,7 @@
         <v>-0.341391558602183</v>
       </c>
       <c r="D239" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E239">
         <v>-0.2613915586021829</v>
@@ -14156,7 +14156,7 @@
         <v>1.286085745836417</v>
       </c>
       <c r="D240" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E240">
         <v>-0.09083549053754325</v>
@@ -14192,7 +14192,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -14206,7 +14206,7 @@
         <v>0.4424501191394743</v>
       </c>
       <c r="D241" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E241">
         <v>-0.2018060457103878</v>
@@ -14242,7 +14242,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -14256,7 +14256,7 @@
         <v>0.4427603882159339</v>
       </c>
       <c r="D242" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E242">
         <v>-0.1133971390361523</v>
@@ -14292,7 +14292,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -14306,7 +14306,7 @@
         <v>0.6059823228109291</v>
       </c>
       <c r="D243" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E243">
         <v>-0.04114575961400391</v>
@@ -14342,7 +14342,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -14356,7 +14356,7 @@
         <v>0.5061891688618996</v>
       </c>
       <c r="D244" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E244">
         <v>-0.04114575961400391</v>
@@ -14392,7 +14392,7 @@
         <v>1</v>
       </c>
       <c r="P244" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -14406,7 +14406,7 @@
         <v>-0.5227368529397651</v>
       </c>
       <c r="D245" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E245">
         <v>-0.3415594517159466</v>
@@ -14442,7 +14442,7 @@
         <v>1</v>
       </c>
       <c r="P245" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -14456,7 +14456,7 @@
         <v>-0.5056087705148382</v>
       </c>
       <c r="D246" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E246">
         <v>-0.3415594517159466</v>
@@ -14492,7 +14492,7 @@
         <v>1</v>
       </c>
       <c r="P246" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -14506,7 +14506,7 @@
         <v>1.220304308582177</v>
       </c>
       <c r="D247" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E247">
         <v>-0.154839051109235</v>
@@ -14556,7 +14556,7 @@
         <v>0.3818837868207066</v>
       </c>
       <c r="D248" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E248">
         <v>-0.2621353278048151</v>
@@ -14606,7 +14606,7 @@
         <v>0.3846830832527317</v>
       </c>
       <c r="D249" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E249">
         <v>-0.1750301973644497</v>
@@ -14656,7 +14656,7 @@
         <v>0.5393712097715007</v>
       </c>
       <c r="D250" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E250">
         <v>-0.1076383475412612</v>
@@ -14706,7 +14706,7 @@
         <v>0.4412374073928493</v>
       </c>
       <c r="D251" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E251">
         <v>-0.1076383475412612</v>
@@ -14756,7 +14756,7 @@
         <v>-0.5905332171008926</v>
       </c>
       <c r="D252" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E252">
         <v>-0.318380300096722</v>
@@ -14806,7 +14806,7 @@
         <v>-0.5124949878498484</v>
       </c>
       <c r="D253" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E253">
         <v>-0.318380300096722</v>
@@ -14856,7 +14856,7 @@
         <v>0.5242887395747005</v>
       </c>
       <c r="D254" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E254">
         <v>-0.1202877329872347</v>
@@ -14906,7 +14906,7 @@
         <v>0.5212357776743701</v>
       </c>
       <c r="D255" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E255">
         <v>-0.03011713389658688</v>
@@ -14956,7 +14956,7 @@
         <v>0.6959887899040744</v>
       </c>
       <c r="D256" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E256">
         <v>0.04870055362310488</v>
@@ -15006,7 +15006,7 @@
         <v>0.5939534819705194</v>
       </c>
       <c r="D257" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E257">
         <v>0.04870055362310488</v>
@@ -15056,7 +15056,7 @@
         <v>-0.3211288472862446</v>
       </c>
       <c r="D258" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E258">
         <v>-0.1326523579478529</v>
@@ -15106,7 +15106,7 @@
         <v>-0.431128847286244</v>
       </c>
       <c r="D259" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E259">
         <v>-0.1326523579478529</v>
@@ -15156,7 +15156,7 @@
         <v>-0.351975902162371</v>
       </c>
       <c r="D260" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E260">
         <v>-0.1326523579478529</v>
@@ -15206,7 +15206,7 @@
         <v>0.5451410172423419</v>
       </c>
       <c r="D261" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E261">
         <v>-0.09951706893081891</v>
@@ -15242,7 +15242,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -15256,7 +15256,7 @@
         <v>0.5412311124241622</v>
       </c>
       <c r="D262" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E262">
         <v>-0.008897594978440893</v>
@@ -15292,7 +15292,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -15306,7 +15306,7 @@
         <v>0.7189222146579191</v>
       </c>
       <c r="D263" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E263">
         <v>0.07159317157133671</v>
@@ -15342,7 +15342,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -15356,7 +15356,7 @@
         <v>0.6163156114457973</v>
       </c>
       <c r="D264" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E264">
         <v>0.07159317157133671</v>
@@ -15392,7 +15392,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15406,7 +15406,7 @@
         <v>-0.2977873544762826</v>
       </c>
       <c r="D265" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E265">
         <v>0.2641354210821554</v>
@@ -15442,7 +15442,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15456,7 +15456,7 @@
         <v>-0.407787354476282</v>
       </c>
       <c r="D266" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E266">
         <v>0.2641354210821554</v>
@@ -15492,7 +15492,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15506,7 +15506,7 @@
         <v>0.6831127115251583</v>
       </c>
       <c r="D267" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E267">
         <v>0.0379146187207553</v>
@@ -15542,7 +15542,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15556,7 +15556,7 @@
         <v>0.6735327370789186</v>
       </c>
       <c r="D268" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E268">
         <v>0.1315041291449752</v>
@@ -15592,7 +15592,7 @@
         <v>1</v>
       </c>
       <c r="P268" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15606,7 +15606,7 @@
         <v>0.8706640780374553</v>
       </c>
       <c r="D269" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E269">
         <v>0.2230650316352509</v>
@@ -15642,7 +15642,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15656,7 +15656,7 @@
         <v>0.7642774284066274</v>
       </c>
       <c r="D270" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E270">
         <v>0.2230650316352509</v>
@@ -15692,7 +15692,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15706,7 +15706,7 @@
         <v>-0.1433454579405264</v>
       </c>
       <c r="D271" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E271">
         <v>0.4234373772991074</v>
@@ -15742,7 +15742,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15756,7 +15756,7 @@
         <v>-0.2533454579405259</v>
       </c>
       <c r="D272" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E272">
         <v>0.4234373772991074</v>
@@ -15792,7 +15792,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15806,7 +15806,7 @@
         <v>-0.05222072710995107</v>
       </c>
       <c r="D273" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E273">
         <v>0.6345003208948405</v>
@@ -15856,7 +15856,7 @@
         <v>0.702314352898032</v>
       </c>
       <c r="D274" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E274">
         <v>0.05704110689843134</v>
@@ -15906,7 +15906,7 @@
         <v>0.6919452699022219</v>
       </c>
       <c r="D275" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E275">
         <v>0.151043959896235</v>
@@ -15956,7 +15956,7 @@
         <v>0.6723143528980309</v>
       </c>
       <c r="D276" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E276">
         <v>0.151043959896235</v>
@@ -16056,7 +16056,7 @@
         <v>0.8917821258878558</v>
       </c>
       <c r="D278" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E278">
         <v>0.2441455028880526</v>
@@ -16106,7 +16106,7 @@
         <v>0.7848694038906459</v>
       </c>
       <c r="D279" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E279">
         <v>0.2441455028880526</v>
@@ -16156,7 +16156,7 @@
         <v>-0.1218516441141411</v>
       </c>
       <c r="D280" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E280">
         <v>0.4456075698822666</v>
@@ -16206,7 +16206,7 @@
         <v>-0.03112774311154531</v>
       </c>
       <c r="D281" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E281">
         <v>0.4456075698822666</v>
@@ -16256,7 +16256,7 @@
         <v>-0.1599756512329034</v>
       </c>
       <c r="D282" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E282">
         <v>0.5314388961892202</v>
@@ -16306,7 +16306,7 @@
         <v>0.6023819278039682</v>
       </c>
       <c r="D283" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E283">
         <v>-0.04250019324418908</v>
@@ -16356,7 +16356,7 @@
         <v>0.5961196567983258</v>
       </c>
       <c r="D284" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E284">
         <v>0.04935147252067118</v>
@@ -16406,7 +16406,7 @@
         <v>0.572381927803967</v>
       </c>
       <c r="D285" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E285">
         <v>0.04935147252067118</v>
@@ -16506,7 +16506,7 @@
         <v>0.7818760145319583</v>
       </c>
       <c r="D287" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E287">
         <v>0.2188455592486616</v>
@@ -16556,7 +16556,7 @@
         <v>0.6777011671948596</v>
       </c>
       <c r="D288" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E288">
         <v>0.1344349540078777</v>
@@ -16606,7 +16606,7 @@
         <v>-0.2337133802272593</v>
       </c>
       <c r="D289" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E289">
         <v>0.3302257092061467</v>
@@ -16656,7 +16656,7 @@
         <v>-0.1404471670402767</v>
       </c>
       <c r="D290" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E290">
         <v>0.3302257092061467</v>
@@ -16706,7 +16706,7 @@
         <v>-0.5297221743420888</v>
       </c>
       <c r="D291" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E291">
         <v>0.177797484794409</v>
@@ -16742,7 +16742,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16756,7 +16756,7 @@
         <v>0.2594772575520725</v>
       </c>
       <c r="D292" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E292">
         <v>-0.3840627708532196</v>
@@ -16792,7 +16792,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16806,7 +16806,7 @@
         <v>0.2160020090057699</v>
       </c>
       <c r="D293" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E293">
         <v>-0.2995926146241139</v>
@@ -16842,7 +16842,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16856,7 +16856,7 @@
         <v>0.2294772575520714</v>
       </c>
       <c r="D294" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E294">
         <v>-0.2995926146241139</v>
@@ -16892,7 +16892,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16942,7 +16942,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16956,7 +16956,7 @@
         <v>0.4047479818870166</v>
       </c>
       <c r="D296" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E296">
         <v>-0.1643218902891714</v>
@@ -16992,7 +16992,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -17006,7 +17006,7 @@
         <v>0.3099677830499701</v>
       </c>
       <c r="D297" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E297">
         <v>-0.2420220323156315</v>
@@ -17042,7 +17042,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -17056,7 +17056,7 @@
         <v>-0.6175518760865248</v>
       </c>
       <c r="D298" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E298">
         <v>-0.06569162043889776</v>
@@ -17092,7 +17092,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -17106,7 +17106,7 @@
         <v>-0.5155620607209208</v>
       </c>
       <c r="D299" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E299">
         <v>-0.06569162043889776</v>
@@ -17142,7 +17142,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -17156,7 +17156,7 @@
         <v>3.711167000814271</v>
       </c>
       <c r="D300" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E300">
         <v>4.512707221119614</v>
@@ -17206,7 +17206,7 @@
         <v>5.260227025292643</v>
       </c>
       <c r="D301" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E301">
         <v>3.883216817226483</v>
@@ -17256,7 +17256,7 @@
         <v>3.612446707073811</v>
       </c>
       <c r="D302" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E302">
         <v>4.036376474529282</v>
@@ -17306,7 +17306,7 @@
         <v>2.778054848675449</v>
       </c>
       <c r="D303" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E303">
         <v>3.550231399857543</v>
@@ -17356,7 +17356,7 @@
         <v>2.800953545963342</v>
       </c>
       <c r="D304" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E304">
         <v>3.550231399857543</v>
@@ -17406,7 +17406,7 @@
         <v>4.323852243251237</v>
       </c>
       <c r="D305" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E305">
         <v>2.974574389357036</v>
@@ -17456,7 +17456,7 @@
         <v>2.718486113765989</v>
       </c>
       <c r="D306" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E306">
         <v>3.123410865296</v>
@@ -17506,7 +17506,7 @@
         <v>1.983160587873193</v>
       </c>
       <c r="D307" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E307">
         <v>2.730322983995075</v>
@@ -17556,7 +17556,7 @@
         <v>2.004669609879961</v>
       </c>
       <c r="D308" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E308">
         <v>2.730322983995075</v>
@@ -17606,7 +17606,7 @@
         <v>3.526178631886735</v>
       </c>
       <c r="D309" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E309">
         <v>2.200525257771622</v>
@@ -17656,7 +17656,7 @@
         <v>1.956944059710679</v>
       </c>
       <c r="D310" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E310">
         <v>2.409218509541397</v>
@@ -17706,7 +17706,7 @@
         <v>0.8799289586838714</v>
       </c>
       <c r="D311" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E311">
         <v>1.592374275565531</v>
@@ -17756,7 +17756,7 @@
         <v>0.9682501402131294</v>
       </c>
       <c r="D312" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E312">
         <v>1.592374275565531</v>
@@ -17806,7 +17806,7 @@
         <v>2.419089549448499</v>
       </c>
       <c r="D313" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E313">
         <v>1.126224527949153</v>
@@ -17856,7 +17856,7 @@
         <v>2.06419891568518</v>
       </c>
       <c r="D314" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E314">
         <v>1.126224527949153</v>
@@ -17906,7 +17906,7 @@
         <v>0.9000018695083227</v>
       </c>
       <c r="D315" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E315">
         <v>1.703012712656575</v>
@@ -17956,7 +17956,7 @@
         <v>0.3940106533845285</v>
       </c>
       <c r="D316" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E316">
         <v>0.9777032963232024</v>
@@ -17992,7 +17992,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -18006,7 +18006,7 @@
         <v>0.284010653384529</v>
       </c>
       <c r="D317" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E317">
         <v>0.9777032963232024</v>
@@ -18042,7 +18042,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -18056,7 +18056,7 @@
         <v>1.821087613711049</v>
       </c>
       <c r="D318" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E318">
         <v>0.5459334509356335</v>
@@ -18092,7 +18092,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -18106,7 +18106,7 @@
         <v>1.5037023278337</v>
       </c>
       <c r="D319" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E319">
         <v>0.5459334509356335</v>
@@ -18142,7 +18142,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -18156,7 +18156,7 @@
         <v>0.3290871294662949</v>
       </c>
       <c r="D320" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E320">
         <v>1.164394244405246</v>
@@ -18192,7 +18192,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -18206,7 +18206,7 @@
         <v>-0.1303378620988589</v>
       </c>
       <c r="D321" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E321">
         <v>0.5687326111345428</v>
@@ -18256,7 +18256,7 @@
         <v>1.405290327194502</v>
       </c>
       <c r="D322" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E322">
         <v>0.1424507182009354</v>
@@ -18306,7 +18306,7 @@
         <v>1.113982919914012</v>
       </c>
       <c r="D323" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E323">
         <v>0.1424507182009354</v>
@@ -18356,7 +18356,7 @@
         <v>0.01807890749429752</v>
       </c>
       <c r="D324" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E324">
         <v>0.7898869323337241</v>
@@ -18406,7 +18406,7 @@
         <v>-0.1449533761282655</v>
       </c>
       <c r="D325" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E325">
         <v>0.5539893391153683</v>
@@ -18456,7 +18456,7 @@
         <v>1.390623709969187</v>
       </c>
       <c r="D326" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E326">
         <v>0.1282184781408322</v>
@@ -18506,7 +18506,7 @@
         <v>1.100236160215024</v>
       </c>
       <c r="D327" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E327">
         <v>0.1282184781408322</v>
@@ -18556,7 +18556,7 @@
         <v>0.003795564238286531</v>
       </c>
       <c r="D328" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E328">
         <v>0.77667675619176</v>
@@ -18606,7 +18606,7 @@
         <v>1.338895251493001</v>
       </c>
       <c r="D329" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E329">
         <v>0.5272283520481338</v>
@@ -18656,7 +18656,7 @@
         <v>-0.04658110525333115</v>
       </c>
       <c r="D330" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E330">
         <v>0.7300850958569374</v>
@@ -18706,7 +18706,7 @@
         <v>5.252623163353501</v>
       </c>
       <c r="D331" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E331">
         <v>5.811442523768368</v>
@@ -18856,7 +18856,7 @@
         <v>5.155821953327571</v>
       </c>
       <c r="D334" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E334">
         <v>5.436800777873812</v>
@@ -18906,7 +18906,7 @@
         <v>5.21461106309421</v>
       </c>
       <c r="D335" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E335">
         <v>5.436800777873812</v>
@@ -19056,7 +19056,7 @@
         <v>5.996975409186557</v>
       </c>
       <c r="D338" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E338">
         <v>6.322440349888621</v>
@@ -19106,7 +19106,7 @@
         <v>6.04103615104905</v>
       </c>
       <c r="D339" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E339">
         <v>6.322440349888621</v>
@@ -19256,7 +19256,7 @@
         <v>6.467595657864342</v>
       </c>
       <c r="D342" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E342">
         <v>6.75843983370544</v>
@@ -19306,7 +19306,7 @@
         <v>6.50341596735699</v>
       </c>
       <c r="D343" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E343">
         <v>6.75843983370544</v>
@@ -19406,7 +19406,7 @@
         <v>7.038673370415092</v>
       </c>
       <c r="D345" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E345">
         <v>7.57711369319794</v>
@@ -19456,7 +19456,7 @@
         <v>6.933612348269409</v>
       </c>
       <c r="D346" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E346">
         <v>7.57711369319794</v>
@@ -19506,7 +19506,7 @@
         <v>7.041012886240821</v>
       </c>
       <c r="D347" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E347">
         <v>7.57711369319794</v>
@@ -19606,7 +19606,7 @@
         <v>7.603480524142883</v>
       </c>
       <c r="D349" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E349">
         <v>8.074842039131216</v>
@@ -19656,7 +19656,7 @@
         <v>7.583949919224556</v>
       </c>
       <c r="D350" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E350">
         <v>8.115780829294561</v>
@@ -19706,7 +19706,7 @@
         <v>7.602119009154551</v>
       </c>
       <c r="D351" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E351">
         <v>8.115780829294561</v>
@@ -19756,7 +19756,7 @@
         <v>7.596203554119548</v>
       </c>
       <c r="D352" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E352">
         <v>8.115780829294561</v>
@@ -19856,7 +19856,7 @@
         <v>8.197082757216956</v>
       </c>
       <c r="D354" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E354">
         <v>8.669626746773165</v>
@@ -19906,7 +19906,7 @@
         <v>8.20282687732055</v>
       </c>
       <c r="D355" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E355">
         <v>8.694010892986238</v>
@@ -19956,7 +19956,7 @@
         <v>8.194538767660747</v>
       </c>
       <c r="D356" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E356">
         <v>8.694010892986238</v>
@@ -20006,7 +20006,7 @@
         <v>8.192170736329373</v>
       </c>
       <c r="D357" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E357">
         <v>8.694010892986238</v>
@@ -20056,7 +20056,7 @@
         <v>-0.9277197529705248</v>
       </c>
       <c r="D358" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E358">
         <v>-1.43484711683287</v>
@@ -20106,7 +20106,7 @@
         <v>-1.739101844557563</v>
       </c>
       <c r="D359" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E359">
         <v>-1.225064022760026</v>
@@ -20156,7 +20156,7 @@
         <v>-1.67793665889768</v>
       </c>
       <c r="D360" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E360">
         <v>-1.225064022760026</v>
@@ -20206,7 +20206,7 @@
         <v>-1.660809295035333</v>
       </c>
       <c r="D361" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E361">
         <v>-0.9252809286871813</v>
@@ -20256,7 +20256,7 @@
         <v>-1.665172475723605</v>
       </c>
       <c r="D362" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E362">
         <v>-0.9252809286871813</v>
@@ -20306,7 +20306,7 @@
         <v>-0.8321510586103233</v>
       </c>
       <c r="D363" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E363">
         <v>-0.4166226922621714</v>
@@ -20356,7 +20356,7 @@
         <v>-3.843022818180284</v>
       </c>
       <c r="D364" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E364">
         <v>-3.26412423419014</v>
@@ -20406,7 +20406,7 @@
         <v>-3.712943072690754</v>
       </c>
       <c r="D365" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E365">
         <v>-3.26412423419014</v>
@@ -20456,7 +20456,7 @@
         <v>-4.087117010683363</v>
       </c>
       <c r="D366" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E366">
         <v>-3.293178553948453</v>
@@ -20506,7 +20506,7 @@
         <v>-2.768453907950921</v>
       </c>
       <c r="D367" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E367">
         <v>-2.083569770974329</v>
@@ -20556,7 +20556,7 @@
         <v>-2.698924870466321</v>
       </c>
       <c r="D368" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E368">
         <v>-2.083569770974329</v>
@@ -20606,7 +20606,7 @@
         <v>-5.897343766119011</v>
       </c>
       <c r="D369" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E369">
         <v>-5.21377186018452</v>
@@ -20656,7 +20656,7 @@
         <v>-5.892794919062931</v>
       </c>
       <c r="D370" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E370">
         <v>-5.287381083735886</v>
@@ -20706,7 +20706,7 @@
         <v>-6.281892613175087</v>
       </c>
       <c r="D371" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E371">
         <v>-5.383339366049038</v>
@@ -20756,7 +20756,7 @@
         <v>-4.84153475427336</v>
       </c>
       <c r="D372" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E372">
         <v>-4.085725742427703</v>
@@ -20806,7 +20806,7 @@
         <v>-4.665255930675347</v>
       </c>
       <c r="D373" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E373">
         <v>-4.085725742427703</v>
@@ -20856,7 +20856,7 @@
         <v>-7.494239379929031</v>
       </c>
       <c r="D374" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E374">
         <v>-6.751752878533589</v>
@@ -20906,7 +20906,7 @@
         <v>-7.492791301055105</v>
       </c>
       <c r="D375" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E375">
         <v>-6.850168247542195</v>
@@ -20956,7 +20956,7 @@
         <v>-7.875687458802952</v>
       </c>
       <c r="D376" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E376">
         <v>-6.901165391214095</v>
@@ -21006,7 +21006,7 @@
         <v>-6.346957706709796</v>
       </c>
       <c r="D377" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E377">
         <v>-5.984607757431821</v>
@@ -21056,7 +21056,7 @@
         <v>-6.382299087003467</v>
       </c>
       <c r="D378" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E378">
         <v>-5.984607757431821</v>
@@ -21106,7 +21106,7 @@
         <v>-8.194922154350412</v>
       </c>
       <c r="D379" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E379">
         <v>-7.42658522050059</v>
@@ -21156,7 +21156,7 @@
         <v>-8.155009684147785</v>
       </c>
       <c r="D380" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E380">
         <v>-7.535884982121567</v>
@@ -21206,7 +21206,7 @@
         <v>-8.575009684147785</v>
       </c>
       <c r="D381" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E381">
         <v>-7.567154164183544</v>
@@ -21256,7 +21256,7 @@
         <v>-7.007504283373057</v>
       </c>
       <c r="D382" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E382">
         <v>-6.779342409117989</v>
@@ -21306,7 +21306,7 @@
         <v>-7.019036054827168</v>
       </c>
       <c r="D383" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E383">
         <v>-6.779342409117989</v>
@@ -21356,7 +21356,7 @@
         <v>-8.936969711340112</v>
       </c>
       <c r="D384" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E384">
         <v>-8.141256265679017</v>
@@ -21406,7 +21406,7 @@
         <v>-8.895616372094786</v>
       </c>
       <c r="D385" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E385">
         <v>-8.262082979641582</v>
@@ -21456,7 +21456,7 @@
         <v>-9.315616372094786</v>
       </c>
       <c r="D386" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E386">
         <v>-8.272459560584432</v>
@@ -21606,7 +21606,7 @@
         <v>-8.948241366187794</v>
       </c>
       <c r="D389" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E389">
         <v>-8.152112073066304</v>
@@ -21656,7 +21656,7 @@
         <v>-8.90686614023403</v>
       </c>
       <c r="D390" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E390">
         <v>-8.273113880696405</v>
@@ -21706,7 +21706,7 @@
         <v>-9.32686614023403</v>
       </c>
       <c r="D391" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E391">
         <v>-7.892485491389962</v>
@@ -21756,7 +21756,7 @@
         <v>-7.646984587574911</v>
       </c>
       <c r="D392" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E392">
         <v>-7.178478260869557</v>
@@ -21806,7 +21806,7 @@
         <v>-7.393291551707726</v>
       </c>
       <c r="D393" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E393">
         <v>-7.178478260869557</v>
@@ -21856,7 +21856,7 @@
         <v>-9.216500648310582</v>
       </c>
       <c r="D394" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E394">
         <v>-8.410474410800093</v>
@@ -21892,7 +21892,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21906,7 +21906,7 @@
         <v>-9.174604530546869</v>
       </c>
       <c r="D395" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E395">
         <v>-8.477110822973078</v>
@@ -21942,7 +21942,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21956,7 +21956,7 @@
         <v>-9.594604530546869</v>
       </c>
       <c r="D396" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E396">
         <v>-8.147201586454123</v>
@@ -21992,7 +21992,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -22042,7 +22042,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -22092,7 +22092,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -22106,7 +22106,7 @@
         <v>-9.488460946517886</v>
       </c>
       <c r="D399" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E399">
         <v>-8.782113312812619</v>
@@ -22156,7 +22156,7 @@
         <v>-9.908460946517886</v>
       </c>
       <c r="D400" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E400">
         <v>-8.445792612543283</v>
@@ -22206,7 +22206,7 @@
         <v>-7.945711812235471</v>
       </c>
       <c r="D401" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E401">
         <v>-7.898110811850708</v>
@@ -22256,7 +22256,7 @@
         <v>-7.914350711812233</v>
       </c>
       <c r="D402" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E402">
         <v>-7.898110811850708</v>
@@ -22306,7 +22306,7 @@
         <v>-9.731958922090953</v>
       </c>
       <c r="D403" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E403">
         <v>-8.922781252412936</v>
@@ -22356,7 +22356,7 @@
         <v>-10.15195892209095</v>
       </c>
       <c r="D404" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E404">
         <v>-8.677447301366684</v>
@@ -22506,7 +22506,7 @@
         <v>-9.713150682287534</v>
       </c>
       <c r="D407" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E407">
         <v>-8.904576779062349</v>
@@ -22556,7 +22556,7 @@
         <v>-10.13315068228753</v>
       </c>
       <c r="D408" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E408">
         <v>-8.659553859219074</v>
@@ -22706,7 +22706,7 @@
         <v>-9.786103124815638</v>
       </c>
       <c r="D411" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E411">
         <v>-9.096428585475211</v>
@@ -22756,7 +22756,7 @@
         <v>-9.885452203496488</v>
       </c>
       <c r="D412" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E412">
         <v>-9.071347220310315</v>
@@ -22806,7 +22806,7 @@
         <v>-10.30545220349649</v>
       </c>
       <c r="D413" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E413">
         <v>-8.823474956244713</v>
@@ -22956,7 +22956,7 @@
         <v>-9.843764571794191</v>
       </c>
       <c r="D416" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E416">
         <v>-9.128491781807984</v>
@@ -23006,7 +23006,7 @@
         <v>-9.944492011757397</v>
       </c>
       <c r="D417" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E417">
         <v>-9.128491781807984</v>
@@ -23056,7 +23056,7 @@
         <v>-10.3644920117574</v>
       </c>
       <c r="D418" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E418">
         <v>-8.879643178500714</v>
@@ -23106,7 +23106,7 @@
         <v>-8.368915738537504</v>
       </c>
       <c r="D419" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E419">
         <v>-7.670672951950555</v>
@@ -23156,7 +23156,7 @@
         <v>-8.412127831876973</v>
       </c>
       <c r="D420" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E420">
         <v>-7.670672951950555</v>
@@ -23206,7 +23206,7 @@
         <v>-8.3229155085881</v>
       </c>
       <c r="D421" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E421">
         <v>-7.670672951950555</v>
@@ -23256,7 +23256,7 @@
         <v>-9.413850870677146</v>
       </c>
       <c r="D422" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E422">
         <v>-8.460862700719371</v>
@@ -23306,7 +23306,7 @@
         <v>-9.504301489099706</v>
       </c>
       <c r="D423" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E423">
         <v>-8.460862700719371</v>
@@ -23356,7 +23356,7 @@
         <v>-9.381313319141935</v>
       </c>
       <c r="D424" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E424">
         <v>-8.460862700719371</v>
@@ -23406,7 +23406,7 @@
         <v>-7.960412082296807</v>
       </c>
       <c r="D425" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E425">
         <v>-7.188091863543228</v>
@@ -23456,7 +23456,7 @@
         <v>-7.928542481965792</v>
       </c>
       <c r="D426" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E426">
         <v>-7.188091863543228</v>
@@ -23506,7 +23506,7 @@
         <v>-7.787273706198183</v>
       </c>
       <c r="D427" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E427">
         <v>-7.188091863543228</v>
@@ -23556,7 +23556,7 @@
         <v>-9.172895884074581</v>
       </c>
       <c r="D428" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E428">
         <v>-8.145576045355</v>
@@ -23606,7 +23606,7 @@
         <v>-9.058289567940399</v>
       </c>
       <c r="D429" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E429">
         <v>-8.145576045355</v>
@@ -23656,7 +23656,7 @@
         <v>-7.622862522769601</v>
       </c>
       <c r="D430" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E430">
         <v>-6.959864303403672</v>
@@ -23706,7 +23706,7 @@
         <v>-7.631631429214679</v>
       </c>
       <c r="D431" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E431">
         <v>-6.959864303403672</v>
@@ -23756,7 +23756,7 @@
         <v>-7.222167461470761</v>
       </c>
       <c r="D432" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E432">
         <v>-6.959864303403672</v>
@@ -23806,7 +23806,7 @@
         <v>-7.490685032440284</v>
       </c>
       <c r="D433" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E433">
         <v>-6.959864303403672</v>
@@ -23856,7 +23856,7 @@
         <v>-8.561827797884455</v>
       </c>
       <c r="D434" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E434">
         <v>-7.564229169582681</v>
@@ -23906,7 +23906,7 @@
         <v>-8.46267651116753</v>
       </c>
       <c r="D435" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E435">
         <v>-7.564229169582681</v>
@@ -23956,7 +23956,7 @@
         <v>-7.05578182799783</v>
       </c>
       <c r="D436" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E436">
         <v>-6.720998980224341</v>
@@ -24006,7 +24006,7 @@
         <v>-6.680647007658305</v>
       </c>
       <c r="D437" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E437">
         <v>-6.720998980224341</v>
@@ -24056,7 +24056,7 @@
         <v>-6.943814760752625</v>
       </c>
       <c r="D438" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E438">
         <v>-6.720998980224341</v>
@@ -24106,7 +24106,7 @@
         <v>-7.900748535322215</v>
       </c>
       <c r="D439" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E439">
         <v>-7.068198896242816</v>
@@ -24156,7 +24156,7 @@
         <v>-7.954473715782516</v>
       </c>
       <c r="D440" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E440">
         <v>-7.068198896242816</v>
@@ -24206,7 +24206,7 @@
         <v>-7.896025874307643</v>
       </c>
       <c r="D441" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E441">
         <v>-7.068198896242816</v>
@@ -24256,7 +24256,7 @@
         <v>-6.218598358361149</v>
       </c>
       <c r="D442" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E442">
         <v>-6.369374437623716</v>
@@ -24306,7 +24306,7 @@
         <v>-6.477201415688539</v>
       </c>
       <c r="D443" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E443">
         <v>-6.369374437623716</v>
@@ -24356,7 +24356,7 @@
         <v>-6.477356631541051</v>
       </c>
       <c r="D444" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E444">
         <v>-6.369374437623716</v>
@@ -24406,7 +24406,7 @@
         <v>0.1544375412573284</v>
       </c>
       <c r="D445" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E445">
         <v>0.7763231468178482</v>
@@ -24456,7 +24456,7 @@
         <v>0.162551935696813</v>
       </c>
       <c r="D446" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E446">
         <v>0.7763231468178482</v>
@@ -24506,7 +24506,7 @@
         <v>1.050094357938882</v>
       </c>
       <c r="D447" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E447">
         <v>0.5910371607191394</v>
@@ -24706,7 +24706,7 @@
         <v>-0.05317325947102702</v>
       </c>
       <c r="D451" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E451">
         <v>0.5712288406437764</v>
@@ -24756,7 +24756,7 @@
         <v>-0.04757535958582615</v>
       </c>
       <c r="D452" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E452">
         <v>0.5712288406437764</v>
@@ -24806,7 +24806,7 @@
         <v>0.8500330408733774</v>
       </c>
       <c r="D453" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E453">
         <v>0.392234090930776</v>
@@ -25006,7 +25006,7 @@
         <v>-0.2692961577804383</v>
       </c>
       <c r="D457" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E457">
         <v>0.3577256138290235</v>
@@ -25056,7 +25056,7 @@
         <v>-0.2663179293898956</v>
       </c>
       <c r="D458" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E458">
         <v>0.3577256138290235</v>
@@ -25106,7 +25106,7 @@
         <v>0.6417691570479445</v>
       </c>
       <c r="D459" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E459">
         <v>0.1852800428526731</v>
@@ -25306,7 +25306,7 @@
         <v>0.05587008030584961</v>
       </c>
       <c r="D463" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E463">
         <v>0.6789504429688105</v>
@@ -25356,7 +25356,7 @@
         <v>0.06278971764289132</v>
       </c>
       <c r="D464" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E464">
         <v>0.6789504429688105</v>
@@ -25406,7 +25406,7 @@
         <v>0.9551111682947298</v>
       </c>
       <c r="D465" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E465">
         <v>0.4966513496262088</v>
@@ -25606,7 +25606,7 @@
         <v>-0.1893348809203133</v>
       </c>
       <c r="D469" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E469">
         <v>0.4367176630908425</v>
@@ -25656,7 +25656,7 @@
         <v>-0.1853874249314682</v>
       </c>
       <c r="D470" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E470">
         <v>0.4367176630908425</v>
@@ -25706,7 +25706,7 @@
         <v>0.7188227511131551</v>
       </c>
       <c r="D471" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E471">
         <v>0.2618490231187316</v>
@@ -25906,7 +25906,7 @@
         <v>4.371485982915774</v>
       </c>
       <c r="D475" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E475">
         <v>4.962528234821984</v>
@@ -25956,7 +25956,7 @@
         <v>5.060047010261989</v>
       </c>
       <c r="D476" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E476">
         <v>4.670741844866129</v>
@@ -26106,7 +26106,7 @@
         <v>3.620560894635664</v>
       </c>
       <c r="D479" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E479">
         <v>4.229589376201279</v>
@@ -26156,7 +26156,7 @@
         <v>4.317639349991246</v>
       </c>
       <c r="D480" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E480">
         <v>3.938374978158294</v>
@@ -26206,7 +26206,7 @@
         <v>4.370574873318176</v>
       </c>
       <c r="D481" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E481">
         <v>3.818139087890952</v>
@@ -26306,7 +26306,7 @@
         <v>6.853299645934258</v>
       </c>
       <c r="D483" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E483">
         <v>5.774682369171286</v>
@@ -26356,7 +26356,7 @@
         <v>6.891491094566248</v>
       </c>
       <c r="D484" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E484">
         <v>5.774682369171286</v>
@@ -26406,7 +26406,7 @@
         <v>5.361224864970907</v>
       </c>
       <c r="D485" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E485">
         <v>5.018618668978591</v>
@@ -26456,7 +26456,7 @@
         <v>5.403937692022923</v>
       </c>
       <c r="D486" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E486">
         <v>5.018618668978591</v>
@@ -26506,7 +26506,7 @@
         <v>5.435905841926575</v>
       </c>
       <c r="D487" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E487">
         <v>5.018618668978591</v>
@@ -26556,7 +26556,7 @@
         <v>6.006575212731824</v>
       </c>
       <c r="D488" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E488">
         <v>5.049928678956259</v>
@@ -26592,7 +26592,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26606,7 +26606,7 @@
         <v>6.064211272564705</v>
       </c>
       <c r="D489" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E489">
         <v>5.049928678956259</v>
@@ -26642,7 +26642,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26656,7 +26656,7 @@
         <v>4.663870399629863</v>
       </c>
       <c r="D490" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E490">
         <v>4.316971023154751</v>
@@ -26692,7 +26692,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26706,7 +26706,7 @@
         <v>4.677416309880542</v>
       </c>
       <c r="D491" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E491">
         <v>4.316971023154751</v>
@@ -26742,7 +26742,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26756,7 +26756,7 @@
         <v>4.678449851055503</v>
       </c>
       <c r="D492" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E492">
         <v>4.316971023154751</v>
@@ -26792,7 +26792,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -26806,7 +26806,7 @@
         <v>5.45724271386503</v>
       </c>
       <c r="D493" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E493">
         <v>4.579727583892824</v>
@@ -26856,7 +26856,7 @@
         <v>5.527493925028882</v>
       </c>
       <c r="D494" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E494">
         <v>4.579727583892824</v>
@@ -26906,7 +26906,7 @@
         <v>4.201445199623705</v>
       </c>
       <c r="D495" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E495">
         <v>3.460664324521434</v>
@@ -26956,7 +26956,7 @@
         <v>4.150453975773659</v>
       </c>
       <c r="D496" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E496">
         <v>3.460664324521434</v>
@@ -27006,7 +27006,7 @@
         <v>4.187032365117255</v>
       </c>
       <c r="D497" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E497">
         <v>3.460664324521434</v>
@@ -27056,7 +27056,7 @@
         <v>4.42199553766301</v>
       </c>
       <c r="D498" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E498">
         <v>3.693607871486083</v>
@@ -27106,7 +27106,7 @@
         <v>4.365726240572206</v>
       </c>
       <c r="D499" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E499">
         <v>3.693607871486083</v>
@@ -27156,7 +27156,7 @@
         <v>4.516020692330457</v>
       </c>
       <c r="D500" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E500">
         <v>3.693607871486083</v>
@@ -27206,7 +27206,7 @@
         <v>3.247044122637031</v>
       </c>
       <c r="D501" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E501">
         <v>2.605123035361114</v>
@@ -27256,7 +27256,7 @@
         <v>3.194659905181848</v>
       </c>
       <c r="D502" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E502">
         <v>2.605123035361114</v>
@@ -27306,7 +27306,7 @@
         <v>-3.705984123275019</v>
       </c>
       <c r="D503" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E503">
         <v>-2.970035313701199</v>
@@ -27356,7 +27356,7 @@
         <v>-3.693186241046869</v>
       </c>
       <c r="D504" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E504">
         <v>-2.970035313701199</v>
@@ -27406,7 +27406,7 @@
         <v>-2.752427193387811</v>
       </c>
       <c r="D505" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E505">
         <v>-3.420167707261241</v>
@@ -27456,7 +27456,7 @@
         <v>-2.600361880106711</v>
       </c>
       <c r="D506" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E506">
         <v>-3.420167707261241</v>
@@ -27506,7 +27506,7 @@
         <v>-3.678102393980136</v>
       </c>
       <c r="D507" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E507">
         <v>-3.136716692222066</v>
@@ -27556,7 +27556,7 @@
         <v>-4.366813091974395</v>
       </c>
       <c r="D508" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E508">
         <v>-3.818652183810219</v>
@@ -27606,7 +27606,7 @@
         <v>-4.484310216846968</v>
       </c>
       <c r="D509" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E509">
         <v>-3.818652183810219</v>
@@ -27656,7 +27656,7 @@
         <v>-4.322051603836151</v>
       </c>
       <c r="D510" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E510">
         <v>-3.818652183810219</v>
@@ -27706,7 +27706,7 @@
         <v>-3.347068854600705</v>
       </c>
       <c r="D511" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E511">
         <v>-4.118163659577004</v>
@@ -27756,7 +27756,7 @@
         <v>-3.324798741080183</v>
       </c>
       <c r="D512" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E512">
         <v>-4.118163659577004</v>
@@ -27806,7 +27806,7 @@
         <v>-3.351387820544549</v>
       </c>
       <c r="D513" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E513">
         <v>-4.118163659577004</v>
@@ -27856,7 +27856,7 @@
         <v>-4.379071704985211</v>
       </c>
       <c r="D514" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E514">
         <v>-3.832482625520846</v>
@@ -27906,7 +27906,7 @@
         <v>8.995980915690074</v>
       </c>
       <c r="D515" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E515">
         <v>10.66390789578366</v>
@@ -27956,7 +27956,7 @@
         <v>11.51142958743078</v>
       </c>
       <c r="D516" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E516">
         <v>11.61008037782884</v>
@@ -28006,7 +28006,7 @@
         <v>11.33896292349641</v>
       </c>
       <c r="D517" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E517">
         <v>11.61008037782884</v>
@@ -28056,7 +28056,7 @@
         <v>11.25741689188049</v>
       </c>
       <c r="D518" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E518">
         <v>11.61008037782884</v>
@@ -28106,7 +28106,7 @@
         <v>11.28637455971803</v>
       </c>
       <c r="D519" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E519">
         <v>11.61008037782884</v>
@@ -28156,7 +28156,7 @@
         <v>9.394053857479914</v>
       </c>
       <c r="D520" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E520">
         <v>11.10574062904685</v>
@@ -28206,7 +28206,7 @@
         <v>11.96926052402832</v>
       </c>
       <c r="D521" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E521">
         <v>11.78545564208547</v>
@@ -28256,7 +28256,7 @@
         <v>11.76715013038619</v>
       </c>
       <c r="D522" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E522">
         <v>11.78545564208547</v>
@@ -28306,7 +28306,7 @@
         <v>11.79715013038619</v>
       </c>
       <c r="D523" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E523">
         <v>11.78545564208547</v>
@@ -28356,7 +28356,7 @@
         <v>11.75785102268897</v>
       </c>
       <c r="D524" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E524">
         <v>11.78545564208547</v>
@@ -28406,7 +28406,7 @@
         <v>6.4997071892945</v>
       </c>
       <c r="D525" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E525">
         <v>7.893221100174392</v>
@@ -28606,7 +28606,7 @@
         <v>8.621088353970423</v>
       </c>
       <c r="D529" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E529">
         <v>8.269277714135617</v>
@@ -28656,7 +28656,7 @@
         <v>8.578286988055545</v>
       </c>
       <c r="D530" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E530">
         <v>8.269277714135617</v>
@@ -28706,7 +28706,7 @@
         <v>8.739580302223263</v>
       </c>
       <c r="D531" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E531">
         <v>8.269277714135617</v>
@@ -28756,7 +28756,7 @@
         <v>8.957510999554914</v>
       </c>
       <c r="D532" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E532">
         <v>8.269277714135617</v>
@@ -29006,7 +29006,7 @@
         <v>1.438738012295818</v>
       </c>
       <c r="D537" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E537">
         <v>2.100412073152636</v>
@@ -29056,7 +29056,7 @@
         <v>1.573030977807695</v>
       </c>
       <c r="D538" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E538">
         <v>2.100412073152636</v>
@@ -29106,7 +29106,7 @@
         <v>1.547818547789148</v>
       </c>
       <c r="D539" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E539">
         <v>2.100412073152636</v>
@@ -29256,7 +29256,7 @@
         <v>-0.8761721984660475</v>
       </c>
       <c r="D542" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E542">
         <v>-1.556082773365931</v>
@@ -29306,7 +29306,7 @@
         <v>-1.017858379148869</v>
       </c>
       <c r="D543" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E543">
         <v>-1.556082773365931</v>
@@ -29356,7 +29356,7 @@
         <v>-0.5723250526030199</v>
       </c>
       <c r="D544" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E544">
         <v>-1.556082773365931</v>
@@ -29406,7 +29406,7 @@
         <v>-1.931822609108822</v>
       </c>
       <c r="D545" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E545">
         <v>-1.673095771397564</v>
@@ -29456,7 +29456,7 @@
         <v>-2.066468132763205</v>
       </c>
       <c r="D546" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E546">
         <v>-1.673095771397564</v>
@@ -29506,7 +29506,7 @@
         <v>-1.956055114369123</v>
       </c>
       <c r="D547" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E547">
         <v>-1.673095771397564</v>
@@ -29556,7 +29556,7 @@
         <v>-1.910907147220547</v>
       </c>
       <c r="D548" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E548">
         <v>-1.673095771397564</v>
@@ -29606,7 +29606,7 @@
         <v>-1.911499015814858</v>
       </c>
       <c r="D549" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E549">
         <v>-1.673095771397564</v>
@@ -29656,7 +29656,7 @@
         <v>-2.047060001357517</v>
       </c>
       <c r="D550" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E550">
         <v>-1.673095771397564</v>
@@ -29856,7 +29856,7 @@
         <v>-1.458250204365703</v>
       </c>
       <c r="D554" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E554">
         <v>-2.203959675076526</v>
@@ -29956,7 +29956,7 @@
         <v>-1.426121365901643</v>
       </c>
       <c r="D556" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E556">
         <v>-1.878985527382707</v>
@@ -30006,7 +30006,7 @@
         <v>-1.43657143149991</v>
       </c>
       <c r="D557" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E557">
         <v>-1.878985527382707</v>
@@ -30056,7 +30056,7 @@
         <v>-1.282291566067462</v>
       </c>
       <c r="D558" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E558">
         <v>-1.878985527382707</v>
@@ -30106,7 +30106,7 @@
         <v>-2.390900427299799</v>
       </c>
       <c r="D559" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E559">
         <v>-1.749918412157532</v>
@@ -30156,7 +30156,7 @@
         <v>-1.371342304503491</v>
       </c>
       <c r="D560" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E560">
         <v>-2.176137742690791</v>
@@ -30206,7 +30206,7 @@
         <v>-2.66184968886377</v>
       </c>
       <c r="D561" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E561">
         <v>-3.062340696434903</v>
@@ -30256,7 +30256,7 @@
         <v>-1.173473832043332</v>
       </c>
       <c r="D562" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E562">
         <v>-1.733424630557323</v>
@@ -30306,7 +30306,7 @@
         <v>-1.200137867726374</v>
       </c>
       <c r="D563" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E563">
         <v>-1.733424630557323</v>
@@ -30356,7 +30356,7 @@
         <v>-1.042228008991366</v>
       </c>
       <c r="D564" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E564">
         <v>-1.733424630557323</v>
@@ -30406,7 +30406,7 @@
         <v>-2.127604913087305</v>
       </c>
       <c r="D565" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E565">
         <v>-1.505014864011352</v>
@@ -30456,7 +30456,7 @@
         <v>-1.173621436501358</v>
       </c>
       <c r="D566" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E566">
         <v>-1.913326227585305</v>
@@ -30506,7 +30506,7 @@
         <v>-1.12934275099936</v>
       </c>
       <c r="D567" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E567">
         <v>-1.913326227585305</v>
@@ -30606,7 +30606,7 @@
         <v>-1.009918389553857</v>
       </c>
       <c r="D569" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E569">
         <v>-1.567675915850558</v>
@@ -30656,7 +30656,7 @@
         <v>-1.047078799419653</v>
       </c>
       <c r="D570" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E570">
         <v>-1.567675915850558</v>
@@ -30706,7 +30706,7 @@
         <v>-0.8868190061661174</v>
       </c>
       <c r="D571" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E571">
         <v>-1.567675915850558</v>
@@ -30756,7 +30756,7 @@
         <v>-1.957156329343485</v>
       </c>
       <c r="D572" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E572">
         <v>-1.346472615161401</v>
@@ -30806,7 +30806,7 @@
         <v>-1.016645810663759</v>
       </c>
       <c r="D573" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E573">
         <v>-1.743190968443955</v>
@@ -30856,7 +30856,7 @@
         <v>-0.9726804497642316</v>
       </c>
       <c r="D574" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E574">
         <v>-1.743190968443955</v>
@@ -30906,7 +30906,7 @@
         <v>-2.23129488574537</v>
       </c>
       <c r="D575" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E575">
         <v>-2.752324990932166</v>
@@ -30956,7 +30956,7 @@
         <v>-2.130775299238296</v>
       </c>
       <c r="D576" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E576">
         <v>-2.752324990932166</v>
@@ -31006,7 +31006,7 @@
         <v>-0.896848743456049</v>
       </c>
       <c r="D577" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E577">
         <v>-1.453090010130747</v>
@@ -31056,7 +31056,7 @@
         <v>-0.9412655386557081</v>
       </c>
       <c r="D578" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E578">
         <v>-1.453090010130747</v>
@@ -31106,7 +31106,7 @@
         <v>-0.7793811815214564</v>
       </c>
       <c r="D579" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E579">
         <v>-1.453090010130747</v>
@@ -31156,7 +31156,7 @@
         <v>-1.860567553008542</v>
       </c>
       <c r="D580" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E580">
         <v>-1.236868705342454</v>
@@ -31206,7 +31206,7 @@
         <v>-0.9081249434319556</v>
       </c>
       <c r="D581" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E581">
         <v>-1.625572543480143</v>
@@ -31256,7 +31256,7 @@
         <v>-0.8643761910498551</v>
       </c>
       <c r="D582" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E582">
         <v>-1.625572543480143</v>
@@ -31506,7 +31506,7 @@
         <v>2.369548064861299</v>
       </c>
       <c r="D587" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E587">
         <v>1.926875447544282</v>
@@ -31556,7 +31556,7 @@
         <v>2.406754555749798</v>
       </c>
       <c r="D588" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E588">
         <v>1.926875447544282</v>
@@ -31606,7 +31606,7 @@
         <v>2.636430011324778</v>
       </c>
       <c r="D589" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E589">
         <v>1.926875447544282</v>
@@ -31756,7 +31756,7 @@
         <v>1.522496508679898</v>
       </c>
       <c r="D592" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E592">
         <v>0.6622717696267184</v>
@@ -31806,7 +31806,7 @@
         <v>0.1531498180160149</v>
       </c>
       <c r="D593" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E593">
         <v>0.9108693301133393</v>
@@ -31856,7 +31856,7 @@
         <v>0.1409442431310648</v>
       </c>
       <c r="D594" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E594">
         <v>0.9108693301133393</v>
@@ -31906,7 +31906,7 @@
         <v>0.1454303059186906</v>
       </c>
       <c r="D595" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E595">
         <v>0.9108693301133393</v>
@@ -31956,7 +31956,7 @@
         <v>1.410955900715591</v>
       </c>
       <c r="D596" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E596">
         <v>0.5447199911733147</v>
@@ -32006,7 +32006,7 @@
         <v>0.02936423312947767</v>
       </c>
       <c r="D597" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E597">
         <v>0.7855252936185178</v>
@@ -32056,7 +32056,7 @@
         <v>0.01760393013260675</v>
       </c>
       <c r="D598" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E598">
         <v>0.7855252936185178</v>
@@ -32106,7 +32106,7 @@
         <v>0.02320317264043581</v>
       </c>
       <c r="D599" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E599">
         <v>0.7855252936185178</v>
@@ -32156,7 +32156,7 @@
         <v>1.411909103777088</v>
       </c>
       <c r="D600" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E600">
         <v>0.545724564459686</v>
@@ -32206,7 +32206,7 @@
         <v>0.03042207924163876</v>
       </c>
       <c r="D601" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E601">
         <v>0.7865964579371276</v>
@@ -32256,7 +32256,7 @@
         <v>0.0186579710429271</v>
       </c>
       <c r="D602" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E602">
         <v>0.7865964579371276</v>
@@ -32306,7 +32306,7 @@
         <v>0.02424770054614989</v>
       </c>
       <c r="D603" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E603">
         <v>0.7865964579371276</v>
@@ -32356,7 +32356,7 @@
         <v>1.336834708204746</v>
       </c>
       <c r="D604" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E604">
         <v>0.4666042433774571</v>
@@ -32406,7 +32406,7 @@
         <v>-0.05289401644343528</v>
       </c>
       <c r="D605" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E605">
         <v>0.7022314186013414</v>
@@ -32456,7 +32456,7 @@
         <v>-0.06435842645623069</v>
       </c>
       <c r="D606" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E606">
         <v>0.7022314186013414</v>
@@ -32506,7 +32506,7 @@
         <v>-0.05801945148821375</v>
       </c>
       <c r="D607" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E607">
         <v>0.7022314186013414</v>
@@ -32556,7 +32556,7 @@
         <v>1.405196855980458</v>
       </c>
       <c r="D608" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E608">
         <v>0.5386505787578475</v>
@@ -32606,7 +32606,7 @@
         <v>0.02297295793440135</v>
       </c>
       <c r="D609" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E609">
         <v>0.7790535527285396</v>
@@ -32656,7 +32656,7 @@
         <v>0.01123564513607533</v>
       </c>
       <c r="D610" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E610">
         <v>0.7790535527285396</v>
@@ -32706,7 +32706,7 @@
         <v>0.01689236314026132</v>
       </c>
       <c r="D611" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E611">
         <v>0.7790535527285396</v>
@@ -32756,7 +32756,7 @@
         <v>1.640062494593103</v>
       </c>
       <c r="D612" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E612">
         <v>0.786173646996323</v>
@@ -32806,7 +32806,7 @@
         <v>0.2836222494885536</v>
       </c>
       <c r="D613" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E613">
         <v>0.8556593002896253</v>
@@ -32856,7 +32856,7 @@
         <v>0.2709473493105357</v>
       </c>
       <c r="D614" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E614">
         <v>0.8556593002896253</v>
@@ -32906,7 +32906,7 @@
         <v>0.2742600988654935</v>
       </c>
       <c r="D615" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E615">
         <v>0.8556593002896253</v>
@@ -32956,7 +32956,7 @@
         <v>4.955952265919407</v>
       </c>
       <c r="D616" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E616">
         <v>3.781714175282632</v>
@@ -33006,7 +33006,7 @@
         <v>4.836984732824422</v>
       </c>
       <c r="D617" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E617">
         <v>3.781714175282632</v>
@@ -33056,7 +33056,7 @@
         <v>3.399157889651168</v>
       </c>
       <c r="D618" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E618">
         <v>4.104212001159528</v>
@@ -33106,7 +33106,7 @@
         <v>3.413995555126094</v>
       </c>
       <c r="D619" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E619">
         <v>4.104212001159528</v>
@@ -33156,7 +33156,7 @@
         <v>3.388941443617735</v>
       </c>
       <c r="D620" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E620">
         <v>4.104212001159528</v>
@@ -33256,7 +33256,7 @@
         <v>5.39157323691697</v>
       </c>
       <c r="D622" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E622">
         <v>4.199910307440291</v>
@@ -33306,7 +33306,7 @@
         <v>5.274981818209244</v>
       </c>
       <c r="D623" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E623">
         <v>4.199910307440291</v>
@@ -33356,7 +33356,7 @@
         <v>3.849827585101373</v>
       </c>
       <c r="D624" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E624">
         <v>4.558841887255165</v>
@@ -33406,7 +33406,7 @@
         <v>3.716953213901664</v>
       </c>
       <c r="D625" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E625">
         <v>4.558841887255165</v>
@@ -33456,7 +33456,7 @@
         <v>3.823770376486211</v>
       </c>
       <c r="D626" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E626">
         <v>4.558841887255165</v>
@@ -33506,7 +33506,7 @@
         <v>3.783996120363035</v>
       </c>
       <c r="D627" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E627">
         <v>4.558841887255165</v>
@@ -33556,7 +33556,7 @@
         <v>5.240670261409678</v>
       </c>
       <c r="D628" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E628">
         <v>5.66120447150224</v>
@@ -33606,7 +33606,7 @@
         <v>13.35754674285762</v>
       </c>
       <c r="D629" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E629">
         <v>12.11200719763176</v>
@@ -33656,7 +33656,7 @@
         <v>13.63116000592201</v>
       </c>
       <c r="D630" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E630">
         <v>12.11200719763176</v>
@@ -33706,7 +33706,7 @@
         <v>13.48645284737274</v>
       </c>
       <c r="D631" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E631">
         <v>12.11200719763176</v>
@@ -33756,7 +33756,7 @@
         <v>13.35488379452298</v>
       </c>
       <c r="D632" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E632">
         <v>12.11200719763176</v>
@@ -33956,7 +33956,7 @@
         <v>12.00063570730863</v>
       </c>
       <c r="D636" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E636">
         <v>10.96336131546034</v>
@@ -34006,7 +34006,7 @@
         <v>12.16808033477629</v>
       </c>
       <c r="D637" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E637">
         <v>10.96336131546034</v>
@@ -34056,7 +34056,7 @@
         <v>12.18508198198523</v>
       </c>
       <c r="D638" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E638">
         <v>10.96336131546034</v>
@@ -34106,7 +34106,7 @@
         <v>11.93759839099766</v>
       </c>
       <c r="D639" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E639">
         <v>10.96336131546034</v>
@@ -34156,7 +34156,7 @@
         <v>12.10741586438821</v>
       </c>
       <c r="D640" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E640">
         <v>10.96336131546034</v>
@@ -34206,7 +34206,7 @@
         <v>9.996138178122038</v>
       </c>
       <c r="D641" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E641">
         <v>10.07070134335836</v>
@@ -34256,7 +34256,7 @@
         <v>9.950336290139454</v>
       </c>
       <c r="D642" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E642">
         <v>10.07070134335836</v>
@@ -34306,7 +34306,7 @@
         <v>3.726163694975139</v>
       </c>
       <c r="D643" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E643">
         <v>2.839609794743838</v>
@@ -34342,7 +34342,7 @@
         <v>1</v>
       </c>
       <c r="P643" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -34356,7 +34356,7 @@
         <v>2.070333381900306</v>
       </c>
       <c r="D644" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E644">
         <v>2.539922141074908</v>
@@ -34392,7 +34392,7 @@
         <v>1</v>
       </c>
       <c r="P644" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -34406,7 +34406,7 @@
         <v>2.116517657129328</v>
       </c>
       <c r="D645" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E645">
         <v>2.539922141074908</v>
@@ -34442,7 +34442,7 @@
         <v>1</v>
       </c>
       <c r="P645" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -34456,7 +34456,7 @@
         <v>2.11502886699328</v>
       </c>
       <c r="D646" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E646">
         <v>2.539922141074908</v>
@@ -34492,7 +34492,7 @@
         <v>1</v>
       </c>
       <c r="P646" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -34506,7 +34506,7 @@
         <v>-1.891199427015522</v>
       </c>
       <c r="D647" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E647">
         <v>-1.014426804305828</v>
@@ -34556,7 +34556,7 @@
         <v>-0.2104376111309492</v>
       </c>
       <c r="D648" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E648">
         <v>-1.044462827056231</v>
@@ -34606,7 +34606,7 @@
         <v>-0.08646642933127069</v>
       </c>
       <c r="D649" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E649">
         <v>-1.044462827056231</v>
@@ -34656,7 +34656,7 @@
         <v>-1.78244121340599</v>
       </c>
       <c r="D650" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E650">
         <v>-1.021661386146215</v>
@@ -34706,7 +34706,7 @@
         <v>-1.791643374771013</v>
       </c>
       <c r="D651" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E651">
         <v>-1.021661386146215</v>
@@ -34806,7 +34806,7 @@
         <v>-3.477913686861863</v>
       </c>
       <c r="D653" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E653">
         <v>-4.521174267980019</v>
@@ -34856,7 +34856,7 @@
         <v>-3.500008845709822</v>
       </c>
       <c r="D654" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E654">
         <v>-4.521174267980019</v>
@@ -34906,7 +34906,7 @@
         <v>-5.32431700625196</v>
       </c>
       <c r="D655" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E655">
         <v>-4.437952967810602</v>
@@ -35106,7 +35106,7 @@
         <v>-7.577993318403742</v>
       </c>
       <c r="D659" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E659">
         <v>-6.567354813971781</v>
@@ -35156,7 +35156,7 @@
         <v>-7.616049006530655</v>
       </c>
       <c r="D660" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E660">
         <v>-6.567354813971781</v>
@@ -35206,7 +35206,7 @@
         <v>-2.725135055328662</v>
       </c>
       <c r="D661" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E661">
         <v>-2.204192425359905</v>
@@ -35256,7 +35256,7 @@
         <v>-2.704148294566643</v>
       </c>
       <c r="D662" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E662">
         <v>-2.204192425359905</v>
@@ -35306,7 +35306,7 @@
         <v>-1.813662855840759</v>
       </c>
       <c r="D663" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E663">
         <v>-2.111011489107529</v>
@@ -35356,7 +35356,7 @@
         <v>-1.845002662948879</v>
       </c>
       <c r="D664" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E664">
         <v>-2.111011489107529</v>
@@ -35406,7 +35406,7 @@
         <v>-1.891998249869552</v>
       </c>
       <c r="D665" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E665">
         <v>-2.111011489107529</v>
@@ -35456,7 +35456,7 @@
         <v>1.830334637155163</v>
       </c>
       <c r="D666" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E666">
         <v>2.267871354156875</v>
@@ -35556,7 +35556,7 @@
         <v>1.518226736005792</v>
       </c>
       <c r="D668" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E668">
         <v>1.938055203296901</v>
@@ -35606,7 +35606,7 @@
         <v>1.532693205245188</v>
       </c>
       <c r="D669" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E669">
         <v>1.906531480554312</v>
@@ -35656,7 +35656,7 @@
         <v>2.271617246908757</v>
       </c>
       <c r="D670" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E670">
         <v>2.443417201348617</v>
@@ -35706,7 +35706,7 @@
         <v>1.121481137909713</v>
       </c>
       <c r="D671" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E671">
         <v>1.518799216656364</v>
@@ -35756,7 +35756,7 @@
         <v>1.1435965093108</v>
       </c>
       <c r="D672" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E672">
         <v>1.506034151034157</v>
@@ -35806,7 +35806,7 @@
         <v>1.093271662200239</v>
       </c>
       <c r="D673" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E673">
         <v>1.506034151034157</v>
@@ -35856,7 +35856,7 @@
         <v>1.88237511166083</v>
       </c>
       <c r="D674" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E674">
         <v>1.894895897753045</v>
@@ -35906,7 +35906,7 @@
         <v>0.849444604521004</v>
       </c>
       <c r="D675" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E675">
         <v>1.303653302247787</v>
@@ -35956,7 +35956,7 @@
         <v>0.8477648181552304</v>
       </c>
       <c r="D676" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E676">
         <v>1.303653302247787</v>
@@ -36006,7 +36006,7 @@
         <v>0.7919735158820114</v>
       </c>
       <c r="D677" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E677">
         <v>1.303653302247787</v>
@@ -36106,7 +36106,7 @@
         <v>0.4742545585727438</v>
       </c>
       <c r="D679" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E679">
         <v>0.9209239764164039</v>
@@ -36156,7 +36156,7 @@
         <v>0.4776016477910456</v>
       </c>
       <c r="D680" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E680">
         <v>0.9209239764164039</v>
@@ -36206,7 +36206,7 @@
         <v>0.4397567303627969</v>
       </c>
       <c r="D681" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E681">
         <v>0.9209239764164039</v>
@@ -36256,7 +36256,7 @@
         <v>0.3764261482064555</v>
       </c>
       <c r="D682" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E682">
         <v>0.9209239764164039</v>
@@ -36306,7 +36306,7 @@
         <v>1.247389224131652</v>
       </c>
       <c r="D683" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E683">
         <v>1.332491309195859</v>
@@ -36356,7 +36356,7 @@
         <v>0.06936123169383812</v>
       </c>
       <c r="D684" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E684">
         <v>0.5078944952148738</v>
@@ -36406,7 +36406,7 @@
         <v>0.03202754929901275</v>
       </c>
       <c r="D685" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E685">
         <v>0.5078944952148738</v>
@@ -36456,7 +36456,7 @@
         <v>0.06067852147795705</v>
       </c>
       <c r="D686" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E686">
         <v>0.5078944952148738</v>
@@ -36506,7 +36506,7 @@
         <v>-0.07201953416415208</v>
       </c>
       <c r="D687" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E687">
         <v>0.5078944952148738</v>
@@ -36556,7 +36556,7 @@
         <v>0.07833359180957977</v>
       </c>
       <c r="D688" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E688">
         <v>0.4747573429780569</v>
@@ -36606,7 +36606,7 @@
         <v>0.07349428577797745</v>
       </c>
       <c r="D689" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E689">
         <v>0.4747573429780569</v>
@@ -36656,7 +36656,7 @@
         <v>0.8501534542622782</v>
       </c>
       <c r="D690" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E690">
         <v>0.8793612316938386</v>
@@ -36706,7 +36706,7 @@
         <v>1.041941578678037</v>
       </c>
       <c r="D691" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E691">
         <v>0.8793612316938386</v>
@@ -36756,7 +36756,7 @@
         <v>0.09878287093698646</v>
       </c>
       <c r="D692" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E692">
         <v>0.5379073494309932</v>
@@ -36806,7 +36806,7 @@
         <v>0.06440526340701602</v>
       </c>
       <c r="D693" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E693">
         <v>0.5379073494309932</v>
@@ -36856,7 +36856,7 @@
         <v>0.09312579028866175</v>
       </c>
       <c r="D694" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E694">
         <v>0.5379073494309932</v>
@@ -36906,7 +36906,7 @@
         <v>-0.03943315594804098</v>
       </c>
       <c r="D695" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E695">
         <v>0.5379073494309932</v>
@@ -36956,7 +36956,7 @@
         <v>0.109354989214884</v>
       </c>
       <c r="D696" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E696">
         <v>0.503900763410396</v>
@@ -37006,7 +37006,7 @@
         <v>0.1052807849130097</v>
       </c>
       <c r="D697" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E697">
         <v>0.503900763410396</v>
@@ -37156,7 +37156,7 @@
         <v>0.2871962372863237</v>
       </c>
       <c r="D700" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E700">
         <v>0.9851462492612573</v>
@@ -37206,7 +37206,7 @@
         <v>0.4202978053995725</v>
       </c>
       <c r="D701" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E701">
         <v>0.9851462492612573</v>
@@ -37256,7 +37256,7 @@
         <v>0.423892594321984</v>
       </c>
       <c r="D702" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E702">
         <v>0.9851462492612573</v>
@@ -37306,7 +37306,7 @@
         <v>0.4949561407287284</v>
       </c>
       <c r="D703" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E703">
         <v>0.9851462492612573</v>
@@ -37356,7 +37356,7 @@
         <v>0.4370951998607797</v>
       </c>
       <c r="D704" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E704">
         <v>0.9851462492612573</v>
@@ -37406,7 +37406,7 @@
         <v>0.4441837402800548</v>
       </c>
       <c r="D705" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E705">
         <v>0.9851462492612573</v>
@@ -37456,7 +37456,7 @@
         <v>1.300386876506556</v>
       </c>
       <c r="D706" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E706">
         <v>1.066703016477163</v>
@@ -37506,7 +37506,7 @@
         <v>1.387766562883906</v>
       </c>
       <c r="D707" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E707">
         <v>1.066703016477163</v>
@@ -37556,7 +37556,7 @@
         <v>1.3704879139321</v>
       </c>
       <c r="D708" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E708">
         <v>1.066703016477163</v>
@@ -37606,7 +37606,7 @@
         <v>1.275437395219328</v>
       </c>
       <c r="D709" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E709">
         <v>1.066703016477163</v>
@@ -37656,7 +37656,7 @@
         <v>1.361652497764391</v>
       </c>
       <c r="D710" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E710">
         <v>1.066703016477163</v>
@@ -37706,7 +37706,7 @@
         <v>1.930987869234452</v>
       </c>
       <c r="D711" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E711">
         <v>2.371871770269339</v>
@@ -37756,7 +37756,7 @@
         <v>1.92605256665067</v>
       </c>
       <c r="D712" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E712">
         <v>2.371871770269339</v>
@@ -37806,7 +37806,7 @@
         <v>1.931979302309637</v>
       </c>
       <c r="D713" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E713">
         <v>2.371871770269339</v>
@@ -38056,7 +38056,7 @@
         <v>1.929178123500783</v>
       </c>
       <c r="D718" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E718">
         <v>1.904587279830026</v>
@@ -38106,7 +38106,7 @@
         <v>1.854846069494888</v>
       </c>
       <c r="D719" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E719">
         <v>1.904587279830026</v>
@@ -38156,7 +38156,7 @@
         <v>1.986094439213979</v>
       </c>
       <c r="D720" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E720">
         <v>2.427791166532621</v>
@@ -38406,7 +38406,7 @@
         <v>1.979578720846286</v>
       </c>
       <c r="D725" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E725">
         <v>1.826397195864058</v>
@@ -38456,7 +38456,7 @@
         <v>1.907972820522667</v>
       </c>
       <c r="D726" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E726">
         <v>1.826397195864058</v>
@@ -38706,7 +38706,7 @@
         <v>2.097186801510141</v>
       </c>
       <c r="D731" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E731">
         <v>2.32091239377587</v>
@@ -38756,7 +38756,7 @@
         <v>2.031942288135359</v>
       </c>
       <c r="D732" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E732">
         <v>2.32091239377587</v>
@@ -39306,7 +39306,7 @@
         <v>2.417703574220445</v>
       </c>
       <c r="D743" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E743">
         <v>2.366004733779205</v>
@@ -39356,7 +39356,7 @@
         <v>2.369795720055587</v>
       </c>
       <c r="D744" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E744">
         <v>2.366004733779205</v>
@@ -39406,7 +39406,7 @@
         <v>2.268006981238599</v>
       </c>
       <c r="D745" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E745">
         <v>2.366004733779205</v>
@@ -39656,7 +39656,7 @@
         <v>2.653994288166441</v>
       </c>
       <c r="D750" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E750">
         <v>3.270325396942835</v>
@@ -39706,7 +39706,7 @@
         <v>3.683411667997373</v>
       </c>
       <c r="D751" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E751">
         <v>3.25827796154194</v>
@@ -39756,7 +39756,7 @@
         <v>3.70572139342618</v>
       </c>
       <c r="D752" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E752">
         <v>3.25827796154194</v>
@@ -39806,7 +39806,7 @@
         <v>3.758092829526726</v>
       </c>
       <c r="D753" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E753">
         <v>3.25827796154194</v>
@@ -39856,7 +39856,7 @@
         <v>3.738113399750641</v>
       </c>
       <c r="D754" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E754">
         <v>3.25827796154194</v>
@@ -39906,7 +39906,7 @@
         <v>2.866153368128345</v>
       </c>
       <c r="D755" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E755">
         <v>3.327619714376737</v>
@@ -39956,7 +39956,7 @@
         <v>2.707907697511514</v>
       </c>
       <c r="D756" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E756">
         <v>3.327619714376737</v>
@@ -40006,7 +40006,7 @@
         <v>3.773013759826179</v>
       </c>
       <c r="D757" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E757">
         <v>3.350810436248167</v>
@@ -40056,7 +40056,7 @@
         <v>3.799493645503623</v>
       </c>
       <c r="D758" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E758">
         <v>3.350810436248167</v>
@@ -40106,7 +40106,7 @@
         <v>3.854682757447843</v>
       </c>
       <c r="D759" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E759">
         <v>3.350810436248167</v>
@@ -40156,7 +40156,7 @@
         <v>3.834252499536769</v>
       </c>
       <c r="D760" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E760">
         <v>3.350810436248167</v>
@@ -40206,7 +40206,7 @@
         <v>2.950458229371047</v>
       </c>
       <c r="D761" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E761">
         <v>3.434578689402571</v>
@@ -40256,7 +40256,7 @@
         <v>2.80855507864752</v>
       </c>
       <c r="D762" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E762">
         <v>3.434578689402571</v>
@@ -40306,7 +40306,7 @@
         <v>4.059126950443869</v>
       </c>
       <c r="D763" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E763">
         <v>3.646280787816876</v>
@@ -40356,7 +40356,7 @@
         <v>4.098922795936224</v>
       </c>
       <c r="D764" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E764">
         <v>3.646280787816876</v>
@@ -40406,7 +40406,7 @@
         <v>4.163109178025654</v>
       </c>
       <c r="D765" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E765">
         <v>3.646280787816876</v>
@@ -40456,7 +40456,7 @@
         <v>4.141239356891347</v>
       </c>
       <c r="D766" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E766">
         <v>3.646280787816876</v>
@@ -40506,7 +40506,7 @@
         <v>3.219656552115741</v>
       </c>
       <c r="D767" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E767">
         <v>3.776115064114756</v>
@@ -40556,7 +40556,7 @@
         <v>3.129937568234435</v>
       </c>
       <c r="D768" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E768">
         <v>3.776115064114756</v>
@@ -40606,7 +40606,7 @@
         <v>4.587925539948646</v>
       </c>
       <c r="D769" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E769">
         <v>4.161392287167092</v>
@@ -40656,7 +40656,7 @@
         <v>4.61478704123244</v>
       </c>
       <c r="D770" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E770">
         <v>4.161392287167092</v>
@@ -40706,7 +40706,7 @@
         <v>4.62093591099028</v>
       </c>
       <c r="D771" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E771">
         <v>4.161392287167092</v>
@@ -40756,7 +40756,7 @@
         <v>4.700807783315709</v>
       </c>
       <c r="D772" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E772">
         <v>4.161392287167092</v>
@@ -40806,7 +40806,7 @@
         <v>4.676428283743642</v>
       </c>
       <c r="D773" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E773">
         <v>4.161392287167092</v>
@@ -40856,7 +40856,7 @@
         <v>3.68896641997684</v>
       </c>
       <c r="D774" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E774">
         <v>4.371536273473288</v>
@@ -40906,7 +40906,7 @@
         <v>3.690223279464329</v>
       </c>
       <c r="D775" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E775">
         <v>4.371536273473288</v>
@@ -40956,7 +40956,7 @@
         <v>4.640951769621907</v>
       </c>
       <c r="D776" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E776">
         <v>4.4619926496501</v>
@@ -41006,7 +41006,7 @@
         <v>4.679892441845094</v>
       </c>
       <c r="D777" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E777">
         <v>4.229657336851623</v>
@@ -41056,7 +41056,7 @@
         <v>4.69011559593246</v>
       </c>
       <c r="D778" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E778">
         <v>4.229657336851623</v>
@@ -41106,7 +41106,7 @@
         <v>4.772066184752546</v>
       </c>
       <c r="D779" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E779">
         <v>4.229657336851623</v>
@@ -41156,7 +41156,7 @@
         <v>4.747354090541334</v>
       </c>
       <c r="D780" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E780">
         <v>4.229657336851623</v>
@@ -41206,7 +41206,7 @@
         <v>3.751161617496972</v>
       </c>
       <c r="D781" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E781">
         <v>4.450444351610463</v>
@@ -41256,7 +41256,7 @@
         <v>3.764475032653471</v>
       </c>
       <c r="D782" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E782">
         <v>4.450444351610463</v>
@@ -41306,7 +41306,7 @@
         <v>4.722853199511387</v>
       </c>
       <c r="D783" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E783">
         <v>4.494475032653471</v>
@@ -41356,7 +41356,7 @@
         <v>4.769412494689534</v>
       </c>
       <c r="D784" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E784">
         <v>4.258529056637524</v>
@@ -41406,7 +41406,7 @@
         <v>4.719374147530353</v>
       </c>
       <c r="D785" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E785">
         <v>4.258529056637524</v>
@@ -41456,7 +41456,7 @@
         <v>4.802203899559511</v>
       </c>
       <c r="D786" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E786">
         <v>4.258529056637524</v>
@@ -41506,7 +41506,7 @@
         <v>4.777351139234847</v>
       </c>
       <c r="D787" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E787">
         <v>4.258529056637524</v>
@@ -41556,7 +41556,7 @@
         <v>3.777466180712386</v>
       </c>
       <c r="D788" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E788">
         <v>4.483817387026809</v>
@@ -41606,7 +41606,7 @@
         <v>3.795878742481499</v>
       </c>
       <c r="D789" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E789">
         <v>4.483817387026809</v>
@@ -41706,7 +41706,7 @@
         <v>4.79820132156508</v>
       </c>
       <c r="D791" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E791">
         <v>4.288184799253363</v>
@@ -41756,7 +41756,7 @@
         <v>4.833160015785789</v>
       </c>
       <c r="D792" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E792">
         <v>4.288184799253363</v>
@@ -41806,7 +41806,7 @@
         <v>4.80816276950441</v>
       </c>
       <c r="D793" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E793">
         <v>4.288184799253363</v>
@@ -41856,7 +41856,7 @@
         <v>3.804485054618168</v>
       </c>
       <c r="D794" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E794">
         <v>4.518096680257542</v>
@@ -41906,7 +41906,7 @@
         <v>3.828135232318215</v>
       </c>
       <c r="D795" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E795">
         <v>4.518096680257542</v>
@@ -41956,7 +41956,7 @@
         <v>4.793071896789968</v>
       </c>
       <c r="D796" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E796">
         <v>4.976887297607179</v>
@@ -42006,7 +42006,7 @@
         <v>4.969372152154773</v>
       </c>
       <c r="D797" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E797">
         <v>4.976887297607179</v>
@@ -42056,7 +42056,7 @@
         <v>4.88512898189049</v>
       </c>
       <c r="D798" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E798">
         <v>4.377730105560969</v>
@@ -42106,7 +42106,7 @@
         <v>4.926631791066686</v>
       </c>
       <c r="D799" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E799">
         <v>4.377730105560969</v>
@@ -42156,7 +42156,7 @@
         <v>4.901198270454942</v>
       </c>
       <c r="D800" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E800">
         <v>4.377730105560969</v>
@@ -42206,7 +42206,7 @@
         <v>3.886068354396595</v>
       </c>
       <c r="D801" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E801">
         <v>4.621602765136856</v>
@@ -42256,7 +42256,7 @@
         <v>3.925533476572406</v>
       </c>
       <c r="D802" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E802">
         <v>4.621602765136856</v>
@@ -42306,7 +42306,7 @@
         <v>4.900504450642575</v>
       </c>
       <c r="D803" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E803">
         <v>5.323640452137244</v>
@@ -42356,7 +42356,7 @@
         <v>5.068842699478202</v>
       </c>
       <c r="D804" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E804">
         <v>5.323640452137244</v>
@@ -42406,7 +42406,7 @@
         <v>4.666640897343765</v>
       </c>
       <c r="D805" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E805">
         <v>4.152662706046714</v>
@@ -42456,7 +42456,7 @@
         <v>4.691695419101137</v>
       </c>
       <c r="D806" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E806">
         <v>4.152662706046714</v>
@@ -42506,7 +42506,7 @@
         <v>4.667358450983981</v>
       </c>
       <c r="D807" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E807">
         <v>4.152662706046714</v>
@@ -42556,7 +42556,7 @@
         <v>3.681013037908578</v>
       </c>
       <c r="D808" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E808">
         <v>4.361445685795776</v>
@@ -42606,7 +42606,7 @@
         <v>3.680728132155562</v>
       </c>
       <c r="D809" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E809">
         <v>4.361445685795776</v>
@@ -42656,7 +42656,7 @@
         <v>4.715209316235119</v>
       </c>
       <c r="D810" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E810">
         <v>5.110369355335455</v>
@@ -42706,7 +42706,7 @@
         <v>4.818828730712063</v>
       </c>
       <c r="D811" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E811">
         <v>5.110369355335455</v>
@@ -42756,7 +42756,7 @@
         <v>4.677780979452113</v>
       </c>
       <c r="D812" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E812">
         <v>4.139332770280262</v>
@@ -42792,7 +42792,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42806,7 +42806,7 @@
         <v>4.685525171192977</v>
       </c>
       <c r="D813" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E813">
         <v>4.139332770280262</v>
@@ -42842,7 +42842,7 @@
         <v>1</v>
       </c>
       <c r="P813" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="814" spans="1:16">
@@ -42856,7 +42856,7 @@
         <v>3.668868346126232</v>
       </c>
       <c r="D814" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E814">
         <v>4.346037514002399</v>
@@ -42892,7 +42892,7 @@
         <v>1</v>
       </c>
       <c r="P814" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="815" spans="1:16">
@@ -42906,7 +42906,7 @@
         <v>3.666229188623965</v>
       </c>
       <c r="D815" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E815">
         <v>4.346037514002399</v>
@@ -42942,7 +42942,7 @@
         <v>1</v>
       </c>
       <c r="P815" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="816" spans="1:16">
@@ -42956,7 +42956,7 @@
         <v>4.699557601157337</v>
       </c>
       <c r="D816" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E816">
         <v>5.177220717987302</v>
@@ -42992,7 +42992,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -43006,7 +43006,7 @@
         <v>4.80402129902022</v>
       </c>
       <c r="D817" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E817">
         <v>5.177220717987302</v>
@@ -43042,7 +43042,7 @@
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -43056,7 +43056,7 @@
         <v>3.803770388208568</v>
       </c>
       <c r="D818" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E818">
         <v>4.517189971136271</v>
@@ -43092,7 +43092,7 @@
         <v>1</v>
       </c>
       <c r="P818" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="819" spans="1:16">
@@ -43106,7 +43106,7 @@
         <v>3.827282027634027</v>
       </c>
       <c r="D819" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E819">
         <v>4.517189971136271</v>
@@ -43142,7 +43142,7 @@
         <v>1</v>
       </c>
       <c r="P819" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="820" spans="1:16">
@@ -43156,7 +43156,7 @@
         <v>4.873415313145802</v>
       </c>
       <c r="D820" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E820">
         <v>5.19492340011272</v>
@@ -43192,7 +43192,7 @@
         <v>1</v>
       </c>
       <c r="P820" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="821" spans="1:16">
@@ -43206,7 +43206,7 @@
         <v>4.968500794179431</v>
       </c>
       <c r="D821" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E821">
         <v>5.19492340011272</v>
@@ -43242,7 +43242,7 @@
         <v>1</v>
       </c>
       <c r="P821" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="822" spans="1:16">
@@ -43256,7 +43256,7 @@
         <v>4.15270680227816</v>
       </c>
       <c r="D822" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E822">
         <v>4.95989138417376</v>
@@ -43306,7 +43306,7 @@
         <v>4.243859858869514</v>
       </c>
       <c r="D823" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E823">
         <v>4.95989138417376</v>
@@ -43356,7 +43356,7 @@
         <v>5.32311411416597</v>
       </c>
       <c r="D824" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E824">
         <v>5.313449235585522</v>
@@ -43406,7 +43406,7 @@
         <v>5.393941983526312</v>
       </c>
       <c r="D825" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E825">
         <v>5.313449235585522</v>
@@ -43456,7 +43456,7 @@
         <v>4.427422884586818</v>
       </c>
       <c r="D826" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E826">
         <v>5.308428231915627</v>
@@ -43506,7 +43506,7 @@
         <v>4.571829727187204</v>
       </c>
       <c r="D827" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E827">
         <v>5.308428231915627</v>
@@ -43656,7 +43656,7 @@
         <v>4.492909746290213</v>
       </c>
       <c r="D830" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E830">
         <v>5.391512498969801</v>
@@ -43706,7 +43706,7 @@
         <v>4.650011234541658</v>
       </c>
       <c r="D831" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E831">
         <v>5.391512498969801</v>
@@ -43756,7 +43756,7 @@
         <v>5.699620454673608</v>
       </c>
       <c r="D832" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E832">
         <v>5.584366029175103</v>
@@ -43806,7 +43806,7 @@
         <v>5.808734877829779</v>
       </c>
       <c r="D833" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E833">
         <v>5.584366029175103</v>
@@ -43856,7 +43856,7 @@
         <v>4.400292583551392</v>
       </c>
       <c r="D834" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E834">
         <v>5.274007569238329</v>
@@ -43906,7 +43906,7 @@
         <v>4.539440210041969</v>
       </c>
       <c r="D835" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E835">
         <v>5.274007569238329</v>
@@ -43956,7 +43956,7 @@
         <v>5.577658014435989</v>
       </c>
       <c r="D836" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E836">
         <v>5.419384274951261</v>
@@ -44006,7 +44006,7 @@
         <v>5.695811278340734</v>
       </c>
       <c r="D837" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E837">
         <v>5.419384274951261</v>
@@ -44056,7 +44056,7 @@
         <v>4.244834847003374</v>
       </c>
       <c r="D838" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E838">
         <v>5.076775761772995</v>
@@ -44106,7 +44106,7 @@
         <v>4.353846949697878</v>
       </c>
       <c r="D839" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E839">
         <v>5.076775761772995</v>
@@ -44156,7 +44156,7 @@
         <v>5.441845979293118</v>
       </c>
       <c r="D840" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E840">
         <v>5.241229035520813</v>
@@ -44206,7 +44206,7 @@
         <v>5.506269225223365</v>
       </c>
       <c r="D841" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E841">
         <v>5.241229035520813</v>
@@ -44256,7 +44256,7 @@
         <v>4.273702172751312</v>
       </c>
       <c r="D842" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E842">
         <v>5.113400216498656</v>
@@ -44306,7 +44306,7 @@
         <v>4.38831021426059</v>
       </c>
       <c r="D843" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E843">
         <v>5.113400216498656</v>
@@ -44356,7 +44356,7 @@
         <v>5.479049324240996</v>
       </c>
       <c r="D844" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E844">
         <v>5.245636638515749</v>
@@ -44406,7 +44406,7 @@
         <v>5.54146575073422</v>
       </c>
       <c r="D845" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E845">
         <v>5.245636638515749</v>
@@ -44456,7 +44456,7 @@
         <v>5.560572351202844</v>
       </c>
       <c r="D846" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E846">
         <v>5.245636638515749</v>
@@ -44506,7 +44506,7 @@
         <v>4.347094984058314</v>
       </c>
       <c r="D847" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E847">
         <v>5.206514892876123</v>
@@ -44556,7 +44556,7 @@
         <v>4.475930241663201</v>
       </c>
       <c r="D848" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E848">
         <v>5.206514892876123</v>
@@ -44606,7 +44606,7 @@
         <v>5.573635781593871</v>
       </c>
       <c r="D849" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E849">
         <v>5.027134568809939</v>
@@ -44656,7 +44656,7 @@
         <v>5.630950034039015</v>
       </c>
       <c r="D850" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E850">
         <v>5.027134568809939</v>
@@ -44706,7 +44706,7 @@
         <v>5.633670806314765</v>
       </c>
       <c r="D851" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E851">
         <v>5.027134568809939</v>
@@ -44756,7 +44756,7 @@
         <v>5.402224156621893</v>
       </c>
       <c r="D852" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E852">
         <v>5.844101410902759</v>
@@ -44806,7 +44806,7 @@
         <v>5.365845252056308</v>
       </c>
       <c r="D853" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E853">
         <v>5.844101410902759</v>
@@ -44856,7 +44856,7 @@
         <v>5.351830183888868</v>
       </c>
       <c r="D854" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E854">
         <v>5.844101410902759</v>
@@ -44906,7 +44906,7 @@
         <v>6.177027170255381</v>
       </c>
       <c r="D855" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E855">
         <v>5.99166223366742</v>
@@ -44956,7 +44956,7 @@
         <v>6.176389906463717</v>
       </c>
       <c r="D856" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E856">
         <v>5.99166223366742</v>
@@ -45006,7 +45006,7 @@
         <v>6.145283329101833</v>
       </c>
       <c r="D857" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E857">
         <v>5.99166223366742</v>
@@ -45056,7 +45056,7 @@
         <v>6.120874288201371</v>
       </c>
       <c r="D858" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E858">
         <v>5.99166223366742</v>
@@ -45106,7 +45106,7 @@
         <v>5.357680894209214</v>
       </c>
       <c r="D859" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E859">
         <v>5.805234021262887</v>
@@ -45156,7 +45156,7 @@
         <v>5.321733849528515</v>
       </c>
       <c r="D860" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E860">
         <v>5.805234021262887</v>
@@ -45206,7 +45206,7 @@
         <v>5.307410310014729</v>
       </c>
       <c r="D861" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E861">
         <v>5.805234021262887</v>
@@ -45256,7 +45256,7 @@
         <v>6.132545602111971</v>
       </c>
       <c r="D862" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E862">
         <v>5.861451650138072</v>
@@ -45306,7 +45306,7 @@
         <v>6.135239828860867</v>
       </c>
       <c r="D863" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E863">
         <v>5.861451650138072</v>
@@ -45356,7 +45356,7 @@
         <v>6.106045773846343</v>
       </c>
       <c r="D864" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E864">
         <v>5.861451650138072</v>
@@ -45406,7 +45406,7 @@
         <v>6.081451650138071</v>
       </c>
       <c r="D865" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E865">
         <v>5.861451650138072</v>
@@ -45456,7 +45456,7 @@
         <v>5.32659332168792</v>
       </c>
       <c r="D866" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E866">
         <v>5.778107746071176</v>
@@ -45506,7 +45506,7 @@
         <v>5.290947680064908</v>
       </c>
       <c r="D867" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E867">
         <v>5.778107746071176</v>
@@ -45556,7 +45556,7 @@
         <v>5.276408852652773</v>
       </c>
       <c r="D868" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E868">
         <v>5.778107746071176</v>
@@ -45606,7 +45606,7 @@
         <v>6.101501087170347</v>
       </c>
       <c r="D869" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E869">
         <v>5.779952436422644</v>
@@ -45656,7 +45656,7 @@
         <v>6.10652042322139</v>
       </c>
       <c r="D870" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E870">
         <v>5.779952436422644</v>
@@ -45706,7 +45706,7 @@
         <v>6.078661153176616</v>
       </c>
       <c r="D871" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E871">
         <v>5.779952436422644</v>
@@ -45756,7 +45756,7 @@
         <v>6.053937856729336</v>
       </c>
       <c r="D872" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E872">
         <v>5.779952436422644</v>
@@ -45806,7 +45806,7 @@
         <v>5.388093706617724</v>
       </c>
       <c r="D873" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E873">
         <v>5.831771516854801</v>
@@ -45856,7 +45856,7 @@
         <v>5.351851800874894</v>
       </c>
       <c r="D874" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E874">
         <v>5.831771516854801</v>
@@ -45906,7 +45906,7 @@
         <v>5.337738876405488</v>
       </c>
       <c r="D875" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E875">
         <v>5.831771516854801</v>
@@ -45956,7 +45956,7 @@
         <v>6.162916291511607</v>
       </c>
       <c r="D876" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E876">
         <v>5.809432743446582</v>
@@ -46006,7 +46006,7 @@
         <v>6.163335875781195</v>
       </c>
       <c r="D877" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E877">
         <v>5.809432743446582</v>
@@ -46056,7 +46056,7 @@
         <v>6.132836007491512</v>
       </c>
       <c r="D878" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E878">
         <v>5.809432743446582</v>
@@ -46106,7 +46106,7 @@
         <v>6.10836825280987</v>
       </c>
       <c r="D879" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E879">
         <v>5.809432743446582</v>
@@ -46156,7 +46156,7 @@
         <v>5.504130795560521</v>
       </c>
       <c r="D880" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E880">
         <v>5.933022716347823</v>
@@ -46206,7 +46206,7 @@
         <v>5.46676387648999</v>
       </c>
       <c r="D881" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E881">
         <v>5.933022716347823</v>
@@ -46256,7 +46256,7 @@
         <v>5.453454532968942</v>
       </c>
       <c r="D882" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E882">
         <v>5.933022716347823</v>
@@ -46306,7 +46306,7 @@
         <v>6.278792664264731</v>
       </c>
       <c r="D883" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E883">
         <v>5.82295074691097</v>
@@ -46356,7 +46356,7 @@
         <v>6.270533574292061</v>
       </c>
       <c r="D884" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E884">
         <v>5.82295074691097</v>
@@ -46406,7 +46406,7 @@
         <v>6.235051504122564</v>
       </c>
       <c r="D885" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E885">
         <v>5.854447210967837</v>
@@ -46456,7 +46456,7 @@
         <v>6.211065898009934</v>
       </c>
       <c r="D886" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E886">
         <v>5.854447210967837</v>
@@ -46506,7 +46506,7 @@
         <v>5.527008554379917</v>
       </c>
       <c r="D887" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E887">
         <v>5.952985303683308</v>
@@ -46556,7 +46556,7 @@
         <v>5.489419828783438</v>
       </c>
       <c r="D888" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E888">
         <v>5.952985303683308</v>
@@ -46606,7 +46606,7 @@
         <v>5.47626891849521</v>
       </c>
       <c r="D889" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E889">
         <v>5.952985303683308</v>
@@ -46656,7 +46656,7 @@
         <v>6.301638736437564</v>
       </c>
       <c r="D890" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E890">
         <v>5.842438034547991</v>
@@ -46706,7 +46706,7 @@
         <v>6.291668567550424</v>
       </c>
       <c r="D891" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E891">
         <v>5.842438034547991</v>
@@ -46756,7 +46756,7 @@
         <v>6.255204211337434</v>
       </c>
       <c r="D892" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E892">
         <v>5.805943847222144</v>
@@ -46806,7 +46806,7 @@
         <v>6.231313665164498</v>
       </c>
       <c r="D893" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E893">
         <v>5.805943847222144</v>
@@ -46856,7 +46856,7 @@
         <v>5.362358580199855</v>
       </c>
       <c r="D894" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E894">
         <v>5.809315658623142</v>
@@ -46906,7 +46906,7 @@
         <v>5.326366183992933</v>
       </c>
       <c r="D895" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E895">
         <v>5.809315658623142</v>
@@ -46956,7 +46956,7 @@
         <v>5.31207503842645</v>
       </c>
       <c r="D896" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E896">
         <v>5.809315658623142</v>
@@ -47006,7 +47006,7 @@
         <v>6.137216809313153</v>
       </c>
       <c r="D897" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E897">
         <v>5.660449825716769</v>
@@ -47056,7 +47056,7 @@
         <v>6.139561181431169</v>
       </c>
       <c r="D898" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E898">
         <v>5.660449825716769</v>
@@ -47106,7 +47106,7 @@
         <v>6.110166283943363</v>
       </c>
       <c r="D899" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E899">
         <v>5.660449825716769</v>
@@ -47156,7 +47156,7 @@
         <v>6.085591596603473</v>
       </c>
       <c r="D900" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E900">
         <v>5.660449825716769</v>
@@ -47206,7 +47206,7 @@
         <v>5.21583595429709</v>
       </c>
       <c r="D901" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E901">
         <v>5.6814635058271</v>
@@ -47256,7 +47256,7 @@
         <v>5.181264137565678</v>
       </c>
       <c r="D902" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E902">
         <v>5.6814635058271</v>
@@ -47306,7 +47306,7 @@
         <v>5.16595829237383</v>
       </c>
       <c r="D903" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E903">
         <v>5.6814635058271</v>
@@ -47356,7 +47356,7 @@
         <v>5.990897123335461</v>
       </c>
       <c r="D904" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E904">
         <v>5.530974153520144</v>
@@ -47406,7 +47406,7 @@
         <v>6.00595829237383</v>
       </c>
       <c r="D905" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E905">
         <v>5.530974153520144</v>
@@ -47456,7 +47456,7 @@
         <v>6.004200251407424</v>
       </c>
       <c r="D906" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E906">
         <v>5.530974153520144</v>
@@ -47506,7 +47506,7 @@
         <v>5.981096491596882</v>
       </c>
       <c r="D907" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E907">
         <v>5.530974153520144</v>
@@ -47556,7 +47556,7 @@
         <v>5.955912984481774</v>
       </c>
       <c r="D908" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E908">
         <v>5.530974153520144</v>
@@ -47606,7 +47606,7 @@
         <v>5.246905622239758</v>
       </c>
       <c r="D909" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E909">
         <v>5.708574157910038</v>
@@ -47656,7 +47656,7 @@
         <v>5.212032576040759</v>
       </c>
       <c r="D910" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E910">
         <v>5.708574157910038</v>
@@ -47706,7 +47706,7 @@
         <v>5.19694189475433</v>
       </c>
       <c r="D911" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E911">
         <v>5.708574157910038</v>
@@ -47756,7 +47756,7 @@
         <v>6.021923758497046</v>
       </c>
       <c r="D912" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E912">
         <v>5.558429067851753</v>
@@ -47806,7 +47806,7 @@
         <v>6.03694189475433</v>
       </c>
       <c r="D913" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E913">
         <v>5.558429067851753</v>
@@ -47856,7 +47856,7 @@
         <v>6.032903116390471</v>
       </c>
       <c r="D914" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E914">
         <v>5.558429067851753</v>
@@ -47906,7 +47906,7 @@
         <v>6.008465340366325</v>
       </c>
       <c r="D915" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E915">
         <v>5.558429067851753</v>
@@ -47956,7 +47956,7 @@
         <v>5.983410931594468</v>
       </c>
       <c r="D916" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E916">
         <v>5.558429067851753</v>
@@ -48006,7 +48006,7 @@
         <v>5.260021169191447</v>
       </c>
       <c r="D917" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E917">
         <v>5.720018471732149</v>
@@ -48056,7 +48056,7 @@
         <v>5.22502096394998</v>
       </c>
       <c r="D918" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E918">
         <v>5.720018471732149</v>
@@ -48106,7 +48106,7 @@
         <v>5.210021110551029</v>
       </c>
       <c r="D919" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E919">
         <v>5.720018471732149</v>
@@ -48156,7 +48156,7 @@
         <v>6.035021139871239</v>
       </c>
       <c r="D920" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E920">
         <v>5.570018706293828</v>
@@ -48206,7 +48206,7 @@
         <v>6.050021110551029</v>
       </c>
       <c r="D921" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E921">
         <v>5.570018706293828</v>
@@ -48256,7 +48256,7 @@
         <v>6.045019556579911</v>
       </c>
       <c r="D922" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E922">
         <v>5.570018706293828</v>
@@ -48306,7 +48306,7 @@
         <v>6.020018647653407</v>
       </c>
       <c r="D923" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E923">
         <v>5.570018706293828</v>
@@ -48356,7 +48356,7 @@
         <v>5.995018735614037</v>
       </c>
       <c r="D924" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E924">
         <v>5.570018706293828</v>
@@ -48456,7 +48456,7 @@
         <v>5.615668781285493</v>
       </c>
       <c r="D926" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E926">
         <v>6.030348105553824</v>
@@ -48506,7 +48506,7 @@
         <v>5.577220469001563</v>
       </c>
       <c r="D927" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E927">
         <v>6.030348105553824</v>
@@ -48556,7 +48556,7 @@
         <v>5.56468354920437</v>
       </c>
       <c r="D928" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E928">
         <v>6.030348105553824</v>
@@ -48606,7 +48606,7 @@
         <v>6.390176165244933</v>
       </c>
       <c r="D929" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E929">
         <v>5.917958864945399</v>
@@ -48656,7 +48656,7 @@
         <v>6.373574899054605</v>
       </c>
       <c r="D930" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E930">
         <v>5.917958864945399</v>
@@ -48706,7 +48706,7 @@
         <v>6.333303801797193</v>
       </c>
       <c r="D931" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E931">
         <v>5.884289033878317</v>
@@ -48756,7 +48756,7 @@
         <v>6.309781649918879</v>
       </c>
       <c r="D932" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E932">
         <v>5.884289033878317</v>
@@ -48806,7 +48806,7 @@
         <v>6.262613928093605</v>
       </c>
       <c r="D933" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E933">
         <v>6.212195151647427</v>
@@ -48856,7 +48856,7 @@
         <v>7.24816372476549</v>
       </c>
       <c r="D934" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E934">
         <v>7.595603386150444</v>
@@ -48906,7 +48906,7 @@
         <v>7.261638134101141</v>
       </c>
       <c r="D935" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E935">
         <v>7.595603386150444</v>
@@ -48956,7 +48956,7 @@
         <v>7.253775244709231</v>
       </c>
       <c r="D936" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E936">
         <v>7.595603386150444</v>
@@ -49006,7 +49006,7 @@
         <v>8.181523875261066</v>
       </c>
       <c r="D937" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E937">
         <v>7.445946162670672</v>
@@ -49056,7 +49056,7 @@
         <v>8.030757870733884</v>
       </c>
       <c r="D938" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E938">
         <v>7.445946162670672</v>
@@ -49106,7 +49106,7 @@
         <v>7.913466275542353</v>
       </c>
       <c r="D939" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E939">
         <v>7.567169202558158</v>
@@ -49156,7 +49156,7 @@
         <v>7.897397720238308</v>
       </c>
       <c r="D940" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E940">
         <v>7.567169202558158</v>
@@ -49206,7 +49206,7 @@
         <v>7.886369390677626</v>
       </c>
       <c r="D941" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E941">
         <v>7.567169202558158</v>
@@ -49256,7 +49256,7 @@
         <v>6.461998806928756</v>
       </c>
       <c r="D942" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E942">
         <v>6.809943004706455</v>
@@ -49306,7 +49306,7 @@
         <v>6.455649148235951</v>
       </c>
       <c r="D943" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E943">
         <v>6.809943004706455</v>
@@ -49356,7 +49356,7 @@
         <v>7.28237921649739</v>
       </c>
       <c r="D944" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E944">
         <v>6.678991980784874</v>
@@ -49406,7 +49406,7 @@
         <v>7.198955530379694</v>
       </c>
       <c r="D945" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E945">
         <v>6.678991980784874</v>
@@ -49456,7 +49456,7 @@
         <v>7.120323414275088</v>
       </c>
       <c r="D946" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E946">
         <v>6.757814301673794</v>
@@ -49506,7 +49506,7 @@
         <v>7.100513619059405</v>
       </c>
       <c r="D947" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E947">
         <v>6.757814301673794</v>
@@ -49556,7 +49556,7 @@
         <v>5.391263694581674</v>
       </c>
       <c r="D948" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E948">
         <v>4.981328216936646</v>
@@ -49606,7 +49606,7 @@
         <v>5.376664084342806</v>
       </c>
       <c r="D949" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E949">
         <v>5.183908869880363</v>
@@ -49656,7 +49656,7 @@
         <v>4.255036972488333</v>
       </c>
       <c r="D950" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E950">
         <v>4.585738592012135</v>
@@ -49692,7 +49692,7 @@
         <v>1</v>
       </c>
       <c r="P950" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="951" spans="1:16">
@@ -49742,7 +49742,7 @@
         <v>1</v>
       </c>
       <c r="P951" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="952" spans="1:16">
@@ -49756,7 +49756,7 @@
         <v>3.887235867264729</v>
       </c>
       <c r="D952" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E952">
         <v>4.261316022454437</v>
@@ -49792,7 +49792,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -49806,7 +49806,7 @@
         <v>4.52226704989957</v>
       </c>
       <c r="D953" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E953">
         <v>4.566623250498453</v>
@@ -49842,7 +49842,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -49856,7 +49856,7 @@
         <v>3.595471601271687</v>
       </c>
       <c r="D954" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E954">
         <v>4.003962492151604</v>
@@ -49892,7 +49892,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -49906,7 +49906,7 @@
         <v>4.274122026330736</v>
       </c>
       <c r="D955" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E955">
         <v>4.284760163047268</v>
@@ -49942,7 +49942,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -49956,7 +49956,7 @@
         <v>3.51283445556241</v>
       </c>
       <c r="D956" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E956">
         <v>3.931071587879801</v>
@@ -49992,7 +49992,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -50006,7 +50006,7 @@
         <v>4.203839271176003</v>
       </c>
       <c r="D957" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E957">
         <v>4.224910004360815</v>
@@ -50042,7 +50042,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -50056,7 +50056,7 @@
         <v>3.757771340160315</v>
       </c>
       <c r="D958" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E958">
         <v>4.020831110855603</v>
@@ -50092,7 +50092,7 @@
         <v>1</v>
       </c>
       <c r="P958" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="959" spans="1:16">
@@ -50106,7 +50106,7 @@
         <v>3.577092549221526</v>
       </c>
       <c r="D959" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E959">
         <v>3.987751069163838</v>
@@ -50142,7 +50142,7 @@
         <v>1</v>
       </c>
       <c r="P959" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="960" spans="1:16">
@@ -50192,7 +50192,7 @@
         <v>1</v>
       </c>
       <c r="P960" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="961" spans="1:16">
@@ -50206,7 +50206,7 @@
         <v>3.969181490046898</v>
       </c>
       <c r="D961" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E961">
         <v>4.227966423152568</v>
@@ -50242,7 +50242,7 @@
         <v>1</v>
       </c>
       <c r="P961" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="962" spans="1:16">
@@ -50256,7 +50256,7 @@
         <v>3.987966423152567</v>
       </c>
       <c r="D962" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E962">
         <v>4.227966423152568</v>
@@ -50292,7 +50292,7 @@
         <v>1</v>
       </c>
       <c r="P962" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="963" spans="1:16">
@@ -50342,7 +50342,7 @@
         <v>1</v>
       </c>
       <c r="P963" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="964" spans="1:16">
@@ -50356,7 +50356,7 @@
         <v>4.457464931808846</v>
       </c>
       <c r="D964" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E964">
         <v>4.34281674843841</v>
@@ -50392,7 +50392,7 @@
         <v>1</v>
       </c>
       <c r="P964" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="965" spans="1:16">
@@ -50406,7 +50406,7 @@
         <v>4.129665945672787</v>
       </c>
       <c r="D965" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E965">
         <v>4.385205788683081</v>
@@ -50556,7 +50556,7 @@
         <v>4.608509125339094</v>
       </c>
       <c r="D968" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E968">
         <v>4.501722471963149</v>
@@ -50606,7 +50606,7 @@
         <v>4.165381741025112</v>
       </c>
       <c r="D969" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E969">
         <v>4.420199389644091</v>
@@ -50856,7 +50856,7 @@
         <v>4.358277886497062</v>
       </c>
       <c r="D974" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E974">
         <v>4.609195061586275</v>
@@ -51056,7 +51056,7 @@
         <v>4.823673304938412</v>
       </c>
       <c r="D978" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E978">
         <v>4.78043513295729</v>
@@ -51106,7 +51106,7 @@
         <v>4.773780937032344</v>
       </c>
       <c r="D979" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E979">
         <v>4.78043513295729</v>
@@ -51156,7 +51156,7 @@
         <v>4.76066910325774</v>
       </c>
       <c r="D980" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E980">
         <v>4.78043513295729</v>
@@ -51206,7 +51206,7 @@
         <v>4.781010705652122</v>
       </c>
       <c r="D981" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E981">
         <v>4.78043513295729</v>
@@ -51256,7 +51256,7 @@
         <v>6.134818623398694</v>
       </c>
       <c r="D982" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E982">
         <v>5.774464332861776</v>
@@ -51306,7 +51306,7 @@
         <v>6.102771384660437</v>
       </c>
       <c r="D983" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E983">
         <v>5.778795004029567</v>
@@ -51356,7 +51356,7 @@
         <v>5.514582429707415</v>
       </c>
       <c r="D984" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E984">
         <v>5.241133593669833</v>
@@ -51406,7 +51406,7 @@
         <v>6.089893354328455</v>
       </c>
       <c r="D985" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E985">
         <v>5.69937873528254</v>
@@ -51456,7 +51456,7 @@
         <v>6.090496725476864</v>
       </c>
       <c r="D986" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E986">
         <v>5.69937873528254</v>
@@ -51506,7 +51506,7 @@
         <v>6.083345023798447</v>
       </c>
       <c r="D987" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E987">
         <v>5.69937873528254</v>
@@ -51556,7 +51556,7 @@
         <v>6.151446158250724</v>
       </c>
       <c r="D988" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E988">
         <v>5.740368070715386</v>
@@ -51606,7 +51606,7 @@
         <v>5.471792219876177</v>
       </c>
       <c r="D989" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E989">
         <v>5.499161328418567</v>
@@ -51656,7 +51656,7 @@
         <v>5.429161328418567</v>
       </c>
       <c r="D990" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E990">
         <v>5.499161328418567</v>
@@ -51706,7 +51706,7 @@
         <v>5.859820355215962</v>
       </c>
       <c r="D991" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E991">
         <v>5.498824536056178</v>
@@ -51756,7 +51756,7 @@
         <v>5.962203814850136</v>
       </c>
       <c r="D992" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E992">
         <v>5.498824536056178</v>
@@ -51806,7 +51806,7 @@
         <v>5.867235562966728</v>
       </c>
       <c r="D993" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E993">
         <v>5.498824536056178</v>
@@ -51856,7 +51856,7 @@
         <v>5.864221779328541</v>
       </c>
       <c r="D994" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E994">
         <v>5.498824536056178</v>
@@ -51906,7 +51906,7 @@
         <v>5.891472824538594</v>
       </c>
       <c r="D995" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E995">
         <v>5.498824536056178</v>
@@ -51956,7 +51956,7 @@
         <v>5.933527959091345</v>
       </c>
       <c r="D996" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E996">
         <v>5.516806571577774</v>
@@ -52106,7 +52106,7 @@
         <v>5.536448803884926</v>
       </c>
       <c r="D999" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E999">
         <v>5.114647162880539</v>
@@ -52156,7 +52156,7 @@
         <v>5.473079556721592</v>
       </c>
       <c r="D1000" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E1000">
         <v>5.114647162880539</v>
@@ -52206,7 +52206,7 @@
         <v>5.516088475684048</v>
       </c>
       <c r="D1001" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E1001">
         <v>5.088556902345189</v>
@@ -52256,7 +52256,7 @@
         <v>4.87693542544124</v>
       </c>
       <c r="D1002" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E1002">
         <v>4.790484836705014</v>
@@ -52306,7 +52306,7 @@
         <v>4.782412771064838</v>
       </c>
       <c r="D1003" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E1003">
         <v>4.790484836705014</v>
@@ -52356,7 +52356,7 @@
         <v>5.183884767385427</v>
       </c>
       <c r="D1004" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E1004">
         <v>4.796513208070444</v>
@@ -52406,7 +52406,7 @@
         <v>5.146682382306041</v>
       </c>
       <c r="D1005" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E1005">
         <v>4.796513208070444</v>
@@ -52456,7 +52456,7 @@
         <v>5.170410455522431</v>
       </c>
       <c r="D1006" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E1006">
         <v>4.733927060944326</v>
@@ -52506,7 +52506,7 @@
         <v>4.433208070443044</v>
       </c>
       <c r="D1007" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E1007">
         <v>4.48045274908133</v>
@@ -52556,7 +52556,7 @@
         <v>4.430537336199128</v>
       </c>
       <c r="D1008" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E1008">
         <v>4.48045274908133</v>
@@ -52606,7 +52606,7 @@
         <v>6.107518054315049</v>
       </c>
       <c r="D1009" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E1009">
         <v>5.738203236233369</v>
@@ -52656,7 +52656,7 @@
         <v>6.135203726571758</v>
       </c>
       <c r="D1010" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E1010">
         <v>5.738203236233369</v>
@@ -52706,7 +52706,7 @@
         <v>6.102046072361725</v>
       </c>
       <c r="D1011" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E1011">
         <v>5.738203236233369</v>
@@ -52756,7 +52756,7 @@
         <v>6.120488810422401</v>
       </c>
       <c r="D1012" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E1012">
         <v>5.738203236233369</v>
@@ -52806,7 +52806,7 @@
         <v>6.193632087855306</v>
       </c>
       <c r="D1013" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E1013">
         <v>5.783646464632436</v>
@@ -52856,7 +52856,7 @@
         <v>5.378974678814465</v>
       </c>
       <c r="D1014" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E1014">
         <v>5.579789251726952</v>
@@ -52906,7 +52906,7 @@
         <v>5.416732234956823</v>
       </c>
       <c r="D1015" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E1015">
         <v>5.579789251726952</v>
@@ -52956,7 +52956,7 @@
         <v>5.472103579470241</v>
       </c>
       <c r="D1016" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E1016">
         <v>5.579789251726952</v>
@@ -53006,7 +53006,7 @@
         <v>5.430560694308047</v>
       </c>
       <c r="D1017" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E1017">
         <v>5.579789251726952</v>
@@ -53056,7 +53056,7 @@
         <v>5.402846268497081</v>
       </c>
       <c r="D1018" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E1018">
         <v>5.579789251726952</v>
@@ -53142,7 +53142,7 @@
         <v>1</v>
       </c>
       <c r="P1019" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="1020" spans="1:16">
@@ -53192,7 +53192,7 @@
         <v>1</v>
       </c>
       <c r="P1020" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="1021" spans="1:16">
@@ -53206,7 +53206,7 @@
         <v>5.020295300931229</v>
       </c>
       <c r="D1021" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1021">
         <v>5.342572941191464</v>
@@ -53242,7 +53242,7 @@
         <v>1</v>
       </c>
       <c r="P1021" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="1022" spans="1:16">
@@ -53256,7 +53256,7 @@
         <v>5.54274578942891</v>
       </c>
       <c r="D1022" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E1022">
         <v>5.322745789428909</v>
@@ -53292,7 +53292,7 @@
         <v>1</v>
       </c>
       <c r="P1022" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="1023" spans="1:16">
@@ -53306,7 +53306,7 @@
         <v>5.6130914859038</v>
       </c>
       <c r="D1023" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E1023">
         <v>5.322745789428909</v>
@@ -53342,7 +53342,7 @@
         <v>1</v>
       </c>
       <c r="P1023" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="1024" spans="1:16">
@@ -53356,7 +53356,7 @@
         <v>5.147961849725716</v>
       </c>
       <c r="D1024" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E1024">
         <v>5.187875425606993</v>
@@ -53392,7 +53392,7 @@
         <v>1</v>
       </c>
       <c r="P1024" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="1025" spans="1:16">
@@ -53406,7 +53406,7 @@
         <v>4.481259603973901</v>
       </c>
       <c r="D1025" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1025">
         <v>4.729065207154505</v>
@@ -53456,7 +53456,7 @@
         <v>4.933966438698594</v>
       </c>
       <c r="D1026" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E1026">
         <v>4.713966438698593</v>
@@ -53506,7 +53506,7 @@
         <v>4.545092978128704</v>
       </c>
       <c r="D1027" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E1027">
         <v>4.51376890178677</v>
@@ -53556,7 +53556,7 @@
         <v>4.556417054470637</v>
       </c>
       <c r="D1028" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E1028">
         <v>4.51376890178677</v>
@@ -53606,7 +53606,7 @@
         <v>4.521721707925945</v>
       </c>
       <c r="D1029" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E1029">
         <v>4.242337996671525</v>
@@ -53656,7 +53656,7 @@
         <v>3.995431662159355</v>
       </c>
       <c r="D1030" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E1030">
         <v>4.028576685042651</v>
@@ -53706,7 +53706,7 @@
         <v>4.0220812096942</v>
       </c>
       <c r="D1031" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E1031">
         <v>4.028576685042651</v>
@@ -53756,7 +53756,7 @@
         <v>3.998833472019975</v>
       </c>
       <c r="D1032" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E1032">
         <v>4.028576685042651</v>
@@ -53806,7 +53806,7 @@
         <v>2.312870417300224</v>
       </c>
       <c r="D1033" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E1033">
         <v>2.600174015881064</v>
@@ -53856,7 +53856,7 @@
         <v>2.342806217266434</v>
       </c>
       <c r="D1034" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E1034">
         <v>2.600174015881064</v>
@@ -53906,7 +53906,7 @@
         <v>2.333191417469171</v>
       </c>
       <c r="D1035" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E1035">
         <v>2.600174015881064</v>
@@ -53956,7 +53956,7 @@
         <v>2.830944416286538</v>
       </c>
       <c r="D1036" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E1036">
         <v>2.501072816354117</v>
@@ -54006,7 +54006,7 @@
         <v>3.735551545505884</v>
       </c>
       <c r="D1037" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E1037">
         <v>3.537025852544748</v>
@@ -54056,7 +54056,7 @@
         <v>3.727025852544749</v>
       </c>
       <c r="D1038" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E1038">
         <v>3.537025852544748</v>
@@ -54106,7 +54106,7 @@
         <v>3.707843043382194</v>
       </c>
       <c r="D1039" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E1039">
         <v>3.537025852544748</v>
@@ -54156,7 +54156,7 @@
         <v>3.371288699025316</v>
       </c>
       <c r="D1040" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E1040">
         <v>3.571768922933395</v>
@@ -54206,7 +54206,7 @@
         <v>3.36981439198645</v>
       </c>
       <c r="D1041" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E1041">
         <v>3.571768922933395</v>
@@ -54256,7 +54256,7 @@
         <v>3.347025852544749</v>
       </c>
       <c r="D1042" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E1042">
         <v>3.571768922933395</v>
@@ -54306,7 +54306,7 @@
         <v>3.718820308855666</v>
       </c>
       <c r="D1043" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E1043">
         <v>3.501608848297368</v>
@@ -54356,7 +54356,7 @@
         <v>7.818784706417835</v>
       </c>
       <c r="D1044" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E1044">
         <v>8.66434683659535</v>
@@ -54406,7 +54406,7 @@
         <v>7.736183913922513</v>
       </c>
       <c r="D1045" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E1045">
         <v>8.114051730148025</v>
@@ -54456,7 +54456,7 @@
         <v>5.66445723600427</v>
       </c>
       <c r="D1046" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E1046">
         <v>5.237456064387949</v>
@@ -54506,7 +54506,7 @@
         <v>5.440858208955218</v>
       </c>
       <c r="D1047" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E1047">
         <v>5.007731036597828</v>
@@ -54606,7 +54606,7 @@
         <v>4.988258892022188</v>
       </c>
       <c r="D1049" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E1049">
         <v>4.542731738378961</v>
@@ -54656,7 +54656,7 @@
         <v>5.374367473486714</v>
       </c>
       <c r="D1050" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E1050">
         <v>4.939418637143884</v>
@@ -54706,7 +54706,7 @@
         <v>5.639230769230771</v>
       </c>
       <c r="D1051" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E1051">
         <v>5.211538461538465</v>
@@ -54806,7 +54806,7 @@
         <v>-0.9618136339318442</v>
       </c>
       <c r="D1053" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E1053">
         <v>-0.6309048928601628</v>
@@ -54856,7 +54856,7 @@
         <v>-1.021813633931844</v>
       </c>
       <c r="D1054" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E1054">
         <v>-0.6309048928601628</v>
@@ -54906,7 +54906,7 @@
         <v>-0.9417911078156269</v>
       </c>
       <c r="D1055" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E1055">
         <v>-0.6309048928601628</v>
@@ -54956,7 +54956,7 @@
         <v>-0.4983138263424198</v>
       </c>
       <c r="D1056" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E1056">
         <v>-0.7326773227710905</v>
@@ -55006,10 +55006,10 @@
         <v>-1.04421149425495</v>
       </c>
       <c r="D1057" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E1057">
-        <v>-0.8170515119382786</v>
+        <v>-0.7069644562353377</v>
       </c>
       <c r="F1057">
         <v>1</v>
@@ -55018,10 +55018,10 @@
         <v>0.01630421149425495</v>
       </c>
       <c r="H1057">
-        <v>0.01539705151193828</v>
+        <v>0.01530696445623534</v>
       </c>
       <c r="I1057">
-        <v>0.227159982316671</v>
+        <v>0.337247038019612</v>
       </c>
       <c r="J1057">
         <v>1.668117595049029</v>
@@ -55033,10 +55033,10 @@
         <v>7.63</v>
       </c>
       <c r="M1057">
-        <v>4.86</v>
+        <v>4.8</v>
       </c>
       <c r="N1057">
-        <v>7.29</v>
+        <v>7.3</v>
       </c>
       <c r="O1057">
         <v>1</v>
@@ -55056,10 +55056,10 @@
         <v>-1.104211494254949</v>
       </c>
       <c r="D1058" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E1058">
-        <v>-0.8170515119382786</v>
+        <v>-0.7069644562353377</v>
       </c>
       <c r="F1058">
         <v>1</v>
@@ -55068,10 +55068,10 @@
         <v>0.01624421149425495</v>
       </c>
       <c r="H1058">
-        <v>0.01539705151193828</v>
+        <v>0.01530696445623534</v>
       </c>
       <c r="I1058">
-        <v>0.2871599823166706</v>
+        <v>0.3972470380196116</v>
       </c>
       <c r="J1058">
         <v>1.668117595049029</v>
@@ -55083,10 +55083,10 @@
         <v>7.57</v>
       </c>
       <c r="M1058">
-        <v>4.86</v>
+        <v>4.8</v>
       </c>
       <c r="N1058">
-        <v>7.29</v>
+        <v>7.3</v>
       </c>
       <c r="O1058">
         <v>1</v>
@@ -55100,43 +55100,43 @@
         <v>2</v>
       </c>
       <c r="B1059" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C1059">
-        <v>-0.5772256233441624</v>
+        <v>-1.020544447393672</v>
       </c>
       <c r="D1059" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E1059">
-        <v>-0.8674432626015163</v>
+        <v>-0.7069644562353377</v>
       </c>
       <c r="F1059">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1059">
-        <v>0.01603722562334416</v>
+        <v>0.01556054444739367</v>
       </c>
       <c r="H1059">
-        <v>0.01624744326260152</v>
+        <v>0.01530696445623534</v>
       </c>
       <c r="I1059">
-        <v>0.2902176392573539</v>
+        <v>0.3135799911583339</v>
       </c>
       <c r="J1059">
         <v>1.668117595049029</v>
       </c>
       <c r="K1059">
-        <v>4.98</v>
+        <v>4.97</v>
       </c>
       <c r="L1059">
-        <v>7.73</v>
+        <v>7.27</v>
       </c>
       <c r="M1059">
-        <v>5.13</v>
+        <v>4.8</v>
       </c>
       <c r="N1059">
-        <v>7.69</v>
+        <v>7.3</v>
       </c>
       <c r="O1059">
         <v>1</v>
@@ -55147,66 +55147,66 @@
     </row>
     <row r="1060" spans="1:16">
       <c r="A1060" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1060" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C1060">
-        <v>-1.097822582940394</v>
+        <v>-0.5772256233441624</v>
       </c>
       <c r="D1060" t="s">
-        <v>471</v>
+        <v>295</v>
       </c>
       <c r="E1060">
-        <v>-0.8710786311994871</v>
+        <v>-0.8674432626015163</v>
       </c>
       <c r="F1060">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1060">
-        <v>0.01635782258294039</v>
+        <v>0.01603722562334416</v>
       </c>
       <c r="H1060">
-        <v>0.01561107863119949</v>
+        <v>0.01624744326260152</v>
       </c>
       <c r="I1060">
-        <v>0.2267439517409073</v>
+        <v>0.2902176392573539</v>
       </c>
       <c r="J1060">
-        <v>1.67842741979623</v>
+        <v>1.668117595049029</v>
       </c>
       <c r="K1060">
-        <v>5.2</v>
+        <v>4.98</v>
       </c>
       <c r="L1060">
-        <v>7.63</v>
+        <v>7.73</v>
       </c>
       <c r="M1060">
-        <v>4.91</v>
+        <v>5.13</v>
       </c>
       <c r="N1060">
-        <v>7.37</v>
+        <v>7.69</v>
       </c>
       <c r="O1060">
         <v>1</v>
       </c>
       <c r="P1060" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="1061" spans="1:16">
       <c r="A1061" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1061" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C1061">
-        <v>-1.157822582940394</v>
+        <v>-1.097822582940394</v>
       </c>
       <c r="D1061" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E1061">
         <v>-0.8710786311994871</v>
@@ -55215,13 +55215,13 @@
         <v>1</v>
       </c>
       <c r="G1061">
-        <v>0.01629782258294039</v>
+        <v>0.01635782258294039</v>
       </c>
       <c r="H1061">
         <v>0.01561107863119949</v>
       </c>
       <c r="I1061">
-        <v>0.2867439517409069</v>
+        <v>0.2267439517409073</v>
       </c>
       <c r="J1061">
         <v>1.67842741979623</v>
@@ -55230,7 +55230,7 @@
         <v>5.2</v>
       </c>
       <c r="L1061">
-        <v>7.57</v>
+        <v>7.63</v>
       </c>
       <c r="M1061">
         <v>4.91</v>
@@ -55247,46 +55247,46 @@
     </row>
     <row r="1062" spans="1:16">
       <c r="A1062" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1062" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C1062">
-        <v>-0.6285685505852232</v>
+        <v>-1.157822582940394</v>
       </c>
       <c r="D1062" t="s">
         <v>470</v>
       </c>
       <c r="E1062">
-        <v>-0.9203326635546576</v>
+        <v>-0.8710786311994871</v>
       </c>
       <c r="F1062">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1062">
-        <v>0.01608856855058522</v>
+        <v>0.01629782258294039</v>
       </c>
       <c r="H1062">
-        <v>0.01630033266355466</v>
+        <v>0.01561107863119949</v>
       </c>
       <c r="I1062">
-        <v>0.2917641129694344</v>
+        <v>0.2867439517409069</v>
       </c>
       <c r="J1062">
         <v>1.67842741979623</v>
       </c>
       <c r="K1062">
-        <v>4.98</v>
+        <v>5.2</v>
       </c>
       <c r="L1062">
-        <v>7.73</v>
+        <v>7.57</v>
       </c>
       <c r="M1062">
-        <v>5.13</v>
+        <v>4.91</v>
       </c>
       <c r="N1062">
-        <v>7.69</v>
+        <v>7.37</v>
       </c>
       <c r="O1062">
         <v>1</v>
@@ -55297,66 +55297,66 @@
     </row>
     <row r="1063" spans="1:16">
       <c r="A1063" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1063" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C1063">
-        <v>-1.132542776541119</v>
+        <v>-0.6285685505852232</v>
       </c>
       <c r="D1063" t="s">
-        <v>471</v>
+        <v>295</v>
       </c>
       <c r="E1063">
-        <v>-0.9038625063109409</v>
+        <v>-0.9203326635546576</v>
       </c>
       <c r="F1063">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1063">
-        <v>0.01639254277654112</v>
+        <v>0.01608856855058522</v>
       </c>
       <c r="H1063">
-        <v>0.01564386250631094</v>
+        <v>0.01630033266355466</v>
       </c>
       <c r="I1063">
-        <v>0.2286802702301785</v>
+        <v>0.2917641129694344</v>
       </c>
       <c r="J1063">
-        <v>1.685104380104061</v>
+        <v>1.67842741979623</v>
       </c>
       <c r="K1063">
-        <v>5.2</v>
+        <v>4.98</v>
       </c>
       <c r="L1063">
-        <v>7.63</v>
+        <v>7.73</v>
       </c>
       <c r="M1063">
-        <v>4.91</v>
+        <v>5.13</v>
       </c>
       <c r="N1063">
-        <v>7.37</v>
+        <v>7.69</v>
       </c>
       <c r="O1063">
         <v>1</v>
       </c>
       <c r="P1063" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="1064" spans="1:16">
       <c r="A1064" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1064" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C1064">
-        <v>-1.192542776541119</v>
+        <v>-1.132542776541119</v>
       </c>
       <c r="D1064" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E1064">
         <v>-0.9038625063109409</v>
@@ -55365,13 +55365,13 @@
         <v>1</v>
       </c>
       <c r="G1064">
-        <v>0.01633254277654112</v>
+        <v>0.01639254277654112</v>
       </c>
       <c r="H1064">
         <v>0.01564386250631094</v>
       </c>
       <c r="I1064">
-        <v>0.2886802702301781</v>
+        <v>0.2286802702301785</v>
       </c>
       <c r="J1064">
         <v>1.685104380104061</v>
@@ -55380,7 +55380,7 @@
         <v>5.2</v>
       </c>
       <c r="L1064">
-        <v>7.57</v>
+        <v>7.63</v>
       </c>
       <c r="M1064">
         <v>4.91</v>
@@ -55397,46 +55397,46 @@
     </row>
     <row r="1065" spans="1:16">
       <c r="A1065" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1065" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C1065">
-        <v>-0.6618198129182247</v>
+        <v>-1.192542776541119</v>
       </c>
       <c r="D1065" t="s">
         <v>470</v>
       </c>
       <c r="E1065">
-        <v>-0.954585469933833</v>
+        <v>-0.9038625063109409</v>
       </c>
       <c r="F1065">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1065">
-        <v>0.01612181981291822</v>
+        <v>0.01633254277654112</v>
       </c>
       <c r="H1065">
-        <v>0.01633458546993383</v>
+        <v>0.01564386250631094</v>
       </c>
       <c r="I1065">
-        <v>0.2927656570156083</v>
+        <v>0.2886802702301781</v>
       </c>
       <c r="J1065">
         <v>1.685104380104061</v>
       </c>
       <c r="K1065">
-        <v>4.98</v>
+        <v>5.2</v>
       </c>
       <c r="L1065">
-        <v>7.73</v>
+        <v>7.57</v>
       </c>
       <c r="M1065">
-        <v>5.13</v>
+        <v>4.91</v>
       </c>
       <c r="N1065">
-        <v>7.69</v>
+        <v>7.37</v>
       </c>
       <c r="O1065">
         <v>1</v>
@@ -55447,16 +55447,16 @@
     </row>
     <row r="1066" spans="1:16">
       <c r="A1066" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1066" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C1066">
-        <v>-0.7149687691171831</v>
+        <v>-0.6618198129182247</v>
       </c>
       <c r="D1066" t="s">
-        <v>470</v>
+        <v>295</v>
       </c>
       <c r="E1066">
         <v>-0.954585469933833</v>
@@ -55465,22 +55465,22 @@
         <v>-1</v>
       </c>
       <c r="G1066">
-        <v>0.01603496876911719</v>
+        <v>0.01612181981291822</v>
       </c>
       <c r="H1066">
         <v>0.01633458546993383</v>
       </c>
       <c r="I1066">
-        <v>0.2396167008166499</v>
+        <v>0.2927656570156083</v>
       </c>
       <c r="J1066">
         <v>1.685104380104061</v>
       </c>
       <c r="K1066">
-        <v>4.97</v>
+        <v>4.98</v>
       </c>
       <c r="L1066">
-        <v>7.66</v>
+        <v>7.73</v>
       </c>
       <c r="M1066">
         <v>5.13</v>
@@ -55497,66 +55497,66 @@
     </row>
     <row r="1067" spans="1:16">
       <c r="A1067" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1067" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C1067">
-        <v>-1.157889853450652</v>
+        <v>-0.7149687691171831</v>
       </c>
       <c r="D1067" t="s">
-        <v>471</v>
+        <v>295</v>
       </c>
       <c r="E1067">
-        <v>-0.9277959962389817</v>
+        <v>-0.954585469933833</v>
       </c>
       <c r="F1067">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1067">
-        <v>0.01641788985345065</v>
+        <v>0.01603496876911719</v>
       </c>
       <c r="H1067">
-        <v>0.01566779599623898</v>
+        <v>0.01633458546993383</v>
       </c>
       <c r="I1067">
-        <v>0.2300938572116706</v>
+        <v>0.2396167008166499</v>
       </c>
       <c r="J1067">
-        <v>1.689978817971279</v>
+        <v>1.685104380104061</v>
       </c>
       <c r="K1067">
-        <v>5.2</v>
+        <v>4.97</v>
       </c>
       <c r="L1067">
-        <v>7.63</v>
+        <v>7.66</v>
       </c>
       <c r="M1067">
-        <v>4.91</v>
+        <v>5.13</v>
       </c>
       <c r="N1067">
-        <v>7.37</v>
+        <v>7.69</v>
       </c>
       <c r="O1067">
         <v>1</v>
       </c>
       <c r="P1067" t="s">
-        <v>465</v>
+        <v>606</v>
       </c>
     </row>
     <row r="1068" spans="1:16">
       <c r="A1068" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1068" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C1068">
-        <v>-1.217889853450652</v>
+        <v>-1.157889853450652</v>
       </c>
       <c r="D1068" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E1068">
         <v>-0.9277959962389817</v>
@@ -55565,13 +55565,13 @@
         <v>1</v>
       </c>
       <c r="G1068">
-        <v>0.01635788985345065</v>
+        <v>0.01641788985345065</v>
       </c>
       <c r="H1068">
         <v>0.01566779599623898</v>
       </c>
       <c r="I1068">
-        <v>0.2900938572116702</v>
+        <v>0.2300938572116706</v>
       </c>
       <c r="J1068">
         <v>1.689978817971279</v>
@@ -55580,7 +55580,7 @@
         <v>5.2</v>
       </c>
       <c r="L1068">
-        <v>7.57</v>
+        <v>7.63</v>
       </c>
       <c r="M1068">
         <v>4.91</v>
@@ -55592,71 +55592,71 @@
         <v>1</v>
       </c>
       <c r="P1068" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="1069" spans="1:16">
       <c r="A1069" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1069" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C1069">
-        <v>-0.6860945134969718</v>
+        <v>-1.217889853450652</v>
       </c>
       <c r="D1069" t="s">
         <v>470</v>
       </c>
       <c r="E1069">
-        <v>-0.9795913361926631</v>
+        <v>-0.9277959962389817</v>
       </c>
       <c r="F1069">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1069">
-        <v>0.01614609451349697</v>
+        <v>0.01635788985345065</v>
       </c>
       <c r="H1069">
-        <v>0.01635959133619266</v>
+        <v>0.01566779599623898</v>
       </c>
       <c r="I1069">
-        <v>0.2934968226956913</v>
+        <v>0.2900938572116702</v>
       </c>
       <c r="J1069">
         <v>1.689978817971279</v>
       </c>
       <c r="K1069">
-        <v>4.98</v>
+        <v>5.2</v>
       </c>
       <c r="L1069">
-        <v>7.73</v>
+        <v>7.57</v>
       </c>
       <c r="M1069">
-        <v>5.13</v>
+        <v>4.91</v>
       </c>
       <c r="N1069">
-        <v>7.69</v>
+        <v>7.37</v>
       </c>
       <c r="O1069">
         <v>1</v>
       </c>
       <c r="P1069" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="1070" spans="1:16">
       <c r="A1070" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1070" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C1070">
-        <v>-0.7391947253172582</v>
+        <v>-0.6860945134969718</v>
       </c>
       <c r="D1070" t="s">
-        <v>470</v>
+        <v>295</v>
       </c>
       <c r="E1070">
         <v>-0.9795913361926631</v>
@@ -55665,22 +55665,22 @@
         <v>-1</v>
       </c>
       <c r="G1070">
-        <v>0.01605919472531726</v>
+        <v>0.01614609451349697</v>
       </c>
       <c r="H1070">
         <v>0.01635959133619266</v>
       </c>
       <c r="I1070">
-        <v>0.240396610875405</v>
+        <v>0.2934968226956913</v>
       </c>
       <c r="J1070">
         <v>1.689978817971279</v>
       </c>
       <c r="K1070">
-        <v>4.97</v>
+        <v>4.98</v>
       </c>
       <c r="L1070">
-        <v>7.66</v>
+        <v>7.73</v>
       </c>
       <c r="M1070">
         <v>5.13</v>
@@ -55692,106 +55692,206 @@
         <v>1</v>
       </c>
       <c r="P1070" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="1071" spans="1:16">
       <c r="A1071" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1071" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C1071">
-        <v>-2.807532631974992</v>
+        <v>-0.7391947253172582</v>
       </c>
       <c r="D1071" t="s">
-        <v>467</v>
+        <v>295</v>
       </c>
       <c r="E1071">
-        <v>-2.509249826348689</v>
+        <v>-0.9795913361926631</v>
       </c>
       <c r="F1071">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1071">
-        <v>0.01758753263197499</v>
+        <v>0.01605919472531726</v>
       </c>
       <c r="H1071">
-        <v>0.01710924982634869</v>
+        <v>0.01635959133619266</v>
       </c>
       <c r="I1071">
-        <v>0.2982828056263038</v>
+        <v>0.240396610875405</v>
       </c>
       <c r="J1071">
-        <v>2.043593713822644</v>
+        <v>1.689978817971279</v>
       </c>
       <c r="K1071">
-        <v>4.99</v>
+        <v>4.97</v>
       </c>
       <c r="L1071">
-        <v>7.39</v>
+        <v>7.66</v>
       </c>
       <c r="M1071">
-        <v>4.8</v>
+        <v>5.13</v>
       </c>
       <c r="N1071">
-        <v>7.3</v>
+        <v>7.69</v>
       </c>
       <c r="O1071">
         <v>1</v>
       </c>
       <c r="P1071" t="s">
-        <v>607</v>
+        <v>466</v>
       </c>
     </row>
     <row r="1072" spans="1:16">
       <c r="A1072" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1072" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C1072">
-        <v>-2.496660757698539</v>
+        <v>-2.807532631974992</v>
       </c>
       <c r="D1072" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E1072">
-        <v>-2.672763877633709</v>
+        <v>-2.509249826348689</v>
       </c>
       <c r="F1072">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1072">
-        <v>0.01781666075769854</v>
+        <v>0.01758753263197499</v>
       </c>
       <c r="H1072">
-        <v>0.01821276387763371</v>
+        <v>0.01710924982634869</v>
       </c>
       <c r="I1072">
-        <v>0.1761031199351706</v>
+        <v>0.2982828056263038</v>
       </c>
       <c r="J1072">
         <v>2.043593713822644</v>
       </c>
       <c r="K1072">
+        <v>4.99</v>
+      </c>
+      <c r="L1072">
+        <v>7.39</v>
+      </c>
+      <c r="M1072">
+        <v>4.8</v>
+      </c>
+      <c r="N1072">
+        <v>7.3</v>
+      </c>
+      <c r="O1072">
+        <v>1</v>
+      </c>
+      <c r="P1072" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:16">
+      <c r="A1073" s="1">
+        <v>1</v>
+      </c>
+      <c r="B1073" t="s">
+        <v>293</v>
+      </c>
+      <c r="C1073">
+        <v>-2.496660757698539</v>
+      </c>
+      <c r="D1073" t="s">
+        <v>471</v>
+      </c>
+      <c r="E1073">
+        <v>-2.672763877633709</v>
+      </c>
+      <c r="F1073">
+        <v>-1</v>
+      </c>
+      <c r="G1073">
+        <v>0.01781666075769854</v>
+      </c>
+      <c r="H1073">
+        <v>0.01821276387763371</v>
+      </c>
+      <c r="I1073">
+        <v>0.1761031199351706</v>
+      </c>
+      <c r="J1073">
+        <v>2.043593713822644</v>
+      </c>
+      <c r="K1073">
         <v>4.97</v>
       </c>
-      <c r="L1072">
+      <c r="L1073">
         <v>7.66</v>
       </c>
-      <c r="M1072">
+      <c r="M1073">
         <v>5.11</v>
       </c>
-      <c r="N1072">
+      <c r="N1073">
         <v>7.77</v>
       </c>
-      <c r="O1072">
-        <v>1</v>
-      </c>
-      <c r="P1072" t="s">
+      <c r="O1073">
+        <v>1</v>
+      </c>
+      <c r="P1073" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:16">
+      <c r="A1074" s="1">
+        <v>2</v>
+      </c>
+      <c r="B1074" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1074">
+        <v>-2.793635751910162</v>
+      </c>
+      <c r="D1074" t="s">
+        <v>472</v>
+      </c>
+      <c r="E1074">
+        <v>-2.627096694836767</v>
+      </c>
+      <c r="F1074">
+        <v>1</v>
+      </c>
+      <c r="G1074">
+        <v>0.01817363575191016</v>
+      </c>
+      <c r="H1074">
+        <v>0.01772709669483677</v>
+      </c>
+      <c r="I1074">
+        <v>0.1665390570733951</v>
+      </c>
+      <c r="J1074">
+        <v>2.043593713822644</v>
+      </c>
+      <c r="K1074">
+        <v>5.13</v>
+      </c>
+      <c r="L1074">
+        <v>7.69</v>
+      </c>
+      <c r="M1074">
+        <v>4.98</v>
+      </c>
+      <c r="N1074">
+        <v>7.55</v>
+      </c>
+      <c r="O1074">
+        <v>1</v>
+      </c>
+      <c r="P1074" t="s">
         <v>607</v>
       </c>
     </row>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3237" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3234" uniqueCount="610">
   <si>
     <t>trade_time</t>
   </si>
@@ -1427,6 +1427,9 @@
   </si>
   <si>
     <t>2021-12-09</t>
+  </si>
+  <si>
+    <t>2021-11-22</t>
   </si>
   <si>
     <t>2021-11-15</t>
@@ -2198,7 +2201,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1075"/>
+  <dimension ref="A1:P1074"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2295,7 +2298,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2345,7 +2348,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2395,7 +2398,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2445,7 +2448,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2495,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2545,7 +2548,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2595,7 +2598,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2645,7 +2648,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2695,7 +2698,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2745,7 +2748,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2795,7 +2798,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2845,7 +2848,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2895,7 +2898,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -2945,7 +2948,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2995,7 +2998,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -3045,7 +3048,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -3095,7 +3098,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -3145,7 +3148,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -3195,7 +3198,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -3245,7 +3248,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -3295,7 +3298,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3345,7 +3348,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3395,7 +3398,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3445,7 +3448,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -3495,7 +3498,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -3545,7 +3548,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -3595,7 +3598,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3645,7 +3648,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3695,7 +3698,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3745,7 +3748,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3795,7 +3798,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3845,7 +3848,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3895,7 +3898,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3945,7 +3948,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3995,7 +3998,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -4045,7 +4048,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -4095,7 +4098,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -4145,7 +4148,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -4195,7 +4198,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -4245,7 +4248,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -4295,7 +4298,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4345,7 +4348,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4395,7 +4398,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4445,7 +4448,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -4495,7 +4498,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -4545,7 +4548,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -4595,7 +4598,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4645,7 +4648,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4695,7 +4698,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4745,7 +4748,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4795,7 +4798,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4845,7 +4848,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4895,7 +4898,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4945,7 +4948,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4995,7 +4998,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -5045,7 +5048,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -5095,7 +5098,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -5145,7 +5148,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -5195,7 +5198,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -5245,7 +5248,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -5295,7 +5298,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5345,7 +5348,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5395,7 +5398,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5995,7 +5998,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -6045,7 +6048,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -6095,7 +6098,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -6145,7 +6148,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -6195,7 +6198,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -6245,7 +6248,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -6295,7 +6298,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -6345,7 +6348,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -6395,7 +6398,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6445,7 +6448,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -6495,7 +6498,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -6545,7 +6548,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -6595,7 +6598,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6645,7 +6648,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6695,7 +6698,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6745,7 +6748,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6795,7 +6798,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6845,7 +6848,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6895,7 +6898,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6945,7 +6948,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6995,7 +6998,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -7345,7 +7348,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7395,7 +7398,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7445,7 +7448,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -7495,7 +7498,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -7545,7 +7548,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -7595,7 +7598,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -7645,7 +7648,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7695,7 +7698,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7745,7 +7748,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7795,7 +7798,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7845,7 +7848,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7895,7 +7898,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -7945,7 +7948,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -7995,7 +7998,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -8045,7 +8048,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -8095,7 +8098,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -8145,7 +8148,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -8195,7 +8198,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -8245,7 +8248,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -8595,7 +8598,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -8645,7 +8648,7 @@
         <v>1</v>
       </c>
       <c r="P129" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -8695,7 +8698,7 @@
         <v>1</v>
       </c>
       <c r="P130" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -8745,7 +8748,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8795,7 +8798,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8845,7 +8848,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8895,7 +8898,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8945,7 +8948,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8995,7 +8998,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -9045,7 +9048,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -9095,7 +9098,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -9145,7 +9148,7 @@
         <v>1</v>
       </c>
       <c r="P139" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -9195,7 +9198,7 @@
         <v>1</v>
       </c>
       <c r="P140" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -9245,7 +9248,7 @@
         <v>1</v>
       </c>
       <c r="P141" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -9295,7 +9298,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -9345,7 +9348,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9395,7 +9398,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9445,7 +9448,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -10795,7 +10798,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10845,7 +10848,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10895,7 +10898,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10945,7 +10948,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10995,7 +10998,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -11045,7 +11048,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -11095,7 +11098,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -11145,7 +11148,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -11195,7 +11198,7 @@
         <v>1</v>
       </c>
       <c r="P180" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -11345,7 +11348,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -11395,7 +11398,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11595,7 +11598,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11645,7 +11648,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11695,7 +11698,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11745,7 +11748,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11795,7 +11798,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11845,7 +11848,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -12295,7 +12298,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -12345,7 +12348,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12395,7 +12398,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12445,7 +12448,7 @@
         <v>1</v>
       </c>
       <c r="P205" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12495,7 +12498,7 @@
         <v>1</v>
       </c>
       <c r="P206" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -17195,7 +17198,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -17245,7 +17248,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -17295,7 +17298,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -17345,7 +17348,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17395,7 +17398,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17445,7 +17448,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17495,7 +17498,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17745,7 +17748,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17795,7 +17798,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17845,7 +17848,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17895,7 +17898,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17945,7 +17948,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -18445,7 +18448,7 @@
         <v>1</v>
       </c>
       <c r="P325" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="326" spans="1:16">
@@ -18495,7 +18498,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -18545,7 +18548,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -18595,7 +18598,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18745,7 +18748,7 @@
         <v>1</v>
       </c>
       <c r="P331" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="332" spans="1:16">
@@ -18795,7 +18798,7 @@
         <v>1</v>
       </c>
       <c r="P332" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="333" spans="1:16">
@@ -18845,7 +18848,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -18895,7 +18898,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -18945,7 +18948,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -19195,7 +19198,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -19245,7 +19248,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -19295,7 +19298,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -19345,7 +19348,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19395,7 +19398,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19445,7 +19448,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19495,7 +19498,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19545,7 +19548,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19595,7 +19598,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19645,7 +19648,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19695,7 +19698,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19745,7 +19748,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19795,7 +19798,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19845,7 +19848,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19895,7 +19898,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19945,7 +19948,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19995,7 +19998,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -20045,7 +20048,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -20095,7 +20098,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -20145,7 +20148,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -20195,7 +20198,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -20245,7 +20248,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -20295,7 +20298,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -20345,7 +20348,7 @@
         <v>1</v>
       </c>
       <c r="P363" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -20395,7 +20398,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20445,7 +20448,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20495,7 +20498,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20545,7 +20548,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20595,7 +20598,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20645,7 +20648,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20695,7 +20698,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20745,7 +20748,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20795,7 +20798,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20845,7 +20848,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20895,7 +20898,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20945,7 +20948,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20995,7 +20998,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -21045,7 +21048,7 @@
         <v>1</v>
       </c>
       <c r="P377" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="378" spans="1:16">
@@ -21095,7 +21098,7 @@
         <v>1</v>
       </c>
       <c r="P378" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="379" spans="1:16">
@@ -21145,7 +21148,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -21195,7 +21198,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -21245,7 +21248,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -21295,7 +21298,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -21345,7 +21348,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21645,7 +21648,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21695,7 +21698,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21745,7 +21748,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21795,7 +21798,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21845,7 +21848,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -22545,7 +22548,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22595,7 +22598,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22645,7 +22648,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22695,7 +22698,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22745,7 +22748,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22795,7 +22798,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22845,7 +22848,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22895,7 +22898,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22945,7 +22948,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22995,7 +22998,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -23045,7 +23048,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -23095,7 +23098,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -23145,7 +23148,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -23195,7 +23198,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -23245,7 +23248,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -23295,7 +23298,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -23345,7 +23348,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -23395,7 +23398,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -23445,7 +23448,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -23495,7 +23498,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -23545,7 +23548,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23895,7 +23898,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23945,7 +23948,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23995,7 +23998,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -24045,7 +24048,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -24095,7 +24098,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -24145,7 +24148,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -24195,7 +24198,7 @@
         <v>1</v>
       </c>
       <c r="P440" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -24245,7 +24248,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -24295,7 +24298,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -24345,7 +24348,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24395,7 +24398,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24445,7 +24448,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24495,7 +24498,7 @@
         <v>1</v>
       </c>
       <c r="P446" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24545,7 +24548,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24595,7 +24598,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24645,7 +24648,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24695,7 +24698,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24745,7 +24748,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24795,7 +24798,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24845,7 +24848,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24895,7 +24898,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -24945,7 +24948,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -24995,7 +24998,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -25045,7 +25048,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -25095,7 +25098,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -25145,7 +25148,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -25195,7 +25198,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -25245,7 +25248,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -25295,7 +25298,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -25345,7 +25348,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -25395,7 +25398,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25445,7 +25448,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -25495,7 +25498,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -25545,7 +25548,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -25595,7 +25598,7 @@
         <v>1</v>
       </c>
       <c r="P468" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="469" spans="1:16">
@@ -25645,7 +25648,7 @@
         <v>1</v>
       </c>
       <c r="P469" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="470" spans="1:16">
@@ -25695,7 +25698,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25745,7 +25748,7 @@
         <v>1</v>
       </c>
       <c r="P471" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -25795,7 +25798,7 @@
         <v>1</v>
       </c>
       <c r="P472" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -25845,7 +25848,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25895,7 +25898,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25945,7 +25948,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25995,7 +25998,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -26045,7 +26048,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -26095,7 +26098,7 @@
         <v>1</v>
       </c>
       <c r="P478" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -26345,7 +26348,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -26395,7 +26398,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26445,7 +26448,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26495,7 +26498,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26545,7 +26548,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26845,7 +26848,7 @@
         <v>1</v>
       </c>
       <c r="P493" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -26895,7 +26898,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26945,7 +26948,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26995,7 +26998,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -27045,7 +27048,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -27595,7 +27598,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27645,7 +27648,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27695,7 +27698,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27745,7 +27748,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27795,7 +27798,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27845,7 +27848,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27895,7 +27898,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -28195,7 +28198,7 @@
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -28245,7 +28248,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -28295,7 +28298,7 @@
         <v>1</v>
       </c>
       <c r="P522" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -28345,7 +28348,7 @@
         <v>1</v>
       </c>
       <c r="P523" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -28395,7 +28398,7 @@
         <v>1</v>
       </c>
       <c r="P524" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28445,7 +28448,7 @@
         <v>1</v>
       </c>
       <c r="P525" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28495,7 +28498,7 @@
         <v>1</v>
       </c>
       <c r="P526" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28545,7 +28548,7 @@
         <v>1</v>
       </c>
       <c r="P527" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28595,7 +28598,7 @@
         <v>1</v>
       </c>
       <c r="P528" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28645,7 +28648,7 @@
         <v>1</v>
       </c>
       <c r="P529" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28695,7 +28698,7 @@
         <v>1</v>
       </c>
       <c r="P530" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -28745,7 +28748,7 @@
         <v>1</v>
       </c>
       <c r="P531" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="532" spans="1:16">
@@ -28795,7 +28798,7 @@
         <v>1</v>
       </c>
       <c r="P532" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="533" spans="1:16">
@@ -28845,7 +28848,7 @@
         <v>1</v>
       </c>
       <c r="P533" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="534" spans="1:16">
@@ -28895,7 +28898,7 @@
         <v>1</v>
       </c>
       <c r="P534" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -28945,7 +28948,7 @@
         <v>1</v>
       </c>
       <c r="P535" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -28995,7 +28998,7 @@
         <v>1</v>
       </c>
       <c r="P536" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -29295,7 +29298,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -29345,7 +29348,7 @@
         <v>1</v>
       </c>
       <c r="P543" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -29395,7 +29398,7 @@
         <v>1</v>
       </c>
       <c r="P544" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -29445,7 +29448,7 @@
         <v>1</v>
       </c>
       <c r="P545" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -29495,7 +29498,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -29545,7 +29548,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29595,7 +29598,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29645,7 +29648,7 @@
         <v>1</v>
       </c>
       <c r="P549" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29695,7 +29698,7 @@
         <v>1</v>
       </c>
       <c r="P550" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -30295,7 +30298,7 @@
         <v>1</v>
       </c>
       <c r="P562" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -30345,7 +30348,7 @@
         <v>1</v>
       </c>
       <c r="P563" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="564" spans="1:16">
@@ -30395,7 +30398,7 @@
         <v>1</v>
       </c>
       <c r="P564" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="565" spans="1:16">
@@ -30445,7 +30448,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -30495,7 +30498,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -30545,7 +30548,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30595,7 +30598,7 @@
         <v>1</v>
       </c>
       <c r="P568" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30645,7 +30648,7 @@
         <v>1</v>
       </c>
       <c r="P569" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30695,7 +30698,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30745,7 +30748,7 @@
         <v>1</v>
       </c>
       <c r="P571" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30795,7 +30798,7 @@
         <v>1</v>
       </c>
       <c r="P572" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30845,7 +30848,7 @@
         <v>1</v>
       </c>
       <c r="P573" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30895,7 +30898,7 @@
         <v>1</v>
       </c>
       <c r="P574" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -30945,7 +30948,7 @@
         <v>1</v>
       </c>
       <c r="P575" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="576" spans="1:16">
@@ -30995,7 +30998,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -31045,7 +31048,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -31095,7 +31098,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -31145,7 +31148,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -31195,7 +31198,7 @@
         <v>1</v>
       </c>
       <c r="P580" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -31245,7 +31248,7 @@
         <v>1</v>
       </c>
       <c r="P581" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -31295,7 +31298,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -31345,7 +31348,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31395,7 +31398,7 @@
         <v>1</v>
       </c>
       <c r="P584" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31445,7 +31448,7 @@
         <v>1</v>
       </c>
       <c r="P585" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -31495,7 +31498,7 @@
         <v>1</v>
       </c>
       <c r="P586" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31545,7 +31548,7 @@
         <v>1</v>
       </c>
       <c r="P587" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31595,7 +31598,7 @@
         <v>1</v>
       </c>
       <c r="P588" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31645,7 +31648,7 @@
         <v>1</v>
       </c>
       <c r="P589" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31695,7 +31698,7 @@
         <v>1</v>
       </c>
       <c r="P590" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31745,7 +31748,7 @@
         <v>1</v>
       </c>
       <c r="P591" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -31795,7 +31798,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -31845,7 +31848,7 @@
         <v>1</v>
       </c>
       <c r="P593" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -31895,7 +31898,7 @@
         <v>1</v>
       </c>
       <c r="P594" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -31945,7 +31948,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -32195,7 +32198,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -32245,7 +32248,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -32295,7 +32298,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -32345,7 +32348,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -32395,7 +32398,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32445,7 +32448,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32495,7 +32498,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -32545,7 +32548,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32595,7 +32598,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32645,7 +32648,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32695,7 +32698,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32745,7 +32748,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -33295,7 +33298,7 @@
         <v>1</v>
       </c>
       <c r="P622" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="623" spans="1:16">
@@ -33345,7 +33348,7 @@
         <v>1</v>
       </c>
       <c r="P623" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="624" spans="1:16">
@@ -33395,7 +33398,7 @@
         <v>1</v>
       </c>
       <c r="P624" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="625" spans="1:16">
@@ -33445,7 +33448,7 @@
         <v>1</v>
       </c>
       <c r="P625" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="626" spans="1:16">
@@ -33495,7 +33498,7 @@
         <v>1</v>
       </c>
       <c r="P626" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="627" spans="1:16">
@@ -33545,7 +33548,7 @@
         <v>1</v>
       </c>
       <c r="P627" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="628" spans="1:16">
@@ -33595,7 +33598,7 @@
         <v>1</v>
       </c>
       <c r="P628" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="629" spans="1:16">
@@ -33645,7 +33648,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -33695,7 +33698,7 @@
         <v>1</v>
       </c>
       <c r="P630" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -33745,7 +33748,7 @@
         <v>1</v>
       </c>
       <c r="P631" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33795,7 +33798,7 @@
         <v>1</v>
       </c>
       <c r="P632" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33845,7 +33848,7 @@
         <v>1</v>
       </c>
       <c r="P633" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33895,7 +33898,7 @@
         <v>1</v>
       </c>
       <c r="P634" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -33945,7 +33948,7 @@
         <v>1</v>
       </c>
       <c r="P635" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -33995,7 +33998,7 @@
         <v>1</v>
       </c>
       <c r="P636" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -34045,7 +34048,7 @@
         <v>1</v>
       </c>
       <c r="P637" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -34095,7 +34098,7 @@
         <v>1</v>
       </c>
       <c r="P638" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -34145,7 +34148,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -34195,7 +34198,7 @@
         <v>1</v>
       </c>
       <c r="P640" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -34245,7 +34248,7 @@
         <v>1</v>
       </c>
       <c r="P641" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -34295,7 +34298,7 @@
         <v>1</v>
       </c>
       <c r="P642" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -34795,7 +34798,7 @@
         <v>1</v>
       </c>
       <c r="P652" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="653" spans="1:16">
@@ -34845,7 +34848,7 @@
         <v>1</v>
       </c>
       <c r="P653" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="654" spans="1:16">
@@ -34895,7 +34898,7 @@
         <v>1</v>
       </c>
       <c r="P654" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="655" spans="1:16">
@@ -34945,7 +34948,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -34995,7 +34998,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -35045,7 +35048,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -35095,7 +35098,7 @@
         <v>1</v>
       </c>
       <c r="P658" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="659" spans="1:16">
@@ -35145,7 +35148,7 @@
         <v>1</v>
       </c>
       <c r="P659" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="660" spans="1:16">
@@ -35195,7 +35198,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -35245,7 +35248,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -35295,7 +35298,7 @@
         <v>1</v>
       </c>
       <c r="P662" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="663" spans="1:16">
@@ -35345,7 +35348,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -35395,7 +35398,7 @@
         <v>1</v>
       </c>
       <c r="P664" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="665" spans="1:16">
@@ -35445,7 +35448,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -35495,7 +35498,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -35545,7 +35548,7 @@
         <v>1</v>
       </c>
       <c r="P667" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35595,7 +35598,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35645,7 +35648,7 @@
         <v>1</v>
       </c>
       <c r="P669" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35695,7 +35698,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35745,7 +35748,7 @@
         <v>1</v>
       </c>
       <c r="P671" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35795,7 +35798,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35845,7 +35848,7 @@
         <v>1</v>
       </c>
       <c r="P673" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35895,7 +35898,7 @@
         <v>1</v>
       </c>
       <c r="P674" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35945,7 +35948,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -35995,7 +35998,7 @@
         <v>1</v>
       </c>
       <c r="P676" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -36045,7 +36048,7 @@
         <v>1</v>
       </c>
       <c r="P677" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -36095,7 +36098,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -36145,7 +36148,7 @@
         <v>1</v>
       </c>
       <c r="P679" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -36195,7 +36198,7 @@
         <v>1</v>
       </c>
       <c r="P680" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -36245,7 +36248,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -36295,7 +36298,7 @@
         <v>1</v>
       </c>
       <c r="P682" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36345,7 +36348,7 @@
         <v>1</v>
       </c>
       <c r="P683" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36795,7 +36798,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36845,7 +36848,7 @@
         <v>1</v>
       </c>
       <c r="P693" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36895,7 +36898,7 @@
         <v>1</v>
       </c>
       <c r="P694" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36945,7 +36948,7 @@
         <v>1</v>
       </c>
       <c r="P695" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36995,7 +36998,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -37045,7 +37048,7 @@
         <v>1</v>
       </c>
       <c r="P697" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -37095,7 +37098,7 @@
         <v>1</v>
       </c>
       <c r="P698" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -37145,7 +37148,7 @@
         <v>1</v>
       </c>
       <c r="P699" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -37745,7 +37748,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37795,7 +37798,7 @@
         <v>1</v>
       </c>
       <c r="P712" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37845,7 +37848,7 @@
         <v>1</v>
       </c>
       <c r="P713" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37895,7 +37898,7 @@
         <v>1</v>
       </c>
       <c r="P714" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37945,7 +37948,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37995,7 +37998,7 @@
         <v>1</v>
       </c>
       <c r="P716" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -38045,7 +38048,7 @@
         <v>1</v>
       </c>
       <c r="P717" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -38095,7 +38098,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -38145,7 +38148,7 @@
         <v>1</v>
       </c>
       <c r="P719" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -38545,7 +38548,7 @@
         <v>1</v>
       </c>
       <c r="P727" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38595,7 +38598,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -38645,7 +38648,7 @@
         <v>1</v>
       </c>
       <c r="P729" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -38695,7 +38698,7 @@
         <v>1</v>
       </c>
       <c r="P730" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -38745,7 +38748,7 @@
         <v>1</v>
       </c>
       <c r="P731" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="732" spans="1:16">
@@ -38795,7 +38798,7 @@
         <v>1</v>
       </c>
       <c r="P732" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="733" spans="1:16">
@@ -38845,7 +38848,7 @@
         <v>1</v>
       </c>
       <c r="P733" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="734" spans="1:16">
@@ -38895,7 +38898,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38945,7 +38948,7 @@
         <v>1</v>
       </c>
       <c r="P735" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38995,7 +38998,7 @@
         <v>1</v>
       </c>
       <c r="P736" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -39045,7 +39048,7 @@
         <v>1</v>
       </c>
       <c r="P737" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -39095,7 +39098,7 @@
         <v>1</v>
       </c>
       <c r="P738" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="739" spans="1:16">
@@ -39145,7 +39148,7 @@
         <v>1</v>
       </c>
       <c r="P739" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="740" spans="1:16">
@@ -39195,7 +39198,7 @@
         <v>1</v>
       </c>
       <c r="P740" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="741" spans="1:16">
@@ -39245,7 +39248,7 @@
         <v>1</v>
       </c>
       <c r="P741" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="742" spans="1:16">
@@ -39295,7 +39298,7 @@
         <v>1</v>
       </c>
       <c r="P742" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="743" spans="1:16">
@@ -39345,7 +39348,7 @@
         <v>1</v>
       </c>
       <c r="P743" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="744" spans="1:16">
@@ -39395,7 +39398,7 @@
         <v>1</v>
       </c>
       <c r="P744" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="745" spans="1:16">
@@ -39445,7 +39448,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -39745,7 +39748,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39795,7 +39798,7 @@
         <v>1</v>
       </c>
       <c r="P752" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39845,7 +39848,7 @@
         <v>1</v>
       </c>
       <c r="P753" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39895,7 +39898,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39945,7 +39948,7 @@
         <v>1</v>
       </c>
       <c r="P755" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39995,7 +39998,7 @@
         <v>1</v>
       </c>
       <c r="P756" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -40045,7 +40048,7 @@
         <v>1</v>
       </c>
       <c r="P757" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -40095,7 +40098,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -40145,7 +40148,7 @@
         <v>1</v>
       </c>
       <c r="P759" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -40195,7 +40198,7 @@
         <v>1</v>
       </c>
       <c r="P760" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -40245,7 +40248,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -40295,7 +40298,7 @@
         <v>1</v>
       </c>
       <c r="P762" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -40645,7 +40648,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -40695,7 +40698,7 @@
         <v>1</v>
       </c>
       <c r="P770" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="771" spans="1:16">
@@ -40745,7 +40748,7 @@
         <v>1</v>
       </c>
       <c r="P771" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -40795,7 +40798,7 @@
         <v>1</v>
       </c>
       <c r="P772" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -40845,7 +40848,7 @@
         <v>1</v>
       </c>
       <c r="P773" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40895,7 +40898,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40945,7 +40948,7 @@
         <v>1</v>
       </c>
       <c r="P775" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40995,7 +40998,7 @@
         <v>1</v>
       </c>
       <c r="P776" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -41045,7 +41048,7 @@
         <v>1</v>
       </c>
       <c r="P777" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -41095,7 +41098,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -41145,7 +41148,7 @@
         <v>1</v>
       </c>
       <c r="P779" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -41195,7 +41198,7 @@
         <v>1</v>
       </c>
       <c r="P780" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -41245,7 +41248,7 @@
         <v>1</v>
       </c>
       <c r="P781" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -41295,7 +41298,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -41345,7 +41348,7 @@
         <v>1</v>
       </c>
       <c r="P783" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -42095,7 +42098,7 @@
         <v>1</v>
       </c>
       <c r="P798" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="799" spans="1:16">
@@ -42145,7 +42148,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -42195,7 +42198,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -42245,7 +42248,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -42295,7 +42298,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -42345,7 +42348,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -42395,7 +42398,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -42445,7 +42448,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -42495,7 +42498,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -42545,7 +42548,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42595,7 +42598,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42645,7 +42648,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42695,7 +42698,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -42745,7 +42748,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -43295,7 +43298,7 @@
         <v>1</v>
       </c>
       <c r="P822" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="823" spans="1:16">
@@ -43345,7 +43348,7 @@
         <v>1</v>
       </c>
       <c r="P823" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="824" spans="1:16">
@@ -43395,7 +43398,7 @@
         <v>1</v>
       </c>
       <c r="P824" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="825" spans="1:16">
@@ -43445,7 +43448,7 @@
         <v>1</v>
       </c>
       <c r="P825" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="826" spans="1:16">
@@ -43495,7 +43498,7 @@
         <v>1</v>
       </c>
       <c r="P826" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="827" spans="1:16">
@@ -43545,7 +43548,7 @@
         <v>1</v>
       </c>
       <c r="P827" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="828" spans="1:16">
@@ -43595,7 +43598,7 @@
         <v>1</v>
       </c>
       <c r="P828" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="829" spans="1:16">
@@ -43645,7 +43648,7 @@
         <v>1</v>
       </c>
       <c r="P829" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="830" spans="1:16">
@@ -43695,7 +43698,7 @@
         <v>1</v>
       </c>
       <c r="P830" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="831" spans="1:16">
@@ -43745,7 +43748,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -43795,7 +43798,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43845,7 +43848,7 @@
         <v>1</v>
       </c>
       <c r="P833" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="834" spans="1:16">
@@ -43895,7 +43898,7 @@
         <v>1</v>
       </c>
       <c r="P834" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="835" spans="1:16">
@@ -43945,7 +43948,7 @@
         <v>1</v>
       </c>
       <c r="P835" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="836" spans="1:16">
@@ -43995,7 +43998,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -44045,7 +44048,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -44095,7 +44098,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -44145,7 +44148,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -44195,7 +44198,7 @@
         <v>1</v>
       </c>
       <c r="P840" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -44245,7 +44248,7 @@
         <v>1</v>
       </c>
       <c r="P841" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="842" spans="1:16">
@@ -44295,7 +44298,7 @@
         <v>1</v>
       </c>
       <c r="P842" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="843" spans="1:16">
@@ -44345,7 +44348,7 @@
         <v>1</v>
       </c>
       <c r="P843" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="844" spans="1:16">
@@ -44395,7 +44398,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -44445,7 +44448,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44495,7 +44498,7 @@
         <v>1</v>
       </c>
       <c r="P846" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44545,7 +44548,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44595,7 +44598,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44645,7 +44648,7 @@
         <v>1</v>
       </c>
       <c r="P849" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44695,7 +44698,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44745,7 +44748,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -44795,7 +44798,7 @@
         <v>1</v>
       </c>
       <c r="P852" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -44845,7 +44848,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -44895,7 +44898,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44945,7 +44948,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -44995,7 +44998,7 @@
         <v>1</v>
       </c>
       <c r="P856" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -45045,7 +45048,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -45095,7 +45098,7 @@
         <v>1</v>
       </c>
       <c r="P858" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="859" spans="1:16">
@@ -45145,7 +45148,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -45195,7 +45198,7 @@
         <v>1</v>
       </c>
       <c r="P860" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -45245,7 +45248,7 @@
         <v>1</v>
       </c>
       <c r="P861" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="862" spans="1:16">
@@ -45295,7 +45298,7 @@
         <v>1</v>
       </c>
       <c r="P862" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="863" spans="1:16">
@@ -45345,7 +45348,7 @@
         <v>1</v>
       </c>
       <c r="P863" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="864" spans="1:16">
@@ -45395,7 +45398,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -45445,7 +45448,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45495,7 +45498,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45545,7 +45548,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45595,7 +45598,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45645,7 +45648,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45695,7 +45698,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45745,7 +45748,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45795,7 +45798,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45845,7 +45848,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -45895,7 +45898,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45945,7 +45948,7 @@
         <v>1</v>
       </c>
       <c r="P875" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45995,7 +45998,7 @@
         <v>1</v>
       </c>
       <c r="P876" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -46045,7 +46048,7 @@
         <v>1</v>
       </c>
       <c r="P877" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -46095,7 +46098,7 @@
         <v>1</v>
       </c>
       <c r="P878" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="879" spans="1:16">
@@ -46145,7 +46148,7 @@
         <v>1</v>
       </c>
       <c r="P879" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="880" spans="1:16">
@@ -46195,7 +46198,7 @@
         <v>1</v>
       </c>
       <c r="P880" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="881" spans="1:16">
@@ -46245,7 +46248,7 @@
         <v>1</v>
       </c>
       <c r="P881" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="882" spans="1:16">
@@ -46295,7 +46298,7 @@
         <v>1</v>
       </c>
       <c r="P882" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -46345,7 +46348,7 @@
         <v>1</v>
       </c>
       <c r="P883" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46395,7 +46398,7 @@
         <v>1</v>
       </c>
       <c r="P884" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46445,7 +46448,7 @@
         <v>1</v>
       </c>
       <c r="P885" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46495,7 +46498,7 @@
         <v>1</v>
       </c>
       <c r="P886" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46545,7 +46548,7 @@
         <v>1</v>
       </c>
       <c r="P887" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="888" spans="1:16">
@@ -46595,7 +46598,7 @@
         <v>1</v>
       </c>
       <c r="P888" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="889" spans="1:16">
@@ -46645,7 +46648,7 @@
         <v>1</v>
       </c>
       <c r="P889" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="890" spans="1:16">
@@ -46695,7 +46698,7 @@
         <v>1</v>
       </c>
       <c r="P890" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="891" spans="1:16">
@@ -46745,7 +46748,7 @@
         <v>1</v>
       </c>
       <c r="P891" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="892" spans="1:16">
@@ -46795,7 +46798,7 @@
         <v>1</v>
       </c>
       <c r="P892" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="893" spans="1:16">
@@ -46845,7 +46848,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46895,7 +46898,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46945,7 +46948,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -46995,7 +46998,7 @@
         <v>1</v>
       </c>
       <c r="P896" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="897" spans="1:16">
@@ -47045,7 +47048,7 @@
         <v>1</v>
       </c>
       <c r="P897" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="898" spans="1:16">
@@ -47095,7 +47098,7 @@
         <v>1</v>
       </c>
       <c r="P898" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="899" spans="1:16">
@@ -47145,7 +47148,7 @@
         <v>1</v>
       </c>
       <c r="P899" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="900" spans="1:16">
@@ -47195,7 +47198,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -47245,7 +47248,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -47295,7 +47298,7 @@
         <v>1</v>
       </c>
       <c r="P902" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="903" spans="1:16">
@@ -47345,7 +47348,7 @@
         <v>1</v>
       </c>
       <c r="P903" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="904" spans="1:16">
@@ -47395,7 +47398,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -47445,7 +47448,7 @@
         <v>1</v>
       </c>
       <c r="P905" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="906" spans="1:16">
@@ -47495,7 +47498,7 @@
         <v>1</v>
       </c>
       <c r="P906" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="907" spans="1:16">
@@ -47545,7 +47548,7 @@
         <v>1</v>
       </c>
       <c r="P907" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="908" spans="1:16">
@@ -47595,7 +47598,7 @@
         <v>1</v>
       </c>
       <c r="P908" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="909" spans="1:16">
@@ -47645,7 +47648,7 @@
         <v>1</v>
       </c>
       <c r="P909" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="910" spans="1:16">
@@ -47695,7 +47698,7 @@
         <v>1</v>
       </c>
       <c r="P910" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="911" spans="1:16">
@@ -47745,7 +47748,7 @@
         <v>1</v>
       </c>
       <c r="P911" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="912" spans="1:16">
@@ -47795,7 +47798,7 @@
         <v>1</v>
       </c>
       <c r="P912" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="913" spans="1:16">
@@ -47845,7 +47848,7 @@
         <v>1</v>
       </c>
       <c r="P913" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="914" spans="1:16">
@@ -47895,7 +47898,7 @@
         <v>1</v>
       </c>
       <c r="P914" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="915" spans="1:16">
@@ -47945,7 +47948,7 @@
         <v>1</v>
       </c>
       <c r="P915" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="916" spans="1:16">
@@ -47995,7 +47998,7 @@
         <v>1</v>
       </c>
       <c r="P916" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="917" spans="1:16">
@@ -48045,7 +48048,7 @@
         <v>1</v>
       </c>
       <c r="P917" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="918" spans="1:16">
@@ -48095,7 +48098,7 @@
         <v>1</v>
       </c>
       <c r="P918" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="919" spans="1:16">
@@ -48145,7 +48148,7 @@
         <v>1</v>
       </c>
       <c r="P919" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="920" spans="1:16">
@@ -48195,7 +48198,7 @@
         <v>1</v>
       </c>
       <c r="P920" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="921" spans="1:16">
@@ -48245,7 +48248,7 @@
         <v>1</v>
       </c>
       <c r="P921" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="922" spans="1:16">
@@ -48295,7 +48298,7 @@
         <v>1</v>
       </c>
       <c r="P922" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="923" spans="1:16">
@@ -48345,7 +48348,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -48395,7 +48398,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -48445,7 +48448,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48495,7 +48498,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48545,7 +48548,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -48595,7 +48598,7 @@
         <v>1</v>
       </c>
       <c r="P928" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="929" spans="1:16">
@@ -48645,7 +48648,7 @@
         <v>1</v>
       </c>
       <c r="P929" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="930" spans="1:16">
@@ -48695,7 +48698,7 @@
         <v>1</v>
       </c>
       <c r="P930" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="931" spans="1:16">
@@ -48745,7 +48748,7 @@
         <v>1</v>
       </c>
       <c r="P931" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="932" spans="1:16">
@@ -48795,7 +48798,7 @@
         <v>1</v>
       </c>
       <c r="P932" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="933" spans="1:16">
@@ -48845,7 +48848,7 @@
         <v>1</v>
       </c>
       <c r="P933" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="934" spans="1:16">
@@ -48895,7 +48898,7 @@
         <v>1</v>
       </c>
       <c r="P934" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="935" spans="1:16">
@@ -48945,7 +48948,7 @@
         <v>1</v>
       </c>
       <c r="P935" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="936" spans="1:16">
@@ -48995,7 +48998,7 @@
         <v>1</v>
       </c>
       <c r="P936" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="937" spans="1:16">
@@ -49045,7 +49048,7 @@
         <v>1</v>
       </c>
       <c r="P937" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="938" spans="1:16">
@@ -49095,7 +49098,7 @@
         <v>1</v>
       </c>
       <c r="P938" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="939" spans="1:16">
@@ -49145,7 +49148,7 @@
         <v>1</v>
       </c>
       <c r="P939" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="940" spans="1:16">
@@ -49195,7 +49198,7 @@
         <v>1</v>
       </c>
       <c r="P940" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="941" spans="1:16">
@@ -49245,7 +49248,7 @@
         <v>1</v>
       </c>
       <c r="P941" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="942" spans="1:16">
@@ -50445,7 +50448,7 @@
         <v>1</v>
       </c>
       <c r="P965" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="966" spans="1:16">
@@ -50495,7 +50498,7 @@
         <v>1</v>
       </c>
       <c r="P966" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="967" spans="1:16">
@@ -50545,7 +50548,7 @@
         <v>1</v>
       </c>
       <c r="P967" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="968" spans="1:16">
@@ -50595,7 +50598,7 @@
         <v>1</v>
       </c>
       <c r="P968" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="969" spans="1:16">
@@ -51295,7 +51298,7 @@
         <v>1</v>
       </c>
       <c r="P982" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="983" spans="1:16">
@@ -51345,7 +51348,7 @@
         <v>1</v>
       </c>
       <c r="P983" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="984" spans="1:16">
@@ -51395,7 +51398,7 @@
         <v>1</v>
       </c>
       <c r="P984" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="985" spans="1:16">
@@ -51445,7 +51448,7 @@
         <v>1</v>
       </c>
       <c r="P985" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="986" spans="1:16">
@@ -51495,7 +51498,7 @@
         <v>1</v>
       </c>
       <c r="P986" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="987" spans="1:16">
@@ -51545,7 +51548,7 @@
         <v>1</v>
       </c>
       <c r="P987" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="988" spans="1:16">
@@ -51595,7 +51598,7 @@
         <v>1</v>
       </c>
       <c r="P988" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="989" spans="1:16">
@@ -51645,7 +51648,7 @@
         <v>1</v>
       </c>
       <c r="P989" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="990" spans="1:16">
@@ -51695,7 +51698,7 @@
         <v>1</v>
       </c>
       <c r="P990" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="991" spans="1:16">
@@ -52145,7 +52148,7 @@
         <v>1</v>
       </c>
       <c r="P999" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1000" spans="1:16">
@@ -52195,7 +52198,7 @@
         <v>1</v>
       </c>
       <c r="P1000" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1001" spans="1:16">
@@ -52245,7 +52248,7 @@
         <v>1</v>
       </c>
       <c r="P1001" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1002" spans="1:16">
@@ -52295,7 +52298,7 @@
         <v>1</v>
       </c>
       <c r="P1002" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1003" spans="1:16">
@@ -52345,7 +52348,7 @@
         <v>1</v>
       </c>
       <c r="P1003" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="1004" spans="1:16">
@@ -52395,7 +52398,7 @@
         <v>1</v>
       </c>
       <c r="P1004" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1005" spans="1:16">
@@ -52445,7 +52448,7 @@
         <v>1</v>
       </c>
       <c r="P1005" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1006" spans="1:16">
@@ -52495,7 +52498,7 @@
         <v>1</v>
       </c>
       <c r="P1006" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1007" spans="1:16">
@@ -52545,7 +52548,7 @@
         <v>1</v>
       </c>
       <c r="P1007" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1008" spans="1:16">
@@ -52595,7 +52598,7 @@
         <v>1</v>
       </c>
       <c r="P1008" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="1009" spans="1:16">
@@ -53445,7 +53448,7 @@
         <v>1</v>
       </c>
       <c r="P1025" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="1026" spans="1:16">
@@ -53495,7 +53498,7 @@
         <v>1</v>
       </c>
       <c r="P1026" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="1027" spans="1:16">
@@ -53545,7 +53548,7 @@
         <v>1</v>
       </c>
       <c r="P1027" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="1028" spans="1:16">
@@ -53595,7 +53598,7 @@
         <v>1</v>
       </c>
       <c r="P1028" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="1029" spans="1:16">
@@ -53645,7 +53648,7 @@
         <v>1</v>
       </c>
       <c r="P1029" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="1030" spans="1:16">
@@ -53695,7 +53698,7 @@
         <v>1</v>
       </c>
       <c r="P1030" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="1031" spans="1:16">
@@ -53745,7 +53748,7 @@
         <v>1</v>
       </c>
       <c r="P1031" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="1032" spans="1:16">
@@ -53795,7 +53798,7 @@
         <v>1</v>
       </c>
       <c r="P1032" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="1033" spans="1:16">
@@ -53845,7 +53848,7 @@
         <v>1</v>
       </c>
       <c r="P1033" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1034" spans="1:16">
@@ -53895,7 +53898,7 @@
         <v>1</v>
       </c>
       <c r="P1034" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1035" spans="1:16">
@@ -53945,7 +53948,7 @@
         <v>1</v>
       </c>
       <c r="P1035" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1036" spans="1:16">
@@ -53995,7 +53998,7 @@
         <v>1</v>
       </c>
       <c r="P1036" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="1037" spans="1:16">
@@ -54045,7 +54048,7 @@
         <v>1</v>
       </c>
       <c r="P1037" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="1038" spans="1:16">
@@ -54095,7 +54098,7 @@
         <v>1</v>
       </c>
       <c r="P1038" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="1039" spans="1:16">
@@ -54145,7 +54148,7 @@
         <v>1</v>
       </c>
       <c r="P1039" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="1040" spans="1:16">
@@ -54195,7 +54198,7 @@
         <v>1</v>
       </c>
       <c r="P1040" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="1041" spans="1:16">
@@ -54245,7 +54248,7 @@
         <v>1</v>
       </c>
       <c r="P1041" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="1042" spans="1:16">
@@ -54295,7 +54298,7 @@
         <v>1</v>
       </c>
       <c r="P1042" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="1043" spans="1:16">
@@ -54345,7 +54348,7 @@
         <v>1</v>
       </c>
       <c r="P1043" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="1044" spans="1:16">
@@ -54395,7 +54398,7 @@
         <v>1</v>
       </c>
       <c r="P1044" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="1045" spans="1:16">
@@ -54445,7 +54448,7 @@
         <v>1</v>
       </c>
       <c r="P1045" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="1046" spans="1:16">
@@ -54495,7 +54498,7 @@
         <v>1</v>
       </c>
       <c r="P1046" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="1047" spans="1:16">
@@ -54595,7 +54598,7 @@
         <v>1</v>
       </c>
       <c r="P1048" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="1049" spans="1:16">
@@ -54645,7 +54648,7 @@
         <v>1</v>
       </c>
       <c r="P1049" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="1050" spans="1:16">
@@ -54695,7 +54698,7 @@
         <v>1</v>
       </c>
       <c r="P1050" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="1051" spans="1:16">
@@ -54745,7 +54748,7 @@
         <v>1</v>
       </c>
       <c r="P1051" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="1052" spans="1:16">
@@ -54795,7 +54798,7 @@
         <v>1</v>
       </c>
       <c r="P1052" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="1053" spans="1:16">
@@ -54845,7 +54848,7 @@
         <v>1</v>
       </c>
       <c r="P1053" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="1054" spans="1:16">
@@ -54895,7 +54898,7 @@
         <v>1</v>
       </c>
       <c r="P1054" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="1055" spans="1:16">
@@ -54945,7 +54948,7 @@
         <v>1</v>
       </c>
       <c r="P1055" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="1056" spans="1:16">
@@ -54995,7 +54998,7 @@
         <v>1</v>
       </c>
       <c r="P1056" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="1057" spans="1:16">
@@ -55045,7 +55048,7 @@
         <v>1</v>
       </c>
       <c r="P1057" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="1058" spans="1:16">
@@ -55095,7 +55098,7 @@
         <v>1</v>
       </c>
       <c r="P1058" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="1059" spans="1:16">
@@ -55145,7 +55148,7 @@
         <v>1</v>
       </c>
       <c r="P1059" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="1060" spans="1:16">
@@ -55159,10 +55162,10 @@
         <v>-0.5772256233441624</v>
       </c>
       <c r="D1060" t="s">
-        <v>296</v>
+        <v>470</v>
       </c>
       <c r="E1060">
-        <v>-0.8674432626015163</v>
+        <v>-0.8141244385520068</v>
       </c>
       <c r="F1060">
         <v>-1</v>
@@ -55171,10 +55174,10 @@
         <v>0.01603722562334416</v>
       </c>
       <c r="H1060">
-        <v>0.01624744326260152</v>
+        <v>0.01633412443855201</v>
       </c>
       <c r="I1060">
-        <v>0.2902176392573539</v>
+        <v>0.2368988152078444</v>
       </c>
       <c r="J1060">
         <v>1.668117595049029</v>
@@ -55186,16 +55189,16 @@
         <v>7.73</v>
       </c>
       <c r="M1060">
-        <v>5.13</v>
+        <v>5.14</v>
       </c>
       <c r="N1060">
-        <v>7.69</v>
+        <v>7.76</v>
       </c>
       <c r="O1060">
         <v>1</v>
       </c>
       <c r="P1060" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="1061" spans="1:16">
@@ -55212,7 +55215,7 @@
         <v>471</v>
       </c>
       <c r="E1061">
-        <v>-0.8710786311994871</v>
+        <v>-0.8671572602096775</v>
       </c>
       <c r="F1061">
         <v>1</v>
@@ -55221,10 +55224,10 @@
         <v>0.01635782258294039</v>
       </c>
       <c r="H1061">
-        <v>0.01561107863119949</v>
+        <v>0.01544715726020968</v>
       </c>
       <c r="I1061">
-        <v>0.2267439517409073</v>
+        <v>0.2306653227307169</v>
       </c>
       <c r="J1061">
         <v>1.67842741979623</v>
@@ -55236,16 +55239,16 @@
         <v>7.63</v>
       </c>
       <c r="M1061">
-        <v>4.91</v>
+        <v>4.86</v>
       </c>
       <c r="N1061">
-        <v>7.37</v>
+        <v>7.29</v>
       </c>
       <c r="O1061">
         <v>1</v>
       </c>
       <c r="P1061" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="1062" spans="1:16">
@@ -55253,49 +55256,49 @@
         <v>1</v>
       </c>
       <c r="B1062" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C1062">
-        <v>-1.157822582940394</v>
+        <v>-1.071038308742433</v>
       </c>
       <c r="D1062" t="s">
         <v>471</v>
       </c>
       <c r="E1062">
-        <v>-0.8710786311994871</v>
+        <v>-0.8671572602096775</v>
       </c>
       <c r="F1062">
         <v>1</v>
       </c>
       <c r="G1062">
-        <v>0.01629782258294039</v>
+        <v>0.01635103830874243</v>
       </c>
       <c r="H1062">
-        <v>0.01561107863119949</v>
+        <v>0.01544715726020968</v>
       </c>
       <c r="I1062">
-        <v>0.2867439517409069</v>
+        <v>0.2038810485327556</v>
       </c>
       <c r="J1062">
         <v>1.67842741979623</v>
       </c>
       <c r="K1062">
-        <v>5.2</v>
+        <v>5.19</v>
       </c>
       <c r="L1062">
-        <v>7.57</v>
+        <v>7.64</v>
       </c>
       <c r="M1062">
-        <v>4.91</v>
+        <v>4.86</v>
       </c>
       <c r="N1062">
-        <v>7.37</v>
+        <v>7.29</v>
       </c>
       <c r="O1062">
         <v>1</v>
       </c>
       <c r="P1062" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="1063" spans="1:16">
@@ -55312,7 +55315,7 @@
         <v>471</v>
       </c>
       <c r="E1063">
-        <v>-0.8710786311994871</v>
+        <v>-0.8671572602096775</v>
       </c>
       <c r="F1063">
         <v>1</v>
@@ -55321,10 +55324,10 @@
         <v>0.01561178427638726</v>
       </c>
       <c r="H1063">
-        <v>0.01561107863119949</v>
+        <v>0.01544715726020968</v>
       </c>
       <c r="I1063">
-        <v>0.2007056451877736</v>
+        <v>0.2046270161775832</v>
       </c>
       <c r="J1063">
         <v>1.67842741979623</v>
@@ -55336,16 +55339,16 @@
         <v>7.27</v>
       </c>
       <c r="M1063">
-        <v>4.91</v>
+        <v>4.86</v>
       </c>
       <c r="N1063">
-        <v>7.37</v>
+        <v>7.29</v>
       </c>
       <c r="O1063">
         <v>1</v>
       </c>
       <c r="P1063" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="1064" spans="1:16">
@@ -55395,7 +55398,7 @@
         <v>1</v>
       </c>
       <c r="P1064" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="1065" spans="1:16">
@@ -55409,7 +55412,7 @@
         <v>-1.132542776541119</v>
       </c>
       <c r="D1065" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E1065">
         <v>-0.9038625063109409</v>
@@ -55445,7 +55448,7 @@
         <v>1</v>
       </c>
       <c r="P1065" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="1066" spans="1:16">
@@ -55453,13 +55456,13 @@
         <v>1</v>
       </c>
       <c r="B1066" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C1066">
-        <v>-1.192542776541119</v>
+        <v>-1.105691732740079</v>
       </c>
       <c r="D1066" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E1066">
         <v>-0.9038625063109409</v>
@@ -55468,22 +55471,22 @@
         <v>1</v>
       </c>
       <c r="G1066">
-        <v>0.01633254277654112</v>
+        <v>0.01638569173274008</v>
       </c>
       <c r="H1066">
         <v>0.01564386250631094</v>
       </c>
       <c r="I1066">
-        <v>0.2886802702301781</v>
+        <v>0.2018292264291386</v>
       </c>
       <c r="J1066">
         <v>1.685104380104061</v>
       </c>
       <c r="K1066">
-        <v>5.2</v>
+        <v>5.19</v>
       </c>
       <c r="L1066">
-        <v>7.57</v>
+        <v>7.64</v>
       </c>
       <c r="M1066">
         <v>4.91</v>
@@ -55495,7 +55498,7 @@
         <v>1</v>
       </c>
       <c r="P1066" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="1067" spans="1:16">
@@ -55545,71 +55548,71 @@
         <v>1</v>
       </c>
       <c r="P1067" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="1068" spans="1:16">
       <c r="A1068" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1068" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C1068">
-        <v>-0.7149687691171831</v>
+        <v>-1.157889853450652</v>
       </c>
       <c r="D1068" t="s">
-        <v>296</v>
+        <v>472</v>
       </c>
       <c r="E1068">
-        <v>-0.954585469933833</v>
+        <v>-0.9277959962389817</v>
       </c>
       <c r="F1068">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1068">
-        <v>0.01603496876911719</v>
+        <v>0.01641788985345065</v>
       </c>
       <c r="H1068">
-        <v>0.01633458546993383</v>
+        <v>0.01566779599623898</v>
       </c>
       <c r="I1068">
-        <v>0.2396167008166499</v>
+        <v>0.2300938572116706</v>
       </c>
       <c r="J1068">
-        <v>1.685104380104061</v>
+        <v>1.689978817971279</v>
       </c>
       <c r="K1068">
-        <v>4.97</v>
+        <v>5.2</v>
       </c>
       <c r="L1068">
-        <v>7.66</v>
+        <v>7.63</v>
       </c>
       <c r="M1068">
-        <v>5.13</v>
+        <v>4.91</v>
       </c>
       <c r="N1068">
-        <v>7.69</v>
+        <v>7.37</v>
       </c>
       <c r="O1068">
         <v>1</v>
       </c>
       <c r="P1068" t="s">
-        <v>607</v>
+        <v>467</v>
       </c>
     </row>
     <row r="1069" spans="1:16">
       <c r="A1069" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1069" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C1069">
-        <v>-1.157889853450652</v>
+        <v>-1.217889853450652</v>
       </c>
       <c r="D1069" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E1069">
         <v>-0.9277959962389817</v>
@@ -55618,13 +55621,13 @@
         <v>1</v>
       </c>
       <c r="G1069">
-        <v>0.01641788985345065</v>
+        <v>0.01635788985345065</v>
       </c>
       <c r="H1069">
         <v>0.01566779599623898</v>
       </c>
       <c r="I1069">
-        <v>0.2300938572116706</v>
+        <v>0.2900938572116702</v>
       </c>
       <c r="J1069">
         <v>1.689978817971279</v>
@@ -55633,7 +55636,7 @@
         <v>5.2</v>
       </c>
       <c r="L1069">
-        <v>7.63</v>
+        <v>7.57</v>
       </c>
       <c r="M1069">
         <v>4.91</v>
@@ -55650,46 +55653,46 @@
     </row>
     <row r="1070" spans="1:16">
       <c r="A1070" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1070" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C1070">
-        <v>-1.217889853450652</v>
+        <v>-0.6860945134969718</v>
       </c>
       <c r="D1070" t="s">
-        <v>471</v>
+        <v>296</v>
       </c>
       <c r="E1070">
-        <v>-0.9277959962389817</v>
+        <v>-0.9795913361926631</v>
       </c>
       <c r="F1070">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1070">
-        <v>0.01635788985345065</v>
+        <v>0.01614609451349697</v>
       </c>
       <c r="H1070">
-        <v>0.01566779599623898</v>
+        <v>0.01635959133619266</v>
       </c>
       <c r="I1070">
-        <v>0.2900938572116702</v>
+        <v>0.2934968226956913</v>
       </c>
       <c r="J1070">
         <v>1.689978817971279</v>
       </c>
       <c r="K1070">
-        <v>5.2</v>
+        <v>4.98</v>
       </c>
       <c r="L1070">
-        <v>7.57</v>
+        <v>7.73</v>
       </c>
       <c r="M1070">
-        <v>4.91</v>
+        <v>5.13</v>
       </c>
       <c r="N1070">
-        <v>7.37</v>
+        <v>7.69</v>
       </c>
       <c r="O1070">
         <v>1</v>
@@ -55700,13 +55703,13 @@
     </row>
     <row r="1071" spans="1:16">
       <c r="A1071" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1071" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C1071">
-        <v>-0.6860945134969718</v>
+        <v>-0.7391947253172582</v>
       </c>
       <c r="D1071" t="s">
         <v>296</v>
@@ -55718,22 +55721,22 @@
         <v>-1</v>
       </c>
       <c r="G1071">
-        <v>0.01614609451349697</v>
+        <v>0.01605919472531726</v>
       </c>
       <c r="H1071">
         <v>0.01635959133619266</v>
       </c>
       <c r="I1071">
-        <v>0.2934968226956913</v>
+        <v>0.240396610875405</v>
       </c>
       <c r="J1071">
         <v>1.689978817971279</v>
       </c>
       <c r="K1071">
-        <v>4.98</v>
+        <v>4.97</v>
       </c>
       <c r="L1071">
-        <v>7.73</v>
+        <v>7.66</v>
       </c>
       <c r="M1071">
         <v>5.13</v>
@@ -55750,202 +55753,152 @@
     </row>
     <row r="1072" spans="1:16">
       <c r="A1072" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B1072" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C1072">
-        <v>-0.7391947253172582</v>
+        <v>-2.807532631974992</v>
       </c>
       <c r="D1072" t="s">
-        <v>296</v>
+        <v>469</v>
       </c>
       <c r="E1072">
-        <v>-0.9795913361926631</v>
+        <v>-2.509249826348689</v>
       </c>
       <c r="F1072">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1072">
-        <v>0.01605919472531726</v>
+        <v>0.01758753263197499</v>
       </c>
       <c r="H1072">
-        <v>0.01635959133619266</v>
+        <v>0.01710924982634869</v>
       </c>
       <c r="I1072">
-        <v>0.240396610875405</v>
+        <v>0.2982828056263038</v>
       </c>
       <c r="J1072">
-        <v>1.689978817971279</v>
+        <v>2.043593713822644</v>
       </c>
       <c r="K1072">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
       <c r="L1072">
-        <v>7.66</v>
+        <v>7.39</v>
       </c>
       <c r="M1072">
-        <v>5.13</v>
+        <v>4.8</v>
       </c>
       <c r="N1072">
-        <v>7.69</v>
+        <v>7.3</v>
       </c>
       <c r="O1072">
         <v>1</v>
       </c>
       <c r="P1072" t="s">
-        <v>467</v>
+        <v>609</v>
       </c>
     </row>
     <row r="1073" spans="1:16">
       <c r="A1073" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1073" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C1073">
-        <v>-2.807532631974992</v>
+        <v>-2.496660757698539</v>
       </c>
       <c r="D1073" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="E1073">
-        <v>-2.509249826348689</v>
+        <v>-2.672763877633709</v>
       </c>
       <c r="F1073">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1073">
-        <v>0.01758753263197499</v>
+        <v>0.01781666075769854</v>
       </c>
       <c r="H1073">
-        <v>0.01710924982634869</v>
+        <v>0.01821276387763371</v>
       </c>
       <c r="I1073">
-        <v>0.2982828056263038</v>
+        <v>0.1761031199351706</v>
       </c>
       <c r="J1073">
         <v>2.043593713822644</v>
       </c>
       <c r="K1073">
-        <v>4.99</v>
+        <v>4.97</v>
       </c>
       <c r="L1073">
-        <v>7.39</v>
+        <v>7.66</v>
       </c>
       <c r="M1073">
-        <v>4.8</v>
+        <v>5.11</v>
       </c>
       <c r="N1073">
-        <v>7.3</v>
+        <v>7.77</v>
       </c>
       <c r="O1073">
         <v>1</v>
       </c>
       <c r="P1073" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="1074" spans="1:16">
       <c r="A1074" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1074" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C1074">
-        <v>-2.496660757698539</v>
+        <v>-2.793635751910162</v>
       </c>
       <c r="D1074" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E1074">
-        <v>-2.672763877633709</v>
+        <v>-2.627096694836767</v>
       </c>
       <c r="F1074">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1074">
-        <v>0.01781666075769854</v>
+        <v>0.01817363575191016</v>
       </c>
       <c r="H1074">
-        <v>0.01821276387763371</v>
+        <v>0.01772709669483677</v>
       </c>
       <c r="I1074">
-        <v>0.1761031199351706</v>
+        <v>0.1665390570733951</v>
       </c>
       <c r="J1074">
         <v>2.043593713822644</v>
       </c>
       <c r="K1074">
-        <v>4.97</v>
+        <v>5.13</v>
       </c>
       <c r="L1074">
-        <v>7.66</v>
+        <v>7.69</v>
       </c>
       <c r="M1074">
-        <v>5.11</v>
+        <v>4.98</v>
       </c>
       <c r="N1074">
-        <v>7.77</v>
+        <v>7.55</v>
       </c>
       <c r="O1074">
         <v>1</v>
       </c>
       <c r="P1074" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="1075" spans="1:16">
-      <c r="A1075" s="1">
-        <v>2</v>
-      </c>
-      <c r="B1075" t="s">
-        <v>296</v>
-      </c>
-      <c r="C1075">
-        <v>-2.793635751910162</v>
-      </c>
-      <c r="D1075" t="s">
-        <v>473</v>
-      </c>
-      <c r="E1075">
-        <v>-2.627096694836767</v>
-      </c>
-      <c r="F1075">
-        <v>1</v>
-      </c>
-      <c r="G1075">
-        <v>0.01817363575191016</v>
-      </c>
-      <c r="H1075">
-        <v>0.01772709669483677</v>
-      </c>
-      <c r="I1075">
-        <v>0.1665390570733951</v>
-      </c>
-      <c r="J1075">
-        <v>2.043593713822644</v>
-      </c>
-      <c r="K1075">
-        <v>5.13</v>
-      </c>
-      <c r="L1075">
-        <v>7.69</v>
-      </c>
-      <c r="M1075">
-        <v>4.98</v>
-      </c>
-      <c r="N1075">
-        <v>7.55</v>
-      </c>
-      <c r="O1075">
-        <v>1</v>
-      </c>
-      <c r="P1075" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-01186-601186.xlsx
+++ b/s60_signal/position-01186-601186.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3243" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3261" uniqueCount="610">
   <si>
     <t>trade_time</t>
   </si>
@@ -895,544 +895,550 @@
     <t>2021-12-02</t>
   </si>
   <si>
+    <t>2021-12-20</t>
+  </si>
+  <si>
+    <t>2021-11-24</t>
+  </si>
+  <si>
+    <t>2021-11-30</t>
+  </si>
+  <si>
+    <t>2021-12-09</t>
+  </si>
+  <si>
+    <t>2021-12-13</t>
+  </si>
+  <si>
+    <t>2016-04-28</t>
+  </si>
+  <si>
+    <t>2016-07-05</t>
+  </si>
+  <si>
+    <t>2016-04-21</t>
+  </si>
+  <si>
+    <t>2016-07-26</t>
+  </si>
+  <si>
+    <t>2016-05-17</t>
+  </si>
+  <si>
+    <t>2016-08-24</t>
+  </si>
+  <si>
+    <t>2016-09-29</t>
+  </si>
+  <si>
+    <t>2016-09-30</t>
+  </si>
+  <si>
+    <t>2016-10-12</t>
+  </si>
+  <si>
+    <t>2016-08-19</t>
+  </si>
+  <si>
+    <t>2016-10-25</t>
+  </si>
+  <si>
+    <t>2016-11-07</t>
+  </si>
+  <si>
+    <t>2016-11-10</t>
+  </si>
+  <si>
+    <t>2016-11-11</t>
+  </si>
+  <si>
+    <t>2016-11-16</t>
+  </si>
+  <si>
+    <t>2016-11-18</t>
+  </si>
+  <si>
+    <t>2016-10-13</t>
+  </si>
+  <si>
+    <t>2016-11-23</t>
+  </si>
+  <si>
+    <t>2016-09-14</t>
+  </si>
+  <si>
+    <t>2016-11-24</t>
+  </si>
+  <si>
+    <t>2016-11-29</t>
+  </si>
+  <si>
+    <t>2016-11-30</t>
+  </si>
+  <si>
+    <t>2016-12-14</t>
+  </si>
+  <si>
+    <t>2017-02-22</t>
+  </si>
+  <si>
+    <t>2017-01-12</t>
+  </si>
+  <si>
+    <t>2017-03-01</t>
+  </si>
+  <si>
+    <t>2016-12-06</t>
+  </si>
+  <si>
+    <t>2017-01-11</t>
+  </si>
+  <si>
+    <t>2017-03-06</t>
+  </si>
+  <si>
+    <t>2017-03-20</t>
+  </si>
+  <si>
+    <t>2017-03-21</t>
+  </si>
+  <si>
+    <t>2017-03-22</t>
+  </si>
+  <si>
+    <t>2017-03-23</t>
+  </si>
+  <si>
+    <t>2017-03-24</t>
+  </si>
+  <si>
+    <t>2016-12-09</t>
+  </si>
+  <si>
+    <t>2017-05-10</t>
+  </si>
+  <si>
+    <t>2017-06-01</t>
+  </si>
+  <si>
+    <t>2017-06-02</t>
+  </si>
+  <si>
+    <t>2017-06-05</t>
+  </si>
+  <si>
+    <t>2017-06-09</t>
+  </si>
+  <si>
+    <t>2017-03-27</t>
+  </si>
+  <si>
+    <t>2017-04-26</t>
+  </si>
+  <si>
+    <t>2017-07-14</t>
+  </si>
+  <si>
+    <t>2017-10-27</t>
+  </si>
+  <si>
+    <t>2017-10-30</t>
+  </si>
+  <si>
+    <t>2017-10-31</t>
+  </si>
+  <si>
+    <t>2017-11-01</t>
+  </si>
+  <si>
+    <t>2017-08-17</t>
+  </si>
+  <si>
+    <t>2017-08-02</t>
+  </si>
+  <si>
+    <t>2017-11-20</t>
+  </si>
+  <si>
+    <t>2017-11-21</t>
+  </si>
+  <si>
+    <t>2017-08-18</t>
+  </si>
+  <si>
+    <t>2017-09-06</t>
+  </si>
+  <si>
+    <t>2017-11-22</t>
+  </si>
+  <si>
+    <t>2017-11-23</t>
+  </si>
+  <si>
+    <t>2017-11-24</t>
+  </si>
+  <si>
+    <t>2017-11-28</t>
+  </si>
+  <si>
+    <t>2017-09-07</t>
+  </si>
+  <si>
+    <t>2017-11-30</t>
+  </si>
+  <si>
+    <t>2017-09-18</t>
+  </si>
+  <si>
+    <t>2017-12-06</t>
+  </si>
+  <si>
+    <t>2017-12-07</t>
+  </si>
+  <si>
+    <t>2017-12-08</t>
+  </si>
+  <si>
+    <t>2017-12-11</t>
+  </si>
+  <si>
+    <t>2017-12-12</t>
+  </si>
+  <si>
+    <t>2017-11-13</t>
+  </si>
+  <si>
+    <t>2017-12-15</t>
+  </si>
+  <si>
+    <t>2017-12-21</t>
+  </si>
+  <si>
+    <t>2018-02-09</t>
+  </si>
+  <si>
+    <t>2018-04-26</t>
+  </si>
+  <si>
+    <t>2018-04-27</t>
+  </si>
+  <si>
+    <t>2018-05-02</t>
+  </si>
+  <si>
+    <t>2018-05-03</t>
+  </si>
+  <si>
+    <t>2018-06-26</t>
+  </si>
+  <si>
+    <t>2018-07-24</t>
+  </si>
+  <si>
+    <t>2018-08-02</t>
+  </si>
+  <si>
+    <t>2018-06-25</t>
+  </si>
+  <si>
+    <t>2018-09-27</t>
+  </si>
+  <si>
+    <t>2018-10-08</t>
+  </si>
+  <si>
+    <t>2018-10-16</t>
+  </si>
+  <si>
+    <t>2018-07-23</t>
+  </si>
+  <si>
+    <t>2018-09-05</t>
+  </si>
+  <si>
+    <t>2018-10-22</t>
+  </si>
+  <si>
+    <t>2018-12-12</t>
+  </si>
+  <si>
+    <t>2018-11-02</t>
+  </si>
+  <si>
+    <t>2018-11-26</t>
+  </si>
+  <si>
+    <t>2018-12-20</t>
+  </si>
+  <si>
+    <t>2019-01-11</t>
+  </si>
+  <si>
+    <t>2018-11-06</t>
+  </si>
+  <si>
+    <t>2019-01-15</t>
+  </si>
+  <si>
+    <t>2018-12-27</t>
+  </si>
+  <si>
+    <t>2019-03-01</t>
+  </si>
+  <si>
+    <t>2019-02-28</t>
+  </si>
+  <si>
+    <t>2019-02-26</t>
+  </si>
+  <si>
+    <t>2019-04-15</t>
+  </si>
+  <si>
+    <t>2019-04-26</t>
+  </si>
+  <si>
+    <t>2019-06-19</t>
+  </si>
+  <si>
+    <t>2019-05-06</t>
+  </si>
+  <si>
+    <t>2019-07-03</t>
+  </si>
+  <si>
+    <t>2019-03-27</t>
+  </si>
+  <si>
+    <t>2019-05-08</t>
+  </si>
+  <si>
+    <t>2019-07-05</t>
+  </si>
+  <si>
+    <t>2019-05-15</t>
+  </si>
+  <si>
+    <t>2019-07-04</t>
+  </si>
+  <si>
+    <t>2019-09-23</t>
+  </si>
+  <si>
+    <t>2019-09-04</t>
+  </si>
+  <si>
+    <t>2019-09-27</t>
+  </si>
+  <si>
+    <t>2019-12-17</t>
+  </si>
+  <si>
+    <t>2019-12-18</t>
+  </si>
+  <si>
+    <t>2019-10-15</t>
+  </si>
+  <si>
+    <t>2019-12-20</t>
+  </si>
+  <si>
+    <t>2019-11-13</t>
+  </si>
+  <si>
+    <t>2019-12-23</t>
+  </si>
+  <si>
+    <t>2019-11-14</t>
+  </si>
+  <si>
+    <t>2020-01-15</t>
+  </si>
+  <si>
+    <t>2020-02-24</t>
+  </si>
+  <si>
+    <t>2020-02-25</t>
+  </si>
+  <si>
+    <t>2020-02-26</t>
+  </si>
+  <si>
+    <t>2020-02-28</t>
+  </si>
+  <si>
+    <t>2020-03-02</t>
+  </si>
+  <si>
+    <t>2020-01-23</t>
+  </si>
+  <si>
+    <t>2020-03-06</t>
+  </si>
+  <si>
+    <t>2020-03-09</t>
+  </si>
+  <si>
+    <t>2020-03-11</t>
+  </si>
+  <si>
+    <t>2020-03-12</t>
+  </si>
+  <si>
+    <t>2020-03-13</t>
+  </si>
+  <si>
+    <t>2020-03-16</t>
+  </si>
+  <si>
+    <t>2020-03-17</t>
+  </si>
+  <si>
+    <t>2020-03-18</t>
+  </si>
+  <si>
+    <t>2020-03-20</t>
+  </si>
+  <si>
+    <t>2020-03-23</t>
+  </si>
+  <si>
+    <t>2020-03-24</t>
+  </si>
+  <si>
+    <t>2020-03-25</t>
+  </si>
+  <si>
+    <t>2020-03-26</t>
+  </si>
+  <si>
+    <t>2020-07-02</t>
+  </si>
+  <si>
+    <t>2020-08-19</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>2020-08-21</t>
+  </si>
+  <si>
+    <t>2020-08-24</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>2020-08-26</t>
+  </si>
+  <si>
+    <t>2020-09-02</t>
+  </si>
+  <si>
+    <t>2020-09-25</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>2020-12-21</t>
+  </si>
+  <si>
+    <t>2020-12-22</t>
+  </si>
+  <si>
+    <t>2020-12-23</t>
+  </si>
+  <si>
+    <t>2020-10-12</t>
+  </si>
+  <si>
+    <t>2020-12-28</t>
+  </si>
+  <si>
+    <t>2020-12-30</t>
+  </si>
+  <si>
+    <t>2021-01-04</t>
+  </si>
+  <si>
+    <t>2021-01-18</t>
+  </si>
+  <si>
+    <t>2021-02-18</t>
+  </si>
+  <si>
+    <t>2021-01-11</t>
+  </si>
+  <si>
+    <t>2021-01-19</t>
+  </si>
+  <si>
+    <t>2021-03-01</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>2021-03-04</t>
+  </si>
+  <si>
+    <t>2021-03-17</t>
+  </si>
+  <si>
+    <t>2021-02-19</t>
+  </si>
+  <si>
+    <t>2021-04-21</t>
+  </si>
+  <si>
+    <t>2021-05-17</t>
+  </si>
+  <si>
+    <t>2021-05-24</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>2021-07-26</t>
+  </si>
+  <si>
+    <t>2021-07-27</t>
+  </si>
+  <si>
+    <t>2021-08-04</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>2021-09-09</t>
+  </si>
+  <si>
+    <t>2021-09-23</t>
+  </si>
+  <si>
     <t>2021-10-15</t>
   </si>
   <si>
-    <t>2021-11-24</t>
-  </si>
-  <si>
-    <t>2021-11-30</t>
-  </si>
-  <si>
-    <t>2021-12-09</t>
-  </si>
-  <si>
-    <t>2021-12-13</t>
-  </si>
-  <si>
-    <t>2016-04-28</t>
-  </si>
-  <si>
-    <t>2016-07-05</t>
-  </si>
-  <si>
-    <t>2016-04-21</t>
-  </si>
-  <si>
-    <t>2016-07-26</t>
-  </si>
-  <si>
-    <t>2016-05-17</t>
-  </si>
-  <si>
-    <t>2016-08-24</t>
-  </si>
-  <si>
-    <t>2016-09-29</t>
-  </si>
-  <si>
-    <t>2016-09-30</t>
-  </si>
-  <si>
-    <t>2016-10-12</t>
-  </si>
-  <si>
-    <t>2016-08-19</t>
-  </si>
-  <si>
-    <t>2016-10-25</t>
-  </si>
-  <si>
-    <t>2016-11-07</t>
-  </si>
-  <si>
-    <t>2016-11-10</t>
-  </si>
-  <si>
-    <t>2016-11-11</t>
-  </si>
-  <si>
-    <t>2016-11-16</t>
-  </si>
-  <si>
-    <t>2016-11-18</t>
-  </si>
-  <si>
-    <t>2016-10-13</t>
-  </si>
-  <si>
-    <t>2016-11-23</t>
-  </si>
-  <si>
-    <t>2016-09-14</t>
-  </si>
-  <si>
-    <t>2016-11-24</t>
-  </si>
-  <si>
-    <t>2016-11-29</t>
-  </si>
-  <si>
-    <t>2016-11-30</t>
-  </si>
-  <si>
-    <t>2016-12-14</t>
-  </si>
-  <si>
-    <t>2017-02-22</t>
-  </si>
-  <si>
-    <t>2017-01-12</t>
-  </si>
-  <si>
-    <t>2017-03-01</t>
-  </si>
-  <si>
-    <t>2016-12-06</t>
-  </si>
-  <si>
-    <t>2017-01-11</t>
-  </si>
-  <si>
-    <t>2017-03-06</t>
-  </si>
-  <si>
-    <t>2017-03-20</t>
-  </si>
-  <si>
-    <t>2017-03-21</t>
-  </si>
-  <si>
-    <t>2017-03-22</t>
-  </si>
-  <si>
-    <t>2017-03-23</t>
-  </si>
-  <si>
-    <t>2017-03-24</t>
-  </si>
-  <si>
-    <t>2016-12-09</t>
-  </si>
-  <si>
-    <t>2017-05-10</t>
-  </si>
-  <si>
-    <t>2017-06-01</t>
-  </si>
-  <si>
-    <t>2017-06-02</t>
-  </si>
-  <si>
-    <t>2017-06-05</t>
-  </si>
-  <si>
-    <t>2017-06-09</t>
-  </si>
-  <si>
-    <t>2017-03-27</t>
-  </si>
-  <si>
-    <t>2017-04-26</t>
-  </si>
-  <si>
-    <t>2017-07-14</t>
-  </si>
-  <si>
-    <t>2017-10-27</t>
-  </si>
-  <si>
-    <t>2017-10-30</t>
-  </si>
-  <si>
-    <t>2017-10-31</t>
-  </si>
-  <si>
-    <t>2017-11-01</t>
-  </si>
-  <si>
-    <t>2017-08-17</t>
-  </si>
-  <si>
-    <t>2017-08-02</t>
-  </si>
-  <si>
-    <t>2017-11-20</t>
-  </si>
-  <si>
-    <t>2017-11-21</t>
-  </si>
-  <si>
-    <t>2017-08-18</t>
-  </si>
-  <si>
-    <t>2017-09-06</t>
-  </si>
-  <si>
-    <t>2017-11-22</t>
-  </si>
-  <si>
-    <t>2017-11-23</t>
-  </si>
-  <si>
-    <t>2017-11-24</t>
-  </si>
-  <si>
-    <t>2017-11-28</t>
-  </si>
-  <si>
-    <t>2017-09-07</t>
-  </si>
-  <si>
-    <t>2017-11-30</t>
-  </si>
-  <si>
-    <t>2017-09-18</t>
-  </si>
-  <si>
-    <t>2017-12-06</t>
-  </si>
-  <si>
-    <t>2017-12-07</t>
-  </si>
-  <si>
-    <t>2017-12-08</t>
-  </si>
-  <si>
-    <t>2017-12-11</t>
-  </si>
-  <si>
-    <t>2017-12-12</t>
-  </si>
-  <si>
-    <t>2017-11-13</t>
-  </si>
-  <si>
-    <t>2017-12-15</t>
-  </si>
-  <si>
-    <t>2017-12-21</t>
-  </si>
-  <si>
-    <t>2018-02-09</t>
-  </si>
-  <si>
-    <t>2018-04-26</t>
-  </si>
-  <si>
-    <t>2018-04-27</t>
-  </si>
-  <si>
-    <t>2018-05-02</t>
-  </si>
-  <si>
-    <t>2018-05-03</t>
-  </si>
-  <si>
-    <t>2018-06-26</t>
-  </si>
-  <si>
-    <t>2018-07-24</t>
-  </si>
-  <si>
-    <t>2018-08-02</t>
-  </si>
-  <si>
-    <t>2018-06-25</t>
-  </si>
-  <si>
-    <t>2018-09-27</t>
-  </si>
-  <si>
-    <t>2018-10-08</t>
-  </si>
-  <si>
-    <t>2018-10-16</t>
-  </si>
-  <si>
-    <t>2018-07-23</t>
-  </si>
-  <si>
-    <t>2018-09-05</t>
-  </si>
-  <si>
-    <t>2018-10-22</t>
-  </si>
-  <si>
-    <t>2018-12-12</t>
-  </si>
-  <si>
-    <t>2018-11-02</t>
-  </si>
-  <si>
-    <t>2018-11-26</t>
-  </si>
-  <si>
-    <t>2018-12-20</t>
-  </si>
-  <si>
-    <t>2019-01-11</t>
-  </si>
-  <si>
-    <t>2018-11-06</t>
-  </si>
-  <si>
-    <t>2019-01-15</t>
-  </si>
-  <si>
-    <t>2018-12-27</t>
-  </si>
-  <si>
-    <t>2019-03-01</t>
-  </si>
-  <si>
-    <t>2019-02-28</t>
-  </si>
-  <si>
-    <t>2019-02-26</t>
-  </si>
-  <si>
-    <t>2019-04-15</t>
-  </si>
-  <si>
-    <t>2019-04-26</t>
-  </si>
-  <si>
-    <t>2019-06-19</t>
-  </si>
-  <si>
-    <t>2019-05-06</t>
-  </si>
-  <si>
-    <t>2019-07-03</t>
-  </si>
-  <si>
-    <t>2019-03-27</t>
-  </si>
-  <si>
-    <t>2019-05-08</t>
-  </si>
-  <si>
-    <t>2019-07-05</t>
-  </si>
-  <si>
-    <t>2019-05-15</t>
-  </si>
-  <si>
-    <t>2019-07-04</t>
-  </si>
-  <si>
-    <t>2019-09-23</t>
-  </si>
-  <si>
-    <t>2019-09-04</t>
-  </si>
-  <si>
-    <t>2019-09-27</t>
-  </si>
-  <si>
-    <t>2019-12-17</t>
-  </si>
-  <si>
-    <t>2019-12-18</t>
-  </si>
-  <si>
-    <t>2019-10-15</t>
-  </si>
-  <si>
-    <t>2019-12-20</t>
-  </si>
-  <si>
-    <t>2019-11-13</t>
-  </si>
-  <si>
-    <t>2019-12-23</t>
-  </si>
-  <si>
-    <t>2019-11-14</t>
-  </si>
-  <si>
-    <t>2020-01-15</t>
-  </si>
-  <si>
-    <t>2020-02-24</t>
-  </si>
-  <si>
-    <t>2020-02-25</t>
-  </si>
-  <si>
-    <t>2020-02-26</t>
-  </si>
-  <si>
-    <t>2020-02-28</t>
-  </si>
-  <si>
-    <t>2020-03-02</t>
-  </si>
-  <si>
-    <t>2020-01-23</t>
-  </si>
-  <si>
-    <t>2020-03-06</t>
-  </si>
-  <si>
-    <t>2020-03-09</t>
-  </si>
-  <si>
-    <t>2020-03-11</t>
-  </si>
-  <si>
-    <t>2020-03-12</t>
-  </si>
-  <si>
-    <t>2020-03-13</t>
-  </si>
-  <si>
-    <t>2020-03-16</t>
-  </si>
-  <si>
-    <t>2020-03-17</t>
-  </si>
-  <si>
-    <t>2020-03-18</t>
-  </si>
-  <si>
-    <t>2020-03-20</t>
-  </si>
-  <si>
-    <t>2020-03-23</t>
-  </si>
-  <si>
-    <t>2020-03-24</t>
-  </si>
-  <si>
-    <t>2020-03-25</t>
-  </si>
-  <si>
-    <t>2020-03-26</t>
-  </si>
-  <si>
-    <t>2020-07-02</t>
-  </si>
-  <si>
-    <t>2020-08-19</t>
-  </si>
-  <si>
-    <t>2020-08-20</t>
-  </si>
-  <si>
-    <t>2020-08-21</t>
-  </si>
-  <si>
-    <t>2020-08-24</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>2020-08-26</t>
-  </si>
-  <si>
-    <t>2020-09-02</t>
-  </si>
-  <si>
-    <t>2020-09-25</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>2020-12-21</t>
-  </si>
-  <si>
-    <t>2020-12-22</t>
-  </si>
-  <si>
-    <t>2020-12-23</t>
-  </si>
-  <si>
-    <t>2020-10-12</t>
-  </si>
-  <si>
-    <t>2020-12-28</t>
-  </si>
-  <si>
-    <t>2020-12-30</t>
-  </si>
-  <si>
-    <t>2021-01-04</t>
-  </si>
-  <si>
-    <t>2021-01-18</t>
-  </si>
-  <si>
-    <t>2021-02-18</t>
-  </si>
-  <si>
-    <t>2021-01-11</t>
-  </si>
-  <si>
-    <t>2021-01-19</t>
-  </si>
-  <si>
-    <t>2021-03-01</t>
-  </si>
-  <si>
-    <t>2021-03-03</t>
-  </si>
-  <si>
-    <t>2021-03-04</t>
-  </si>
-  <si>
-    <t>2021-03-17</t>
-  </si>
-  <si>
-    <t>2021-02-19</t>
-  </si>
-  <si>
-    <t>2021-04-21</t>
-  </si>
-  <si>
-    <t>2021-05-17</t>
-  </si>
-  <si>
-    <t>2021-05-24</t>
-  </si>
-  <si>
-    <t>2021-05-06</t>
-  </si>
-  <si>
-    <t>2021-07-26</t>
-  </si>
-  <si>
-    <t>2021-07-27</t>
-  </si>
-  <si>
-    <t>2021-08-04</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>2021-09-09</t>
-  </si>
-  <si>
-    <t>2021-09-23</t>
-  </si>
-  <si>
     <t>2021-11-29</t>
   </si>
   <si>
-    <t>2021-11-22</t>
+    <t>2021-12-29</t>
   </si>
   <si>
     <t>2021-12-08</t>
   </si>
   <si>
     <t>2021-12-15</t>
+  </si>
+  <si>
+    <t>2021-12-28</t>
   </si>
   <si>
     <t>2016-03-24</t>
@@ -2195,7 +2201,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1077"/>
+  <dimension ref="A1:P1083"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2292,7 +2298,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2342,7 +2348,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2392,7 +2398,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2442,7 +2448,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -2492,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -2542,7 +2548,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -2592,7 +2598,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2642,7 +2648,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2692,7 +2698,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2742,7 +2748,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2792,7 +